--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,583 +31,583 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>24.02.20261</t>
-  </si>
-  <si>
-    <t>25.02.20262</t>
-  </si>
-  <si>
-    <t>25.02.20263</t>
-  </si>
-  <si>
-    <t>25.02.20264</t>
-  </si>
-  <si>
-    <t>25.02.20265</t>
-  </si>
-  <si>
-    <t>25.02.20266</t>
-  </si>
-  <si>
-    <t>25.02.20267</t>
-  </si>
-  <si>
-    <t>25.02.20268</t>
-  </si>
-  <si>
-    <t>25.02.20269</t>
-  </si>
-  <si>
-    <t>25.02.202610</t>
-  </si>
-  <si>
-    <t>25.02.202611</t>
-  </si>
-  <si>
-    <t>25.02.202612</t>
-  </si>
-  <si>
-    <t>25.02.202613</t>
-  </si>
-  <si>
-    <t>25.02.202614</t>
-  </si>
-  <si>
-    <t>25.02.202615</t>
-  </si>
-  <si>
-    <t>25.02.202616</t>
-  </si>
-  <si>
-    <t>25.02.202617</t>
-  </si>
-  <si>
-    <t>25.02.202618</t>
-  </si>
-  <si>
-    <t>25.02.202619</t>
-  </si>
-  <si>
-    <t>25.02.202620</t>
-  </si>
-  <si>
-    <t>25.02.202621</t>
-  </si>
-  <si>
-    <t>25.02.202622</t>
-  </si>
-  <si>
-    <t>25.02.202623</t>
-  </si>
-  <si>
-    <t>25.02.202624</t>
-  </si>
-  <si>
-    <t>25.02.202625</t>
-  </si>
-  <si>
-    <t>25.02.202626</t>
-  </si>
-  <si>
-    <t>25.02.202627</t>
-  </si>
-  <si>
-    <t>25.02.202628</t>
-  </si>
-  <si>
-    <t>25.02.202629</t>
-  </si>
-  <si>
-    <t>25.02.202630</t>
-  </si>
-  <si>
-    <t>25.02.202631</t>
-  </si>
-  <si>
-    <t>25.02.202632</t>
-  </si>
-  <si>
-    <t>25.02.202633</t>
-  </si>
-  <si>
-    <t>25.02.202634</t>
-  </si>
-  <si>
-    <t>25.02.202635</t>
-  </si>
-  <si>
-    <t>25.02.202636</t>
-  </si>
-  <si>
-    <t>25.02.202637</t>
-  </si>
-  <si>
-    <t>25.02.202638</t>
-  </si>
-  <si>
-    <t>25.02.202639</t>
-  </si>
-  <si>
-    <t>25.02.202640</t>
-  </si>
-  <si>
-    <t>25.02.202641</t>
-  </si>
-  <si>
-    <t>25.02.202642</t>
-  </si>
-  <si>
-    <t>25.02.202643</t>
-  </si>
-  <si>
-    <t>25.02.202644</t>
-  </si>
-  <si>
-    <t>25.02.202645</t>
-  </si>
-  <si>
-    <t>25.02.202646</t>
-  </si>
-  <si>
-    <t>25.02.202647</t>
-  </si>
-  <si>
-    <t>25.02.202648</t>
-  </si>
-  <si>
-    <t>25.02.202649</t>
-  </si>
-  <si>
-    <t>25.02.202650</t>
-  </si>
-  <si>
-    <t>25.02.202651</t>
-  </si>
-  <si>
-    <t>25.02.202652</t>
-  </si>
-  <si>
-    <t>25.02.202653</t>
-  </si>
-  <si>
-    <t>25.02.202654</t>
-  </si>
-  <si>
-    <t>25.02.202655</t>
-  </si>
-  <si>
-    <t>25.02.202656</t>
-  </si>
-  <si>
-    <t>25.02.202657</t>
-  </si>
-  <si>
-    <t>25.02.202658</t>
-  </si>
-  <si>
-    <t>25.02.202659</t>
-  </si>
-  <si>
-    <t>25.02.202660</t>
-  </si>
-  <si>
-    <t>25.02.202661</t>
-  </si>
-  <si>
-    <t>25.02.202662</t>
-  </si>
-  <si>
-    <t>25.02.202663</t>
-  </si>
-  <si>
-    <t>25.02.202664</t>
-  </si>
-  <si>
-    <t>25.02.202665</t>
-  </si>
-  <si>
-    <t>25.02.202666</t>
-  </si>
-  <si>
-    <t>25.02.202667</t>
-  </si>
-  <si>
-    <t>25.02.202668</t>
-  </si>
-  <si>
-    <t>25.02.202669</t>
-  </si>
-  <si>
-    <t>25.02.202670</t>
-  </si>
-  <si>
-    <t>25.02.202671</t>
-  </si>
-  <si>
-    <t>25.02.202672</t>
-  </si>
-  <si>
-    <t>25.02.202673</t>
-  </si>
-  <si>
-    <t>25.02.202674</t>
-  </si>
-  <si>
-    <t>25.02.202675</t>
-  </si>
-  <si>
-    <t>25.02.202676</t>
-  </si>
-  <si>
-    <t>25.02.202677</t>
-  </si>
-  <si>
-    <t>25.02.202678</t>
-  </si>
-  <si>
-    <t>25.02.202679</t>
-  </si>
-  <si>
-    <t>25.02.202680</t>
-  </si>
-  <si>
-    <t>25.02.202681</t>
-  </si>
-  <si>
-    <t>25.02.202682</t>
-  </si>
-  <si>
-    <t>25.02.202683</t>
-  </si>
-  <si>
-    <t>25.02.202684</t>
-  </si>
-  <si>
-    <t>25.02.202685</t>
-  </si>
-  <si>
-    <t>25.02.202686</t>
-  </si>
-  <si>
-    <t>25.02.202687</t>
-  </si>
-  <si>
-    <t>25.02.202688</t>
-  </si>
-  <si>
-    <t>25.02.202689</t>
-  </si>
-  <si>
-    <t>25.02.202690</t>
-  </si>
-  <si>
-    <t>25.02.202691</t>
-  </si>
-  <si>
-    <t>25.02.202692</t>
-  </si>
-  <si>
-    <t>25.02.202693</t>
-  </si>
-  <si>
-    <t>25.02.202694</t>
-  </si>
-  <si>
-    <t>25.02.202695</t>
-  </si>
-  <si>
-    <t>25.02.202696</t>
-  </si>
-  <si>
-    <t>25.02.20261</t>
-  </si>
-  <si>
-    <t>26.02.20263</t>
-  </si>
-  <si>
-    <t>26.02.20264</t>
-  </si>
-  <si>
-    <t>26.02.20265</t>
-  </si>
-  <si>
-    <t>26.02.20266</t>
-  </si>
-  <si>
-    <t>26.02.20267</t>
-  </si>
-  <si>
-    <t>26.02.20268</t>
-  </si>
-  <si>
-    <t>26.02.20269</t>
-  </si>
-  <si>
-    <t>26.02.202610</t>
-  </si>
-  <si>
-    <t>26.02.202611</t>
-  </si>
-  <si>
-    <t>26.02.202612</t>
-  </si>
-  <si>
-    <t>26.02.202613</t>
-  </si>
-  <si>
-    <t>26.02.202614</t>
-  </si>
-  <si>
-    <t>26.02.202615</t>
-  </si>
-  <si>
-    <t>26.02.202616</t>
-  </si>
-  <si>
-    <t>26.02.202617</t>
-  </si>
-  <si>
-    <t>26.02.202618</t>
-  </si>
-  <si>
-    <t>26.02.202619</t>
-  </si>
-  <si>
-    <t>26.02.202620</t>
-  </si>
-  <si>
-    <t>26.02.202621</t>
-  </si>
-  <si>
-    <t>26.02.202622</t>
-  </si>
-  <si>
-    <t>26.02.202623</t>
-  </si>
-  <si>
-    <t>26.02.202624</t>
-  </si>
-  <si>
-    <t>26.02.202625</t>
-  </si>
-  <si>
-    <t>26.02.202626</t>
-  </si>
-  <si>
-    <t>26.02.202627</t>
-  </si>
-  <si>
-    <t>26.02.202628</t>
-  </si>
-  <si>
-    <t>26.02.202629</t>
-  </si>
-  <si>
-    <t>26.02.202630</t>
-  </si>
-  <si>
-    <t>26.02.202631</t>
-  </si>
-  <si>
-    <t>26.02.202632</t>
-  </si>
-  <si>
-    <t>26.02.202633</t>
-  </si>
-  <si>
-    <t>26.02.202634</t>
-  </si>
-  <si>
-    <t>26.02.202635</t>
-  </si>
-  <si>
-    <t>26.02.202636</t>
-  </si>
-  <si>
-    <t>26.02.202637</t>
-  </si>
-  <si>
-    <t>26.02.202638</t>
-  </si>
-  <si>
-    <t>26.02.202639</t>
-  </si>
-  <si>
-    <t>26.02.202640</t>
-  </si>
-  <si>
-    <t>26.02.202641</t>
-  </si>
-  <si>
-    <t>26.02.202642</t>
-  </si>
-  <si>
-    <t>26.02.202643</t>
-  </si>
-  <si>
-    <t>26.02.202644</t>
-  </si>
-  <si>
-    <t>26.02.202645</t>
-  </si>
-  <si>
-    <t>26.02.202646</t>
-  </si>
-  <si>
-    <t>26.02.202647</t>
-  </si>
-  <si>
-    <t>26.02.202648</t>
-  </si>
-  <si>
-    <t>26.02.202649</t>
-  </si>
-  <si>
-    <t>26.02.202650</t>
-  </si>
-  <si>
-    <t>26.02.202651</t>
-  </si>
-  <si>
-    <t>26.02.202652</t>
-  </si>
-  <si>
-    <t>26.02.202653</t>
-  </si>
-  <si>
-    <t>26.02.202654</t>
-  </si>
-  <si>
-    <t>26.02.202655</t>
-  </si>
-  <si>
-    <t>26.02.202656</t>
-  </si>
-  <si>
-    <t>26.02.202657</t>
-  </si>
-  <si>
-    <t>26.02.202658</t>
-  </si>
-  <si>
-    <t>26.02.202659</t>
-  </si>
-  <si>
-    <t>26.02.202660</t>
-  </si>
-  <si>
-    <t>26.02.202661</t>
-  </si>
-  <si>
-    <t>26.02.202662</t>
-  </si>
-  <si>
-    <t>26.02.202663</t>
-  </si>
-  <si>
-    <t>26.02.202664</t>
-  </si>
-  <si>
-    <t>26.02.202665</t>
-  </si>
-  <si>
-    <t>26.02.202666</t>
-  </si>
-  <si>
-    <t>26.02.202667</t>
-  </si>
-  <si>
-    <t>26.02.202668</t>
-  </si>
-  <si>
-    <t>26.02.202669</t>
-  </si>
-  <si>
-    <t>26.02.202670</t>
-  </si>
-  <si>
-    <t>26.02.202671</t>
-  </si>
-  <si>
-    <t>26.02.202672</t>
-  </si>
-  <si>
-    <t>26.02.202673</t>
-  </si>
-  <si>
-    <t>26.02.202674</t>
-  </si>
-  <si>
-    <t>26.02.202675</t>
-  </si>
-  <si>
-    <t>26.02.202676</t>
-  </si>
-  <si>
-    <t>26.02.202677</t>
-  </si>
-  <si>
-    <t>26.02.202678</t>
-  </si>
-  <si>
-    <t>26.02.202679</t>
-  </si>
-  <si>
-    <t>26.02.202680</t>
-  </si>
-  <si>
-    <t>26.02.202681</t>
-  </si>
-  <si>
-    <t>26.02.202682</t>
-  </si>
-  <si>
-    <t>26.02.202683</t>
-  </si>
-  <si>
-    <t>26.02.202684</t>
-  </si>
-  <si>
-    <t>26.02.202685</t>
-  </si>
-  <si>
-    <t>26.02.202686</t>
-  </si>
-  <si>
-    <t>26.02.202687</t>
-  </si>
-  <si>
-    <t>26.02.202688</t>
-  </si>
-  <si>
-    <t>26.02.202689</t>
-  </si>
-  <si>
-    <t>26.02.202690</t>
-  </si>
-  <si>
-    <t>26.02.202691</t>
-  </si>
-  <si>
-    <t>26.02.202692</t>
-  </si>
-  <si>
-    <t>26.02.202693</t>
-  </si>
-  <si>
-    <t>26.02.202694</t>
-  </si>
-  <si>
-    <t>26.02.202695</t>
-  </si>
-  <si>
-    <t>26.02.202696</t>
-  </si>
-  <si>
-    <t>26.02.20261</t>
-  </si>
-  <si>
-    <t>26.02.20262</t>
+    <t>11.03.20261</t>
+  </si>
+  <si>
+    <t>12.03.20262</t>
+  </si>
+  <si>
+    <t>12.03.20263</t>
+  </si>
+  <si>
+    <t>12.03.20264</t>
+  </si>
+  <si>
+    <t>12.03.20265</t>
+  </si>
+  <si>
+    <t>12.03.20266</t>
+  </si>
+  <si>
+    <t>12.03.20267</t>
+  </si>
+  <si>
+    <t>12.03.20268</t>
+  </si>
+  <si>
+    <t>12.03.20269</t>
+  </si>
+  <si>
+    <t>12.03.202610</t>
+  </si>
+  <si>
+    <t>12.03.202611</t>
+  </si>
+  <si>
+    <t>12.03.202612</t>
+  </si>
+  <si>
+    <t>12.03.202613</t>
+  </si>
+  <si>
+    <t>12.03.202614</t>
+  </si>
+  <si>
+    <t>12.03.202615</t>
+  </si>
+  <si>
+    <t>12.03.202616</t>
+  </si>
+  <si>
+    <t>12.03.202617</t>
+  </si>
+  <si>
+    <t>12.03.202618</t>
+  </si>
+  <si>
+    <t>12.03.202619</t>
+  </si>
+  <si>
+    <t>12.03.202620</t>
+  </si>
+  <si>
+    <t>12.03.202621</t>
+  </si>
+  <si>
+    <t>12.03.202622</t>
+  </si>
+  <si>
+    <t>12.03.202623</t>
+  </si>
+  <si>
+    <t>12.03.202624</t>
+  </si>
+  <si>
+    <t>12.03.202625</t>
+  </si>
+  <si>
+    <t>12.03.202626</t>
+  </si>
+  <si>
+    <t>12.03.202627</t>
+  </si>
+  <si>
+    <t>12.03.202628</t>
+  </si>
+  <si>
+    <t>12.03.202629</t>
+  </si>
+  <si>
+    <t>12.03.202630</t>
+  </si>
+  <si>
+    <t>12.03.202631</t>
+  </si>
+  <si>
+    <t>12.03.202632</t>
+  </si>
+  <si>
+    <t>12.03.202633</t>
+  </si>
+  <si>
+    <t>12.03.202634</t>
+  </si>
+  <si>
+    <t>12.03.202635</t>
+  </si>
+  <si>
+    <t>12.03.202636</t>
+  </si>
+  <si>
+    <t>12.03.202637</t>
+  </si>
+  <si>
+    <t>12.03.202638</t>
+  </si>
+  <si>
+    <t>12.03.202639</t>
+  </si>
+  <si>
+    <t>12.03.202640</t>
+  </si>
+  <si>
+    <t>12.03.202641</t>
+  </si>
+  <si>
+    <t>12.03.202642</t>
+  </si>
+  <si>
+    <t>12.03.202643</t>
+  </si>
+  <si>
+    <t>12.03.202644</t>
+  </si>
+  <si>
+    <t>12.03.202645</t>
+  </si>
+  <si>
+    <t>12.03.202646</t>
+  </si>
+  <si>
+    <t>12.03.202647</t>
+  </si>
+  <si>
+    <t>12.03.202648</t>
+  </si>
+  <si>
+    <t>12.03.202649</t>
+  </si>
+  <si>
+    <t>12.03.202650</t>
+  </si>
+  <si>
+    <t>12.03.202651</t>
+  </si>
+  <si>
+    <t>12.03.202652</t>
+  </si>
+  <si>
+    <t>12.03.202653</t>
+  </si>
+  <si>
+    <t>12.03.202654</t>
+  </si>
+  <si>
+    <t>12.03.202655</t>
+  </si>
+  <si>
+    <t>12.03.202656</t>
+  </si>
+  <si>
+    <t>12.03.202657</t>
+  </si>
+  <si>
+    <t>12.03.202658</t>
+  </si>
+  <si>
+    <t>12.03.202659</t>
+  </si>
+  <si>
+    <t>12.03.202660</t>
+  </si>
+  <si>
+    <t>12.03.202661</t>
+  </si>
+  <si>
+    <t>12.03.202662</t>
+  </si>
+  <si>
+    <t>12.03.202663</t>
+  </si>
+  <si>
+    <t>12.03.202664</t>
+  </si>
+  <si>
+    <t>12.03.202665</t>
+  </si>
+  <si>
+    <t>12.03.202666</t>
+  </si>
+  <si>
+    <t>12.03.202667</t>
+  </si>
+  <si>
+    <t>12.03.202668</t>
+  </si>
+  <si>
+    <t>12.03.202669</t>
+  </si>
+  <si>
+    <t>12.03.202670</t>
+  </si>
+  <si>
+    <t>12.03.202671</t>
+  </si>
+  <si>
+    <t>12.03.202672</t>
+  </si>
+  <si>
+    <t>12.03.202673</t>
+  </si>
+  <si>
+    <t>12.03.202674</t>
+  </si>
+  <si>
+    <t>12.03.202675</t>
+  </si>
+  <si>
+    <t>12.03.202676</t>
+  </si>
+  <si>
+    <t>12.03.202677</t>
+  </si>
+  <si>
+    <t>12.03.202678</t>
+  </si>
+  <si>
+    <t>12.03.202679</t>
+  </si>
+  <si>
+    <t>12.03.202680</t>
+  </si>
+  <si>
+    <t>12.03.202681</t>
+  </si>
+  <si>
+    <t>12.03.202682</t>
+  </si>
+  <si>
+    <t>12.03.202683</t>
+  </si>
+  <si>
+    <t>12.03.202684</t>
+  </si>
+  <si>
+    <t>12.03.202685</t>
+  </si>
+  <si>
+    <t>12.03.202686</t>
+  </si>
+  <si>
+    <t>12.03.202687</t>
+  </si>
+  <si>
+    <t>12.03.202688</t>
+  </si>
+  <si>
+    <t>12.03.202689</t>
+  </si>
+  <si>
+    <t>12.03.202690</t>
+  </si>
+  <si>
+    <t>12.03.202691</t>
+  </si>
+  <si>
+    <t>12.03.202692</t>
+  </si>
+  <si>
+    <t>12.03.202693</t>
+  </si>
+  <si>
+    <t>12.03.202694</t>
+  </si>
+  <si>
+    <t>12.03.202695</t>
+  </si>
+  <si>
+    <t>12.03.202696</t>
+  </si>
+  <si>
+    <t>12.03.20261</t>
+  </si>
+  <si>
+    <t>13.03.20263</t>
+  </si>
+  <si>
+    <t>13.03.20264</t>
+  </si>
+  <si>
+    <t>13.03.20265</t>
+  </si>
+  <si>
+    <t>13.03.20266</t>
+  </si>
+  <si>
+    <t>13.03.20267</t>
+  </si>
+  <si>
+    <t>13.03.20268</t>
+  </si>
+  <si>
+    <t>13.03.20269</t>
+  </si>
+  <si>
+    <t>13.03.202610</t>
+  </si>
+  <si>
+    <t>13.03.202611</t>
+  </si>
+  <si>
+    <t>13.03.202612</t>
+  </si>
+  <si>
+    <t>13.03.202613</t>
+  </si>
+  <si>
+    <t>13.03.202614</t>
+  </si>
+  <si>
+    <t>13.03.202615</t>
+  </si>
+  <si>
+    <t>13.03.202616</t>
+  </si>
+  <si>
+    <t>13.03.202617</t>
+  </si>
+  <si>
+    <t>13.03.202618</t>
+  </si>
+  <si>
+    <t>13.03.202619</t>
+  </si>
+  <si>
+    <t>13.03.202620</t>
+  </si>
+  <si>
+    <t>13.03.202621</t>
+  </si>
+  <si>
+    <t>13.03.202622</t>
+  </si>
+  <si>
+    <t>13.03.202623</t>
+  </si>
+  <si>
+    <t>13.03.202624</t>
+  </si>
+  <si>
+    <t>13.03.202625</t>
+  </si>
+  <si>
+    <t>13.03.202626</t>
+  </si>
+  <si>
+    <t>13.03.202627</t>
+  </si>
+  <si>
+    <t>13.03.202628</t>
+  </si>
+  <si>
+    <t>13.03.202629</t>
+  </si>
+  <si>
+    <t>13.03.202630</t>
+  </si>
+  <si>
+    <t>13.03.202631</t>
+  </si>
+  <si>
+    <t>13.03.202632</t>
+  </si>
+  <si>
+    <t>13.03.202633</t>
+  </si>
+  <si>
+    <t>13.03.202634</t>
+  </si>
+  <si>
+    <t>13.03.202635</t>
+  </si>
+  <si>
+    <t>13.03.202636</t>
+  </si>
+  <si>
+    <t>13.03.202637</t>
+  </si>
+  <si>
+    <t>13.03.202638</t>
+  </si>
+  <si>
+    <t>13.03.202639</t>
+  </si>
+  <si>
+    <t>13.03.202640</t>
+  </si>
+  <si>
+    <t>13.03.202641</t>
+  </si>
+  <si>
+    <t>13.03.202642</t>
+  </si>
+  <si>
+    <t>13.03.202643</t>
+  </si>
+  <si>
+    <t>13.03.202644</t>
+  </si>
+  <si>
+    <t>13.03.202645</t>
+  </si>
+  <si>
+    <t>13.03.202646</t>
+  </si>
+  <si>
+    <t>13.03.202647</t>
+  </si>
+  <si>
+    <t>13.03.202648</t>
+  </si>
+  <si>
+    <t>13.03.202649</t>
+  </si>
+  <si>
+    <t>13.03.202650</t>
+  </si>
+  <si>
+    <t>13.03.202651</t>
+  </si>
+  <si>
+    <t>13.03.202652</t>
+  </si>
+  <si>
+    <t>13.03.202653</t>
+  </si>
+  <si>
+    <t>13.03.202654</t>
+  </si>
+  <si>
+    <t>13.03.202655</t>
+  </si>
+  <si>
+    <t>13.03.202656</t>
+  </si>
+  <si>
+    <t>13.03.202657</t>
+  </si>
+  <si>
+    <t>13.03.202658</t>
+  </si>
+  <si>
+    <t>13.03.202659</t>
+  </si>
+  <si>
+    <t>13.03.202660</t>
+  </si>
+  <si>
+    <t>13.03.202661</t>
+  </si>
+  <si>
+    <t>13.03.202662</t>
+  </si>
+  <si>
+    <t>13.03.202663</t>
+  </si>
+  <si>
+    <t>13.03.202664</t>
+  </si>
+  <si>
+    <t>13.03.202665</t>
+  </si>
+  <si>
+    <t>13.03.202666</t>
+  </si>
+  <si>
+    <t>13.03.202667</t>
+  </si>
+  <si>
+    <t>13.03.202668</t>
+  </si>
+  <si>
+    <t>13.03.202669</t>
+  </si>
+  <si>
+    <t>13.03.202670</t>
+  </si>
+  <si>
+    <t>13.03.202671</t>
+  </si>
+  <si>
+    <t>13.03.202672</t>
+  </si>
+  <si>
+    <t>13.03.202673</t>
+  </si>
+  <si>
+    <t>13.03.202674</t>
+  </si>
+  <si>
+    <t>13.03.202675</t>
+  </si>
+  <si>
+    <t>13.03.202676</t>
+  </si>
+  <si>
+    <t>13.03.202677</t>
+  </si>
+  <si>
+    <t>13.03.202678</t>
+  </si>
+  <si>
+    <t>13.03.202679</t>
+  </si>
+  <si>
+    <t>13.03.202680</t>
+  </si>
+  <si>
+    <t>13.03.202681</t>
+  </si>
+  <si>
+    <t>13.03.202682</t>
+  </si>
+  <si>
+    <t>13.03.202683</t>
+  </si>
+  <si>
+    <t>13.03.202684</t>
+  </si>
+  <si>
+    <t>13.03.202685</t>
+  </si>
+  <si>
+    <t>13.03.202686</t>
+  </si>
+  <si>
+    <t>13.03.202687</t>
+  </si>
+  <si>
+    <t>13.03.202688</t>
+  </si>
+  <si>
+    <t>13.03.202689</t>
+  </si>
+  <si>
+    <t>13.03.202690</t>
+  </si>
+  <si>
+    <t>13.03.202691</t>
+  </si>
+  <si>
+    <t>13.03.202692</t>
+  </si>
+  <si>
+    <t>13.03.202693</t>
+  </si>
+  <si>
+    <t>13.03.202694</t>
+  </si>
+  <si>
+    <t>13.03.202695</t>
+  </si>
+  <si>
+    <t>13.03.202696</t>
+  </si>
+  <si>
+    <t>13.03.20261</t>
+  </si>
+  <si>
+    <t>13.03.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46077.99444444444</v>
+        <v>46092.99444444444</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46078.00486111111</v>
+        <v>46093.00486111111</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46078.01527777778</v>
+        <v>46093.01527777778</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46078.02569444444</v>
+        <v>46093.02569444444</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46078.03611111111</v>
+        <v>46093.03611111111</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46078.04652777778</v>
+        <v>46093.04652777778</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46078.05694444444</v>
+        <v>46093.05694444444</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46078.06736111111</v>
+        <v>46093.06736111111</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46078.07777777778</v>
+        <v>46093.07777777778</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46078.08819444444</v>
+        <v>46093.08819444444</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46078.09861111111</v>
+        <v>46093.09861111111</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46078.10902777778</v>
+        <v>46093.10902777778</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46078.11944444444</v>
+        <v>46093.11944444444</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46078.12986111111</v>
+        <v>46093.12986111111</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46078.14027777778</v>
+        <v>46093.14027777778</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46078.15069444444</v>
+        <v>46093.15069444444</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46078.16111111111</v>
+        <v>46093.16111111111</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46078.17152777778</v>
+        <v>46093.17152777778</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46078.18194444444</v>
+        <v>46093.18194444444</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46078.19236111111</v>
+        <v>46093.19236111111</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46078.20277777778</v>
+        <v>46093.20277777778</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46078.21319444444</v>
+        <v>46093.21319444444</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46078.22361111111</v>
+        <v>46093.22361111111</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46078.23402777778</v>
+        <v>46093.23402777778</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46078.24444444444</v>
+        <v>46093.24444444444</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46078.25486111111</v>
+        <v>46093.25486111111</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46078.26527777778</v>
+        <v>46093.26527777778</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46078.27569444444</v>
+        <v>46093.27569444444</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46078.28611111111</v>
+        <v>46093.28611111111</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46078.29652777778</v>
+        <v>46093.29652777778</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46078.30694444444</v>
+        <v>46093.30694444444</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46078.31736111111</v>
+        <v>46093.31736111111</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46078.32777777778</v>
+        <v>46093.32777777778</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46078.33819444444</v>
+        <v>46093.33819444444</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46078.34861111111</v>
+        <v>46093.34861111111</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46078.35902777778</v>
+        <v>46093.35902777778</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46078.36944444444</v>
+        <v>46093.36944444444</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46078.37986111111</v>
+        <v>46093.37986111111</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46078.39027777778</v>
+        <v>46093.39027777778</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46078.40069444444</v>
+        <v>46093.40069444444</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46078.41111111111</v>
+        <v>46093.41111111111</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46078.42152777778</v>
+        <v>46093.42152777778</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46078.43194444444</v>
+        <v>46093.43194444444</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46078.44236111111</v>
+        <v>46093.44236111111</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46078.45277777778</v>
+        <v>46093.45277777778</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46078.46319444444</v>
+        <v>46093.46319444444</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46078.47361111111</v>
+        <v>46093.47361111111</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46078.48402777778</v>
+        <v>46093.48402777778</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46078.49444444444</v>
+        <v>46093.49444444444</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46078.50486111111</v>
+        <v>46093.50486111111</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46078.51527777778</v>
+        <v>46093.51527777778</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46078.52569444444</v>
+        <v>46093.52569444444</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46078.53611111111</v>
+        <v>46093.53611111111</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46078.54652777778</v>
+        <v>46093.54652777778</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46078.55694444444</v>
+        <v>46093.55694444444</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46078.56736111111</v>
+        <v>46093.56736111111</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46078.57777777778</v>
+        <v>46093.57777777778</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46078.58819444444</v>
+        <v>46093.58819444444</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46078.59861111111</v>
+        <v>46093.59861111111</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46078.60902777778</v>
+        <v>46093.60902777778</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46078.61944444444</v>
+        <v>46093.61944444444</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46078.62986111111</v>
+        <v>46093.62986111111</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46078.64027777778</v>
+        <v>46093.64027777778</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46078.65069444444</v>
+        <v>46093.65069444444</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46078.66111111111</v>
+        <v>46093.66111111111</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46078.67152777778</v>
+        <v>46093.67152777778</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46078.68194444444</v>
+        <v>46093.68194444444</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46078.69236111111</v>
+        <v>46093.69236111111</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46078.70277777778</v>
+        <v>46093.70277777778</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46078.71319444444</v>
+        <v>46093.71319444444</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46078.72361111111</v>
+        <v>46093.72361111111</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46078.73402777778</v>
+        <v>46093.73402777778</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46078.74444444444</v>
+        <v>46093.74444444444</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46078.75486111111</v>
+        <v>46093.75486111111</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46078.76527777778</v>
+        <v>46093.76527777778</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46078.77569444444</v>
+        <v>46093.77569444444</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46078.78611111111</v>
+        <v>46093.78611111111</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46078.79652777778</v>
+        <v>46093.79652777778</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46078.80694444444</v>
+        <v>46093.80694444444</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46078.81736111111</v>
+        <v>46093.81736111111</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46078.82777777778</v>
+        <v>46093.82777777778</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46078.83819444444</v>
+        <v>46093.83819444444</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46078.84861111111</v>
+        <v>46093.84861111111</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46078.85902777778</v>
+        <v>46093.85902777778</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46078.86944444444</v>
+        <v>46093.86944444444</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46078.87986111111</v>
+        <v>46093.87986111111</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46078.89027777778</v>
+        <v>46093.89027777778</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46078.90069444444</v>
+        <v>46093.90069444444</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46078.91111111111</v>
+        <v>46093.91111111111</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46078.92152777778</v>
+        <v>46093.92152777778</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46078.93194444444</v>
+        <v>46093.93194444444</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46078.94236111111</v>
+        <v>46093.94236111111</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46078.95277777778</v>
+        <v>46093.95277777778</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46078.96319444444</v>
+        <v>46093.96319444444</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46078.97361111111</v>
+        <v>46093.97361111111</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46078.98402777778</v>
+        <v>46093.98402777778</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46078.99444444444</v>
+        <v>46093.99444444444</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46078.99444444444</v>
+        <v>46093.99444444444</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46079.00486111111</v>
+        <v>46094.00486111111</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46079.01527777778</v>
+        <v>46094.01527777778</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46079.02569444444</v>
+        <v>46094.02569444444</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46079.03611111111</v>
+        <v>46094.03611111111</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46079.04652777778</v>
+        <v>46094.04652777778</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46079.05694444444</v>
+        <v>46094.05694444444</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46079.06736111111</v>
+        <v>46094.06736111111</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46079.07777777778</v>
+        <v>46094.07777777778</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46079.08819444444</v>
+        <v>46094.08819444444</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46079.09861111111</v>
+        <v>46094.09861111111</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46079.10902777778</v>
+        <v>46094.10902777778</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46079.11944444444</v>
+        <v>46094.11944444444</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46079.12986111111</v>
+        <v>46094.12986111111</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46079.14027777778</v>
+        <v>46094.14027777778</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46079.15069444444</v>
+        <v>46094.15069444444</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46079.16111111111</v>
+        <v>46094.16111111111</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46079.17152777778</v>
+        <v>46094.17152777778</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46079.18194444444</v>
+        <v>46094.18194444444</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46079.19236111111</v>
+        <v>46094.19236111111</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46079.20277777778</v>
+        <v>46094.20277777778</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46079.21319444444</v>
+        <v>46094.21319444444</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46079.22361111111</v>
+        <v>46094.22361111111</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46079.23402777778</v>
+        <v>46094.23402777778</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46079.24444444444</v>
+        <v>46094.24444444444</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46079.25486111111</v>
+        <v>46094.25486111111</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46079.26527777778</v>
+        <v>46094.26527777778</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46079.27569444444</v>
+        <v>46094.27569444444</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46079.28611111111</v>
+        <v>46094.28611111111</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46079.29652777778</v>
+        <v>46094.29652777778</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46079.30694444444</v>
+        <v>46094.30694444444</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46079.31736111111</v>
+        <v>46094.31736111111</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46079.32777777778</v>
+        <v>46094.32777777778</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46079.33819444444</v>
+        <v>46094.33819444444</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46079.34861111111</v>
+        <v>46094.34861111111</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46079.35902777778</v>
+        <v>46094.35902777778</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46079.36944444444</v>
+        <v>46094.36944444444</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46079.37986111111</v>
+        <v>46094.37986111111</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46079.39027777778</v>
+        <v>46094.39027777778</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46079.40069444444</v>
+        <v>46094.40069444444</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46079.41111111111</v>
+        <v>46094.41111111111</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46079.42152777778</v>
+        <v>46094.42152777778</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46079.43194444444</v>
+        <v>46094.43194444444</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46079.44236111111</v>
+        <v>46094.44236111111</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46079.45277777778</v>
+        <v>46094.45277777778</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46079.46319444444</v>
+        <v>46094.46319444444</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46079.47361111111</v>
+        <v>46094.47361111111</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46079.48402777778</v>
+        <v>46094.48402777778</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46079.49444444444</v>
+        <v>46094.49444444444</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46079.50486111111</v>
+        <v>46094.50486111111</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46079.51527777778</v>
+        <v>46094.51527777778</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46079.52569444444</v>
+        <v>46094.52569444444</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46079.53611111111</v>
+        <v>46094.53611111111</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46079.54652777778</v>
+        <v>46094.54652777778</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46079.55694444444</v>
+        <v>46094.55694444444</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46079.56736111111</v>
+        <v>46094.56736111111</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46079.57777777778</v>
+        <v>46094.57777777778</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46079.58819444444</v>
+        <v>46094.58819444444</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46079.59861111111</v>
+        <v>46094.59861111111</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46079.60902777778</v>
+        <v>46094.60902777778</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46079.61944444444</v>
+        <v>46094.61944444444</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46079.62986111111</v>
+        <v>46094.62986111111</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46079.64027777778</v>
+        <v>46094.64027777778</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46079.65069444444</v>
+        <v>46094.65069444444</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46079.66111111111</v>
+        <v>46094.66111111111</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46079.67152777778</v>
+        <v>46094.67152777778</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46079.68194444444</v>
+        <v>46094.68194444444</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46079.69236111111</v>
+        <v>46094.69236111111</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46079.70277777778</v>
+        <v>46094.70277777778</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46079.71319444444</v>
+        <v>46094.71319444444</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46079.72361111111</v>
+        <v>46094.72361111111</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46079.73402777778</v>
+        <v>46094.73402777778</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46079.74444444444</v>
+        <v>46094.74444444444</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46079.75486111111</v>
+        <v>46094.75486111111</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46079.76527777778</v>
+        <v>46094.76527777778</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46079.77569444444</v>
+        <v>46094.77569444444</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46079.78611111111</v>
+        <v>46094.78611111111</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46079.79652777778</v>
+        <v>46094.79652777778</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46079.80694444444</v>
+        <v>46094.80694444444</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46079.81736111111</v>
+        <v>46094.81736111111</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46079.82777777778</v>
+        <v>46094.82777777778</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46079.83819444444</v>
+        <v>46094.83819444444</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46079.84861111111</v>
+        <v>46094.84861111111</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46079.85902777778</v>
+        <v>46094.85902777778</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46079.86944444444</v>
+        <v>46094.86944444444</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46079.87986111111</v>
+        <v>46094.87986111111</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46079.89027777778</v>
+        <v>46094.89027777778</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46079.90069444444</v>
+        <v>46094.90069444444</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46079.91111111111</v>
+        <v>46094.91111111111</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46079.92152777778</v>
+        <v>46094.92152777778</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46079.93194444444</v>
+        <v>46094.93194444444</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46079.94236111111</v>
+        <v>46094.94236111111</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46079.95277777778</v>
+        <v>46094.95277777778</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46079.96319444444</v>
+        <v>46094.96319444444</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46079.97361111111</v>
+        <v>46094.97361111111</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46079.98402777778</v>
+        <v>46094.98402777778</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46079.99444444444</v>
+        <v>46094.99444444444</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,583 +31,583 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.03.20261</t>
-  </si>
-  <si>
-    <t>12.03.20262</t>
-  </si>
-  <si>
-    <t>12.03.20263</t>
-  </si>
-  <si>
-    <t>12.03.20264</t>
-  </si>
-  <si>
-    <t>12.03.20265</t>
-  </si>
-  <si>
-    <t>12.03.20266</t>
-  </si>
-  <si>
-    <t>12.03.20267</t>
-  </si>
-  <si>
-    <t>12.03.20268</t>
-  </si>
-  <si>
-    <t>12.03.20269</t>
-  </si>
-  <si>
-    <t>12.03.202610</t>
-  </si>
-  <si>
-    <t>12.03.202611</t>
-  </si>
-  <si>
-    <t>12.03.202612</t>
-  </si>
-  <si>
-    <t>12.03.202613</t>
-  </si>
-  <si>
-    <t>12.03.202614</t>
-  </si>
-  <si>
-    <t>12.03.202615</t>
-  </si>
-  <si>
-    <t>12.03.202616</t>
-  </si>
-  <si>
-    <t>12.03.202617</t>
-  </si>
-  <si>
-    <t>12.03.202618</t>
-  </si>
-  <si>
-    <t>12.03.202619</t>
-  </si>
-  <si>
-    <t>12.03.202620</t>
-  </si>
-  <si>
-    <t>12.03.202621</t>
-  </si>
-  <si>
-    <t>12.03.202622</t>
-  </si>
-  <si>
-    <t>12.03.202623</t>
-  </si>
-  <si>
-    <t>12.03.202624</t>
-  </si>
-  <si>
-    <t>12.03.202625</t>
-  </si>
-  <si>
-    <t>12.03.202626</t>
-  </si>
-  <si>
-    <t>12.03.202627</t>
-  </si>
-  <si>
-    <t>12.03.202628</t>
-  </si>
-  <si>
-    <t>12.03.202629</t>
-  </si>
-  <si>
-    <t>12.03.202630</t>
-  </si>
-  <si>
-    <t>12.03.202631</t>
-  </si>
-  <si>
-    <t>12.03.202632</t>
-  </si>
-  <si>
-    <t>12.03.202633</t>
-  </si>
-  <si>
-    <t>12.03.202634</t>
-  </si>
-  <si>
-    <t>12.03.202635</t>
-  </si>
-  <si>
-    <t>12.03.202636</t>
-  </si>
-  <si>
-    <t>12.03.202637</t>
-  </si>
-  <si>
-    <t>12.03.202638</t>
-  </si>
-  <si>
-    <t>12.03.202639</t>
-  </si>
-  <si>
-    <t>12.03.202640</t>
-  </si>
-  <si>
-    <t>12.03.202641</t>
-  </si>
-  <si>
-    <t>12.03.202642</t>
-  </si>
-  <si>
-    <t>12.03.202643</t>
-  </si>
-  <si>
-    <t>12.03.202644</t>
-  </si>
-  <si>
-    <t>12.03.202645</t>
-  </si>
-  <si>
-    <t>12.03.202646</t>
-  </si>
-  <si>
-    <t>12.03.202647</t>
-  </si>
-  <si>
-    <t>12.03.202648</t>
-  </si>
-  <si>
-    <t>12.03.202649</t>
-  </si>
-  <si>
-    <t>12.03.202650</t>
-  </si>
-  <si>
-    <t>12.03.202651</t>
-  </si>
-  <si>
-    <t>12.03.202652</t>
-  </si>
-  <si>
-    <t>12.03.202653</t>
-  </si>
-  <si>
-    <t>12.03.202654</t>
-  </si>
-  <si>
-    <t>12.03.202655</t>
-  </si>
-  <si>
-    <t>12.03.202656</t>
-  </si>
-  <si>
-    <t>12.03.202657</t>
-  </si>
-  <si>
-    <t>12.03.202658</t>
-  </si>
-  <si>
-    <t>12.03.202659</t>
-  </si>
-  <si>
-    <t>12.03.202660</t>
-  </si>
-  <si>
-    <t>12.03.202661</t>
-  </si>
-  <si>
-    <t>12.03.202662</t>
-  </si>
-  <si>
-    <t>12.03.202663</t>
-  </si>
-  <si>
-    <t>12.03.202664</t>
-  </si>
-  <si>
-    <t>12.03.202665</t>
-  </si>
-  <si>
-    <t>12.03.202666</t>
-  </si>
-  <si>
-    <t>12.03.202667</t>
-  </si>
-  <si>
-    <t>12.03.202668</t>
-  </si>
-  <si>
-    <t>12.03.202669</t>
-  </si>
-  <si>
-    <t>12.03.202670</t>
-  </si>
-  <si>
-    <t>12.03.202671</t>
-  </si>
-  <si>
-    <t>12.03.202672</t>
-  </si>
-  <si>
-    <t>12.03.202673</t>
-  </si>
-  <si>
-    <t>12.03.202674</t>
-  </si>
-  <si>
-    <t>12.03.202675</t>
-  </si>
-  <si>
-    <t>12.03.202676</t>
-  </si>
-  <si>
-    <t>12.03.202677</t>
-  </si>
-  <si>
-    <t>12.03.202678</t>
-  </si>
-  <si>
-    <t>12.03.202679</t>
-  </si>
-  <si>
-    <t>12.03.202680</t>
-  </si>
-  <si>
-    <t>12.03.202681</t>
-  </si>
-  <si>
-    <t>12.03.202682</t>
-  </si>
-  <si>
-    <t>12.03.202683</t>
-  </si>
-  <si>
-    <t>12.03.202684</t>
-  </si>
-  <si>
-    <t>12.03.202685</t>
-  </si>
-  <si>
-    <t>12.03.202686</t>
-  </si>
-  <si>
-    <t>12.03.202687</t>
-  </si>
-  <si>
-    <t>12.03.202688</t>
-  </si>
-  <si>
-    <t>12.03.202689</t>
-  </si>
-  <si>
-    <t>12.03.202690</t>
-  </si>
-  <si>
-    <t>12.03.202691</t>
-  </si>
-  <si>
-    <t>12.03.202692</t>
-  </si>
-  <si>
-    <t>12.03.202693</t>
-  </si>
-  <si>
-    <t>12.03.202694</t>
-  </si>
-  <si>
-    <t>12.03.202695</t>
-  </si>
-  <si>
-    <t>12.03.202696</t>
-  </si>
-  <si>
-    <t>12.03.20261</t>
-  </si>
-  <si>
-    <t>13.03.20263</t>
-  </si>
-  <si>
-    <t>13.03.20264</t>
-  </si>
-  <si>
-    <t>13.03.20265</t>
-  </si>
-  <si>
-    <t>13.03.20266</t>
-  </si>
-  <si>
-    <t>13.03.20267</t>
-  </si>
-  <si>
-    <t>13.03.20268</t>
-  </si>
-  <si>
-    <t>13.03.20269</t>
-  </si>
-  <si>
-    <t>13.03.202610</t>
-  </si>
-  <si>
-    <t>13.03.202611</t>
-  </si>
-  <si>
-    <t>13.03.202612</t>
-  </si>
-  <si>
-    <t>13.03.202613</t>
-  </si>
-  <si>
-    <t>13.03.202614</t>
-  </si>
-  <si>
-    <t>13.03.202615</t>
-  </si>
-  <si>
-    <t>13.03.202616</t>
-  </si>
-  <si>
-    <t>13.03.202617</t>
-  </si>
-  <si>
-    <t>13.03.202618</t>
-  </si>
-  <si>
-    <t>13.03.202619</t>
-  </si>
-  <si>
-    <t>13.03.202620</t>
-  </si>
-  <si>
-    <t>13.03.202621</t>
-  </si>
-  <si>
-    <t>13.03.202622</t>
-  </si>
-  <si>
-    <t>13.03.202623</t>
-  </si>
-  <si>
-    <t>13.03.202624</t>
-  </si>
-  <si>
-    <t>13.03.202625</t>
-  </si>
-  <si>
-    <t>13.03.202626</t>
-  </si>
-  <si>
-    <t>13.03.202627</t>
-  </si>
-  <si>
-    <t>13.03.202628</t>
-  </si>
-  <si>
-    <t>13.03.202629</t>
-  </si>
-  <si>
-    <t>13.03.202630</t>
-  </si>
-  <si>
-    <t>13.03.202631</t>
-  </si>
-  <si>
-    <t>13.03.202632</t>
-  </si>
-  <si>
-    <t>13.03.202633</t>
-  </si>
-  <si>
-    <t>13.03.202634</t>
-  </si>
-  <si>
-    <t>13.03.202635</t>
-  </si>
-  <si>
-    <t>13.03.202636</t>
-  </si>
-  <si>
-    <t>13.03.202637</t>
-  </si>
-  <si>
-    <t>13.03.202638</t>
-  </si>
-  <si>
-    <t>13.03.202639</t>
-  </si>
-  <si>
-    <t>13.03.202640</t>
-  </si>
-  <si>
-    <t>13.03.202641</t>
-  </si>
-  <si>
-    <t>13.03.202642</t>
-  </si>
-  <si>
-    <t>13.03.202643</t>
-  </si>
-  <si>
-    <t>13.03.202644</t>
-  </si>
-  <si>
-    <t>13.03.202645</t>
-  </si>
-  <si>
-    <t>13.03.202646</t>
-  </si>
-  <si>
-    <t>13.03.202647</t>
-  </si>
-  <si>
-    <t>13.03.202648</t>
-  </si>
-  <si>
-    <t>13.03.202649</t>
-  </si>
-  <si>
-    <t>13.03.202650</t>
-  </si>
-  <si>
-    <t>13.03.202651</t>
-  </si>
-  <si>
-    <t>13.03.202652</t>
-  </si>
-  <si>
-    <t>13.03.202653</t>
-  </si>
-  <si>
-    <t>13.03.202654</t>
-  </si>
-  <si>
-    <t>13.03.202655</t>
-  </si>
-  <si>
-    <t>13.03.202656</t>
-  </si>
-  <si>
-    <t>13.03.202657</t>
-  </si>
-  <si>
-    <t>13.03.202658</t>
-  </si>
-  <si>
-    <t>13.03.202659</t>
-  </si>
-  <si>
-    <t>13.03.202660</t>
-  </si>
-  <si>
-    <t>13.03.202661</t>
-  </si>
-  <si>
-    <t>13.03.202662</t>
-  </si>
-  <si>
-    <t>13.03.202663</t>
-  </si>
-  <si>
-    <t>13.03.202664</t>
-  </si>
-  <si>
-    <t>13.03.202665</t>
-  </si>
-  <si>
-    <t>13.03.202666</t>
-  </si>
-  <si>
-    <t>13.03.202667</t>
-  </si>
-  <si>
-    <t>13.03.202668</t>
-  </si>
-  <si>
-    <t>13.03.202669</t>
-  </si>
-  <si>
-    <t>13.03.202670</t>
-  </si>
-  <si>
-    <t>13.03.202671</t>
-  </si>
-  <si>
-    <t>13.03.202672</t>
-  </si>
-  <si>
-    <t>13.03.202673</t>
-  </si>
-  <si>
-    <t>13.03.202674</t>
-  </si>
-  <si>
-    <t>13.03.202675</t>
-  </si>
-  <si>
-    <t>13.03.202676</t>
-  </si>
-  <si>
-    <t>13.03.202677</t>
-  </si>
-  <si>
-    <t>13.03.202678</t>
-  </si>
-  <si>
-    <t>13.03.202679</t>
-  </si>
-  <si>
-    <t>13.03.202680</t>
-  </si>
-  <si>
-    <t>13.03.202681</t>
-  </si>
-  <si>
-    <t>13.03.202682</t>
-  </si>
-  <si>
-    <t>13.03.202683</t>
-  </si>
-  <si>
-    <t>13.03.202684</t>
-  </si>
-  <si>
-    <t>13.03.202685</t>
-  </si>
-  <si>
-    <t>13.03.202686</t>
-  </si>
-  <si>
-    <t>13.03.202687</t>
-  </si>
-  <si>
-    <t>13.03.202688</t>
-  </si>
-  <si>
-    <t>13.03.202689</t>
-  </si>
-  <si>
-    <t>13.03.202690</t>
-  </si>
-  <si>
-    <t>13.03.202691</t>
-  </si>
-  <si>
-    <t>13.03.202692</t>
-  </si>
-  <si>
-    <t>13.03.202693</t>
-  </si>
-  <si>
-    <t>13.03.202694</t>
-  </si>
-  <si>
-    <t>13.03.202695</t>
-  </si>
-  <si>
-    <t>13.03.202696</t>
-  </si>
-  <si>
-    <t>13.03.20261</t>
-  </si>
-  <si>
-    <t>13.03.20262</t>
+    <t>24.03.20261</t>
+  </si>
+  <si>
+    <t>25.03.20262</t>
+  </si>
+  <si>
+    <t>25.03.20263</t>
+  </si>
+  <si>
+    <t>25.03.20264</t>
+  </si>
+  <si>
+    <t>25.03.20265</t>
+  </si>
+  <si>
+    <t>25.03.20266</t>
+  </si>
+  <si>
+    <t>25.03.20267</t>
+  </si>
+  <si>
+    <t>25.03.20268</t>
+  </si>
+  <si>
+    <t>25.03.20269</t>
+  </si>
+  <si>
+    <t>25.03.202610</t>
+  </si>
+  <si>
+    <t>25.03.202611</t>
+  </si>
+  <si>
+    <t>25.03.202612</t>
+  </si>
+  <si>
+    <t>25.03.202613</t>
+  </si>
+  <si>
+    <t>25.03.202614</t>
+  </si>
+  <si>
+    <t>25.03.202615</t>
+  </si>
+  <si>
+    <t>25.03.202616</t>
+  </si>
+  <si>
+    <t>25.03.202617</t>
+  </si>
+  <si>
+    <t>25.03.202618</t>
+  </si>
+  <si>
+    <t>25.03.202619</t>
+  </si>
+  <si>
+    <t>25.03.202620</t>
+  </si>
+  <si>
+    <t>25.03.202621</t>
+  </si>
+  <si>
+    <t>25.03.202622</t>
+  </si>
+  <si>
+    <t>25.03.202623</t>
+  </si>
+  <si>
+    <t>25.03.202624</t>
+  </si>
+  <si>
+    <t>25.03.202625</t>
+  </si>
+  <si>
+    <t>25.03.202626</t>
+  </si>
+  <si>
+    <t>25.03.202627</t>
+  </si>
+  <si>
+    <t>25.03.202628</t>
+  </si>
+  <si>
+    <t>25.03.202629</t>
+  </si>
+  <si>
+    <t>25.03.202630</t>
+  </si>
+  <si>
+    <t>25.03.202631</t>
+  </si>
+  <si>
+    <t>25.03.202632</t>
+  </si>
+  <si>
+    <t>25.03.202633</t>
+  </si>
+  <si>
+    <t>25.03.202634</t>
+  </si>
+  <si>
+    <t>25.03.202635</t>
+  </si>
+  <si>
+    <t>25.03.202636</t>
+  </si>
+  <si>
+    <t>25.03.202637</t>
+  </si>
+  <si>
+    <t>25.03.202638</t>
+  </si>
+  <si>
+    <t>25.03.202639</t>
+  </si>
+  <si>
+    <t>25.03.202640</t>
+  </si>
+  <si>
+    <t>25.03.202641</t>
+  </si>
+  <si>
+    <t>25.03.202642</t>
+  </si>
+  <si>
+    <t>25.03.202643</t>
+  </si>
+  <si>
+    <t>25.03.202644</t>
+  </si>
+  <si>
+    <t>25.03.202645</t>
+  </si>
+  <si>
+    <t>25.03.202646</t>
+  </si>
+  <si>
+    <t>25.03.202647</t>
+  </si>
+  <si>
+    <t>25.03.202648</t>
+  </si>
+  <si>
+    <t>25.03.202649</t>
+  </si>
+  <si>
+    <t>25.03.202650</t>
+  </si>
+  <si>
+    <t>25.03.202651</t>
+  </si>
+  <si>
+    <t>25.03.202652</t>
+  </si>
+  <si>
+    <t>25.03.202653</t>
+  </si>
+  <si>
+    <t>25.03.202654</t>
+  </si>
+  <si>
+    <t>25.03.202655</t>
+  </si>
+  <si>
+    <t>25.03.202656</t>
+  </si>
+  <si>
+    <t>25.03.202657</t>
+  </si>
+  <si>
+    <t>25.03.202658</t>
+  </si>
+  <si>
+    <t>25.03.202659</t>
+  </si>
+  <si>
+    <t>25.03.202660</t>
+  </si>
+  <si>
+    <t>25.03.202661</t>
+  </si>
+  <si>
+    <t>25.03.202662</t>
+  </si>
+  <si>
+    <t>25.03.202663</t>
+  </si>
+  <si>
+    <t>25.03.202664</t>
+  </si>
+  <si>
+    <t>25.03.202665</t>
+  </si>
+  <si>
+    <t>25.03.202666</t>
+  </si>
+  <si>
+    <t>25.03.202667</t>
+  </si>
+  <si>
+    <t>25.03.202668</t>
+  </si>
+  <si>
+    <t>25.03.202669</t>
+  </si>
+  <si>
+    <t>25.03.202670</t>
+  </si>
+  <si>
+    <t>25.03.202671</t>
+  </si>
+  <si>
+    <t>25.03.202672</t>
+  </si>
+  <si>
+    <t>25.03.202673</t>
+  </si>
+  <si>
+    <t>25.03.202674</t>
+  </si>
+  <si>
+    <t>25.03.202675</t>
+  </si>
+  <si>
+    <t>25.03.202676</t>
+  </si>
+  <si>
+    <t>25.03.202677</t>
+  </si>
+  <si>
+    <t>25.03.202678</t>
+  </si>
+  <si>
+    <t>25.03.202679</t>
+  </si>
+  <si>
+    <t>25.03.202680</t>
+  </si>
+  <si>
+    <t>25.03.202681</t>
+  </si>
+  <si>
+    <t>25.03.202682</t>
+  </si>
+  <si>
+    <t>25.03.202683</t>
+  </si>
+  <si>
+    <t>25.03.202684</t>
+  </si>
+  <si>
+    <t>25.03.202685</t>
+  </si>
+  <si>
+    <t>25.03.202686</t>
+  </si>
+  <si>
+    <t>25.03.202687</t>
+  </si>
+  <si>
+    <t>25.03.202688</t>
+  </si>
+  <si>
+    <t>25.03.202689</t>
+  </si>
+  <si>
+    <t>25.03.202690</t>
+  </si>
+  <si>
+    <t>25.03.202691</t>
+  </si>
+  <si>
+    <t>25.03.202692</t>
+  </si>
+  <si>
+    <t>25.03.202693</t>
+  </si>
+  <si>
+    <t>25.03.202694</t>
+  </si>
+  <si>
+    <t>25.03.202695</t>
+  </si>
+  <si>
+    <t>25.03.202696</t>
+  </si>
+  <si>
+    <t>25.03.20261</t>
+  </si>
+  <si>
+    <t>26.03.20263</t>
+  </si>
+  <si>
+    <t>26.03.20264</t>
+  </si>
+  <si>
+    <t>26.03.20265</t>
+  </si>
+  <si>
+    <t>26.03.20266</t>
+  </si>
+  <si>
+    <t>26.03.20267</t>
+  </si>
+  <si>
+    <t>26.03.20268</t>
+  </si>
+  <si>
+    <t>26.03.20269</t>
+  </si>
+  <si>
+    <t>26.03.202610</t>
+  </si>
+  <si>
+    <t>26.03.202611</t>
+  </si>
+  <si>
+    <t>26.03.202612</t>
+  </si>
+  <si>
+    <t>26.03.202613</t>
+  </si>
+  <si>
+    <t>26.03.202614</t>
+  </si>
+  <si>
+    <t>26.03.202615</t>
+  </si>
+  <si>
+    <t>26.03.202616</t>
+  </si>
+  <si>
+    <t>26.03.202617</t>
+  </si>
+  <si>
+    <t>26.03.202618</t>
+  </si>
+  <si>
+    <t>26.03.202619</t>
+  </si>
+  <si>
+    <t>26.03.202620</t>
+  </si>
+  <si>
+    <t>26.03.202621</t>
+  </si>
+  <si>
+    <t>26.03.202622</t>
+  </si>
+  <si>
+    <t>26.03.202623</t>
+  </si>
+  <si>
+    <t>26.03.202624</t>
+  </si>
+  <si>
+    <t>26.03.202625</t>
+  </si>
+  <si>
+    <t>26.03.202626</t>
+  </si>
+  <si>
+    <t>26.03.202627</t>
+  </si>
+  <si>
+    <t>26.03.202628</t>
+  </si>
+  <si>
+    <t>26.03.202629</t>
+  </si>
+  <si>
+    <t>26.03.202630</t>
+  </si>
+  <si>
+    <t>26.03.202631</t>
+  </si>
+  <si>
+    <t>26.03.202632</t>
+  </si>
+  <si>
+    <t>26.03.202633</t>
+  </si>
+  <si>
+    <t>26.03.202634</t>
+  </si>
+  <si>
+    <t>26.03.202635</t>
+  </si>
+  <si>
+    <t>26.03.202636</t>
+  </si>
+  <si>
+    <t>26.03.202637</t>
+  </si>
+  <si>
+    <t>26.03.202638</t>
+  </si>
+  <si>
+    <t>26.03.202639</t>
+  </si>
+  <si>
+    <t>26.03.202640</t>
+  </si>
+  <si>
+    <t>26.03.202641</t>
+  </si>
+  <si>
+    <t>26.03.202642</t>
+  </si>
+  <si>
+    <t>26.03.202643</t>
+  </si>
+  <si>
+    <t>26.03.202644</t>
+  </si>
+  <si>
+    <t>26.03.202645</t>
+  </si>
+  <si>
+    <t>26.03.202646</t>
+  </si>
+  <si>
+    <t>26.03.202647</t>
+  </si>
+  <si>
+    <t>26.03.202648</t>
+  </si>
+  <si>
+    <t>26.03.202649</t>
+  </si>
+  <si>
+    <t>26.03.202650</t>
+  </si>
+  <si>
+    <t>26.03.202651</t>
+  </si>
+  <si>
+    <t>26.03.202652</t>
+  </si>
+  <si>
+    <t>26.03.202653</t>
+  </si>
+  <si>
+    <t>26.03.202654</t>
+  </si>
+  <si>
+    <t>26.03.202655</t>
+  </si>
+  <si>
+    <t>26.03.202656</t>
+  </si>
+  <si>
+    <t>26.03.202657</t>
+  </si>
+  <si>
+    <t>26.03.202658</t>
+  </si>
+  <si>
+    <t>26.03.202659</t>
+  </si>
+  <si>
+    <t>26.03.202660</t>
+  </si>
+  <si>
+    <t>26.03.202661</t>
+  </si>
+  <si>
+    <t>26.03.202662</t>
+  </si>
+  <si>
+    <t>26.03.202663</t>
+  </si>
+  <si>
+    <t>26.03.202664</t>
+  </si>
+  <si>
+    <t>26.03.202665</t>
+  </si>
+  <si>
+    <t>26.03.202666</t>
+  </si>
+  <si>
+    <t>26.03.202667</t>
+  </si>
+  <si>
+    <t>26.03.202668</t>
+  </si>
+  <si>
+    <t>26.03.202669</t>
+  </si>
+  <si>
+    <t>26.03.202670</t>
+  </si>
+  <si>
+    <t>26.03.202671</t>
+  </si>
+  <si>
+    <t>26.03.202672</t>
+  </si>
+  <si>
+    <t>26.03.202673</t>
+  </si>
+  <si>
+    <t>26.03.202674</t>
+  </si>
+  <si>
+    <t>26.03.202675</t>
+  </si>
+  <si>
+    <t>26.03.202676</t>
+  </si>
+  <si>
+    <t>26.03.202677</t>
+  </si>
+  <si>
+    <t>26.03.202678</t>
+  </si>
+  <si>
+    <t>26.03.202679</t>
+  </si>
+  <si>
+    <t>26.03.202680</t>
+  </si>
+  <si>
+    <t>26.03.202681</t>
+  </si>
+  <si>
+    <t>26.03.202682</t>
+  </si>
+  <si>
+    <t>26.03.202683</t>
+  </si>
+  <si>
+    <t>26.03.202684</t>
+  </si>
+  <si>
+    <t>26.03.202685</t>
+  </si>
+  <si>
+    <t>26.03.202686</t>
+  </si>
+  <si>
+    <t>26.03.202687</t>
+  </si>
+  <si>
+    <t>26.03.202688</t>
+  </si>
+  <si>
+    <t>26.03.202689</t>
+  </si>
+  <si>
+    <t>26.03.202690</t>
+  </si>
+  <si>
+    <t>26.03.202691</t>
+  </si>
+  <si>
+    <t>26.03.202692</t>
+  </si>
+  <si>
+    <t>26.03.202693</t>
+  </si>
+  <si>
+    <t>26.03.202694</t>
+  </si>
+  <si>
+    <t>26.03.202695</t>
+  </si>
+  <si>
+    <t>26.03.202696</t>
+  </si>
+  <si>
+    <t>26.03.20261</t>
+  </si>
+  <si>
+    <t>26.03.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46092.99444444444</v>
+        <v>46105.99444444444</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46093.00486111111</v>
+        <v>46106.00486111111</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46093.01527777778</v>
+        <v>46106.01527777778</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46093.02569444444</v>
+        <v>46106.02569444444</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46093.03611111111</v>
+        <v>46106.03611111111</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46093.04652777778</v>
+        <v>46106.04652777778</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46093.05694444444</v>
+        <v>46106.05694444444</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46093.06736111111</v>
+        <v>46106.06736111111</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46093.07777777778</v>
+        <v>46106.07777777778</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46093.08819444444</v>
+        <v>46106.08819444444</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46093.09861111111</v>
+        <v>46106.09861111111</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46093.10902777778</v>
+        <v>46106.10902777778</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46093.11944444444</v>
+        <v>46106.11944444444</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46093.12986111111</v>
+        <v>46106.12986111111</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46093.14027777778</v>
+        <v>46106.14027777778</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46093.15069444444</v>
+        <v>46106.15069444444</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46093.16111111111</v>
+        <v>46106.16111111111</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46093.17152777778</v>
+        <v>46106.17152777778</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46093.18194444444</v>
+        <v>46106.18194444444</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46093.19236111111</v>
+        <v>46106.19236111111</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46093.20277777778</v>
+        <v>46106.20277777778</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46093.21319444444</v>
+        <v>46106.21319444444</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46093.22361111111</v>
+        <v>46106.22361111111</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46093.23402777778</v>
+        <v>46106.23402777778</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46093.24444444444</v>
+        <v>46106.24444444444</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46093.25486111111</v>
+        <v>46106.25486111111</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46093.26527777778</v>
+        <v>46106.26527777778</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46093.27569444444</v>
+        <v>46106.27569444444</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46093.28611111111</v>
+        <v>46106.28611111111</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46093.29652777778</v>
+        <v>46106.29652777778</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46093.30694444444</v>
+        <v>46106.30694444444</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46093.31736111111</v>
+        <v>46106.31736111111</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46093.32777777778</v>
+        <v>46106.32777777778</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46093.33819444444</v>
+        <v>46106.33819444444</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46093.34861111111</v>
+        <v>46106.34861111111</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46093.35902777778</v>
+        <v>46106.35902777778</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46093.36944444444</v>
+        <v>46106.36944444444</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46093.37986111111</v>
+        <v>46106.37986111111</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46093.39027777778</v>
+        <v>46106.39027777778</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46093.40069444444</v>
+        <v>46106.40069444444</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46093.41111111111</v>
+        <v>46106.41111111111</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46093.42152777778</v>
+        <v>46106.42152777778</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46093.43194444444</v>
+        <v>46106.43194444444</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46093.44236111111</v>
+        <v>46106.44236111111</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46093.45277777778</v>
+        <v>46106.45277777778</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46093.46319444444</v>
+        <v>46106.46319444444</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46093.47361111111</v>
+        <v>46106.47361111111</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46093.48402777778</v>
+        <v>46106.48402777778</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46093.49444444444</v>
+        <v>46106.49444444444</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46093.50486111111</v>
+        <v>46106.50486111111</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46093.51527777778</v>
+        <v>46106.51527777778</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46093.52569444444</v>
+        <v>46106.52569444444</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46093.53611111111</v>
+        <v>46106.53611111111</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46093.54652777778</v>
+        <v>46106.54652777778</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46093.55694444444</v>
+        <v>46106.55694444444</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46093.56736111111</v>
+        <v>46106.56736111111</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46093.57777777778</v>
+        <v>46106.57777777778</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46093.58819444444</v>
+        <v>46106.58819444444</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46093.59861111111</v>
+        <v>46106.59861111111</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46093.60902777778</v>
+        <v>46106.60902777778</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46093.61944444444</v>
+        <v>46106.61944444444</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46093.62986111111</v>
+        <v>46106.62986111111</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46093.64027777778</v>
+        <v>46106.64027777778</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46093.65069444444</v>
+        <v>46106.65069444444</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46093.66111111111</v>
+        <v>46106.66111111111</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46093.67152777778</v>
+        <v>46106.67152777778</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46093.68194444444</v>
+        <v>46106.68194444444</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46093.69236111111</v>
+        <v>46106.69236111111</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46093.70277777778</v>
+        <v>46106.70277777778</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46093.71319444444</v>
+        <v>46106.71319444444</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46093.72361111111</v>
+        <v>46106.72361111111</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46093.73402777778</v>
+        <v>46106.73402777778</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46093.74444444444</v>
+        <v>46106.74444444444</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46093.75486111111</v>
+        <v>46106.75486111111</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46093.76527777778</v>
+        <v>46106.76527777778</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46093.77569444444</v>
+        <v>46106.77569444444</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46093.78611111111</v>
+        <v>46106.78611111111</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46093.79652777778</v>
+        <v>46106.79652777778</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46093.80694444444</v>
+        <v>46106.80694444444</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46093.81736111111</v>
+        <v>46106.81736111111</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46093.82777777778</v>
+        <v>46106.82777777778</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46093.83819444444</v>
+        <v>46106.83819444444</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46093.84861111111</v>
+        <v>46106.84861111111</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46093.85902777778</v>
+        <v>46106.85902777778</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46093.86944444444</v>
+        <v>46106.86944444444</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46093.87986111111</v>
+        <v>46106.87986111111</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46093.89027777778</v>
+        <v>46106.89027777778</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46093.90069444444</v>
+        <v>46106.90069444444</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46093.91111111111</v>
+        <v>46106.91111111111</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46093.92152777778</v>
+        <v>46106.92152777778</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46093.93194444444</v>
+        <v>46106.93194444444</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46093.94236111111</v>
+        <v>46106.94236111111</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46093.95277777778</v>
+        <v>46106.95277777778</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46093.96319444444</v>
+        <v>46106.96319444444</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46093.97361111111</v>
+        <v>46106.97361111111</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46093.98402777778</v>
+        <v>46106.98402777778</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46093.99444444444</v>
+        <v>46106.99444444444</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46093.99444444444</v>
+        <v>46106.99444444444</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46094.00486111111</v>
+        <v>46107.00486111111</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46094.01527777778</v>
+        <v>46107.01527777778</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46094.02569444444</v>
+        <v>46107.02569444444</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46094.03611111111</v>
+        <v>46107.03611111111</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46094.04652777778</v>
+        <v>46107.04652777778</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46094.05694444444</v>
+        <v>46107.05694444444</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46094.06736111111</v>
+        <v>46107.06736111111</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46094.07777777778</v>
+        <v>46107.07777777778</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46094.08819444444</v>
+        <v>46107.08819444444</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46094.09861111111</v>
+        <v>46107.09861111111</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46094.10902777778</v>
+        <v>46107.10902777778</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46094.11944444444</v>
+        <v>46107.11944444444</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46094.12986111111</v>
+        <v>46107.12986111111</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46094.14027777778</v>
+        <v>46107.14027777778</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46094.15069444444</v>
+        <v>46107.15069444444</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46094.16111111111</v>
+        <v>46107.16111111111</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46094.17152777778</v>
+        <v>46107.17152777778</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46094.18194444444</v>
+        <v>46107.18194444444</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46094.19236111111</v>
+        <v>46107.19236111111</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46094.20277777778</v>
+        <v>46107.20277777778</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46094.21319444444</v>
+        <v>46107.21319444444</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46094.22361111111</v>
+        <v>46107.22361111111</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46094.23402777778</v>
+        <v>46107.23402777778</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46094.24444444444</v>
+        <v>46107.24444444444</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46094.25486111111</v>
+        <v>46107.25486111111</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46094.26527777778</v>
+        <v>46107.26527777778</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46094.27569444444</v>
+        <v>46107.27569444444</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46094.28611111111</v>
+        <v>46107.28611111111</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46094.29652777778</v>
+        <v>46107.29652777778</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46094.30694444444</v>
+        <v>46107.30694444444</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46094.31736111111</v>
+        <v>46107.31736111111</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46094.32777777778</v>
+        <v>46107.32777777778</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46094.33819444444</v>
+        <v>46107.33819444444</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46094.34861111111</v>
+        <v>46107.34861111111</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46094.35902777778</v>
+        <v>46107.35902777778</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46094.36944444444</v>
+        <v>46107.36944444444</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46094.37986111111</v>
+        <v>46107.37986111111</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46094.39027777778</v>
+        <v>46107.39027777778</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46094.40069444444</v>
+        <v>46107.40069444444</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46094.41111111111</v>
+        <v>46107.41111111111</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46094.42152777778</v>
+        <v>46107.42152777778</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46094.43194444444</v>
+        <v>46107.43194444444</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46094.44236111111</v>
+        <v>46107.44236111111</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46094.45277777778</v>
+        <v>46107.45277777778</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46094.46319444444</v>
+        <v>46107.46319444444</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46094.47361111111</v>
+        <v>46107.47361111111</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46094.48402777778</v>
+        <v>46107.48402777778</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46094.49444444444</v>
+        <v>46107.49444444444</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46094.50486111111</v>
+        <v>46107.50486111111</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46094.51527777778</v>
+        <v>46107.51527777778</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46094.52569444444</v>
+        <v>46107.52569444444</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46094.53611111111</v>
+        <v>46107.53611111111</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46094.54652777778</v>
+        <v>46107.54652777778</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46094.55694444444</v>
+        <v>46107.55694444444</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46094.56736111111</v>
+        <v>46107.56736111111</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46094.57777777778</v>
+        <v>46107.57777777778</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46094.58819444444</v>
+        <v>46107.58819444444</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46094.59861111111</v>
+        <v>46107.59861111111</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46094.60902777778</v>
+        <v>46107.60902777778</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46094.61944444444</v>
+        <v>46107.61944444444</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46094.62986111111</v>
+        <v>46107.62986111111</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46094.64027777778</v>
+        <v>46107.64027777778</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46094.65069444444</v>
+        <v>46107.65069444444</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46094.66111111111</v>
+        <v>46107.66111111111</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46094.67152777778</v>
+        <v>46107.67152777778</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46094.68194444444</v>
+        <v>46107.68194444444</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46094.69236111111</v>
+        <v>46107.69236111111</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46094.70277777778</v>
+        <v>46107.70277777778</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46094.71319444444</v>
+        <v>46107.71319444444</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46094.72361111111</v>
+        <v>46107.72361111111</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46094.73402777778</v>
+        <v>46107.73402777778</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46094.74444444444</v>
+        <v>46107.74444444444</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46094.75486111111</v>
+        <v>46107.75486111111</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46094.76527777778</v>
+        <v>46107.76527777778</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46094.77569444444</v>
+        <v>46107.77569444444</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46094.78611111111</v>
+        <v>46107.78611111111</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46094.79652777778</v>
+        <v>46107.79652777778</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46094.80694444444</v>
+        <v>46107.80694444444</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46094.81736111111</v>
+        <v>46107.81736111111</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46094.82777777778</v>
+        <v>46107.82777777778</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46094.83819444444</v>
+        <v>46107.83819444444</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46094.84861111111</v>
+        <v>46107.84861111111</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46094.85902777778</v>
+        <v>46107.85902777778</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46094.86944444444</v>
+        <v>46107.86944444444</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46094.87986111111</v>
+        <v>46107.87986111111</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46094.89027777778</v>
+        <v>46107.89027777778</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46094.90069444444</v>
+        <v>46107.90069444444</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46094.91111111111</v>
+        <v>46107.91111111111</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46094.92152777778</v>
+        <v>46107.92152777778</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46094.93194444444</v>
+        <v>46107.93194444444</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46094.94236111111</v>
+        <v>46107.94236111111</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46094.95277777778</v>
+        <v>46107.95277777778</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46094.96319444444</v>
+        <v>46107.96319444444</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46094.97361111111</v>
+        <v>46107.97361111111</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46094.98402777778</v>
+        <v>46107.98402777778</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46094.99444444444</v>
+        <v>46107.99444444444</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="582">
   <si>
     <t>Timestamp</t>
   </si>
@@ -608,6 +608,1158 @@
   </si>
   <si>
     <t>26.03.20262</t>
+  </si>
+  <si>
+    <t>27.03.20264</t>
+  </si>
+  <si>
+    <t>27.03.20265</t>
+  </si>
+  <si>
+    <t>27.03.20266</t>
+  </si>
+  <si>
+    <t>27.03.20267</t>
+  </si>
+  <si>
+    <t>27.03.20268</t>
+  </si>
+  <si>
+    <t>27.03.20269</t>
+  </si>
+  <si>
+    <t>27.03.202610</t>
+  </si>
+  <si>
+    <t>27.03.202611</t>
+  </si>
+  <si>
+    <t>27.03.202612</t>
+  </si>
+  <si>
+    <t>27.03.202613</t>
+  </si>
+  <si>
+    <t>27.03.202614</t>
+  </si>
+  <si>
+    <t>27.03.202615</t>
+  </si>
+  <si>
+    <t>27.03.202616</t>
+  </si>
+  <si>
+    <t>27.03.202617</t>
+  </si>
+  <si>
+    <t>27.03.202618</t>
+  </si>
+  <si>
+    <t>27.03.202619</t>
+  </si>
+  <si>
+    <t>27.03.202620</t>
+  </si>
+  <si>
+    <t>27.03.202621</t>
+  </si>
+  <si>
+    <t>27.03.202622</t>
+  </si>
+  <si>
+    <t>27.03.202623</t>
+  </si>
+  <si>
+    <t>27.03.202624</t>
+  </si>
+  <si>
+    <t>27.03.202625</t>
+  </si>
+  <si>
+    <t>27.03.202626</t>
+  </si>
+  <si>
+    <t>27.03.202627</t>
+  </si>
+  <si>
+    <t>27.03.202628</t>
+  </si>
+  <si>
+    <t>27.03.202629</t>
+  </si>
+  <si>
+    <t>27.03.202630</t>
+  </si>
+  <si>
+    <t>27.03.202631</t>
+  </si>
+  <si>
+    <t>27.03.202632</t>
+  </si>
+  <si>
+    <t>27.03.202633</t>
+  </si>
+  <si>
+    <t>27.03.202634</t>
+  </si>
+  <si>
+    <t>27.03.202635</t>
+  </si>
+  <si>
+    <t>27.03.202636</t>
+  </si>
+  <si>
+    <t>27.03.202637</t>
+  </si>
+  <si>
+    <t>27.03.202638</t>
+  </si>
+  <si>
+    <t>27.03.202639</t>
+  </si>
+  <si>
+    <t>27.03.202640</t>
+  </si>
+  <si>
+    <t>27.03.202641</t>
+  </si>
+  <si>
+    <t>27.03.202642</t>
+  </si>
+  <si>
+    <t>27.03.202643</t>
+  </si>
+  <si>
+    <t>27.03.202644</t>
+  </si>
+  <si>
+    <t>27.03.202645</t>
+  </si>
+  <si>
+    <t>27.03.202646</t>
+  </si>
+  <si>
+    <t>27.03.202647</t>
+  </si>
+  <si>
+    <t>27.03.202648</t>
+  </si>
+  <si>
+    <t>27.03.202649</t>
+  </si>
+  <si>
+    <t>27.03.202650</t>
+  </si>
+  <si>
+    <t>27.03.202651</t>
+  </si>
+  <si>
+    <t>27.03.202652</t>
+  </si>
+  <si>
+    <t>27.03.202653</t>
+  </si>
+  <si>
+    <t>27.03.202654</t>
+  </si>
+  <si>
+    <t>27.03.202655</t>
+  </si>
+  <si>
+    <t>27.03.202656</t>
+  </si>
+  <si>
+    <t>27.03.202657</t>
+  </si>
+  <si>
+    <t>27.03.202658</t>
+  </si>
+  <si>
+    <t>27.03.202659</t>
+  </si>
+  <si>
+    <t>27.03.202660</t>
+  </si>
+  <si>
+    <t>27.03.202661</t>
+  </si>
+  <si>
+    <t>27.03.202662</t>
+  </si>
+  <si>
+    <t>27.03.202663</t>
+  </si>
+  <si>
+    <t>27.03.202664</t>
+  </si>
+  <si>
+    <t>27.03.202665</t>
+  </si>
+  <si>
+    <t>27.03.202666</t>
+  </si>
+  <si>
+    <t>27.03.202667</t>
+  </si>
+  <si>
+    <t>27.03.202668</t>
+  </si>
+  <si>
+    <t>27.03.202669</t>
+  </si>
+  <si>
+    <t>27.03.202670</t>
+  </si>
+  <si>
+    <t>27.03.202671</t>
+  </si>
+  <si>
+    <t>27.03.202672</t>
+  </si>
+  <si>
+    <t>27.03.202673</t>
+  </si>
+  <si>
+    <t>27.03.202674</t>
+  </si>
+  <si>
+    <t>27.03.202675</t>
+  </si>
+  <si>
+    <t>27.03.202676</t>
+  </si>
+  <si>
+    <t>27.03.202677</t>
+  </si>
+  <si>
+    <t>27.03.202678</t>
+  </si>
+  <si>
+    <t>27.03.202679</t>
+  </si>
+  <si>
+    <t>27.03.202680</t>
+  </si>
+  <si>
+    <t>27.03.202681</t>
+  </si>
+  <si>
+    <t>27.03.202682</t>
+  </si>
+  <si>
+    <t>27.03.202683</t>
+  </si>
+  <si>
+    <t>27.03.202684</t>
+  </si>
+  <si>
+    <t>27.03.202685</t>
+  </si>
+  <si>
+    <t>27.03.202686</t>
+  </si>
+  <si>
+    <t>27.03.202687</t>
+  </si>
+  <si>
+    <t>27.03.202688</t>
+  </si>
+  <si>
+    <t>27.03.202689</t>
+  </si>
+  <si>
+    <t>27.03.202690</t>
+  </si>
+  <si>
+    <t>27.03.202691</t>
+  </si>
+  <si>
+    <t>27.03.202692</t>
+  </si>
+  <si>
+    <t>27.03.202693</t>
+  </si>
+  <si>
+    <t>27.03.202694</t>
+  </si>
+  <si>
+    <t>27.03.202695</t>
+  </si>
+  <si>
+    <t>27.03.202696</t>
+  </si>
+  <si>
+    <t>27.03.20261</t>
+  </si>
+  <si>
+    <t>27.03.20262</t>
+  </si>
+  <si>
+    <t>27.03.20263</t>
+  </si>
+  <si>
+    <t>28.03.20265</t>
+  </si>
+  <si>
+    <t>28.03.20266</t>
+  </si>
+  <si>
+    <t>28.03.20267</t>
+  </si>
+  <si>
+    <t>28.03.20268</t>
+  </si>
+  <si>
+    <t>28.03.20269</t>
+  </si>
+  <si>
+    <t>28.03.202610</t>
+  </si>
+  <si>
+    <t>28.03.202611</t>
+  </si>
+  <si>
+    <t>28.03.202612</t>
+  </si>
+  <si>
+    <t>28.03.202613</t>
+  </si>
+  <si>
+    <t>28.03.202614</t>
+  </si>
+  <si>
+    <t>28.03.202615</t>
+  </si>
+  <si>
+    <t>28.03.202616</t>
+  </si>
+  <si>
+    <t>28.03.202617</t>
+  </si>
+  <si>
+    <t>28.03.202618</t>
+  </si>
+  <si>
+    <t>28.03.202619</t>
+  </si>
+  <si>
+    <t>28.03.202620</t>
+  </si>
+  <si>
+    <t>28.03.202621</t>
+  </si>
+  <si>
+    <t>28.03.202622</t>
+  </si>
+  <si>
+    <t>28.03.202623</t>
+  </si>
+  <si>
+    <t>28.03.202624</t>
+  </si>
+  <si>
+    <t>28.03.202625</t>
+  </si>
+  <si>
+    <t>28.03.202626</t>
+  </si>
+  <si>
+    <t>28.03.202627</t>
+  </si>
+  <si>
+    <t>28.03.202628</t>
+  </si>
+  <si>
+    <t>28.03.202629</t>
+  </si>
+  <si>
+    <t>28.03.202630</t>
+  </si>
+  <si>
+    <t>28.03.202631</t>
+  </si>
+  <si>
+    <t>28.03.202632</t>
+  </si>
+  <si>
+    <t>28.03.202633</t>
+  </si>
+  <si>
+    <t>28.03.202634</t>
+  </si>
+  <si>
+    <t>28.03.202635</t>
+  </si>
+  <si>
+    <t>28.03.202636</t>
+  </si>
+  <si>
+    <t>28.03.202637</t>
+  </si>
+  <si>
+    <t>28.03.202638</t>
+  </si>
+  <si>
+    <t>28.03.202639</t>
+  </si>
+  <si>
+    <t>28.03.202640</t>
+  </si>
+  <si>
+    <t>28.03.202641</t>
+  </si>
+  <si>
+    <t>28.03.202642</t>
+  </si>
+  <si>
+    <t>28.03.202643</t>
+  </si>
+  <si>
+    <t>28.03.202644</t>
+  </si>
+  <si>
+    <t>28.03.202645</t>
+  </si>
+  <si>
+    <t>28.03.202646</t>
+  </si>
+  <si>
+    <t>28.03.202647</t>
+  </si>
+  <si>
+    <t>28.03.202648</t>
+  </si>
+  <si>
+    <t>28.03.202649</t>
+  </si>
+  <si>
+    <t>28.03.202650</t>
+  </si>
+  <si>
+    <t>28.03.202651</t>
+  </si>
+  <si>
+    <t>28.03.202652</t>
+  </si>
+  <si>
+    <t>28.03.202653</t>
+  </si>
+  <si>
+    <t>28.03.202654</t>
+  </si>
+  <si>
+    <t>28.03.202655</t>
+  </si>
+  <si>
+    <t>28.03.202656</t>
+  </si>
+  <si>
+    <t>28.03.202657</t>
+  </si>
+  <si>
+    <t>28.03.202658</t>
+  </si>
+  <si>
+    <t>28.03.202659</t>
+  </si>
+  <si>
+    <t>28.03.202660</t>
+  </si>
+  <si>
+    <t>28.03.202661</t>
+  </si>
+  <si>
+    <t>28.03.202662</t>
+  </si>
+  <si>
+    <t>28.03.202663</t>
+  </si>
+  <si>
+    <t>28.03.202664</t>
+  </si>
+  <si>
+    <t>28.03.202665</t>
+  </si>
+  <si>
+    <t>28.03.202666</t>
+  </si>
+  <si>
+    <t>28.03.202667</t>
+  </si>
+  <si>
+    <t>28.03.202668</t>
+  </si>
+  <si>
+    <t>28.03.202669</t>
+  </si>
+  <si>
+    <t>28.03.202670</t>
+  </si>
+  <si>
+    <t>28.03.202671</t>
+  </si>
+  <si>
+    <t>28.03.202672</t>
+  </si>
+  <si>
+    <t>28.03.202673</t>
+  </si>
+  <si>
+    <t>28.03.202674</t>
+  </si>
+  <si>
+    <t>28.03.202675</t>
+  </si>
+  <si>
+    <t>28.03.202676</t>
+  </si>
+  <si>
+    <t>28.03.202677</t>
+  </si>
+  <si>
+    <t>28.03.202678</t>
+  </si>
+  <si>
+    <t>28.03.202679</t>
+  </si>
+  <si>
+    <t>28.03.202680</t>
+  </si>
+  <si>
+    <t>28.03.202681</t>
+  </si>
+  <si>
+    <t>28.03.202682</t>
+  </si>
+  <si>
+    <t>28.03.202683</t>
+  </si>
+  <si>
+    <t>28.03.202684</t>
+  </si>
+  <si>
+    <t>28.03.202685</t>
+  </si>
+  <si>
+    <t>28.03.202686</t>
+  </si>
+  <si>
+    <t>28.03.202687</t>
+  </si>
+  <si>
+    <t>28.03.202688</t>
+  </si>
+  <si>
+    <t>28.03.202689</t>
+  </si>
+  <si>
+    <t>28.03.202690</t>
+  </si>
+  <si>
+    <t>28.03.202691</t>
+  </si>
+  <si>
+    <t>28.03.202692</t>
+  </si>
+  <si>
+    <t>28.03.202693</t>
+  </si>
+  <si>
+    <t>28.03.202694</t>
+  </si>
+  <si>
+    <t>28.03.202695</t>
+  </si>
+  <si>
+    <t>28.03.202696</t>
+  </si>
+  <si>
+    <t>28.03.20261</t>
+  </si>
+  <si>
+    <t>28.03.20262</t>
+  </si>
+  <si>
+    <t>28.03.20263</t>
+  </si>
+  <si>
+    <t>28.03.20264</t>
+  </si>
+  <si>
+    <t>29.03.20266</t>
+  </si>
+  <si>
+    <t>29.03.20267</t>
+  </si>
+  <si>
+    <t>29.03.20268</t>
+  </si>
+  <si>
+    <t>29.03.20269</t>
+  </si>
+  <si>
+    <t>29.03.202610</t>
+  </si>
+  <si>
+    <t>29.03.202611</t>
+  </si>
+  <si>
+    <t>29.03.202612</t>
+  </si>
+  <si>
+    <t>29.03.202613</t>
+  </si>
+  <si>
+    <t>29.03.202614</t>
+  </si>
+  <si>
+    <t>29.03.202615</t>
+  </si>
+  <si>
+    <t>29.03.202616</t>
+  </si>
+  <si>
+    <t>29.03.202617</t>
+  </si>
+  <si>
+    <t>29.03.202618</t>
+  </si>
+  <si>
+    <t>29.03.202619</t>
+  </si>
+  <si>
+    <t>29.03.202620</t>
+  </si>
+  <si>
+    <t>29.03.202621</t>
+  </si>
+  <si>
+    <t>29.03.202622</t>
+  </si>
+  <si>
+    <t>29.03.202623</t>
+  </si>
+  <si>
+    <t>29.03.202624</t>
+  </si>
+  <si>
+    <t>29.03.202625</t>
+  </si>
+  <si>
+    <t>29.03.202626</t>
+  </si>
+  <si>
+    <t>29.03.202627</t>
+  </si>
+  <si>
+    <t>29.03.202628</t>
+  </si>
+  <si>
+    <t>29.03.202629</t>
+  </si>
+  <si>
+    <t>29.03.202630</t>
+  </si>
+  <si>
+    <t>29.03.202631</t>
+  </si>
+  <si>
+    <t>29.03.202632</t>
+  </si>
+  <si>
+    <t>29.03.202633</t>
+  </si>
+  <si>
+    <t>29.03.202634</t>
+  </si>
+  <si>
+    <t>29.03.202635</t>
+  </si>
+  <si>
+    <t>29.03.202636</t>
+  </si>
+  <si>
+    <t>29.03.202637</t>
+  </si>
+  <si>
+    <t>29.03.202638</t>
+  </si>
+  <si>
+    <t>29.03.202639</t>
+  </si>
+  <si>
+    <t>29.03.202640</t>
+  </si>
+  <si>
+    <t>29.03.202641</t>
+  </si>
+  <si>
+    <t>29.03.202642</t>
+  </si>
+  <si>
+    <t>29.03.202643</t>
+  </si>
+  <si>
+    <t>29.03.202644</t>
+  </si>
+  <si>
+    <t>29.03.202645</t>
+  </si>
+  <si>
+    <t>29.03.202646</t>
+  </si>
+  <si>
+    <t>29.03.202647</t>
+  </si>
+  <si>
+    <t>29.03.202648</t>
+  </si>
+  <si>
+    <t>29.03.202649</t>
+  </si>
+  <si>
+    <t>29.03.202650</t>
+  </si>
+  <si>
+    <t>29.03.202651</t>
+  </si>
+  <si>
+    <t>29.03.202652</t>
+  </si>
+  <si>
+    <t>29.03.202653</t>
+  </si>
+  <si>
+    <t>29.03.202654</t>
+  </si>
+  <si>
+    <t>29.03.202655</t>
+  </si>
+  <si>
+    <t>29.03.202656</t>
+  </si>
+  <si>
+    <t>29.03.202657</t>
+  </si>
+  <si>
+    <t>29.03.202658</t>
+  </si>
+  <si>
+    <t>29.03.202659</t>
+  </si>
+  <si>
+    <t>29.03.202660</t>
+  </si>
+  <si>
+    <t>29.03.202661</t>
+  </si>
+  <si>
+    <t>29.03.202662</t>
+  </si>
+  <si>
+    <t>29.03.202663</t>
+  </si>
+  <si>
+    <t>29.03.202664</t>
+  </si>
+  <si>
+    <t>29.03.202665</t>
+  </si>
+  <si>
+    <t>29.03.202666</t>
+  </si>
+  <si>
+    <t>29.03.202667</t>
+  </si>
+  <si>
+    <t>29.03.202668</t>
+  </si>
+  <si>
+    <t>29.03.202669</t>
+  </si>
+  <si>
+    <t>29.03.202670</t>
+  </si>
+  <si>
+    <t>29.03.202671</t>
+  </si>
+  <si>
+    <t>29.03.202672</t>
+  </si>
+  <si>
+    <t>29.03.202673</t>
+  </si>
+  <si>
+    <t>29.03.202674</t>
+  </si>
+  <si>
+    <t>29.03.202675</t>
+  </si>
+  <si>
+    <t>29.03.202676</t>
+  </si>
+  <si>
+    <t>29.03.202677</t>
+  </si>
+  <si>
+    <t>29.03.202678</t>
+  </si>
+  <si>
+    <t>29.03.202679</t>
+  </si>
+  <si>
+    <t>29.03.202680</t>
+  </si>
+  <si>
+    <t>29.03.202681</t>
+  </si>
+  <si>
+    <t>29.03.202682</t>
+  </si>
+  <si>
+    <t>29.03.202683</t>
+  </si>
+  <si>
+    <t>29.03.202684</t>
+  </si>
+  <si>
+    <t>29.03.202685</t>
+  </si>
+  <si>
+    <t>29.03.202686</t>
+  </si>
+  <si>
+    <t>29.03.202687</t>
+  </si>
+  <si>
+    <t>29.03.202688</t>
+  </si>
+  <si>
+    <t>29.03.202689</t>
+  </si>
+  <si>
+    <t>29.03.202690</t>
+  </si>
+  <si>
+    <t>29.03.202691</t>
+  </si>
+  <si>
+    <t>29.03.202692</t>
+  </si>
+  <si>
+    <t>29.03.202693</t>
+  </si>
+  <si>
+    <t>29.03.202694</t>
+  </si>
+  <si>
+    <t>29.03.202695</t>
+  </si>
+  <si>
+    <t>29.03.202696</t>
+  </si>
+  <si>
+    <t>29.03.20261</t>
+  </si>
+  <si>
+    <t>30.03.20262</t>
+  </si>
+  <si>
+    <t>30.03.20263</t>
+  </si>
+  <si>
+    <t>30.03.20264</t>
+  </si>
+  <si>
+    <t>30.03.20265</t>
+  </si>
+  <si>
+    <t>30.03.20266</t>
+  </si>
+  <si>
+    <t>30.03.20267</t>
+  </si>
+  <si>
+    <t>30.03.20268</t>
+  </si>
+  <si>
+    <t>30.03.20269</t>
+  </si>
+  <si>
+    <t>30.03.202610</t>
+  </si>
+  <si>
+    <t>30.03.202611</t>
+  </si>
+  <si>
+    <t>30.03.202612</t>
+  </si>
+  <si>
+    <t>30.03.202613</t>
+  </si>
+  <si>
+    <t>30.03.202614</t>
+  </si>
+  <si>
+    <t>30.03.202615</t>
+  </si>
+  <si>
+    <t>30.03.202616</t>
+  </si>
+  <si>
+    <t>30.03.202617</t>
+  </si>
+  <si>
+    <t>30.03.202618</t>
+  </si>
+  <si>
+    <t>30.03.202619</t>
+  </si>
+  <si>
+    <t>30.03.202620</t>
+  </si>
+  <si>
+    <t>30.03.202621</t>
+  </si>
+  <si>
+    <t>30.03.202622</t>
+  </si>
+  <si>
+    <t>30.03.202623</t>
+  </si>
+  <si>
+    <t>30.03.202624</t>
+  </si>
+  <si>
+    <t>30.03.202625</t>
+  </si>
+  <si>
+    <t>30.03.202626</t>
+  </si>
+  <si>
+    <t>30.03.202627</t>
+  </si>
+  <si>
+    <t>30.03.202628</t>
+  </si>
+  <si>
+    <t>30.03.202629</t>
+  </si>
+  <si>
+    <t>30.03.202630</t>
+  </si>
+  <si>
+    <t>30.03.202631</t>
+  </si>
+  <si>
+    <t>30.03.202632</t>
+  </si>
+  <si>
+    <t>30.03.202633</t>
+  </si>
+  <si>
+    <t>30.03.202634</t>
+  </si>
+  <si>
+    <t>30.03.202635</t>
+  </si>
+  <si>
+    <t>30.03.202636</t>
+  </si>
+  <si>
+    <t>30.03.202637</t>
+  </si>
+  <si>
+    <t>30.03.202638</t>
+  </si>
+  <si>
+    <t>30.03.202639</t>
+  </si>
+  <si>
+    <t>30.03.202640</t>
+  </si>
+  <si>
+    <t>30.03.202641</t>
+  </si>
+  <si>
+    <t>30.03.202642</t>
+  </si>
+  <si>
+    <t>30.03.202643</t>
+  </si>
+  <si>
+    <t>30.03.202644</t>
+  </si>
+  <si>
+    <t>30.03.202645</t>
+  </si>
+  <si>
+    <t>30.03.202646</t>
+  </si>
+  <si>
+    <t>30.03.202647</t>
+  </si>
+  <si>
+    <t>30.03.202648</t>
+  </si>
+  <si>
+    <t>30.03.202649</t>
+  </si>
+  <si>
+    <t>30.03.202650</t>
+  </si>
+  <si>
+    <t>30.03.202651</t>
+  </si>
+  <si>
+    <t>30.03.202652</t>
+  </si>
+  <si>
+    <t>30.03.202653</t>
+  </si>
+  <si>
+    <t>30.03.202654</t>
+  </si>
+  <si>
+    <t>30.03.202655</t>
+  </si>
+  <si>
+    <t>30.03.202656</t>
+  </si>
+  <si>
+    <t>30.03.202657</t>
+  </si>
+  <si>
+    <t>30.03.202658</t>
+  </si>
+  <si>
+    <t>30.03.202659</t>
+  </si>
+  <si>
+    <t>30.03.202660</t>
+  </si>
+  <si>
+    <t>30.03.202661</t>
+  </si>
+  <si>
+    <t>30.03.202662</t>
+  </si>
+  <si>
+    <t>30.03.202663</t>
+  </si>
+  <si>
+    <t>30.03.202664</t>
+  </si>
+  <si>
+    <t>30.03.202665</t>
+  </si>
+  <si>
+    <t>30.03.202666</t>
+  </si>
+  <si>
+    <t>30.03.202667</t>
+  </si>
+  <si>
+    <t>30.03.202668</t>
+  </si>
+  <si>
+    <t>30.03.202669</t>
+  </si>
+  <si>
+    <t>30.03.202670</t>
+  </si>
+  <si>
+    <t>30.03.202671</t>
+  </si>
+  <si>
+    <t>30.03.202672</t>
+  </si>
+  <si>
+    <t>30.03.202673</t>
+  </si>
+  <si>
+    <t>30.03.202674</t>
+  </si>
+  <si>
+    <t>30.03.202675</t>
+  </si>
+  <si>
+    <t>30.03.202676</t>
+  </si>
+  <si>
+    <t>30.03.202677</t>
+  </si>
+  <si>
+    <t>30.03.202678</t>
+  </si>
+  <si>
+    <t>30.03.202679</t>
+  </si>
+  <si>
+    <t>30.03.202680</t>
+  </si>
+  <si>
+    <t>30.03.202681</t>
+  </si>
+  <si>
+    <t>30.03.202682</t>
+  </si>
+  <si>
+    <t>30.03.202683</t>
+  </si>
+  <si>
+    <t>30.03.202684</t>
+  </si>
+  <si>
+    <t>30.03.202685</t>
+  </si>
+  <si>
+    <t>30.03.202686</t>
+  </si>
+  <si>
+    <t>30.03.202687</t>
+  </si>
+  <si>
+    <t>30.03.202688</t>
+  </si>
+  <si>
+    <t>30.03.202689</t>
+  </si>
+  <si>
+    <t>30.03.202690</t>
+  </si>
+  <si>
+    <t>30.03.202691</t>
+  </si>
+  <si>
+    <t>30.03.202692</t>
+  </si>
+  <si>
+    <t>30.03.202693</t>
+  </si>
+  <si>
+    <t>30.03.202694</t>
+  </si>
+  <si>
+    <t>30.03.202695</t>
+  </si>
+  <si>
+    <t>30.03.202696</t>
+  </si>
+  <si>
+    <t>30.03.20261</t>
+  </si>
+  <si>
+    <t>31.03.20263</t>
+  </si>
+  <si>
+    <t>31.03.20264</t>
+  </si>
+  <si>
+    <t>31.03.20265</t>
+  </si>
+  <si>
+    <t>31.03.20266</t>
   </si>
 </sst>
 </file>
@@ -969,7 +2121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E583"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4287,6 +5439,6602 @@
         <v>197</v>
       </c>
     </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46107.99444444444</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46108.00486111111</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46108.01527777778</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46108.02569444444</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46108.03611111111</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46108.04652777778</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46108.05694444444</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46108.06736111111</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46108.07777777778</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46108.08819444444</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46108.09861111111</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46108.10902777778</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46108.11944444444</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46108.12986111111</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46108.14027777778</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46108.15069444444</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46108.16111111111</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46108.17152777778</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46108.18194444444</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46108.19236111111</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46108.20277777778</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46108.21319444444</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46108.22361111111</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46108.23402777778</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46108.24444444444</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46108.25486111111</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46108.26527777778</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46108.27569444444</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46108.28611111111</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46108.29652777778</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46108.30694444444</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46108.31736111111</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46108.32777777778</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46108.33819444444</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46108.34861111111</v>
+      </c>
+      <c r="B230">
+        <v>0</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46108.35902777778</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46108.36944444444</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46108.37986111111</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46108.39027777778</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46108.40069444444</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46108.41111111111</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46108.42152777778</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46108.43194444444</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46108.44236111111</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46108.45277777778</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46108.46319444444</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46108.47361111111</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46108.48402777778</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46108.49444444444</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46108.50486111111</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46108.51527777778</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46108.52569444444</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46108.53611111111</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46108.54652777778</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46108.55694444444</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46108.56736111111</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46108.57777777778</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46108.58819444444</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46108.59861111111</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46108.60902777778</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46108.61944444444</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46108.62986111111</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46108.64027777778</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46108.65069444444</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46108.66111111111</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46108.67152777778</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46108.68194444444</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46108.69236111111</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46108.70277777778</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46108.71319444444</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46108.72361111111</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46108.73402777778</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46108.74444444444</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46108.75486111111</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46108.76527777778</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46108.77569444444</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46108.78611111111</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46108.79652777778</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46108.80694444444</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46108.81736111111</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46108.82777777778</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46108.83819444444</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46108.84861111111</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46108.85902777778</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46108.86944444444</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46108.87986111111</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46108.89027777778</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46108.90069444444</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46108.91111111111</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46108.92152777778</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46108.93194444444</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46108.94236111111</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46108.95277777778</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46108.96319444444</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46108.97361111111</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46108.98402777778</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46108.99444444444</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46108.99444444444</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46109.00486111111</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46109.01527777778</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46109.02569444444</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46109.03611111111</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46109.04652777778</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46109.05694444444</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46109.06736111111</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46109.07777777778</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46109.08819444444</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46109.09861111111</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46109.10902777778</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46109.11944444444</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46109.12986111111</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46109.14027777778</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46109.15069444444</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46109.16111111111</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46109.17152777778</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46109.18194444444</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46109.19236111111</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46109.20277777778</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46109.21319444444</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46109.22361111111</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46109.23402777778</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46109.24444444444</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46109.25486111111</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46109.26527777778</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46109.27569444444</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46109.28611111111</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46109.29652777778</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46109.30694444444</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46109.31736111111</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46109.32777777778</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46109.33819444444</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46109.34861111111</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46109.35902777778</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46109.36944444444</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46109.37986111111</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46109.39027777778</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46109.40069444444</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46109.41111111111</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46109.42152777778</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46109.43194444444</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46109.44236111111</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46109.45277777778</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46109.46319444444</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46109.47361111111</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46109.48402777778</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46109.49444444444</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46109.50486111111</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46109.51527777778</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46109.52569444444</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46109.53611111111</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46109.54652777778</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46109.55694444444</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46109.56736111111</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46109.57777777778</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46109.58819444444</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46109.59861111111</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46109.60902777778</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46109.61944444444</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46109.62986111111</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46109.64027777778</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46109.65069444444</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46109.66111111111</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46109.67152777778</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46109.68194444444</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46109.69236111111</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46109.70277777778</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46109.71319444444</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46109.72361111111</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46109.73402777778</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46109.74444444444</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46109.75486111111</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46109.76527777778</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46109.77569444444</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46109.78611111111</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46109.79652777778</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46109.80694444444</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46109.81736111111</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46109.82777777778</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46109.83819444444</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46109.84861111111</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46109.85902777778</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46109.86944444444</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46109.87986111111</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46109.89027777778</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46109.90069444444</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46109.91111111111</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46109.92152777778</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46109.93194444444</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46109.94236111111</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46109.95277777778</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2">
+        <v>46109.96319444444</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2">
+        <v>46109.97361111111</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2">
+        <v>46109.98402777778</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2">
+        <v>46109.99444444444</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
+      <c r="E389" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="2">
+        <v>46109.99444444444</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390">
+        <v>5</v>
+      </c>
+      <c r="E390" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="2">
+        <v>46110.00486111111</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+      <c r="D391">
+        <v>6</v>
+      </c>
+      <c r="E391" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="2">
+        <v>46110.01527777778</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392">
+        <v>7</v>
+      </c>
+      <c r="E392" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="2">
+        <v>46110.02569444444</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393">
+        <v>8</v>
+      </c>
+      <c r="E393" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="2">
+        <v>46110.03611111111</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
+      </c>
+      <c r="D394">
+        <v>9</v>
+      </c>
+      <c r="E394" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="2">
+        <v>46110.04652777778</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>10</v>
+      </c>
+      <c r="E395" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="2">
+        <v>46110.05694444444</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396">
+        <v>11</v>
+      </c>
+      <c r="E396" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="2">
+        <v>46110.06736111111</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397">
+        <v>12</v>
+      </c>
+      <c r="E397" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="2">
+        <v>46110.07777777778</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398">
+        <v>13</v>
+      </c>
+      <c r="E398" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="2">
+        <v>46110.12986111111</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399">
+        <v>14</v>
+      </c>
+      <c r="E399" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="2">
+        <v>46110.14027777778</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+      <c r="D400">
+        <v>15</v>
+      </c>
+      <c r="E400" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="2">
+        <v>46110.15069444444</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401">
+        <v>16</v>
+      </c>
+      <c r="E401" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="2">
+        <v>46110.16111111111</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402">
+        <v>17</v>
+      </c>
+      <c r="E402" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="2">
+        <v>46110.17152777778</v>
+      </c>
+      <c r="B403">
+        <v>0</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+      <c r="D403">
+        <v>18</v>
+      </c>
+      <c r="E403" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="2">
+        <v>46110.18194444444</v>
+      </c>
+      <c r="B404">
+        <v>0</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404">
+        <v>19</v>
+      </c>
+      <c r="E404" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="2">
+        <v>46110.19236111111</v>
+      </c>
+      <c r="B405">
+        <v>0</v>
+      </c>
+      <c r="C405">
+        <v>0</v>
+      </c>
+      <c r="D405">
+        <v>20</v>
+      </c>
+      <c r="E405" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="2">
+        <v>46110.20277777778</v>
+      </c>
+      <c r="B406">
+        <v>0</v>
+      </c>
+      <c r="C406">
+        <v>0</v>
+      </c>
+      <c r="D406">
+        <v>21</v>
+      </c>
+      <c r="E406" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="2">
+        <v>46110.21319444444</v>
+      </c>
+      <c r="B407">
+        <v>0</v>
+      </c>
+      <c r="C407">
+        <v>0</v>
+      </c>
+      <c r="D407">
+        <v>22</v>
+      </c>
+      <c r="E407" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="2">
+        <v>46110.22361111111</v>
+      </c>
+      <c r="B408">
+        <v>0</v>
+      </c>
+      <c r="C408">
+        <v>0</v>
+      </c>
+      <c r="D408">
+        <v>23</v>
+      </c>
+      <c r="E408" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="2">
+        <v>46110.23402777778</v>
+      </c>
+      <c r="B409">
+        <v>0</v>
+      </c>
+      <c r="C409">
+        <v>0</v>
+      </c>
+      <c r="D409">
+        <v>24</v>
+      </c>
+      <c r="E409" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="2">
+        <v>46110.24444444444</v>
+      </c>
+      <c r="B410">
+        <v>0</v>
+      </c>
+      <c r="C410">
+        <v>0</v>
+      </c>
+      <c r="D410">
+        <v>25</v>
+      </c>
+      <c r="E410" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="2">
+        <v>46110.25486111111</v>
+      </c>
+      <c r="B411">
+        <v>0</v>
+      </c>
+      <c r="C411">
+        <v>0</v>
+      </c>
+      <c r="D411">
+        <v>26</v>
+      </c>
+      <c r="E411" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="2">
+        <v>46110.26527777778</v>
+      </c>
+      <c r="B412">
+        <v>0</v>
+      </c>
+      <c r="C412">
+        <v>0</v>
+      </c>
+      <c r="D412">
+        <v>27</v>
+      </c>
+      <c r="E412" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="2">
+        <v>46110.27569444444</v>
+      </c>
+      <c r="B413">
+        <v>0</v>
+      </c>
+      <c r="C413">
+        <v>0</v>
+      </c>
+      <c r="D413">
+        <v>28</v>
+      </c>
+      <c r="E413" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="2">
+        <v>46110.28611111111</v>
+      </c>
+      <c r="B414">
+        <v>0</v>
+      </c>
+      <c r="C414">
+        <v>0</v>
+      </c>
+      <c r="D414">
+        <v>29</v>
+      </c>
+      <c r="E414" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="2">
+        <v>46110.29652777778</v>
+      </c>
+      <c r="B415">
+        <v>0</v>
+      </c>
+      <c r="C415">
+        <v>0</v>
+      </c>
+      <c r="D415">
+        <v>30</v>
+      </c>
+      <c r="E415" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="2">
+        <v>46110.30694444444</v>
+      </c>
+      <c r="B416">
+        <v>0</v>
+      </c>
+      <c r="C416">
+        <v>0</v>
+      </c>
+      <c r="D416">
+        <v>31</v>
+      </c>
+      <c r="E416" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="2">
+        <v>46110.31736111111</v>
+      </c>
+      <c r="B417">
+        <v>0</v>
+      </c>
+      <c r="C417">
+        <v>0</v>
+      </c>
+      <c r="D417">
+        <v>32</v>
+      </c>
+      <c r="E417" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="2">
+        <v>46110.32777777778</v>
+      </c>
+      <c r="B418">
+        <v>0</v>
+      </c>
+      <c r="C418">
+        <v>0</v>
+      </c>
+      <c r="D418">
+        <v>33</v>
+      </c>
+      <c r="E418" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="2">
+        <v>46110.33819444444</v>
+      </c>
+      <c r="B419">
+        <v>0</v>
+      </c>
+      <c r="C419">
+        <v>0</v>
+      </c>
+      <c r="D419">
+        <v>34</v>
+      </c>
+      <c r="E419" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="2">
+        <v>46110.34861111111</v>
+      </c>
+      <c r="B420">
+        <v>0</v>
+      </c>
+      <c r="C420">
+        <v>0</v>
+      </c>
+      <c r="D420">
+        <v>35</v>
+      </c>
+      <c r="E420" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="2">
+        <v>46110.35902777778</v>
+      </c>
+      <c r="B421">
+        <v>0</v>
+      </c>
+      <c r="C421">
+        <v>0</v>
+      </c>
+      <c r="D421">
+        <v>36</v>
+      </c>
+      <c r="E421" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="2">
+        <v>46110.36944444444</v>
+      </c>
+      <c r="B422">
+        <v>0</v>
+      </c>
+      <c r="C422">
+        <v>0</v>
+      </c>
+      <c r="D422">
+        <v>37</v>
+      </c>
+      <c r="E422" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="2">
+        <v>46110.37986111111</v>
+      </c>
+      <c r="B423">
+        <v>0</v>
+      </c>
+      <c r="C423">
+        <v>0</v>
+      </c>
+      <c r="D423">
+        <v>38</v>
+      </c>
+      <c r="E423" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="2">
+        <v>46110.39027777778</v>
+      </c>
+      <c r="B424">
+        <v>0</v>
+      </c>
+      <c r="C424">
+        <v>0</v>
+      </c>
+      <c r="D424">
+        <v>39</v>
+      </c>
+      <c r="E424" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="2">
+        <v>46110.40069444444</v>
+      </c>
+      <c r="B425">
+        <v>0</v>
+      </c>
+      <c r="C425">
+        <v>0</v>
+      </c>
+      <c r="D425">
+        <v>40</v>
+      </c>
+      <c r="E425" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="2">
+        <v>46110.41111111111</v>
+      </c>
+      <c r="B426">
+        <v>0</v>
+      </c>
+      <c r="C426">
+        <v>0</v>
+      </c>
+      <c r="D426">
+        <v>41</v>
+      </c>
+      <c r="E426" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" s="2">
+        <v>46110.42152777778</v>
+      </c>
+      <c r="B427">
+        <v>0</v>
+      </c>
+      <c r="C427">
+        <v>0</v>
+      </c>
+      <c r="D427">
+        <v>42</v>
+      </c>
+      <c r="E427" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" s="2">
+        <v>46110.43194444444</v>
+      </c>
+      <c r="B428">
+        <v>0</v>
+      </c>
+      <c r="C428">
+        <v>0</v>
+      </c>
+      <c r="D428">
+        <v>43</v>
+      </c>
+      <c r="E428" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" s="2">
+        <v>46110.44236111111</v>
+      </c>
+      <c r="B429">
+        <v>0</v>
+      </c>
+      <c r="C429">
+        <v>0</v>
+      </c>
+      <c r="D429">
+        <v>44</v>
+      </c>
+      <c r="E429" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" s="2">
+        <v>46110.45277777778</v>
+      </c>
+      <c r="B430">
+        <v>0</v>
+      </c>
+      <c r="C430">
+        <v>0</v>
+      </c>
+      <c r="D430">
+        <v>45</v>
+      </c>
+      <c r="E430" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" s="2">
+        <v>46110.46319444444</v>
+      </c>
+      <c r="B431">
+        <v>0</v>
+      </c>
+      <c r="C431">
+        <v>0</v>
+      </c>
+      <c r="D431">
+        <v>46</v>
+      </c>
+      <c r="E431" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" s="2">
+        <v>46110.47361111111</v>
+      </c>
+      <c r="B432">
+        <v>0</v>
+      </c>
+      <c r="C432">
+        <v>0</v>
+      </c>
+      <c r="D432">
+        <v>47</v>
+      </c>
+      <c r="E432" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" s="2">
+        <v>46110.48402777778</v>
+      </c>
+      <c r="B433">
+        <v>0</v>
+      </c>
+      <c r="C433">
+        <v>0</v>
+      </c>
+      <c r="D433">
+        <v>48</v>
+      </c>
+      <c r="E433" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" s="2">
+        <v>46110.49444444444</v>
+      </c>
+      <c r="B434">
+        <v>0</v>
+      </c>
+      <c r="C434">
+        <v>0</v>
+      </c>
+      <c r="D434">
+        <v>49</v>
+      </c>
+      <c r="E434" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" s="2">
+        <v>46110.50486111111</v>
+      </c>
+      <c r="B435">
+        <v>0</v>
+      </c>
+      <c r="C435">
+        <v>0</v>
+      </c>
+      <c r="D435">
+        <v>50</v>
+      </c>
+      <c r="E435" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" s="2">
+        <v>46110.51527777778</v>
+      </c>
+      <c r="B436">
+        <v>0</v>
+      </c>
+      <c r="C436">
+        <v>0</v>
+      </c>
+      <c r="D436">
+        <v>51</v>
+      </c>
+      <c r="E436" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" s="2">
+        <v>46110.52569444444</v>
+      </c>
+      <c r="B437">
+        <v>0</v>
+      </c>
+      <c r="C437">
+        <v>0</v>
+      </c>
+      <c r="D437">
+        <v>52</v>
+      </c>
+      <c r="E437" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" s="2">
+        <v>46110.53611111111</v>
+      </c>
+      <c r="B438">
+        <v>0</v>
+      </c>
+      <c r="C438">
+        <v>0</v>
+      </c>
+      <c r="D438">
+        <v>53</v>
+      </c>
+      <c r="E438" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" s="2">
+        <v>46110.54652777778</v>
+      </c>
+      <c r="B439">
+        <v>0</v>
+      </c>
+      <c r="C439">
+        <v>0</v>
+      </c>
+      <c r="D439">
+        <v>54</v>
+      </c>
+      <c r="E439" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" s="2">
+        <v>46110.55694444444</v>
+      </c>
+      <c r="B440">
+        <v>0</v>
+      </c>
+      <c r="C440">
+        <v>0</v>
+      </c>
+      <c r="D440">
+        <v>55</v>
+      </c>
+      <c r="E440" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" s="2">
+        <v>46110.56736111111</v>
+      </c>
+      <c r="B441">
+        <v>0</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+      <c r="D441">
+        <v>56</v>
+      </c>
+      <c r="E441" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" s="2">
+        <v>46110.57777777778</v>
+      </c>
+      <c r="B442">
+        <v>0</v>
+      </c>
+      <c r="C442">
+        <v>0</v>
+      </c>
+      <c r="D442">
+        <v>57</v>
+      </c>
+      <c r="E442" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" s="2">
+        <v>46110.58819444444</v>
+      </c>
+      <c r="B443">
+        <v>0</v>
+      </c>
+      <c r="C443">
+        <v>0</v>
+      </c>
+      <c r="D443">
+        <v>58</v>
+      </c>
+      <c r="E443" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" s="2">
+        <v>46110.59861111111</v>
+      </c>
+      <c r="B444">
+        <v>0</v>
+      </c>
+      <c r="C444">
+        <v>0</v>
+      </c>
+      <c r="D444">
+        <v>59</v>
+      </c>
+      <c r="E444" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" s="2">
+        <v>46110.60902777778</v>
+      </c>
+      <c r="B445">
+        <v>0</v>
+      </c>
+      <c r="C445">
+        <v>0</v>
+      </c>
+      <c r="D445">
+        <v>60</v>
+      </c>
+      <c r="E445" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" s="2">
+        <v>46110.61944444444</v>
+      </c>
+      <c r="B446">
+        <v>0</v>
+      </c>
+      <c r="C446">
+        <v>0</v>
+      </c>
+      <c r="D446">
+        <v>61</v>
+      </c>
+      <c r="E446" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" s="2">
+        <v>46110.62986111111</v>
+      </c>
+      <c r="B447">
+        <v>0</v>
+      </c>
+      <c r="C447">
+        <v>0</v>
+      </c>
+      <c r="D447">
+        <v>62</v>
+      </c>
+      <c r="E447" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" s="2">
+        <v>46110.64027777778</v>
+      </c>
+      <c r="B448">
+        <v>0</v>
+      </c>
+      <c r="C448">
+        <v>0</v>
+      </c>
+      <c r="D448">
+        <v>63</v>
+      </c>
+      <c r="E448" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" s="2">
+        <v>46110.65069444444</v>
+      </c>
+      <c r="B449">
+        <v>0</v>
+      </c>
+      <c r="C449">
+        <v>0</v>
+      </c>
+      <c r="D449">
+        <v>64</v>
+      </c>
+      <c r="E449" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" s="2">
+        <v>46110.66111111111</v>
+      </c>
+      <c r="B450">
+        <v>0</v>
+      </c>
+      <c r="C450">
+        <v>0</v>
+      </c>
+      <c r="D450">
+        <v>65</v>
+      </c>
+      <c r="E450" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" s="2">
+        <v>46110.67152777778</v>
+      </c>
+      <c r="B451">
+        <v>0</v>
+      </c>
+      <c r="C451">
+        <v>0</v>
+      </c>
+      <c r="D451">
+        <v>66</v>
+      </c>
+      <c r="E451" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" s="2">
+        <v>46110.68194444444</v>
+      </c>
+      <c r="B452">
+        <v>0</v>
+      </c>
+      <c r="C452">
+        <v>0</v>
+      </c>
+      <c r="D452">
+        <v>67</v>
+      </c>
+      <c r="E452" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" s="2">
+        <v>46110.69236111111</v>
+      </c>
+      <c r="B453">
+        <v>0</v>
+      </c>
+      <c r="C453">
+        <v>0</v>
+      </c>
+      <c r="D453">
+        <v>68</v>
+      </c>
+      <c r="E453" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" s="2">
+        <v>46110.70277777778</v>
+      </c>
+      <c r="B454">
+        <v>0</v>
+      </c>
+      <c r="C454">
+        <v>0</v>
+      </c>
+      <c r="D454">
+        <v>69</v>
+      </c>
+      <c r="E454" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" s="2">
+        <v>46110.71319444444</v>
+      </c>
+      <c r="B455">
+        <v>0</v>
+      </c>
+      <c r="C455">
+        <v>0</v>
+      </c>
+      <c r="D455">
+        <v>70</v>
+      </c>
+      <c r="E455" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" s="2">
+        <v>46110.72361111111</v>
+      </c>
+      <c r="B456">
+        <v>0</v>
+      </c>
+      <c r="C456">
+        <v>0</v>
+      </c>
+      <c r="D456">
+        <v>71</v>
+      </c>
+      <c r="E456" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" s="2">
+        <v>46110.73402777778</v>
+      </c>
+      <c r="B457">
+        <v>0</v>
+      </c>
+      <c r="C457">
+        <v>0</v>
+      </c>
+      <c r="D457">
+        <v>72</v>
+      </c>
+      <c r="E457" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" s="2">
+        <v>46110.74444444444</v>
+      </c>
+      <c r="B458">
+        <v>0</v>
+      </c>
+      <c r="C458">
+        <v>0</v>
+      </c>
+      <c r="D458">
+        <v>73</v>
+      </c>
+      <c r="E458" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" s="2">
+        <v>46110.75486111111</v>
+      </c>
+      <c r="B459">
+        <v>0</v>
+      </c>
+      <c r="C459">
+        <v>0</v>
+      </c>
+      <c r="D459">
+        <v>74</v>
+      </c>
+      <c r="E459" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" s="2">
+        <v>46110.76527777778</v>
+      </c>
+      <c r="B460">
+        <v>0</v>
+      </c>
+      <c r="C460">
+        <v>0</v>
+      </c>
+      <c r="D460">
+        <v>75</v>
+      </c>
+      <c r="E460" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" s="2">
+        <v>46110.77569444444</v>
+      </c>
+      <c r="B461">
+        <v>0</v>
+      </c>
+      <c r="C461">
+        <v>0</v>
+      </c>
+      <c r="D461">
+        <v>76</v>
+      </c>
+      <c r="E461" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462" s="2">
+        <v>46110.78611111111</v>
+      </c>
+      <c r="B462">
+        <v>0</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+      <c r="D462">
+        <v>77</v>
+      </c>
+      <c r="E462" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" s="2">
+        <v>46110.79652777778</v>
+      </c>
+      <c r="B463">
+        <v>0</v>
+      </c>
+      <c r="C463">
+        <v>0</v>
+      </c>
+      <c r="D463">
+        <v>78</v>
+      </c>
+      <c r="E463" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" s="2">
+        <v>46110.80694444444</v>
+      </c>
+      <c r="B464">
+        <v>0</v>
+      </c>
+      <c r="C464">
+        <v>0</v>
+      </c>
+      <c r="D464">
+        <v>79</v>
+      </c>
+      <c r="E464" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" s="2">
+        <v>46110.81736111111</v>
+      </c>
+      <c r="B465">
+        <v>0</v>
+      </c>
+      <c r="C465">
+        <v>0</v>
+      </c>
+      <c r="D465">
+        <v>80</v>
+      </c>
+      <c r="E465" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" s="2">
+        <v>46110.82777777778</v>
+      </c>
+      <c r="B466">
+        <v>0</v>
+      </c>
+      <c r="C466">
+        <v>0</v>
+      </c>
+      <c r="D466">
+        <v>81</v>
+      </c>
+      <c r="E466" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467" s="2">
+        <v>46110.83819444444</v>
+      </c>
+      <c r="B467">
+        <v>0</v>
+      </c>
+      <c r="C467">
+        <v>0</v>
+      </c>
+      <c r="D467">
+        <v>82</v>
+      </c>
+      <c r="E467" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468" s="2">
+        <v>46110.84861111111</v>
+      </c>
+      <c r="B468">
+        <v>0</v>
+      </c>
+      <c r="C468">
+        <v>0</v>
+      </c>
+      <c r="D468">
+        <v>83</v>
+      </c>
+      <c r="E468" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469" s="2">
+        <v>46110.85902777778</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+      <c r="C469">
+        <v>0</v>
+      </c>
+      <c r="D469">
+        <v>84</v>
+      </c>
+      <c r="E469" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470" s="2">
+        <v>46110.86944444444</v>
+      </c>
+      <c r="B470">
+        <v>0</v>
+      </c>
+      <c r="C470">
+        <v>0</v>
+      </c>
+      <c r="D470">
+        <v>85</v>
+      </c>
+      <c r="E470" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471" s="2">
+        <v>46110.87986111111</v>
+      </c>
+      <c r="B471">
+        <v>0</v>
+      </c>
+      <c r="C471">
+        <v>0</v>
+      </c>
+      <c r="D471">
+        <v>86</v>
+      </c>
+      <c r="E471" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5">
+      <c r="A472" s="2">
+        <v>46110.89027777778</v>
+      </c>
+      <c r="B472">
+        <v>0</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+      <c r="D472">
+        <v>87</v>
+      </c>
+      <c r="E472" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5">
+      <c r="A473" s="2">
+        <v>46110.90069444444</v>
+      </c>
+      <c r="B473">
+        <v>0</v>
+      </c>
+      <c r="C473">
+        <v>0</v>
+      </c>
+      <c r="D473">
+        <v>88</v>
+      </c>
+      <c r="E473" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5">
+      <c r="A474" s="2">
+        <v>46110.91111111111</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+      <c r="C474">
+        <v>0</v>
+      </c>
+      <c r="D474">
+        <v>89</v>
+      </c>
+      <c r="E474" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475" s="2">
+        <v>46110.92152777778</v>
+      </c>
+      <c r="B475">
+        <v>0</v>
+      </c>
+      <c r="C475">
+        <v>0</v>
+      </c>
+      <c r="D475">
+        <v>90</v>
+      </c>
+      <c r="E475" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5">
+      <c r="A476" s="2">
+        <v>46110.93194444444</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+      <c r="C476">
+        <v>0</v>
+      </c>
+      <c r="D476">
+        <v>91</v>
+      </c>
+      <c r="E476" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5">
+      <c r="A477" s="2">
+        <v>46110.94236111111</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+      <c r="C477">
+        <v>0</v>
+      </c>
+      <c r="D477">
+        <v>92</v>
+      </c>
+      <c r="E477" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5">
+      <c r="A478" s="2">
+        <v>46110.95277777778</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+      <c r="C478">
+        <v>0</v>
+      </c>
+      <c r="D478">
+        <v>93</v>
+      </c>
+      <c r="E478" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5">
+      <c r="A479" s="2">
+        <v>46110.96319444444</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+      <c r="C479">
+        <v>0</v>
+      </c>
+      <c r="D479">
+        <v>94</v>
+      </c>
+      <c r="E479" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5">
+      <c r="A480" s="2">
+        <v>46110.97361111111</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+      <c r="C480">
+        <v>0</v>
+      </c>
+      <c r="D480">
+        <v>95</v>
+      </c>
+      <c r="E480" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5">
+      <c r="A481" s="2">
+        <v>46110.98402777778</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+      <c r="C481">
+        <v>0</v>
+      </c>
+      <c r="D481">
+        <v>96</v>
+      </c>
+      <c r="E481" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5">
+      <c r="A482" s="2">
+        <v>46110.99444444444</v>
+      </c>
+      <c r="B482">
+        <v>0</v>
+      </c>
+      <c r="C482">
+        <v>0</v>
+      </c>
+      <c r="D482">
+        <v>1</v>
+      </c>
+      <c r="E482" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5">
+      <c r="A483" s="2">
+        <v>46111.00486111111</v>
+      </c>
+      <c r="B483">
+        <v>0</v>
+      </c>
+      <c r="C483">
+        <v>0</v>
+      </c>
+      <c r="D483">
+        <v>2</v>
+      </c>
+      <c r="E483" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5">
+      <c r="A484" s="2">
+        <v>46111.01527777778</v>
+      </c>
+      <c r="B484">
+        <v>0</v>
+      </c>
+      <c r="C484">
+        <v>0</v>
+      </c>
+      <c r="D484">
+        <v>3</v>
+      </c>
+      <c r="E484" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5">
+      <c r="A485" s="2">
+        <v>46111.02569444444</v>
+      </c>
+      <c r="B485">
+        <v>0</v>
+      </c>
+      <c r="C485">
+        <v>0</v>
+      </c>
+      <c r="D485">
+        <v>4</v>
+      </c>
+      <c r="E485" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5">
+      <c r="A486" s="2">
+        <v>46111.03611111111</v>
+      </c>
+      <c r="B486">
+        <v>0</v>
+      </c>
+      <c r="C486">
+        <v>0</v>
+      </c>
+      <c r="D486">
+        <v>5</v>
+      </c>
+      <c r="E486" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5">
+      <c r="A487" s="2">
+        <v>46111.03611111111</v>
+      </c>
+      <c r="B487">
+        <v>0</v>
+      </c>
+      <c r="C487">
+        <v>0</v>
+      </c>
+      <c r="D487">
+        <v>6</v>
+      </c>
+      <c r="E487" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5">
+      <c r="A488" s="2">
+        <v>46111.04652777778</v>
+      </c>
+      <c r="B488">
+        <v>0</v>
+      </c>
+      <c r="C488">
+        <v>0</v>
+      </c>
+      <c r="D488">
+        <v>7</v>
+      </c>
+      <c r="E488" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5">
+      <c r="A489" s="2">
+        <v>46111.05694444444</v>
+      </c>
+      <c r="B489">
+        <v>0</v>
+      </c>
+      <c r="C489">
+        <v>0</v>
+      </c>
+      <c r="D489">
+        <v>8</v>
+      </c>
+      <c r="E489" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5">
+      <c r="A490" s="2">
+        <v>46111.06736111111</v>
+      </c>
+      <c r="B490">
+        <v>0</v>
+      </c>
+      <c r="C490">
+        <v>0</v>
+      </c>
+      <c r="D490">
+        <v>9</v>
+      </c>
+      <c r="E490" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5">
+      <c r="A491" s="2">
+        <v>46111.07777777778</v>
+      </c>
+      <c r="B491">
+        <v>0</v>
+      </c>
+      <c r="C491">
+        <v>0</v>
+      </c>
+      <c r="D491">
+        <v>10</v>
+      </c>
+      <c r="E491" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5">
+      <c r="A492" s="2">
+        <v>46111.08819444444</v>
+      </c>
+      <c r="B492">
+        <v>0</v>
+      </c>
+      <c r="C492">
+        <v>0</v>
+      </c>
+      <c r="D492">
+        <v>11</v>
+      </c>
+      <c r="E492" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5">
+      <c r="A493" s="2">
+        <v>46111.09861111111</v>
+      </c>
+      <c r="B493">
+        <v>0</v>
+      </c>
+      <c r="C493">
+        <v>0</v>
+      </c>
+      <c r="D493">
+        <v>12</v>
+      </c>
+      <c r="E493" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5">
+      <c r="A494" s="2">
+        <v>46111.10902777778</v>
+      </c>
+      <c r="B494">
+        <v>0</v>
+      </c>
+      <c r="C494">
+        <v>0</v>
+      </c>
+      <c r="D494">
+        <v>13</v>
+      </c>
+      <c r="E494" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5">
+      <c r="A495" s="2">
+        <v>46111.11944444444</v>
+      </c>
+      <c r="B495">
+        <v>0</v>
+      </c>
+      <c r="C495">
+        <v>0</v>
+      </c>
+      <c r="D495">
+        <v>14</v>
+      </c>
+      <c r="E495" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5">
+      <c r="A496" s="2">
+        <v>46111.12986111111</v>
+      </c>
+      <c r="B496">
+        <v>0</v>
+      </c>
+      <c r="C496">
+        <v>0</v>
+      </c>
+      <c r="D496">
+        <v>15</v>
+      </c>
+      <c r="E496" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5">
+      <c r="A497" s="2">
+        <v>46111.14027777778</v>
+      </c>
+      <c r="B497">
+        <v>0</v>
+      </c>
+      <c r="C497">
+        <v>0</v>
+      </c>
+      <c r="D497">
+        <v>16</v>
+      </c>
+      <c r="E497" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5">
+      <c r="A498" s="2">
+        <v>46111.15069444444</v>
+      </c>
+      <c r="B498">
+        <v>0</v>
+      </c>
+      <c r="C498">
+        <v>0</v>
+      </c>
+      <c r="D498">
+        <v>17</v>
+      </c>
+      <c r="E498" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5">
+      <c r="A499" s="2">
+        <v>46111.16111111111</v>
+      </c>
+      <c r="B499">
+        <v>0</v>
+      </c>
+      <c r="C499">
+        <v>0</v>
+      </c>
+      <c r="D499">
+        <v>18</v>
+      </c>
+      <c r="E499" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5">
+      <c r="A500" s="2">
+        <v>46111.17152777778</v>
+      </c>
+      <c r="B500">
+        <v>0</v>
+      </c>
+      <c r="C500">
+        <v>0</v>
+      </c>
+      <c r="D500">
+        <v>19</v>
+      </c>
+      <c r="E500" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5">
+      <c r="A501" s="2">
+        <v>46111.18194444444</v>
+      </c>
+      <c r="B501">
+        <v>0</v>
+      </c>
+      <c r="C501">
+        <v>0</v>
+      </c>
+      <c r="D501">
+        <v>20</v>
+      </c>
+      <c r="E501" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5">
+      <c r="A502" s="2">
+        <v>46111.19236111111</v>
+      </c>
+      <c r="B502">
+        <v>0</v>
+      </c>
+      <c r="C502">
+        <v>0</v>
+      </c>
+      <c r="D502">
+        <v>21</v>
+      </c>
+      <c r="E502" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5">
+      <c r="A503" s="2">
+        <v>46111.20277777778</v>
+      </c>
+      <c r="B503">
+        <v>0</v>
+      </c>
+      <c r="C503">
+        <v>0</v>
+      </c>
+      <c r="D503">
+        <v>22</v>
+      </c>
+      <c r="E503" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5">
+      <c r="A504" s="2">
+        <v>46111.21319444444</v>
+      </c>
+      <c r="B504">
+        <v>0</v>
+      </c>
+      <c r="C504">
+        <v>0</v>
+      </c>
+      <c r="D504">
+        <v>23</v>
+      </c>
+      <c r="E504" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5">
+      <c r="A505" s="2">
+        <v>46111.22361111111</v>
+      </c>
+      <c r="B505">
+        <v>0</v>
+      </c>
+      <c r="C505">
+        <v>0</v>
+      </c>
+      <c r="D505">
+        <v>24</v>
+      </c>
+      <c r="E505" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5">
+      <c r="A506" s="2">
+        <v>46111.23402777778</v>
+      </c>
+      <c r="B506">
+        <v>0</v>
+      </c>
+      <c r="C506">
+        <v>0</v>
+      </c>
+      <c r="D506">
+        <v>25</v>
+      </c>
+      <c r="E506" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5">
+      <c r="A507" s="2">
+        <v>46111.24444444444</v>
+      </c>
+      <c r="B507">
+        <v>0</v>
+      </c>
+      <c r="C507">
+        <v>0</v>
+      </c>
+      <c r="D507">
+        <v>26</v>
+      </c>
+      <c r="E507" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5">
+      <c r="A508" s="2">
+        <v>46111.25486111111</v>
+      </c>
+      <c r="B508">
+        <v>0</v>
+      </c>
+      <c r="C508">
+        <v>0</v>
+      </c>
+      <c r="D508">
+        <v>27</v>
+      </c>
+      <c r="E508" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5">
+      <c r="A509" s="2">
+        <v>46111.26527777778</v>
+      </c>
+      <c r="B509">
+        <v>0</v>
+      </c>
+      <c r="C509">
+        <v>0</v>
+      </c>
+      <c r="D509">
+        <v>28</v>
+      </c>
+      <c r="E509" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5">
+      <c r="A510" s="2">
+        <v>46111.27569444444</v>
+      </c>
+      <c r="B510">
+        <v>0</v>
+      </c>
+      <c r="C510">
+        <v>0</v>
+      </c>
+      <c r="D510">
+        <v>29</v>
+      </c>
+      <c r="E510" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5">
+      <c r="A511" s="2">
+        <v>46111.28611111111</v>
+      </c>
+      <c r="B511">
+        <v>0</v>
+      </c>
+      <c r="C511">
+        <v>0</v>
+      </c>
+      <c r="D511">
+        <v>30</v>
+      </c>
+      <c r="E511" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5">
+      <c r="A512" s="2">
+        <v>46111.29652777778</v>
+      </c>
+      <c r="B512">
+        <v>0</v>
+      </c>
+      <c r="C512">
+        <v>0</v>
+      </c>
+      <c r="D512">
+        <v>31</v>
+      </c>
+      <c r="E512" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5">
+      <c r="A513" s="2">
+        <v>46111.30694444444</v>
+      </c>
+      <c r="B513">
+        <v>0</v>
+      </c>
+      <c r="C513">
+        <v>0</v>
+      </c>
+      <c r="D513">
+        <v>32</v>
+      </c>
+      <c r="E513" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5">
+      <c r="A514" s="2">
+        <v>46111.31736111111</v>
+      </c>
+      <c r="B514">
+        <v>0</v>
+      </c>
+      <c r="C514">
+        <v>0</v>
+      </c>
+      <c r="D514">
+        <v>33</v>
+      </c>
+      <c r="E514" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5">
+      <c r="A515" s="2">
+        <v>46111.32777777778</v>
+      </c>
+      <c r="B515">
+        <v>0</v>
+      </c>
+      <c r="C515">
+        <v>0</v>
+      </c>
+      <c r="D515">
+        <v>34</v>
+      </c>
+      <c r="E515" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5">
+      <c r="A516" s="2">
+        <v>46111.33819444444</v>
+      </c>
+      <c r="B516">
+        <v>0</v>
+      </c>
+      <c r="C516">
+        <v>0</v>
+      </c>
+      <c r="D516">
+        <v>35</v>
+      </c>
+      <c r="E516" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5">
+      <c r="A517" s="2">
+        <v>46111.34861111111</v>
+      </c>
+      <c r="B517">
+        <v>0</v>
+      </c>
+      <c r="C517">
+        <v>0</v>
+      </c>
+      <c r="D517">
+        <v>36</v>
+      </c>
+      <c r="E517" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5">
+      <c r="A518" s="2">
+        <v>46111.35902777778</v>
+      </c>
+      <c r="B518">
+        <v>0</v>
+      </c>
+      <c r="C518">
+        <v>0</v>
+      </c>
+      <c r="D518">
+        <v>37</v>
+      </c>
+      <c r="E518" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5">
+      <c r="A519" s="2">
+        <v>46111.36944444444</v>
+      </c>
+      <c r="B519">
+        <v>0</v>
+      </c>
+      <c r="C519">
+        <v>0</v>
+      </c>
+      <c r="D519">
+        <v>38</v>
+      </c>
+      <c r="E519" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5">
+      <c r="A520" s="2">
+        <v>46111.37986111111</v>
+      </c>
+      <c r="B520">
+        <v>0</v>
+      </c>
+      <c r="C520">
+        <v>0</v>
+      </c>
+      <c r="D520">
+        <v>39</v>
+      </c>
+      <c r="E520" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5">
+      <c r="A521" s="2">
+        <v>46111.39027777778</v>
+      </c>
+      <c r="B521">
+        <v>0</v>
+      </c>
+      <c r="C521">
+        <v>0</v>
+      </c>
+      <c r="D521">
+        <v>40</v>
+      </c>
+      <c r="E521" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5">
+      <c r="A522" s="2">
+        <v>46111.40069444444</v>
+      </c>
+      <c r="B522">
+        <v>0</v>
+      </c>
+      <c r="C522">
+        <v>0</v>
+      </c>
+      <c r="D522">
+        <v>41</v>
+      </c>
+      <c r="E522" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5">
+      <c r="A523" s="2">
+        <v>46111.41111111111</v>
+      </c>
+      <c r="B523">
+        <v>0</v>
+      </c>
+      <c r="C523">
+        <v>0</v>
+      </c>
+      <c r="D523">
+        <v>42</v>
+      </c>
+      <c r="E523" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5">
+      <c r="A524" s="2">
+        <v>46111.42152777778</v>
+      </c>
+      <c r="B524">
+        <v>0</v>
+      </c>
+      <c r="C524">
+        <v>0</v>
+      </c>
+      <c r="D524">
+        <v>43</v>
+      </c>
+      <c r="E524" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5">
+      <c r="A525" s="2">
+        <v>46111.43194444444</v>
+      </c>
+      <c r="B525">
+        <v>0</v>
+      </c>
+      <c r="C525">
+        <v>0</v>
+      </c>
+      <c r="D525">
+        <v>44</v>
+      </c>
+      <c r="E525" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5">
+      <c r="A526" s="2">
+        <v>46111.44236111111</v>
+      </c>
+      <c r="B526">
+        <v>0</v>
+      </c>
+      <c r="C526">
+        <v>0</v>
+      </c>
+      <c r="D526">
+        <v>45</v>
+      </c>
+      <c r="E526" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5">
+      <c r="A527" s="2">
+        <v>46111.45277777778</v>
+      </c>
+      <c r="B527">
+        <v>0</v>
+      </c>
+      <c r="C527">
+        <v>0</v>
+      </c>
+      <c r="D527">
+        <v>46</v>
+      </c>
+      <c r="E527" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5">
+      <c r="A528" s="2">
+        <v>46111.46319444444</v>
+      </c>
+      <c r="B528">
+        <v>0</v>
+      </c>
+      <c r="C528">
+        <v>0</v>
+      </c>
+      <c r="D528">
+        <v>47</v>
+      </c>
+      <c r="E528" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5">
+      <c r="A529" s="2">
+        <v>46111.47361111111</v>
+      </c>
+      <c r="B529">
+        <v>0</v>
+      </c>
+      <c r="C529">
+        <v>0</v>
+      </c>
+      <c r="D529">
+        <v>48</v>
+      </c>
+      <c r="E529" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5">
+      <c r="A530" s="2">
+        <v>46111.48402777778</v>
+      </c>
+      <c r="B530">
+        <v>0</v>
+      </c>
+      <c r="C530">
+        <v>0</v>
+      </c>
+      <c r="D530">
+        <v>49</v>
+      </c>
+      <c r="E530" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5">
+      <c r="A531" s="2">
+        <v>46111.49444444444</v>
+      </c>
+      <c r="B531">
+        <v>0</v>
+      </c>
+      <c r="C531">
+        <v>0</v>
+      </c>
+      <c r="D531">
+        <v>50</v>
+      </c>
+      <c r="E531" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5">
+      <c r="A532" s="2">
+        <v>46111.50486111111</v>
+      </c>
+      <c r="B532">
+        <v>0</v>
+      </c>
+      <c r="C532">
+        <v>0</v>
+      </c>
+      <c r="D532">
+        <v>51</v>
+      </c>
+      <c r="E532" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5">
+      <c r="A533" s="2">
+        <v>46111.51527777778</v>
+      </c>
+      <c r="B533">
+        <v>0</v>
+      </c>
+      <c r="C533">
+        <v>0</v>
+      </c>
+      <c r="D533">
+        <v>52</v>
+      </c>
+      <c r="E533" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5">
+      <c r="A534" s="2">
+        <v>46111.52569444444</v>
+      </c>
+      <c r="B534">
+        <v>0</v>
+      </c>
+      <c r="C534">
+        <v>0</v>
+      </c>
+      <c r="D534">
+        <v>53</v>
+      </c>
+      <c r="E534" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5">
+      <c r="A535" s="2">
+        <v>46111.53611111111</v>
+      </c>
+      <c r="B535">
+        <v>0</v>
+      </c>
+      <c r="C535">
+        <v>0</v>
+      </c>
+      <c r="D535">
+        <v>54</v>
+      </c>
+      <c r="E535" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5">
+      <c r="A536" s="2">
+        <v>46111.54652777778</v>
+      </c>
+      <c r="B536">
+        <v>0</v>
+      </c>
+      <c r="C536">
+        <v>0</v>
+      </c>
+      <c r="D536">
+        <v>55</v>
+      </c>
+      <c r="E536" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5">
+      <c r="A537" s="2">
+        <v>46111.55694444444</v>
+      </c>
+      <c r="B537">
+        <v>0</v>
+      </c>
+      <c r="C537">
+        <v>0</v>
+      </c>
+      <c r="D537">
+        <v>56</v>
+      </c>
+      <c r="E537" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5">
+      <c r="A538" s="2">
+        <v>46111.56736111111</v>
+      </c>
+      <c r="B538">
+        <v>0</v>
+      </c>
+      <c r="C538">
+        <v>0</v>
+      </c>
+      <c r="D538">
+        <v>57</v>
+      </c>
+      <c r="E538" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5">
+      <c r="A539" s="2">
+        <v>46111.57777777778</v>
+      </c>
+      <c r="B539">
+        <v>0</v>
+      </c>
+      <c r="C539">
+        <v>0</v>
+      </c>
+      <c r="D539">
+        <v>58</v>
+      </c>
+      <c r="E539" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5">
+      <c r="A540" s="2">
+        <v>46111.58819444444</v>
+      </c>
+      <c r="B540">
+        <v>0</v>
+      </c>
+      <c r="C540">
+        <v>0</v>
+      </c>
+      <c r="D540">
+        <v>59</v>
+      </c>
+      <c r="E540" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5">
+      <c r="A541" s="2">
+        <v>46111.59861111111</v>
+      </c>
+      <c r="B541">
+        <v>0</v>
+      </c>
+      <c r="C541">
+        <v>0</v>
+      </c>
+      <c r="D541">
+        <v>60</v>
+      </c>
+      <c r="E541" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5">
+      <c r="A542" s="2">
+        <v>46111.60902777778</v>
+      </c>
+      <c r="B542">
+        <v>0</v>
+      </c>
+      <c r="C542">
+        <v>0</v>
+      </c>
+      <c r="D542">
+        <v>61</v>
+      </c>
+      <c r="E542" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5">
+      <c r="A543" s="2">
+        <v>46111.61944444444</v>
+      </c>
+      <c r="B543">
+        <v>0</v>
+      </c>
+      <c r="C543">
+        <v>0</v>
+      </c>
+      <c r="D543">
+        <v>62</v>
+      </c>
+      <c r="E543" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5">
+      <c r="A544" s="2">
+        <v>46111.62986111111</v>
+      </c>
+      <c r="B544">
+        <v>0</v>
+      </c>
+      <c r="C544">
+        <v>0</v>
+      </c>
+      <c r="D544">
+        <v>63</v>
+      </c>
+      <c r="E544" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5">
+      <c r="A545" s="2">
+        <v>46111.64027777778</v>
+      </c>
+      <c r="B545">
+        <v>0</v>
+      </c>
+      <c r="C545">
+        <v>0</v>
+      </c>
+      <c r="D545">
+        <v>64</v>
+      </c>
+      <c r="E545" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5">
+      <c r="A546" s="2">
+        <v>46111.65069444444</v>
+      </c>
+      <c r="B546">
+        <v>0</v>
+      </c>
+      <c r="C546">
+        <v>0</v>
+      </c>
+      <c r="D546">
+        <v>65</v>
+      </c>
+      <c r="E546" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5">
+      <c r="A547" s="2">
+        <v>46111.66111111111</v>
+      </c>
+      <c r="B547">
+        <v>0</v>
+      </c>
+      <c r="C547">
+        <v>0</v>
+      </c>
+      <c r="D547">
+        <v>66</v>
+      </c>
+      <c r="E547" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5">
+      <c r="A548" s="2">
+        <v>46111.67152777778</v>
+      </c>
+      <c r="B548">
+        <v>0</v>
+      </c>
+      <c r="C548">
+        <v>0</v>
+      </c>
+      <c r="D548">
+        <v>67</v>
+      </c>
+      <c r="E548" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5">
+      <c r="A549" s="2">
+        <v>46111.68194444444</v>
+      </c>
+      <c r="B549">
+        <v>0</v>
+      </c>
+      <c r="C549">
+        <v>0</v>
+      </c>
+      <c r="D549">
+        <v>68</v>
+      </c>
+      <c r="E549" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5">
+      <c r="A550" s="2">
+        <v>46111.69236111111</v>
+      </c>
+      <c r="B550">
+        <v>0</v>
+      </c>
+      <c r="C550">
+        <v>0</v>
+      </c>
+      <c r="D550">
+        <v>69</v>
+      </c>
+      <c r="E550" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5">
+      <c r="A551" s="2">
+        <v>46111.70277777778</v>
+      </c>
+      <c r="B551">
+        <v>0</v>
+      </c>
+      <c r="C551">
+        <v>0</v>
+      </c>
+      <c r="D551">
+        <v>70</v>
+      </c>
+      <c r="E551" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5">
+      <c r="A552" s="2">
+        <v>46111.71319444444</v>
+      </c>
+      <c r="B552">
+        <v>0</v>
+      </c>
+      <c r="C552">
+        <v>0</v>
+      </c>
+      <c r="D552">
+        <v>71</v>
+      </c>
+      <c r="E552" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5">
+      <c r="A553" s="2">
+        <v>46111.72361111111</v>
+      </c>
+      <c r="B553">
+        <v>0</v>
+      </c>
+      <c r="C553">
+        <v>0</v>
+      </c>
+      <c r="D553">
+        <v>72</v>
+      </c>
+      <c r="E553" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5">
+      <c r="A554" s="2">
+        <v>46111.73402777778</v>
+      </c>
+      <c r="B554">
+        <v>0</v>
+      </c>
+      <c r="C554">
+        <v>0</v>
+      </c>
+      <c r="D554">
+        <v>73</v>
+      </c>
+      <c r="E554" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5">
+      <c r="A555" s="2">
+        <v>46111.74444444444</v>
+      </c>
+      <c r="B555">
+        <v>0</v>
+      </c>
+      <c r="C555">
+        <v>0</v>
+      </c>
+      <c r="D555">
+        <v>74</v>
+      </c>
+      <c r="E555" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5">
+      <c r="A556" s="2">
+        <v>46111.75486111111</v>
+      </c>
+      <c r="B556">
+        <v>0</v>
+      </c>
+      <c r="C556">
+        <v>0</v>
+      </c>
+      <c r="D556">
+        <v>75</v>
+      </c>
+      <c r="E556" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5">
+      <c r="A557" s="2">
+        <v>46111.76527777778</v>
+      </c>
+      <c r="B557">
+        <v>0</v>
+      </c>
+      <c r="C557">
+        <v>0</v>
+      </c>
+      <c r="D557">
+        <v>76</v>
+      </c>
+      <c r="E557" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5">
+      <c r="A558" s="2">
+        <v>46111.77569444444</v>
+      </c>
+      <c r="B558">
+        <v>0</v>
+      </c>
+      <c r="C558">
+        <v>0</v>
+      </c>
+      <c r="D558">
+        <v>77</v>
+      </c>
+      <c r="E558" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5">
+      <c r="A559" s="2">
+        <v>46111.78611111111</v>
+      </c>
+      <c r="B559">
+        <v>0</v>
+      </c>
+      <c r="C559">
+        <v>0</v>
+      </c>
+      <c r="D559">
+        <v>78</v>
+      </c>
+      <c r="E559" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5">
+      <c r="A560" s="2">
+        <v>46111.79652777778</v>
+      </c>
+      <c r="B560">
+        <v>0</v>
+      </c>
+      <c r="C560">
+        <v>0</v>
+      </c>
+      <c r="D560">
+        <v>79</v>
+      </c>
+      <c r="E560" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5">
+      <c r="A561" s="2">
+        <v>46111.80694444444</v>
+      </c>
+      <c r="B561">
+        <v>0</v>
+      </c>
+      <c r="C561">
+        <v>0</v>
+      </c>
+      <c r="D561">
+        <v>80</v>
+      </c>
+      <c r="E561" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5">
+      <c r="A562" s="2">
+        <v>46111.81736111111</v>
+      </c>
+      <c r="B562">
+        <v>0</v>
+      </c>
+      <c r="C562">
+        <v>0</v>
+      </c>
+      <c r="D562">
+        <v>81</v>
+      </c>
+      <c r="E562" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5">
+      <c r="A563" s="2">
+        <v>46111.82777777778</v>
+      </c>
+      <c r="B563">
+        <v>0</v>
+      </c>
+      <c r="C563">
+        <v>0</v>
+      </c>
+      <c r="D563">
+        <v>82</v>
+      </c>
+      <c r="E563" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5">
+      <c r="A564" s="2">
+        <v>46111.83819444444</v>
+      </c>
+      <c r="B564">
+        <v>0</v>
+      </c>
+      <c r="C564">
+        <v>0</v>
+      </c>
+      <c r="D564">
+        <v>83</v>
+      </c>
+      <c r="E564" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5">
+      <c r="A565" s="2">
+        <v>46111.84861111111</v>
+      </c>
+      <c r="B565">
+        <v>0</v>
+      </c>
+      <c r="C565">
+        <v>0</v>
+      </c>
+      <c r="D565">
+        <v>84</v>
+      </c>
+      <c r="E565" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5">
+      <c r="A566" s="2">
+        <v>46111.85902777778</v>
+      </c>
+      <c r="B566">
+        <v>0</v>
+      </c>
+      <c r="C566">
+        <v>0</v>
+      </c>
+      <c r="D566">
+        <v>85</v>
+      </c>
+      <c r="E566" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5">
+      <c r="A567" s="2">
+        <v>46111.86944444444</v>
+      </c>
+      <c r="B567">
+        <v>0</v>
+      </c>
+      <c r="C567">
+        <v>0</v>
+      </c>
+      <c r="D567">
+        <v>86</v>
+      </c>
+      <c r="E567" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5">
+      <c r="A568" s="2">
+        <v>46111.87986111111</v>
+      </c>
+      <c r="B568">
+        <v>0</v>
+      </c>
+      <c r="C568">
+        <v>0</v>
+      </c>
+      <c r="D568">
+        <v>87</v>
+      </c>
+      <c r="E568" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5">
+      <c r="A569" s="2">
+        <v>46111.89027777778</v>
+      </c>
+      <c r="B569">
+        <v>0</v>
+      </c>
+      <c r="C569">
+        <v>0</v>
+      </c>
+      <c r="D569">
+        <v>88</v>
+      </c>
+      <c r="E569" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="570" spans="1:5">
+      <c r="A570" s="2">
+        <v>46111.90069444444</v>
+      </c>
+      <c r="B570">
+        <v>0</v>
+      </c>
+      <c r="C570">
+        <v>0</v>
+      </c>
+      <c r="D570">
+        <v>89</v>
+      </c>
+      <c r="E570" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="571" spans="1:5">
+      <c r="A571" s="2">
+        <v>46111.91111111111</v>
+      </c>
+      <c r="B571">
+        <v>0</v>
+      </c>
+      <c r="C571">
+        <v>0</v>
+      </c>
+      <c r="D571">
+        <v>90</v>
+      </c>
+      <c r="E571" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5">
+      <c r="A572" s="2">
+        <v>46111.92152777778</v>
+      </c>
+      <c r="B572">
+        <v>0</v>
+      </c>
+      <c r="C572">
+        <v>0</v>
+      </c>
+      <c r="D572">
+        <v>91</v>
+      </c>
+      <c r="E572" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5">
+      <c r="A573" s="2">
+        <v>46111.93194444444</v>
+      </c>
+      <c r="B573">
+        <v>0</v>
+      </c>
+      <c r="C573">
+        <v>0</v>
+      </c>
+      <c r="D573">
+        <v>92</v>
+      </c>
+      <c r="E573" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="574" spans="1:5">
+      <c r="A574" s="2">
+        <v>46111.94236111111</v>
+      </c>
+      <c r="B574">
+        <v>0</v>
+      </c>
+      <c r="C574">
+        <v>0</v>
+      </c>
+      <c r="D574">
+        <v>93</v>
+      </c>
+      <c r="E574" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="575" spans="1:5">
+      <c r="A575" s="2">
+        <v>46111.95277777778</v>
+      </c>
+      <c r="B575">
+        <v>0</v>
+      </c>
+      <c r="C575">
+        <v>0</v>
+      </c>
+      <c r="D575">
+        <v>94</v>
+      </c>
+      <c r="E575" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="576" spans="1:5">
+      <c r="A576" s="2">
+        <v>46111.96319444444</v>
+      </c>
+      <c r="B576">
+        <v>0</v>
+      </c>
+      <c r="C576">
+        <v>0</v>
+      </c>
+      <c r="D576">
+        <v>95</v>
+      </c>
+      <c r="E576" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="577" spans="1:5">
+      <c r="A577" s="2">
+        <v>46111.97361111111</v>
+      </c>
+      <c r="B577">
+        <v>0</v>
+      </c>
+      <c r="C577">
+        <v>0</v>
+      </c>
+      <c r="D577">
+        <v>96</v>
+      </c>
+      <c r="E577" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5">
+      <c r="A578" s="2">
+        <v>46111.98402777778</v>
+      </c>
+      <c r="B578">
+        <v>0</v>
+      </c>
+      <c r="C578">
+        <v>0</v>
+      </c>
+      <c r="D578">
+        <v>1</v>
+      </c>
+      <c r="E578" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="579" spans="1:5">
+      <c r="A579" s="2">
+        <v>46111.99444444444</v>
+      </c>
+      <c r="B579">
+        <v>0</v>
+      </c>
+      <c r="C579">
+        <v>0</v>
+      </c>
+      <c r="D579">
+        <v>2</v>
+      </c>
+      <c r="E579" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="580" spans="1:5">
+      <c r="A580" s="2">
+        <v>46112.00486111111</v>
+      </c>
+      <c r="B580">
+        <v>0</v>
+      </c>
+      <c r="C580">
+        <v>0</v>
+      </c>
+      <c r="D580">
+        <v>3</v>
+      </c>
+      <c r="E580" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="581" spans="1:5">
+      <c r="A581" s="2">
+        <v>46112.01527777778</v>
+      </c>
+      <c r="B581">
+        <v>0</v>
+      </c>
+      <c r="C581">
+        <v>0</v>
+      </c>
+      <c r="D581">
+        <v>4</v>
+      </c>
+      <c r="E581" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="582" spans="1:5">
+      <c r="A582" s="2">
+        <v>46112.02569444444</v>
+      </c>
+      <c r="B582">
+        <v>0</v>
+      </c>
+      <c r="C582">
+        <v>0</v>
+      </c>
+      <c r="D582">
+        <v>5</v>
+      </c>
+      <c r="E582" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5">
+      <c r="A583" s="2">
+        <v>46112.03611111111</v>
+      </c>
+      <c r="B583">
+        <v>0</v>
+      </c>
+      <c r="C583">
+        <v>0</v>
+      </c>
+      <c r="D583">
+        <v>6</v>
+      </c>
+      <c r="E583" t="s">
+        <v>581</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,583 +31,583 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.04.20261</t>
-  </si>
-  <si>
-    <t>09.04.20262</t>
-  </si>
-  <si>
-    <t>09.04.20263</t>
-  </si>
-  <si>
-    <t>09.04.20264</t>
-  </si>
-  <si>
-    <t>09.04.20265</t>
-  </si>
-  <si>
-    <t>09.04.20266</t>
-  </si>
-  <si>
-    <t>09.04.20267</t>
-  </si>
-  <si>
-    <t>09.04.20268</t>
-  </si>
-  <si>
-    <t>09.04.20269</t>
-  </si>
-  <si>
-    <t>09.04.202610</t>
-  </si>
-  <si>
-    <t>09.04.202611</t>
-  </si>
-  <si>
-    <t>09.04.202612</t>
-  </si>
-  <si>
-    <t>09.04.202613</t>
-  </si>
-  <si>
-    <t>09.04.202614</t>
-  </si>
-  <si>
-    <t>09.04.202615</t>
-  </si>
-  <si>
-    <t>09.04.202616</t>
-  </si>
-  <si>
-    <t>09.04.202617</t>
-  </si>
-  <si>
-    <t>09.04.202618</t>
-  </si>
-  <si>
-    <t>09.04.202619</t>
-  </si>
-  <si>
-    <t>09.04.202620</t>
-  </si>
-  <si>
-    <t>09.04.202621</t>
-  </si>
-  <si>
-    <t>09.04.202622</t>
-  </si>
-  <si>
-    <t>09.04.202623</t>
-  </si>
-  <si>
-    <t>09.04.202624</t>
-  </si>
-  <si>
-    <t>09.04.202625</t>
-  </si>
-  <si>
-    <t>09.04.202626</t>
-  </si>
-  <si>
-    <t>09.04.202627</t>
-  </si>
-  <si>
-    <t>09.04.202628</t>
-  </si>
-  <si>
-    <t>09.04.202629</t>
-  </si>
-  <si>
-    <t>09.04.202630</t>
-  </si>
-  <si>
-    <t>09.04.202631</t>
-  </si>
-  <si>
-    <t>09.04.202632</t>
-  </si>
-  <si>
-    <t>09.04.202633</t>
-  </si>
-  <si>
-    <t>09.04.202634</t>
-  </si>
-  <si>
-    <t>09.04.202635</t>
-  </si>
-  <si>
-    <t>09.04.202636</t>
-  </si>
-  <si>
-    <t>09.04.202637</t>
-  </si>
-  <si>
-    <t>09.04.202638</t>
-  </si>
-  <si>
-    <t>09.04.202639</t>
-  </si>
-  <si>
-    <t>09.04.202640</t>
-  </si>
-  <si>
-    <t>09.04.202641</t>
-  </si>
-  <si>
-    <t>09.04.202642</t>
-  </si>
-  <si>
-    <t>09.04.202643</t>
-  </si>
-  <si>
-    <t>09.04.202644</t>
-  </si>
-  <si>
-    <t>09.04.202645</t>
-  </si>
-  <si>
-    <t>09.04.202646</t>
-  </si>
-  <si>
-    <t>09.04.202647</t>
-  </si>
-  <si>
-    <t>09.04.202648</t>
-  </si>
-  <si>
-    <t>09.04.202649</t>
-  </si>
-  <si>
-    <t>09.04.202650</t>
-  </si>
-  <si>
-    <t>09.04.202651</t>
-  </si>
-  <si>
-    <t>09.04.202652</t>
-  </si>
-  <si>
-    <t>09.04.202653</t>
-  </si>
-  <si>
-    <t>09.04.202654</t>
-  </si>
-  <si>
-    <t>09.04.202655</t>
-  </si>
-  <si>
-    <t>09.04.202656</t>
-  </si>
-  <si>
-    <t>09.04.202657</t>
-  </si>
-  <si>
-    <t>09.04.202658</t>
-  </si>
-  <si>
-    <t>09.04.202659</t>
-  </si>
-  <si>
-    <t>09.04.202660</t>
-  </si>
-  <si>
-    <t>09.04.202661</t>
-  </si>
-  <si>
-    <t>09.04.202662</t>
-  </si>
-  <si>
-    <t>09.04.202663</t>
-  </si>
-  <si>
-    <t>09.04.202664</t>
-  </si>
-  <si>
-    <t>09.04.202665</t>
-  </si>
-  <si>
-    <t>09.04.202666</t>
-  </si>
-  <si>
-    <t>09.04.202667</t>
-  </si>
-  <si>
-    <t>09.04.202668</t>
-  </si>
-  <si>
-    <t>09.04.202669</t>
-  </si>
-  <si>
-    <t>09.04.202670</t>
-  </si>
-  <si>
-    <t>09.04.202671</t>
-  </si>
-  <si>
-    <t>09.04.202672</t>
-  </si>
-  <si>
-    <t>09.04.202673</t>
-  </si>
-  <si>
-    <t>09.04.202674</t>
-  </si>
-  <si>
-    <t>09.04.202675</t>
-  </si>
-  <si>
-    <t>09.04.202676</t>
-  </si>
-  <si>
-    <t>09.04.202677</t>
-  </si>
-  <si>
-    <t>09.04.202678</t>
-  </si>
-  <si>
-    <t>09.04.202679</t>
-  </si>
-  <si>
-    <t>09.04.202680</t>
-  </si>
-  <si>
-    <t>09.04.202681</t>
-  </si>
-  <si>
-    <t>09.04.202682</t>
-  </si>
-  <si>
-    <t>09.04.202683</t>
-  </si>
-  <si>
-    <t>09.04.202684</t>
-  </si>
-  <si>
-    <t>09.04.202685</t>
-  </si>
-  <si>
-    <t>09.04.202686</t>
-  </si>
-  <si>
-    <t>09.04.202687</t>
-  </si>
-  <si>
-    <t>09.04.202688</t>
-  </si>
-  <si>
-    <t>09.04.202689</t>
-  </si>
-  <si>
-    <t>09.04.202690</t>
-  </si>
-  <si>
-    <t>09.04.202691</t>
-  </si>
-  <si>
-    <t>09.04.202692</t>
-  </si>
-  <si>
-    <t>09.04.202693</t>
-  </si>
-  <si>
-    <t>10.04.202694</t>
-  </si>
-  <si>
-    <t>10.04.202695</t>
-  </si>
-  <si>
-    <t>10.04.202696</t>
-  </si>
-  <si>
-    <t>10.04.20261</t>
-  </si>
-  <si>
-    <t>10.04.20262</t>
-  </si>
-  <si>
-    <t>10.04.20263</t>
-  </si>
-  <si>
-    <t>10.04.20264</t>
-  </si>
-  <si>
-    <t>10.04.20265</t>
-  </si>
-  <si>
-    <t>10.04.20266</t>
-  </si>
-  <si>
-    <t>10.04.20267</t>
-  </si>
-  <si>
-    <t>10.04.20268</t>
-  </si>
-  <si>
-    <t>10.04.20269</t>
-  </si>
-  <si>
-    <t>10.04.202610</t>
-  </si>
-  <si>
-    <t>10.04.202611</t>
-  </si>
-  <si>
-    <t>10.04.202612</t>
-  </si>
-  <si>
-    <t>10.04.202613</t>
-  </si>
-  <si>
-    <t>10.04.202614</t>
-  </si>
-  <si>
-    <t>10.04.202615</t>
-  </si>
-  <si>
-    <t>10.04.202616</t>
-  </si>
-  <si>
-    <t>10.04.202617</t>
-  </si>
-  <si>
-    <t>10.04.202618</t>
-  </si>
-  <si>
-    <t>10.04.202619</t>
-  </si>
-  <si>
-    <t>10.04.202620</t>
-  </si>
-  <si>
-    <t>10.04.202621</t>
-  </si>
-  <si>
-    <t>10.04.202622</t>
-  </si>
-  <si>
-    <t>10.04.202623</t>
-  </si>
-  <si>
-    <t>10.04.202624</t>
-  </si>
-  <si>
-    <t>10.04.202625</t>
-  </si>
-  <si>
-    <t>10.04.202626</t>
-  </si>
-  <si>
-    <t>10.04.202627</t>
-  </si>
-  <si>
-    <t>10.04.202628</t>
-  </si>
-  <si>
-    <t>10.04.202629</t>
-  </si>
-  <si>
-    <t>10.04.202630</t>
-  </si>
-  <si>
-    <t>10.04.202631</t>
-  </si>
-  <si>
-    <t>10.04.202632</t>
-  </si>
-  <si>
-    <t>10.04.202633</t>
-  </si>
-  <si>
-    <t>10.04.202634</t>
-  </si>
-  <si>
-    <t>10.04.202635</t>
-  </si>
-  <si>
-    <t>10.04.202636</t>
-  </si>
-  <si>
-    <t>10.04.202637</t>
-  </si>
-  <si>
-    <t>10.04.202638</t>
-  </si>
-  <si>
-    <t>10.04.202639</t>
-  </si>
-  <si>
-    <t>10.04.202640</t>
-  </si>
-  <si>
-    <t>10.04.202641</t>
-  </si>
-  <si>
-    <t>10.04.202642</t>
-  </si>
-  <si>
-    <t>10.04.202643</t>
-  </si>
-  <si>
-    <t>10.04.202644</t>
-  </si>
-  <si>
-    <t>10.04.202645</t>
-  </si>
-  <si>
-    <t>10.04.202646</t>
-  </si>
-  <si>
-    <t>10.04.202647</t>
-  </si>
-  <si>
-    <t>10.04.202648</t>
-  </si>
-  <si>
-    <t>10.04.202649</t>
-  </si>
-  <si>
-    <t>10.04.202650</t>
-  </si>
-  <si>
-    <t>10.04.202651</t>
-  </si>
-  <si>
-    <t>10.04.202652</t>
-  </si>
-  <si>
-    <t>10.04.202653</t>
-  </si>
-  <si>
-    <t>10.04.202654</t>
-  </si>
-  <si>
-    <t>10.04.202655</t>
-  </si>
-  <si>
-    <t>10.04.202656</t>
-  </si>
-  <si>
-    <t>10.04.202657</t>
-  </si>
-  <si>
-    <t>10.04.202658</t>
-  </si>
-  <si>
-    <t>10.04.202659</t>
-  </si>
-  <si>
-    <t>10.04.202660</t>
-  </si>
-  <si>
-    <t>10.04.202661</t>
-  </si>
-  <si>
-    <t>10.04.202662</t>
-  </si>
-  <si>
-    <t>10.04.202663</t>
-  </si>
-  <si>
-    <t>10.04.202664</t>
-  </si>
-  <si>
-    <t>10.04.202665</t>
-  </si>
-  <si>
-    <t>10.04.202666</t>
-  </si>
-  <si>
-    <t>10.04.202667</t>
-  </si>
-  <si>
-    <t>10.04.202668</t>
-  </si>
-  <si>
-    <t>10.04.202669</t>
-  </si>
-  <si>
-    <t>10.04.202670</t>
-  </si>
-  <si>
-    <t>10.04.202671</t>
-  </si>
-  <si>
-    <t>10.04.202672</t>
-  </si>
-  <si>
-    <t>10.04.202673</t>
-  </si>
-  <si>
-    <t>10.04.202674</t>
-  </si>
-  <si>
-    <t>10.04.202675</t>
-  </si>
-  <si>
-    <t>10.04.202676</t>
-  </si>
-  <si>
-    <t>10.04.202677</t>
-  </si>
-  <si>
-    <t>10.04.202678</t>
-  </si>
-  <si>
-    <t>10.04.202679</t>
-  </si>
-  <si>
-    <t>10.04.202680</t>
-  </si>
-  <si>
-    <t>10.04.202681</t>
-  </si>
-  <si>
-    <t>10.04.202682</t>
-  </si>
-  <si>
-    <t>10.04.202683</t>
-  </si>
-  <si>
-    <t>10.04.202684</t>
-  </si>
-  <si>
-    <t>10.04.202685</t>
-  </si>
-  <si>
-    <t>10.04.202686</t>
-  </si>
-  <si>
-    <t>10.04.202687</t>
-  </si>
-  <si>
-    <t>10.04.202688</t>
-  </si>
-  <si>
-    <t>10.04.202689</t>
-  </si>
-  <si>
-    <t>10.04.202690</t>
-  </si>
-  <si>
-    <t>10.04.202691</t>
-  </si>
-  <si>
-    <t>10.04.202692</t>
-  </si>
-  <si>
-    <t>10.04.202693</t>
-  </si>
-  <si>
-    <t>11.04.202695</t>
-  </si>
-  <si>
-    <t>11.04.202696</t>
-  </si>
-  <si>
-    <t>11.04.20261</t>
-  </si>
-  <si>
-    <t>11.04.20262</t>
+    <t>16.04.20261</t>
+  </si>
+  <si>
+    <t>16.04.20262</t>
+  </si>
+  <si>
+    <t>16.04.20263</t>
+  </si>
+  <si>
+    <t>16.04.20264</t>
+  </si>
+  <si>
+    <t>16.04.20265</t>
+  </si>
+  <si>
+    <t>16.04.20266</t>
+  </si>
+  <si>
+    <t>16.04.20267</t>
+  </si>
+  <si>
+    <t>16.04.20268</t>
+  </si>
+  <si>
+    <t>16.04.20269</t>
+  </si>
+  <si>
+    <t>16.04.202610</t>
+  </si>
+  <si>
+    <t>16.04.202611</t>
+  </si>
+  <si>
+    <t>16.04.202612</t>
+  </si>
+  <si>
+    <t>16.04.202613</t>
+  </si>
+  <si>
+    <t>16.04.202614</t>
+  </si>
+  <si>
+    <t>16.04.202615</t>
+  </si>
+  <si>
+    <t>16.04.202616</t>
+  </si>
+  <si>
+    <t>16.04.202617</t>
+  </si>
+  <si>
+    <t>16.04.202618</t>
+  </si>
+  <si>
+    <t>16.04.202619</t>
+  </si>
+  <si>
+    <t>16.04.202620</t>
+  </si>
+  <si>
+    <t>16.04.202621</t>
+  </si>
+  <si>
+    <t>16.04.202622</t>
+  </si>
+  <si>
+    <t>16.04.202623</t>
+  </si>
+  <si>
+    <t>16.04.202624</t>
+  </si>
+  <si>
+    <t>16.04.202625</t>
+  </si>
+  <si>
+    <t>16.04.202626</t>
+  </si>
+  <si>
+    <t>16.04.202627</t>
+  </si>
+  <si>
+    <t>16.04.202628</t>
+  </si>
+  <si>
+    <t>16.04.202629</t>
+  </si>
+  <si>
+    <t>16.04.202630</t>
+  </si>
+  <si>
+    <t>16.04.202631</t>
+  </si>
+  <si>
+    <t>16.04.202632</t>
+  </si>
+  <si>
+    <t>16.04.202633</t>
+  </si>
+  <si>
+    <t>16.04.202634</t>
+  </si>
+  <si>
+    <t>16.04.202635</t>
+  </si>
+  <si>
+    <t>16.04.202636</t>
+  </si>
+  <si>
+    <t>16.04.202637</t>
+  </si>
+  <si>
+    <t>16.04.202638</t>
+  </si>
+  <si>
+    <t>16.04.202639</t>
+  </si>
+  <si>
+    <t>16.04.202640</t>
+  </si>
+  <si>
+    <t>16.04.202641</t>
+  </si>
+  <si>
+    <t>16.04.202642</t>
+  </si>
+  <si>
+    <t>16.04.202643</t>
+  </si>
+  <si>
+    <t>16.04.202644</t>
+  </si>
+  <si>
+    <t>16.04.202645</t>
+  </si>
+  <si>
+    <t>16.04.202646</t>
+  </si>
+  <si>
+    <t>16.04.202647</t>
+  </si>
+  <si>
+    <t>16.04.202648</t>
+  </si>
+  <si>
+    <t>16.04.202649</t>
+  </si>
+  <si>
+    <t>16.04.202650</t>
+  </si>
+  <si>
+    <t>16.04.202651</t>
+  </si>
+  <si>
+    <t>16.04.202652</t>
+  </si>
+  <si>
+    <t>16.04.202653</t>
+  </si>
+  <si>
+    <t>16.04.202654</t>
+  </si>
+  <si>
+    <t>16.04.202655</t>
+  </si>
+  <si>
+    <t>16.04.202656</t>
+  </si>
+  <si>
+    <t>16.04.202657</t>
+  </si>
+  <si>
+    <t>16.04.202658</t>
+  </si>
+  <si>
+    <t>16.04.202659</t>
+  </si>
+  <si>
+    <t>16.04.202660</t>
+  </si>
+  <si>
+    <t>16.04.202661</t>
+  </si>
+  <si>
+    <t>16.04.202662</t>
+  </si>
+  <si>
+    <t>16.04.202663</t>
+  </si>
+  <si>
+    <t>16.04.202664</t>
+  </si>
+  <si>
+    <t>16.04.202665</t>
+  </si>
+  <si>
+    <t>16.04.202666</t>
+  </si>
+  <si>
+    <t>16.04.202667</t>
+  </si>
+  <si>
+    <t>16.04.202668</t>
+  </si>
+  <si>
+    <t>16.04.202669</t>
+  </si>
+  <si>
+    <t>16.04.202670</t>
+  </si>
+  <si>
+    <t>16.04.202671</t>
+  </si>
+  <si>
+    <t>16.04.202672</t>
+  </si>
+  <si>
+    <t>16.04.202673</t>
+  </si>
+  <si>
+    <t>16.04.202674</t>
+  </si>
+  <si>
+    <t>16.04.202675</t>
+  </si>
+  <si>
+    <t>16.04.202676</t>
+  </si>
+  <si>
+    <t>16.04.202677</t>
+  </si>
+  <si>
+    <t>16.04.202678</t>
+  </si>
+  <si>
+    <t>16.04.202679</t>
+  </si>
+  <si>
+    <t>16.04.202680</t>
+  </si>
+  <si>
+    <t>16.04.202681</t>
+  </si>
+  <si>
+    <t>16.04.202682</t>
+  </si>
+  <si>
+    <t>16.04.202683</t>
+  </si>
+  <si>
+    <t>16.04.202684</t>
+  </si>
+  <si>
+    <t>16.04.202685</t>
+  </si>
+  <si>
+    <t>16.04.202686</t>
+  </si>
+  <si>
+    <t>16.04.202687</t>
+  </si>
+  <si>
+    <t>16.04.202688</t>
+  </si>
+  <si>
+    <t>16.04.202689</t>
+  </si>
+  <si>
+    <t>16.04.202690</t>
+  </si>
+  <si>
+    <t>16.04.202691</t>
+  </si>
+  <si>
+    <t>16.04.202692</t>
+  </si>
+  <si>
+    <t>16.04.202693</t>
+  </si>
+  <si>
+    <t>17.04.202694</t>
+  </si>
+  <si>
+    <t>17.04.202695</t>
+  </si>
+  <si>
+    <t>17.04.202696</t>
+  </si>
+  <si>
+    <t>17.04.20261</t>
+  </si>
+  <si>
+    <t>17.04.20262</t>
+  </si>
+  <si>
+    <t>17.04.20263</t>
+  </si>
+  <si>
+    <t>17.04.20264</t>
+  </si>
+  <si>
+    <t>17.04.20265</t>
+  </si>
+  <si>
+    <t>17.04.20266</t>
+  </si>
+  <si>
+    <t>17.04.20267</t>
+  </si>
+  <si>
+    <t>17.04.20268</t>
+  </si>
+  <si>
+    <t>17.04.20269</t>
+  </si>
+  <si>
+    <t>17.04.202610</t>
+  </si>
+  <si>
+    <t>17.04.202611</t>
+  </si>
+  <si>
+    <t>17.04.202612</t>
+  </si>
+  <si>
+    <t>17.04.202613</t>
+  </si>
+  <si>
+    <t>17.04.202614</t>
+  </si>
+  <si>
+    <t>17.04.202615</t>
+  </si>
+  <si>
+    <t>17.04.202616</t>
+  </si>
+  <si>
+    <t>17.04.202617</t>
+  </si>
+  <si>
+    <t>17.04.202618</t>
+  </si>
+  <si>
+    <t>17.04.202619</t>
+  </si>
+  <si>
+    <t>17.04.202620</t>
+  </si>
+  <si>
+    <t>17.04.202621</t>
+  </si>
+  <si>
+    <t>17.04.202622</t>
+  </si>
+  <si>
+    <t>17.04.202623</t>
+  </si>
+  <si>
+    <t>17.04.202624</t>
+  </si>
+  <si>
+    <t>17.04.202625</t>
+  </si>
+  <si>
+    <t>17.04.202626</t>
+  </si>
+  <si>
+    <t>17.04.202627</t>
+  </si>
+  <si>
+    <t>17.04.202628</t>
+  </si>
+  <si>
+    <t>17.04.202629</t>
+  </si>
+  <si>
+    <t>17.04.202630</t>
+  </si>
+  <si>
+    <t>17.04.202631</t>
+  </si>
+  <si>
+    <t>17.04.202632</t>
+  </si>
+  <si>
+    <t>17.04.202633</t>
+  </si>
+  <si>
+    <t>17.04.202634</t>
+  </si>
+  <si>
+    <t>17.04.202635</t>
+  </si>
+  <si>
+    <t>17.04.202636</t>
+  </si>
+  <si>
+    <t>17.04.202637</t>
+  </si>
+  <si>
+    <t>17.04.202638</t>
+  </si>
+  <si>
+    <t>17.04.202639</t>
+  </si>
+  <si>
+    <t>17.04.202640</t>
+  </si>
+  <si>
+    <t>17.04.202641</t>
+  </si>
+  <si>
+    <t>17.04.202642</t>
+  </si>
+  <si>
+    <t>17.04.202643</t>
+  </si>
+  <si>
+    <t>17.04.202644</t>
+  </si>
+  <si>
+    <t>17.04.202645</t>
+  </si>
+  <si>
+    <t>17.04.202646</t>
+  </si>
+  <si>
+    <t>17.04.202647</t>
+  </si>
+  <si>
+    <t>17.04.202648</t>
+  </si>
+  <si>
+    <t>17.04.202649</t>
+  </si>
+  <si>
+    <t>17.04.202650</t>
+  </si>
+  <si>
+    <t>17.04.202651</t>
+  </si>
+  <si>
+    <t>17.04.202652</t>
+  </si>
+  <si>
+    <t>17.04.202653</t>
+  </si>
+  <si>
+    <t>17.04.202654</t>
+  </si>
+  <si>
+    <t>17.04.202655</t>
+  </si>
+  <si>
+    <t>17.04.202656</t>
+  </si>
+  <si>
+    <t>17.04.202657</t>
+  </si>
+  <si>
+    <t>17.04.202658</t>
+  </si>
+  <si>
+    <t>17.04.202659</t>
+  </si>
+  <si>
+    <t>17.04.202660</t>
+  </si>
+  <si>
+    <t>17.04.202661</t>
+  </si>
+  <si>
+    <t>17.04.202662</t>
+  </si>
+  <si>
+    <t>17.04.202663</t>
+  </si>
+  <si>
+    <t>17.04.202664</t>
+  </si>
+  <si>
+    <t>17.04.202665</t>
+  </si>
+  <si>
+    <t>17.04.202666</t>
+  </si>
+  <si>
+    <t>17.04.202667</t>
+  </si>
+  <si>
+    <t>17.04.202668</t>
+  </si>
+  <si>
+    <t>17.04.202669</t>
+  </si>
+  <si>
+    <t>17.04.202670</t>
+  </si>
+  <si>
+    <t>17.04.202671</t>
+  </si>
+  <si>
+    <t>17.04.202672</t>
+  </si>
+  <si>
+    <t>17.04.202673</t>
+  </si>
+  <si>
+    <t>17.04.202674</t>
+  </si>
+  <si>
+    <t>17.04.202675</t>
+  </si>
+  <si>
+    <t>17.04.202676</t>
+  </si>
+  <si>
+    <t>17.04.202677</t>
+  </si>
+  <si>
+    <t>17.04.202678</t>
+  </si>
+  <si>
+    <t>17.04.202679</t>
+  </si>
+  <si>
+    <t>17.04.202680</t>
+  </si>
+  <si>
+    <t>17.04.202681</t>
+  </si>
+  <si>
+    <t>17.04.202682</t>
+  </si>
+  <si>
+    <t>17.04.202683</t>
+  </si>
+  <si>
+    <t>17.04.202684</t>
+  </si>
+  <si>
+    <t>17.04.202685</t>
+  </si>
+  <si>
+    <t>17.04.202686</t>
+  </si>
+  <si>
+    <t>17.04.202687</t>
+  </si>
+  <si>
+    <t>17.04.202688</t>
+  </si>
+  <si>
+    <t>17.04.202689</t>
+  </si>
+  <si>
+    <t>17.04.202690</t>
+  </si>
+  <si>
+    <t>17.04.202691</t>
+  </si>
+  <si>
+    <t>17.04.202692</t>
+  </si>
+  <si>
+    <t>17.04.202693</t>
+  </si>
+  <si>
+    <t>18.04.202695</t>
+  </si>
+  <si>
+    <t>18.04.202696</t>
+  </si>
+  <si>
+    <t>18.04.20261</t>
+  </si>
+  <si>
+    <t>18.04.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46121.03611111111</v>
+        <v>46128.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46121.04652777778</v>
+        <v>46128.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46121.05694444444</v>
+        <v>46128.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46121.06736111111</v>
+        <v>46128.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46121.07777777778</v>
+        <v>46128.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46121.08819444444</v>
+        <v>46128.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46121.09861111111</v>
+        <v>46128.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46121.10902777778</v>
+        <v>46128.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46121.11944444444</v>
+        <v>46128.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46121.12986111111</v>
+        <v>46128.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46121.14027777778</v>
+        <v>46128.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46121.15069444444</v>
+        <v>46128.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46121.16111111111</v>
+        <v>46128.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46121.17152777778</v>
+        <v>46128.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46121.18194444444</v>
+        <v>46128.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46121.19236111111</v>
+        <v>46128.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46121.20277777778</v>
+        <v>46128.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46121.21319444444</v>
+        <v>46128.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46121.22361111111</v>
+        <v>46128.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46121.23402777778</v>
+        <v>46128.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46121.24444444444</v>
+        <v>46128.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46121.25486111111</v>
+        <v>46128.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46121.26527777778</v>
+        <v>46128.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46121.27569444444</v>
+        <v>46128.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46121.28611111111</v>
+        <v>46128.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46121.29652777778</v>
+        <v>46128.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46121.30694444444</v>
+        <v>46128.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46121.31736111111</v>
+        <v>46128.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46121.32777777778</v>
+        <v>46128.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46121.33819444444</v>
+        <v>46128.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46121.34861111111</v>
+        <v>46128.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46121.35902777778</v>
+        <v>46128.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46121.36944444444</v>
+        <v>46128.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46121.37986111111</v>
+        <v>46128.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46121.39027777778</v>
+        <v>46128.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46121.40069444444</v>
+        <v>46128.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46121.41111111111</v>
+        <v>46128.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46121.42152777778</v>
+        <v>46128.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46121.43194444444</v>
+        <v>46128.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46121.44236111111</v>
+        <v>46128.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46121.45277777778</v>
+        <v>46128.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46121.46319444444</v>
+        <v>46128.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46121.47361111111</v>
+        <v>46128.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46121.48402777778</v>
+        <v>46128.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46121.49444444444</v>
+        <v>46128.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46121.50486111111</v>
+        <v>46128.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46121.51527777778</v>
+        <v>46128.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46121.52569444444</v>
+        <v>46128.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46121.53611111111</v>
+        <v>46128.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46121.54652777778</v>
+        <v>46128.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46121.55694444444</v>
+        <v>46128.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46121.56736111111</v>
+        <v>46128.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46121.57777777778</v>
+        <v>46128.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46121.58819444444</v>
+        <v>46128.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46121.59861111111</v>
+        <v>46128.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46121.60902777778</v>
+        <v>46128.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46121.61944444444</v>
+        <v>46128.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46121.62986111111</v>
+        <v>46128.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46121.64027777778</v>
+        <v>46128.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46121.65069444444</v>
+        <v>46128.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46121.66111111111</v>
+        <v>46128.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46121.67152777778</v>
+        <v>46128.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46121.68194444444</v>
+        <v>46128.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46121.69236111111</v>
+        <v>46128.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46121.70277777778</v>
+        <v>46128.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46121.71319444444</v>
+        <v>46128.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46121.72361111111</v>
+        <v>46128.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46121.73402777778</v>
+        <v>46128.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46121.74444444444</v>
+        <v>46128.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46121.75486111111</v>
+        <v>46128.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46121.76527777778</v>
+        <v>46128.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46121.77569444444</v>
+        <v>46128.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46121.78611111111</v>
+        <v>46128.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46121.79652777778</v>
+        <v>46128.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46121.80694444444</v>
+        <v>46128.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46121.81736111111</v>
+        <v>46128.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46121.82777777778</v>
+        <v>46128.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46121.83819444444</v>
+        <v>46128.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46121.84861111111</v>
+        <v>46128.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46121.85902777778</v>
+        <v>46128.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46121.86944444444</v>
+        <v>46128.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46121.87986111111</v>
+        <v>46128.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46121.89027777778</v>
+        <v>46128.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46121.90069444444</v>
+        <v>46128.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46121.91111111111</v>
+        <v>46128.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46121.92152777778</v>
+        <v>46128.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46121.93194444444</v>
+        <v>46128.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46121.94236111111</v>
+        <v>46128.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46121.95277777778</v>
+        <v>46128.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46121.96319444444</v>
+        <v>46128.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46121.97361111111</v>
+        <v>46128.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46121.98402777778</v>
+        <v>46128.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46121.99444444444</v>
+        <v>46128.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46122.00486111111</v>
+        <v>46129.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46122.01527777778</v>
+        <v>46129.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46122.02569444444</v>
+        <v>46129.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46122.03611111111</v>
+        <v>46129.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46122.03611111111</v>
+        <v>46129.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46122.04652777778</v>
+        <v>46129.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46122.05694444444</v>
+        <v>46129.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46122.06736111111</v>
+        <v>46129.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46122.07777777778</v>
+        <v>46129.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46122.08819444444</v>
+        <v>46129.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46122.09861111111</v>
+        <v>46129.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46122.10902777778</v>
+        <v>46129.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46122.11944444444</v>
+        <v>46129.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46122.12986111111</v>
+        <v>46129.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46122.14027777778</v>
+        <v>46129.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46122.15069444444</v>
+        <v>46129.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46122.16111111111</v>
+        <v>46129.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46122.17152777778</v>
+        <v>46129.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46122.18194444444</v>
+        <v>46129.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46122.19236111111</v>
+        <v>46129.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46122.20277777778</v>
+        <v>46129.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46122.21319444444</v>
+        <v>46129.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46122.22361111111</v>
+        <v>46129.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46122.23402777778</v>
+        <v>46129.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46122.24444444444</v>
+        <v>46129.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46122.25486111111</v>
+        <v>46129.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46122.26527777778</v>
+        <v>46129.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46122.27569444444</v>
+        <v>46129.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46122.28611111111</v>
+        <v>46129.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46122.29652777778</v>
+        <v>46129.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46122.30694444444</v>
+        <v>46129.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46122.31736111111</v>
+        <v>46129.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46122.32777777778</v>
+        <v>46129.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46122.33819444444</v>
+        <v>46129.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46122.34861111111</v>
+        <v>46129.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46122.35902777778</v>
+        <v>46129.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46122.36944444444</v>
+        <v>46129.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46122.37986111111</v>
+        <v>46129.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46122.39027777778</v>
+        <v>46129.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46122.40069444444</v>
+        <v>46129.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46122.41111111111</v>
+        <v>46129.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46122.42152777778</v>
+        <v>46129.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46122.43194444444</v>
+        <v>46129.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46122.44236111111</v>
+        <v>46129.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46122.45277777778</v>
+        <v>46129.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46122.46319444444</v>
+        <v>46129.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46122.47361111111</v>
+        <v>46129.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46122.48402777778</v>
+        <v>46129.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46122.49444444444</v>
+        <v>46129.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46122.50486111111</v>
+        <v>46129.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46122.51527777778</v>
+        <v>46129.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46122.52569444444</v>
+        <v>46129.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46122.53611111111</v>
+        <v>46129.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46122.54652777778</v>
+        <v>46129.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46122.55694444444</v>
+        <v>46129.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46122.56736111111</v>
+        <v>46129.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46122.57777777778</v>
+        <v>46129.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46122.58819444444</v>
+        <v>46129.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46122.59861111111</v>
+        <v>46129.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46122.60902777778</v>
+        <v>46129.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46122.61944444444</v>
+        <v>46129.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46122.62986111111</v>
+        <v>46129.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46122.64027777778</v>
+        <v>46129.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46122.65069444444</v>
+        <v>46129.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46122.66111111111</v>
+        <v>46129.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46122.67152777778</v>
+        <v>46129.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46122.68194444444</v>
+        <v>46129.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46122.69236111111</v>
+        <v>46129.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46122.70277777778</v>
+        <v>46129.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46122.71319444444</v>
+        <v>46129.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46122.72361111111</v>
+        <v>46129.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46122.73402777778</v>
+        <v>46129.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46122.74444444444</v>
+        <v>46129.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46122.75486111111</v>
+        <v>46129.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46122.76527777778</v>
+        <v>46129.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46122.77569444444</v>
+        <v>46129.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46122.78611111111</v>
+        <v>46129.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46122.79652777778</v>
+        <v>46129.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46122.80694444444</v>
+        <v>46129.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46122.81736111111</v>
+        <v>46129.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46122.82777777778</v>
+        <v>46129.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46122.83819444444</v>
+        <v>46129.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46122.84861111111</v>
+        <v>46129.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46122.85902777778</v>
+        <v>46129.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46122.86944444444</v>
+        <v>46129.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46122.87986111111</v>
+        <v>46129.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46122.89027777778</v>
+        <v>46129.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46122.90069444444</v>
+        <v>46129.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46122.91111111111</v>
+        <v>46129.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46122.92152777778</v>
+        <v>46129.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46122.93194444444</v>
+        <v>46129.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46122.94236111111</v>
+        <v>46129.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46122.95277777778</v>
+        <v>46129.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46122.96319444444</v>
+        <v>46129.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46122.97361111111</v>
+        <v>46129.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46122.98402777778</v>
+        <v>46129.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46122.99444444444</v>
+        <v>46129.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46123.00486111111</v>
+        <v>46130.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46123.01527777778</v>
+        <v>46130.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46123.02569444444</v>
+        <v>46130.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46123.03611111111</v>
+        <v>46130.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="390">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>16.04.20261</t>
-  </si>
-  <si>
-    <t>16.04.20262</t>
-  </si>
-  <si>
-    <t>16.04.20263</t>
-  </si>
-  <si>
-    <t>16.04.20264</t>
-  </si>
-  <si>
-    <t>16.04.20265</t>
-  </si>
-  <si>
-    <t>16.04.20266</t>
-  </si>
-  <si>
-    <t>16.04.20267</t>
-  </si>
-  <si>
-    <t>16.04.20268</t>
-  </si>
-  <si>
-    <t>16.04.20269</t>
-  </si>
-  <si>
-    <t>16.04.202610</t>
-  </si>
-  <si>
-    <t>16.04.202611</t>
-  </si>
-  <si>
-    <t>16.04.202612</t>
-  </si>
-  <si>
-    <t>16.04.202613</t>
-  </si>
-  <si>
-    <t>16.04.202614</t>
-  </si>
-  <si>
-    <t>16.04.202615</t>
-  </si>
-  <si>
-    <t>16.04.202616</t>
-  </si>
-  <si>
-    <t>16.04.202617</t>
-  </si>
-  <si>
-    <t>16.04.202618</t>
-  </si>
-  <si>
-    <t>16.04.202619</t>
-  </si>
-  <si>
-    <t>16.04.202620</t>
-  </si>
-  <si>
-    <t>16.04.202621</t>
-  </si>
-  <si>
-    <t>16.04.202622</t>
-  </si>
-  <si>
-    <t>16.04.202623</t>
-  </si>
-  <si>
-    <t>16.04.202624</t>
-  </si>
-  <si>
-    <t>16.04.202625</t>
-  </si>
-  <si>
-    <t>16.04.202626</t>
-  </si>
-  <si>
-    <t>16.04.202627</t>
-  </si>
-  <si>
-    <t>16.04.202628</t>
-  </si>
-  <si>
-    <t>16.04.202629</t>
-  </si>
-  <si>
-    <t>16.04.202630</t>
-  </si>
-  <si>
-    <t>16.04.202631</t>
-  </si>
-  <si>
-    <t>16.04.202632</t>
-  </si>
-  <si>
-    <t>16.04.202633</t>
-  </si>
-  <si>
-    <t>16.04.202634</t>
-  </si>
-  <si>
-    <t>16.04.202635</t>
-  </si>
-  <si>
-    <t>16.04.202636</t>
-  </si>
-  <si>
-    <t>16.04.202637</t>
-  </si>
-  <si>
-    <t>16.04.202638</t>
-  </si>
-  <si>
-    <t>16.04.202639</t>
-  </si>
-  <si>
-    <t>16.04.202640</t>
-  </si>
-  <si>
-    <t>16.04.202641</t>
-  </si>
-  <si>
-    <t>16.04.202642</t>
-  </si>
-  <si>
-    <t>16.04.202643</t>
-  </si>
-  <si>
-    <t>16.04.202644</t>
-  </si>
-  <si>
-    <t>16.04.202645</t>
-  </si>
-  <si>
-    <t>16.04.202646</t>
-  </si>
-  <si>
-    <t>16.04.202647</t>
-  </si>
-  <si>
-    <t>16.04.202648</t>
-  </si>
-  <si>
-    <t>16.04.202649</t>
-  </si>
-  <si>
-    <t>16.04.202650</t>
-  </si>
-  <si>
-    <t>16.04.202651</t>
-  </si>
-  <si>
-    <t>16.04.202652</t>
-  </si>
-  <si>
-    <t>16.04.202653</t>
-  </si>
-  <si>
-    <t>16.04.202654</t>
-  </si>
-  <si>
-    <t>16.04.202655</t>
-  </si>
-  <si>
-    <t>16.04.202656</t>
-  </si>
-  <si>
-    <t>16.04.202657</t>
-  </si>
-  <si>
-    <t>16.04.202658</t>
-  </si>
-  <si>
-    <t>16.04.202659</t>
-  </si>
-  <si>
-    <t>16.04.202660</t>
-  </si>
-  <si>
-    <t>16.04.202661</t>
-  </si>
-  <si>
-    <t>16.04.202662</t>
-  </si>
-  <si>
-    <t>16.04.202663</t>
-  </si>
-  <si>
-    <t>16.04.202664</t>
-  </si>
-  <si>
-    <t>16.04.202665</t>
-  </si>
-  <si>
-    <t>16.04.202666</t>
-  </si>
-  <si>
-    <t>16.04.202667</t>
-  </si>
-  <si>
-    <t>16.04.202668</t>
-  </si>
-  <si>
-    <t>16.04.202669</t>
-  </si>
-  <si>
-    <t>16.04.202670</t>
-  </si>
-  <si>
-    <t>16.04.202671</t>
-  </si>
-  <si>
-    <t>16.04.202672</t>
-  </si>
-  <si>
-    <t>16.04.202673</t>
-  </si>
-  <si>
-    <t>16.04.202674</t>
-  </si>
-  <si>
-    <t>16.04.202675</t>
-  </si>
-  <si>
-    <t>16.04.202676</t>
-  </si>
-  <si>
-    <t>16.04.202677</t>
-  </si>
-  <si>
-    <t>16.04.202678</t>
-  </si>
-  <si>
-    <t>16.04.202679</t>
-  </si>
-  <si>
-    <t>16.04.202680</t>
-  </si>
-  <si>
-    <t>16.04.202681</t>
-  </si>
-  <si>
-    <t>16.04.202682</t>
-  </si>
-  <si>
-    <t>16.04.202683</t>
-  </si>
-  <si>
-    <t>16.04.202684</t>
-  </si>
-  <si>
-    <t>16.04.202685</t>
-  </si>
-  <si>
-    <t>16.04.202686</t>
-  </si>
-  <si>
-    <t>16.04.202687</t>
-  </si>
-  <si>
-    <t>16.04.202688</t>
-  </si>
-  <si>
-    <t>16.04.202689</t>
-  </si>
-  <si>
-    <t>16.04.202690</t>
-  </si>
-  <si>
-    <t>16.04.202691</t>
-  </si>
-  <si>
-    <t>16.04.202692</t>
-  </si>
-  <si>
-    <t>16.04.202693</t>
-  </si>
-  <si>
-    <t>17.04.202694</t>
-  </si>
-  <si>
-    <t>17.04.202695</t>
-  </si>
-  <si>
-    <t>17.04.202696</t>
-  </si>
-  <si>
     <t>17.04.20261</t>
   </si>
   <si>
@@ -598,6 +310,9 @@
     <t>17.04.202693</t>
   </si>
   <si>
+    <t>18.04.202694</t>
+  </si>
+  <si>
     <t>18.04.202695</t>
   </si>
   <si>
@@ -608,6 +323,867 @@
   </si>
   <si>
     <t>18.04.20262</t>
+  </si>
+  <si>
+    <t>18.04.20263</t>
+  </si>
+  <si>
+    <t>18.04.20264</t>
+  </si>
+  <si>
+    <t>18.04.20265</t>
+  </si>
+  <si>
+    <t>18.04.20266</t>
+  </si>
+  <si>
+    <t>18.04.20267</t>
+  </si>
+  <si>
+    <t>18.04.20268</t>
+  </si>
+  <si>
+    <t>18.04.20269</t>
+  </si>
+  <si>
+    <t>18.04.202610</t>
+  </si>
+  <si>
+    <t>18.04.202611</t>
+  </si>
+  <si>
+    <t>18.04.202612</t>
+  </si>
+  <si>
+    <t>18.04.202613</t>
+  </si>
+  <si>
+    <t>18.04.202614</t>
+  </si>
+  <si>
+    <t>18.04.202615</t>
+  </si>
+  <si>
+    <t>18.04.202616</t>
+  </si>
+  <si>
+    <t>18.04.202617</t>
+  </si>
+  <si>
+    <t>18.04.202618</t>
+  </si>
+  <si>
+    <t>18.04.202619</t>
+  </si>
+  <si>
+    <t>18.04.202620</t>
+  </si>
+  <si>
+    <t>18.04.202621</t>
+  </si>
+  <si>
+    <t>18.04.202622</t>
+  </si>
+  <si>
+    <t>18.04.202623</t>
+  </si>
+  <si>
+    <t>18.04.202624</t>
+  </si>
+  <si>
+    <t>18.04.202625</t>
+  </si>
+  <si>
+    <t>18.04.202626</t>
+  </si>
+  <si>
+    <t>18.04.202627</t>
+  </si>
+  <si>
+    <t>18.04.202628</t>
+  </si>
+  <si>
+    <t>18.04.202629</t>
+  </si>
+  <si>
+    <t>18.04.202630</t>
+  </si>
+  <si>
+    <t>18.04.202631</t>
+  </si>
+  <si>
+    <t>18.04.202632</t>
+  </si>
+  <si>
+    <t>18.04.202633</t>
+  </si>
+  <si>
+    <t>18.04.202634</t>
+  </si>
+  <si>
+    <t>18.04.202635</t>
+  </si>
+  <si>
+    <t>18.04.202636</t>
+  </si>
+  <si>
+    <t>18.04.202637</t>
+  </si>
+  <si>
+    <t>18.04.202638</t>
+  </si>
+  <si>
+    <t>18.04.202639</t>
+  </si>
+  <si>
+    <t>18.04.202640</t>
+  </si>
+  <si>
+    <t>18.04.202641</t>
+  </si>
+  <si>
+    <t>18.04.202642</t>
+  </si>
+  <si>
+    <t>18.04.202643</t>
+  </si>
+  <si>
+    <t>18.04.202644</t>
+  </si>
+  <si>
+    <t>18.04.202645</t>
+  </si>
+  <si>
+    <t>18.04.202646</t>
+  </si>
+  <si>
+    <t>18.04.202647</t>
+  </si>
+  <si>
+    <t>18.04.202648</t>
+  </si>
+  <si>
+    <t>18.04.202649</t>
+  </si>
+  <si>
+    <t>18.04.202650</t>
+  </si>
+  <si>
+    <t>18.04.202651</t>
+  </si>
+  <si>
+    <t>18.04.202652</t>
+  </si>
+  <si>
+    <t>18.04.202653</t>
+  </si>
+  <si>
+    <t>18.04.202654</t>
+  </si>
+  <si>
+    <t>18.04.202655</t>
+  </si>
+  <si>
+    <t>18.04.202656</t>
+  </si>
+  <si>
+    <t>18.04.202657</t>
+  </si>
+  <si>
+    <t>18.04.202658</t>
+  </si>
+  <si>
+    <t>18.04.202659</t>
+  </si>
+  <si>
+    <t>18.04.202660</t>
+  </si>
+  <si>
+    <t>18.04.202661</t>
+  </si>
+  <si>
+    <t>18.04.202662</t>
+  </si>
+  <si>
+    <t>18.04.202663</t>
+  </si>
+  <si>
+    <t>18.04.202664</t>
+  </si>
+  <si>
+    <t>18.04.202665</t>
+  </si>
+  <si>
+    <t>18.04.202666</t>
+  </si>
+  <si>
+    <t>18.04.202667</t>
+  </si>
+  <si>
+    <t>18.04.202668</t>
+  </si>
+  <si>
+    <t>18.04.202669</t>
+  </si>
+  <si>
+    <t>18.04.202670</t>
+  </si>
+  <si>
+    <t>18.04.202671</t>
+  </si>
+  <si>
+    <t>18.04.202672</t>
+  </si>
+  <si>
+    <t>18.04.202673</t>
+  </si>
+  <si>
+    <t>18.04.202674</t>
+  </si>
+  <si>
+    <t>18.04.202675</t>
+  </si>
+  <si>
+    <t>18.04.202676</t>
+  </si>
+  <si>
+    <t>18.04.202677</t>
+  </si>
+  <si>
+    <t>18.04.202678</t>
+  </si>
+  <si>
+    <t>18.04.202679</t>
+  </si>
+  <si>
+    <t>18.04.202680</t>
+  </si>
+  <si>
+    <t>18.04.202681</t>
+  </si>
+  <si>
+    <t>18.04.202682</t>
+  </si>
+  <si>
+    <t>18.04.202683</t>
+  </si>
+  <si>
+    <t>18.04.202684</t>
+  </si>
+  <si>
+    <t>18.04.202685</t>
+  </si>
+  <si>
+    <t>18.04.202686</t>
+  </si>
+  <si>
+    <t>18.04.202687</t>
+  </si>
+  <si>
+    <t>18.04.202688</t>
+  </si>
+  <si>
+    <t>18.04.202689</t>
+  </si>
+  <si>
+    <t>18.04.202690</t>
+  </si>
+  <si>
+    <t>18.04.202691</t>
+  </si>
+  <si>
+    <t>18.04.202692</t>
+  </si>
+  <si>
+    <t>18.04.202693</t>
+  </si>
+  <si>
+    <t>19.04.202695</t>
+  </si>
+  <si>
+    <t>19.04.202696</t>
+  </si>
+  <si>
+    <t>19.04.20261</t>
+  </si>
+  <si>
+    <t>19.04.20262</t>
+  </si>
+  <si>
+    <t>19.04.20263</t>
+  </si>
+  <si>
+    <t>19.04.20264</t>
+  </si>
+  <si>
+    <t>19.04.20265</t>
+  </si>
+  <si>
+    <t>19.04.20266</t>
+  </si>
+  <si>
+    <t>19.04.20267</t>
+  </si>
+  <si>
+    <t>19.04.20268</t>
+  </si>
+  <si>
+    <t>19.04.20269</t>
+  </si>
+  <si>
+    <t>19.04.202610</t>
+  </si>
+  <si>
+    <t>19.04.202611</t>
+  </si>
+  <si>
+    <t>19.04.202612</t>
+  </si>
+  <si>
+    <t>19.04.202613</t>
+  </si>
+  <si>
+    <t>19.04.202614</t>
+  </si>
+  <si>
+    <t>19.04.202615</t>
+  </si>
+  <si>
+    <t>19.04.202616</t>
+  </si>
+  <si>
+    <t>19.04.202617</t>
+  </si>
+  <si>
+    <t>19.04.202618</t>
+  </si>
+  <si>
+    <t>19.04.202619</t>
+  </si>
+  <si>
+    <t>19.04.202620</t>
+  </si>
+  <si>
+    <t>19.04.202621</t>
+  </si>
+  <si>
+    <t>19.04.202622</t>
+  </si>
+  <si>
+    <t>19.04.202623</t>
+  </si>
+  <si>
+    <t>19.04.202624</t>
+  </si>
+  <si>
+    <t>19.04.202625</t>
+  </si>
+  <si>
+    <t>19.04.202626</t>
+  </si>
+  <si>
+    <t>19.04.202627</t>
+  </si>
+  <si>
+    <t>19.04.202628</t>
+  </si>
+  <si>
+    <t>19.04.202629</t>
+  </si>
+  <si>
+    <t>19.04.202630</t>
+  </si>
+  <si>
+    <t>19.04.202631</t>
+  </si>
+  <si>
+    <t>19.04.202632</t>
+  </si>
+  <si>
+    <t>19.04.202633</t>
+  </si>
+  <si>
+    <t>19.04.202634</t>
+  </si>
+  <si>
+    <t>19.04.202635</t>
+  </si>
+  <si>
+    <t>19.04.202636</t>
+  </si>
+  <si>
+    <t>19.04.202637</t>
+  </si>
+  <si>
+    <t>19.04.202638</t>
+  </si>
+  <si>
+    <t>19.04.202639</t>
+  </si>
+  <si>
+    <t>19.04.202640</t>
+  </si>
+  <si>
+    <t>19.04.202641</t>
+  </si>
+  <si>
+    <t>19.04.202642</t>
+  </si>
+  <si>
+    <t>19.04.202643</t>
+  </si>
+  <si>
+    <t>19.04.202644</t>
+  </si>
+  <si>
+    <t>19.04.202645</t>
+  </si>
+  <si>
+    <t>19.04.202646</t>
+  </si>
+  <si>
+    <t>19.04.202647</t>
+  </si>
+  <si>
+    <t>19.04.202648</t>
+  </si>
+  <si>
+    <t>19.04.202649</t>
+  </si>
+  <si>
+    <t>19.04.202650</t>
+  </si>
+  <si>
+    <t>19.04.202651</t>
+  </si>
+  <si>
+    <t>19.04.202652</t>
+  </si>
+  <si>
+    <t>19.04.202653</t>
+  </si>
+  <si>
+    <t>19.04.202654</t>
+  </si>
+  <si>
+    <t>19.04.202655</t>
+  </si>
+  <si>
+    <t>19.04.202656</t>
+  </si>
+  <si>
+    <t>19.04.202657</t>
+  </si>
+  <si>
+    <t>19.04.202658</t>
+  </si>
+  <si>
+    <t>19.04.202659</t>
+  </si>
+  <si>
+    <t>19.04.202660</t>
+  </si>
+  <si>
+    <t>19.04.202661</t>
+  </si>
+  <si>
+    <t>19.04.202662</t>
+  </si>
+  <si>
+    <t>19.04.202663</t>
+  </si>
+  <si>
+    <t>19.04.202664</t>
+  </si>
+  <si>
+    <t>19.04.202665</t>
+  </si>
+  <si>
+    <t>19.04.202666</t>
+  </si>
+  <si>
+    <t>19.04.202667</t>
+  </si>
+  <si>
+    <t>19.04.202668</t>
+  </si>
+  <si>
+    <t>19.04.202669</t>
+  </si>
+  <si>
+    <t>19.04.202670</t>
+  </si>
+  <si>
+    <t>19.04.202671</t>
+  </si>
+  <si>
+    <t>19.04.202672</t>
+  </si>
+  <si>
+    <t>19.04.202673</t>
+  </si>
+  <si>
+    <t>19.04.202674</t>
+  </si>
+  <si>
+    <t>19.04.202675</t>
+  </si>
+  <si>
+    <t>19.04.202676</t>
+  </si>
+  <si>
+    <t>19.04.202677</t>
+  </si>
+  <si>
+    <t>19.04.202678</t>
+  </si>
+  <si>
+    <t>19.04.202679</t>
+  </si>
+  <si>
+    <t>19.04.202680</t>
+  </si>
+  <si>
+    <t>19.04.202681</t>
+  </si>
+  <si>
+    <t>19.04.202682</t>
+  </si>
+  <si>
+    <t>19.04.202683</t>
+  </si>
+  <si>
+    <t>19.04.202684</t>
+  </si>
+  <si>
+    <t>19.04.202685</t>
+  </si>
+  <si>
+    <t>19.04.202686</t>
+  </si>
+  <si>
+    <t>19.04.202687</t>
+  </si>
+  <si>
+    <t>19.04.202688</t>
+  </si>
+  <si>
+    <t>19.04.202689</t>
+  </si>
+  <si>
+    <t>19.04.202690</t>
+  </si>
+  <si>
+    <t>19.04.202691</t>
+  </si>
+  <si>
+    <t>19.04.202692</t>
+  </si>
+  <si>
+    <t>19.04.202693</t>
+  </si>
+  <si>
+    <t>19.04.202694</t>
+  </si>
+  <si>
+    <t>20.04.202696</t>
+  </si>
+  <si>
+    <t>20.04.20261</t>
+  </si>
+  <si>
+    <t>20.04.20262</t>
+  </si>
+  <si>
+    <t>20.04.20263</t>
+  </si>
+  <si>
+    <t>20.04.20264</t>
+  </si>
+  <si>
+    <t>20.04.20265</t>
+  </si>
+  <si>
+    <t>20.04.20266</t>
+  </si>
+  <si>
+    <t>20.04.20267</t>
+  </si>
+  <si>
+    <t>20.04.20268</t>
+  </si>
+  <si>
+    <t>20.04.20269</t>
+  </si>
+  <si>
+    <t>20.04.202610</t>
+  </si>
+  <si>
+    <t>20.04.202611</t>
+  </si>
+  <si>
+    <t>20.04.202612</t>
+  </si>
+  <si>
+    <t>20.04.202613</t>
+  </si>
+  <si>
+    <t>20.04.202614</t>
+  </si>
+  <si>
+    <t>20.04.202615</t>
+  </si>
+  <si>
+    <t>20.04.202616</t>
+  </si>
+  <si>
+    <t>20.04.202617</t>
+  </si>
+  <si>
+    <t>20.04.202618</t>
+  </si>
+  <si>
+    <t>20.04.202619</t>
+  </si>
+  <si>
+    <t>20.04.202620</t>
+  </si>
+  <si>
+    <t>20.04.202621</t>
+  </si>
+  <si>
+    <t>20.04.202622</t>
+  </si>
+  <si>
+    <t>20.04.202623</t>
+  </si>
+  <si>
+    <t>20.04.202624</t>
+  </si>
+  <si>
+    <t>20.04.202625</t>
+  </si>
+  <si>
+    <t>20.04.202626</t>
+  </si>
+  <si>
+    <t>20.04.202627</t>
+  </si>
+  <si>
+    <t>20.04.202628</t>
+  </si>
+  <si>
+    <t>20.04.202629</t>
+  </si>
+  <si>
+    <t>20.04.202630</t>
+  </si>
+  <si>
+    <t>20.04.202631</t>
+  </si>
+  <si>
+    <t>20.04.202632</t>
+  </si>
+  <si>
+    <t>20.04.202633</t>
+  </si>
+  <si>
+    <t>20.04.202634</t>
+  </si>
+  <si>
+    <t>20.04.202635</t>
+  </si>
+  <si>
+    <t>20.04.202636</t>
+  </si>
+  <si>
+    <t>20.04.202637</t>
+  </si>
+  <si>
+    <t>20.04.202638</t>
+  </si>
+  <si>
+    <t>20.04.202639</t>
+  </si>
+  <si>
+    <t>20.04.202640</t>
+  </si>
+  <si>
+    <t>20.04.202641</t>
+  </si>
+  <si>
+    <t>20.04.202642</t>
+  </si>
+  <si>
+    <t>20.04.202643</t>
+  </si>
+  <si>
+    <t>20.04.202644</t>
+  </si>
+  <si>
+    <t>20.04.202645</t>
+  </si>
+  <si>
+    <t>20.04.202646</t>
+  </si>
+  <si>
+    <t>20.04.202647</t>
+  </si>
+  <si>
+    <t>20.04.202648</t>
+  </si>
+  <si>
+    <t>20.04.202649</t>
+  </si>
+  <si>
+    <t>20.04.202650</t>
+  </si>
+  <si>
+    <t>20.04.202651</t>
+  </si>
+  <si>
+    <t>20.04.202652</t>
+  </si>
+  <si>
+    <t>20.04.202653</t>
+  </si>
+  <si>
+    <t>20.04.202654</t>
+  </si>
+  <si>
+    <t>20.04.202655</t>
+  </si>
+  <si>
+    <t>20.04.202656</t>
+  </si>
+  <si>
+    <t>20.04.202657</t>
+  </si>
+  <si>
+    <t>20.04.202658</t>
+  </si>
+  <si>
+    <t>20.04.202659</t>
+  </si>
+  <si>
+    <t>20.04.202660</t>
+  </si>
+  <si>
+    <t>20.04.202661</t>
+  </si>
+  <si>
+    <t>20.04.202662</t>
+  </si>
+  <si>
+    <t>20.04.202663</t>
+  </si>
+  <si>
+    <t>20.04.202664</t>
+  </si>
+  <si>
+    <t>20.04.202665</t>
+  </si>
+  <si>
+    <t>20.04.202666</t>
+  </si>
+  <si>
+    <t>20.04.202667</t>
+  </si>
+  <si>
+    <t>20.04.202668</t>
+  </si>
+  <si>
+    <t>20.04.202669</t>
+  </si>
+  <si>
+    <t>20.04.202670</t>
+  </si>
+  <si>
+    <t>20.04.202671</t>
+  </si>
+  <si>
+    <t>20.04.202672</t>
+  </si>
+  <si>
+    <t>20.04.202673</t>
+  </si>
+  <si>
+    <t>20.04.202674</t>
+  </si>
+  <si>
+    <t>20.04.202675</t>
+  </si>
+  <si>
+    <t>20.04.202676</t>
+  </si>
+  <si>
+    <t>20.04.202677</t>
+  </si>
+  <si>
+    <t>20.04.202678</t>
+  </si>
+  <si>
+    <t>20.04.202679</t>
+  </si>
+  <si>
+    <t>20.04.202680</t>
+  </si>
+  <si>
+    <t>20.04.202681</t>
+  </si>
+  <si>
+    <t>20.04.202682</t>
+  </si>
+  <si>
+    <t>20.04.202683</t>
+  </si>
+  <si>
+    <t>20.04.202684</t>
+  </si>
+  <si>
+    <t>20.04.202685</t>
+  </si>
+  <si>
+    <t>20.04.202686</t>
+  </si>
+  <si>
+    <t>20.04.202687</t>
+  </si>
+  <si>
+    <t>20.04.202688</t>
+  </si>
+  <si>
+    <t>20.04.202689</t>
+  </si>
+  <si>
+    <t>20.04.202690</t>
+  </si>
+  <si>
+    <t>20.04.202691</t>
+  </si>
+  <si>
+    <t>20.04.202692</t>
+  </si>
+  <si>
+    <t>20.04.202693</t>
+  </si>
+  <si>
+    <t>20.04.202694</t>
+  </si>
+  <si>
+    <t>20.04.202695</t>
+  </si>
+  <si>
+    <t>21.04.20261</t>
+  </si>
+  <si>
+    <t>21.04.20262</t>
+  </si>
+  <si>
+    <t>21.04.20263</t>
+  </si>
+  <si>
+    <t>21.04.20264</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E389"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -991,7 +1567,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46128.03611111111</v>
+        <v>46129.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1584,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46128.04652777778</v>
+        <v>46129.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1601,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46128.05694444444</v>
+        <v>46129.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1618,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46128.06736111111</v>
+        <v>46129.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1635,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46128.07777777778</v>
+        <v>46129.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1652,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46128.08819444444</v>
+        <v>46129.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1669,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46128.09861111111</v>
+        <v>46129.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1686,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46128.10902777778</v>
+        <v>46129.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1703,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46128.11944444444</v>
+        <v>46129.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1720,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46128.12986111111</v>
+        <v>46129.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1737,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46128.14027777778</v>
+        <v>46129.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1754,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46128.15069444444</v>
+        <v>46129.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1771,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46128.16111111111</v>
+        <v>46129.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1788,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46128.17152777778</v>
+        <v>46129.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1805,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46128.18194444444</v>
+        <v>46129.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1822,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46128.19236111111</v>
+        <v>46129.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1839,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46128.20277777778</v>
+        <v>46129.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1856,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46128.21319444444</v>
+        <v>46129.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1873,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46128.22361111111</v>
+        <v>46129.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1890,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46128.23402777778</v>
+        <v>46129.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1907,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46128.24444444444</v>
+        <v>46129.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1924,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46128.25486111111</v>
+        <v>46129.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1941,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46128.26527777778</v>
+        <v>46129.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1958,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46128.27569444444</v>
+        <v>46129.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1975,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46128.28611111111</v>
+        <v>46129.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1992,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46128.29652777778</v>
+        <v>46129.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +2009,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46128.30694444444</v>
+        <v>46129.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +2026,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46128.31736111111</v>
+        <v>46129.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +2043,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46128.32777777778</v>
+        <v>46129.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +2060,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46128.33819444444</v>
+        <v>46129.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +2077,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46128.34861111111</v>
+        <v>46129.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +2094,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46128.35902777778</v>
+        <v>46129.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +2111,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46128.36944444444</v>
+        <v>46129.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +2128,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46128.37986111111</v>
+        <v>46129.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +2145,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46128.39027777778</v>
+        <v>46129.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +2162,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46128.40069444444</v>
+        <v>46129.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +2179,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46128.41111111111</v>
+        <v>46129.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +2196,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46128.42152777778</v>
+        <v>46129.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +2213,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46128.43194444444</v>
+        <v>46129.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +2230,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46128.44236111111</v>
+        <v>46129.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +2247,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46128.45277777778</v>
+        <v>46129.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +2264,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46128.46319444444</v>
+        <v>46129.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +2281,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46128.47361111111</v>
+        <v>46129.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +2298,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46128.48402777778</v>
+        <v>46129.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +2315,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46128.49444444444</v>
+        <v>46129.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +2332,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46128.50486111111</v>
+        <v>46129.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +2349,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46128.51527777778</v>
+        <v>46129.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +2366,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46128.52569444444</v>
+        <v>46129.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +2383,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46128.53611111111</v>
+        <v>46129.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +2400,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46128.54652777778</v>
+        <v>46129.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +2417,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46128.55694444444</v>
+        <v>46129.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +2434,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46128.56736111111</v>
+        <v>46129.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +2451,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46128.57777777778</v>
+        <v>46129.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +2468,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46128.58819444444</v>
+        <v>46129.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +2485,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46128.59861111111</v>
+        <v>46129.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +2502,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46128.60902777778</v>
+        <v>46129.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +2519,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46128.61944444444</v>
+        <v>46129.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +2536,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46128.62986111111</v>
+        <v>46129.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +2553,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46128.64027777778</v>
+        <v>46129.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +2570,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46128.65069444444</v>
+        <v>46129.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2587,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46128.66111111111</v>
+        <v>46129.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2604,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46128.67152777778</v>
+        <v>46129.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2621,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46128.68194444444</v>
+        <v>46129.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2638,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46128.69236111111</v>
+        <v>46129.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2655,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46128.70277777778</v>
+        <v>46129.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2672,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46128.71319444444</v>
+        <v>46129.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2689,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46128.72361111111</v>
+        <v>46129.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2706,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46128.73402777778</v>
+        <v>46129.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2723,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46128.74444444444</v>
+        <v>46129.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2740,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46128.75486111111</v>
+        <v>46129.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2757,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46128.76527777778</v>
+        <v>46129.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2774,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46128.77569444444</v>
+        <v>46129.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2791,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46128.78611111111</v>
+        <v>46129.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2808,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46128.79652777778</v>
+        <v>46129.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2825,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46128.80694444444</v>
+        <v>46129.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2842,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46128.81736111111</v>
+        <v>46129.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2859,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46128.82777777778</v>
+        <v>46129.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2876,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46128.83819444444</v>
+        <v>46129.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2893,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46128.84861111111</v>
+        <v>46129.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2910,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46128.85902777778</v>
+        <v>46129.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2927,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46128.86944444444</v>
+        <v>46129.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2944,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46128.87986111111</v>
+        <v>46129.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2961,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46128.89027777778</v>
+        <v>46129.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2978,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46128.90069444444</v>
+        <v>46129.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2995,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46128.91111111111</v>
+        <v>46129.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +3012,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46128.92152777778</v>
+        <v>46129.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +3029,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46128.93194444444</v>
+        <v>46129.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +3046,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46128.94236111111</v>
+        <v>46129.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +3063,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46128.95277777778</v>
+        <v>46129.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +3080,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46128.96319444444</v>
+        <v>46129.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +3097,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46128.97361111111</v>
+        <v>46129.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +3114,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46128.98402777778</v>
+        <v>46129.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +3131,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46128.99444444444</v>
+        <v>46129.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +3148,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46129.00486111111</v>
+        <v>46130.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +3165,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46129.01527777778</v>
+        <v>46130.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +3182,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46129.02569444444</v>
+        <v>46130.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +3199,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46129.03611111111</v>
+        <v>46130.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +3216,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46129.03611111111</v>
+        <v>46130.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +3233,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46129.04652777778</v>
+        <v>46130.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +3250,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46129.05694444444</v>
+        <v>46130.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +3267,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46129.06736111111</v>
+        <v>46130.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +3284,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46129.07777777778</v>
+        <v>46130.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +3301,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46129.08819444444</v>
+        <v>46130.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +3318,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46129.09861111111</v>
+        <v>46130.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +3335,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46129.10902777778</v>
+        <v>46130.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +3352,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46129.11944444444</v>
+        <v>46130.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +3369,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46129.12986111111</v>
+        <v>46130.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +3386,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46129.14027777778</v>
+        <v>46130.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +3403,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46129.15069444444</v>
+        <v>46130.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +3420,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46129.16111111111</v>
+        <v>46130.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +3437,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46129.17152777778</v>
+        <v>46130.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +3454,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46129.18194444444</v>
+        <v>46130.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +3471,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46129.19236111111</v>
+        <v>46130.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +3488,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46129.20277777778</v>
+        <v>46130.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +3505,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46129.21319444444</v>
+        <v>46130.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +3522,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46129.22361111111</v>
+        <v>46130.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +3539,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46129.23402777778</v>
+        <v>46130.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +3556,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46129.24444444444</v>
+        <v>46130.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +3573,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46129.25486111111</v>
+        <v>46130.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3590,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46129.26527777778</v>
+        <v>46130.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3607,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46129.27569444444</v>
+        <v>46130.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3624,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46129.28611111111</v>
+        <v>46130.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3641,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46129.29652777778</v>
+        <v>46130.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3658,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46129.30694444444</v>
+        <v>46130.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3675,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46129.31736111111</v>
+        <v>46130.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3692,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46129.32777777778</v>
+        <v>46130.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3709,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46129.33819444444</v>
+        <v>46130.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3726,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46129.34861111111</v>
+        <v>46130.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3743,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46129.35902777778</v>
+        <v>46130.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3760,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46129.36944444444</v>
+        <v>46130.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3777,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46129.37986111111</v>
+        <v>46130.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3794,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46129.39027777778</v>
+        <v>46130.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3811,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46129.40069444444</v>
+        <v>46130.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3828,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46129.41111111111</v>
+        <v>46130.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3845,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46129.42152777778</v>
+        <v>46130.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3862,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46129.43194444444</v>
+        <v>46130.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3879,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46129.44236111111</v>
+        <v>46130.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3896,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46129.45277777778</v>
+        <v>46130.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3913,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46129.46319444444</v>
+        <v>46130.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3930,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46129.47361111111</v>
+        <v>46130.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3947,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46129.48402777778</v>
+        <v>46130.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3964,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46129.49444444444</v>
+        <v>46130.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3981,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46129.50486111111</v>
+        <v>46130.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3998,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46129.51527777778</v>
+        <v>46130.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +4015,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46129.52569444444</v>
+        <v>46130.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +4032,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46129.53611111111</v>
+        <v>46130.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +4049,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46129.54652777778</v>
+        <v>46130.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +4066,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46129.55694444444</v>
+        <v>46130.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +4083,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46129.56736111111</v>
+        <v>46130.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +4100,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46129.57777777778</v>
+        <v>46130.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +4117,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46129.58819444444</v>
+        <v>46130.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +4134,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46129.59861111111</v>
+        <v>46130.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +4151,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46129.60902777778</v>
+        <v>46130.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +4168,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46129.61944444444</v>
+        <v>46130.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +4185,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46129.62986111111</v>
+        <v>46130.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +4202,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46129.64027777778</v>
+        <v>46130.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +4219,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46129.65069444444</v>
+        <v>46130.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +4236,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46129.66111111111</v>
+        <v>46130.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +4253,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46129.67152777778</v>
+        <v>46130.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +4270,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46129.68194444444</v>
+        <v>46130.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +4287,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46129.69236111111</v>
+        <v>46130.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +4304,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46129.70277777778</v>
+        <v>46130.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +4321,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46129.71319444444</v>
+        <v>46130.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +4338,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46129.72361111111</v>
+        <v>46130.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +4355,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46129.73402777778</v>
+        <v>46130.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +4372,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46129.74444444444</v>
+        <v>46130.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +4389,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46129.75486111111</v>
+        <v>46130.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +4406,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46129.76527777778</v>
+        <v>46130.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +4423,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46129.77569444444</v>
+        <v>46130.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +4440,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46129.78611111111</v>
+        <v>46130.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +4457,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46129.79652777778</v>
+        <v>46130.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +4474,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46129.80694444444</v>
+        <v>46130.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +4491,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46129.81736111111</v>
+        <v>46130.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +4508,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46129.82777777778</v>
+        <v>46130.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +4525,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46129.83819444444</v>
+        <v>46130.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +4542,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46129.84861111111</v>
+        <v>46130.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +4559,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46129.85902777778</v>
+        <v>46130.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4576,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46129.86944444444</v>
+        <v>46130.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4593,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46129.87986111111</v>
+        <v>46130.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4610,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46129.89027777778</v>
+        <v>46130.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4627,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46129.90069444444</v>
+        <v>46130.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4644,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46129.91111111111</v>
+        <v>46130.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4661,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46129.92152777778</v>
+        <v>46130.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4678,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46129.93194444444</v>
+        <v>46130.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4695,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46129.94236111111</v>
+        <v>46130.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4712,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46129.95277777778</v>
+        <v>46130.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4729,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46129.96319444444</v>
+        <v>46130.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4746,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46129.97361111111</v>
+        <v>46130.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4763,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46129.98402777778</v>
+        <v>46130.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4780,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46129.99444444444</v>
+        <v>46130.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4797,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46130.00486111111</v>
+        <v>46131.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4814,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46130.01527777778</v>
+        <v>46131.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4831,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46130.02569444444</v>
+        <v>46131.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4848,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46130.03611111111</v>
+        <v>46131.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -4285,6 +4861,3304 @@
       </c>
       <c r="E195" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46131.03611111111</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46131.04652777778</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46131.05694444444</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46131.06736111111</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46131.07777777778</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46131.08819444444</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46131.09861111111</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46131.10902777778</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46131.11944444444</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46131.12986111111</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46131.14027777778</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46131.15069444444</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46131.16111111111</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46131.17152777778</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46131.18194444444</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46131.19236111111</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46131.20277777778</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46131.21319444444</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46131.22361111111</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46131.23402777778</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46131.24444444444</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46131.25486111111</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46131.26527777778</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46131.27569444444</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46131.28611111111</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46131.29652777778</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46131.30694444444</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46131.31736111111</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46131.32777777778</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46131.33819444444</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46131.34861111111</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46131.35902777778</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46131.36944444444</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46131.37986111111</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46131.39027777778</v>
+      </c>
+      <c r="B230">
+        <v>0</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46131.40069444444</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46131.41111111111</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46131.42152777778</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46131.43194444444</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46131.44236111111</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46131.45277777778</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46131.46319444444</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46131.47361111111</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46131.48402777778</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46131.49444444444</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46131.50486111111</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46131.51527777778</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46131.52569444444</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46131.53611111111</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46131.54652777778</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46131.55694444444</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46131.56736111111</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46131.57777777778</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46131.58819444444</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46131.59861111111</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46131.60902777778</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46131.61944444444</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46131.62986111111</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46131.64027777778</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46131.65069444444</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46131.66111111111</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46131.67152777778</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46131.68194444444</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46131.69236111111</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46131.70277777778</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46131.71319444444</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46131.72361111111</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46131.73402777778</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46131.74444444444</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46131.75486111111</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46131.76527777778</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46131.77569444444</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46131.78611111111</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46131.79652777778</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46131.80694444444</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46131.81736111111</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46131.82777777778</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46131.83819444444</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46131.84861111111</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46131.85902777778</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46131.86944444444</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46131.87986111111</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46131.89027777778</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46131.90069444444</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46131.91111111111</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46131.92152777778</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46131.93194444444</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46131.94236111111</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46131.95277777778</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46131.96319444444</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46131.97361111111</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46131.98402777778</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46131.99444444444</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46132.00486111111</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46132.01527777778</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46132.02569444444</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46132.03611111111</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46132.03611111111</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46132.04652777778</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46132.05694444444</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46132.06736111111</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46132.07777777778</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46132.08819444444</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46132.09861111111</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46132.10902777778</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46132.11944444444</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46132.12986111111</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46132.14027777778</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46132.15069444444</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46132.16111111111</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46132.17152777778</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46132.18194444444</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46132.19236111111</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46132.20277777778</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46132.21319444444</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46132.22361111111</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46132.23402777778</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46132.24444444444</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46132.25486111111</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46132.26527777778</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46132.27569444444</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46132.28611111111</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46132.29652777778</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46132.30694444444</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46132.31736111111</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46132.32777777778</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46132.33819444444</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46132.34861111111</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46132.35902777778</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46132.36944444444</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46132.37986111111</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46132.39027777778</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46132.40069444444</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46132.41111111111</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46132.42152777778</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46132.43194444444</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46132.44236111111</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46132.45277777778</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46132.46319444444</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46132.47361111111</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46132.48402777778</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46132.49444444444</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46132.50486111111</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46132.51527777778</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46132.52569444444</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46132.53611111111</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46132.54652777778</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46132.55694444444</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46132.56736111111</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46132.57777777778</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46132.58819444444</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46132.59861111111</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46132.60902777778</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46132.61944444444</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46132.62986111111</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46132.64027777778</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46132.65069444444</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46132.66111111111</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46132.67152777778</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46132.68194444444</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46132.69236111111</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46132.70277777778</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46132.71319444444</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46132.72361111111</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46132.73402777778</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46132.74444444444</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46132.75486111111</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46132.76527777778</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46132.77569444444</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46132.78611111111</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46132.79652777778</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46132.80694444444</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46132.81736111111</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46132.82777777778</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46132.83819444444</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46132.84861111111</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46132.85902777778</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46132.86944444444</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46132.87986111111</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46132.89027777778</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46132.90069444444</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46132.91111111111</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46132.92152777778</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46132.93194444444</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46132.94236111111</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46132.95277777778</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46132.96319444444</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46132.97361111111</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46132.98402777778</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46132.99444444444</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2">
+        <v>46133.00486111111</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2">
+        <v>46133.01527777778</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2">
+        <v>46133.02569444444</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2">
+        <v>46133.03611111111</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
+      <c r="E389" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.04.20261</t>
-  </si>
-  <si>
-    <t>20.04.20262</t>
-  </si>
-  <si>
-    <t>20.04.20263</t>
-  </si>
-  <si>
-    <t>20.04.20264</t>
-  </si>
-  <si>
-    <t>20.04.20265</t>
-  </si>
-  <si>
-    <t>20.04.20266</t>
-  </si>
-  <si>
-    <t>20.04.20267</t>
-  </si>
-  <si>
-    <t>20.04.20268</t>
-  </si>
-  <si>
-    <t>20.04.20269</t>
-  </si>
-  <si>
-    <t>20.04.202610</t>
-  </si>
-  <si>
-    <t>20.04.202611</t>
-  </si>
-  <si>
-    <t>20.04.202612</t>
-  </si>
-  <si>
-    <t>20.04.202613</t>
-  </si>
-  <si>
-    <t>20.04.202614</t>
-  </si>
-  <si>
-    <t>20.04.202615</t>
-  </si>
-  <si>
-    <t>20.04.202616</t>
-  </si>
-  <si>
-    <t>20.04.202617</t>
-  </si>
-  <si>
-    <t>20.04.202618</t>
-  </si>
-  <si>
-    <t>20.04.202619</t>
-  </si>
-  <si>
-    <t>20.04.202620</t>
-  </si>
-  <si>
-    <t>20.04.202621</t>
-  </si>
-  <si>
-    <t>20.04.202622</t>
-  </si>
-  <si>
-    <t>20.04.202623</t>
-  </si>
-  <si>
-    <t>20.04.202624</t>
-  </si>
-  <si>
-    <t>20.04.202625</t>
-  </si>
-  <si>
-    <t>20.04.202626</t>
-  </si>
-  <si>
-    <t>20.04.202627</t>
-  </si>
-  <si>
-    <t>20.04.202628</t>
-  </si>
-  <si>
-    <t>20.04.202629</t>
-  </si>
-  <si>
-    <t>20.04.202630</t>
-  </si>
-  <si>
-    <t>20.04.202631</t>
-  </si>
-  <si>
-    <t>20.04.202632</t>
-  </si>
-  <si>
-    <t>20.04.202633</t>
-  </si>
-  <si>
-    <t>20.04.202634</t>
-  </si>
-  <si>
-    <t>20.04.202635</t>
-  </si>
-  <si>
-    <t>20.04.202636</t>
-  </si>
-  <si>
-    <t>20.04.202637</t>
-  </si>
-  <si>
-    <t>20.04.202638</t>
-  </si>
-  <si>
-    <t>20.04.202639</t>
-  </si>
-  <si>
-    <t>20.04.202640</t>
-  </si>
-  <si>
-    <t>20.04.202641</t>
-  </si>
-  <si>
-    <t>20.04.202642</t>
-  </si>
-  <si>
-    <t>20.04.202643</t>
-  </si>
-  <si>
-    <t>20.04.202644</t>
-  </si>
-  <si>
-    <t>20.04.202645</t>
-  </si>
-  <si>
-    <t>20.04.202646</t>
-  </si>
-  <si>
-    <t>20.04.202647</t>
-  </si>
-  <si>
-    <t>20.04.202648</t>
-  </si>
-  <si>
-    <t>20.04.202649</t>
-  </si>
-  <si>
-    <t>20.04.202650</t>
-  </si>
-  <si>
-    <t>20.04.202651</t>
-  </si>
-  <si>
-    <t>20.04.202652</t>
-  </si>
-  <si>
-    <t>20.04.202653</t>
-  </si>
-  <si>
-    <t>20.04.202654</t>
-  </si>
-  <si>
-    <t>20.04.202655</t>
-  </si>
-  <si>
-    <t>20.04.202656</t>
-  </si>
-  <si>
-    <t>20.04.202657</t>
-  </si>
-  <si>
-    <t>20.04.202658</t>
-  </si>
-  <si>
-    <t>20.04.202659</t>
-  </si>
-  <si>
-    <t>20.04.202660</t>
-  </si>
-  <si>
-    <t>20.04.202661</t>
-  </si>
-  <si>
-    <t>20.04.202662</t>
-  </si>
-  <si>
-    <t>20.04.202663</t>
-  </si>
-  <si>
-    <t>20.04.202664</t>
-  </si>
-  <si>
-    <t>20.04.202665</t>
-  </si>
-  <si>
-    <t>20.04.202666</t>
-  </si>
-  <si>
-    <t>20.04.202667</t>
-  </si>
-  <si>
-    <t>20.04.202668</t>
-  </si>
-  <si>
-    <t>20.04.202669</t>
-  </si>
-  <si>
-    <t>20.04.202670</t>
-  </si>
-  <si>
-    <t>20.04.202671</t>
-  </si>
-  <si>
-    <t>20.04.202672</t>
-  </si>
-  <si>
-    <t>20.04.202673</t>
-  </si>
-  <si>
-    <t>20.04.202674</t>
-  </si>
-  <si>
-    <t>20.04.202675</t>
-  </si>
-  <si>
-    <t>20.04.202676</t>
-  </si>
-  <si>
-    <t>20.04.202677</t>
-  </si>
-  <si>
-    <t>20.04.202678</t>
-  </si>
-  <si>
-    <t>20.04.202679</t>
-  </si>
-  <si>
-    <t>20.04.202680</t>
-  </si>
-  <si>
-    <t>20.04.202681</t>
-  </si>
-  <si>
-    <t>20.04.202682</t>
-  </si>
-  <si>
-    <t>20.04.202683</t>
-  </si>
-  <si>
-    <t>20.04.202684</t>
-  </si>
-  <si>
-    <t>20.04.202685</t>
-  </si>
-  <si>
-    <t>20.04.202686</t>
-  </si>
-  <si>
-    <t>20.04.202687</t>
-  </si>
-  <si>
-    <t>20.04.202688</t>
-  </si>
-  <si>
-    <t>20.04.202689</t>
-  </si>
-  <si>
-    <t>20.04.202690</t>
-  </si>
-  <si>
-    <t>20.04.202691</t>
-  </si>
-  <si>
-    <t>20.04.202692</t>
-  </si>
-  <si>
-    <t>20.04.202693</t>
-  </si>
-  <si>
-    <t>21.04.202694</t>
-  </si>
-  <si>
-    <t>21.04.202695</t>
-  </si>
-  <si>
-    <t>21.04.202696</t>
-  </si>
-  <si>
     <t>21.04.20261</t>
   </si>
   <si>
@@ -598,6 +310,9 @@
     <t>21.04.202693</t>
   </si>
   <si>
+    <t>22.04.202694</t>
+  </si>
+  <si>
     <t>22.04.202695</t>
   </si>
   <si>
@@ -608,6 +323,291 @@
   </si>
   <si>
     <t>22.04.20262</t>
+  </si>
+  <si>
+    <t>22.04.20263</t>
+  </si>
+  <si>
+    <t>22.04.20264</t>
+  </si>
+  <si>
+    <t>22.04.20265</t>
+  </si>
+  <si>
+    <t>22.04.20266</t>
+  </si>
+  <si>
+    <t>22.04.20267</t>
+  </si>
+  <si>
+    <t>22.04.20268</t>
+  </si>
+  <si>
+    <t>22.04.20269</t>
+  </si>
+  <si>
+    <t>22.04.202610</t>
+  </si>
+  <si>
+    <t>22.04.202611</t>
+  </si>
+  <si>
+    <t>22.04.202612</t>
+  </si>
+  <si>
+    <t>22.04.202613</t>
+  </si>
+  <si>
+    <t>22.04.202614</t>
+  </si>
+  <si>
+    <t>22.04.202615</t>
+  </si>
+  <si>
+    <t>22.04.202616</t>
+  </si>
+  <si>
+    <t>22.04.202617</t>
+  </si>
+  <si>
+    <t>22.04.202618</t>
+  </si>
+  <si>
+    <t>22.04.202619</t>
+  </si>
+  <si>
+    <t>22.04.202620</t>
+  </si>
+  <si>
+    <t>22.04.202621</t>
+  </si>
+  <si>
+    <t>22.04.202622</t>
+  </si>
+  <si>
+    <t>22.04.202623</t>
+  </si>
+  <si>
+    <t>22.04.202624</t>
+  </si>
+  <si>
+    <t>22.04.202625</t>
+  </si>
+  <si>
+    <t>22.04.202626</t>
+  </si>
+  <si>
+    <t>22.04.202627</t>
+  </si>
+  <si>
+    <t>22.04.202628</t>
+  </si>
+  <si>
+    <t>22.04.202629</t>
+  </si>
+  <si>
+    <t>22.04.202630</t>
+  </si>
+  <si>
+    <t>22.04.202631</t>
+  </si>
+  <si>
+    <t>22.04.202632</t>
+  </si>
+  <si>
+    <t>22.04.202633</t>
+  </si>
+  <si>
+    <t>22.04.202634</t>
+  </si>
+  <si>
+    <t>22.04.202635</t>
+  </si>
+  <si>
+    <t>22.04.202636</t>
+  </si>
+  <si>
+    <t>22.04.202637</t>
+  </si>
+  <si>
+    <t>22.04.202638</t>
+  </si>
+  <si>
+    <t>22.04.202639</t>
+  </si>
+  <si>
+    <t>22.04.202640</t>
+  </si>
+  <si>
+    <t>22.04.202641</t>
+  </si>
+  <si>
+    <t>22.04.202642</t>
+  </si>
+  <si>
+    <t>22.04.202643</t>
+  </si>
+  <si>
+    <t>22.04.202644</t>
+  </si>
+  <si>
+    <t>22.04.202645</t>
+  </si>
+  <si>
+    <t>22.04.202646</t>
+  </si>
+  <si>
+    <t>22.04.202647</t>
+  </si>
+  <si>
+    <t>22.04.202648</t>
+  </si>
+  <si>
+    <t>22.04.202649</t>
+  </si>
+  <si>
+    <t>22.04.202650</t>
+  </si>
+  <si>
+    <t>22.04.202651</t>
+  </si>
+  <si>
+    <t>22.04.202652</t>
+  </si>
+  <si>
+    <t>22.04.202653</t>
+  </si>
+  <si>
+    <t>22.04.202654</t>
+  </si>
+  <si>
+    <t>22.04.202655</t>
+  </si>
+  <si>
+    <t>22.04.202656</t>
+  </si>
+  <si>
+    <t>22.04.202657</t>
+  </si>
+  <si>
+    <t>22.04.202658</t>
+  </si>
+  <si>
+    <t>22.04.202659</t>
+  </si>
+  <si>
+    <t>22.04.202660</t>
+  </si>
+  <si>
+    <t>22.04.202661</t>
+  </si>
+  <si>
+    <t>22.04.202662</t>
+  </si>
+  <si>
+    <t>22.04.202663</t>
+  </si>
+  <si>
+    <t>22.04.202664</t>
+  </si>
+  <si>
+    <t>22.04.202665</t>
+  </si>
+  <si>
+    <t>22.04.202666</t>
+  </si>
+  <si>
+    <t>22.04.202667</t>
+  </si>
+  <si>
+    <t>22.04.202668</t>
+  </si>
+  <si>
+    <t>22.04.202669</t>
+  </si>
+  <si>
+    <t>22.04.202670</t>
+  </si>
+  <si>
+    <t>22.04.202671</t>
+  </si>
+  <si>
+    <t>22.04.202672</t>
+  </si>
+  <si>
+    <t>22.04.202673</t>
+  </si>
+  <si>
+    <t>22.04.202674</t>
+  </si>
+  <si>
+    <t>22.04.202675</t>
+  </si>
+  <si>
+    <t>22.04.202676</t>
+  </si>
+  <si>
+    <t>22.04.202677</t>
+  </si>
+  <si>
+    <t>22.04.202678</t>
+  </si>
+  <si>
+    <t>22.04.202679</t>
+  </si>
+  <si>
+    <t>22.04.202680</t>
+  </si>
+  <si>
+    <t>22.04.202681</t>
+  </si>
+  <si>
+    <t>22.04.202682</t>
+  </si>
+  <si>
+    <t>22.04.202683</t>
+  </si>
+  <si>
+    <t>22.04.202684</t>
+  </si>
+  <si>
+    <t>22.04.202685</t>
+  </si>
+  <si>
+    <t>22.04.202686</t>
+  </si>
+  <si>
+    <t>22.04.202687</t>
+  </si>
+  <si>
+    <t>22.04.202688</t>
+  </si>
+  <si>
+    <t>22.04.202689</t>
+  </si>
+  <si>
+    <t>22.04.202690</t>
+  </si>
+  <si>
+    <t>22.04.202691</t>
+  </si>
+  <si>
+    <t>22.04.202692</t>
+  </si>
+  <si>
+    <t>22.04.202693</t>
+  </si>
+  <si>
+    <t>23.04.202695</t>
+  </si>
+  <si>
+    <t>23.04.202696</t>
+  </si>
+  <si>
+    <t>23.04.20261</t>
+  </si>
+  <si>
+    <t>23.04.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46132.03611111111</v>
+        <v>46133.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46132.04652777778</v>
+        <v>46133.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46132.05694444444</v>
+        <v>46133.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46132.06736111111</v>
+        <v>46133.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46132.07777777778</v>
+        <v>46133.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46132.08819444444</v>
+        <v>46133.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46132.09861111111</v>
+        <v>46133.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46132.10902777778</v>
+        <v>46133.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46132.11944444444</v>
+        <v>46133.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46132.12986111111</v>
+        <v>46133.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46132.14027777778</v>
+        <v>46133.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46132.15069444444</v>
+        <v>46133.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46132.16111111111</v>
+        <v>46133.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46132.17152777778</v>
+        <v>46133.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46132.18194444444</v>
+        <v>46133.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46132.19236111111</v>
+        <v>46133.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46132.20277777778</v>
+        <v>46133.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46132.21319444444</v>
+        <v>46133.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46132.22361111111</v>
+        <v>46133.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46132.23402777778</v>
+        <v>46133.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46132.24444444444</v>
+        <v>46133.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46132.25486111111</v>
+        <v>46133.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46132.26527777778</v>
+        <v>46133.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46132.27569444444</v>
+        <v>46133.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46132.28611111111</v>
+        <v>46133.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46132.29652777778</v>
+        <v>46133.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46132.30694444444</v>
+        <v>46133.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46132.31736111111</v>
+        <v>46133.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46132.32777777778</v>
+        <v>46133.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46132.33819444444</v>
+        <v>46133.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46132.34861111111</v>
+        <v>46133.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46132.35902777778</v>
+        <v>46133.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46132.36944444444</v>
+        <v>46133.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46132.37986111111</v>
+        <v>46133.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46132.39027777778</v>
+        <v>46133.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46132.40069444444</v>
+        <v>46133.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46132.41111111111</v>
+        <v>46133.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46132.42152777778</v>
+        <v>46133.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46132.43194444444</v>
+        <v>46133.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46132.44236111111</v>
+        <v>46133.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46132.45277777778</v>
+        <v>46133.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46132.46319444444</v>
+        <v>46133.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46132.47361111111</v>
+        <v>46133.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46132.48402777778</v>
+        <v>46133.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46132.49444444444</v>
+        <v>46133.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46132.50486111111</v>
+        <v>46133.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46132.51527777778</v>
+        <v>46133.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46132.52569444444</v>
+        <v>46133.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46132.53611111111</v>
+        <v>46133.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46132.54652777778</v>
+        <v>46133.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46132.55694444444</v>
+        <v>46133.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46132.56736111111</v>
+        <v>46133.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46132.57777777778</v>
+        <v>46133.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46132.58819444444</v>
+        <v>46133.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46132.59861111111</v>
+        <v>46133.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46132.60902777778</v>
+        <v>46133.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46132.61944444444</v>
+        <v>46133.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46132.62986111111</v>
+        <v>46133.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46132.64027777778</v>
+        <v>46133.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46132.65069444444</v>
+        <v>46133.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46132.66111111111</v>
+        <v>46133.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46132.67152777778</v>
+        <v>46133.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46132.68194444444</v>
+        <v>46133.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46132.69236111111</v>
+        <v>46133.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46132.70277777778</v>
+        <v>46133.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46132.71319444444</v>
+        <v>46133.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46132.72361111111</v>
+        <v>46133.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46132.73402777778</v>
+        <v>46133.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46132.74444444444</v>
+        <v>46133.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46132.75486111111</v>
+        <v>46133.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46132.76527777778</v>
+        <v>46133.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46132.77569444444</v>
+        <v>46133.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46132.78611111111</v>
+        <v>46133.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46132.79652777778</v>
+        <v>46133.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46132.80694444444</v>
+        <v>46133.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46132.81736111111</v>
+        <v>46133.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46132.82777777778</v>
+        <v>46133.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46132.83819444444</v>
+        <v>46133.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46132.84861111111</v>
+        <v>46133.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46132.85902777778</v>
+        <v>46133.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46132.86944444444</v>
+        <v>46133.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46132.87986111111</v>
+        <v>46133.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46132.89027777778</v>
+        <v>46133.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46132.90069444444</v>
+        <v>46133.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46132.91111111111</v>
+        <v>46133.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46132.92152777778</v>
+        <v>46133.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46132.93194444444</v>
+        <v>46133.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46132.94236111111</v>
+        <v>46133.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46132.95277777778</v>
+        <v>46133.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46132.96319444444</v>
+        <v>46133.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46132.97361111111</v>
+        <v>46133.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46132.98402777778</v>
+        <v>46133.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46132.99444444444</v>
+        <v>46133.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46133.00486111111</v>
+        <v>46134.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46133.01527777778</v>
+        <v>46134.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46133.02569444444</v>
+        <v>46134.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46133.03611111111</v>
+        <v>46134.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46133.03611111111</v>
+        <v>46134.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46133.04652777778</v>
+        <v>46134.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46133.05694444444</v>
+        <v>46134.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46133.06736111111</v>
+        <v>46134.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46133.07777777778</v>
+        <v>46134.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46133.08819444444</v>
+        <v>46134.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46133.09861111111</v>
+        <v>46134.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46133.10902777778</v>
+        <v>46134.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46133.11944444444</v>
+        <v>46134.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46133.12986111111</v>
+        <v>46134.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46133.14027777778</v>
+        <v>46134.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46133.15069444444</v>
+        <v>46134.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46133.16111111111</v>
+        <v>46134.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46133.17152777778</v>
+        <v>46134.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46133.18194444444</v>
+        <v>46134.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46133.19236111111</v>
+        <v>46134.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46133.20277777778</v>
+        <v>46134.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46133.21319444444</v>
+        <v>46134.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46133.22361111111</v>
+        <v>46134.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46133.23402777778</v>
+        <v>46134.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46133.24444444444</v>
+        <v>46134.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46133.25486111111</v>
+        <v>46134.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46133.26527777778</v>
+        <v>46134.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46133.27569444444</v>
+        <v>46134.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46133.28611111111</v>
+        <v>46134.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46133.29652777778</v>
+        <v>46134.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46133.30694444444</v>
+        <v>46134.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46133.31736111111</v>
+        <v>46134.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46133.32777777778</v>
+        <v>46134.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46133.33819444444</v>
+        <v>46134.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46133.34861111111</v>
+        <v>46134.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46133.35902777778</v>
+        <v>46134.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46133.36944444444</v>
+        <v>46134.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46133.37986111111</v>
+        <v>46134.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46133.39027777778</v>
+        <v>46134.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46133.40069444444</v>
+        <v>46134.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46133.41111111111</v>
+        <v>46134.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46133.42152777778</v>
+        <v>46134.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46133.43194444444</v>
+        <v>46134.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46133.44236111111</v>
+        <v>46134.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46133.45277777778</v>
+        <v>46134.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46133.46319444444</v>
+        <v>46134.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46133.47361111111</v>
+        <v>46134.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46133.48402777778</v>
+        <v>46134.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46133.49444444444</v>
+        <v>46134.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46133.50486111111</v>
+        <v>46134.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46133.51527777778</v>
+        <v>46134.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46133.52569444444</v>
+        <v>46134.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46133.53611111111</v>
+        <v>46134.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46133.54652777778</v>
+        <v>46134.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46133.55694444444</v>
+        <v>46134.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46133.56736111111</v>
+        <v>46134.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46133.57777777778</v>
+        <v>46134.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46133.58819444444</v>
+        <v>46134.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46133.59861111111</v>
+        <v>46134.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46133.60902777778</v>
+        <v>46134.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46133.61944444444</v>
+        <v>46134.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46133.62986111111</v>
+        <v>46134.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46133.64027777778</v>
+        <v>46134.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46133.65069444444</v>
+        <v>46134.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46133.66111111111</v>
+        <v>46134.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46133.67152777778</v>
+        <v>46134.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46133.68194444444</v>
+        <v>46134.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46133.69236111111</v>
+        <v>46134.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46133.70277777778</v>
+        <v>46134.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46133.71319444444</v>
+        <v>46134.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46133.72361111111</v>
+        <v>46134.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46133.73402777778</v>
+        <v>46134.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46133.74444444444</v>
+        <v>46134.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46133.75486111111</v>
+        <v>46134.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46133.76527777778</v>
+        <v>46134.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46133.77569444444</v>
+        <v>46134.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46133.78611111111</v>
+        <v>46134.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46133.79652777778</v>
+        <v>46134.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46133.80694444444</v>
+        <v>46134.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46133.81736111111</v>
+        <v>46134.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46133.82777777778</v>
+        <v>46134.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46133.83819444444</v>
+        <v>46134.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46133.84861111111</v>
+        <v>46134.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46133.85902777778</v>
+        <v>46134.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46133.86944444444</v>
+        <v>46134.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46133.87986111111</v>
+        <v>46134.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46133.89027777778</v>
+        <v>46134.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46133.90069444444</v>
+        <v>46134.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46133.91111111111</v>
+        <v>46134.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46133.92152777778</v>
+        <v>46134.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46133.93194444444</v>
+        <v>46134.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46133.94236111111</v>
+        <v>46134.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46133.95277777778</v>
+        <v>46134.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46133.96319444444</v>
+        <v>46134.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46133.97361111111</v>
+        <v>46134.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46133.98402777778</v>
+        <v>46134.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46133.99444444444</v>
+        <v>46134.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46134.00486111111</v>
+        <v>46135.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46134.01527777778</v>
+        <v>46135.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46134.02569444444</v>
+        <v>46135.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46134.03611111111</v>
+        <v>46135.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="390">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,583 +31,1159 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.04.20261</t>
-  </si>
-  <si>
-    <t>21.04.20262</t>
-  </si>
-  <si>
-    <t>21.04.20263</t>
-  </si>
-  <si>
-    <t>21.04.20264</t>
-  </si>
-  <si>
-    <t>21.04.20265</t>
-  </si>
-  <si>
-    <t>21.04.20266</t>
-  </si>
-  <si>
-    <t>21.04.20267</t>
-  </si>
-  <si>
-    <t>21.04.20268</t>
-  </si>
-  <si>
-    <t>21.04.20269</t>
-  </si>
-  <si>
-    <t>21.04.202610</t>
-  </si>
-  <si>
-    <t>21.04.202611</t>
-  </si>
-  <si>
-    <t>21.04.202612</t>
-  </si>
-  <si>
-    <t>21.04.202613</t>
-  </si>
-  <si>
-    <t>21.04.202614</t>
-  </si>
-  <si>
-    <t>21.04.202615</t>
-  </si>
-  <si>
-    <t>21.04.202616</t>
-  </si>
-  <si>
-    <t>21.04.202617</t>
-  </si>
-  <si>
-    <t>21.04.202618</t>
-  </si>
-  <si>
-    <t>21.04.202619</t>
-  </si>
-  <si>
-    <t>21.04.202620</t>
-  </si>
-  <si>
-    <t>21.04.202621</t>
-  </si>
-  <si>
-    <t>21.04.202622</t>
-  </si>
-  <si>
-    <t>21.04.202623</t>
-  </si>
-  <si>
-    <t>21.04.202624</t>
-  </si>
-  <si>
-    <t>21.04.202625</t>
-  </si>
-  <si>
-    <t>21.04.202626</t>
-  </si>
-  <si>
-    <t>21.04.202627</t>
-  </si>
-  <si>
-    <t>21.04.202628</t>
-  </si>
-  <si>
-    <t>21.04.202629</t>
-  </si>
-  <si>
-    <t>21.04.202630</t>
-  </si>
-  <si>
-    <t>21.04.202631</t>
-  </si>
-  <si>
-    <t>21.04.202632</t>
-  </si>
-  <si>
-    <t>21.04.202633</t>
-  </si>
-  <si>
-    <t>21.04.202634</t>
-  </si>
-  <si>
-    <t>21.04.202635</t>
-  </si>
-  <si>
-    <t>21.04.202636</t>
-  </si>
-  <si>
-    <t>21.04.202637</t>
-  </si>
-  <si>
-    <t>21.04.202638</t>
-  </si>
-  <si>
-    <t>21.04.202639</t>
-  </si>
-  <si>
-    <t>21.04.202640</t>
-  </si>
-  <si>
-    <t>21.04.202641</t>
-  </si>
-  <si>
-    <t>21.04.202642</t>
-  </si>
-  <si>
-    <t>21.04.202643</t>
-  </si>
-  <si>
-    <t>21.04.202644</t>
-  </si>
-  <si>
-    <t>21.04.202645</t>
-  </si>
-  <si>
-    <t>21.04.202646</t>
-  </si>
-  <si>
-    <t>21.04.202647</t>
-  </si>
-  <si>
-    <t>21.04.202648</t>
-  </si>
-  <si>
-    <t>21.04.202649</t>
-  </si>
-  <si>
-    <t>21.04.202650</t>
-  </si>
-  <si>
-    <t>21.04.202651</t>
-  </si>
-  <si>
-    <t>21.04.202652</t>
-  </si>
-  <si>
-    <t>21.04.202653</t>
-  </si>
-  <si>
-    <t>21.04.202654</t>
-  </si>
-  <si>
-    <t>21.04.202655</t>
-  </si>
-  <si>
-    <t>21.04.202656</t>
-  </si>
-  <si>
-    <t>21.04.202657</t>
-  </si>
-  <si>
-    <t>21.04.202658</t>
-  </si>
-  <si>
-    <t>21.04.202659</t>
-  </si>
-  <si>
-    <t>21.04.202660</t>
-  </si>
-  <si>
-    <t>21.04.202661</t>
-  </si>
-  <si>
-    <t>21.04.202662</t>
-  </si>
-  <si>
-    <t>21.04.202663</t>
-  </si>
-  <si>
-    <t>21.04.202664</t>
-  </si>
-  <si>
-    <t>21.04.202665</t>
-  </si>
-  <si>
-    <t>21.04.202666</t>
-  </si>
-  <si>
-    <t>21.04.202667</t>
-  </si>
-  <si>
-    <t>21.04.202668</t>
-  </si>
-  <si>
-    <t>21.04.202669</t>
-  </si>
-  <si>
-    <t>21.04.202670</t>
-  </si>
-  <si>
-    <t>21.04.202671</t>
-  </si>
-  <si>
-    <t>21.04.202672</t>
-  </si>
-  <si>
-    <t>21.04.202673</t>
-  </si>
-  <si>
-    <t>21.04.202674</t>
-  </si>
-  <si>
-    <t>21.04.202675</t>
-  </si>
-  <si>
-    <t>21.04.202676</t>
-  </si>
-  <si>
-    <t>21.04.202677</t>
-  </si>
-  <si>
-    <t>21.04.202678</t>
-  </si>
-  <si>
-    <t>21.04.202679</t>
-  </si>
-  <si>
-    <t>21.04.202680</t>
-  </si>
-  <si>
-    <t>21.04.202681</t>
-  </si>
-  <si>
-    <t>21.04.202682</t>
-  </si>
-  <si>
-    <t>21.04.202683</t>
-  </si>
-  <si>
-    <t>21.04.202684</t>
-  </si>
-  <si>
-    <t>21.04.202685</t>
-  </si>
-  <si>
-    <t>21.04.202686</t>
-  </si>
-  <si>
-    <t>21.04.202687</t>
-  </si>
-  <si>
-    <t>21.04.202688</t>
-  </si>
-  <si>
-    <t>21.04.202689</t>
-  </si>
-  <si>
-    <t>21.04.202690</t>
-  </si>
-  <si>
-    <t>21.04.202691</t>
-  </si>
-  <si>
-    <t>21.04.202692</t>
-  </si>
-  <si>
-    <t>21.04.202693</t>
-  </si>
-  <si>
-    <t>22.04.202694</t>
-  </si>
-  <si>
-    <t>22.04.202695</t>
-  </si>
-  <si>
-    <t>22.04.202696</t>
-  </si>
-  <si>
-    <t>22.04.20261</t>
-  </si>
-  <si>
-    <t>22.04.20262</t>
-  </si>
-  <si>
-    <t>22.04.20263</t>
-  </si>
-  <si>
-    <t>22.04.20264</t>
-  </si>
-  <si>
-    <t>22.04.20265</t>
-  </si>
-  <si>
-    <t>22.04.20266</t>
-  </si>
-  <si>
-    <t>22.04.20267</t>
-  </si>
-  <si>
-    <t>22.04.20268</t>
-  </si>
-  <si>
-    <t>22.04.20269</t>
-  </si>
-  <si>
-    <t>22.04.202610</t>
-  </si>
-  <si>
-    <t>22.04.202611</t>
-  </si>
-  <si>
-    <t>22.04.202612</t>
-  </si>
-  <si>
-    <t>22.04.202613</t>
-  </si>
-  <si>
-    <t>22.04.202614</t>
-  </si>
-  <si>
-    <t>22.04.202615</t>
-  </si>
-  <si>
-    <t>22.04.202616</t>
-  </si>
-  <si>
-    <t>22.04.202617</t>
-  </si>
-  <si>
-    <t>22.04.202618</t>
-  </si>
-  <si>
-    <t>22.04.202619</t>
-  </si>
-  <si>
-    <t>22.04.202620</t>
-  </si>
-  <si>
-    <t>22.04.202621</t>
-  </si>
-  <si>
-    <t>22.04.202622</t>
-  </si>
-  <si>
-    <t>22.04.202623</t>
-  </si>
-  <si>
-    <t>22.04.202624</t>
-  </si>
-  <si>
-    <t>22.04.202625</t>
-  </si>
-  <si>
-    <t>22.04.202626</t>
-  </si>
-  <si>
-    <t>22.04.202627</t>
-  </si>
-  <si>
-    <t>22.04.202628</t>
-  </si>
-  <si>
-    <t>22.04.202629</t>
-  </si>
-  <si>
-    <t>22.04.202630</t>
-  </si>
-  <si>
-    <t>22.04.202631</t>
-  </si>
-  <si>
-    <t>22.04.202632</t>
-  </si>
-  <si>
-    <t>22.04.202633</t>
-  </si>
-  <si>
-    <t>22.04.202634</t>
-  </si>
-  <si>
-    <t>22.04.202635</t>
-  </si>
-  <si>
-    <t>22.04.202636</t>
-  </si>
-  <si>
-    <t>22.04.202637</t>
-  </si>
-  <si>
-    <t>22.04.202638</t>
-  </si>
-  <si>
-    <t>22.04.202639</t>
-  </si>
-  <si>
-    <t>22.04.202640</t>
-  </si>
-  <si>
-    <t>22.04.202641</t>
-  </si>
-  <si>
-    <t>22.04.202642</t>
-  </si>
-  <si>
-    <t>22.04.202643</t>
-  </si>
-  <si>
-    <t>22.04.202644</t>
-  </si>
-  <si>
-    <t>22.04.202645</t>
-  </si>
-  <si>
-    <t>22.04.202646</t>
-  </si>
-  <si>
-    <t>22.04.202647</t>
-  </si>
-  <si>
-    <t>22.04.202648</t>
-  </si>
-  <si>
-    <t>22.04.202649</t>
-  </si>
-  <si>
-    <t>22.04.202650</t>
-  </si>
-  <si>
-    <t>22.04.202651</t>
-  </si>
-  <si>
-    <t>22.04.202652</t>
-  </si>
-  <si>
-    <t>22.04.202653</t>
-  </si>
-  <si>
-    <t>22.04.202654</t>
-  </si>
-  <si>
-    <t>22.04.202655</t>
-  </si>
-  <si>
-    <t>22.04.202656</t>
-  </si>
-  <si>
-    <t>22.04.202657</t>
-  </si>
-  <si>
-    <t>22.04.202658</t>
-  </si>
-  <si>
-    <t>22.04.202659</t>
-  </si>
-  <si>
-    <t>22.04.202660</t>
-  </si>
-  <si>
-    <t>22.04.202661</t>
-  </si>
-  <si>
-    <t>22.04.202662</t>
-  </si>
-  <si>
-    <t>22.04.202663</t>
-  </si>
-  <si>
-    <t>22.04.202664</t>
-  </si>
-  <si>
-    <t>22.04.202665</t>
-  </si>
-  <si>
-    <t>22.04.202666</t>
-  </si>
-  <si>
-    <t>22.04.202667</t>
-  </si>
-  <si>
-    <t>22.04.202668</t>
-  </si>
-  <si>
-    <t>22.04.202669</t>
-  </si>
-  <si>
-    <t>22.04.202670</t>
-  </si>
-  <si>
-    <t>22.04.202671</t>
-  </si>
-  <si>
-    <t>22.04.202672</t>
-  </si>
-  <si>
-    <t>22.04.202673</t>
-  </si>
-  <si>
-    <t>22.04.202674</t>
-  </si>
-  <si>
-    <t>22.04.202675</t>
-  </si>
-  <si>
-    <t>22.04.202676</t>
-  </si>
-  <si>
-    <t>22.04.202677</t>
-  </si>
-  <si>
-    <t>22.04.202678</t>
-  </si>
-  <si>
-    <t>22.04.202679</t>
-  </si>
-  <si>
-    <t>22.04.202680</t>
-  </si>
-  <si>
-    <t>22.04.202681</t>
-  </si>
-  <si>
-    <t>22.04.202682</t>
-  </si>
-  <si>
-    <t>22.04.202683</t>
-  </si>
-  <si>
-    <t>22.04.202684</t>
-  </si>
-  <si>
-    <t>22.04.202685</t>
-  </si>
-  <si>
-    <t>22.04.202686</t>
-  </si>
-  <si>
-    <t>22.04.202687</t>
-  </si>
-  <si>
-    <t>22.04.202688</t>
-  </si>
-  <si>
-    <t>22.04.202689</t>
-  </si>
-  <si>
-    <t>22.04.202690</t>
-  </si>
-  <si>
-    <t>22.04.202691</t>
-  </si>
-  <si>
-    <t>22.04.202692</t>
-  </si>
-  <si>
-    <t>22.04.202693</t>
-  </si>
-  <si>
-    <t>23.04.202695</t>
-  </si>
-  <si>
-    <t>23.04.202696</t>
-  </si>
-  <si>
-    <t>23.04.20261</t>
-  </si>
-  <si>
-    <t>23.04.20262</t>
+    <t>24.04.20261</t>
+  </si>
+  <si>
+    <t>24.04.20262</t>
+  </si>
+  <si>
+    <t>24.04.20263</t>
+  </si>
+  <si>
+    <t>24.04.20264</t>
+  </si>
+  <si>
+    <t>24.04.20265</t>
+  </si>
+  <si>
+    <t>24.04.20266</t>
+  </si>
+  <si>
+    <t>24.04.20267</t>
+  </si>
+  <si>
+    <t>24.04.20268</t>
+  </si>
+  <si>
+    <t>24.04.20269</t>
+  </si>
+  <si>
+    <t>24.04.202610</t>
+  </si>
+  <si>
+    <t>24.04.202611</t>
+  </si>
+  <si>
+    <t>24.04.202612</t>
+  </si>
+  <si>
+    <t>24.04.202613</t>
+  </si>
+  <si>
+    <t>24.04.202614</t>
+  </si>
+  <si>
+    <t>24.04.202615</t>
+  </si>
+  <si>
+    <t>24.04.202616</t>
+  </si>
+  <si>
+    <t>24.04.202617</t>
+  </si>
+  <si>
+    <t>24.04.202618</t>
+  </si>
+  <si>
+    <t>24.04.202619</t>
+  </si>
+  <si>
+    <t>24.04.202620</t>
+  </si>
+  <si>
+    <t>24.04.202621</t>
+  </si>
+  <si>
+    <t>24.04.202622</t>
+  </si>
+  <si>
+    <t>24.04.202623</t>
+  </si>
+  <si>
+    <t>24.04.202624</t>
+  </si>
+  <si>
+    <t>24.04.202625</t>
+  </si>
+  <si>
+    <t>24.04.202626</t>
+  </si>
+  <si>
+    <t>24.04.202627</t>
+  </si>
+  <si>
+    <t>24.04.202628</t>
+  </si>
+  <si>
+    <t>24.04.202629</t>
+  </si>
+  <si>
+    <t>24.04.202630</t>
+  </si>
+  <si>
+    <t>24.04.202631</t>
+  </si>
+  <si>
+    <t>24.04.202632</t>
+  </si>
+  <si>
+    <t>24.04.202633</t>
+  </si>
+  <si>
+    <t>24.04.202634</t>
+  </si>
+  <si>
+    <t>24.04.202635</t>
+  </si>
+  <si>
+    <t>24.04.202636</t>
+  </si>
+  <si>
+    <t>24.04.202637</t>
+  </si>
+  <si>
+    <t>24.04.202638</t>
+  </si>
+  <si>
+    <t>24.04.202639</t>
+  </si>
+  <si>
+    <t>24.04.202640</t>
+  </si>
+  <si>
+    <t>24.04.202641</t>
+  </si>
+  <si>
+    <t>24.04.202642</t>
+  </si>
+  <si>
+    <t>24.04.202643</t>
+  </si>
+  <si>
+    <t>24.04.202644</t>
+  </si>
+  <si>
+    <t>24.04.202645</t>
+  </si>
+  <si>
+    <t>24.04.202646</t>
+  </si>
+  <si>
+    <t>24.04.202647</t>
+  </si>
+  <si>
+    <t>24.04.202648</t>
+  </si>
+  <si>
+    <t>24.04.202649</t>
+  </si>
+  <si>
+    <t>24.04.202650</t>
+  </si>
+  <si>
+    <t>24.04.202651</t>
+  </si>
+  <si>
+    <t>24.04.202652</t>
+  </si>
+  <si>
+    <t>24.04.202653</t>
+  </si>
+  <si>
+    <t>24.04.202654</t>
+  </si>
+  <si>
+    <t>24.04.202655</t>
+  </si>
+  <si>
+    <t>24.04.202656</t>
+  </si>
+  <si>
+    <t>24.04.202657</t>
+  </si>
+  <si>
+    <t>24.04.202658</t>
+  </si>
+  <si>
+    <t>24.04.202659</t>
+  </si>
+  <si>
+    <t>24.04.202660</t>
+  </si>
+  <si>
+    <t>24.04.202661</t>
+  </si>
+  <si>
+    <t>24.04.202662</t>
+  </si>
+  <si>
+    <t>24.04.202663</t>
+  </si>
+  <si>
+    <t>24.04.202664</t>
+  </si>
+  <si>
+    <t>24.04.202665</t>
+  </si>
+  <si>
+    <t>24.04.202666</t>
+  </si>
+  <si>
+    <t>24.04.202667</t>
+  </si>
+  <si>
+    <t>24.04.202668</t>
+  </si>
+  <si>
+    <t>24.04.202669</t>
+  </si>
+  <si>
+    <t>24.04.202670</t>
+  </si>
+  <si>
+    <t>24.04.202671</t>
+  </si>
+  <si>
+    <t>24.04.202672</t>
+  </si>
+  <si>
+    <t>24.04.202673</t>
+  </si>
+  <si>
+    <t>24.04.202674</t>
+  </si>
+  <si>
+    <t>24.04.202675</t>
+  </si>
+  <si>
+    <t>24.04.202676</t>
+  </si>
+  <si>
+    <t>24.04.202677</t>
+  </si>
+  <si>
+    <t>24.04.202678</t>
+  </si>
+  <si>
+    <t>24.04.202679</t>
+  </si>
+  <si>
+    <t>24.04.202680</t>
+  </si>
+  <si>
+    <t>24.04.202681</t>
+  </si>
+  <si>
+    <t>24.04.202682</t>
+  </si>
+  <si>
+    <t>24.04.202683</t>
+  </si>
+  <si>
+    <t>24.04.202684</t>
+  </si>
+  <si>
+    <t>24.04.202685</t>
+  </si>
+  <si>
+    <t>24.04.202686</t>
+  </si>
+  <si>
+    <t>24.04.202687</t>
+  </si>
+  <si>
+    <t>24.04.202688</t>
+  </si>
+  <si>
+    <t>24.04.202689</t>
+  </si>
+  <si>
+    <t>24.04.202690</t>
+  </si>
+  <si>
+    <t>24.04.202691</t>
+  </si>
+  <si>
+    <t>24.04.202692</t>
+  </si>
+  <si>
+    <t>24.04.202693</t>
+  </si>
+  <si>
+    <t>25.04.202694</t>
+  </si>
+  <si>
+    <t>25.04.202695</t>
+  </si>
+  <si>
+    <t>25.04.202696</t>
+  </si>
+  <si>
+    <t>25.04.20261</t>
+  </si>
+  <si>
+    <t>25.04.20262</t>
+  </si>
+  <si>
+    <t>25.04.20263</t>
+  </si>
+  <si>
+    <t>25.04.20264</t>
+  </si>
+  <si>
+    <t>25.04.20265</t>
+  </si>
+  <si>
+    <t>25.04.20266</t>
+  </si>
+  <si>
+    <t>25.04.20267</t>
+  </si>
+  <si>
+    <t>25.04.20268</t>
+  </si>
+  <si>
+    <t>25.04.20269</t>
+  </si>
+  <si>
+    <t>25.04.202610</t>
+  </si>
+  <si>
+    <t>25.04.202611</t>
+  </si>
+  <si>
+    <t>25.04.202612</t>
+  </si>
+  <si>
+    <t>25.04.202613</t>
+  </si>
+  <si>
+    <t>25.04.202614</t>
+  </si>
+  <si>
+    <t>25.04.202615</t>
+  </si>
+  <si>
+    <t>25.04.202616</t>
+  </si>
+  <si>
+    <t>25.04.202617</t>
+  </si>
+  <si>
+    <t>25.04.202618</t>
+  </si>
+  <si>
+    <t>25.04.202619</t>
+  </si>
+  <si>
+    <t>25.04.202620</t>
+  </si>
+  <si>
+    <t>25.04.202621</t>
+  </si>
+  <si>
+    <t>25.04.202622</t>
+  </si>
+  <si>
+    <t>25.04.202623</t>
+  </si>
+  <si>
+    <t>25.04.202624</t>
+  </si>
+  <si>
+    <t>25.04.202625</t>
+  </si>
+  <si>
+    <t>25.04.202626</t>
+  </si>
+  <si>
+    <t>25.04.202627</t>
+  </si>
+  <si>
+    <t>25.04.202628</t>
+  </si>
+  <si>
+    <t>25.04.202629</t>
+  </si>
+  <si>
+    <t>25.04.202630</t>
+  </si>
+  <si>
+    <t>25.04.202631</t>
+  </si>
+  <si>
+    <t>25.04.202632</t>
+  </si>
+  <si>
+    <t>25.04.202633</t>
+  </si>
+  <si>
+    <t>25.04.202634</t>
+  </si>
+  <si>
+    <t>25.04.202635</t>
+  </si>
+  <si>
+    <t>25.04.202636</t>
+  </si>
+  <si>
+    <t>25.04.202637</t>
+  </si>
+  <si>
+    <t>25.04.202638</t>
+  </si>
+  <si>
+    <t>25.04.202639</t>
+  </si>
+  <si>
+    <t>25.04.202640</t>
+  </si>
+  <si>
+    <t>25.04.202641</t>
+  </si>
+  <si>
+    <t>25.04.202642</t>
+  </si>
+  <si>
+    <t>25.04.202643</t>
+  </si>
+  <si>
+    <t>25.04.202644</t>
+  </si>
+  <si>
+    <t>25.04.202645</t>
+  </si>
+  <si>
+    <t>25.04.202646</t>
+  </si>
+  <si>
+    <t>25.04.202647</t>
+  </si>
+  <si>
+    <t>25.04.202648</t>
+  </si>
+  <si>
+    <t>25.04.202649</t>
+  </si>
+  <si>
+    <t>25.04.202650</t>
+  </si>
+  <si>
+    <t>25.04.202651</t>
+  </si>
+  <si>
+    <t>25.04.202652</t>
+  </si>
+  <si>
+    <t>25.04.202653</t>
+  </si>
+  <si>
+    <t>25.04.202654</t>
+  </si>
+  <si>
+    <t>25.04.202655</t>
+  </si>
+  <si>
+    <t>25.04.202656</t>
+  </si>
+  <si>
+    <t>25.04.202657</t>
+  </si>
+  <si>
+    <t>25.04.202658</t>
+  </si>
+  <si>
+    <t>25.04.202659</t>
+  </si>
+  <si>
+    <t>25.04.202660</t>
+  </si>
+  <si>
+    <t>25.04.202661</t>
+  </si>
+  <si>
+    <t>25.04.202662</t>
+  </si>
+  <si>
+    <t>25.04.202663</t>
+  </si>
+  <si>
+    <t>25.04.202664</t>
+  </si>
+  <si>
+    <t>25.04.202665</t>
+  </si>
+  <si>
+    <t>25.04.202666</t>
+  </si>
+  <si>
+    <t>25.04.202667</t>
+  </si>
+  <si>
+    <t>25.04.202668</t>
+  </si>
+  <si>
+    <t>25.04.202669</t>
+  </si>
+  <si>
+    <t>25.04.202670</t>
+  </si>
+  <si>
+    <t>25.04.202671</t>
+  </si>
+  <si>
+    <t>25.04.202672</t>
+  </si>
+  <si>
+    <t>25.04.202673</t>
+  </si>
+  <si>
+    <t>25.04.202674</t>
+  </si>
+  <si>
+    <t>25.04.202675</t>
+  </si>
+  <si>
+    <t>25.04.202676</t>
+  </si>
+  <si>
+    <t>25.04.202677</t>
+  </si>
+  <si>
+    <t>25.04.202678</t>
+  </si>
+  <si>
+    <t>25.04.202679</t>
+  </si>
+  <si>
+    <t>25.04.202680</t>
+  </si>
+  <si>
+    <t>25.04.202681</t>
+  </si>
+  <si>
+    <t>25.04.202682</t>
+  </si>
+  <si>
+    <t>25.04.202683</t>
+  </si>
+  <si>
+    <t>25.04.202684</t>
+  </si>
+  <si>
+    <t>25.04.202685</t>
+  </si>
+  <si>
+    <t>25.04.202686</t>
+  </si>
+  <si>
+    <t>25.04.202687</t>
+  </si>
+  <si>
+    <t>25.04.202688</t>
+  </si>
+  <si>
+    <t>25.04.202689</t>
+  </si>
+  <si>
+    <t>25.04.202690</t>
+  </si>
+  <si>
+    <t>25.04.202691</t>
+  </si>
+  <si>
+    <t>25.04.202692</t>
+  </si>
+  <si>
+    <t>25.04.202693</t>
+  </si>
+  <si>
+    <t>26.04.202695</t>
+  </si>
+  <si>
+    <t>26.04.202696</t>
+  </si>
+  <si>
+    <t>26.04.20261</t>
+  </si>
+  <si>
+    <t>26.04.20262</t>
+  </si>
+  <si>
+    <t>26.04.20263</t>
+  </si>
+  <si>
+    <t>26.04.20264</t>
+  </si>
+  <si>
+    <t>26.04.20265</t>
+  </si>
+  <si>
+    <t>26.04.20266</t>
+  </si>
+  <si>
+    <t>26.04.20267</t>
+  </si>
+  <si>
+    <t>26.04.20268</t>
+  </si>
+  <si>
+    <t>26.04.20269</t>
+  </si>
+  <si>
+    <t>26.04.202610</t>
+  </si>
+  <si>
+    <t>26.04.202611</t>
+  </si>
+  <si>
+    <t>26.04.202612</t>
+  </si>
+  <si>
+    <t>26.04.202613</t>
+  </si>
+  <si>
+    <t>26.04.202614</t>
+  </si>
+  <si>
+    <t>26.04.202615</t>
+  </si>
+  <si>
+    <t>26.04.202616</t>
+  </si>
+  <si>
+    <t>26.04.202617</t>
+  </si>
+  <si>
+    <t>26.04.202618</t>
+  </si>
+  <si>
+    <t>26.04.202619</t>
+  </si>
+  <si>
+    <t>26.04.202620</t>
+  </si>
+  <si>
+    <t>26.04.202621</t>
+  </si>
+  <si>
+    <t>26.04.202622</t>
+  </si>
+  <si>
+    <t>26.04.202623</t>
+  </si>
+  <si>
+    <t>26.04.202624</t>
+  </si>
+  <si>
+    <t>26.04.202625</t>
+  </si>
+  <si>
+    <t>26.04.202626</t>
+  </si>
+  <si>
+    <t>26.04.202627</t>
+  </si>
+  <si>
+    <t>26.04.202628</t>
+  </si>
+  <si>
+    <t>26.04.202629</t>
+  </si>
+  <si>
+    <t>26.04.202630</t>
+  </si>
+  <si>
+    <t>26.04.202631</t>
+  </si>
+  <si>
+    <t>26.04.202632</t>
+  </si>
+  <si>
+    <t>26.04.202633</t>
+  </si>
+  <si>
+    <t>26.04.202634</t>
+  </si>
+  <si>
+    <t>26.04.202635</t>
+  </si>
+  <si>
+    <t>26.04.202636</t>
+  </si>
+  <si>
+    <t>26.04.202637</t>
+  </si>
+  <si>
+    <t>26.04.202638</t>
+  </si>
+  <si>
+    <t>26.04.202639</t>
+  </si>
+  <si>
+    <t>26.04.202640</t>
+  </si>
+  <si>
+    <t>26.04.202641</t>
+  </si>
+  <si>
+    <t>26.04.202642</t>
+  </si>
+  <si>
+    <t>26.04.202643</t>
+  </si>
+  <si>
+    <t>26.04.202644</t>
+  </si>
+  <si>
+    <t>26.04.202645</t>
+  </si>
+  <si>
+    <t>26.04.202646</t>
+  </si>
+  <si>
+    <t>26.04.202647</t>
+  </si>
+  <si>
+    <t>26.04.202648</t>
+  </si>
+  <si>
+    <t>26.04.202649</t>
+  </si>
+  <si>
+    <t>26.04.202650</t>
+  </si>
+  <si>
+    <t>26.04.202651</t>
+  </si>
+  <si>
+    <t>26.04.202652</t>
+  </si>
+  <si>
+    <t>26.04.202653</t>
+  </si>
+  <si>
+    <t>26.04.202654</t>
+  </si>
+  <si>
+    <t>26.04.202655</t>
+  </si>
+  <si>
+    <t>26.04.202656</t>
+  </si>
+  <si>
+    <t>26.04.202657</t>
+  </si>
+  <si>
+    <t>26.04.202658</t>
+  </si>
+  <si>
+    <t>26.04.202659</t>
+  </si>
+  <si>
+    <t>26.04.202660</t>
+  </si>
+  <si>
+    <t>26.04.202661</t>
+  </si>
+  <si>
+    <t>26.04.202662</t>
+  </si>
+  <si>
+    <t>26.04.202663</t>
+  </si>
+  <si>
+    <t>26.04.202664</t>
+  </si>
+  <si>
+    <t>26.04.202665</t>
+  </si>
+  <si>
+    <t>26.04.202666</t>
+  </si>
+  <si>
+    <t>26.04.202667</t>
+  </si>
+  <si>
+    <t>26.04.202668</t>
+  </si>
+  <si>
+    <t>26.04.202669</t>
+  </si>
+  <si>
+    <t>26.04.202670</t>
+  </si>
+  <si>
+    <t>26.04.202671</t>
+  </si>
+  <si>
+    <t>26.04.202672</t>
+  </si>
+  <si>
+    <t>26.04.202673</t>
+  </si>
+  <si>
+    <t>26.04.202674</t>
+  </si>
+  <si>
+    <t>26.04.202675</t>
+  </si>
+  <si>
+    <t>26.04.202676</t>
+  </si>
+  <si>
+    <t>26.04.202677</t>
+  </si>
+  <si>
+    <t>26.04.202678</t>
+  </si>
+  <si>
+    <t>26.04.202679</t>
+  </si>
+  <si>
+    <t>26.04.202680</t>
+  </si>
+  <si>
+    <t>26.04.202681</t>
+  </si>
+  <si>
+    <t>26.04.202682</t>
+  </si>
+  <si>
+    <t>26.04.202683</t>
+  </si>
+  <si>
+    <t>26.04.202684</t>
+  </si>
+  <si>
+    <t>26.04.202685</t>
+  </si>
+  <si>
+    <t>26.04.202686</t>
+  </si>
+  <si>
+    <t>26.04.202687</t>
+  </si>
+  <si>
+    <t>26.04.202688</t>
+  </si>
+  <si>
+    <t>26.04.202689</t>
+  </si>
+  <si>
+    <t>26.04.202690</t>
+  </si>
+  <si>
+    <t>26.04.202691</t>
+  </si>
+  <si>
+    <t>26.04.202692</t>
+  </si>
+  <si>
+    <t>26.04.202693</t>
+  </si>
+  <si>
+    <t>26.04.202694</t>
+  </si>
+  <si>
+    <t>27.04.202696</t>
+  </si>
+  <si>
+    <t>27.04.20261</t>
+  </si>
+  <si>
+    <t>27.04.20262</t>
+  </si>
+  <si>
+    <t>27.04.20263</t>
+  </si>
+  <si>
+    <t>27.04.20264</t>
+  </si>
+  <si>
+    <t>27.04.20265</t>
+  </si>
+  <si>
+    <t>27.04.20266</t>
+  </si>
+  <si>
+    <t>27.04.20267</t>
+  </si>
+  <si>
+    <t>27.04.20268</t>
+  </si>
+  <si>
+    <t>27.04.20269</t>
+  </si>
+  <si>
+    <t>27.04.202610</t>
+  </si>
+  <si>
+    <t>27.04.202611</t>
+  </si>
+  <si>
+    <t>27.04.202612</t>
+  </si>
+  <si>
+    <t>27.04.202613</t>
+  </si>
+  <si>
+    <t>27.04.202614</t>
+  </si>
+  <si>
+    <t>27.04.202615</t>
+  </si>
+  <si>
+    <t>27.04.202616</t>
+  </si>
+  <si>
+    <t>27.04.202617</t>
+  </si>
+  <si>
+    <t>27.04.202618</t>
+  </si>
+  <si>
+    <t>27.04.202619</t>
+  </si>
+  <si>
+    <t>27.04.202620</t>
+  </si>
+  <si>
+    <t>27.04.202621</t>
+  </si>
+  <si>
+    <t>27.04.202622</t>
+  </si>
+  <si>
+    <t>27.04.202623</t>
+  </si>
+  <si>
+    <t>27.04.202624</t>
+  </si>
+  <si>
+    <t>27.04.202625</t>
+  </si>
+  <si>
+    <t>27.04.202626</t>
+  </si>
+  <si>
+    <t>27.04.202627</t>
+  </si>
+  <si>
+    <t>27.04.202628</t>
+  </si>
+  <si>
+    <t>27.04.202629</t>
+  </si>
+  <si>
+    <t>27.04.202630</t>
+  </si>
+  <si>
+    <t>27.04.202631</t>
+  </si>
+  <si>
+    <t>27.04.202632</t>
+  </si>
+  <si>
+    <t>27.04.202633</t>
+  </si>
+  <si>
+    <t>27.04.202634</t>
+  </si>
+  <si>
+    <t>27.04.202635</t>
+  </si>
+  <si>
+    <t>27.04.202636</t>
+  </si>
+  <si>
+    <t>27.04.202637</t>
+  </si>
+  <si>
+    <t>27.04.202638</t>
+  </si>
+  <si>
+    <t>27.04.202639</t>
+  </si>
+  <si>
+    <t>27.04.202640</t>
+  </si>
+  <si>
+    <t>27.04.202641</t>
+  </si>
+  <si>
+    <t>27.04.202642</t>
+  </si>
+  <si>
+    <t>27.04.202643</t>
+  </si>
+  <si>
+    <t>27.04.202644</t>
+  </si>
+  <si>
+    <t>27.04.202645</t>
+  </si>
+  <si>
+    <t>27.04.202646</t>
+  </si>
+  <si>
+    <t>27.04.202647</t>
+  </si>
+  <si>
+    <t>27.04.202648</t>
+  </si>
+  <si>
+    <t>27.04.202649</t>
+  </si>
+  <si>
+    <t>27.04.202650</t>
+  </si>
+  <si>
+    <t>27.04.202651</t>
+  </si>
+  <si>
+    <t>27.04.202652</t>
+  </si>
+  <si>
+    <t>27.04.202653</t>
+  </si>
+  <si>
+    <t>27.04.202654</t>
+  </si>
+  <si>
+    <t>27.04.202655</t>
+  </si>
+  <si>
+    <t>27.04.202656</t>
+  </si>
+  <si>
+    <t>27.04.202657</t>
+  </si>
+  <si>
+    <t>27.04.202658</t>
+  </si>
+  <si>
+    <t>27.04.202659</t>
+  </si>
+  <si>
+    <t>27.04.202660</t>
+  </si>
+  <si>
+    <t>27.04.202661</t>
+  </si>
+  <si>
+    <t>27.04.202662</t>
+  </si>
+  <si>
+    <t>27.04.202663</t>
+  </si>
+  <si>
+    <t>27.04.202664</t>
+  </si>
+  <si>
+    <t>27.04.202665</t>
+  </si>
+  <si>
+    <t>27.04.202666</t>
+  </si>
+  <si>
+    <t>27.04.202667</t>
+  </si>
+  <si>
+    <t>27.04.202668</t>
+  </si>
+  <si>
+    <t>27.04.202669</t>
+  </si>
+  <si>
+    <t>27.04.202670</t>
+  </si>
+  <si>
+    <t>27.04.202671</t>
+  </si>
+  <si>
+    <t>27.04.202672</t>
+  </si>
+  <si>
+    <t>27.04.202673</t>
+  </si>
+  <si>
+    <t>27.04.202674</t>
+  </si>
+  <si>
+    <t>27.04.202675</t>
+  </si>
+  <si>
+    <t>27.04.202676</t>
+  </si>
+  <si>
+    <t>27.04.202677</t>
+  </si>
+  <si>
+    <t>27.04.202678</t>
+  </si>
+  <si>
+    <t>27.04.202679</t>
+  </si>
+  <si>
+    <t>27.04.202680</t>
+  </si>
+  <si>
+    <t>27.04.202681</t>
+  </si>
+  <si>
+    <t>27.04.202682</t>
+  </si>
+  <si>
+    <t>27.04.202683</t>
+  </si>
+  <si>
+    <t>27.04.202684</t>
+  </si>
+  <si>
+    <t>27.04.202685</t>
+  </si>
+  <si>
+    <t>27.04.202686</t>
+  </si>
+  <si>
+    <t>27.04.202687</t>
+  </si>
+  <si>
+    <t>27.04.202688</t>
+  </si>
+  <si>
+    <t>27.04.202689</t>
+  </si>
+  <si>
+    <t>27.04.202690</t>
+  </si>
+  <si>
+    <t>27.04.202691</t>
+  </si>
+  <si>
+    <t>27.04.202692</t>
+  </si>
+  <si>
+    <t>27.04.202693</t>
+  </si>
+  <si>
+    <t>27.04.202694</t>
+  </si>
+  <si>
+    <t>27.04.202695</t>
+  </si>
+  <si>
+    <t>28.04.20261</t>
+  </si>
+  <si>
+    <t>28.04.20262</t>
+  </si>
+  <si>
+    <t>28.04.20263</t>
+  </si>
+  <si>
+    <t>28.04.20264</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E389"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -991,7 +1567,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46133.03611111111</v>
+        <v>46136.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1584,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46133.04652777778</v>
+        <v>46136.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1601,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46133.05694444444</v>
+        <v>46136.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1618,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46133.06736111111</v>
+        <v>46136.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1635,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46133.07777777778</v>
+        <v>46136.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1652,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46133.08819444444</v>
+        <v>46136.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1669,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46133.09861111111</v>
+        <v>46136.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1686,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46133.10902777778</v>
+        <v>46136.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1703,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46133.11944444444</v>
+        <v>46136.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1720,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46133.12986111111</v>
+        <v>46136.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1737,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46133.14027777778</v>
+        <v>46136.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1754,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46133.15069444444</v>
+        <v>46136.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1771,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46133.16111111111</v>
+        <v>46136.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1788,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46133.17152777778</v>
+        <v>46136.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1805,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46133.18194444444</v>
+        <v>46136.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1822,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46133.19236111111</v>
+        <v>46136.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1839,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46133.20277777778</v>
+        <v>46136.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1856,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46133.21319444444</v>
+        <v>46136.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1873,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46133.22361111111</v>
+        <v>46136.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1890,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46133.23402777778</v>
+        <v>46136.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1907,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46133.24444444444</v>
+        <v>46136.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1924,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46133.25486111111</v>
+        <v>46136.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1941,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46133.26527777778</v>
+        <v>46136.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1958,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46133.27569444444</v>
+        <v>46136.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1975,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46133.28611111111</v>
+        <v>46136.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1992,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46133.29652777778</v>
+        <v>46136.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +2009,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46133.30694444444</v>
+        <v>46136.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +2026,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46133.31736111111</v>
+        <v>46136.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +2043,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46133.32777777778</v>
+        <v>46136.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +2060,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46133.33819444444</v>
+        <v>46136.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +2077,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46133.34861111111</v>
+        <v>46136.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +2094,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46133.35902777778</v>
+        <v>46136.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +2111,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46133.36944444444</v>
+        <v>46136.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +2128,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46133.37986111111</v>
+        <v>46136.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +2145,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46133.39027777778</v>
+        <v>46136.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +2162,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46133.40069444444</v>
+        <v>46136.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +2179,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46133.41111111111</v>
+        <v>46136.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +2196,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46133.42152777778</v>
+        <v>46136.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +2213,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46133.43194444444</v>
+        <v>46136.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +2230,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46133.44236111111</v>
+        <v>46136.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +2247,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46133.45277777778</v>
+        <v>46136.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +2264,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46133.46319444444</v>
+        <v>46136.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +2281,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46133.47361111111</v>
+        <v>46136.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +2298,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46133.48402777778</v>
+        <v>46136.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +2315,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46133.49444444444</v>
+        <v>46136.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +2332,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46133.50486111111</v>
+        <v>46136.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +2349,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46133.51527777778</v>
+        <v>46136.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +2366,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46133.52569444444</v>
+        <v>46136.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +2383,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46133.53611111111</v>
+        <v>46136.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +2400,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46133.54652777778</v>
+        <v>46136.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +2417,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46133.55694444444</v>
+        <v>46136.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +2434,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46133.56736111111</v>
+        <v>46136.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +2451,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46133.57777777778</v>
+        <v>46136.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +2468,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46133.58819444444</v>
+        <v>46136.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +2485,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46133.59861111111</v>
+        <v>46136.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +2502,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46133.60902777778</v>
+        <v>46136.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +2519,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46133.61944444444</v>
+        <v>46136.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +2536,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46133.62986111111</v>
+        <v>46136.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +2553,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46133.64027777778</v>
+        <v>46136.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +2570,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46133.65069444444</v>
+        <v>46136.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2587,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46133.66111111111</v>
+        <v>46136.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2604,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46133.67152777778</v>
+        <v>46136.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2621,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46133.68194444444</v>
+        <v>46136.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2638,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46133.69236111111</v>
+        <v>46136.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2655,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46133.70277777778</v>
+        <v>46136.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2672,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46133.71319444444</v>
+        <v>46136.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2689,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46133.72361111111</v>
+        <v>46136.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2706,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46133.73402777778</v>
+        <v>46136.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2723,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46133.74444444444</v>
+        <v>46136.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2740,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46133.75486111111</v>
+        <v>46136.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2757,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46133.76527777778</v>
+        <v>46136.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2774,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46133.77569444444</v>
+        <v>46136.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2791,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46133.78611111111</v>
+        <v>46136.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2808,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46133.79652777778</v>
+        <v>46136.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2825,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46133.80694444444</v>
+        <v>46136.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2842,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46133.81736111111</v>
+        <v>46136.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2859,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46133.82777777778</v>
+        <v>46136.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2876,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46133.83819444444</v>
+        <v>46136.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2893,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46133.84861111111</v>
+        <v>46136.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2910,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46133.85902777778</v>
+        <v>46136.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2927,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46133.86944444444</v>
+        <v>46136.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2944,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46133.87986111111</v>
+        <v>46136.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2961,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46133.89027777778</v>
+        <v>46136.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2978,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46133.90069444444</v>
+        <v>46136.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2995,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46133.91111111111</v>
+        <v>46136.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +3012,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46133.92152777778</v>
+        <v>46136.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +3029,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46133.93194444444</v>
+        <v>46136.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +3046,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46133.94236111111</v>
+        <v>46136.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +3063,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46133.95277777778</v>
+        <v>46136.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +3080,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46133.96319444444</v>
+        <v>46136.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +3097,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46133.97361111111</v>
+        <v>46136.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +3114,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46133.98402777778</v>
+        <v>46136.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +3131,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46133.99444444444</v>
+        <v>46136.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +3148,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46134.00486111111</v>
+        <v>46137.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +3165,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46134.01527777778</v>
+        <v>46137.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +3182,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46134.02569444444</v>
+        <v>46137.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +3199,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46134.03611111111</v>
+        <v>46137.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +3216,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46134.03611111111</v>
+        <v>46137.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +3233,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46134.04652777778</v>
+        <v>46137.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +3250,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46134.05694444444</v>
+        <v>46137.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +3267,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46134.06736111111</v>
+        <v>46137.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +3284,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46134.07777777778</v>
+        <v>46137.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +3301,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46134.08819444444</v>
+        <v>46137.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +3318,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46134.09861111111</v>
+        <v>46137.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +3335,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46134.10902777778</v>
+        <v>46137.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +3352,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46134.11944444444</v>
+        <v>46137.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +3369,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46134.12986111111</v>
+        <v>46137.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +3386,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46134.14027777778</v>
+        <v>46137.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +3403,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46134.15069444444</v>
+        <v>46137.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +3420,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46134.16111111111</v>
+        <v>46137.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +3437,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46134.17152777778</v>
+        <v>46137.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +3454,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46134.18194444444</v>
+        <v>46137.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +3471,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46134.19236111111</v>
+        <v>46137.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +3488,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46134.20277777778</v>
+        <v>46137.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +3505,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46134.21319444444</v>
+        <v>46137.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +3522,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46134.22361111111</v>
+        <v>46137.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +3539,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46134.23402777778</v>
+        <v>46137.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +3556,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46134.24444444444</v>
+        <v>46137.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +3573,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46134.25486111111</v>
+        <v>46137.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3590,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46134.26527777778</v>
+        <v>46137.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3607,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46134.27569444444</v>
+        <v>46137.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3624,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46134.28611111111</v>
+        <v>46137.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3641,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46134.29652777778</v>
+        <v>46137.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3658,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46134.30694444444</v>
+        <v>46137.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3675,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46134.31736111111</v>
+        <v>46137.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3692,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46134.32777777778</v>
+        <v>46137.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3709,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46134.33819444444</v>
+        <v>46137.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3726,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46134.34861111111</v>
+        <v>46137.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3743,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46134.35902777778</v>
+        <v>46137.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3760,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46134.36944444444</v>
+        <v>46137.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3777,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46134.37986111111</v>
+        <v>46137.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3794,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46134.39027777778</v>
+        <v>46137.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3811,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46134.40069444444</v>
+        <v>46137.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3828,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46134.41111111111</v>
+        <v>46137.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3845,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46134.42152777778</v>
+        <v>46137.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3862,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46134.43194444444</v>
+        <v>46137.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3879,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46134.44236111111</v>
+        <v>46137.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3896,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46134.45277777778</v>
+        <v>46137.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3913,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46134.46319444444</v>
+        <v>46137.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3930,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46134.47361111111</v>
+        <v>46137.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3947,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46134.48402777778</v>
+        <v>46137.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3964,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46134.49444444444</v>
+        <v>46137.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3981,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46134.50486111111</v>
+        <v>46137.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3998,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46134.51527777778</v>
+        <v>46137.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +4015,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46134.52569444444</v>
+        <v>46137.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +4032,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46134.53611111111</v>
+        <v>46137.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +4049,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46134.54652777778</v>
+        <v>46137.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +4066,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46134.55694444444</v>
+        <v>46137.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +4083,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46134.56736111111</v>
+        <v>46137.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +4100,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46134.57777777778</v>
+        <v>46137.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +4117,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46134.58819444444</v>
+        <v>46137.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +4134,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46134.59861111111</v>
+        <v>46137.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +4151,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46134.60902777778</v>
+        <v>46137.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +4168,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46134.61944444444</v>
+        <v>46137.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +4185,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46134.62986111111</v>
+        <v>46137.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +4202,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46134.64027777778</v>
+        <v>46137.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +4219,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46134.65069444444</v>
+        <v>46137.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +4236,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46134.66111111111</v>
+        <v>46137.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +4253,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46134.67152777778</v>
+        <v>46137.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +4270,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46134.68194444444</v>
+        <v>46137.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +4287,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46134.69236111111</v>
+        <v>46137.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +4304,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46134.70277777778</v>
+        <v>46137.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +4321,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46134.71319444444</v>
+        <v>46137.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +4338,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46134.72361111111</v>
+        <v>46137.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +4355,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46134.73402777778</v>
+        <v>46137.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +4372,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46134.74444444444</v>
+        <v>46137.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +4389,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46134.75486111111</v>
+        <v>46137.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +4406,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46134.76527777778</v>
+        <v>46137.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +4423,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46134.77569444444</v>
+        <v>46137.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +4440,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46134.78611111111</v>
+        <v>46137.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +4457,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46134.79652777778</v>
+        <v>46137.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +4474,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46134.80694444444</v>
+        <v>46137.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +4491,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46134.81736111111</v>
+        <v>46137.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +4508,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46134.82777777778</v>
+        <v>46137.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +4525,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46134.83819444444</v>
+        <v>46137.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +4542,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46134.84861111111</v>
+        <v>46137.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +4559,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46134.85902777778</v>
+        <v>46137.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4576,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46134.86944444444</v>
+        <v>46137.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4593,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46134.87986111111</v>
+        <v>46137.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4610,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46134.89027777778</v>
+        <v>46137.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4627,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46134.90069444444</v>
+        <v>46137.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4644,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46134.91111111111</v>
+        <v>46137.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4661,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46134.92152777778</v>
+        <v>46137.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4678,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46134.93194444444</v>
+        <v>46137.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4695,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46134.94236111111</v>
+        <v>46137.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4712,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46134.95277777778</v>
+        <v>46137.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4729,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46134.96319444444</v>
+        <v>46137.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4746,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46134.97361111111</v>
+        <v>46137.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4763,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46134.98402777778</v>
+        <v>46137.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4780,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46134.99444444444</v>
+        <v>46137.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4797,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46135.00486111111</v>
+        <v>46138.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4814,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46135.01527777778</v>
+        <v>46138.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4831,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46135.02569444444</v>
+        <v>46138.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4848,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46135.03611111111</v>
+        <v>46138.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -4285,6 +4861,3304 @@
       </c>
       <c r="E195" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46138.03611111111</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46138.04652777778</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46138.05694444444</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46138.06736111111</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46138.07777777778</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46138.08819444444</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46138.09861111111</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46138.10902777778</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46138.11944444444</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46138.12986111111</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46138.14027777778</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46138.15069444444</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46138.16111111111</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46138.17152777778</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46138.18194444444</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46138.19236111111</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46138.20277777778</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46138.21319444444</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46138.22361111111</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46138.23402777778</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46138.24444444444</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46138.25486111111</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46138.26527777778</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46138.27569444444</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46138.28611111111</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46138.29652777778</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46138.30694444444</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46138.31736111111</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46138.32777777778</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46138.33819444444</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46138.34861111111</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46138.35902777778</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46138.36944444444</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46138.37986111111</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46138.39027777778</v>
+      </c>
+      <c r="B230">
+        <v>0</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46138.40069444444</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46138.41111111111</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46138.42152777778</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46138.43194444444</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46138.44236111111</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46138.45277777778</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46138.46319444444</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46138.47361111111</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46138.48402777778</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46138.49444444444</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46138.50486111111</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46138.51527777778</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46138.52569444444</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46138.53611111111</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46138.54652777778</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46138.55694444444</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46138.56736111111</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46138.57777777778</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46138.58819444444</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46138.59861111111</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46138.60902777778</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46138.61944444444</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46138.62986111111</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46138.64027777778</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46138.65069444444</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46138.66111111111</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46138.67152777778</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46138.68194444444</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46138.69236111111</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46138.70277777778</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46138.71319444444</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46138.72361111111</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46138.73402777778</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46138.74444444444</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46138.75486111111</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46138.76527777778</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46138.77569444444</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46138.78611111111</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46138.79652777778</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46138.80694444444</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46138.81736111111</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46138.82777777778</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46138.83819444444</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46138.84861111111</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46138.85902777778</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46138.86944444444</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46138.87986111111</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46138.89027777778</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46138.90069444444</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46138.91111111111</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46138.92152777778</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46138.93194444444</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46138.94236111111</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46138.95277777778</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46138.96319444444</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46138.97361111111</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46138.98402777778</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46138.99444444444</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46139.00486111111</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46139.01527777778</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46139.02569444444</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46139.03611111111</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46139.03611111111</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46139.04652777778</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46139.05694444444</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46139.06736111111</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46139.07777777778</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46139.08819444444</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46139.09861111111</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46139.10902777778</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46139.11944444444</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46139.12986111111</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46139.14027777778</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46139.15069444444</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46139.16111111111</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46139.17152777778</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46139.18194444444</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46139.19236111111</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46139.20277777778</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46139.21319444444</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46139.22361111111</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46139.23402777778</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46139.24444444444</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46139.25486111111</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46139.26527777778</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46139.27569444444</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46139.28611111111</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46139.29652777778</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46139.30694444444</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46139.31736111111</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46139.32777777778</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46139.33819444444</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46139.34861111111</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46139.35902777778</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46139.36944444444</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46139.37986111111</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46139.39027777778</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46139.40069444444</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46139.41111111111</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46139.42152777778</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46139.43194444444</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46139.44236111111</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46139.45277777778</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46139.46319444444</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46139.47361111111</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46139.48402777778</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46139.49444444444</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46139.50486111111</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46139.51527777778</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46139.52569444444</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46139.53611111111</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46139.54652777778</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46139.55694444444</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46139.56736111111</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46139.57777777778</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46139.58819444444</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46139.59861111111</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46139.60902777778</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46139.61944444444</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46139.62986111111</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46139.64027777778</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46139.65069444444</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46139.66111111111</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46139.67152777778</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46139.68194444444</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46139.69236111111</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46139.70277777778</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46139.71319444444</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46139.72361111111</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46139.73402777778</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46139.74444444444</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46139.75486111111</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46139.76527777778</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46139.77569444444</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46139.78611111111</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46139.79652777778</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46139.80694444444</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46139.81736111111</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46139.82777777778</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46139.83819444444</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46139.84861111111</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46139.85902777778</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46139.86944444444</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46139.87986111111</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46139.89027777778</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46139.90069444444</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46139.91111111111</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46139.92152777778</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46139.93194444444</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46139.94236111111</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46139.95277777778</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46139.96319444444</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46139.97361111111</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46139.98402777778</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46139.99444444444</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2">
+        <v>46140.00486111111</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2">
+        <v>46140.01527777778</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2">
+        <v>46140.02569444444</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2">
+        <v>46140.03611111111</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
+      <c r="E389" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="294">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,1149 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>24.04.20261</t>
-  </si>
-  <si>
-    <t>24.04.20262</t>
-  </si>
-  <si>
-    <t>24.04.20263</t>
-  </si>
-  <si>
-    <t>24.04.20264</t>
-  </si>
-  <si>
-    <t>24.04.20265</t>
-  </si>
-  <si>
-    <t>24.04.20266</t>
-  </si>
-  <si>
-    <t>24.04.20267</t>
-  </si>
-  <si>
-    <t>24.04.20268</t>
-  </si>
-  <si>
-    <t>24.04.20269</t>
-  </si>
-  <si>
-    <t>24.04.202610</t>
-  </si>
-  <si>
-    <t>24.04.202611</t>
-  </si>
-  <si>
-    <t>24.04.202612</t>
-  </si>
-  <si>
-    <t>24.04.202613</t>
-  </si>
-  <si>
-    <t>24.04.202614</t>
-  </si>
-  <si>
-    <t>24.04.202615</t>
-  </si>
-  <si>
-    <t>24.04.202616</t>
-  </si>
-  <si>
-    <t>24.04.202617</t>
-  </si>
-  <si>
-    <t>24.04.202618</t>
-  </si>
-  <si>
-    <t>24.04.202619</t>
-  </si>
-  <si>
-    <t>24.04.202620</t>
-  </si>
-  <si>
-    <t>24.04.202621</t>
-  </si>
-  <si>
-    <t>24.04.202622</t>
-  </si>
-  <si>
-    <t>24.04.202623</t>
-  </si>
-  <si>
-    <t>24.04.202624</t>
-  </si>
-  <si>
-    <t>24.04.202625</t>
-  </si>
-  <si>
-    <t>24.04.202626</t>
-  </si>
-  <si>
-    <t>24.04.202627</t>
-  </si>
-  <si>
-    <t>24.04.202628</t>
-  </si>
-  <si>
-    <t>24.04.202629</t>
-  </si>
-  <si>
-    <t>24.04.202630</t>
-  </si>
-  <si>
-    <t>24.04.202631</t>
-  </si>
-  <si>
-    <t>24.04.202632</t>
-  </si>
-  <si>
-    <t>24.04.202633</t>
-  </si>
-  <si>
-    <t>24.04.202634</t>
-  </si>
-  <si>
-    <t>24.04.202635</t>
-  </si>
-  <si>
-    <t>24.04.202636</t>
-  </si>
-  <si>
-    <t>24.04.202637</t>
-  </si>
-  <si>
-    <t>24.04.202638</t>
-  </si>
-  <si>
-    <t>24.04.202639</t>
-  </si>
-  <si>
-    <t>24.04.202640</t>
-  </si>
-  <si>
-    <t>24.04.202641</t>
-  </si>
-  <si>
-    <t>24.04.202642</t>
-  </si>
-  <si>
-    <t>24.04.202643</t>
-  </si>
-  <si>
-    <t>24.04.202644</t>
-  </si>
-  <si>
-    <t>24.04.202645</t>
-  </si>
-  <si>
-    <t>24.04.202646</t>
-  </si>
-  <si>
-    <t>24.04.202647</t>
-  </si>
-  <si>
-    <t>24.04.202648</t>
-  </si>
-  <si>
-    <t>24.04.202649</t>
-  </si>
-  <si>
-    <t>24.04.202650</t>
-  </si>
-  <si>
-    <t>24.04.202651</t>
-  </si>
-  <si>
-    <t>24.04.202652</t>
-  </si>
-  <si>
-    <t>24.04.202653</t>
-  </si>
-  <si>
-    <t>24.04.202654</t>
-  </si>
-  <si>
-    <t>24.04.202655</t>
-  </si>
-  <si>
-    <t>24.04.202656</t>
-  </si>
-  <si>
-    <t>24.04.202657</t>
-  </si>
-  <si>
-    <t>24.04.202658</t>
-  </si>
-  <si>
-    <t>24.04.202659</t>
-  </si>
-  <si>
-    <t>24.04.202660</t>
-  </si>
-  <si>
-    <t>24.04.202661</t>
-  </si>
-  <si>
-    <t>24.04.202662</t>
-  </si>
-  <si>
-    <t>24.04.202663</t>
-  </si>
-  <si>
-    <t>24.04.202664</t>
-  </si>
-  <si>
-    <t>24.04.202665</t>
-  </si>
-  <si>
-    <t>24.04.202666</t>
-  </si>
-  <si>
-    <t>24.04.202667</t>
-  </si>
-  <si>
-    <t>24.04.202668</t>
-  </si>
-  <si>
-    <t>24.04.202669</t>
-  </si>
-  <si>
-    <t>24.04.202670</t>
-  </si>
-  <si>
-    <t>24.04.202671</t>
-  </si>
-  <si>
-    <t>24.04.202672</t>
-  </si>
-  <si>
-    <t>24.04.202673</t>
-  </si>
-  <si>
-    <t>24.04.202674</t>
-  </si>
-  <si>
-    <t>24.04.202675</t>
-  </si>
-  <si>
-    <t>24.04.202676</t>
-  </si>
-  <si>
-    <t>24.04.202677</t>
-  </si>
-  <si>
-    <t>24.04.202678</t>
-  </si>
-  <si>
-    <t>24.04.202679</t>
-  </si>
-  <si>
-    <t>24.04.202680</t>
-  </si>
-  <si>
-    <t>24.04.202681</t>
-  </si>
-  <si>
-    <t>24.04.202682</t>
-  </si>
-  <si>
-    <t>24.04.202683</t>
-  </si>
-  <si>
-    <t>24.04.202684</t>
-  </si>
-  <si>
-    <t>24.04.202685</t>
-  </si>
-  <si>
-    <t>24.04.202686</t>
-  </si>
-  <si>
-    <t>24.04.202687</t>
-  </si>
-  <si>
-    <t>24.04.202688</t>
-  </si>
-  <si>
-    <t>24.04.202689</t>
-  </si>
-  <si>
-    <t>24.04.202690</t>
-  </si>
-  <si>
-    <t>24.04.202691</t>
-  </si>
-  <si>
-    <t>24.04.202692</t>
-  </si>
-  <si>
-    <t>24.04.202693</t>
-  </si>
-  <si>
-    <t>25.04.202694</t>
-  </si>
-  <si>
-    <t>25.04.202695</t>
-  </si>
-  <si>
-    <t>25.04.202696</t>
-  </si>
-  <si>
-    <t>25.04.20261</t>
-  </si>
-  <si>
-    <t>25.04.20262</t>
-  </si>
-  <si>
-    <t>25.04.20263</t>
-  </si>
-  <si>
-    <t>25.04.20264</t>
-  </si>
-  <si>
-    <t>25.04.20265</t>
-  </si>
-  <si>
-    <t>25.04.20266</t>
-  </si>
-  <si>
-    <t>25.04.20267</t>
-  </si>
-  <si>
-    <t>25.04.20268</t>
-  </si>
-  <si>
-    <t>25.04.20269</t>
-  </si>
-  <si>
-    <t>25.04.202610</t>
-  </si>
-  <si>
-    <t>25.04.202611</t>
-  </si>
-  <si>
-    <t>25.04.202612</t>
-  </si>
-  <si>
-    <t>25.04.202613</t>
-  </si>
-  <si>
-    <t>25.04.202614</t>
-  </si>
-  <si>
-    <t>25.04.202615</t>
-  </si>
-  <si>
-    <t>25.04.202616</t>
-  </si>
-  <si>
-    <t>25.04.202617</t>
-  </si>
-  <si>
-    <t>25.04.202618</t>
-  </si>
-  <si>
-    <t>25.04.202619</t>
-  </si>
-  <si>
-    <t>25.04.202620</t>
-  </si>
-  <si>
-    <t>25.04.202621</t>
-  </si>
-  <si>
-    <t>25.04.202622</t>
-  </si>
-  <si>
-    <t>25.04.202623</t>
-  </si>
-  <si>
-    <t>25.04.202624</t>
-  </si>
-  <si>
-    <t>25.04.202625</t>
-  </si>
-  <si>
-    <t>25.04.202626</t>
-  </si>
-  <si>
-    <t>25.04.202627</t>
-  </si>
-  <si>
-    <t>25.04.202628</t>
-  </si>
-  <si>
-    <t>25.04.202629</t>
-  </si>
-  <si>
-    <t>25.04.202630</t>
-  </si>
-  <si>
-    <t>25.04.202631</t>
-  </si>
-  <si>
-    <t>25.04.202632</t>
-  </si>
-  <si>
-    <t>25.04.202633</t>
-  </si>
-  <si>
-    <t>25.04.202634</t>
-  </si>
-  <si>
-    <t>25.04.202635</t>
-  </si>
-  <si>
-    <t>25.04.202636</t>
-  </si>
-  <si>
-    <t>25.04.202637</t>
-  </si>
-  <si>
-    <t>25.04.202638</t>
-  </si>
-  <si>
-    <t>25.04.202639</t>
-  </si>
-  <si>
-    <t>25.04.202640</t>
-  </si>
-  <si>
-    <t>25.04.202641</t>
-  </si>
-  <si>
-    <t>25.04.202642</t>
-  </si>
-  <si>
-    <t>25.04.202643</t>
-  </si>
-  <si>
-    <t>25.04.202644</t>
-  </si>
-  <si>
-    <t>25.04.202645</t>
-  </si>
-  <si>
-    <t>25.04.202646</t>
-  </si>
-  <si>
-    <t>25.04.202647</t>
-  </si>
-  <si>
-    <t>25.04.202648</t>
-  </si>
-  <si>
-    <t>25.04.202649</t>
-  </si>
-  <si>
-    <t>25.04.202650</t>
-  </si>
-  <si>
-    <t>25.04.202651</t>
-  </si>
-  <si>
-    <t>25.04.202652</t>
-  </si>
-  <si>
-    <t>25.04.202653</t>
-  </si>
-  <si>
-    <t>25.04.202654</t>
-  </si>
-  <si>
-    <t>25.04.202655</t>
-  </si>
-  <si>
-    <t>25.04.202656</t>
-  </si>
-  <si>
-    <t>25.04.202657</t>
-  </si>
-  <si>
-    <t>25.04.202658</t>
-  </si>
-  <si>
-    <t>25.04.202659</t>
-  </si>
-  <si>
-    <t>25.04.202660</t>
-  </si>
-  <si>
-    <t>25.04.202661</t>
-  </si>
-  <si>
-    <t>25.04.202662</t>
-  </si>
-  <si>
-    <t>25.04.202663</t>
-  </si>
-  <si>
-    <t>25.04.202664</t>
-  </si>
-  <si>
-    <t>25.04.202665</t>
-  </si>
-  <si>
-    <t>25.04.202666</t>
-  </si>
-  <si>
-    <t>25.04.202667</t>
-  </si>
-  <si>
-    <t>25.04.202668</t>
-  </si>
-  <si>
-    <t>25.04.202669</t>
-  </si>
-  <si>
-    <t>25.04.202670</t>
-  </si>
-  <si>
-    <t>25.04.202671</t>
-  </si>
-  <si>
-    <t>25.04.202672</t>
-  </si>
-  <si>
-    <t>25.04.202673</t>
-  </si>
-  <si>
-    <t>25.04.202674</t>
-  </si>
-  <si>
-    <t>25.04.202675</t>
-  </si>
-  <si>
-    <t>25.04.202676</t>
-  </si>
-  <si>
-    <t>25.04.202677</t>
-  </si>
-  <si>
-    <t>25.04.202678</t>
-  </si>
-  <si>
-    <t>25.04.202679</t>
-  </si>
-  <si>
-    <t>25.04.202680</t>
-  </si>
-  <si>
-    <t>25.04.202681</t>
-  </si>
-  <si>
-    <t>25.04.202682</t>
-  </si>
-  <si>
-    <t>25.04.202683</t>
-  </si>
-  <si>
-    <t>25.04.202684</t>
-  </si>
-  <si>
-    <t>25.04.202685</t>
-  </si>
-  <si>
-    <t>25.04.202686</t>
-  </si>
-  <si>
-    <t>25.04.202687</t>
-  </si>
-  <si>
-    <t>25.04.202688</t>
-  </si>
-  <si>
-    <t>25.04.202689</t>
-  </si>
-  <si>
-    <t>25.04.202690</t>
-  </si>
-  <si>
-    <t>25.04.202691</t>
-  </si>
-  <si>
-    <t>25.04.202692</t>
-  </si>
-  <si>
-    <t>25.04.202693</t>
-  </si>
-  <si>
-    <t>26.04.202695</t>
-  </si>
-  <si>
-    <t>26.04.202696</t>
-  </si>
-  <si>
-    <t>26.04.20261</t>
-  </si>
-  <si>
-    <t>26.04.20262</t>
-  </si>
-  <si>
-    <t>26.04.20263</t>
-  </si>
-  <si>
-    <t>26.04.20264</t>
-  </si>
-  <si>
-    <t>26.04.20265</t>
-  </si>
-  <si>
-    <t>26.04.20266</t>
-  </si>
-  <si>
-    <t>26.04.20267</t>
-  </si>
-  <si>
-    <t>26.04.20268</t>
-  </si>
-  <si>
-    <t>26.04.20269</t>
-  </si>
-  <si>
-    <t>26.04.202610</t>
-  </si>
-  <si>
-    <t>26.04.202611</t>
-  </si>
-  <si>
-    <t>26.04.202612</t>
-  </si>
-  <si>
-    <t>26.04.202613</t>
-  </si>
-  <si>
-    <t>26.04.202614</t>
-  </si>
-  <si>
-    <t>26.04.202615</t>
-  </si>
-  <si>
-    <t>26.04.202616</t>
-  </si>
-  <si>
-    <t>26.04.202617</t>
-  </si>
-  <si>
-    <t>26.04.202618</t>
-  </si>
-  <si>
-    <t>26.04.202619</t>
-  </si>
-  <si>
-    <t>26.04.202620</t>
-  </si>
-  <si>
-    <t>26.04.202621</t>
-  </si>
-  <si>
-    <t>26.04.202622</t>
-  </si>
-  <si>
-    <t>26.04.202623</t>
-  </si>
-  <si>
-    <t>26.04.202624</t>
-  </si>
-  <si>
-    <t>26.04.202625</t>
-  </si>
-  <si>
-    <t>26.04.202626</t>
-  </si>
-  <si>
-    <t>26.04.202627</t>
-  </si>
-  <si>
-    <t>26.04.202628</t>
-  </si>
-  <si>
-    <t>26.04.202629</t>
-  </si>
-  <si>
-    <t>26.04.202630</t>
-  </si>
-  <si>
-    <t>26.04.202631</t>
-  </si>
-  <si>
-    <t>26.04.202632</t>
-  </si>
-  <si>
-    <t>26.04.202633</t>
-  </si>
-  <si>
-    <t>26.04.202634</t>
-  </si>
-  <si>
-    <t>26.04.202635</t>
-  </si>
-  <si>
-    <t>26.04.202636</t>
-  </si>
-  <si>
-    <t>26.04.202637</t>
-  </si>
-  <si>
-    <t>26.04.202638</t>
-  </si>
-  <si>
-    <t>26.04.202639</t>
-  </si>
-  <si>
-    <t>26.04.202640</t>
-  </si>
-  <si>
-    <t>26.04.202641</t>
-  </si>
-  <si>
-    <t>26.04.202642</t>
-  </si>
-  <si>
-    <t>26.04.202643</t>
-  </si>
-  <si>
-    <t>26.04.202644</t>
-  </si>
-  <si>
-    <t>26.04.202645</t>
-  </si>
-  <si>
-    <t>26.04.202646</t>
-  </si>
-  <si>
-    <t>26.04.202647</t>
-  </si>
-  <si>
-    <t>26.04.202648</t>
-  </si>
-  <si>
-    <t>26.04.202649</t>
-  </si>
-  <si>
-    <t>26.04.202650</t>
-  </si>
-  <si>
-    <t>26.04.202651</t>
-  </si>
-  <si>
-    <t>26.04.202652</t>
-  </si>
-  <si>
-    <t>26.04.202653</t>
-  </si>
-  <si>
-    <t>26.04.202654</t>
-  </si>
-  <si>
-    <t>26.04.202655</t>
-  </si>
-  <si>
-    <t>26.04.202656</t>
-  </si>
-  <si>
-    <t>26.04.202657</t>
-  </si>
-  <si>
-    <t>26.04.202658</t>
-  </si>
-  <si>
-    <t>26.04.202659</t>
-  </si>
-  <si>
-    <t>26.04.202660</t>
-  </si>
-  <si>
-    <t>26.04.202661</t>
-  </si>
-  <si>
-    <t>26.04.202662</t>
-  </si>
-  <si>
-    <t>26.04.202663</t>
-  </si>
-  <si>
-    <t>26.04.202664</t>
-  </si>
-  <si>
-    <t>26.04.202665</t>
-  </si>
-  <si>
-    <t>26.04.202666</t>
-  </si>
-  <si>
-    <t>26.04.202667</t>
-  </si>
-  <si>
-    <t>26.04.202668</t>
-  </si>
-  <si>
-    <t>26.04.202669</t>
-  </si>
-  <si>
-    <t>26.04.202670</t>
-  </si>
-  <si>
-    <t>26.04.202671</t>
-  </si>
-  <si>
-    <t>26.04.202672</t>
-  </si>
-  <si>
-    <t>26.04.202673</t>
-  </si>
-  <si>
-    <t>26.04.202674</t>
-  </si>
-  <si>
-    <t>26.04.202675</t>
-  </si>
-  <si>
-    <t>26.04.202676</t>
-  </si>
-  <si>
-    <t>26.04.202677</t>
-  </si>
-  <si>
-    <t>26.04.202678</t>
-  </si>
-  <si>
-    <t>26.04.202679</t>
-  </si>
-  <si>
-    <t>26.04.202680</t>
-  </si>
-  <si>
-    <t>26.04.202681</t>
-  </si>
-  <si>
-    <t>26.04.202682</t>
-  </si>
-  <si>
-    <t>26.04.202683</t>
-  </si>
-  <si>
-    <t>26.04.202684</t>
-  </si>
-  <si>
-    <t>26.04.202685</t>
-  </si>
-  <si>
-    <t>26.04.202686</t>
-  </si>
-  <si>
-    <t>26.04.202687</t>
-  </si>
-  <si>
-    <t>26.04.202688</t>
-  </si>
-  <si>
-    <t>26.04.202689</t>
-  </si>
-  <si>
-    <t>26.04.202690</t>
-  </si>
-  <si>
-    <t>26.04.202691</t>
-  </si>
-  <si>
-    <t>26.04.202692</t>
-  </si>
-  <si>
-    <t>26.04.202693</t>
-  </si>
-  <si>
-    <t>26.04.202694</t>
-  </si>
-  <si>
-    <t>27.04.202696</t>
-  </si>
-  <si>
-    <t>27.04.20261</t>
-  </si>
-  <si>
-    <t>27.04.20262</t>
-  </si>
-  <si>
-    <t>27.04.20263</t>
-  </si>
-  <si>
-    <t>27.04.20264</t>
-  </si>
-  <si>
-    <t>27.04.20265</t>
-  </si>
-  <si>
-    <t>27.04.20266</t>
-  </si>
-  <si>
-    <t>27.04.20267</t>
-  </si>
-  <si>
-    <t>27.04.20268</t>
-  </si>
-  <si>
-    <t>27.04.20269</t>
-  </si>
-  <si>
-    <t>27.04.202610</t>
-  </si>
-  <si>
-    <t>27.04.202611</t>
-  </si>
-  <si>
-    <t>27.04.202612</t>
-  </si>
-  <si>
-    <t>27.04.202613</t>
-  </si>
-  <si>
-    <t>27.04.202614</t>
-  </si>
-  <si>
-    <t>27.04.202615</t>
-  </si>
-  <si>
-    <t>27.04.202616</t>
-  </si>
-  <si>
-    <t>27.04.202617</t>
-  </si>
-  <si>
-    <t>27.04.202618</t>
-  </si>
-  <si>
-    <t>27.04.202619</t>
-  </si>
-  <si>
-    <t>27.04.202620</t>
-  </si>
-  <si>
-    <t>27.04.202621</t>
-  </si>
-  <si>
-    <t>27.04.202622</t>
-  </si>
-  <si>
-    <t>27.04.202623</t>
-  </si>
-  <si>
-    <t>27.04.202624</t>
-  </si>
-  <si>
-    <t>27.04.202625</t>
-  </si>
-  <si>
-    <t>27.04.202626</t>
-  </si>
-  <si>
-    <t>27.04.202627</t>
-  </si>
-  <si>
-    <t>27.04.202628</t>
-  </si>
-  <si>
-    <t>27.04.202629</t>
-  </si>
-  <si>
-    <t>27.04.202630</t>
-  </si>
-  <si>
-    <t>27.04.202631</t>
-  </si>
-  <si>
-    <t>27.04.202632</t>
-  </si>
-  <si>
-    <t>27.04.202633</t>
-  </si>
-  <si>
-    <t>27.04.202634</t>
-  </si>
-  <si>
-    <t>27.04.202635</t>
-  </si>
-  <si>
-    <t>27.04.202636</t>
-  </si>
-  <si>
-    <t>27.04.202637</t>
-  </si>
-  <si>
-    <t>27.04.202638</t>
-  </si>
-  <si>
-    <t>27.04.202639</t>
-  </si>
-  <si>
-    <t>27.04.202640</t>
-  </si>
-  <si>
-    <t>27.04.202641</t>
-  </si>
-  <si>
-    <t>27.04.202642</t>
-  </si>
-  <si>
-    <t>27.04.202643</t>
-  </si>
-  <si>
-    <t>27.04.202644</t>
-  </si>
-  <si>
-    <t>27.04.202645</t>
-  </si>
-  <si>
-    <t>27.04.202646</t>
-  </si>
-  <si>
-    <t>27.04.202647</t>
-  </si>
-  <si>
-    <t>27.04.202648</t>
-  </si>
-  <si>
-    <t>27.04.202649</t>
-  </si>
-  <si>
-    <t>27.04.202650</t>
-  </si>
-  <si>
-    <t>27.04.202651</t>
-  </si>
-  <si>
-    <t>27.04.202652</t>
-  </si>
-  <si>
-    <t>27.04.202653</t>
-  </si>
-  <si>
-    <t>27.04.202654</t>
-  </si>
-  <si>
-    <t>27.04.202655</t>
-  </si>
-  <si>
-    <t>27.04.202656</t>
-  </si>
-  <si>
-    <t>27.04.202657</t>
-  </si>
-  <si>
-    <t>27.04.202658</t>
-  </si>
-  <si>
-    <t>27.04.202659</t>
-  </si>
-  <si>
-    <t>27.04.202660</t>
-  </si>
-  <si>
-    <t>27.04.202661</t>
-  </si>
-  <si>
-    <t>27.04.202662</t>
-  </si>
-  <si>
-    <t>27.04.202663</t>
-  </si>
-  <si>
-    <t>27.04.202664</t>
-  </si>
-  <si>
-    <t>27.04.202665</t>
-  </si>
-  <si>
-    <t>27.04.202666</t>
-  </si>
-  <si>
-    <t>27.04.202667</t>
-  </si>
-  <si>
-    <t>27.04.202668</t>
-  </si>
-  <si>
-    <t>27.04.202669</t>
-  </si>
-  <si>
-    <t>27.04.202670</t>
-  </si>
-  <si>
-    <t>27.04.202671</t>
-  </si>
-  <si>
-    <t>27.04.202672</t>
-  </si>
-  <si>
-    <t>27.04.202673</t>
-  </si>
-  <si>
-    <t>27.04.202674</t>
-  </si>
-  <si>
-    <t>27.04.202675</t>
-  </si>
-  <si>
-    <t>27.04.202676</t>
-  </si>
-  <si>
-    <t>27.04.202677</t>
-  </si>
-  <si>
-    <t>27.04.202678</t>
-  </si>
-  <si>
-    <t>27.04.202679</t>
-  </si>
-  <si>
-    <t>27.04.202680</t>
-  </si>
-  <si>
-    <t>27.04.202681</t>
-  </si>
-  <si>
-    <t>27.04.202682</t>
-  </si>
-  <si>
-    <t>27.04.202683</t>
-  </si>
-  <si>
-    <t>27.04.202684</t>
-  </si>
-  <si>
-    <t>27.04.202685</t>
-  </si>
-  <si>
-    <t>27.04.202686</t>
-  </si>
-  <si>
-    <t>27.04.202687</t>
-  </si>
-  <si>
-    <t>27.04.202688</t>
-  </si>
-  <si>
-    <t>27.04.202689</t>
-  </si>
-  <si>
-    <t>27.04.202690</t>
-  </si>
-  <si>
-    <t>27.04.202691</t>
-  </si>
-  <si>
-    <t>27.04.202692</t>
-  </si>
-  <si>
-    <t>27.04.202693</t>
-  </si>
-  <si>
-    <t>27.04.202694</t>
-  </si>
-  <si>
-    <t>27.04.202695</t>
-  </si>
-  <si>
     <t>28.04.20261</t>
   </si>
   <si>
@@ -1184,6 +41,861 @@
   </si>
   <si>
     <t>28.04.20264</t>
+  </si>
+  <si>
+    <t>28.04.20265</t>
+  </si>
+  <si>
+    <t>28.04.20266</t>
+  </si>
+  <si>
+    <t>28.04.20267</t>
+  </si>
+  <si>
+    <t>28.04.20268</t>
+  </si>
+  <si>
+    <t>28.04.20269</t>
+  </si>
+  <si>
+    <t>28.04.202610</t>
+  </si>
+  <si>
+    <t>28.04.202611</t>
+  </si>
+  <si>
+    <t>28.04.202612</t>
+  </si>
+  <si>
+    <t>28.04.202613</t>
+  </si>
+  <si>
+    <t>28.04.202614</t>
+  </si>
+  <si>
+    <t>28.04.202615</t>
+  </si>
+  <si>
+    <t>28.04.202616</t>
+  </si>
+  <si>
+    <t>28.04.202617</t>
+  </si>
+  <si>
+    <t>28.04.202618</t>
+  </si>
+  <si>
+    <t>28.04.202619</t>
+  </si>
+  <si>
+    <t>28.04.202620</t>
+  </si>
+  <si>
+    <t>28.04.202621</t>
+  </si>
+  <si>
+    <t>28.04.202622</t>
+  </si>
+  <si>
+    <t>28.04.202623</t>
+  </si>
+  <si>
+    <t>28.04.202624</t>
+  </si>
+  <si>
+    <t>28.04.202625</t>
+  </si>
+  <si>
+    <t>28.04.202626</t>
+  </si>
+  <si>
+    <t>28.04.202627</t>
+  </si>
+  <si>
+    <t>28.04.202628</t>
+  </si>
+  <si>
+    <t>28.04.202629</t>
+  </si>
+  <si>
+    <t>28.04.202630</t>
+  </si>
+  <si>
+    <t>28.04.202631</t>
+  </si>
+  <si>
+    <t>28.04.202632</t>
+  </si>
+  <si>
+    <t>28.04.202633</t>
+  </si>
+  <si>
+    <t>28.04.202634</t>
+  </si>
+  <si>
+    <t>28.04.202635</t>
+  </si>
+  <si>
+    <t>28.04.202636</t>
+  </si>
+  <si>
+    <t>28.04.202637</t>
+  </si>
+  <si>
+    <t>28.04.202638</t>
+  </si>
+  <si>
+    <t>28.04.202639</t>
+  </si>
+  <si>
+    <t>28.04.202640</t>
+  </si>
+  <si>
+    <t>28.04.202641</t>
+  </si>
+  <si>
+    <t>28.04.202642</t>
+  </si>
+  <si>
+    <t>28.04.202643</t>
+  </si>
+  <si>
+    <t>28.04.202644</t>
+  </si>
+  <si>
+    <t>28.04.202645</t>
+  </si>
+  <si>
+    <t>28.04.202646</t>
+  </si>
+  <si>
+    <t>28.04.202647</t>
+  </si>
+  <si>
+    <t>28.04.202648</t>
+  </si>
+  <si>
+    <t>28.04.202649</t>
+  </si>
+  <si>
+    <t>28.04.202650</t>
+  </si>
+  <si>
+    <t>28.04.202651</t>
+  </si>
+  <si>
+    <t>28.04.202652</t>
+  </si>
+  <si>
+    <t>28.04.202653</t>
+  </si>
+  <si>
+    <t>28.04.202654</t>
+  </si>
+  <si>
+    <t>28.04.202655</t>
+  </si>
+  <si>
+    <t>28.04.202656</t>
+  </si>
+  <si>
+    <t>28.04.202657</t>
+  </si>
+  <si>
+    <t>28.04.202658</t>
+  </si>
+  <si>
+    <t>28.04.202659</t>
+  </si>
+  <si>
+    <t>28.04.202660</t>
+  </si>
+  <si>
+    <t>28.04.202661</t>
+  </si>
+  <si>
+    <t>28.04.202662</t>
+  </si>
+  <si>
+    <t>28.04.202663</t>
+  </si>
+  <si>
+    <t>28.04.202664</t>
+  </si>
+  <si>
+    <t>28.04.202665</t>
+  </si>
+  <si>
+    <t>28.04.202666</t>
+  </si>
+  <si>
+    <t>28.04.202667</t>
+  </si>
+  <si>
+    <t>28.04.202668</t>
+  </si>
+  <si>
+    <t>28.04.202669</t>
+  </si>
+  <si>
+    <t>28.04.202670</t>
+  </si>
+  <si>
+    <t>28.04.202671</t>
+  </si>
+  <si>
+    <t>28.04.202672</t>
+  </si>
+  <si>
+    <t>28.04.202673</t>
+  </si>
+  <si>
+    <t>28.04.202674</t>
+  </si>
+  <si>
+    <t>28.04.202675</t>
+  </si>
+  <si>
+    <t>28.04.202676</t>
+  </si>
+  <si>
+    <t>28.04.202677</t>
+  </si>
+  <si>
+    <t>28.04.202678</t>
+  </si>
+  <si>
+    <t>28.04.202679</t>
+  </si>
+  <si>
+    <t>28.04.202680</t>
+  </si>
+  <si>
+    <t>28.04.202681</t>
+  </si>
+  <si>
+    <t>28.04.202682</t>
+  </si>
+  <si>
+    <t>28.04.202683</t>
+  </si>
+  <si>
+    <t>28.04.202684</t>
+  </si>
+  <si>
+    <t>28.04.202685</t>
+  </si>
+  <si>
+    <t>28.04.202686</t>
+  </si>
+  <si>
+    <t>28.04.202687</t>
+  </si>
+  <si>
+    <t>28.04.202688</t>
+  </si>
+  <si>
+    <t>28.04.202689</t>
+  </si>
+  <si>
+    <t>28.04.202690</t>
+  </si>
+  <si>
+    <t>28.04.202691</t>
+  </si>
+  <si>
+    <t>28.04.202692</t>
+  </si>
+  <si>
+    <t>28.04.202693</t>
+  </si>
+  <si>
+    <t>29.04.202694</t>
+  </si>
+  <si>
+    <t>29.04.202695</t>
+  </si>
+  <si>
+    <t>29.04.202696</t>
+  </si>
+  <si>
+    <t>29.04.20261</t>
+  </si>
+  <si>
+    <t>29.04.20262</t>
+  </si>
+  <si>
+    <t>29.04.20263</t>
+  </si>
+  <si>
+    <t>29.04.20264</t>
+  </si>
+  <si>
+    <t>29.04.20265</t>
+  </si>
+  <si>
+    <t>29.04.20266</t>
+  </si>
+  <si>
+    <t>29.04.20267</t>
+  </si>
+  <si>
+    <t>29.04.20268</t>
+  </si>
+  <si>
+    <t>29.04.20269</t>
+  </si>
+  <si>
+    <t>29.04.202610</t>
+  </si>
+  <si>
+    <t>29.04.202611</t>
+  </si>
+  <si>
+    <t>29.04.202612</t>
+  </si>
+  <si>
+    <t>29.04.202613</t>
+  </si>
+  <si>
+    <t>29.04.202614</t>
+  </si>
+  <si>
+    <t>29.04.202615</t>
+  </si>
+  <si>
+    <t>29.04.202616</t>
+  </si>
+  <si>
+    <t>29.04.202617</t>
+  </si>
+  <si>
+    <t>29.04.202618</t>
+  </si>
+  <si>
+    <t>29.04.202619</t>
+  </si>
+  <si>
+    <t>29.04.202620</t>
+  </si>
+  <si>
+    <t>29.04.202621</t>
+  </si>
+  <si>
+    <t>29.04.202622</t>
+  </si>
+  <si>
+    <t>29.04.202623</t>
+  </si>
+  <si>
+    <t>29.04.202624</t>
+  </si>
+  <si>
+    <t>29.04.202625</t>
+  </si>
+  <si>
+    <t>29.04.202626</t>
+  </si>
+  <si>
+    <t>29.04.202627</t>
+  </si>
+  <si>
+    <t>29.04.202628</t>
+  </si>
+  <si>
+    <t>29.04.202629</t>
+  </si>
+  <si>
+    <t>29.04.202630</t>
+  </si>
+  <si>
+    <t>29.04.202631</t>
+  </si>
+  <si>
+    <t>29.04.202632</t>
+  </si>
+  <si>
+    <t>29.04.202633</t>
+  </si>
+  <si>
+    <t>29.04.202634</t>
+  </si>
+  <si>
+    <t>29.04.202635</t>
+  </si>
+  <si>
+    <t>29.04.202636</t>
+  </si>
+  <si>
+    <t>29.04.202637</t>
+  </si>
+  <si>
+    <t>29.04.202638</t>
+  </si>
+  <si>
+    <t>29.04.202639</t>
+  </si>
+  <si>
+    <t>29.04.202640</t>
+  </si>
+  <si>
+    <t>29.04.202641</t>
+  </si>
+  <si>
+    <t>29.04.202642</t>
+  </si>
+  <si>
+    <t>29.04.202643</t>
+  </si>
+  <si>
+    <t>29.04.202644</t>
+  </si>
+  <si>
+    <t>29.04.202645</t>
+  </si>
+  <si>
+    <t>29.04.202646</t>
+  </si>
+  <si>
+    <t>29.04.202647</t>
+  </si>
+  <si>
+    <t>29.04.202648</t>
+  </si>
+  <si>
+    <t>29.04.202649</t>
+  </si>
+  <si>
+    <t>29.04.202650</t>
+  </si>
+  <si>
+    <t>29.04.202651</t>
+  </si>
+  <si>
+    <t>29.04.202652</t>
+  </si>
+  <si>
+    <t>29.04.202653</t>
+  </si>
+  <si>
+    <t>29.04.202654</t>
+  </si>
+  <si>
+    <t>29.04.202655</t>
+  </si>
+  <si>
+    <t>29.04.202656</t>
+  </si>
+  <si>
+    <t>29.04.202657</t>
+  </si>
+  <si>
+    <t>29.04.202658</t>
+  </si>
+  <si>
+    <t>29.04.202659</t>
+  </si>
+  <si>
+    <t>29.04.202660</t>
+  </si>
+  <si>
+    <t>29.04.202661</t>
+  </si>
+  <si>
+    <t>29.04.202662</t>
+  </si>
+  <si>
+    <t>29.04.202663</t>
+  </si>
+  <si>
+    <t>29.04.202664</t>
+  </si>
+  <si>
+    <t>29.04.202665</t>
+  </si>
+  <si>
+    <t>29.04.202666</t>
+  </si>
+  <si>
+    <t>29.04.202667</t>
+  </si>
+  <si>
+    <t>29.04.202668</t>
+  </si>
+  <si>
+    <t>29.04.202669</t>
+  </si>
+  <si>
+    <t>29.04.202670</t>
+  </si>
+  <si>
+    <t>29.04.202671</t>
+  </si>
+  <si>
+    <t>29.04.202672</t>
+  </si>
+  <si>
+    <t>29.04.202673</t>
+  </si>
+  <si>
+    <t>29.04.202674</t>
+  </si>
+  <si>
+    <t>29.04.202675</t>
+  </si>
+  <si>
+    <t>29.04.202676</t>
+  </si>
+  <si>
+    <t>29.04.202677</t>
+  </si>
+  <si>
+    <t>29.04.202678</t>
+  </si>
+  <si>
+    <t>29.04.202679</t>
+  </si>
+  <si>
+    <t>29.04.202680</t>
+  </si>
+  <si>
+    <t>29.04.202681</t>
+  </si>
+  <si>
+    <t>29.04.202682</t>
+  </si>
+  <si>
+    <t>29.04.202683</t>
+  </si>
+  <si>
+    <t>29.04.202684</t>
+  </si>
+  <si>
+    <t>29.04.202685</t>
+  </si>
+  <si>
+    <t>29.04.202686</t>
+  </si>
+  <si>
+    <t>29.04.202687</t>
+  </si>
+  <si>
+    <t>29.04.202688</t>
+  </si>
+  <si>
+    <t>29.04.202689</t>
+  </si>
+  <si>
+    <t>29.04.202690</t>
+  </si>
+  <si>
+    <t>29.04.202691</t>
+  </si>
+  <si>
+    <t>29.04.202692</t>
+  </si>
+  <si>
+    <t>29.04.202693</t>
+  </si>
+  <si>
+    <t>30.04.202695</t>
+  </si>
+  <si>
+    <t>30.04.202696</t>
+  </si>
+  <si>
+    <t>30.04.20261</t>
+  </si>
+  <si>
+    <t>30.04.20262</t>
+  </si>
+  <si>
+    <t>30.04.20263</t>
+  </si>
+  <si>
+    <t>30.04.20264</t>
+  </si>
+  <si>
+    <t>30.04.20265</t>
+  </si>
+  <si>
+    <t>30.04.20266</t>
+  </si>
+  <si>
+    <t>30.04.20267</t>
+  </si>
+  <si>
+    <t>30.04.20268</t>
+  </si>
+  <si>
+    <t>30.04.20269</t>
+  </si>
+  <si>
+    <t>30.04.202610</t>
+  </si>
+  <si>
+    <t>30.04.202611</t>
+  </si>
+  <si>
+    <t>30.04.202612</t>
+  </si>
+  <si>
+    <t>30.04.202613</t>
+  </si>
+  <si>
+    <t>30.04.202614</t>
+  </si>
+  <si>
+    <t>30.04.202615</t>
+  </si>
+  <si>
+    <t>30.04.202616</t>
+  </si>
+  <si>
+    <t>30.04.202617</t>
+  </si>
+  <si>
+    <t>30.04.202618</t>
+  </si>
+  <si>
+    <t>30.04.202619</t>
+  </si>
+  <si>
+    <t>30.04.202620</t>
+  </si>
+  <si>
+    <t>30.04.202621</t>
+  </si>
+  <si>
+    <t>30.04.202622</t>
+  </si>
+  <si>
+    <t>30.04.202623</t>
+  </si>
+  <si>
+    <t>30.04.202624</t>
+  </si>
+  <si>
+    <t>30.04.202625</t>
+  </si>
+  <si>
+    <t>30.04.202626</t>
+  </si>
+  <si>
+    <t>30.04.202627</t>
+  </si>
+  <si>
+    <t>30.04.202628</t>
+  </si>
+  <si>
+    <t>30.04.202629</t>
+  </si>
+  <si>
+    <t>30.04.202630</t>
+  </si>
+  <si>
+    <t>30.04.202631</t>
+  </si>
+  <si>
+    <t>30.04.202632</t>
+  </si>
+  <si>
+    <t>30.04.202633</t>
+  </si>
+  <si>
+    <t>30.04.202634</t>
+  </si>
+  <si>
+    <t>30.04.202635</t>
+  </si>
+  <si>
+    <t>30.04.202636</t>
+  </si>
+  <si>
+    <t>30.04.202637</t>
+  </si>
+  <si>
+    <t>30.04.202638</t>
+  </si>
+  <si>
+    <t>30.04.202639</t>
+  </si>
+  <si>
+    <t>30.04.202640</t>
+  </si>
+  <si>
+    <t>30.04.202641</t>
+  </si>
+  <si>
+    <t>30.04.202642</t>
+  </si>
+  <si>
+    <t>30.04.202643</t>
+  </si>
+  <si>
+    <t>30.04.202644</t>
+  </si>
+  <si>
+    <t>30.04.202645</t>
+  </si>
+  <si>
+    <t>30.04.202646</t>
+  </si>
+  <si>
+    <t>30.04.202647</t>
+  </si>
+  <si>
+    <t>30.04.202648</t>
+  </si>
+  <si>
+    <t>30.04.202649</t>
+  </si>
+  <si>
+    <t>30.04.202650</t>
+  </si>
+  <si>
+    <t>30.04.202651</t>
+  </si>
+  <si>
+    <t>30.04.202652</t>
+  </si>
+  <si>
+    <t>30.04.202653</t>
+  </si>
+  <si>
+    <t>30.04.202654</t>
+  </si>
+  <si>
+    <t>30.04.202655</t>
+  </si>
+  <si>
+    <t>30.04.202656</t>
+  </si>
+  <si>
+    <t>30.04.202657</t>
+  </si>
+  <si>
+    <t>30.04.202658</t>
+  </si>
+  <si>
+    <t>30.04.202659</t>
+  </si>
+  <si>
+    <t>30.04.202660</t>
+  </si>
+  <si>
+    <t>30.04.202661</t>
+  </si>
+  <si>
+    <t>30.04.202662</t>
+  </si>
+  <si>
+    <t>30.04.202663</t>
+  </si>
+  <si>
+    <t>30.04.202664</t>
+  </si>
+  <si>
+    <t>30.04.202665</t>
+  </si>
+  <si>
+    <t>30.04.202666</t>
+  </si>
+  <si>
+    <t>30.04.202667</t>
+  </si>
+  <si>
+    <t>30.04.202668</t>
+  </si>
+  <si>
+    <t>30.04.202669</t>
+  </si>
+  <si>
+    <t>30.04.202670</t>
+  </si>
+  <si>
+    <t>30.04.202671</t>
+  </si>
+  <si>
+    <t>30.04.202672</t>
+  </si>
+  <si>
+    <t>30.04.202673</t>
+  </si>
+  <si>
+    <t>30.04.202674</t>
+  </si>
+  <si>
+    <t>30.04.202675</t>
+  </si>
+  <si>
+    <t>30.04.202676</t>
+  </si>
+  <si>
+    <t>30.04.202677</t>
+  </si>
+  <si>
+    <t>30.04.202678</t>
+  </si>
+  <si>
+    <t>30.04.202679</t>
+  </si>
+  <si>
+    <t>30.04.202680</t>
+  </si>
+  <si>
+    <t>30.04.202681</t>
+  </si>
+  <si>
+    <t>30.04.202682</t>
+  </si>
+  <si>
+    <t>30.04.202683</t>
+  </si>
+  <si>
+    <t>30.04.202684</t>
+  </si>
+  <si>
+    <t>30.04.202685</t>
+  </si>
+  <si>
+    <t>30.04.202686</t>
+  </si>
+  <si>
+    <t>30.04.202687</t>
+  </si>
+  <si>
+    <t>30.04.202688</t>
+  </si>
+  <si>
+    <t>30.04.202689</t>
+  </si>
+  <si>
+    <t>30.04.202690</t>
+  </si>
+  <si>
+    <t>30.04.202691</t>
+  </si>
+  <si>
+    <t>30.04.202692</t>
+  </si>
+  <si>
+    <t>30.04.202693</t>
+  </si>
+  <si>
+    <t>30.04.202694</t>
+  </si>
+  <si>
+    <t>01.05.202696</t>
+  </si>
+  <si>
+    <t>01.05.20261</t>
+  </si>
+  <si>
+    <t>01.05.20262</t>
+  </si>
+  <si>
+    <t>01.05.20263</t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E389"/>
+  <dimension ref="A1:E292"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1567,7 +1279,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46136.03611111111</v>
+        <v>46140.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1584,7 +1296,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46136.04652777778</v>
+        <v>46140.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1601,7 +1313,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46136.05694444444</v>
+        <v>46140.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1618,7 +1330,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46136.06736111111</v>
+        <v>46140.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1635,7 +1347,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46136.07777777778</v>
+        <v>46140.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1652,7 +1364,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46136.08819444444</v>
+        <v>46140.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1669,7 +1381,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46136.09861111111</v>
+        <v>46140.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1686,7 +1398,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46136.10902777778</v>
+        <v>46140.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1703,7 +1415,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46136.11944444444</v>
+        <v>46140.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1720,7 +1432,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46136.12986111111</v>
+        <v>46140.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1737,7 +1449,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46136.14027777778</v>
+        <v>46140.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1754,7 +1466,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46136.15069444444</v>
+        <v>46140.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1771,7 +1483,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46136.16111111111</v>
+        <v>46140.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1788,7 +1500,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46136.17152777778</v>
+        <v>46140.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1805,7 +1517,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46136.18194444444</v>
+        <v>46140.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1822,7 +1534,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46136.19236111111</v>
+        <v>46140.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1839,7 +1551,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46136.20277777778</v>
+        <v>46140.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1856,7 +1568,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46136.21319444444</v>
+        <v>46140.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1873,7 +1585,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46136.22361111111</v>
+        <v>46140.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1890,7 +1602,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46136.23402777778</v>
+        <v>46140.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1907,7 +1619,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46136.24444444444</v>
+        <v>46140.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1924,7 +1636,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46136.25486111111</v>
+        <v>46140.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1941,7 +1653,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46136.26527777778</v>
+        <v>46140.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1958,7 +1670,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46136.27569444444</v>
+        <v>46140.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1975,7 +1687,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46136.28611111111</v>
+        <v>46140.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1992,7 +1704,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46136.29652777778</v>
+        <v>46140.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2009,7 +1721,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46136.30694444444</v>
+        <v>46140.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2026,7 +1738,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46136.31736111111</v>
+        <v>46140.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2043,7 +1755,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46136.32777777778</v>
+        <v>46140.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2060,7 +1772,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46136.33819444444</v>
+        <v>46140.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2077,7 +1789,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46136.34861111111</v>
+        <v>46140.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2094,7 +1806,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46136.35902777778</v>
+        <v>46140.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2111,7 +1823,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46136.36944444444</v>
+        <v>46140.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -2128,7 +1840,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46136.37986111111</v>
+        <v>46140.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2145,7 +1857,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46136.39027777778</v>
+        <v>46140.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -2162,7 +1874,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46136.40069444444</v>
+        <v>46140.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -2179,7 +1891,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46136.41111111111</v>
+        <v>46140.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -2196,7 +1908,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46136.42152777778</v>
+        <v>46140.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -2213,7 +1925,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46136.43194444444</v>
+        <v>46140.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -2230,7 +1942,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46136.44236111111</v>
+        <v>46140.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -2247,7 +1959,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46136.45277777778</v>
+        <v>46140.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -2264,7 +1976,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46136.46319444444</v>
+        <v>46140.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -2281,7 +1993,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46136.47361111111</v>
+        <v>46140.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2298,7 +2010,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46136.48402777778</v>
+        <v>46140.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2315,7 +2027,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46136.49444444444</v>
+        <v>46140.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2332,7 +2044,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46136.50486111111</v>
+        <v>46140.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2349,7 +2061,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46136.51527777778</v>
+        <v>46140.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2366,7 +2078,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46136.52569444444</v>
+        <v>46140.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2383,7 +2095,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46136.53611111111</v>
+        <v>46140.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2400,7 +2112,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46136.54652777778</v>
+        <v>46140.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2417,7 +2129,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46136.55694444444</v>
+        <v>46140.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2434,7 +2146,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46136.56736111111</v>
+        <v>46140.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2451,7 +2163,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46136.57777777778</v>
+        <v>46140.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -2468,7 +2180,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46136.58819444444</v>
+        <v>46140.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -2485,7 +2197,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46136.59861111111</v>
+        <v>46140.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -2502,7 +2214,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46136.60902777778</v>
+        <v>46140.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -2519,7 +2231,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46136.61944444444</v>
+        <v>46140.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -2536,7 +2248,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46136.62986111111</v>
+        <v>46140.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -2553,7 +2265,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46136.64027777778</v>
+        <v>46140.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -2570,7 +2282,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46136.65069444444</v>
+        <v>46140.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2587,7 +2299,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46136.66111111111</v>
+        <v>46140.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2604,7 +2316,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46136.67152777778</v>
+        <v>46140.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2621,7 +2333,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46136.68194444444</v>
+        <v>46140.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2638,7 +2350,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46136.69236111111</v>
+        <v>46140.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2655,7 +2367,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46136.70277777778</v>
+        <v>46140.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2672,7 +2384,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46136.71319444444</v>
+        <v>46140.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2689,7 +2401,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46136.72361111111</v>
+        <v>46140.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2706,7 +2418,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46136.73402777778</v>
+        <v>46140.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2723,7 +2435,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46136.74444444444</v>
+        <v>46140.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2740,7 +2452,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46136.75486111111</v>
+        <v>46140.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2757,7 +2469,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46136.76527777778</v>
+        <v>46140.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2774,7 +2486,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46136.77569444444</v>
+        <v>46140.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2791,7 +2503,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46136.78611111111</v>
+        <v>46140.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2808,7 +2520,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46136.79652777778</v>
+        <v>46140.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2825,7 +2537,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46136.80694444444</v>
+        <v>46140.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2842,7 +2554,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46136.81736111111</v>
+        <v>46140.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2859,7 +2571,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46136.82777777778</v>
+        <v>46140.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2876,7 +2588,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46136.83819444444</v>
+        <v>46140.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2893,7 +2605,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46136.84861111111</v>
+        <v>46140.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2910,7 +2622,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46136.85902777778</v>
+        <v>46140.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2927,7 +2639,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46136.86944444444</v>
+        <v>46140.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2944,7 +2656,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46136.87986111111</v>
+        <v>46140.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2961,7 +2673,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46136.89027777778</v>
+        <v>46140.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2978,7 +2690,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46136.90069444444</v>
+        <v>46140.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2995,7 +2707,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46136.91111111111</v>
+        <v>46140.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -3012,7 +2724,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46136.92152777778</v>
+        <v>46140.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -3029,7 +2741,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46136.93194444444</v>
+        <v>46140.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -3046,7 +2758,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46136.94236111111</v>
+        <v>46140.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -3063,7 +2775,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46136.95277777778</v>
+        <v>46140.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -3080,7 +2792,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46136.96319444444</v>
+        <v>46140.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -3097,7 +2809,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46136.97361111111</v>
+        <v>46140.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -3114,7 +2826,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46136.98402777778</v>
+        <v>46140.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -3131,7 +2843,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46136.99444444444</v>
+        <v>46140.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -3148,7 +2860,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46137.00486111111</v>
+        <v>46141.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -3165,7 +2877,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46137.01527777778</v>
+        <v>46141.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -3182,7 +2894,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46137.02569444444</v>
+        <v>46141.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -3199,7 +2911,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46137.03611111111</v>
+        <v>46141.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -3216,7 +2928,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46137.03611111111</v>
+        <v>46141.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -3233,7 +2945,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46137.04652777778</v>
+        <v>46141.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -3250,7 +2962,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46137.05694444444</v>
+        <v>46141.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -3267,7 +2979,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46137.06736111111</v>
+        <v>46141.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3284,7 +2996,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46137.07777777778</v>
+        <v>46141.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3301,7 +3013,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46137.08819444444</v>
+        <v>46141.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3318,7 +3030,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46137.09861111111</v>
+        <v>46141.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3335,7 +3047,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46137.10902777778</v>
+        <v>46141.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3352,7 +3064,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46137.11944444444</v>
+        <v>46141.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3369,7 +3081,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46137.12986111111</v>
+        <v>46141.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -3386,7 +3098,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46137.14027777778</v>
+        <v>46141.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3403,7 +3115,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46137.15069444444</v>
+        <v>46141.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3420,7 +3132,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46137.16111111111</v>
+        <v>46141.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3437,7 +3149,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46137.17152777778</v>
+        <v>46141.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3454,7 +3166,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46137.18194444444</v>
+        <v>46141.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3471,7 +3183,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46137.19236111111</v>
+        <v>46141.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3488,7 +3200,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46137.20277777778</v>
+        <v>46141.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3505,7 +3217,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46137.21319444444</v>
+        <v>46141.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3522,7 +3234,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46137.22361111111</v>
+        <v>46141.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3539,7 +3251,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46137.23402777778</v>
+        <v>46141.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3556,7 +3268,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46137.24444444444</v>
+        <v>46141.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3573,7 +3285,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46137.25486111111</v>
+        <v>46141.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3590,7 +3302,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46137.26527777778</v>
+        <v>46141.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3607,7 +3319,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46137.27569444444</v>
+        <v>46141.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3624,7 +3336,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46137.28611111111</v>
+        <v>46141.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3641,7 +3353,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46137.29652777778</v>
+        <v>46141.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3658,7 +3370,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46137.30694444444</v>
+        <v>46141.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3675,7 +3387,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46137.31736111111</v>
+        <v>46141.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3692,7 +3404,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46137.32777777778</v>
+        <v>46141.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3709,7 +3421,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46137.33819444444</v>
+        <v>46141.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3726,7 +3438,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46137.34861111111</v>
+        <v>46141.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3743,7 +3455,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46137.35902777778</v>
+        <v>46141.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3760,7 +3472,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46137.36944444444</v>
+        <v>46141.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3777,7 +3489,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46137.37986111111</v>
+        <v>46141.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3794,7 +3506,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46137.39027777778</v>
+        <v>46141.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3811,7 +3523,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46137.40069444444</v>
+        <v>46141.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3828,7 +3540,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46137.41111111111</v>
+        <v>46141.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3845,7 +3557,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46137.42152777778</v>
+        <v>46141.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3862,7 +3574,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46137.43194444444</v>
+        <v>46141.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3879,7 +3591,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46137.44236111111</v>
+        <v>46141.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3896,7 +3608,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46137.45277777778</v>
+        <v>46141.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3913,7 +3625,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46137.46319444444</v>
+        <v>46141.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3930,7 +3642,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46137.47361111111</v>
+        <v>46141.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3947,7 +3659,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46137.48402777778</v>
+        <v>46141.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3964,7 +3676,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46137.49444444444</v>
+        <v>46141.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3981,7 +3693,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46137.50486111111</v>
+        <v>46141.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3998,7 +3710,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46137.51527777778</v>
+        <v>46141.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -4015,7 +3727,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46137.52569444444</v>
+        <v>46141.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -4032,7 +3744,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46137.53611111111</v>
+        <v>46141.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -4049,7 +3761,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46137.54652777778</v>
+        <v>46141.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -4066,7 +3778,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46137.55694444444</v>
+        <v>46141.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -4083,7 +3795,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46137.56736111111</v>
+        <v>46141.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4100,7 +3812,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46137.57777777778</v>
+        <v>46141.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4117,7 +3829,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46137.58819444444</v>
+        <v>46141.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4134,7 +3846,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46137.59861111111</v>
+        <v>46141.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -4151,7 +3863,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46137.60902777778</v>
+        <v>46141.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4168,7 +3880,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46137.61944444444</v>
+        <v>46141.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4185,7 +3897,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46137.62986111111</v>
+        <v>46141.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -4202,7 +3914,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46137.64027777778</v>
+        <v>46141.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -4219,7 +3931,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46137.65069444444</v>
+        <v>46141.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -4236,7 +3948,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46137.66111111111</v>
+        <v>46141.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4253,7 +3965,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46137.67152777778</v>
+        <v>46141.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4270,7 +3982,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46137.68194444444</v>
+        <v>46141.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4287,7 +3999,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46137.69236111111</v>
+        <v>46141.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4304,7 +4016,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46137.70277777778</v>
+        <v>46141.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4321,7 +4033,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46137.71319444444</v>
+        <v>46141.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4338,7 +4050,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46137.72361111111</v>
+        <v>46141.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4355,7 +4067,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46137.73402777778</v>
+        <v>46141.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4372,7 +4084,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46137.74444444444</v>
+        <v>46141.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4389,7 +4101,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46137.75486111111</v>
+        <v>46141.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4406,7 +4118,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46137.76527777778</v>
+        <v>46141.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4423,7 +4135,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46137.77569444444</v>
+        <v>46141.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4440,7 +4152,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46137.78611111111</v>
+        <v>46141.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4457,7 +4169,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46137.79652777778</v>
+        <v>46141.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4474,7 +4186,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46137.80694444444</v>
+        <v>46141.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4491,7 +4203,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46137.81736111111</v>
+        <v>46141.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4508,7 +4220,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46137.82777777778</v>
+        <v>46141.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4525,7 +4237,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46137.83819444444</v>
+        <v>46141.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4542,7 +4254,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46137.84861111111</v>
+        <v>46141.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4559,7 +4271,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46137.85902777778</v>
+        <v>46141.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4576,7 +4288,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46137.86944444444</v>
+        <v>46141.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4593,7 +4305,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46137.87986111111</v>
+        <v>46141.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4610,7 +4322,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46137.89027777778</v>
+        <v>46141.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4627,7 +4339,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46137.90069444444</v>
+        <v>46141.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4644,7 +4356,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46137.91111111111</v>
+        <v>46141.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4661,7 +4373,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46137.92152777778</v>
+        <v>46141.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4678,7 +4390,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46137.93194444444</v>
+        <v>46141.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4695,7 +4407,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46137.94236111111</v>
+        <v>46141.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4712,7 +4424,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46137.95277777778</v>
+        <v>46141.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4729,7 +4441,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46137.96319444444</v>
+        <v>46141.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4746,7 +4458,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46137.97361111111</v>
+        <v>46141.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4763,7 +4475,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46137.98402777778</v>
+        <v>46141.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4780,7 +4492,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46137.99444444444</v>
+        <v>46141.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4797,7 +4509,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46138.00486111111</v>
+        <v>46142.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4814,7 +4526,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46138.01527777778</v>
+        <v>46142.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4831,7 +4543,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46138.02569444444</v>
+        <v>46142.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4848,7 +4560,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46138.03611111111</v>
+        <v>46142.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -4865,7 +4577,7 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46138.03611111111</v>
+        <v>46142.03611111111</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -4882,7 +4594,7 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46138.04652777778</v>
+        <v>46142.04652777778</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -4899,7 +4611,7 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46138.05694444444</v>
+        <v>46142.05694444444</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -4916,7 +4628,7 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46138.06736111111</v>
+        <v>46142.06736111111</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -4933,7 +4645,7 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46138.07777777778</v>
+        <v>46142.07777777778</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -4950,7 +4662,7 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46138.08819444444</v>
+        <v>46142.08819444444</v>
       </c>
       <c r="B201">
         <v>0</v>
@@ -4967,7 +4679,7 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46138.09861111111</v>
+        <v>46142.09861111111</v>
       </c>
       <c r="B202">
         <v>0</v>
@@ -4984,7 +4696,7 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46138.10902777778</v>
+        <v>46142.10902777778</v>
       </c>
       <c r="B203">
         <v>0</v>
@@ -5001,7 +4713,7 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46138.11944444444</v>
+        <v>46142.11944444444</v>
       </c>
       <c r="B204">
         <v>0</v>
@@ -5018,7 +4730,7 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46138.12986111111</v>
+        <v>46142.12986111111</v>
       </c>
       <c r="B205">
         <v>0</v>
@@ -5035,7 +4747,7 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46138.14027777778</v>
+        <v>46142.14027777778</v>
       </c>
       <c r="B206">
         <v>0</v>
@@ -5052,7 +4764,7 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46138.15069444444</v>
+        <v>46142.15069444444</v>
       </c>
       <c r="B207">
         <v>0</v>
@@ -5069,7 +4781,7 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46138.16111111111</v>
+        <v>46142.16111111111</v>
       </c>
       <c r="B208">
         <v>0</v>
@@ -5086,7 +4798,7 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46138.17152777778</v>
+        <v>46142.17152777778</v>
       </c>
       <c r="B209">
         <v>0</v>
@@ -5103,7 +4815,7 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46138.18194444444</v>
+        <v>46142.18194444444</v>
       </c>
       <c r="B210">
         <v>0</v>
@@ -5120,7 +4832,7 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46138.19236111111</v>
+        <v>46142.19236111111</v>
       </c>
       <c r="B211">
         <v>0</v>
@@ -5137,7 +4849,7 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46138.20277777778</v>
+        <v>46142.20277777778</v>
       </c>
       <c r="B212">
         <v>0</v>
@@ -5154,7 +4866,7 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46138.21319444444</v>
+        <v>46142.21319444444</v>
       </c>
       <c r="B213">
         <v>0</v>
@@ -5171,7 +4883,7 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46138.22361111111</v>
+        <v>46142.22361111111</v>
       </c>
       <c r="B214">
         <v>0</v>
@@ -5188,7 +4900,7 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46138.23402777778</v>
+        <v>46142.23402777778</v>
       </c>
       <c r="B215">
         <v>0</v>
@@ -5205,7 +4917,7 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46138.24444444444</v>
+        <v>46142.24444444444</v>
       </c>
       <c r="B216">
         <v>0</v>
@@ -5222,7 +4934,7 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46138.25486111111</v>
+        <v>46142.25486111111</v>
       </c>
       <c r="B217">
         <v>0</v>
@@ -5239,7 +4951,7 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46138.26527777778</v>
+        <v>46142.26527777778</v>
       </c>
       <c r="B218">
         <v>0</v>
@@ -5256,7 +4968,7 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46138.27569444444</v>
+        <v>46142.27569444444</v>
       </c>
       <c r="B219">
         <v>0</v>
@@ -5273,7 +4985,7 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46138.28611111111</v>
+        <v>46142.28611111111</v>
       </c>
       <c r="B220">
         <v>0</v>
@@ -5290,7 +5002,7 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46138.29652777778</v>
+        <v>46142.29652777778</v>
       </c>
       <c r="B221">
         <v>0</v>
@@ -5307,7 +5019,7 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46138.30694444444</v>
+        <v>46142.30694444444</v>
       </c>
       <c r="B222">
         <v>0</v>
@@ -5324,7 +5036,7 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46138.31736111111</v>
+        <v>46142.31736111111</v>
       </c>
       <c r="B223">
         <v>0</v>
@@ -5341,7 +5053,7 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46138.32777777778</v>
+        <v>46142.32777777778</v>
       </c>
       <c r="B224">
         <v>0</v>
@@ -5358,7 +5070,7 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46138.33819444444</v>
+        <v>46142.33819444444</v>
       </c>
       <c r="B225">
         <v>0</v>
@@ -5375,7 +5087,7 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46138.34861111111</v>
+        <v>46142.34861111111</v>
       </c>
       <c r="B226">
         <v>0</v>
@@ -5392,7 +5104,7 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2">
-        <v>46138.35902777778</v>
+        <v>46142.35902777778</v>
       </c>
       <c r="B227">
         <v>0</v>
@@ -5409,7 +5121,7 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2">
-        <v>46138.36944444444</v>
+        <v>46142.36944444444</v>
       </c>
       <c r="B228">
         <v>0</v>
@@ -5426,7 +5138,7 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2">
-        <v>46138.37986111111</v>
+        <v>46142.37986111111</v>
       </c>
       <c r="B229">
         <v>0</v>
@@ -5443,7 +5155,7 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2">
-        <v>46138.39027777778</v>
+        <v>46142.39027777778</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -5460,7 +5172,7 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2">
-        <v>46138.40069444444</v>
+        <v>46142.40069444444</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -5477,7 +5189,7 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2">
-        <v>46138.41111111111</v>
+        <v>46142.41111111111</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -5494,7 +5206,7 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2">
-        <v>46138.42152777778</v>
+        <v>46142.42152777778</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -5511,7 +5223,7 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2">
-        <v>46138.43194444444</v>
+        <v>46142.43194444444</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -5528,7 +5240,7 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2">
-        <v>46138.44236111111</v>
+        <v>46142.44236111111</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -5545,7 +5257,7 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2">
-        <v>46138.45277777778</v>
+        <v>46142.45277777778</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -5562,7 +5274,7 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2">
-        <v>46138.46319444444</v>
+        <v>46142.46319444444</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -5579,7 +5291,7 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2">
-        <v>46138.47361111111</v>
+        <v>46142.47361111111</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -5596,7 +5308,7 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2">
-        <v>46138.48402777778</v>
+        <v>46142.48402777778</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -5613,7 +5325,7 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2">
-        <v>46138.49444444444</v>
+        <v>46142.49444444444</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -5630,7 +5342,7 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2">
-        <v>46138.50486111111</v>
+        <v>46142.50486111111</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -5647,7 +5359,7 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2">
-        <v>46138.51527777778</v>
+        <v>46142.51527777778</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -5664,7 +5376,7 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2">
-        <v>46138.52569444444</v>
+        <v>46142.52569444444</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -5681,7 +5393,7 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2">
-        <v>46138.53611111111</v>
+        <v>46142.53611111111</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -5698,7 +5410,7 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2">
-        <v>46138.54652777778</v>
+        <v>46142.54652777778</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -5715,7 +5427,7 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2">
-        <v>46138.55694444444</v>
+        <v>46142.55694444444</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -5732,7 +5444,7 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2">
-        <v>46138.56736111111</v>
+        <v>46142.56736111111</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -5749,7 +5461,7 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2">
-        <v>46138.57777777778</v>
+        <v>46142.57777777778</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -5766,7 +5478,7 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2">
-        <v>46138.58819444444</v>
+        <v>46142.58819444444</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -5783,7 +5495,7 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2">
-        <v>46138.59861111111</v>
+        <v>46142.59861111111</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -5800,7 +5512,7 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2">
-        <v>46138.60902777778</v>
+        <v>46142.60902777778</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -5817,7 +5529,7 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2">
-        <v>46138.61944444444</v>
+        <v>46142.61944444444</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -5834,7 +5546,7 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2">
-        <v>46138.62986111111</v>
+        <v>46142.62986111111</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -5851,7 +5563,7 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2">
-        <v>46138.64027777778</v>
+        <v>46142.64027777778</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -5868,7 +5580,7 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2">
-        <v>46138.65069444444</v>
+        <v>46142.65069444444</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -5885,7 +5597,7 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2">
-        <v>46138.66111111111</v>
+        <v>46142.66111111111</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -5902,7 +5614,7 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2">
-        <v>46138.67152777778</v>
+        <v>46142.67152777778</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -5919,7 +5631,7 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2">
-        <v>46138.68194444444</v>
+        <v>46142.68194444444</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -5936,7 +5648,7 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2">
-        <v>46138.69236111111</v>
+        <v>46142.69236111111</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -5953,7 +5665,7 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2">
-        <v>46138.70277777778</v>
+        <v>46142.70277777778</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -5970,7 +5682,7 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2">
-        <v>46138.71319444444</v>
+        <v>46142.71319444444</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -5987,7 +5699,7 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2">
-        <v>46138.72361111111</v>
+        <v>46142.72361111111</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -6004,7 +5716,7 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2">
-        <v>46138.73402777778</v>
+        <v>46142.73402777778</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -6021,7 +5733,7 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2">
-        <v>46138.74444444444</v>
+        <v>46142.74444444444</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -6038,7 +5750,7 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2">
-        <v>46138.75486111111</v>
+        <v>46142.75486111111</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -6055,7 +5767,7 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2">
-        <v>46138.76527777778</v>
+        <v>46142.76527777778</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -6072,7 +5784,7 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2">
-        <v>46138.77569444444</v>
+        <v>46142.77569444444</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -6089,7 +5801,7 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2">
-        <v>46138.78611111111</v>
+        <v>46142.78611111111</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -6106,7 +5818,7 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2">
-        <v>46138.79652777778</v>
+        <v>46142.79652777778</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -6123,7 +5835,7 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2">
-        <v>46138.80694444444</v>
+        <v>46142.80694444444</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -6140,7 +5852,7 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2">
-        <v>46138.81736111111</v>
+        <v>46142.81736111111</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -6157,7 +5869,7 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2">
-        <v>46138.82777777778</v>
+        <v>46142.82777777778</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -6174,7 +5886,7 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2">
-        <v>46138.83819444444</v>
+        <v>46142.83819444444</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -6191,7 +5903,7 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2">
-        <v>46138.84861111111</v>
+        <v>46142.84861111111</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -6208,7 +5920,7 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2">
-        <v>46138.85902777778</v>
+        <v>46142.85902777778</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -6225,7 +5937,7 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2">
-        <v>46138.86944444444</v>
+        <v>46142.86944444444</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -6242,7 +5954,7 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2">
-        <v>46138.87986111111</v>
+        <v>46142.87986111111</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -6259,7 +5971,7 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2">
-        <v>46138.89027777778</v>
+        <v>46142.89027777778</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -6276,7 +5988,7 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2">
-        <v>46138.90069444444</v>
+        <v>46142.90069444444</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -6293,7 +6005,7 @@
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2">
-        <v>46138.91111111111</v>
+        <v>46142.91111111111</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -6310,7 +6022,7 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2">
-        <v>46138.92152777778</v>
+        <v>46142.92152777778</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -6327,7 +6039,7 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2">
-        <v>46138.93194444444</v>
+        <v>46142.93194444444</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -6344,7 +6056,7 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2">
-        <v>46138.94236111111</v>
+        <v>46142.94236111111</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -6361,7 +6073,7 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2">
-        <v>46138.95277777778</v>
+        <v>46142.95277777778</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -6378,7 +6090,7 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="2">
-        <v>46138.96319444444</v>
+        <v>46142.96319444444</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -6395,7 +6107,7 @@
     </row>
     <row r="286" spans="1:5">
       <c r="A286" s="2">
-        <v>46138.97361111111</v>
+        <v>46142.97361111111</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -6412,7 +6124,7 @@
     </row>
     <row r="287" spans="1:5">
       <c r="A287" s="2">
-        <v>46138.98402777778</v>
+        <v>46142.98402777778</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -6429,7 +6141,7 @@
     </row>
     <row r="288" spans="1:5">
       <c r="A288" s="2">
-        <v>46138.99444444444</v>
+        <v>46142.99444444444</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -6446,7 +6158,7 @@
     </row>
     <row r="289" spans="1:5">
       <c r="A289" s="2">
-        <v>46139.00486111111</v>
+        <v>46143.00486111111</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -6463,7 +6175,7 @@
     </row>
     <row r="290" spans="1:5">
       <c r="A290" s="2">
-        <v>46139.01527777778</v>
+        <v>46143.01527777778</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -6480,7 +6192,7 @@
     </row>
     <row r="291" spans="1:5">
       <c r="A291" s="2">
-        <v>46139.02569444444</v>
+        <v>46143.02569444444</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -6497,7 +6209,7 @@
     </row>
     <row r="292" spans="1:5">
       <c r="A292" s="2">
-        <v>46139.03611111111</v>
+        <v>46143.03611111111</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -6510,1655 +6222,6 @@
       </c>
       <c r="E292" t="s">
         <v>293</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5">
-      <c r="A293" s="2">
-        <v>46139.03611111111</v>
-      </c>
-      <c r="B293">
-        <v>0</v>
-      </c>
-      <c r="C293">
-        <v>0</v>
-      </c>
-      <c r="D293">
-        <v>4</v>
-      </c>
-      <c r="E293" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5">
-      <c r="A294" s="2">
-        <v>46139.04652777778</v>
-      </c>
-      <c r="B294">
-        <v>0</v>
-      </c>
-      <c r="C294">
-        <v>0</v>
-      </c>
-      <c r="D294">
-        <v>5</v>
-      </c>
-      <c r="E294" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5">
-      <c r="A295" s="2">
-        <v>46139.05694444444</v>
-      </c>
-      <c r="B295">
-        <v>0</v>
-      </c>
-      <c r="C295">
-        <v>0</v>
-      </c>
-      <c r="D295">
-        <v>6</v>
-      </c>
-      <c r="E295" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5">
-      <c r="A296" s="2">
-        <v>46139.06736111111</v>
-      </c>
-      <c r="B296">
-        <v>0</v>
-      </c>
-      <c r="C296">
-        <v>0</v>
-      </c>
-      <c r="D296">
-        <v>7</v>
-      </c>
-      <c r="E296" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5">
-      <c r="A297" s="2">
-        <v>46139.07777777778</v>
-      </c>
-      <c r="B297">
-        <v>0</v>
-      </c>
-      <c r="C297">
-        <v>0</v>
-      </c>
-      <c r="D297">
-        <v>8</v>
-      </c>
-      <c r="E297" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5">
-      <c r="A298" s="2">
-        <v>46139.08819444444</v>
-      </c>
-      <c r="B298">
-        <v>0</v>
-      </c>
-      <c r="C298">
-        <v>0</v>
-      </c>
-      <c r="D298">
-        <v>9</v>
-      </c>
-      <c r="E298" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5">
-      <c r="A299" s="2">
-        <v>46139.09861111111</v>
-      </c>
-      <c r="B299">
-        <v>0</v>
-      </c>
-      <c r="C299">
-        <v>0</v>
-      </c>
-      <c r="D299">
-        <v>10</v>
-      </c>
-      <c r="E299" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5">
-      <c r="A300" s="2">
-        <v>46139.10902777778</v>
-      </c>
-      <c r="B300">
-        <v>0</v>
-      </c>
-      <c r="C300">
-        <v>0</v>
-      </c>
-      <c r="D300">
-        <v>11</v>
-      </c>
-      <c r="E300" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5">
-      <c r="A301" s="2">
-        <v>46139.11944444444</v>
-      </c>
-      <c r="B301">
-        <v>0</v>
-      </c>
-      <c r="C301">
-        <v>0</v>
-      </c>
-      <c r="D301">
-        <v>12</v>
-      </c>
-      <c r="E301" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5">
-      <c r="A302" s="2">
-        <v>46139.12986111111</v>
-      </c>
-      <c r="B302">
-        <v>0</v>
-      </c>
-      <c r="C302">
-        <v>0</v>
-      </c>
-      <c r="D302">
-        <v>13</v>
-      </c>
-      <c r="E302" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5">
-      <c r="A303" s="2">
-        <v>46139.14027777778</v>
-      </c>
-      <c r="B303">
-        <v>0</v>
-      </c>
-      <c r="C303">
-        <v>0</v>
-      </c>
-      <c r="D303">
-        <v>14</v>
-      </c>
-      <c r="E303" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5">
-      <c r="A304" s="2">
-        <v>46139.15069444444</v>
-      </c>
-      <c r="B304">
-        <v>0</v>
-      </c>
-      <c r="C304">
-        <v>0</v>
-      </c>
-      <c r="D304">
-        <v>15</v>
-      </c>
-      <c r="E304" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5">
-      <c r="A305" s="2">
-        <v>46139.16111111111</v>
-      </c>
-      <c r="B305">
-        <v>0</v>
-      </c>
-      <c r="C305">
-        <v>0</v>
-      </c>
-      <c r="D305">
-        <v>16</v>
-      </c>
-      <c r="E305" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5">
-      <c r="A306" s="2">
-        <v>46139.17152777778</v>
-      </c>
-      <c r="B306">
-        <v>0</v>
-      </c>
-      <c r="C306">
-        <v>0</v>
-      </c>
-      <c r="D306">
-        <v>17</v>
-      </c>
-      <c r="E306" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5">
-      <c r="A307" s="2">
-        <v>46139.18194444444</v>
-      </c>
-      <c r="B307">
-        <v>0</v>
-      </c>
-      <c r="C307">
-        <v>0</v>
-      </c>
-      <c r="D307">
-        <v>18</v>
-      </c>
-      <c r="E307" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5">
-      <c r="A308" s="2">
-        <v>46139.19236111111</v>
-      </c>
-      <c r="B308">
-        <v>0</v>
-      </c>
-      <c r="C308">
-        <v>0</v>
-      </c>
-      <c r="D308">
-        <v>19</v>
-      </c>
-      <c r="E308" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5">
-      <c r="A309" s="2">
-        <v>46139.20277777778</v>
-      </c>
-      <c r="B309">
-        <v>0</v>
-      </c>
-      <c r="C309">
-        <v>0</v>
-      </c>
-      <c r="D309">
-        <v>20</v>
-      </c>
-      <c r="E309" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5">
-      <c r="A310" s="2">
-        <v>46139.21319444444</v>
-      </c>
-      <c r="B310">
-        <v>0</v>
-      </c>
-      <c r="C310">
-        <v>0</v>
-      </c>
-      <c r="D310">
-        <v>21</v>
-      </c>
-      <c r="E310" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5">
-      <c r="A311" s="2">
-        <v>46139.22361111111</v>
-      </c>
-      <c r="B311">
-        <v>0</v>
-      </c>
-      <c r="C311">
-        <v>0</v>
-      </c>
-      <c r="D311">
-        <v>22</v>
-      </c>
-      <c r="E311" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5">
-      <c r="A312" s="2">
-        <v>46139.23402777778</v>
-      </c>
-      <c r="B312">
-        <v>0</v>
-      </c>
-      <c r="C312">
-        <v>0</v>
-      </c>
-      <c r="D312">
-        <v>23</v>
-      </c>
-      <c r="E312" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5">
-      <c r="A313" s="2">
-        <v>46139.24444444444</v>
-      </c>
-      <c r="B313">
-        <v>0</v>
-      </c>
-      <c r="C313">
-        <v>0</v>
-      </c>
-      <c r="D313">
-        <v>24</v>
-      </c>
-      <c r="E313" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5">
-      <c r="A314" s="2">
-        <v>46139.25486111111</v>
-      </c>
-      <c r="B314">
-        <v>0</v>
-      </c>
-      <c r="C314">
-        <v>0</v>
-      </c>
-      <c r="D314">
-        <v>25</v>
-      </c>
-      <c r="E314" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5">
-      <c r="A315" s="2">
-        <v>46139.26527777778</v>
-      </c>
-      <c r="B315">
-        <v>0</v>
-      </c>
-      <c r="C315">
-        <v>0</v>
-      </c>
-      <c r="D315">
-        <v>26</v>
-      </c>
-      <c r="E315" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5">
-      <c r="A316" s="2">
-        <v>46139.27569444444</v>
-      </c>
-      <c r="B316">
-        <v>0</v>
-      </c>
-      <c r="C316">
-        <v>0</v>
-      </c>
-      <c r="D316">
-        <v>27</v>
-      </c>
-      <c r="E316" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5">
-      <c r="A317" s="2">
-        <v>46139.28611111111</v>
-      </c>
-      <c r="B317">
-        <v>0</v>
-      </c>
-      <c r="C317">
-        <v>0</v>
-      </c>
-      <c r="D317">
-        <v>28</v>
-      </c>
-      <c r="E317" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5">
-      <c r="A318" s="2">
-        <v>46139.29652777778</v>
-      </c>
-      <c r="B318">
-        <v>0</v>
-      </c>
-      <c r="C318">
-        <v>0</v>
-      </c>
-      <c r="D318">
-        <v>29</v>
-      </c>
-      <c r="E318" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5">
-      <c r="A319" s="2">
-        <v>46139.30694444444</v>
-      </c>
-      <c r="B319">
-        <v>0</v>
-      </c>
-      <c r="C319">
-        <v>0</v>
-      </c>
-      <c r="D319">
-        <v>30</v>
-      </c>
-      <c r="E319" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5">
-      <c r="A320" s="2">
-        <v>46139.31736111111</v>
-      </c>
-      <c r="B320">
-        <v>0</v>
-      </c>
-      <c r="C320">
-        <v>0</v>
-      </c>
-      <c r="D320">
-        <v>31</v>
-      </c>
-      <c r="E320" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5">
-      <c r="A321" s="2">
-        <v>46139.32777777778</v>
-      </c>
-      <c r="B321">
-        <v>0</v>
-      </c>
-      <c r="C321">
-        <v>0</v>
-      </c>
-      <c r="D321">
-        <v>32</v>
-      </c>
-      <c r="E321" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5">
-      <c r="A322" s="2">
-        <v>46139.33819444444</v>
-      </c>
-      <c r="B322">
-        <v>0</v>
-      </c>
-      <c r="C322">
-        <v>0</v>
-      </c>
-      <c r="D322">
-        <v>33</v>
-      </c>
-      <c r="E322" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5">
-      <c r="A323" s="2">
-        <v>46139.34861111111</v>
-      </c>
-      <c r="B323">
-        <v>0</v>
-      </c>
-      <c r="C323">
-        <v>0</v>
-      </c>
-      <c r="D323">
-        <v>34</v>
-      </c>
-      <c r="E323" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5">
-      <c r="A324" s="2">
-        <v>46139.35902777778</v>
-      </c>
-      <c r="B324">
-        <v>0</v>
-      </c>
-      <c r="C324">
-        <v>0</v>
-      </c>
-      <c r="D324">
-        <v>35</v>
-      </c>
-      <c r="E324" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5">
-      <c r="A325" s="2">
-        <v>46139.36944444444</v>
-      </c>
-      <c r="B325">
-        <v>0</v>
-      </c>
-      <c r="C325">
-        <v>0</v>
-      </c>
-      <c r="D325">
-        <v>36</v>
-      </c>
-      <c r="E325" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5">
-      <c r="A326" s="2">
-        <v>46139.37986111111</v>
-      </c>
-      <c r="B326">
-        <v>0</v>
-      </c>
-      <c r="C326">
-        <v>0</v>
-      </c>
-      <c r="D326">
-        <v>37</v>
-      </c>
-      <c r="E326" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5">
-      <c r="A327" s="2">
-        <v>46139.39027777778</v>
-      </c>
-      <c r="B327">
-        <v>0</v>
-      </c>
-      <c r="C327">
-        <v>0</v>
-      </c>
-      <c r="D327">
-        <v>38</v>
-      </c>
-      <c r="E327" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5">
-      <c r="A328" s="2">
-        <v>46139.40069444444</v>
-      </c>
-      <c r="B328">
-        <v>0</v>
-      </c>
-      <c r="C328">
-        <v>0</v>
-      </c>
-      <c r="D328">
-        <v>39</v>
-      </c>
-      <c r="E328" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5">
-      <c r="A329" s="2">
-        <v>46139.41111111111</v>
-      </c>
-      <c r="B329">
-        <v>0</v>
-      </c>
-      <c r="C329">
-        <v>0</v>
-      </c>
-      <c r="D329">
-        <v>40</v>
-      </c>
-      <c r="E329" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5">
-      <c r="A330" s="2">
-        <v>46139.42152777778</v>
-      </c>
-      <c r="B330">
-        <v>0</v>
-      </c>
-      <c r="C330">
-        <v>0</v>
-      </c>
-      <c r="D330">
-        <v>41</v>
-      </c>
-      <c r="E330" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5">
-      <c r="A331" s="2">
-        <v>46139.43194444444</v>
-      </c>
-      <c r="B331">
-        <v>0</v>
-      </c>
-      <c r="C331">
-        <v>0</v>
-      </c>
-      <c r="D331">
-        <v>42</v>
-      </c>
-      <c r="E331" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5">
-      <c r="A332" s="2">
-        <v>46139.44236111111</v>
-      </c>
-      <c r="B332">
-        <v>0</v>
-      </c>
-      <c r="C332">
-        <v>0</v>
-      </c>
-      <c r="D332">
-        <v>43</v>
-      </c>
-      <c r="E332" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5">
-      <c r="A333" s="2">
-        <v>46139.45277777778</v>
-      </c>
-      <c r="B333">
-        <v>0</v>
-      </c>
-      <c r="C333">
-        <v>0</v>
-      </c>
-      <c r="D333">
-        <v>44</v>
-      </c>
-      <c r="E333" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5">
-      <c r="A334" s="2">
-        <v>46139.46319444444</v>
-      </c>
-      <c r="B334">
-        <v>0</v>
-      </c>
-      <c r="C334">
-        <v>0</v>
-      </c>
-      <c r="D334">
-        <v>45</v>
-      </c>
-      <c r="E334" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5">
-      <c r="A335" s="2">
-        <v>46139.47361111111</v>
-      </c>
-      <c r="B335">
-        <v>0</v>
-      </c>
-      <c r="C335">
-        <v>0</v>
-      </c>
-      <c r="D335">
-        <v>46</v>
-      </c>
-      <c r="E335" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5">
-      <c r="A336" s="2">
-        <v>46139.48402777778</v>
-      </c>
-      <c r="B336">
-        <v>0</v>
-      </c>
-      <c r="C336">
-        <v>0</v>
-      </c>
-      <c r="D336">
-        <v>47</v>
-      </c>
-      <c r="E336" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5">
-      <c r="A337" s="2">
-        <v>46139.49444444444</v>
-      </c>
-      <c r="B337">
-        <v>0</v>
-      </c>
-      <c r="C337">
-        <v>0</v>
-      </c>
-      <c r="D337">
-        <v>48</v>
-      </c>
-      <c r="E337" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5">
-      <c r="A338" s="2">
-        <v>46139.50486111111</v>
-      </c>
-      <c r="B338">
-        <v>0</v>
-      </c>
-      <c r="C338">
-        <v>0</v>
-      </c>
-      <c r="D338">
-        <v>49</v>
-      </c>
-      <c r="E338" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5">
-      <c r="A339" s="2">
-        <v>46139.51527777778</v>
-      </c>
-      <c r="B339">
-        <v>0</v>
-      </c>
-      <c r="C339">
-        <v>0</v>
-      </c>
-      <c r="D339">
-        <v>50</v>
-      </c>
-      <c r="E339" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5">
-      <c r="A340" s="2">
-        <v>46139.52569444444</v>
-      </c>
-      <c r="B340">
-        <v>0</v>
-      </c>
-      <c r="C340">
-        <v>0</v>
-      </c>
-      <c r="D340">
-        <v>51</v>
-      </c>
-      <c r="E340" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="341" spans="1:5">
-      <c r="A341" s="2">
-        <v>46139.53611111111</v>
-      </c>
-      <c r="B341">
-        <v>0</v>
-      </c>
-      <c r="C341">
-        <v>0</v>
-      </c>
-      <c r="D341">
-        <v>52</v>
-      </c>
-      <c r="E341" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5">
-      <c r="A342" s="2">
-        <v>46139.54652777778</v>
-      </c>
-      <c r="B342">
-        <v>0</v>
-      </c>
-      <c r="C342">
-        <v>0</v>
-      </c>
-      <c r="D342">
-        <v>53</v>
-      </c>
-      <c r="E342" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5">
-      <c r="A343" s="2">
-        <v>46139.55694444444</v>
-      </c>
-      <c r="B343">
-        <v>0</v>
-      </c>
-      <c r="C343">
-        <v>0</v>
-      </c>
-      <c r="D343">
-        <v>54</v>
-      </c>
-      <c r="E343" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5">
-      <c r="A344" s="2">
-        <v>46139.56736111111</v>
-      </c>
-      <c r="B344">
-        <v>0</v>
-      </c>
-      <c r="C344">
-        <v>0</v>
-      </c>
-      <c r="D344">
-        <v>55</v>
-      </c>
-      <c r="E344" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="345" spans="1:5">
-      <c r="A345" s="2">
-        <v>46139.57777777778</v>
-      </c>
-      <c r="B345">
-        <v>0</v>
-      </c>
-      <c r="C345">
-        <v>0</v>
-      </c>
-      <c r="D345">
-        <v>56</v>
-      </c>
-      <c r="E345" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="346" spans="1:5">
-      <c r="A346" s="2">
-        <v>46139.58819444444</v>
-      </c>
-      <c r="B346">
-        <v>0</v>
-      </c>
-      <c r="C346">
-        <v>0</v>
-      </c>
-      <c r="D346">
-        <v>57</v>
-      </c>
-      <c r="E346" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5">
-      <c r="A347" s="2">
-        <v>46139.59861111111</v>
-      </c>
-      <c r="B347">
-        <v>0</v>
-      </c>
-      <c r="C347">
-        <v>0</v>
-      </c>
-      <c r="D347">
-        <v>58</v>
-      </c>
-      <c r="E347" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5">
-      <c r="A348" s="2">
-        <v>46139.60902777778</v>
-      </c>
-      <c r="B348">
-        <v>0</v>
-      </c>
-      <c r="C348">
-        <v>0</v>
-      </c>
-      <c r="D348">
-        <v>59</v>
-      </c>
-      <c r="E348" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="349" spans="1:5">
-      <c r="A349" s="2">
-        <v>46139.61944444444</v>
-      </c>
-      <c r="B349">
-        <v>0</v>
-      </c>
-      <c r="C349">
-        <v>0</v>
-      </c>
-      <c r="D349">
-        <v>60</v>
-      </c>
-      <c r="E349" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="350" spans="1:5">
-      <c r="A350" s="2">
-        <v>46139.62986111111</v>
-      </c>
-      <c r="B350">
-        <v>0</v>
-      </c>
-      <c r="C350">
-        <v>0</v>
-      </c>
-      <c r="D350">
-        <v>61</v>
-      </c>
-      <c r="E350" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="351" spans="1:5">
-      <c r="A351" s="2">
-        <v>46139.64027777778</v>
-      </c>
-      <c r="B351">
-        <v>0</v>
-      </c>
-      <c r="C351">
-        <v>0</v>
-      </c>
-      <c r="D351">
-        <v>62</v>
-      </c>
-      <c r="E351" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="352" spans="1:5">
-      <c r="A352" s="2">
-        <v>46139.65069444444</v>
-      </c>
-      <c r="B352">
-        <v>0</v>
-      </c>
-      <c r="C352">
-        <v>0</v>
-      </c>
-      <c r="D352">
-        <v>63</v>
-      </c>
-      <c r="E352" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="353" spans="1:5">
-      <c r="A353" s="2">
-        <v>46139.66111111111</v>
-      </c>
-      <c r="B353">
-        <v>0</v>
-      </c>
-      <c r="C353">
-        <v>0</v>
-      </c>
-      <c r="D353">
-        <v>64</v>
-      </c>
-      <c r="E353" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5">
-      <c r="A354" s="2">
-        <v>46139.67152777778</v>
-      </c>
-      <c r="B354">
-        <v>0</v>
-      </c>
-      <c r="C354">
-        <v>0</v>
-      </c>
-      <c r="D354">
-        <v>65</v>
-      </c>
-      <c r="E354" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="355" spans="1:5">
-      <c r="A355" s="2">
-        <v>46139.68194444444</v>
-      </c>
-      <c r="B355">
-        <v>0</v>
-      </c>
-      <c r="C355">
-        <v>0</v>
-      </c>
-      <c r="D355">
-        <v>66</v>
-      </c>
-      <c r="E355" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5">
-      <c r="A356" s="2">
-        <v>46139.69236111111</v>
-      </c>
-      <c r="B356">
-        <v>0</v>
-      </c>
-      <c r="C356">
-        <v>0</v>
-      </c>
-      <c r="D356">
-        <v>67</v>
-      </c>
-      <c r="E356" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5">
-      <c r="A357" s="2">
-        <v>46139.70277777778</v>
-      </c>
-      <c r="B357">
-        <v>0</v>
-      </c>
-      <c r="C357">
-        <v>0</v>
-      </c>
-      <c r="D357">
-        <v>68</v>
-      </c>
-      <c r="E357" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="358" spans="1:5">
-      <c r="A358" s="2">
-        <v>46139.71319444444</v>
-      </c>
-      <c r="B358">
-        <v>0</v>
-      </c>
-      <c r="C358">
-        <v>0</v>
-      </c>
-      <c r="D358">
-        <v>69</v>
-      </c>
-      <c r="E358" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="359" spans="1:5">
-      <c r="A359" s="2">
-        <v>46139.72361111111</v>
-      </c>
-      <c r="B359">
-        <v>0</v>
-      </c>
-      <c r="C359">
-        <v>0</v>
-      </c>
-      <c r="D359">
-        <v>70</v>
-      </c>
-      <c r="E359" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5">
-      <c r="A360" s="2">
-        <v>46139.73402777778</v>
-      </c>
-      <c r="B360">
-        <v>0</v>
-      </c>
-      <c r="C360">
-        <v>0</v>
-      </c>
-      <c r="D360">
-        <v>71</v>
-      </c>
-      <c r="E360" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5">
-      <c r="A361" s="2">
-        <v>46139.74444444444</v>
-      </c>
-      <c r="B361">
-        <v>0</v>
-      </c>
-      <c r="C361">
-        <v>0</v>
-      </c>
-      <c r="D361">
-        <v>72</v>
-      </c>
-      <c r="E361" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5">
-      <c r="A362" s="2">
-        <v>46139.75486111111</v>
-      </c>
-      <c r="B362">
-        <v>0</v>
-      </c>
-      <c r="C362">
-        <v>0</v>
-      </c>
-      <c r="D362">
-        <v>73</v>
-      </c>
-      <c r="E362" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5">
-      <c r="A363" s="2">
-        <v>46139.76527777778</v>
-      </c>
-      <c r="B363">
-        <v>0</v>
-      </c>
-      <c r="C363">
-        <v>0</v>
-      </c>
-      <c r="D363">
-        <v>74</v>
-      </c>
-      <c r="E363" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5">
-      <c r="A364" s="2">
-        <v>46139.77569444444</v>
-      </c>
-      <c r="B364">
-        <v>0</v>
-      </c>
-      <c r="C364">
-        <v>0</v>
-      </c>
-      <c r="D364">
-        <v>75</v>
-      </c>
-      <c r="E364" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="365" spans="1:5">
-      <c r="A365" s="2">
-        <v>46139.78611111111</v>
-      </c>
-      <c r="B365">
-        <v>0</v>
-      </c>
-      <c r="C365">
-        <v>0</v>
-      </c>
-      <c r="D365">
-        <v>76</v>
-      </c>
-      <c r="E365" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5">
-      <c r="A366" s="2">
-        <v>46139.79652777778</v>
-      </c>
-      <c r="B366">
-        <v>0</v>
-      </c>
-      <c r="C366">
-        <v>0</v>
-      </c>
-      <c r="D366">
-        <v>77</v>
-      </c>
-      <c r="E366" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="367" spans="1:5">
-      <c r="A367" s="2">
-        <v>46139.80694444444</v>
-      </c>
-      <c r="B367">
-        <v>0</v>
-      </c>
-      <c r="C367">
-        <v>0</v>
-      </c>
-      <c r="D367">
-        <v>78</v>
-      </c>
-      <c r="E367" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="368" spans="1:5">
-      <c r="A368" s="2">
-        <v>46139.81736111111</v>
-      </c>
-      <c r="B368">
-        <v>0</v>
-      </c>
-      <c r="C368">
-        <v>0</v>
-      </c>
-      <c r="D368">
-        <v>79</v>
-      </c>
-      <c r="E368" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="369" spans="1:5">
-      <c r="A369" s="2">
-        <v>46139.82777777778</v>
-      </c>
-      <c r="B369">
-        <v>0</v>
-      </c>
-      <c r="C369">
-        <v>0</v>
-      </c>
-      <c r="D369">
-        <v>80</v>
-      </c>
-      <c r="E369" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="370" spans="1:5">
-      <c r="A370" s="2">
-        <v>46139.83819444444</v>
-      </c>
-      <c r="B370">
-        <v>0</v>
-      </c>
-      <c r="C370">
-        <v>0</v>
-      </c>
-      <c r="D370">
-        <v>81</v>
-      </c>
-      <c r="E370" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="371" spans="1:5">
-      <c r="A371" s="2">
-        <v>46139.84861111111</v>
-      </c>
-      <c r="B371">
-        <v>0</v>
-      </c>
-      <c r="C371">
-        <v>0</v>
-      </c>
-      <c r="D371">
-        <v>82</v>
-      </c>
-      <c r="E371" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5">
-      <c r="A372" s="2">
-        <v>46139.85902777778</v>
-      </c>
-      <c r="B372">
-        <v>0</v>
-      </c>
-      <c r="C372">
-        <v>0</v>
-      </c>
-      <c r="D372">
-        <v>83</v>
-      </c>
-      <c r="E372" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="373" spans="1:5">
-      <c r="A373" s="2">
-        <v>46139.86944444444</v>
-      </c>
-      <c r="B373">
-        <v>0</v>
-      </c>
-      <c r="C373">
-        <v>0</v>
-      </c>
-      <c r="D373">
-        <v>84</v>
-      </c>
-      <c r="E373" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="374" spans="1:5">
-      <c r="A374" s="2">
-        <v>46139.87986111111</v>
-      </c>
-      <c r="B374">
-        <v>0</v>
-      </c>
-      <c r="C374">
-        <v>0</v>
-      </c>
-      <c r="D374">
-        <v>85</v>
-      </c>
-      <c r="E374" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="375" spans="1:5">
-      <c r="A375" s="2">
-        <v>46139.89027777778</v>
-      </c>
-      <c r="B375">
-        <v>0</v>
-      </c>
-      <c r="C375">
-        <v>0</v>
-      </c>
-      <c r="D375">
-        <v>86</v>
-      </c>
-      <c r="E375" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="376" spans="1:5">
-      <c r="A376" s="2">
-        <v>46139.90069444444</v>
-      </c>
-      <c r="B376">
-        <v>0</v>
-      </c>
-      <c r="C376">
-        <v>0</v>
-      </c>
-      <c r="D376">
-        <v>87</v>
-      </c>
-      <c r="E376" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="377" spans="1:5">
-      <c r="A377" s="2">
-        <v>46139.91111111111</v>
-      </c>
-      <c r="B377">
-        <v>0</v>
-      </c>
-      <c r="C377">
-        <v>0</v>
-      </c>
-      <c r="D377">
-        <v>88</v>
-      </c>
-      <c r="E377" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="378" spans="1:5">
-      <c r="A378" s="2">
-        <v>46139.92152777778</v>
-      </c>
-      <c r="B378">
-        <v>0</v>
-      </c>
-      <c r="C378">
-        <v>0</v>
-      </c>
-      <c r="D378">
-        <v>89</v>
-      </c>
-      <c r="E378" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="379" spans="1:5">
-      <c r="A379" s="2">
-        <v>46139.93194444444</v>
-      </c>
-      <c r="B379">
-        <v>0</v>
-      </c>
-      <c r="C379">
-        <v>0</v>
-      </c>
-      <c r="D379">
-        <v>90</v>
-      </c>
-      <c r="E379" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="380" spans="1:5">
-      <c r="A380" s="2">
-        <v>46139.94236111111</v>
-      </c>
-      <c r="B380">
-        <v>0</v>
-      </c>
-      <c r="C380">
-        <v>0</v>
-      </c>
-      <c r="D380">
-        <v>91</v>
-      </c>
-      <c r="E380" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="381" spans="1:5">
-      <c r="A381" s="2">
-        <v>46139.95277777778</v>
-      </c>
-      <c r="B381">
-        <v>0</v>
-      </c>
-      <c r="C381">
-        <v>0</v>
-      </c>
-      <c r="D381">
-        <v>92</v>
-      </c>
-      <c r="E381" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="382" spans="1:5">
-      <c r="A382" s="2">
-        <v>46139.96319444444</v>
-      </c>
-      <c r="B382">
-        <v>0</v>
-      </c>
-      <c r="C382">
-        <v>0</v>
-      </c>
-      <c r="D382">
-        <v>93</v>
-      </c>
-      <c r="E382" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="383" spans="1:5">
-      <c r="A383" s="2">
-        <v>46139.97361111111</v>
-      </c>
-      <c r="B383">
-        <v>0</v>
-      </c>
-      <c r="C383">
-        <v>0</v>
-      </c>
-      <c r="D383">
-        <v>94</v>
-      </c>
-      <c r="E383" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="384" spans="1:5">
-      <c r="A384" s="2">
-        <v>46139.98402777778</v>
-      </c>
-      <c r="B384">
-        <v>0</v>
-      </c>
-      <c r="C384">
-        <v>0</v>
-      </c>
-      <c r="D384">
-        <v>95</v>
-      </c>
-      <c r="E384" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="385" spans="1:5">
-      <c r="A385" s="2">
-        <v>46139.99444444444</v>
-      </c>
-      <c r="B385">
-        <v>0</v>
-      </c>
-      <c r="C385">
-        <v>0</v>
-      </c>
-      <c r="D385">
-        <v>96</v>
-      </c>
-      <c r="E385" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="386" spans="1:5">
-      <c r="A386" s="2">
-        <v>46140.00486111111</v>
-      </c>
-      <c r="B386">
-        <v>0</v>
-      </c>
-      <c r="C386">
-        <v>0</v>
-      </c>
-      <c r="D386">
-        <v>1</v>
-      </c>
-      <c r="E386" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="387" spans="1:5">
-      <c r="A387" s="2">
-        <v>46140.01527777778</v>
-      </c>
-      <c r="B387">
-        <v>0</v>
-      </c>
-      <c r="C387">
-        <v>0</v>
-      </c>
-      <c r="D387">
-        <v>2</v>
-      </c>
-      <c r="E387" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="388" spans="1:5">
-      <c r="A388" s="2">
-        <v>46140.02569444444</v>
-      </c>
-      <c r="B388">
-        <v>0</v>
-      </c>
-      <c r="C388">
-        <v>0</v>
-      </c>
-      <c r="D388">
-        <v>3</v>
-      </c>
-      <c r="E388" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5">
-      <c r="A389" s="2">
-        <v>46140.03611111111</v>
-      </c>
-      <c r="B389">
-        <v>0</v>
-      </c>
-      <c r="C389">
-        <v>0</v>
-      </c>
-      <c r="D389">
-        <v>4</v>
-      </c>
-      <c r="E389" t="s">
-        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="486">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,579 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>28.04.20261</t>
-  </si>
-  <si>
-    <t>28.04.20262</t>
-  </si>
-  <si>
-    <t>28.04.20263</t>
-  </si>
-  <si>
-    <t>28.04.20264</t>
-  </si>
-  <si>
-    <t>28.04.20265</t>
-  </si>
-  <si>
-    <t>28.04.20266</t>
-  </si>
-  <si>
-    <t>28.04.20267</t>
-  </si>
-  <si>
-    <t>28.04.20268</t>
-  </si>
-  <si>
-    <t>28.04.20269</t>
-  </si>
-  <si>
-    <t>28.04.202610</t>
-  </si>
-  <si>
-    <t>28.04.202611</t>
-  </si>
-  <si>
-    <t>28.04.202612</t>
-  </si>
-  <si>
-    <t>28.04.202613</t>
-  </si>
-  <si>
-    <t>28.04.202614</t>
-  </si>
-  <si>
-    <t>28.04.202615</t>
-  </si>
-  <si>
-    <t>28.04.202616</t>
-  </si>
-  <si>
-    <t>28.04.202617</t>
-  </si>
-  <si>
-    <t>28.04.202618</t>
-  </si>
-  <si>
-    <t>28.04.202619</t>
-  </si>
-  <si>
-    <t>28.04.202620</t>
-  </si>
-  <si>
-    <t>28.04.202621</t>
-  </si>
-  <si>
-    <t>28.04.202622</t>
-  </si>
-  <si>
-    <t>28.04.202623</t>
-  </si>
-  <si>
-    <t>28.04.202624</t>
-  </si>
-  <si>
-    <t>28.04.202625</t>
-  </si>
-  <si>
-    <t>28.04.202626</t>
-  </si>
-  <si>
-    <t>28.04.202627</t>
-  </si>
-  <si>
-    <t>28.04.202628</t>
-  </si>
-  <si>
-    <t>28.04.202629</t>
-  </si>
-  <si>
-    <t>28.04.202630</t>
-  </si>
-  <si>
-    <t>28.04.202631</t>
-  </si>
-  <si>
-    <t>28.04.202632</t>
-  </si>
-  <si>
-    <t>28.04.202633</t>
-  </si>
-  <si>
-    <t>28.04.202634</t>
-  </si>
-  <si>
-    <t>28.04.202635</t>
-  </si>
-  <si>
-    <t>28.04.202636</t>
-  </si>
-  <si>
-    <t>28.04.202637</t>
-  </si>
-  <si>
-    <t>28.04.202638</t>
-  </si>
-  <si>
-    <t>28.04.202639</t>
-  </si>
-  <si>
-    <t>28.04.202640</t>
-  </si>
-  <si>
-    <t>28.04.202641</t>
-  </si>
-  <si>
-    <t>28.04.202642</t>
-  </si>
-  <si>
-    <t>28.04.202643</t>
-  </si>
-  <si>
-    <t>28.04.202644</t>
-  </si>
-  <si>
-    <t>28.04.202645</t>
-  </si>
-  <si>
-    <t>28.04.202646</t>
-  </si>
-  <si>
-    <t>28.04.202647</t>
-  </si>
-  <si>
-    <t>28.04.202648</t>
-  </si>
-  <si>
-    <t>28.04.202649</t>
-  </si>
-  <si>
-    <t>28.04.202650</t>
-  </si>
-  <si>
-    <t>28.04.202651</t>
-  </si>
-  <si>
-    <t>28.04.202652</t>
-  </si>
-  <si>
-    <t>28.04.202653</t>
-  </si>
-  <si>
-    <t>28.04.202654</t>
-  </si>
-  <si>
-    <t>28.04.202655</t>
-  </si>
-  <si>
-    <t>28.04.202656</t>
-  </si>
-  <si>
-    <t>28.04.202657</t>
-  </si>
-  <si>
-    <t>28.04.202658</t>
-  </si>
-  <si>
-    <t>28.04.202659</t>
-  </si>
-  <si>
-    <t>28.04.202660</t>
-  </si>
-  <si>
-    <t>28.04.202661</t>
-  </si>
-  <si>
-    <t>28.04.202662</t>
-  </si>
-  <si>
-    <t>28.04.202663</t>
-  </si>
-  <si>
-    <t>28.04.202664</t>
-  </si>
-  <si>
-    <t>28.04.202665</t>
-  </si>
-  <si>
-    <t>28.04.202666</t>
-  </si>
-  <si>
-    <t>28.04.202667</t>
-  </si>
-  <si>
-    <t>28.04.202668</t>
-  </si>
-  <si>
-    <t>28.04.202669</t>
-  </si>
-  <si>
-    <t>28.04.202670</t>
-  </si>
-  <si>
-    <t>28.04.202671</t>
-  </si>
-  <si>
-    <t>28.04.202672</t>
-  </si>
-  <si>
-    <t>28.04.202673</t>
-  </si>
-  <si>
-    <t>28.04.202674</t>
-  </si>
-  <si>
-    <t>28.04.202675</t>
-  </si>
-  <si>
-    <t>28.04.202676</t>
-  </si>
-  <si>
-    <t>28.04.202677</t>
-  </si>
-  <si>
-    <t>28.04.202678</t>
-  </si>
-  <si>
-    <t>28.04.202679</t>
-  </si>
-  <si>
-    <t>28.04.202680</t>
-  </si>
-  <si>
-    <t>28.04.202681</t>
-  </si>
-  <si>
-    <t>28.04.202682</t>
-  </si>
-  <si>
-    <t>28.04.202683</t>
-  </si>
-  <si>
-    <t>28.04.202684</t>
-  </si>
-  <si>
-    <t>28.04.202685</t>
-  </si>
-  <si>
-    <t>28.04.202686</t>
-  </si>
-  <si>
-    <t>28.04.202687</t>
-  </si>
-  <si>
-    <t>28.04.202688</t>
-  </si>
-  <si>
-    <t>28.04.202689</t>
-  </si>
-  <si>
-    <t>28.04.202690</t>
-  </si>
-  <si>
-    <t>28.04.202691</t>
-  </si>
-  <si>
-    <t>28.04.202692</t>
-  </si>
-  <si>
-    <t>28.04.202693</t>
-  </si>
-  <si>
-    <t>29.04.202694</t>
-  </si>
-  <si>
-    <t>29.04.202695</t>
-  </si>
-  <si>
-    <t>29.04.202696</t>
-  </si>
-  <si>
-    <t>29.04.20261</t>
-  </si>
-  <si>
-    <t>29.04.20262</t>
-  </si>
-  <si>
-    <t>29.04.20263</t>
-  </si>
-  <si>
-    <t>29.04.20264</t>
-  </si>
-  <si>
-    <t>29.04.20265</t>
-  </si>
-  <si>
-    <t>29.04.20266</t>
-  </si>
-  <si>
-    <t>29.04.20267</t>
-  </si>
-  <si>
-    <t>29.04.20268</t>
-  </si>
-  <si>
-    <t>29.04.20269</t>
-  </si>
-  <si>
-    <t>29.04.202610</t>
-  </si>
-  <si>
-    <t>29.04.202611</t>
-  </si>
-  <si>
-    <t>29.04.202612</t>
-  </si>
-  <si>
-    <t>29.04.202613</t>
-  </si>
-  <si>
-    <t>29.04.202614</t>
-  </si>
-  <si>
-    <t>29.04.202615</t>
-  </si>
-  <si>
-    <t>29.04.202616</t>
-  </si>
-  <si>
-    <t>29.04.202617</t>
-  </si>
-  <si>
-    <t>29.04.202618</t>
-  </si>
-  <si>
-    <t>29.04.202619</t>
-  </si>
-  <si>
-    <t>29.04.202620</t>
-  </si>
-  <si>
-    <t>29.04.202621</t>
-  </si>
-  <si>
-    <t>29.04.202622</t>
-  </si>
-  <si>
-    <t>29.04.202623</t>
-  </si>
-  <si>
-    <t>29.04.202624</t>
-  </si>
-  <si>
-    <t>29.04.202625</t>
-  </si>
-  <si>
-    <t>29.04.202626</t>
-  </si>
-  <si>
-    <t>29.04.202627</t>
-  </si>
-  <si>
-    <t>29.04.202628</t>
-  </si>
-  <si>
-    <t>29.04.202629</t>
-  </si>
-  <si>
-    <t>29.04.202630</t>
-  </si>
-  <si>
-    <t>29.04.202631</t>
-  </si>
-  <si>
-    <t>29.04.202632</t>
-  </si>
-  <si>
-    <t>29.04.202633</t>
-  </si>
-  <si>
-    <t>29.04.202634</t>
-  </si>
-  <si>
-    <t>29.04.202635</t>
-  </si>
-  <si>
-    <t>29.04.202636</t>
-  </si>
-  <si>
-    <t>29.04.202637</t>
-  </si>
-  <si>
-    <t>29.04.202638</t>
-  </si>
-  <si>
-    <t>29.04.202639</t>
-  </si>
-  <si>
-    <t>29.04.202640</t>
-  </si>
-  <si>
-    <t>29.04.202641</t>
-  </si>
-  <si>
-    <t>29.04.202642</t>
-  </si>
-  <si>
-    <t>29.04.202643</t>
-  </si>
-  <si>
-    <t>29.04.202644</t>
-  </si>
-  <si>
-    <t>29.04.202645</t>
-  </si>
-  <si>
-    <t>29.04.202646</t>
-  </si>
-  <si>
-    <t>29.04.202647</t>
-  </si>
-  <si>
-    <t>29.04.202648</t>
-  </si>
-  <si>
-    <t>29.04.202649</t>
-  </si>
-  <si>
-    <t>29.04.202650</t>
-  </si>
-  <si>
-    <t>29.04.202651</t>
-  </si>
-  <si>
-    <t>29.04.202652</t>
-  </si>
-  <si>
-    <t>29.04.202653</t>
-  </si>
-  <si>
-    <t>29.04.202654</t>
-  </si>
-  <si>
-    <t>29.04.202655</t>
-  </si>
-  <si>
-    <t>29.04.202656</t>
-  </si>
-  <si>
-    <t>29.04.202657</t>
-  </si>
-  <si>
-    <t>29.04.202658</t>
-  </si>
-  <si>
-    <t>29.04.202659</t>
-  </si>
-  <si>
-    <t>29.04.202660</t>
-  </si>
-  <si>
-    <t>29.04.202661</t>
-  </si>
-  <si>
-    <t>29.04.202662</t>
-  </si>
-  <si>
-    <t>29.04.202663</t>
-  </si>
-  <si>
-    <t>29.04.202664</t>
-  </si>
-  <si>
-    <t>29.04.202665</t>
-  </si>
-  <si>
-    <t>29.04.202666</t>
-  </si>
-  <si>
-    <t>29.04.202667</t>
-  </si>
-  <si>
-    <t>29.04.202668</t>
-  </si>
-  <si>
-    <t>29.04.202669</t>
-  </si>
-  <si>
-    <t>29.04.202670</t>
-  </si>
-  <si>
-    <t>29.04.202671</t>
-  </si>
-  <si>
-    <t>29.04.202672</t>
-  </si>
-  <si>
-    <t>29.04.202673</t>
-  </si>
-  <si>
-    <t>29.04.202674</t>
-  </si>
-  <si>
-    <t>29.04.202675</t>
-  </si>
-  <si>
-    <t>29.04.202676</t>
-  </si>
-  <si>
-    <t>29.04.202677</t>
-  </si>
-  <si>
-    <t>29.04.202678</t>
-  </si>
-  <si>
-    <t>29.04.202679</t>
-  </si>
-  <si>
-    <t>29.04.202680</t>
-  </si>
-  <si>
-    <t>29.04.202681</t>
-  </si>
-  <si>
-    <t>29.04.202682</t>
-  </si>
-  <si>
-    <t>29.04.202683</t>
-  </si>
-  <si>
-    <t>29.04.202684</t>
-  </si>
-  <si>
-    <t>29.04.202685</t>
-  </si>
-  <si>
-    <t>29.04.202686</t>
-  </si>
-  <si>
-    <t>29.04.202687</t>
-  </si>
-  <si>
-    <t>29.04.202688</t>
-  </si>
-  <si>
-    <t>29.04.202689</t>
-  </si>
-  <si>
-    <t>29.04.202690</t>
-  </si>
-  <si>
-    <t>29.04.202691</t>
-  </si>
-  <si>
-    <t>29.04.202692</t>
-  </si>
-  <si>
-    <t>29.04.202693</t>
-  </si>
-  <si>
-    <t>30.04.202695</t>
-  </si>
-  <si>
-    <t>30.04.202696</t>
-  </si>
-  <si>
     <t>30.04.20261</t>
   </si>
   <si>
@@ -883,7 +310,10 @@
     <t>30.04.202693</t>
   </si>
   <si>
-    <t>30.04.202694</t>
+    <t>01.05.202694</t>
+  </si>
+  <si>
+    <t>01.05.202695</t>
   </si>
   <si>
     <t>01.05.202696</t>
@@ -896,6 +326,1152 @@
   </si>
   <si>
     <t>01.05.20263</t>
+  </si>
+  <si>
+    <t>01.05.20264</t>
+  </si>
+  <si>
+    <t>01.05.20265</t>
+  </si>
+  <si>
+    <t>01.05.20266</t>
+  </si>
+  <si>
+    <t>01.05.20267</t>
+  </si>
+  <si>
+    <t>01.05.20268</t>
+  </si>
+  <si>
+    <t>01.05.20269</t>
+  </si>
+  <si>
+    <t>01.05.202610</t>
+  </si>
+  <si>
+    <t>01.05.202611</t>
+  </si>
+  <si>
+    <t>01.05.202612</t>
+  </si>
+  <si>
+    <t>01.05.202613</t>
+  </si>
+  <si>
+    <t>01.05.202614</t>
+  </si>
+  <si>
+    <t>01.05.202615</t>
+  </si>
+  <si>
+    <t>01.05.202616</t>
+  </si>
+  <si>
+    <t>01.05.202617</t>
+  </si>
+  <si>
+    <t>01.05.202618</t>
+  </si>
+  <si>
+    <t>01.05.202619</t>
+  </si>
+  <si>
+    <t>01.05.202620</t>
+  </si>
+  <si>
+    <t>01.05.202621</t>
+  </si>
+  <si>
+    <t>01.05.202622</t>
+  </si>
+  <si>
+    <t>01.05.202623</t>
+  </si>
+  <si>
+    <t>01.05.202624</t>
+  </si>
+  <si>
+    <t>01.05.202625</t>
+  </si>
+  <si>
+    <t>01.05.202626</t>
+  </si>
+  <si>
+    <t>01.05.202627</t>
+  </si>
+  <si>
+    <t>01.05.202628</t>
+  </si>
+  <si>
+    <t>01.05.202629</t>
+  </si>
+  <si>
+    <t>01.05.202630</t>
+  </si>
+  <si>
+    <t>01.05.202631</t>
+  </si>
+  <si>
+    <t>01.05.202632</t>
+  </si>
+  <si>
+    <t>01.05.202633</t>
+  </si>
+  <si>
+    <t>01.05.202634</t>
+  </si>
+  <si>
+    <t>01.05.202635</t>
+  </si>
+  <si>
+    <t>01.05.202636</t>
+  </si>
+  <si>
+    <t>01.05.202637</t>
+  </si>
+  <si>
+    <t>01.05.202638</t>
+  </si>
+  <si>
+    <t>01.05.202639</t>
+  </si>
+  <si>
+    <t>01.05.202640</t>
+  </si>
+  <si>
+    <t>01.05.202641</t>
+  </si>
+  <si>
+    <t>01.05.202642</t>
+  </si>
+  <si>
+    <t>01.05.202643</t>
+  </si>
+  <si>
+    <t>01.05.202644</t>
+  </si>
+  <si>
+    <t>01.05.202645</t>
+  </si>
+  <si>
+    <t>01.05.202646</t>
+  </si>
+  <si>
+    <t>01.05.202647</t>
+  </si>
+  <si>
+    <t>01.05.202648</t>
+  </si>
+  <si>
+    <t>01.05.202649</t>
+  </si>
+  <si>
+    <t>01.05.202650</t>
+  </si>
+  <si>
+    <t>01.05.202651</t>
+  </si>
+  <si>
+    <t>01.05.202652</t>
+  </si>
+  <si>
+    <t>01.05.202653</t>
+  </si>
+  <si>
+    <t>01.05.202654</t>
+  </si>
+  <si>
+    <t>01.05.202655</t>
+  </si>
+  <si>
+    <t>01.05.202656</t>
+  </si>
+  <si>
+    <t>01.05.202657</t>
+  </si>
+  <si>
+    <t>01.05.202658</t>
+  </si>
+  <si>
+    <t>01.05.202659</t>
+  </si>
+  <si>
+    <t>01.05.202660</t>
+  </si>
+  <si>
+    <t>01.05.202661</t>
+  </si>
+  <si>
+    <t>01.05.202662</t>
+  </si>
+  <si>
+    <t>01.05.202663</t>
+  </si>
+  <si>
+    <t>01.05.202664</t>
+  </si>
+  <si>
+    <t>01.05.202665</t>
+  </si>
+  <si>
+    <t>01.05.202666</t>
+  </si>
+  <si>
+    <t>01.05.202667</t>
+  </si>
+  <si>
+    <t>01.05.202668</t>
+  </si>
+  <si>
+    <t>01.05.202669</t>
+  </si>
+  <si>
+    <t>01.05.202670</t>
+  </si>
+  <si>
+    <t>01.05.202671</t>
+  </si>
+  <si>
+    <t>01.05.202672</t>
+  </si>
+  <si>
+    <t>01.05.202673</t>
+  </si>
+  <si>
+    <t>01.05.202674</t>
+  </si>
+  <si>
+    <t>01.05.202675</t>
+  </si>
+  <si>
+    <t>01.05.202676</t>
+  </si>
+  <si>
+    <t>01.05.202677</t>
+  </si>
+  <si>
+    <t>01.05.202678</t>
+  </si>
+  <si>
+    <t>01.05.202679</t>
+  </si>
+  <si>
+    <t>01.05.202680</t>
+  </si>
+  <si>
+    <t>01.05.202681</t>
+  </si>
+  <si>
+    <t>01.05.202682</t>
+  </si>
+  <si>
+    <t>01.05.202683</t>
+  </si>
+  <si>
+    <t>01.05.202684</t>
+  </si>
+  <si>
+    <t>01.05.202685</t>
+  </si>
+  <si>
+    <t>01.05.202686</t>
+  </si>
+  <si>
+    <t>01.05.202687</t>
+  </si>
+  <si>
+    <t>01.05.202688</t>
+  </si>
+  <si>
+    <t>01.05.202689</t>
+  </si>
+  <si>
+    <t>01.05.202690</t>
+  </si>
+  <si>
+    <t>01.05.202691</t>
+  </si>
+  <si>
+    <t>01.05.202692</t>
+  </si>
+  <si>
+    <t>01.05.202693</t>
+  </si>
+  <si>
+    <t>02.05.202695</t>
+  </si>
+  <si>
+    <t>02.05.202696</t>
+  </si>
+  <si>
+    <t>02.05.20261</t>
+  </si>
+  <si>
+    <t>02.05.20262</t>
+  </si>
+  <si>
+    <t>02.05.20263</t>
+  </si>
+  <si>
+    <t>02.05.20264</t>
+  </si>
+  <si>
+    <t>02.05.20265</t>
+  </si>
+  <si>
+    <t>02.05.20266</t>
+  </si>
+  <si>
+    <t>02.05.20267</t>
+  </si>
+  <si>
+    <t>02.05.20268</t>
+  </si>
+  <si>
+    <t>02.05.20269</t>
+  </si>
+  <si>
+    <t>02.05.202610</t>
+  </si>
+  <si>
+    <t>02.05.202611</t>
+  </si>
+  <si>
+    <t>02.05.202612</t>
+  </si>
+  <si>
+    <t>02.05.202613</t>
+  </si>
+  <si>
+    <t>02.05.202614</t>
+  </si>
+  <si>
+    <t>02.05.202615</t>
+  </si>
+  <si>
+    <t>02.05.202616</t>
+  </si>
+  <si>
+    <t>02.05.202617</t>
+  </si>
+  <si>
+    <t>02.05.202618</t>
+  </si>
+  <si>
+    <t>02.05.202619</t>
+  </si>
+  <si>
+    <t>02.05.202620</t>
+  </si>
+  <si>
+    <t>02.05.202621</t>
+  </si>
+  <si>
+    <t>02.05.202622</t>
+  </si>
+  <si>
+    <t>02.05.202623</t>
+  </si>
+  <si>
+    <t>02.05.202624</t>
+  </si>
+  <si>
+    <t>02.05.202625</t>
+  </si>
+  <si>
+    <t>02.05.202626</t>
+  </si>
+  <si>
+    <t>02.05.202627</t>
+  </si>
+  <si>
+    <t>02.05.202628</t>
+  </si>
+  <si>
+    <t>02.05.202629</t>
+  </si>
+  <si>
+    <t>02.05.202630</t>
+  </si>
+  <si>
+    <t>02.05.202631</t>
+  </si>
+  <si>
+    <t>02.05.202632</t>
+  </si>
+  <si>
+    <t>02.05.202633</t>
+  </si>
+  <si>
+    <t>02.05.202634</t>
+  </si>
+  <si>
+    <t>02.05.202635</t>
+  </si>
+  <si>
+    <t>02.05.202636</t>
+  </si>
+  <si>
+    <t>02.05.202637</t>
+  </si>
+  <si>
+    <t>02.05.202638</t>
+  </si>
+  <si>
+    <t>02.05.202639</t>
+  </si>
+  <si>
+    <t>02.05.202640</t>
+  </si>
+  <si>
+    <t>02.05.202641</t>
+  </si>
+  <si>
+    <t>02.05.202642</t>
+  </si>
+  <si>
+    <t>02.05.202643</t>
+  </si>
+  <si>
+    <t>02.05.202644</t>
+  </si>
+  <si>
+    <t>02.05.202645</t>
+  </si>
+  <si>
+    <t>02.05.202646</t>
+  </si>
+  <si>
+    <t>02.05.202647</t>
+  </si>
+  <si>
+    <t>02.05.202648</t>
+  </si>
+  <si>
+    <t>02.05.202649</t>
+  </si>
+  <si>
+    <t>02.05.202650</t>
+  </si>
+  <si>
+    <t>02.05.202651</t>
+  </si>
+  <si>
+    <t>02.05.202652</t>
+  </si>
+  <si>
+    <t>02.05.202653</t>
+  </si>
+  <si>
+    <t>02.05.202654</t>
+  </si>
+  <si>
+    <t>02.05.202655</t>
+  </si>
+  <si>
+    <t>02.05.202656</t>
+  </si>
+  <si>
+    <t>02.05.202657</t>
+  </si>
+  <si>
+    <t>02.05.202658</t>
+  </si>
+  <si>
+    <t>02.05.202659</t>
+  </si>
+  <si>
+    <t>02.05.202660</t>
+  </si>
+  <si>
+    <t>02.05.202661</t>
+  </si>
+  <si>
+    <t>02.05.202662</t>
+  </si>
+  <si>
+    <t>02.05.202663</t>
+  </si>
+  <si>
+    <t>02.05.202664</t>
+  </si>
+  <si>
+    <t>02.05.202665</t>
+  </si>
+  <si>
+    <t>02.05.202666</t>
+  </si>
+  <si>
+    <t>02.05.202667</t>
+  </si>
+  <si>
+    <t>02.05.202668</t>
+  </si>
+  <si>
+    <t>02.05.202669</t>
+  </si>
+  <si>
+    <t>02.05.202670</t>
+  </si>
+  <si>
+    <t>02.05.202671</t>
+  </si>
+  <si>
+    <t>02.05.202672</t>
+  </si>
+  <si>
+    <t>02.05.202673</t>
+  </si>
+  <si>
+    <t>02.05.202674</t>
+  </si>
+  <si>
+    <t>02.05.202675</t>
+  </si>
+  <si>
+    <t>02.05.202676</t>
+  </si>
+  <si>
+    <t>02.05.202677</t>
+  </si>
+  <si>
+    <t>02.05.202678</t>
+  </si>
+  <si>
+    <t>02.05.202679</t>
+  </si>
+  <si>
+    <t>02.05.202680</t>
+  </si>
+  <si>
+    <t>02.05.202681</t>
+  </si>
+  <si>
+    <t>02.05.202682</t>
+  </si>
+  <si>
+    <t>02.05.202683</t>
+  </si>
+  <si>
+    <t>02.05.202684</t>
+  </si>
+  <si>
+    <t>02.05.202685</t>
+  </si>
+  <si>
+    <t>02.05.202686</t>
+  </si>
+  <si>
+    <t>02.05.202687</t>
+  </si>
+  <si>
+    <t>02.05.202688</t>
+  </si>
+  <si>
+    <t>02.05.202689</t>
+  </si>
+  <si>
+    <t>02.05.202690</t>
+  </si>
+  <si>
+    <t>02.05.202691</t>
+  </si>
+  <si>
+    <t>02.05.202692</t>
+  </si>
+  <si>
+    <t>02.05.202693</t>
+  </si>
+  <si>
+    <t>02.05.202694</t>
+  </si>
+  <si>
+    <t>03.05.202696</t>
+  </si>
+  <si>
+    <t>03.05.20261</t>
+  </si>
+  <si>
+    <t>03.05.20262</t>
+  </si>
+  <si>
+    <t>03.05.20263</t>
+  </si>
+  <si>
+    <t>03.05.20264</t>
+  </si>
+  <si>
+    <t>03.05.20265</t>
+  </si>
+  <si>
+    <t>03.05.20266</t>
+  </si>
+  <si>
+    <t>03.05.20267</t>
+  </si>
+  <si>
+    <t>03.05.20268</t>
+  </si>
+  <si>
+    <t>03.05.20269</t>
+  </si>
+  <si>
+    <t>03.05.202610</t>
+  </si>
+  <si>
+    <t>03.05.202611</t>
+  </si>
+  <si>
+    <t>03.05.202612</t>
+  </si>
+  <si>
+    <t>03.05.202613</t>
+  </si>
+  <si>
+    <t>03.05.202614</t>
+  </si>
+  <si>
+    <t>03.05.202615</t>
+  </si>
+  <si>
+    <t>03.05.202616</t>
+  </si>
+  <si>
+    <t>03.05.202617</t>
+  </si>
+  <si>
+    <t>03.05.202618</t>
+  </si>
+  <si>
+    <t>03.05.202619</t>
+  </si>
+  <si>
+    <t>03.05.202620</t>
+  </si>
+  <si>
+    <t>03.05.202621</t>
+  </si>
+  <si>
+    <t>03.05.202622</t>
+  </si>
+  <si>
+    <t>03.05.202623</t>
+  </si>
+  <si>
+    <t>03.05.202624</t>
+  </si>
+  <si>
+    <t>03.05.202625</t>
+  </si>
+  <si>
+    <t>03.05.202626</t>
+  </si>
+  <si>
+    <t>03.05.202627</t>
+  </si>
+  <si>
+    <t>03.05.202628</t>
+  </si>
+  <si>
+    <t>03.05.202629</t>
+  </si>
+  <si>
+    <t>03.05.202630</t>
+  </si>
+  <si>
+    <t>03.05.202631</t>
+  </si>
+  <si>
+    <t>03.05.202632</t>
+  </si>
+  <si>
+    <t>03.05.202633</t>
+  </si>
+  <si>
+    <t>03.05.202634</t>
+  </si>
+  <si>
+    <t>03.05.202635</t>
+  </si>
+  <si>
+    <t>03.05.202636</t>
+  </si>
+  <si>
+    <t>03.05.202637</t>
+  </si>
+  <si>
+    <t>03.05.202638</t>
+  </si>
+  <si>
+    <t>03.05.202639</t>
+  </si>
+  <si>
+    <t>03.05.202640</t>
+  </si>
+  <si>
+    <t>03.05.202641</t>
+  </si>
+  <si>
+    <t>03.05.202642</t>
+  </si>
+  <si>
+    <t>03.05.202643</t>
+  </si>
+  <si>
+    <t>03.05.202644</t>
+  </si>
+  <si>
+    <t>03.05.202645</t>
+  </si>
+  <si>
+    <t>03.05.202646</t>
+  </si>
+  <si>
+    <t>03.05.202647</t>
+  </si>
+  <si>
+    <t>03.05.202648</t>
+  </si>
+  <si>
+    <t>03.05.202649</t>
+  </si>
+  <si>
+    <t>03.05.202650</t>
+  </si>
+  <si>
+    <t>03.05.202651</t>
+  </si>
+  <si>
+    <t>03.05.202652</t>
+  </si>
+  <si>
+    <t>03.05.202653</t>
+  </si>
+  <si>
+    <t>03.05.202654</t>
+  </si>
+  <si>
+    <t>03.05.202655</t>
+  </si>
+  <si>
+    <t>03.05.202656</t>
+  </si>
+  <si>
+    <t>03.05.202657</t>
+  </si>
+  <si>
+    <t>03.05.202658</t>
+  </si>
+  <si>
+    <t>03.05.202659</t>
+  </si>
+  <si>
+    <t>03.05.202660</t>
+  </si>
+  <si>
+    <t>03.05.202661</t>
+  </si>
+  <si>
+    <t>03.05.202662</t>
+  </si>
+  <si>
+    <t>03.05.202663</t>
+  </si>
+  <si>
+    <t>03.05.202664</t>
+  </si>
+  <si>
+    <t>03.05.202665</t>
+  </si>
+  <si>
+    <t>03.05.202666</t>
+  </si>
+  <si>
+    <t>03.05.202667</t>
+  </si>
+  <si>
+    <t>03.05.202668</t>
+  </si>
+  <si>
+    <t>03.05.202669</t>
+  </si>
+  <si>
+    <t>03.05.202670</t>
+  </si>
+  <si>
+    <t>03.05.202671</t>
+  </si>
+  <si>
+    <t>03.05.202672</t>
+  </si>
+  <si>
+    <t>03.05.202673</t>
+  </si>
+  <si>
+    <t>03.05.202674</t>
+  </si>
+  <si>
+    <t>03.05.202675</t>
+  </si>
+  <si>
+    <t>03.05.202676</t>
+  </si>
+  <si>
+    <t>03.05.202677</t>
+  </si>
+  <si>
+    <t>03.05.202678</t>
+  </si>
+  <si>
+    <t>03.05.202679</t>
+  </si>
+  <si>
+    <t>03.05.202680</t>
+  </si>
+  <si>
+    <t>03.05.202681</t>
+  </si>
+  <si>
+    <t>03.05.202682</t>
+  </si>
+  <si>
+    <t>03.05.202683</t>
+  </si>
+  <si>
+    <t>03.05.202684</t>
+  </si>
+  <si>
+    <t>03.05.202685</t>
+  </si>
+  <si>
+    <t>03.05.202686</t>
+  </si>
+  <si>
+    <t>03.05.202687</t>
+  </si>
+  <si>
+    <t>03.05.202688</t>
+  </si>
+  <si>
+    <t>03.05.202689</t>
+  </si>
+  <si>
+    <t>03.05.202690</t>
+  </si>
+  <si>
+    <t>03.05.202691</t>
+  </si>
+  <si>
+    <t>03.05.202692</t>
+  </si>
+  <si>
+    <t>03.05.202693</t>
+  </si>
+  <si>
+    <t>03.05.202694</t>
+  </si>
+  <si>
+    <t>03.05.202695</t>
+  </si>
+  <si>
+    <t>04.05.20261</t>
+  </si>
+  <si>
+    <t>04.05.20262</t>
+  </si>
+  <si>
+    <t>04.05.20263</t>
+  </si>
+  <si>
+    <t>04.05.20264</t>
+  </si>
+  <si>
+    <t>04.05.20265</t>
+  </si>
+  <si>
+    <t>04.05.20266</t>
+  </si>
+  <si>
+    <t>04.05.20267</t>
+  </si>
+  <si>
+    <t>04.05.20268</t>
+  </si>
+  <si>
+    <t>04.05.20269</t>
+  </si>
+  <si>
+    <t>04.05.202610</t>
+  </si>
+  <si>
+    <t>04.05.202611</t>
+  </si>
+  <si>
+    <t>04.05.202612</t>
+  </si>
+  <si>
+    <t>04.05.202613</t>
+  </si>
+  <si>
+    <t>04.05.202614</t>
+  </si>
+  <si>
+    <t>04.05.202615</t>
+  </si>
+  <si>
+    <t>04.05.202616</t>
+  </si>
+  <si>
+    <t>04.05.202617</t>
+  </si>
+  <si>
+    <t>04.05.202618</t>
+  </si>
+  <si>
+    <t>04.05.202619</t>
+  </si>
+  <si>
+    <t>04.05.202620</t>
+  </si>
+  <si>
+    <t>04.05.202621</t>
+  </si>
+  <si>
+    <t>04.05.202622</t>
+  </si>
+  <si>
+    <t>04.05.202623</t>
+  </si>
+  <si>
+    <t>04.05.202624</t>
+  </si>
+  <si>
+    <t>04.05.202625</t>
+  </si>
+  <si>
+    <t>04.05.202626</t>
+  </si>
+  <si>
+    <t>04.05.202627</t>
+  </si>
+  <si>
+    <t>04.05.202628</t>
+  </si>
+  <si>
+    <t>04.05.202629</t>
+  </si>
+  <si>
+    <t>04.05.202630</t>
+  </si>
+  <si>
+    <t>04.05.202631</t>
+  </si>
+  <si>
+    <t>04.05.202632</t>
+  </si>
+  <si>
+    <t>04.05.202633</t>
+  </si>
+  <si>
+    <t>04.05.202634</t>
+  </si>
+  <si>
+    <t>04.05.202635</t>
+  </si>
+  <si>
+    <t>04.05.202636</t>
+  </si>
+  <si>
+    <t>04.05.202637</t>
+  </si>
+  <si>
+    <t>04.05.202638</t>
+  </si>
+  <si>
+    <t>04.05.202639</t>
+  </si>
+  <si>
+    <t>04.05.202640</t>
+  </si>
+  <si>
+    <t>04.05.202641</t>
+  </si>
+  <si>
+    <t>04.05.202642</t>
+  </si>
+  <si>
+    <t>04.05.202643</t>
+  </si>
+  <si>
+    <t>04.05.202644</t>
+  </si>
+  <si>
+    <t>04.05.202645</t>
+  </si>
+  <si>
+    <t>04.05.202646</t>
+  </si>
+  <si>
+    <t>04.05.202647</t>
+  </si>
+  <si>
+    <t>04.05.202648</t>
+  </si>
+  <si>
+    <t>04.05.202649</t>
+  </si>
+  <si>
+    <t>04.05.202650</t>
+  </si>
+  <si>
+    <t>04.05.202651</t>
+  </si>
+  <si>
+    <t>04.05.202652</t>
+  </si>
+  <si>
+    <t>04.05.202653</t>
+  </si>
+  <si>
+    <t>04.05.202654</t>
+  </si>
+  <si>
+    <t>04.05.202655</t>
+  </si>
+  <si>
+    <t>04.05.202656</t>
+  </si>
+  <si>
+    <t>04.05.202657</t>
+  </si>
+  <si>
+    <t>04.05.202658</t>
+  </si>
+  <si>
+    <t>04.05.202659</t>
+  </si>
+  <si>
+    <t>04.05.202660</t>
+  </si>
+  <si>
+    <t>04.05.202661</t>
+  </si>
+  <si>
+    <t>04.05.202662</t>
+  </si>
+  <si>
+    <t>04.05.202663</t>
+  </si>
+  <si>
+    <t>04.05.202664</t>
+  </si>
+  <si>
+    <t>04.05.202665</t>
+  </si>
+  <si>
+    <t>04.05.202666</t>
+  </si>
+  <si>
+    <t>04.05.202667</t>
+  </si>
+  <si>
+    <t>04.05.202668</t>
+  </si>
+  <si>
+    <t>04.05.202669</t>
+  </si>
+  <si>
+    <t>04.05.202670</t>
+  </si>
+  <si>
+    <t>04.05.202671</t>
+  </si>
+  <si>
+    <t>04.05.202672</t>
+  </si>
+  <si>
+    <t>04.05.202673</t>
+  </si>
+  <si>
+    <t>04.05.202674</t>
+  </si>
+  <si>
+    <t>04.05.202675</t>
+  </si>
+  <si>
+    <t>04.05.202676</t>
+  </si>
+  <si>
+    <t>04.05.202677</t>
+  </si>
+  <si>
+    <t>04.05.202678</t>
+  </si>
+  <si>
+    <t>04.05.202679</t>
+  </si>
+  <si>
+    <t>04.05.202680</t>
+  </si>
+  <si>
+    <t>04.05.202681</t>
+  </si>
+  <si>
+    <t>04.05.202682</t>
+  </si>
+  <si>
+    <t>04.05.202683</t>
+  </si>
+  <si>
+    <t>04.05.202684</t>
+  </si>
+  <si>
+    <t>04.05.202685</t>
+  </si>
+  <si>
+    <t>04.05.202686</t>
+  </si>
+  <si>
+    <t>04.05.202687</t>
+  </si>
+  <si>
+    <t>04.05.202688</t>
+  </si>
+  <si>
+    <t>04.05.202689</t>
+  </si>
+  <si>
+    <t>04.05.202690</t>
+  </si>
+  <si>
+    <t>04.05.202691</t>
+  </si>
+  <si>
+    <t>04.05.202692</t>
+  </si>
+  <si>
+    <t>04.05.202693</t>
+  </si>
+  <si>
+    <t>04.05.202694</t>
+  </si>
+  <si>
+    <t>04.05.202695</t>
+  </si>
+  <si>
+    <t>04.05.202696</t>
+  </si>
+  <si>
+    <t>05.05.20262</t>
+  </si>
+  <si>
+    <t>05.05.20263</t>
+  </si>
+  <si>
+    <t>05.05.20264</t>
+  </si>
+  <si>
+    <t>05.05.20265</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E292"/>
+  <dimension ref="A1:E486"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1279,7 +1855,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46140.03611111111</v>
+        <v>46142.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1296,7 +1872,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46140.04652777778</v>
+        <v>46142.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1313,7 +1889,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46140.05694444444</v>
+        <v>46142.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1330,7 +1906,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46140.06736111111</v>
+        <v>46142.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1347,7 +1923,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46140.07777777778</v>
+        <v>46142.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1364,7 +1940,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46140.08819444444</v>
+        <v>46142.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1381,7 +1957,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46140.09861111111</v>
+        <v>46142.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1398,7 +1974,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46140.10902777778</v>
+        <v>46142.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1415,7 +1991,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46140.11944444444</v>
+        <v>46142.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1432,7 +2008,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46140.12986111111</v>
+        <v>46142.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1449,7 +2025,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46140.14027777778</v>
+        <v>46142.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1466,7 +2042,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46140.15069444444</v>
+        <v>46142.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1483,7 +2059,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46140.16111111111</v>
+        <v>46142.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1500,7 +2076,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46140.17152777778</v>
+        <v>46142.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1517,7 +2093,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46140.18194444444</v>
+        <v>46142.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1534,7 +2110,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46140.19236111111</v>
+        <v>46142.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1551,7 +2127,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46140.20277777778</v>
+        <v>46142.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1568,7 +2144,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46140.21319444444</v>
+        <v>46142.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1585,7 +2161,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46140.22361111111</v>
+        <v>46142.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1602,7 +2178,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46140.23402777778</v>
+        <v>46142.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1619,7 +2195,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46140.24444444444</v>
+        <v>46142.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1636,7 +2212,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46140.25486111111</v>
+        <v>46142.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1653,7 +2229,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46140.26527777778</v>
+        <v>46142.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1670,7 +2246,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46140.27569444444</v>
+        <v>46142.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1687,7 +2263,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46140.28611111111</v>
+        <v>46142.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1704,7 +2280,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46140.29652777778</v>
+        <v>46142.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1721,7 +2297,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46140.30694444444</v>
+        <v>46142.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1738,7 +2314,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46140.31736111111</v>
+        <v>46142.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1755,7 +2331,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46140.32777777778</v>
+        <v>46142.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1772,7 +2348,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46140.33819444444</v>
+        <v>46142.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1789,7 +2365,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46140.34861111111</v>
+        <v>46142.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1806,7 +2382,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46140.35902777778</v>
+        <v>46142.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1823,7 +2399,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46140.36944444444</v>
+        <v>46142.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1840,7 +2416,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46140.37986111111</v>
+        <v>46142.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1857,7 +2433,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46140.39027777778</v>
+        <v>46142.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1874,7 +2450,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46140.40069444444</v>
+        <v>46142.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1891,7 +2467,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46140.41111111111</v>
+        <v>46142.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1908,7 +2484,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46140.42152777778</v>
+        <v>46142.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1925,7 +2501,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46140.43194444444</v>
+        <v>46142.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1942,7 +2518,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46140.44236111111</v>
+        <v>46142.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1959,7 +2535,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46140.45277777778</v>
+        <v>46142.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1976,7 +2552,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46140.46319444444</v>
+        <v>46142.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1993,7 +2569,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46140.47361111111</v>
+        <v>46142.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -2010,7 +2586,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46140.48402777778</v>
+        <v>46142.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -2027,7 +2603,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46140.49444444444</v>
+        <v>46142.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2044,7 +2620,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46140.50486111111</v>
+        <v>46142.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -2061,7 +2637,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46140.51527777778</v>
+        <v>46142.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2078,7 +2654,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46140.52569444444</v>
+        <v>46142.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2095,7 +2671,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46140.53611111111</v>
+        <v>46142.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -2112,7 +2688,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46140.54652777778</v>
+        <v>46142.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -2129,7 +2705,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46140.55694444444</v>
+        <v>46142.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -2146,7 +2722,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46140.56736111111</v>
+        <v>46142.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -2163,7 +2739,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46140.57777777778</v>
+        <v>46142.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -2180,7 +2756,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46140.58819444444</v>
+        <v>46142.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -2197,7 +2773,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46140.59861111111</v>
+        <v>46142.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -2214,7 +2790,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46140.60902777778</v>
+        <v>46142.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -2231,7 +2807,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46140.61944444444</v>
+        <v>46142.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -2248,7 +2824,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46140.62986111111</v>
+        <v>46142.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -2265,7 +2841,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46140.64027777778</v>
+        <v>46142.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -2282,7 +2858,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46140.65069444444</v>
+        <v>46142.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2299,7 +2875,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46140.66111111111</v>
+        <v>46142.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2316,7 +2892,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46140.67152777778</v>
+        <v>46142.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2333,7 +2909,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46140.68194444444</v>
+        <v>46142.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2350,7 +2926,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46140.69236111111</v>
+        <v>46142.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2367,7 +2943,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46140.70277777778</v>
+        <v>46142.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2384,7 +2960,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46140.71319444444</v>
+        <v>46142.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2401,7 +2977,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46140.72361111111</v>
+        <v>46142.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2418,7 +2994,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46140.73402777778</v>
+        <v>46142.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2435,7 +3011,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46140.74444444444</v>
+        <v>46142.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2452,7 +3028,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46140.75486111111</v>
+        <v>46142.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2469,7 +3045,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46140.76527777778</v>
+        <v>46142.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2486,7 +3062,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46140.77569444444</v>
+        <v>46142.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2503,7 +3079,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46140.78611111111</v>
+        <v>46142.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2520,7 +3096,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46140.79652777778</v>
+        <v>46142.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2537,7 +3113,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46140.80694444444</v>
+        <v>46142.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2554,7 +3130,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46140.81736111111</v>
+        <v>46142.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2571,7 +3147,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46140.82777777778</v>
+        <v>46142.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2588,7 +3164,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46140.83819444444</v>
+        <v>46142.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2605,7 +3181,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46140.84861111111</v>
+        <v>46142.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2622,7 +3198,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46140.85902777778</v>
+        <v>46142.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2639,7 +3215,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46140.86944444444</v>
+        <v>46142.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2656,7 +3232,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46140.87986111111</v>
+        <v>46142.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2673,7 +3249,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46140.89027777778</v>
+        <v>46142.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2690,7 +3266,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46140.90069444444</v>
+        <v>46142.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2707,7 +3283,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46140.91111111111</v>
+        <v>46142.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2724,7 +3300,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46140.92152777778</v>
+        <v>46142.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2741,7 +3317,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46140.93194444444</v>
+        <v>46142.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2758,7 +3334,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46140.94236111111</v>
+        <v>46142.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2775,7 +3351,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46140.95277777778</v>
+        <v>46142.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2792,7 +3368,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46140.96319444444</v>
+        <v>46142.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2809,7 +3385,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46140.97361111111</v>
+        <v>46142.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2826,7 +3402,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46140.98402777778</v>
+        <v>46142.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2843,7 +3419,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46140.99444444444</v>
+        <v>46142.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2860,7 +3436,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46141.00486111111</v>
+        <v>46143.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2877,7 +3453,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46141.01527777778</v>
+        <v>46143.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2894,7 +3470,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46141.02569444444</v>
+        <v>46143.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2911,7 +3487,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46141.03611111111</v>
+        <v>46143.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2928,7 +3504,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46141.03611111111</v>
+        <v>46143.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2945,7 +3521,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46141.04652777778</v>
+        <v>46143.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2962,7 +3538,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46141.05694444444</v>
+        <v>46143.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2979,7 +3555,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46141.06736111111</v>
+        <v>46143.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2996,7 +3572,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46141.07777777778</v>
+        <v>46143.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3013,7 +3589,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46141.08819444444</v>
+        <v>46143.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3030,7 +3606,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46141.09861111111</v>
+        <v>46143.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3047,7 +3623,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46141.10902777778</v>
+        <v>46143.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3064,7 +3640,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46141.11944444444</v>
+        <v>46143.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3081,7 +3657,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46141.12986111111</v>
+        <v>46143.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -3098,7 +3674,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46141.14027777778</v>
+        <v>46143.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3115,7 +3691,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46141.15069444444</v>
+        <v>46143.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3132,7 +3708,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46141.16111111111</v>
+        <v>46143.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3149,7 +3725,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46141.17152777778</v>
+        <v>46143.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3166,7 +3742,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46141.18194444444</v>
+        <v>46143.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3183,7 +3759,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46141.19236111111</v>
+        <v>46143.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3200,7 +3776,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46141.20277777778</v>
+        <v>46143.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3217,7 +3793,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46141.21319444444</v>
+        <v>46143.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3234,7 +3810,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46141.22361111111</v>
+        <v>46143.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3251,7 +3827,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46141.23402777778</v>
+        <v>46143.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3268,7 +3844,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46141.24444444444</v>
+        <v>46143.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3285,7 +3861,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46141.25486111111</v>
+        <v>46143.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3302,7 +3878,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46141.26527777778</v>
+        <v>46143.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3319,7 +3895,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46141.27569444444</v>
+        <v>46143.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3336,7 +3912,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46141.28611111111</v>
+        <v>46143.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3353,7 +3929,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46141.29652777778</v>
+        <v>46143.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3370,7 +3946,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46141.30694444444</v>
+        <v>46143.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3387,7 +3963,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46141.31736111111</v>
+        <v>46143.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3404,7 +3980,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46141.32777777778</v>
+        <v>46143.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3421,7 +3997,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46141.33819444444</v>
+        <v>46143.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3438,7 +4014,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46141.34861111111</v>
+        <v>46143.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3455,7 +4031,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46141.35902777778</v>
+        <v>46143.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3472,7 +4048,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46141.36944444444</v>
+        <v>46143.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3489,7 +4065,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46141.37986111111</v>
+        <v>46143.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3506,7 +4082,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46141.39027777778</v>
+        <v>46143.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3523,7 +4099,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46141.40069444444</v>
+        <v>46143.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3540,7 +4116,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46141.41111111111</v>
+        <v>46143.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3557,7 +4133,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46141.42152777778</v>
+        <v>46143.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3574,7 +4150,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46141.43194444444</v>
+        <v>46143.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3591,7 +4167,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46141.44236111111</v>
+        <v>46143.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3608,7 +4184,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46141.45277777778</v>
+        <v>46143.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3625,7 +4201,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46141.46319444444</v>
+        <v>46143.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3642,7 +4218,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46141.47361111111</v>
+        <v>46143.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3659,7 +4235,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46141.48402777778</v>
+        <v>46143.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3676,7 +4252,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46141.49444444444</v>
+        <v>46143.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3693,7 +4269,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46141.50486111111</v>
+        <v>46143.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3710,7 +4286,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46141.51527777778</v>
+        <v>46143.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3727,7 +4303,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46141.52569444444</v>
+        <v>46143.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3744,7 +4320,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46141.53611111111</v>
+        <v>46143.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3761,7 +4337,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46141.54652777778</v>
+        <v>46143.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3778,7 +4354,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46141.55694444444</v>
+        <v>46143.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3795,7 +4371,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46141.56736111111</v>
+        <v>46143.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3812,7 +4388,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46141.57777777778</v>
+        <v>46143.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3829,7 +4405,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46141.58819444444</v>
+        <v>46143.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3846,7 +4422,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46141.59861111111</v>
+        <v>46143.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3863,7 +4439,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46141.60902777778</v>
+        <v>46143.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3880,7 +4456,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46141.61944444444</v>
+        <v>46143.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3897,7 +4473,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46141.62986111111</v>
+        <v>46143.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3914,7 +4490,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46141.64027777778</v>
+        <v>46143.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3931,7 +4507,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46141.65069444444</v>
+        <v>46143.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3948,7 +4524,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46141.66111111111</v>
+        <v>46143.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3965,7 +4541,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46141.67152777778</v>
+        <v>46143.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3982,7 +4558,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46141.68194444444</v>
+        <v>46143.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3999,7 +4575,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46141.69236111111</v>
+        <v>46143.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4016,7 +4592,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46141.70277777778</v>
+        <v>46143.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4033,7 +4609,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46141.71319444444</v>
+        <v>46143.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4050,7 +4626,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46141.72361111111</v>
+        <v>46143.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -4067,7 +4643,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46141.73402777778</v>
+        <v>46143.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -4084,7 +4660,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46141.74444444444</v>
+        <v>46143.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4101,7 +4677,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46141.75486111111</v>
+        <v>46143.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4118,7 +4694,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46141.76527777778</v>
+        <v>46143.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -4135,7 +4711,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46141.77569444444</v>
+        <v>46143.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4152,7 +4728,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46141.78611111111</v>
+        <v>46143.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -4169,7 +4745,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46141.79652777778</v>
+        <v>46143.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4186,7 +4762,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46141.80694444444</v>
+        <v>46143.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -4203,7 +4779,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46141.81736111111</v>
+        <v>46143.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4220,7 +4796,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46141.82777777778</v>
+        <v>46143.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -4237,7 +4813,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46141.83819444444</v>
+        <v>46143.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4254,7 +4830,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46141.84861111111</v>
+        <v>46143.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4271,7 +4847,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46141.85902777778</v>
+        <v>46143.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4288,7 +4864,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46141.86944444444</v>
+        <v>46143.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4305,7 +4881,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46141.87986111111</v>
+        <v>46143.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4322,7 +4898,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46141.89027777778</v>
+        <v>46143.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4339,7 +4915,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46141.90069444444</v>
+        <v>46143.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4356,7 +4932,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46141.91111111111</v>
+        <v>46143.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4373,7 +4949,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46141.92152777778</v>
+        <v>46143.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4390,7 +4966,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46141.93194444444</v>
+        <v>46143.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4407,7 +4983,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46141.94236111111</v>
+        <v>46143.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4424,7 +5000,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46141.95277777778</v>
+        <v>46143.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4441,7 +5017,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46141.96319444444</v>
+        <v>46143.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4458,7 +5034,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46141.97361111111</v>
+        <v>46143.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4475,7 +5051,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46141.98402777778</v>
+        <v>46143.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4492,7 +5068,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46141.99444444444</v>
+        <v>46143.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4509,7 +5085,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46142.00486111111</v>
+        <v>46144.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4526,7 +5102,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46142.01527777778</v>
+        <v>46144.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4543,7 +5119,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46142.02569444444</v>
+        <v>46144.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4560,7 +5136,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46142.03611111111</v>
+        <v>46144.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -4577,7 +5153,7 @@
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2">
-        <v>46142.03611111111</v>
+        <v>46144.03611111111</v>
       </c>
       <c r="B196">
         <v>0</v>
@@ -4594,7 +5170,7 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2">
-        <v>46142.04652777778</v>
+        <v>46144.04652777778</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -4611,7 +5187,7 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2">
-        <v>46142.05694444444</v>
+        <v>46144.05694444444</v>
       </c>
       <c r="B198">
         <v>0</v>
@@ -4628,7 +5204,7 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2">
-        <v>46142.06736111111</v>
+        <v>46144.06736111111</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -4645,7 +5221,7 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2">
-        <v>46142.07777777778</v>
+        <v>46144.07777777778</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -4662,7 +5238,7 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2">
-        <v>46142.08819444444</v>
+        <v>46144.08819444444</v>
       </c>
       <c r="B201">
         <v>0</v>
@@ -4679,7 +5255,7 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2">
-        <v>46142.09861111111</v>
+        <v>46144.09861111111</v>
       </c>
       <c r="B202">
         <v>0</v>
@@ -4696,7 +5272,7 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2">
-        <v>46142.10902777778</v>
+        <v>46144.10902777778</v>
       </c>
       <c r="B203">
         <v>0</v>
@@ -4713,7 +5289,7 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2">
-        <v>46142.11944444444</v>
+        <v>46144.11944444444</v>
       </c>
       <c r="B204">
         <v>0</v>
@@ -4730,7 +5306,7 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2">
-        <v>46142.12986111111</v>
+        <v>46144.12986111111</v>
       </c>
       <c r="B205">
         <v>0</v>
@@ -4747,7 +5323,7 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2">
-        <v>46142.14027777778</v>
+        <v>46144.14027777778</v>
       </c>
       <c r="B206">
         <v>0</v>
@@ -4764,7 +5340,7 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2">
-        <v>46142.15069444444</v>
+        <v>46144.15069444444</v>
       </c>
       <c r="B207">
         <v>0</v>
@@ -4781,7 +5357,7 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2">
-        <v>46142.16111111111</v>
+        <v>46144.16111111111</v>
       </c>
       <c r="B208">
         <v>0</v>
@@ -4798,7 +5374,7 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2">
-        <v>46142.17152777778</v>
+        <v>46144.17152777778</v>
       </c>
       <c r="B209">
         <v>0</v>
@@ -4815,7 +5391,7 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2">
-        <v>46142.18194444444</v>
+        <v>46144.18194444444</v>
       </c>
       <c r="B210">
         <v>0</v>
@@ -4832,7 +5408,7 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2">
-        <v>46142.19236111111</v>
+        <v>46144.19236111111</v>
       </c>
       <c r="B211">
         <v>0</v>
@@ -4849,7 +5425,7 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2">
-        <v>46142.20277777778</v>
+        <v>46144.20277777778</v>
       </c>
       <c r="B212">
         <v>0</v>
@@ -4866,7 +5442,7 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2">
-        <v>46142.21319444444</v>
+        <v>46144.21319444444</v>
       </c>
       <c r="B213">
         <v>0</v>
@@ -4883,7 +5459,7 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2">
-        <v>46142.22361111111</v>
+        <v>46144.22361111111</v>
       </c>
       <c r="B214">
         <v>0</v>
@@ -4900,7 +5476,7 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2">
-        <v>46142.23402777778</v>
+        <v>46144.23402777778</v>
       </c>
       <c r="B215">
         <v>0</v>
@@ -4917,7 +5493,7 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2">
-        <v>46142.24444444444</v>
+        <v>46144.24444444444</v>
       </c>
       <c r="B216">
         <v>0</v>
@@ -4934,7 +5510,7 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2">
-        <v>46142.25486111111</v>
+        <v>46144.25486111111</v>
       </c>
       <c r="B217">
         <v>0</v>
@@ -4951,7 +5527,7 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2">
-        <v>46142.26527777778</v>
+        <v>46144.26527777778</v>
       </c>
       <c r="B218">
         <v>0</v>
@@ -4968,7 +5544,7 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2">
-        <v>46142.27569444444</v>
+        <v>46144.27569444444</v>
       </c>
       <c r="B219">
         <v>0</v>
@@ -4985,7 +5561,7 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2">
-        <v>46142.28611111111</v>
+        <v>46144.28611111111</v>
       </c>
       <c r="B220">
         <v>0</v>
@@ -5002,7 +5578,7 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2">
-        <v>46142.29652777778</v>
+        <v>46144.29652777778</v>
       </c>
       <c r="B221">
         <v>0</v>
@@ -5019,7 +5595,7 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2">
-        <v>46142.30694444444</v>
+        <v>46144.30694444444</v>
       </c>
       <c r="B222">
         <v>0</v>
@@ -5036,7 +5612,7 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2">
-        <v>46142.31736111111</v>
+        <v>46144.31736111111</v>
       </c>
       <c r="B223">
         <v>0</v>
@@ -5053,7 +5629,7 @@
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2">
-        <v>46142.32777777778</v>
+        <v>46144.32777777778</v>
       </c>
       <c r="B224">
         <v>0</v>
@@ -5070,7 +5646,7 @@
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="2">
-        <v>46142.33819444444</v>
+        <v>46144.33819444444</v>
       </c>
       <c r="B225">
         <v>0</v>
@@ -5087,7 +5663,7 @@
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="2">
-        <v>46142.34861111111</v>
+        <v>46144.34861111111</v>
       </c>
       <c r="B226">
         <v>0</v>
@@ -5104,7 +5680,7 @@
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="2">
-        <v>46142.35902777778</v>
+        <v>46144.35902777778</v>
       </c>
       <c r="B227">
         <v>0</v>
@@ -5121,7 +5697,7 @@
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="2">
-        <v>46142.36944444444</v>
+        <v>46144.36944444444</v>
       </c>
       <c r="B228">
         <v>0</v>
@@ -5138,7 +5714,7 @@
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="2">
-        <v>46142.37986111111</v>
+        <v>46144.37986111111</v>
       </c>
       <c r="B229">
         <v>0</v>
@@ -5155,7 +5731,7 @@
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="2">
-        <v>46142.39027777778</v>
+        <v>46144.39027777778</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -5172,7 +5748,7 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="2">
-        <v>46142.40069444444</v>
+        <v>46144.40069444444</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -5189,7 +5765,7 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="2">
-        <v>46142.41111111111</v>
+        <v>46144.41111111111</v>
       </c>
       <c r="B232">
         <v>0</v>
@@ -5206,7 +5782,7 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="2">
-        <v>46142.42152777778</v>
+        <v>46144.42152777778</v>
       </c>
       <c r="B233">
         <v>0</v>
@@ -5223,7 +5799,7 @@
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="2">
-        <v>46142.43194444444</v>
+        <v>46144.43194444444</v>
       </c>
       <c r="B234">
         <v>0</v>
@@ -5240,7 +5816,7 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="2">
-        <v>46142.44236111111</v>
+        <v>46144.44236111111</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -5257,7 +5833,7 @@
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="2">
-        <v>46142.45277777778</v>
+        <v>46144.45277777778</v>
       </c>
       <c r="B236">
         <v>0</v>
@@ -5274,7 +5850,7 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="2">
-        <v>46142.46319444444</v>
+        <v>46144.46319444444</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -5291,7 +5867,7 @@
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="2">
-        <v>46142.47361111111</v>
+        <v>46144.47361111111</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -5308,7 +5884,7 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="2">
-        <v>46142.48402777778</v>
+        <v>46144.48402777778</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -5325,7 +5901,7 @@
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="2">
-        <v>46142.49444444444</v>
+        <v>46144.49444444444</v>
       </c>
       <c r="B240">
         <v>0</v>
@@ -5342,7 +5918,7 @@
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="2">
-        <v>46142.50486111111</v>
+        <v>46144.50486111111</v>
       </c>
       <c r="B241">
         <v>0</v>
@@ -5359,7 +5935,7 @@
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="2">
-        <v>46142.51527777778</v>
+        <v>46144.51527777778</v>
       </c>
       <c r="B242">
         <v>0</v>
@@ -5376,7 +5952,7 @@
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="2">
-        <v>46142.52569444444</v>
+        <v>46144.52569444444</v>
       </c>
       <c r="B243">
         <v>0</v>
@@ -5393,7 +5969,7 @@
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="2">
-        <v>46142.53611111111</v>
+        <v>46144.53611111111</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -5410,7 +5986,7 @@
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="2">
-        <v>46142.54652777778</v>
+        <v>46144.54652777778</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -5427,7 +6003,7 @@
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="2">
-        <v>46142.55694444444</v>
+        <v>46144.55694444444</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -5444,7 +6020,7 @@
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="2">
-        <v>46142.56736111111</v>
+        <v>46144.56736111111</v>
       </c>
       <c r="B247">
         <v>0</v>
@@ -5461,7 +6037,7 @@
     </row>
     <row r="248" spans="1:5">
       <c r="A248" s="2">
-        <v>46142.57777777778</v>
+        <v>46144.57777777778</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -5478,7 +6054,7 @@
     </row>
     <row r="249" spans="1:5">
       <c r="A249" s="2">
-        <v>46142.58819444444</v>
+        <v>46144.58819444444</v>
       </c>
       <c r="B249">
         <v>0</v>
@@ -5495,7 +6071,7 @@
     </row>
     <row r="250" spans="1:5">
       <c r="A250" s="2">
-        <v>46142.59861111111</v>
+        <v>46144.59861111111</v>
       </c>
       <c r="B250">
         <v>0</v>
@@ -5512,7 +6088,7 @@
     </row>
     <row r="251" spans="1:5">
       <c r="A251" s="2">
-        <v>46142.60902777778</v>
+        <v>46144.60902777778</v>
       </c>
       <c r="B251">
         <v>0</v>
@@ -5529,7 +6105,7 @@
     </row>
     <row r="252" spans="1:5">
       <c r="A252" s="2">
-        <v>46142.61944444444</v>
+        <v>46144.61944444444</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -5546,7 +6122,7 @@
     </row>
     <row r="253" spans="1:5">
       <c r="A253" s="2">
-        <v>46142.62986111111</v>
+        <v>46144.62986111111</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -5563,7 +6139,7 @@
     </row>
     <row r="254" spans="1:5">
       <c r="A254" s="2">
-        <v>46142.64027777778</v>
+        <v>46144.64027777778</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -5580,7 +6156,7 @@
     </row>
     <row r="255" spans="1:5">
       <c r="A255" s="2">
-        <v>46142.65069444444</v>
+        <v>46144.65069444444</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -5597,7 +6173,7 @@
     </row>
     <row r="256" spans="1:5">
       <c r="A256" s="2">
-        <v>46142.66111111111</v>
+        <v>46144.66111111111</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -5614,7 +6190,7 @@
     </row>
     <row r="257" spans="1:5">
       <c r="A257" s="2">
-        <v>46142.67152777778</v>
+        <v>46144.67152777778</v>
       </c>
       <c r="B257">
         <v>0</v>
@@ -5631,7 +6207,7 @@
     </row>
     <row r="258" spans="1:5">
       <c r="A258" s="2">
-        <v>46142.68194444444</v>
+        <v>46144.68194444444</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -5648,7 +6224,7 @@
     </row>
     <row r="259" spans="1:5">
       <c r="A259" s="2">
-        <v>46142.69236111111</v>
+        <v>46144.69236111111</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -5665,7 +6241,7 @@
     </row>
     <row r="260" spans="1:5">
       <c r="A260" s="2">
-        <v>46142.70277777778</v>
+        <v>46144.70277777778</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -5682,7 +6258,7 @@
     </row>
     <row r="261" spans="1:5">
       <c r="A261" s="2">
-        <v>46142.71319444444</v>
+        <v>46144.71319444444</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -5699,7 +6275,7 @@
     </row>
     <row r="262" spans="1:5">
       <c r="A262" s="2">
-        <v>46142.72361111111</v>
+        <v>46144.72361111111</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -5716,7 +6292,7 @@
     </row>
     <row r="263" spans="1:5">
       <c r="A263" s="2">
-        <v>46142.73402777778</v>
+        <v>46144.73402777778</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -5733,7 +6309,7 @@
     </row>
     <row r="264" spans="1:5">
       <c r="A264" s="2">
-        <v>46142.74444444444</v>
+        <v>46144.74444444444</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -5750,7 +6326,7 @@
     </row>
     <row r="265" spans="1:5">
       <c r="A265" s="2">
-        <v>46142.75486111111</v>
+        <v>46144.75486111111</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -5767,7 +6343,7 @@
     </row>
     <row r="266" spans="1:5">
       <c r="A266" s="2">
-        <v>46142.76527777778</v>
+        <v>46144.76527777778</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -5784,7 +6360,7 @@
     </row>
     <row r="267" spans="1:5">
       <c r="A267" s="2">
-        <v>46142.77569444444</v>
+        <v>46144.77569444444</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -5801,7 +6377,7 @@
     </row>
     <row r="268" spans="1:5">
       <c r="A268" s="2">
-        <v>46142.78611111111</v>
+        <v>46144.78611111111</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -5818,7 +6394,7 @@
     </row>
     <row r="269" spans="1:5">
       <c r="A269" s="2">
-        <v>46142.79652777778</v>
+        <v>46144.79652777778</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -5835,7 +6411,7 @@
     </row>
     <row r="270" spans="1:5">
       <c r="A270" s="2">
-        <v>46142.80694444444</v>
+        <v>46144.80694444444</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -5852,7 +6428,7 @@
     </row>
     <row r="271" spans="1:5">
       <c r="A271" s="2">
-        <v>46142.81736111111</v>
+        <v>46144.81736111111</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -5869,7 +6445,7 @@
     </row>
     <row r="272" spans="1:5">
       <c r="A272" s="2">
-        <v>46142.82777777778</v>
+        <v>46144.82777777778</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -5886,7 +6462,7 @@
     </row>
     <row r="273" spans="1:5">
       <c r="A273" s="2">
-        <v>46142.83819444444</v>
+        <v>46144.83819444444</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -5903,7 +6479,7 @@
     </row>
     <row r="274" spans="1:5">
       <c r="A274" s="2">
-        <v>46142.84861111111</v>
+        <v>46144.84861111111</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -5920,7 +6496,7 @@
     </row>
     <row r="275" spans="1:5">
       <c r="A275" s="2">
-        <v>46142.85902777778</v>
+        <v>46144.85902777778</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -5937,7 +6513,7 @@
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="2">
-        <v>46142.86944444444</v>
+        <v>46144.86944444444</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -5954,7 +6530,7 @@
     </row>
     <row r="277" spans="1:5">
       <c r="A277" s="2">
-        <v>46142.87986111111</v>
+        <v>46144.87986111111</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -5971,7 +6547,7 @@
     </row>
     <row r="278" spans="1:5">
       <c r="A278" s="2">
-        <v>46142.89027777778</v>
+        <v>46144.89027777778</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -5988,7 +6564,7 @@
     </row>
     <row r="279" spans="1:5">
       <c r="A279" s="2">
-        <v>46142.90069444444</v>
+        <v>46144.90069444444</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -6005,7 +6581,7 @@
     </row>
     <row r="280" spans="1:5">
       <c r="A280" s="2">
-        <v>46142.91111111111</v>
+        <v>46144.91111111111</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -6022,7 +6598,7 @@
     </row>
     <row r="281" spans="1:5">
       <c r="A281" s="2">
-        <v>46142.92152777778</v>
+        <v>46144.92152777778</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -6039,7 +6615,7 @@
     </row>
     <row r="282" spans="1:5">
       <c r="A282" s="2">
-        <v>46142.93194444444</v>
+        <v>46144.93194444444</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -6056,7 +6632,7 @@
     </row>
     <row r="283" spans="1:5">
       <c r="A283" s="2">
-        <v>46142.94236111111</v>
+        <v>46144.94236111111</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -6073,7 +6649,7 @@
     </row>
     <row r="284" spans="1:5">
       <c r="A284" s="2">
-        <v>46142.95277777778</v>
+        <v>46144.95277777778</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -6090,7 +6666,7 @@
     </row>
     <row r="285" spans="1:5">
       <c r="A285" s="2">
-        <v>46142.96319444444</v>
+        <v>46144.96319444444</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -6107,7 +6683,7 @@
     </row>
     <row r="286" spans="1:5">
       <c r="A286" s="2">
-        <v>46142.97361111111</v>
+        <v>46144.97361111111</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -6124,7 +6700,7 @@
     </row>
     <row r="287" spans="1:5">
       <c r="A287" s="2">
-        <v>46142.98402777778</v>
+        <v>46144.98402777778</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -6141,7 +6717,7 @@
     </row>
     <row r="288" spans="1:5">
       <c r="A288" s="2">
-        <v>46142.99444444444</v>
+        <v>46144.99444444444</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -6158,7 +6734,7 @@
     </row>
     <row r="289" spans="1:5">
       <c r="A289" s="2">
-        <v>46143.00486111111</v>
+        <v>46145.00486111111</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -6175,7 +6751,7 @@
     </row>
     <row r="290" spans="1:5">
       <c r="A290" s="2">
-        <v>46143.01527777778</v>
+        <v>46145.01527777778</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -6192,7 +6768,7 @@
     </row>
     <row r="291" spans="1:5">
       <c r="A291" s="2">
-        <v>46143.02569444444</v>
+        <v>46145.02569444444</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -6209,7 +6785,7 @@
     </row>
     <row r="292" spans="1:5">
       <c r="A292" s="2">
-        <v>46143.03611111111</v>
+        <v>46145.03611111111</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -6222,6 +6798,3304 @@
       </c>
       <c r="E292" t="s">
         <v>293</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46145.03611111111</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46145.04652777778</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46145.05694444444</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46145.06736111111</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46145.07777777778</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46145.08819444444</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46145.09861111111</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46145.10902777778</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46145.11944444444</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46145.12986111111</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46145.14027777778</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46145.15069444444</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46145.16111111111</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46145.17152777778</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46145.18194444444</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46145.19236111111</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46145.20277777778</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46145.21319444444</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46145.22361111111</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46145.23402777778</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46145.24444444444</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46145.25486111111</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46145.26527777778</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46145.27569444444</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46145.28611111111</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46145.29652777778</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46145.30694444444</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46145.31736111111</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46145.32777777778</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46145.33819444444</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46145.34861111111</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46145.35902777778</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46145.36944444444</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46145.37986111111</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46145.39027777778</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46145.40069444444</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46145.41111111111</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46145.42152777778</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46145.43194444444</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46145.44236111111</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46145.45277777778</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46145.46319444444</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46145.47361111111</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46145.48402777778</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46145.49444444444</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46145.50486111111</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46145.51527777778</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46145.52569444444</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46145.53611111111</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46145.54652777778</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46145.55694444444</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46145.56736111111</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46145.57777777778</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46145.58819444444</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46145.59861111111</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46145.60902777778</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46145.61944444444</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46145.62986111111</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46145.64027777778</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46145.65069444444</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46145.66111111111</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46145.67152777778</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46145.68194444444</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46145.69236111111</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46145.70277777778</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46145.71319444444</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46145.72361111111</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46145.73402777778</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46145.74444444444</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46145.75486111111</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46145.76527777778</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46145.77569444444</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46145.78611111111</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46145.79652777778</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46145.80694444444</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46145.81736111111</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46145.82777777778</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46145.83819444444</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46145.84861111111</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46145.85902777778</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46145.86944444444</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46145.87986111111</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46145.89027777778</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46145.90069444444</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46145.91111111111</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46145.92152777778</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46145.93194444444</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46145.94236111111</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46145.95277777778</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46145.96319444444</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46145.97361111111</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46145.98402777778</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46145.99444444444</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2">
+        <v>46146.00486111111</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2">
+        <v>46146.01527777778</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2">
+        <v>46146.02569444444</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2">
+        <v>46146.03611111111</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
+      <c r="E389" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5">
+      <c r="A390" s="2">
+        <v>46146.03611111111</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390">
+        <v>5</v>
+      </c>
+      <c r="E390" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5">
+      <c r="A391" s="2">
+        <v>46146.04652777778</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+      <c r="D391">
+        <v>6</v>
+      </c>
+      <c r="E391" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5">
+      <c r="A392" s="2">
+        <v>46146.05694444444</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392">
+        <v>7</v>
+      </c>
+      <c r="E392" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5">
+      <c r="A393" s="2">
+        <v>46146.06736111111</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393">
+        <v>8</v>
+      </c>
+      <c r="E393" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5">
+      <c r="A394" s="2">
+        <v>46146.07777777778</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
+      </c>
+      <c r="D394">
+        <v>9</v>
+      </c>
+      <c r="E394" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5">
+      <c r="A395" s="2">
+        <v>46146.08819444444</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>10</v>
+      </c>
+      <c r="E395" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5">
+      <c r="A396" s="2">
+        <v>46146.09861111111</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396">
+        <v>11</v>
+      </c>
+      <c r="E396" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5">
+      <c r="A397" s="2">
+        <v>46146.10902777778</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397">
+        <v>12</v>
+      </c>
+      <c r="E397" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5">
+      <c r="A398" s="2">
+        <v>46146.11944444444</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398">
+        <v>13</v>
+      </c>
+      <c r="E398" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5">
+      <c r="A399" s="2">
+        <v>46146.12986111111</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399">
+        <v>14</v>
+      </c>
+      <c r="E399" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5">
+      <c r="A400" s="2">
+        <v>46146.14027777778</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+      <c r="D400">
+        <v>15</v>
+      </c>
+      <c r="E400" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
+      <c r="A401" s="2">
+        <v>46146.15069444444</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401">
+        <v>16</v>
+      </c>
+      <c r="E401" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5">
+      <c r="A402" s="2">
+        <v>46146.16111111111</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402">
+        <v>17</v>
+      </c>
+      <c r="E402" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5">
+      <c r="A403" s="2">
+        <v>46146.17152777778</v>
+      </c>
+      <c r="B403">
+        <v>0</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+      <c r="D403">
+        <v>18</v>
+      </c>
+      <c r="E403" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
+      <c r="A404" s="2">
+        <v>46146.18194444444</v>
+      </c>
+      <c r="B404">
+        <v>0</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404">
+        <v>19</v>
+      </c>
+      <c r="E404" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5">
+      <c r="A405" s="2">
+        <v>46146.19236111111</v>
+      </c>
+      <c r="B405">
+        <v>0</v>
+      </c>
+      <c r="C405">
+        <v>0</v>
+      </c>
+      <c r="D405">
+        <v>20</v>
+      </c>
+      <c r="E405" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5">
+      <c r="A406" s="2">
+        <v>46146.20277777778</v>
+      </c>
+      <c r="B406">
+        <v>0</v>
+      </c>
+      <c r="C406">
+        <v>0</v>
+      </c>
+      <c r="D406">
+        <v>21</v>
+      </c>
+      <c r="E406" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5">
+      <c r="A407" s="2">
+        <v>46146.21319444444</v>
+      </c>
+      <c r="B407">
+        <v>0</v>
+      </c>
+      <c r="C407">
+        <v>0</v>
+      </c>
+      <c r="D407">
+        <v>22</v>
+      </c>
+      <c r="E407" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
+      <c r="A408" s="2">
+        <v>46146.22361111111</v>
+      </c>
+      <c r="B408">
+        <v>0</v>
+      </c>
+      <c r="C408">
+        <v>0</v>
+      </c>
+      <c r="D408">
+        <v>23</v>
+      </c>
+      <c r="E408" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5">
+      <c r="A409" s="2">
+        <v>46146.23402777778</v>
+      </c>
+      <c r="B409">
+        <v>0</v>
+      </c>
+      <c r="C409">
+        <v>0</v>
+      </c>
+      <c r="D409">
+        <v>24</v>
+      </c>
+      <c r="E409" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5">
+      <c r="A410" s="2">
+        <v>46146.24444444444</v>
+      </c>
+      <c r="B410">
+        <v>0</v>
+      </c>
+      <c r="C410">
+        <v>0</v>
+      </c>
+      <c r="D410">
+        <v>25</v>
+      </c>
+      <c r="E410" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
+      <c r="A411" s="2">
+        <v>46146.25486111111</v>
+      </c>
+      <c r="B411">
+        <v>0</v>
+      </c>
+      <c r="C411">
+        <v>0</v>
+      </c>
+      <c r="D411">
+        <v>26</v>
+      </c>
+      <c r="E411" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5">
+      <c r="A412" s="2">
+        <v>46146.26527777778</v>
+      </c>
+      <c r="B412">
+        <v>0</v>
+      </c>
+      <c r="C412">
+        <v>0</v>
+      </c>
+      <c r="D412">
+        <v>27</v>
+      </c>
+      <c r="E412" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5">
+      <c r="A413" s="2">
+        <v>46146.27569444444</v>
+      </c>
+      <c r="B413">
+        <v>0</v>
+      </c>
+      <c r="C413">
+        <v>0</v>
+      </c>
+      <c r="D413">
+        <v>28</v>
+      </c>
+      <c r="E413" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5">
+      <c r="A414" s="2">
+        <v>46146.28611111111</v>
+      </c>
+      <c r="B414">
+        <v>0</v>
+      </c>
+      <c r="C414">
+        <v>0</v>
+      </c>
+      <c r="D414">
+        <v>29</v>
+      </c>
+      <c r="E414" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
+      <c r="A415" s="2">
+        <v>46146.29652777778</v>
+      </c>
+      <c r="B415">
+        <v>0</v>
+      </c>
+      <c r="C415">
+        <v>0</v>
+      </c>
+      <c r="D415">
+        <v>30</v>
+      </c>
+      <c r="E415" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5">
+      <c r="A416" s="2">
+        <v>46146.30694444444</v>
+      </c>
+      <c r="B416">
+        <v>0</v>
+      </c>
+      <c r="C416">
+        <v>0</v>
+      </c>
+      <c r="D416">
+        <v>31</v>
+      </c>
+      <c r="E416" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5">
+      <c r="A417" s="2">
+        <v>46146.31736111111</v>
+      </c>
+      <c r="B417">
+        <v>0</v>
+      </c>
+      <c r="C417">
+        <v>0</v>
+      </c>
+      <c r="D417">
+        <v>32</v>
+      </c>
+      <c r="E417" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
+      <c r="A418" s="2">
+        <v>46146.32777777778</v>
+      </c>
+      <c r="B418">
+        <v>0</v>
+      </c>
+      <c r="C418">
+        <v>0</v>
+      </c>
+      <c r="D418">
+        <v>33</v>
+      </c>
+      <c r="E418" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5">
+      <c r="A419" s="2">
+        <v>46146.33819444444</v>
+      </c>
+      <c r="B419">
+        <v>0</v>
+      </c>
+      <c r="C419">
+        <v>0</v>
+      </c>
+      <c r="D419">
+        <v>34</v>
+      </c>
+      <c r="E419" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5">
+      <c r="A420" s="2">
+        <v>46146.34861111111</v>
+      </c>
+      <c r="B420">
+        <v>0</v>
+      </c>
+      <c r="C420">
+        <v>0</v>
+      </c>
+      <c r="D420">
+        <v>35</v>
+      </c>
+      <c r="E420" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5">
+      <c r="A421" s="2">
+        <v>46146.35902777778</v>
+      </c>
+      <c r="B421">
+        <v>0</v>
+      </c>
+      <c r="C421">
+        <v>0</v>
+      </c>
+      <c r="D421">
+        <v>36</v>
+      </c>
+      <c r="E421" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5">
+      <c r="A422" s="2">
+        <v>46146.36944444444</v>
+      </c>
+      <c r="B422">
+        <v>0</v>
+      </c>
+      <c r="C422">
+        <v>0</v>
+      </c>
+      <c r="D422">
+        <v>37</v>
+      </c>
+      <c r="E422" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5">
+      <c r="A423" s="2">
+        <v>46146.37986111111</v>
+      </c>
+      <c r="B423">
+        <v>0</v>
+      </c>
+      <c r="C423">
+        <v>0</v>
+      </c>
+      <c r="D423">
+        <v>38</v>
+      </c>
+      <c r="E423" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5">
+      <c r="A424" s="2">
+        <v>46146.39027777778</v>
+      </c>
+      <c r="B424">
+        <v>0</v>
+      </c>
+      <c r="C424">
+        <v>0</v>
+      </c>
+      <c r="D424">
+        <v>39</v>
+      </c>
+      <c r="E424" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5">
+      <c r="A425" s="2">
+        <v>46146.40069444444</v>
+      </c>
+      <c r="B425">
+        <v>0</v>
+      </c>
+      <c r="C425">
+        <v>0</v>
+      </c>
+      <c r="D425">
+        <v>40</v>
+      </c>
+      <c r="E425" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5">
+      <c r="A426" s="2">
+        <v>46146.41111111111</v>
+      </c>
+      <c r="B426">
+        <v>0</v>
+      </c>
+      <c r="C426">
+        <v>0</v>
+      </c>
+      <c r="D426">
+        <v>41</v>
+      </c>
+      <c r="E426" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5">
+      <c r="A427" s="2">
+        <v>46146.42152777778</v>
+      </c>
+      <c r="B427">
+        <v>0</v>
+      </c>
+      <c r="C427">
+        <v>0</v>
+      </c>
+      <c r="D427">
+        <v>42</v>
+      </c>
+      <c r="E427" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5">
+      <c r="A428" s="2">
+        <v>46146.43194444444</v>
+      </c>
+      <c r="B428">
+        <v>0</v>
+      </c>
+      <c r="C428">
+        <v>0</v>
+      </c>
+      <c r="D428">
+        <v>43</v>
+      </c>
+      <c r="E428" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5">
+      <c r="A429" s="2">
+        <v>46146.44236111111</v>
+      </c>
+      <c r="B429">
+        <v>0</v>
+      </c>
+      <c r="C429">
+        <v>0</v>
+      </c>
+      <c r="D429">
+        <v>44</v>
+      </c>
+      <c r="E429" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5">
+      <c r="A430" s="2">
+        <v>46146.45277777778</v>
+      </c>
+      <c r="B430">
+        <v>0</v>
+      </c>
+      <c r="C430">
+        <v>0</v>
+      </c>
+      <c r="D430">
+        <v>45</v>
+      </c>
+      <c r="E430" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5">
+      <c r="A431" s="2">
+        <v>46146.46319444444</v>
+      </c>
+      <c r="B431">
+        <v>0</v>
+      </c>
+      <c r="C431">
+        <v>0</v>
+      </c>
+      <c r="D431">
+        <v>46</v>
+      </c>
+      <c r="E431" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5">
+      <c r="A432" s="2">
+        <v>46146.47361111111</v>
+      </c>
+      <c r="B432">
+        <v>0</v>
+      </c>
+      <c r="C432">
+        <v>0</v>
+      </c>
+      <c r="D432">
+        <v>47</v>
+      </c>
+      <c r="E432" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5">
+      <c r="A433" s="2">
+        <v>46146.48402777778</v>
+      </c>
+      <c r="B433">
+        <v>0</v>
+      </c>
+      <c r="C433">
+        <v>0</v>
+      </c>
+      <c r="D433">
+        <v>48</v>
+      </c>
+      <c r="E433" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5">
+      <c r="A434" s="2">
+        <v>46146.49444444444</v>
+      </c>
+      <c r="B434">
+        <v>0</v>
+      </c>
+      <c r="C434">
+        <v>0</v>
+      </c>
+      <c r="D434">
+        <v>49</v>
+      </c>
+      <c r="E434" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5">
+      <c r="A435" s="2">
+        <v>46146.50486111111</v>
+      </c>
+      <c r="B435">
+        <v>0</v>
+      </c>
+      <c r="C435">
+        <v>0</v>
+      </c>
+      <c r="D435">
+        <v>50</v>
+      </c>
+      <c r="E435" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5">
+      <c r="A436" s="2">
+        <v>46146.51527777778</v>
+      </c>
+      <c r="B436">
+        <v>0</v>
+      </c>
+      <c r="C436">
+        <v>0</v>
+      </c>
+      <c r="D436">
+        <v>51</v>
+      </c>
+      <c r="E436" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
+      <c r="A437" s="2">
+        <v>46146.52569444444</v>
+      </c>
+      <c r="B437">
+        <v>0</v>
+      </c>
+      <c r="C437">
+        <v>0</v>
+      </c>
+      <c r="D437">
+        <v>52</v>
+      </c>
+      <c r="E437" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5">
+      <c r="A438" s="2">
+        <v>46146.53611111111</v>
+      </c>
+      <c r="B438">
+        <v>0</v>
+      </c>
+      <c r="C438">
+        <v>0</v>
+      </c>
+      <c r="D438">
+        <v>53</v>
+      </c>
+      <c r="E438" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5">
+      <c r="A439" s="2">
+        <v>46146.54652777778</v>
+      </c>
+      <c r="B439">
+        <v>0</v>
+      </c>
+      <c r="C439">
+        <v>0</v>
+      </c>
+      <c r="D439">
+        <v>54</v>
+      </c>
+      <c r="E439" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5">
+      <c r="A440" s="2">
+        <v>46146.55694444444</v>
+      </c>
+      <c r="B440">
+        <v>0</v>
+      </c>
+      <c r="C440">
+        <v>0</v>
+      </c>
+      <c r="D440">
+        <v>55</v>
+      </c>
+      <c r="E440" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5">
+      <c r="A441" s="2">
+        <v>46146.56736111111</v>
+      </c>
+      <c r="B441">
+        <v>0</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+      <c r="D441">
+        <v>56</v>
+      </c>
+      <c r="E441" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5">
+      <c r="A442" s="2">
+        <v>46146.57777777778</v>
+      </c>
+      <c r="B442">
+        <v>0</v>
+      </c>
+      <c r="C442">
+        <v>0</v>
+      </c>
+      <c r="D442">
+        <v>57</v>
+      </c>
+      <c r="E442" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5">
+      <c r="A443" s="2">
+        <v>46146.58819444444</v>
+      </c>
+      <c r="B443">
+        <v>0</v>
+      </c>
+      <c r="C443">
+        <v>0</v>
+      </c>
+      <c r="D443">
+        <v>58</v>
+      </c>
+      <c r="E443" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5">
+      <c r="A444" s="2">
+        <v>46146.59861111111</v>
+      </c>
+      <c r="B444">
+        <v>0</v>
+      </c>
+      <c r="C444">
+        <v>0</v>
+      </c>
+      <c r="D444">
+        <v>59</v>
+      </c>
+      <c r="E444" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5">
+      <c r="A445" s="2">
+        <v>46146.60902777778</v>
+      </c>
+      <c r="B445">
+        <v>0</v>
+      </c>
+      <c r="C445">
+        <v>0</v>
+      </c>
+      <c r="D445">
+        <v>60</v>
+      </c>
+      <c r="E445" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5">
+      <c r="A446" s="2">
+        <v>46146.61944444444</v>
+      </c>
+      <c r="B446">
+        <v>0</v>
+      </c>
+      <c r="C446">
+        <v>0</v>
+      </c>
+      <c r="D446">
+        <v>61</v>
+      </c>
+      <c r="E446" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5">
+      <c r="A447" s="2">
+        <v>46146.62986111111</v>
+      </c>
+      <c r="B447">
+        <v>0</v>
+      </c>
+      <c r="C447">
+        <v>0</v>
+      </c>
+      <c r="D447">
+        <v>62</v>
+      </c>
+      <c r="E447" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5">
+      <c r="A448" s="2">
+        <v>46146.64027777778</v>
+      </c>
+      <c r="B448">
+        <v>0</v>
+      </c>
+      <c r="C448">
+        <v>0</v>
+      </c>
+      <c r="D448">
+        <v>63</v>
+      </c>
+      <c r="E448" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5">
+      <c r="A449" s="2">
+        <v>46146.65069444444</v>
+      </c>
+      <c r="B449">
+        <v>0</v>
+      </c>
+      <c r="C449">
+        <v>0</v>
+      </c>
+      <c r="D449">
+        <v>64</v>
+      </c>
+      <c r="E449" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5">
+      <c r="A450" s="2">
+        <v>46146.66111111111</v>
+      </c>
+      <c r="B450">
+        <v>0</v>
+      </c>
+      <c r="C450">
+        <v>0</v>
+      </c>
+      <c r="D450">
+        <v>65</v>
+      </c>
+      <c r="E450" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5">
+      <c r="A451" s="2">
+        <v>46146.67152777778</v>
+      </c>
+      <c r="B451">
+        <v>0</v>
+      </c>
+      <c r="C451">
+        <v>0</v>
+      </c>
+      <c r="D451">
+        <v>66</v>
+      </c>
+      <c r="E451" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5">
+      <c r="A452" s="2">
+        <v>46146.68194444444</v>
+      </c>
+      <c r="B452">
+        <v>0</v>
+      </c>
+      <c r="C452">
+        <v>0</v>
+      </c>
+      <c r="D452">
+        <v>67</v>
+      </c>
+      <c r="E452" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5">
+      <c r="A453" s="2">
+        <v>46146.69236111111</v>
+      </c>
+      <c r="B453">
+        <v>0</v>
+      </c>
+      <c r="C453">
+        <v>0</v>
+      </c>
+      <c r="D453">
+        <v>68</v>
+      </c>
+      <c r="E453" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5">
+      <c r="A454" s="2">
+        <v>46146.70277777778</v>
+      </c>
+      <c r="B454">
+        <v>0</v>
+      </c>
+      <c r="C454">
+        <v>0</v>
+      </c>
+      <c r="D454">
+        <v>69</v>
+      </c>
+      <c r="E454" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5">
+      <c r="A455" s="2">
+        <v>46146.71319444444</v>
+      </c>
+      <c r="B455">
+        <v>0</v>
+      </c>
+      <c r="C455">
+        <v>0</v>
+      </c>
+      <c r="D455">
+        <v>70</v>
+      </c>
+      <c r="E455" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5">
+      <c r="A456" s="2">
+        <v>46146.72361111111</v>
+      </c>
+      <c r="B456">
+        <v>0</v>
+      </c>
+      <c r="C456">
+        <v>0</v>
+      </c>
+      <c r="D456">
+        <v>71</v>
+      </c>
+      <c r="E456" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5">
+      <c r="A457" s="2">
+        <v>46146.73402777778</v>
+      </c>
+      <c r="B457">
+        <v>0</v>
+      </c>
+      <c r="C457">
+        <v>0</v>
+      </c>
+      <c r="D457">
+        <v>72</v>
+      </c>
+      <c r="E457" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5">
+      <c r="A458" s="2">
+        <v>46146.74444444444</v>
+      </c>
+      <c r="B458">
+        <v>0</v>
+      </c>
+      <c r="C458">
+        <v>0</v>
+      </c>
+      <c r="D458">
+        <v>73</v>
+      </c>
+      <c r="E458" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5">
+      <c r="A459" s="2">
+        <v>46146.75486111111</v>
+      </c>
+      <c r="B459">
+        <v>0</v>
+      </c>
+      <c r="C459">
+        <v>0</v>
+      </c>
+      <c r="D459">
+        <v>74</v>
+      </c>
+      <c r="E459" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5">
+      <c r="A460" s="2">
+        <v>46146.76527777778</v>
+      </c>
+      <c r="B460">
+        <v>0</v>
+      </c>
+      <c r="C460">
+        <v>0</v>
+      </c>
+      <c r="D460">
+        <v>75</v>
+      </c>
+      <c r="E460" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5">
+      <c r="A461" s="2">
+        <v>46146.77569444444</v>
+      </c>
+      <c r="B461">
+        <v>0</v>
+      </c>
+      <c r="C461">
+        <v>0</v>
+      </c>
+      <c r="D461">
+        <v>76</v>
+      </c>
+      <c r="E461" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5">
+      <c r="A462" s="2">
+        <v>46146.78611111111</v>
+      </c>
+      <c r="B462">
+        <v>0</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+      <c r="D462">
+        <v>77</v>
+      </c>
+      <c r="E462" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5">
+      <c r="A463" s="2">
+        <v>46146.79652777778</v>
+      </c>
+      <c r="B463">
+        <v>0</v>
+      </c>
+      <c r="C463">
+        <v>0</v>
+      </c>
+      <c r="D463">
+        <v>78</v>
+      </c>
+      <c r="E463" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5">
+      <c r="A464" s="2">
+        <v>46146.80694444444</v>
+      </c>
+      <c r="B464">
+        <v>0</v>
+      </c>
+      <c r="C464">
+        <v>0</v>
+      </c>
+      <c r="D464">
+        <v>79</v>
+      </c>
+      <c r="E464" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5">
+      <c r="A465" s="2">
+        <v>46146.81736111111</v>
+      </c>
+      <c r="B465">
+        <v>0</v>
+      </c>
+      <c r="C465">
+        <v>0</v>
+      </c>
+      <c r="D465">
+        <v>80</v>
+      </c>
+      <c r="E465" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5">
+      <c r="A466" s="2">
+        <v>46146.82777777778</v>
+      </c>
+      <c r="B466">
+        <v>0</v>
+      </c>
+      <c r="C466">
+        <v>0</v>
+      </c>
+      <c r="D466">
+        <v>81</v>
+      </c>
+      <c r="E466" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5">
+      <c r="A467" s="2">
+        <v>46146.83819444444</v>
+      </c>
+      <c r="B467">
+        <v>0</v>
+      </c>
+      <c r="C467">
+        <v>0</v>
+      </c>
+      <c r="D467">
+        <v>82</v>
+      </c>
+      <c r="E467" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5">
+      <c r="A468" s="2">
+        <v>46146.84861111111</v>
+      </c>
+      <c r="B468">
+        <v>0</v>
+      </c>
+      <c r="C468">
+        <v>0</v>
+      </c>
+      <c r="D468">
+        <v>83</v>
+      </c>
+      <c r="E468" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5">
+      <c r="A469" s="2">
+        <v>46146.85902777778</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+      <c r="C469">
+        <v>0</v>
+      </c>
+      <c r="D469">
+        <v>84</v>
+      </c>
+      <c r="E469" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5">
+      <c r="A470" s="2">
+        <v>46146.86944444444</v>
+      </c>
+      <c r="B470">
+        <v>0</v>
+      </c>
+      <c r="C470">
+        <v>0</v>
+      </c>
+      <c r="D470">
+        <v>85</v>
+      </c>
+      <c r="E470" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5">
+      <c r="A471" s="2">
+        <v>46146.87986111111</v>
+      </c>
+      <c r="B471">
+        <v>0</v>
+      </c>
+      <c r="C471">
+        <v>0</v>
+      </c>
+      <c r="D471">
+        <v>86</v>
+      </c>
+      <c r="E471" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5">
+      <c r="A472" s="2">
+        <v>46146.89027777778</v>
+      </c>
+      <c r="B472">
+        <v>0</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+      <c r="D472">
+        <v>87</v>
+      </c>
+      <c r="E472" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5">
+      <c r="A473" s="2">
+        <v>46146.90069444444</v>
+      </c>
+      <c r="B473">
+        <v>0</v>
+      </c>
+      <c r="C473">
+        <v>0</v>
+      </c>
+      <c r="D473">
+        <v>88</v>
+      </c>
+      <c r="E473" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5">
+      <c r="A474" s="2">
+        <v>46146.91111111111</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+      <c r="C474">
+        <v>0</v>
+      </c>
+      <c r="D474">
+        <v>89</v>
+      </c>
+      <c r="E474" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5">
+      <c r="A475" s="2">
+        <v>46146.92152777778</v>
+      </c>
+      <c r="B475">
+        <v>0</v>
+      </c>
+      <c r="C475">
+        <v>0</v>
+      </c>
+      <c r="D475">
+        <v>90</v>
+      </c>
+      <c r="E475" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5">
+      <c r="A476" s="2">
+        <v>46146.93194444444</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+      <c r="C476">
+        <v>0</v>
+      </c>
+      <c r="D476">
+        <v>91</v>
+      </c>
+      <c r="E476" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5">
+      <c r="A477" s="2">
+        <v>46146.94236111111</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+      <c r="C477">
+        <v>0</v>
+      </c>
+      <c r="D477">
+        <v>92</v>
+      </c>
+      <c r="E477" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5">
+      <c r="A478" s="2">
+        <v>46146.95277777778</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+      <c r="C478">
+        <v>0</v>
+      </c>
+      <c r="D478">
+        <v>93</v>
+      </c>
+      <c r="E478" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5">
+      <c r="A479" s="2">
+        <v>46146.96319444444</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+      <c r="C479">
+        <v>0</v>
+      </c>
+      <c r="D479">
+        <v>94</v>
+      </c>
+      <c r="E479" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5">
+      <c r="A480" s="2">
+        <v>46146.97361111111</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+      <c r="C480">
+        <v>0</v>
+      </c>
+      <c r="D480">
+        <v>95</v>
+      </c>
+      <c r="E480" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5">
+      <c r="A481" s="2">
+        <v>46146.98402777778</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+      <c r="C481">
+        <v>0</v>
+      </c>
+      <c r="D481">
+        <v>96</v>
+      </c>
+      <c r="E481" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5">
+      <c r="A482" s="2">
+        <v>46146.99444444444</v>
+      </c>
+      <c r="B482">
+        <v>0</v>
+      </c>
+      <c r="C482">
+        <v>0</v>
+      </c>
+      <c r="D482">
+        <v>1</v>
+      </c>
+      <c r="E482" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5">
+      <c r="A483" s="2">
+        <v>46147.00486111111</v>
+      </c>
+      <c r="B483">
+        <v>0</v>
+      </c>
+      <c r="C483">
+        <v>0</v>
+      </c>
+      <c r="D483">
+        <v>2</v>
+      </c>
+      <c r="E483" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5">
+      <c r="A484" s="2">
+        <v>46147.01527777778</v>
+      </c>
+      <c r="B484">
+        <v>0</v>
+      </c>
+      <c r="C484">
+        <v>0</v>
+      </c>
+      <c r="D484">
+        <v>3</v>
+      </c>
+      <c r="E484" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5">
+      <c r="A485" s="2">
+        <v>46147.02569444444</v>
+      </c>
+      <c r="B485">
+        <v>0</v>
+      </c>
+      <c r="C485">
+        <v>0</v>
+      </c>
+      <c r="D485">
+        <v>4</v>
+      </c>
+      <c r="E485" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5">
+      <c r="A486" s="2">
+        <v>46147.03611111111</v>
+      </c>
+      <c r="B486">
+        <v>0</v>
+      </c>
+      <c r="C486">
+        <v>0</v>
+      </c>
+      <c r="D486">
+        <v>5</v>
+      </c>
+      <c r="E486" t="s">
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,583 +31,583 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>05.05.20261</t>
-  </si>
-  <si>
-    <t>05.05.20262</t>
-  </si>
-  <si>
-    <t>05.05.20263</t>
-  </si>
-  <si>
-    <t>05.05.20264</t>
-  </si>
-  <si>
-    <t>05.05.20265</t>
-  </si>
-  <si>
-    <t>05.05.20266</t>
-  </si>
-  <si>
-    <t>05.05.20267</t>
-  </si>
-  <si>
-    <t>05.05.20268</t>
-  </si>
-  <si>
-    <t>05.05.20269</t>
-  </si>
-  <si>
-    <t>05.05.202610</t>
-  </si>
-  <si>
-    <t>05.05.202611</t>
-  </si>
-  <si>
-    <t>05.05.202612</t>
-  </si>
-  <si>
-    <t>05.05.202613</t>
-  </si>
-  <si>
-    <t>05.05.202614</t>
-  </si>
-  <si>
-    <t>05.05.202615</t>
-  </si>
-  <si>
-    <t>05.05.202616</t>
-  </si>
-  <si>
-    <t>05.05.202617</t>
-  </si>
-  <si>
-    <t>05.05.202618</t>
-  </si>
-  <si>
-    <t>05.05.202619</t>
-  </si>
-  <si>
-    <t>05.05.202620</t>
-  </si>
-  <si>
-    <t>05.05.202621</t>
-  </si>
-  <si>
-    <t>05.05.202622</t>
-  </si>
-  <si>
-    <t>05.05.202623</t>
-  </si>
-  <si>
-    <t>05.05.202624</t>
-  </si>
-  <si>
-    <t>05.05.202625</t>
-  </si>
-  <si>
-    <t>05.05.202626</t>
-  </si>
-  <si>
-    <t>05.05.202627</t>
-  </si>
-  <si>
-    <t>05.05.202628</t>
-  </si>
-  <si>
-    <t>05.05.202629</t>
-  </si>
-  <si>
-    <t>05.05.202630</t>
-  </si>
-  <si>
-    <t>05.05.202631</t>
-  </si>
-  <si>
-    <t>05.05.202632</t>
-  </si>
-  <si>
-    <t>05.05.202633</t>
-  </si>
-  <si>
-    <t>05.05.202634</t>
-  </si>
-  <si>
-    <t>05.05.202635</t>
-  </si>
-  <si>
-    <t>05.05.202636</t>
-  </si>
-  <si>
-    <t>05.05.202637</t>
-  </si>
-  <si>
-    <t>05.05.202638</t>
-  </si>
-  <si>
-    <t>05.05.202639</t>
-  </si>
-  <si>
-    <t>05.05.202640</t>
-  </si>
-  <si>
-    <t>05.05.202641</t>
-  </si>
-  <si>
-    <t>05.05.202642</t>
-  </si>
-  <si>
-    <t>05.05.202643</t>
-  </si>
-  <si>
-    <t>05.05.202644</t>
-  </si>
-  <si>
-    <t>05.05.202645</t>
-  </si>
-  <si>
-    <t>05.05.202646</t>
-  </si>
-  <si>
-    <t>05.05.202647</t>
-  </si>
-  <si>
-    <t>05.05.202648</t>
-  </si>
-  <si>
-    <t>05.05.202649</t>
-  </si>
-  <si>
-    <t>05.05.202650</t>
-  </si>
-  <si>
-    <t>05.05.202651</t>
-  </si>
-  <si>
-    <t>05.05.202652</t>
-  </si>
-  <si>
-    <t>05.05.202653</t>
-  </si>
-  <si>
-    <t>05.05.202654</t>
-  </si>
-  <si>
-    <t>05.05.202655</t>
-  </si>
-  <si>
-    <t>05.05.202656</t>
-  </si>
-  <si>
-    <t>05.05.202657</t>
-  </si>
-  <si>
-    <t>05.05.202658</t>
-  </si>
-  <si>
-    <t>05.05.202659</t>
-  </si>
-  <si>
-    <t>05.05.202660</t>
-  </si>
-  <si>
-    <t>05.05.202661</t>
-  </si>
-  <si>
-    <t>05.05.202662</t>
-  </si>
-  <si>
-    <t>05.05.202663</t>
-  </si>
-  <si>
-    <t>05.05.202664</t>
-  </si>
-  <si>
-    <t>05.05.202665</t>
-  </si>
-  <si>
-    <t>05.05.202666</t>
-  </si>
-  <si>
-    <t>05.05.202667</t>
-  </si>
-  <si>
-    <t>05.05.202668</t>
-  </si>
-  <si>
-    <t>05.05.202669</t>
-  </si>
-  <si>
-    <t>05.05.202670</t>
-  </si>
-  <si>
-    <t>05.05.202671</t>
-  </si>
-  <si>
-    <t>05.05.202672</t>
-  </si>
-  <si>
-    <t>05.05.202673</t>
-  </si>
-  <si>
-    <t>05.05.202674</t>
-  </si>
-  <si>
-    <t>05.05.202675</t>
-  </si>
-  <si>
-    <t>05.05.202676</t>
-  </si>
-  <si>
-    <t>05.05.202677</t>
-  </si>
-  <si>
-    <t>05.05.202678</t>
-  </si>
-  <si>
-    <t>05.05.202679</t>
-  </si>
-  <si>
-    <t>05.05.202680</t>
-  </si>
-  <si>
-    <t>05.05.202681</t>
-  </si>
-  <si>
-    <t>05.05.202682</t>
-  </si>
-  <si>
-    <t>05.05.202683</t>
-  </si>
-  <si>
-    <t>05.05.202684</t>
-  </si>
-  <si>
-    <t>05.05.202685</t>
-  </si>
-  <si>
-    <t>05.05.202686</t>
-  </si>
-  <si>
-    <t>05.05.202687</t>
-  </si>
-  <si>
-    <t>05.05.202688</t>
-  </si>
-  <si>
-    <t>05.05.202689</t>
-  </si>
-  <si>
-    <t>05.05.202690</t>
-  </si>
-  <si>
-    <t>05.05.202691</t>
-  </si>
-  <si>
-    <t>05.05.202692</t>
-  </si>
-  <si>
-    <t>05.05.202693</t>
-  </si>
-  <si>
-    <t>06.05.202694</t>
-  </si>
-  <si>
-    <t>06.05.202695</t>
-  </si>
-  <si>
-    <t>06.05.202696</t>
-  </si>
-  <si>
-    <t>06.05.20261</t>
-  </si>
-  <si>
-    <t>06.05.20262</t>
-  </si>
-  <si>
-    <t>06.05.20263</t>
-  </si>
-  <si>
-    <t>06.05.20264</t>
-  </si>
-  <si>
-    <t>06.05.20265</t>
-  </si>
-  <si>
-    <t>06.05.20266</t>
-  </si>
-  <si>
-    <t>06.05.20267</t>
-  </si>
-  <si>
-    <t>06.05.20268</t>
-  </si>
-  <si>
-    <t>06.05.20269</t>
-  </si>
-  <si>
-    <t>06.05.202610</t>
-  </si>
-  <si>
-    <t>06.05.202611</t>
-  </si>
-  <si>
-    <t>06.05.202612</t>
-  </si>
-  <si>
-    <t>06.05.202613</t>
-  </si>
-  <si>
-    <t>06.05.202614</t>
-  </si>
-  <si>
-    <t>06.05.202615</t>
-  </si>
-  <si>
-    <t>06.05.202616</t>
-  </si>
-  <si>
-    <t>06.05.202617</t>
-  </si>
-  <si>
-    <t>06.05.202618</t>
-  </si>
-  <si>
-    <t>06.05.202619</t>
-  </si>
-  <si>
-    <t>06.05.202620</t>
-  </si>
-  <si>
-    <t>06.05.202621</t>
-  </si>
-  <si>
-    <t>06.05.202622</t>
-  </si>
-  <si>
-    <t>06.05.202623</t>
-  </si>
-  <si>
-    <t>06.05.202624</t>
-  </si>
-  <si>
-    <t>06.05.202625</t>
-  </si>
-  <si>
-    <t>06.05.202626</t>
-  </si>
-  <si>
-    <t>06.05.202627</t>
-  </si>
-  <si>
-    <t>06.05.202628</t>
-  </si>
-  <si>
-    <t>06.05.202629</t>
-  </si>
-  <si>
-    <t>06.05.202630</t>
-  </si>
-  <si>
-    <t>06.05.202631</t>
-  </si>
-  <si>
-    <t>06.05.202632</t>
-  </si>
-  <si>
-    <t>06.05.202633</t>
-  </si>
-  <si>
-    <t>06.05.202634</t>
-  </si>
-  <si>
-    <t>06.05.202635</t>
-  </si>
-  <si>
-    <t>06.05.202636</t>
-  </si>
-  <si>
-    <t>06.05.202637</t>
-  </si>
-  <si>
-    <t>06.05.202638</t>
-  </si>
-  <si>
-    <t>06.05.202639</t>
-  </si>
-  <si>
-    <t>06.05.202640</t>
-  </si>
-  <si>
-    <t>06.05.202641</t>
-  </si>
-  <si>
-    <t>06.05.202642</t>
-  </si>
-  <si>
-    <t>06.05.202643</t>
-  </si>
-  <si>
-    <t>06.05.202644</t>
-  </si>
-  <si>
-    <t>06.05.202645</t>
-  </si>
-  <si>
-    <t>06.05.202646</t>
-  </si>
-  <si>
-    <t>06.05.202647</t>
-  </si>
-  <si>
-    <t>06.05.202648</t>
-  </si>
-  <si>
-    <t>06.05.202649</t>
-  </si>
-  <si>
-    <t>06.05.202650</t>
-  </si>
-  <si>
-    <t>06.05.202651</t>
-  </si>
-  <si>
-    <t>06.05.202652</t>
-  </si>
-  <si>
-    <t>06.05.202653</t>
-  </si>
-  <si>
-    <t>06.05.202654</t>
-  </si>
-  <si>
-    <t>06.05.202655</t>
-  </si>
-  <si>
-    <t>06.05.202656</t>
-  </si>
-  <si>
-    <t>06.05.202657</t>
-  </si>
-  <si>
-    <t>06.05.202658</t>
-  </si>
-  <si>
-    <t>06.05.202659</t>
-  </si>
-  <si>
-    <t>06.05.202660</t>
-  </si>
-  <si>
-    <t>06.05.202661</t>
-  </si>
-  <si>
-    <t>06.05.202662</t>
-  </si>
-  <si>
-    <t>06.05.202663</t>
-  </si>
-  <si>
-    <t>06.05.202664</t>
-  </si>
-  <si>
-    <t>06.05.202665</t>
-  </si>
-  <si>
-    <t>06.05.202666</t>
-  </si>
-  <si>
-    <t>06.05.202667</t>
-  </si>
-  <si>
-    <t>06.05.202668</t>
-  </si>
-  <si>
-    <t>06.05.202669</t>
-  </si>
-  <si>
-    <t>06.05.202670</t>
-  </si>
-  <si>
-    <t>06.05.202671</t>
-  </si>
-  <si>
-    <t>06.05.202672</t>
-  </si>
-  <si>
-    <t>06.05.202673</t>
-  </si>
-  <si>
-    <t>06.05.202674</t>
-  </si>
-  <si>
-    <t>06.05.202675</t>
-  </si>
-  <si>
-    <t>06.05.202676</t>
-  </si>
-  <si>
-    <t>06.05.202677</t>
-  </si>
-  <si>
-    <t>06.05.202678</t>
-  </si>
-  <si>
-    <t>06.05.202679</t>
-  </si>
-  <si>
-    <t>06.05.202680</t>
-  </si>
-  <si>
-    <t>06.05.202681</t>
-  </si>
-  <si>
-    <t>06.05.202682</t>
-  </si>
-  <si>
-    <t>06.05.202683</t>
-  </si>
-  <si>
-    <t>06.05.202684</t>
-  </si>
-  <si>
-    <t>06.05.202685</t>
-  </si>
-  <si>
-    <t>06.05.202686</t>
-  </si>
-  <si>
-    <t>06.05.202687</t>
-  </si>
-  <si>
-    <t>06.05.202688</t>
-  </si>
-  <si>
-    <t>06.05.202689</t>
-  </si>
-  <si>
-    <t>06.05.202690</t>
-  </si>
-  <si>
-    <t>06.05.202691</t>
-  </si>
-  <si>
-    <t>06.05.202692</t>
-  </si>
-  <si>
-    <t>06.05.202693</t>
-  </si>
-  <si>
-    <t>07.05.202695</t>
-  </si>
-  <si>
-    <t>07.05.202696</t>
-  </si>
-  <si>
     <t>07.05.20261</t>
   </si>
   <si>
     <t>07.05.20262</t>
+  </si>
+  <si>
+    <t>07.05.20263</t>
+  </si>
+  <si>
+    <t>07.05.20264</t>
+  </si>
+  <si>
+    <t>07.05.20265</t>
+  </si>
+  <si>
+    <t>07.05.20266</t>
+  </si>
+  <si>
+    <t>07.05.20267</t>
+  </si>
+  <si>
+    <t>07.05.20268</t>
+  </si>
+  <si>
+    <t>07.05.20269</t>
+  </si>
+  <si>
+    <t>07.05.202610</t>
+  </si>
+  <si>
+    <t>07.05.202611</t>
+  </si>
+  <si>
+    <t>07.05.202612</t>
+  </si>
+  <si>
+    <t>07.05.202613</t>
+  </si>
+  <si>
+    <t>07.05.202614</t>
+  </si>
+  <si>
+    <t>07.05.202615</t>
+  </si>
+  <si>
+    <t>07.05.202616</t>
+  </si>
+  <si>
+    <t>07.05.202617</t>
+  </si>
+  <si>
+    <t>07.05.202618</t>
+  </si>
+  <si>
+    <t>07.05.202619</t>
+  </si>
+  <si>
+    <t>07.05.202620</t>
+  </si>
+  <si>
+    <t>07.05.202621</t>
+  </si>
+  <si>
+    <t>07.05.202622</t>
+  </si>
+  <si>
+    <t>07.05.202623</t>
+  </si>
+  <si>
+    <t>07.05.202624</t>
+  </si>
+  <si>
+    <t>07.05.202625</t>
+  </si>
+  <si>
+    <t>07.05.202626</t>
+  </si>
+  <si>
+    <t>07.05.202627</t>
+  </si>
+  <si>
+    <t>07.05.202628</t>
+  </si>
+  <si>
+    <t>07.05.202629</t>
+  </si>
+  <si>
+    <t>07.05.202630</t>
+  </si>
+  <si>
+    <t>07.05.202631</t>
+  </si>
+  <si>
+    <t>07.05.202632</t>
+  </si>
+  <si>
+    <t>07.05.202633</t>
+  </si>
+  <si>
+    <t>07.05.202634</t>
+  </si>
+  <si>
+    <t>07.05.202635</t>
+  </si>
+  <si>
+    <t>07.05.202636</t>
+  </si>
+  <si>
+    <t>07.05.202637</t>
+  </si>
+  <si>
+    <t>07.05.202638</t>
+  </si>
+  <si>
+    <t>07.05.202639</t>
+  </si>
+  <si>
+    <t>07.05.202640</t>
+  </si>
+  <si>
+    <t>07.05.202641</t>
+  </si>
+  <si>
+    <t>07.05.202642</t>
+  </si>
+  <si>
+    <t>07.05.202643</t>
+  </si>
+  <si>
+    <t>07.05.202644</t>
+  </si>
+  <si>
+    <t>07.05.202645</t>
+  </si>
+  <si>
+    <t>07.05.202646</t>
+  </si>
+  <si>
+    <t>07.05.202647</t>
+  </si>
+  <si>
+    <t>07.05.202648</t>
+  </si>
+  <si>
+    <t>07.05.202649</t>
+  </si>
+  <si>
+    <t>07.05.202650</t>
+  </si>
+  <si>
+    <t>07.05.202651</t>
+  </si>
+  <si>
+    <t>07.05.202652</t>
+  </si>
+  <si>
+    <t>07.05.202653</t>
+  </si>
+  <si>
+    <t>07.05.202654</t>
+  </si>
+  <si>
+    <t>07.05.202655</t>
+  </si>
+  <si>
+    <t>07.05.202656</t>
+  </si>
+  <si>
+    <t>07.05.202657</t>
+  </si>
+  <si>
+    <t>07.05.202658</t>
+  </si>
+  <si>
+    <t>07.05.202659</t>
+  </si>
+  <si>
+    <t>07.05.202660</t>
+  </si>
+  <si>
+    <t>07.05.202661</t>
+  </si>
+  <si>
+    <t>07.05.202662</t>
+  </si>
+  <si>
+    <t>07.05.202663</t>
+  </si>
+  <si>
+    <t>07.05.202664</t>
+  </si>
+  <si>
+    <t>07.05.202665</t>
+  </si>
+  <si>
+    <t>07.05.202666</t>
+  </si>
+  <si>
+    <t>07.05.202667</t>
+  </si>
+  <si>
+    <t>07.05.202668</t>
+  </si>
+  <si>
+    <t>07.05.202669</t>
+  </si>
+  <si>
+    <t>07.05.202670</t>
+  </si>
+  <si>
+    <t>07.05.202671</t>
+  </si>
+  <si>
+    <t>07.05.202672</t>
+  </si>
+  <si>
+    <t>07.05.202673</t>
+  </si>
+  <si>
+    <t>07.05.202674</t>
+  </si>
+  <si>
+    <t>07.05.202675</t>
+  </si>
+  <si>
+    <t>07.05.202676</t>
+  </si>
+  <si>
+    <t>07.05.202677</t>
+  </si>
+  <si>
+    <t>07.05.202678</t>
+  </si>
+  <si>
+    <t>07.05.202679</t>
+  </si>
+  <si>
+    <t>07.05.202680</t>
+  </si>
+  <si>
+    <t>07.05.202681</t>
+  </si>
+  <si>
+    <t>07.05.202682</t>
+  </si>
+  <si>
+    <t>07.05.202683</t>
+  </si>
+  <si>
+    <t>07.05.202684</t>
+  </si>
+  <si>
+    <t>07.05.202685</t>
+  </si>
+  <si>
+    <t>07.05.202686</t>
+  </si>
+  <si>
+    <t>07.05.202687</t>
+  </si>
+  <si>
+    <t>07.05.202688</t>
+  </si>
+  <si>
+    <t>07.05.202689</t>
+  </si>
+  <si>
+    <t>07.05.202690</t>
+  </si>
+  <si>
+    <t>07.05.202691</t>
+  </si>
+  <si>
+    <t>07.05.202692</t>
+  </si>
+  <si>
+    <t>07.05.202693</t>
+  </si>
+  <si>
+    <t>08.05.202694</t>
+  </si>
+  <si>
+    <t>08.05.202695</t>
+  </si>
+  <si>
+    <t>08.05.202696</t>
+  </si>
+  <si>
+    <t>08.05.20261</t>
+  </si>
+  <si>
+    <t>08.05.20262</t>
+  </si>
+  <si>
+    <t>08.05.20263</t>
+  </si>
+  <si>
+    <t>08.05.20264</t>
+  </si>
+  <si>
+    <t>08.05.20265</t>
+  </si>
+  <si>
+    <t>08.05.20266</t>
+  </si>
+  <si>
+    <t>08.05.20267</t>
+  </si>
+  <si>
+    <t>08.05.20268</t>
+  </si>
+  <si>
+    <t>08.05.20269</t>
+  </si>
+  <si>
+    <t>08.05.202610</t>
+  </si>
+  <si>
+    <t>08.05.202611</t>
+  </si>
+  <si>
+    <t>08.05.202612</t>
+  </si>
+  <si>
+    <t>08.05.202613</t>
+  </si>
+  <si>
+    <t>08.05.202614</t>
+  </si>
+  <si>
+    <t>08.05.202615</t>
+  </si>
+  <si>
+    <t>08.05.202616</t>
+  </si>
+  <si>
+    <t>08.05.202617</t>
+  </si>
+  <si>
+    <t>08.05.202618</t>
+  </si>
+  <si>
+    <t>08.05.202619</t>
+  </si>
+  <si>
+    <t>08.05.202620</t>
+  </si>
+  <si>
+    <t>08.05.202621</t>
+  </si>
+  <si>
+    <t>08.05.202622</t>
+  </si>
+  <si>
+    <t>08.05.202623</t>
+  </si>
+  <si>
+    <t>08.05.202624</t>
+  </si>
+  <si>
+    <t>08.05.202625</t>
+  </si>
+  <si>
+    <t>08.05.202626</t>
+  </si>
+  <si>
+    <t>08.05.202627</t>
+  </si>
+  <si>
+    <t>08.05.202628</t>
+  </si>
+  <si>
+    <t>08.05.202629</t>
+  </si>
+  <si>
+    <t>08.05.202630</t>
+  </si>
+  <si>
+    <t>08.05.202631</t>
+  </si>
+  <si>
+    <t>08.05.202632</t>
+  </si>
+  <si>
+    <t>08.05.202633</t>
+  </si>
+  <si>
+    <t>08.05.202634</t>
+  </si>
+  <si>
+    <t>08.05.202635</t>
+  </si>
+  <si>
+    <t>08.05.202636</t>
+  </si>
+  <si>
+    <t>08.05.202637</t>
+  </si>
+  <si>
+    <t>08.05.202638</t>
+  </si>
+  <si>
+    <t>08.05.202639</t>
+  </si>
+  <si>
+    <t>08.05.202640</t>
+  </si>
+  <si>
+    <t>08.05.202641</t>
+  </si>
+  <si>
+    <t>08.05.202642</t>
+  </si>
+  <si>
+    <t>08.05.202643</t>
+  </si>
+  <si>
+    <t>08.05.202644</t>
+  </si>
+  <si>
+    <t>08.05.202645</t>
+  </si>
+  <si>
+    <t>08.05.202646</t>
+  </si>
+  <si>
+    <t>08.05.202647</t>
+  </si>
+  <si>
+    <t>08.05.202648</t>
+  </si>
+  <si>
+    <t>08.05.202649</t>
+  </si>
+  <si>
+    <t>08.05.202650</t>
+  </si>
+  <si>
+    <t>08.05.202651</t>
+  </si>
+  <si>
+    <t>08.05.202652</t>
+  </si>
+  <si>
+    <t>08.05.202653</t>
+  </si>
+  <si>
+    <t>08.05.202654</t>
+  </si>
+  <si>
+    <t>08.05.202655</t>
+  </si>
+  <si>
+    <t>08.05.202656</t>
+  </si>
+  <si>
+    <t>08.05.202657</t>
+  </si>
+  <si>
+    <t>08.05.202658</t>
+  </si>
+  <si>
+    <t>08.05.202659</t>
+  </si>
+  <si>
+    <t>08.05.202660</t>
+  </si>
+  <si>
+    <t>08.05.202661</t>
+  </si>
+  <si>
+    <t>08.05.202662</t>
+  </si>
+  <si>
+    <t>08.05.202663</t>
+  </si>
+  <si>
+    <t>08.05.202664</t>
+  </si>
+  <si>
+    <t>08.05.202665</t>
+  </si>
+  <si>
+    <t>08.05.202666</t>
+  </si>
+  <si>
+    <t>08.05.202667</t>
+  </si>
+  <si>
+    <t>08.05.202668</t>
+  </si>
+  <si>
+    <t>08.05.202669</t>
+  </si>
+  <si>
+    <t>08.05.202670</t>
+  </si>
+  <si>
+    <t>08.05.202671</t>
+  </si>
+  <si>
+    <t>08.05.202672</t>
+  </si>
+  <si>
+    <t>08.05.202673</t>
+  </si>
+  <si>
+    <t>08.05.202674</t>
+  </si>
+  <si>
+    <t>08.05.202675</t>
+  </si>
+  <si>
+    <t>08.05.202676</t>
+  </si>
+  <si>
+    <t>08.05.202677</t>
+  </si>
+  <si>
+    <t>08.05.202678</t>
+  </si>
+  <si>
+    <t>08.05.202679</t>
+  </si>
+  <si>
+    <t>08.05.202680</t>
+  </si>
+  <si>
+    <t>08.05.202681</t>
+  </si>
+  <si>
+    <t>08.05.202682</t>
+  </si>
+  <si>
+    <t>08.05.202683</t>
+  </si>
+  <si>
+    <t>08.05.202684</t>
+  </si>
+  <si>
+    <t>08.05.202685</t>
+  </si>
+  <si>
+    <t>08.05.202686</t>
+  </si>
+  <si>
+    <t>08.05.202687</t>
+  </si>
+  <si>
+    <t>08.05.202688</t>
+  </si>
+  <si>
+    <t>08.05.202689</t>
+  </si>
+  <si>
+    <t>08.05.202690</t>
+  </si>
+  <si>
+    <t>08.05.202691</t>
+  </si>
+  <si>
+    <t>08.05.202692</t>
+  </si>
+  <si>
+    <t>08.05.202693</t>
+  </si>
+  <si>
+    <t>09.05.202695</t>
+  </si>
+  <si>
+    <t>09.05.202696</t>
+  </si>
+  <si>
+    <t>09.05.20261</t>
+  </si>
+  <si>
+    <t>09.05.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46147.03611111111</v>
+        <v>46149.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46147.04652777778</v>
+        <v>46149.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46147.05694444444</v>
+        <v>46149.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46147.06736111111</v>
+        <v>46149.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46147.07777777778</v>
+        <v>46149.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46147.08819444444</v>
+        <v>46149.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46147.09861111111</v>
+        <v>46149.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46147.10902777778</v>
+        <v>46149.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46147.11944444444</v>
+        <v>46149.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46147.12986111111</v>
+        <v>46149.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46147.14027777778</v>
+        <v>46149.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46147.15069444444</v>
+        <v>46149.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46147.16111111111</v>
+        <v>46149.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46147.17152777778</v>
+        <v>46149.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46147.18194444444</v>
+        <v>46149.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46147.19236111111</v>
+        <v>46149.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46147.20277777778</v>
+        <v>46149.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46147.21319444444</v>
+        <v>46149.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46147.22361111111</v>
+        <v>46149.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46147.23402777778</v>
+        <v>46149.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46147.24444444444</v>
+        <v>46149.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46147.25486111111</v>
+        <v>46149.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46147.26527777778</v>
+        <v>46149.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46147.27569444444</v>
+        <v>46149.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46147.28611111111</v>
+        <v>46149.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46147.29652777778</v>
+        <v>46149.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46147.30694444444</v>
+        <v>46149.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46147.31736111111</v>
+        <v>46149.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46147.32777777778</v>
+        <v>46149.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46147.33819444444</v>
+        <v>46149.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46147.34861111111</v>
+        <v>46149.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46147.35902777778</v>
+        <v>46149.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46147.36944444444</v>
+        <v>46149.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46147.37986111111</v>
+        <v>46149.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46147.39027777778</v>
+        <v>46149.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46147.40069444444</v>
+        <v>46149.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46147.41111111111</v>
+        <v>46149.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46147.42152777778</v>
+        <v>46149.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46147.43194444444</v>
+        <v>46149.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46147.44236111111</v>
+        <v>46149.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46147.45277777778</v>
+        <v>46149.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46147.46319444444</v>
+        <v>46149.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46147.47361111111</v>
+        <v>46149.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46147.48402777778</v>
+        <v>46149.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46147.49444444444</v>
+        <v>46149.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46147.50486111111</v>
+        <v>46149.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46147.51527777778</v>
+        <v>46149.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46147.52569444444</v>
+        <v>46149.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46147.53611111111</v>
+        <v>46149.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46147.54652777778</v>
+        <v>46149.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46147.55694444444</v>
+        <v>46149.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46147.56736111111</v>
+        <v>46149.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46147.57777777778</v>
+        <v>46149.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46147.58819444444</v>
+        <v>46149.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46147.59861111111</v>
+        <v>46149.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46147.60902777778</v>
+        <v>46149.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46147.61944444444</v>
+        <v>46149.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46147.62986111111</v>
+        <v>46149.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46147.64027777778</v>
+        <v>46149.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46147.65069444444</v>
+        <v>46149.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46147.66111111111</v>
+        <v>46149.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46147.67152777778</v>
+        <v>46149.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46147.68194444444</v>
+        <v>46149.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46147.69236111111</v>
+        <v>46149.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46147.70277777778</v>
+        <v>46149.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46147.71319444444</v>
+        <v>46149.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46147.72361111111</v>
+        <v>46149.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46147.73402777778</v>
+        <v>46149.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46147.74444444444</v>
+        <v>46149.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46147.75486111111</v>
+        <v>46149.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46147.76527777778</v>
+        <v>46149.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46147.77569444444</v>
+        <v>46149.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46147.78611111111</v>
+        <v>46149.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46147.79652777778</v>
+        <v>46149.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46147.80694444444</v>
+        <v>46149.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46147.81736111111</v>
+        <v>46149.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46147.82777777778</v>
+        <v>46149.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46147.83819444444</v>
+        <v>46149.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46147.84861111111</v>
+        <v>46149.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46147.85902777778</v>
+        <v>46149.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46147.86944444444</v>
+        <v>46149.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46147.87986111111</v>
+        <v>46149.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46147.89027777778</v>
+        <v>46149.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46147.90069444444</v>
+        <v>46149.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46147.91111111111</v>
+        <v>46149.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46147.92152777778</v>
+        <v>46149.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46147.93194444444</v>
+        <v>46149.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46147.94236111111</v>
+        <v>46149.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46147.95277777778</v>
+        <v>46149.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46147.96319444444</v>
+        <v>46149.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46147.97361111111</v>
+        <v>46149.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46147.98402777778</v>
+        <v>46149.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46147.99444444444</v>
+        <v>46149.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46148.00486111111</v>
+        <v>46150.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46148.01527777778</v>
+        <v>46150.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46148.02569444444</v>
+        <v>46150.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46148.03611111111</v>
+        <v>46150.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46148.03611111111</v>
+        <v>46150.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46148.04652777778</v>
+        <v>46150.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46148.05694444444</v>
+        <v>46150.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46148.06736111111</v>
+        <v>46150.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46148.07777777778</v>
+        <v>46150.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46148.08819444444</v>
+        <v>46150.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46148.09861111111</v>
+        <v>46150.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46148.10902777778</v>
+        <v>46150.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46148.11944444444</v>
+        <v>46150.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46148.12986111111</v>
+        <v>46150.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46148.14027777778</v>
+        <v>46150.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46148.15069444444</v>
+        <v>46150.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46148.16111111111</v>
+        <v>46150.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46148.17152777778</v>
+        <v>46150.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46148.18194444444</v>
+        <v>46150.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46148.19236111111</v>
+        <v>46150.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46148.20277777778</v>
+        <v>46150.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46148.21319444444</v>
+        <v>46150.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46148.22361111111</v>
+        <v>46150.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46148.23402777778</v>
+        <v>46150.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46148.24444444444</v>
+        <v>46150.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46148.25486111111</v>
+        <v>46150.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46148.26527777778</v>
+        <v>46150.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46148.27569444444</v>
+        <v>46150.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46148.28611111111</v>
+        <v>46150.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46148.29652777778</v>
+        <v>46150.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46148.30694444444</v>
+        <v>46150.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46148.31736111111</v>
+        <v>46150.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46148.32777777778</v>
+        <v>46150.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46148.33819444444</v>
+        <v>46150.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46148.34861111111</v>
+        <v>46150.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46148.35902777778</v>
+        <v>46150.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46148.36944444444</v>
+        <v>46150.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46148.37986111111</v>
+        <v>46150.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46148.39027777778</v>
+        <v>46150.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46148.40069444444</v>
+        <v>46150.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46148.41111111111</v>
+        <v>46150.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46148.42152777778</v>
+        <v>46150.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46148.43194444444</v>
+        <v>46150.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46148.44236111111</v>
+        <v>46150.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46148.45277777778</v>
+        <v>46150.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46148.46319444444</v>
+        <v>46150.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46148.47361111111</v>
+        <v>46150.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46148.48402777778</v>
+        <v>46150.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46148.49444444444</v>
+        <v>46150.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46148.50486111111</v>
+        <v>46150.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46148.51527777778</v>
+        <v>46150.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46148.52569444444</v>
+        <v>46150.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46148.53611111111</v>
+        <v>46150.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46148.54652777778</v>
+        <v>46150.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46148.55694444444</v>
+        <v>46150.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46148.56736111111</v>
+        <v>46150.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46148.57777777778</v>
+        <v>46150.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46148.58819444444</v>
+        <v>46150.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46148.59861111111</v>
+        <v>46150.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46148.60902777778</v>
+        <v>46150.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46148.61944444444</v>
+        <v>46150.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46148.62986111111</v>
+        <v>46150.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46148.64027777778</v>
+        <v>46150.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46148.65069444444</v>
+        <v>46150.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46148.66111111111</v>
+        <v>46150.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46148.67152777778</v>
+        <v>46150.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46148.68194444444</v>
+        <v>46150.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46148.69236111111</v>
+        <v>46150.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46148.70277777778</v>
+        <v>46150.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46148.71319444444</v>
+        <v>46150.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46148.72361111111</v>
+        <v>46150.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46148.73402777778</v>
+        <v>46150.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46148.74444444444</v>
+        <v>46150.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46148.75486111111</v>
+        <v>46150.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46148.76527777778</v>
+        <v>46150.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46148.77569444444</v>
+        <v>46150.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46148.78611111111</v>
+        <v>46150.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46148.79652777778</v>
+        <v>46150.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46148.80694444444</v>
+        <v>46150.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46148.81736111111</v>
+        <v>46150.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46148.82777777778</v>
+        <v>46150.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46148.83819444444</v>
+        <v>46150.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46148.84861111111</v>
+        <v>46150.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46148.85902777778</v>
+        <v>46150.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46148.86944444444</v>
+        <v>46150.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46148.87986111111</v>
+        <v>46150.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46148.89027777778</v>
+        <v>46150.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46148.90069444444</v>
+        <v>46150.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46148.91111111111</v>
+        <v>46150.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46148.92152777778</v>
+        <v>46150.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46148.93194444444</v>
+        <v>46150.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46148.94236111111</v>
+        <v>46150.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46148.95277777778</v>
+        <v>46150.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46148.96319444444</v>
+        <v>46150.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46148.97361111111</v>
+        <v>46150.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46148.98402777778</v>
+        <v>46150.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46148.99444444444</v>
+        <v>46150.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46149.00486111111</v>
+        <v>46151.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46149.01527777778</v>
+        <v>46151.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46149.02569444444</v>
+        <v>46151.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46149.03611111111</v>
+        <v>46151.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,583 +31,583 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>07.05.20261</t>
-  </si>
-  <si>
-    <t>07.05.20262</t>
-  </si>
-  <si>
-    <t>07.05.20263</t>
-  </si>
-  <si>
-    <t>07.05.20264</t>
-  </si>
-  <si>
-    <t>07.05.20265</t>
-  </si>
-  <si>
-    <t>07.05.20266</t>
-  </si>
-  <si>
-    <t>07.05.20267</t>
-  </si>
-  <si>
-    <t>07.05.20268</t>
-  </si>
-  <si>
-    <t>07.05.20269</t>
-  </si>
-  <si>
-    <t>07.05.202610</t>
-  </si>
-  <si>
-    <t>07.05.202611</t>
-  </si>
-  <si>
-    <t>07.05.202612</t>
-  </si>
-  <si>
-    <t>07.05.202613</t>
-  </si>
-  <si>
-    <t>07.05.202614</t>
-  </si>
-  <si>
-    <t>07.05.202615</t>
-  </si>
-  <si>
-    <t>07.05.202616</t>
-  </si>
-  <si>
-    <t>07.05.202617</t>
-  </si>
-  <si>
-    <t>07.05.202618</t>
-  </si>
-  <si>
-    <t>07.05.202619</t>
-  </si>
-  <si>
-    <t>07.05.202620</t>
-  </si>
-  <si>
-    <t>07.05.202621</t>
-  </si>
-  <si>
-    <t>07.05.202622</t>
-  </si>
-  <si>
-    <t>07.05.202623</t>
-  </si>
-  <si>
-    <t>07.05.202624</t>
-  </si>
-  <si>
-    <t>07.05.202625</t>
-  </si>
-  <si>
-    <t>07.05.202626</t>
-  </si>
-  <si>
-    <t>07.05.202627</t>
-  </si>
-  <si>
-    <t>07.05.202628</t>
-  </si>
-  <si>
-    <t>07.05.202629</t>
-  </si>
-  <si>
-    <t>07.05.202630</t>
-  </si>
-  <si>
-    <t>07.05.202631</t>
-  </si>
-  <si>
-    <t>07.05.202632</t>
-  </si>
-  <si>
-    <t>07.05.202633</t>
-  </si>
-  <si>
-    <t>07.05.202634</t>
-  </si>
-  <si>
-    <t>07.05.202635</t>
-  </si>
-  <si>
-    <t>07.05.202636</t>
-  </si>
-  <si>
-    <t>07.05.202637</t>
-  </si>
-  <si>
-    <t>07.05.202638</t>
-  </si>
-  <si>
-    <t>07.05.202639</t>
-  </si>
-  <si>
-    <t>07.05.202640</t>
-  </si>
-  <si>
-    <t>07.05.202641</t>
-  </si>
-  <si>
-    <t>07.05.202642</t>
-  </si>
-  <si>
-    <t>07.05.202643</t>
-  </si>
-  <si>
-    <t>07.05.202644</t>
-  </si>
-  <si>
-    <t>07.05.202645</t>
-  </si>
-  <si>
-    <t>07.05.202646</t>
-  </si>
-  <si>
-    <t>07.05.202647</t>
-  </si>
-  <si>
-    <t>07.05.202648</t>
-  </si>
-  <si>
-    <t>07.05.202649</t>
-  </si>
-  <si>
-    <t>07.05.202650</t>
-  </si>
-  <si>
-    <t>07.05.202651</t>
-  </si>
-  <si>
-    <t>07.05.202652</t>
-  </si>
-  <si>
-    <t>07.05.202653</t>
-  </si>
-  <si>
-    <t>07.05.202654</t>
-  </si>
-  <si>
-    <t>07.05.202655</t>
-  </si>
-  <si>
-    <t>07.05.202656</t>
-  </si>
-  <si>
-    <t>07.05.202657</t>
-  </si>
-  <si>
-    <t>07.05.202658</t>
-  </si>
-  <si>
-    <t>07.05.202659</t>
-  </si>
-  <si>
-    <t>07.05.202660</t>
-  </si>
-  <si>
-    <t>07.05.202661</t>
-  </si>
-  <si>
-    <t>07.05.202662</t>
-  </si>
-  <si>
-    <t>07.05.202663</t>
-  </si>
-  <si>
-    <t>07.05.202664</t>
-  </si>
-  <si>
-    <t>07.05.202665</t>
-  </si>
-  <si>
-    <t>07.05.202666</t>
-  </si>
-  <si>
-    <t>07.05.202667</t>
-  </si>
-  <si>
-    <t>07.05.202668</t>
-  </si>
-  <si>
-    <t>07.05.202669</t>
-  </si>
-  <si>
-    <t>07.05.202670</t>
-  </si>
-  <si>
-    <t>07.05.202671</t>
-  </si>
-  <si>
-    <t>07.05.202672</t>
-  </si>
-  <si>
-    <t>07.05.202673</t>
-  </si>
-  <si>
-    <t>07.05.202674</t>
-  </si>
-  <si>
-    <t>07.05.202675</t>
-  </si>
-  <si>
-    <t>07.05.202676</t>
-  </si>
-  <si>
-    <t>07.05.202677</t>
-  </si>
-  <si>
-    <t>07.05.202678</t>
-  </si>
-  <si>
-    <t>07.05.202679</t>
-  </si>
-  <si>
-    <t>07.05.202680</t>
-  </si>
-  <si>
-    <t>07.05.202681</t>
-  </si>
-  <si>
-    <t>07.05.202682</t>
-  </si>
-  <si>
-    <t>07.05.202683</t>
-  </si>
-  <si>
-    <t>07.05.202684</t>
-  </si>
-  <si>
-    <t>07.05.202685</t>
-  </si>
-  <si>
-    <t>07.05.202686</t>
-  </si>
-  <si>
-    <t>07.05.202687</t>
-  </si>
-  <si>
-    <t>07.05.202688</t>
-  </si>
-  <si>
-    <t>07.05.202689</t>
-  </si>
-  <si>
-    <t>07.05.202690</t>
-  </si>
-  <si>
-    <t>07.05.202691</t>
-  </si>
-  <si>
-    <t>07.05.202692</t>
-  </si>
-  <si>
-    <t>07.05.202693</t>
-  </si>
-  <si>
-    <t>08.05.202694</t>
-  </si>
-  <si>
-    <t>08.05.202695</t>
-  </si>
-  <si>
-    <t>08.05.202696</t>
-  </si>
-  <si>
-    <t>08.05.20261</t>
-  </si>
-  <si>
-    <t>08.05.20262</t>
-  </si>
-  <si>
-    <t>08.05.20263</t>
-  </si>
-  <si>
-    <t>08.05.20264</t>
-  </si>
-  <si>
-    <t>08.05.20265</t>
-  </si>
-  <si>
-    <t>08.05.20266</t>
-  </si>
-  <si>
-    <t>08.05.20267</t>
-  </si>
-  <si>
-    <t>08.05.20268</t>
-  </si>
-  <si>
-    <t>08.05.20269</t>
-  </si>
-  <si>
-    <t>08.05.202610</t>
-  </si>
-  <si>
-    <t>08.05.202611</t>
-  </si>
-  <si>
-    <t>08.05.202612</t>
-  </si>
-  <si>
-    <t>08.05.202613</t>
-  </si>
-  <si>
-    <t>08.05.202614</t>
-  </si>
-  <si>
-    <t>08.05.202615</t>
-  </si>
-  <si>
-    <t>08.05.202616</t>
-  </si>
-  <si>
-    <t>08.05.202617</t>
-  </si>
-  <si>
-    <t>08.05.202618</t>
-  </si>
-  <si>
-    <t>08.05.202619</t>
-  </si>
-  <si>
-    <t>08.05.202620</t>
-  </si>
-  <si>
-    <t>08.05.202621</t>
-  </si>
-  <si>
-    <t>08.05.202622</t>
-  </si>
-  <si>
-    <t>08.05.202623</t>
-  </si>
-  <si>
-    <t>08.05.202624</t>
-  </si>
-  <si>
-    <t>08.05.202625</t>
-  </si>
-  <si>
-    <t>08.05.202626</t>
-  </si>
-  <si>
-    <t>08.05.202627</t>
-  </si>
-  <si>
-    <t>08.05.202628</t>
-  </si>
-  <si>
-    <t>08.05.202629</t>
-  </si>
-  <si>
-    <t>08.05.202630</t>
-  </si>
-  <si>
-    <t>08.05.202631</t>
-  </si>
-  <si>
-    <t>08.05.202632</t>
-  </si>
-  <si>
-    <t>08.05.202633</t>
-  </si>
-  <si>
-    <t>08.05.202634</t>
-  </si>
-  <si>
-    <t>08.05.202635</t>
-  </si>
-  <si>
-    <t>08.05.202636</t>
-  </si>
-  <si>
-    <t>08.05.202637</t>
-  </si>
-  <si>
-    <t>08.05.202638</t>
-  </si>
-  <si>
-    <t>08.05.202639</t>
-  </si>
-  <si>
-    <t>08.05.202640</t>
-  </si>
-  <si>
-    <t>08.05.202641</t>
-  </si>
-  <si>
-    <t>08.05.202642</t>
-  </si>
-  <si>
-    <t>08.05.202643</t>
-  </si>
-  <si>
-    <t>08.05.202644</t>
-  </si>
-  <si>
-    <t>08.05.202645</t>
-  </si>
-  <si>
-    <t>08.05.202646</t>
-  </si>
-  <si>
-    <t>08.05.202647</t>
-  </si>
-  <si>
-    <t>08.05.202648</t>
-  </si>
-  <si>
-    <t>08.05.202649</t>
-  </si>
-  <si>
-    <t>08.05.202650</t>
-  </si>
-  <si>
-    <t>08.05.202651</t>
-  </si>
-  <si>
-    <t>08.05.202652</t>
-  </si>
-  <si>
-    <t>08.05.202653</t>
-  </si>
-  <si>
-    <t>08.05.202654</t>
-  </si>
-  <si>
-    <t>08.05.202655</t>
-  </si>
-  <si>
-    <t>08.05.202656</t>
-  </si>
-  <si>
-    <t>08.05.202657</t>
-  </si>
-  <si>
-    <t>08.05.202658</t>
-  </si>
-  <si>
-    <t>08.05.202659</t>
-  </si>
-  <si>
-    <t>08.05.202660</t>
-  </si>
-  <si>
-    <t>08.05.202661</t>
-  </si>
-  <si>
-    <t>08.05.202662</t>
-  </si>
-  <si>
-    <t>08.05.202663</t>
-  </si>
-  <si>
-    <t>08.05.202664</t>
-  </si>
-  <si>
-    <t>08.05.202665</t>
-  </si>
-  <si>
-    <t>08.05.202666</t>
-  </si>
-  <si>
-    <t>08.05.202667</t>
-  </si>
-  <si>
-    <t>08.05.202668</t>
-  </si>
-  <si>
-    <t>08.05.202669</t>
-  </si>
-  <si>
-    <t>08.05.202670</t>
-  </si>
-  <si>
-    <t>08.05.202671</t>
-  </si>
-  <si>
-    <t>08.05.202672</t>
-  </si>
-  <si>
-    <t>08.05.202673</t>
-  </si>
-  <si>
-    <t>08.05.202674</t>
-  </si>
-  <si>
-    <t>08.05.202675</t>
-  </si>
-  <si>
-    <t>08.05.202676</t>
-  </si>
-  <si>
-    <t>08.05.202677</t>
-  </si>
-  <si>
-    <t>08.05.202678</t>
-  </si>
-  <si>
-    <t>08.05.202679</t>
-  </si>
-  <si>
-    <t>08.05.202680</t>
-  </si>
-  <si>
-    <t>08.05.202681</t>
-  </si>
-  <si>
-    <t>08.05.202682</t>
-  </si>
-  <si>
-    <t>08.05.202683</t>
-  </si>
-  <si>
-    <t>08.05.202684</t>
-  </si>
-  <si>
-    <t>08.05.202685</t>
-  </si>
-  <si>
-    <t>08.05.202686</t>
-  </si>
-  <si>
-    <t>08.05.202687</t>
-  </si>
-  <si>
-    <t>08.05.202688</t>
-  </si>
-  <si>
-    <t>08.05.202689</t>
-  </si>
-  <si>
-    <t>08.05.202690</t>
-  </si>
-  <si>
-    <t>08.05.202691</t>
-  </si>
-  <si>
-    <t>08.05.202692</t>
-  </si>
-  <si>
-    <t>08.05.202693</t>
-  </si>
-  <si>
-    <t>09.05.202695</t>
-  </si>
-  <si>
-    <t>09.05.202696</t>
-  </si>
-  <si>
-    <t>09.05.20261</t>
-  </si>
-  <si>
-    <t>09.05.20262</t>
+    <t>11.05.20261</t>
+  </si>
+  <si>
+    <t>11.05.20262</t>
+  </si>
+  <si>
+    <t>11.05.20263</t>
+  </si>
+  <si>
+    <t>11.05.20264</t>
+  </si>
+  <si>
+    <t>11.05.20265</t>
+  </si>
+  <si>
+    <t>11.05.20266</t>
+  </si>
+  <si>
+    <t>11.05.20267</t>
+  </si>
+  <si>
+    <t>11.05.20268</t>
+  </si>
+  <si>
+    <t>11.05.20269</t>
+  </si>
+  <si>
+    <t>11.05.202610</t>
+  </si>
+  <si>
+    <t>11.05.202611</t>
+  </si>
+  <si>
+    <t>11.05.202612</t>
+  </si>
+  <si>
+    <t>11.05.202613</t>
+  </si>
+  <si>
+    <t>11.05.202614</t>
+  </si>
+  <si>
+    <t>11.05.202615</t>
+  </si>
+  <si>
+    <t>11.05.202616</t>
+  </si>
+  <si>
+    <t>11.05.202617</t>
+  </si>
+  <si>
+    <t>11.05.202618</t>
+  </si>
+  <si>
+    <t>11.05.202619</t>
+  </si>
+  <si>
+    <t>11.05.202620</t>
+  </si>
+  <si>
+    <t>11.05.202621</t>
+  </si>
+  <si>
+    <t>11.05.202622</t>
+  </si>
+  <si>
+    <t>11.05.202623</t>
+  </si>
+  <si>
+    <t>11.05.202624</t>
+  </si>
+  <si>
+    <t>11.05.202625</t>
+  </si>
+  <si>
+    <t>11.05.202626</t>
+  </si>
+  <si>
+    <t>11.05.202627</t>
+  </si>
+  <si>
+    <t>11.05.202628</t>
+  </si>
+  <si>
+    <t>11.05.202629</t>
+  </si>
+  <si>
+    <t>11.05.202630</t>
+  </si>
+  <si>
+    <t>11.05.202631</t>
+  </si>
+  <si>
+    <t>11.05.202632</t>
+  </si>
+  <si>
+    <t>11.05.202633</t>
+  </si>
+  <si>
+    <t>11.05.202634</t>
+  </si>
+  <si>
+    <t>11.05.202635</t>
+  </si>
+  <si>
+    <t>11.05.202636</t>
+  </si>
+  <si>
+    <t>11.05.202637</t>
+  </si>
+  <si>
+    <t>11.05.202638</t>
+  </si>
+  <si>
+    <t>11.05.202639</t>
+  </si>
+  <si>
+    <t>11.05.202640</t>
+  </si>
+  <si>
+    <t>11.05.202641</t>
+  </si>
+  <si>
+    <t>11.05.202642</t>
+  </si>
+  <si>
+    <t>11.05.202643</t>
+  </si>
+  <si>
+    <t>11.05.202644</t>
+  </si>
+  <si>
+    <t>11.05.202645</t>
+  </si>
+  <si>
+    <t>11.05.202646</t>
+  </si>
+  <si>
+    <t>11.05.202647</t>
+  </si>
+  <si>
+    <t>11.05.202648</t>
+  </si>
+  <si>
+    <t>11.05.202649</t>
+  </si>
+  <si>
+    <t>11.05.202650</t>
+  </si>
+  <si>
+    <t>11.05.202651</t>
+  </si>
+  <si>
+    <t>11.05.202652</t>
+  </si>
+  <si>
+    <t>11.05.202653</t>
+  </si>
+  <si>
+    <t>11.05.202654</t>
+  </si>
+  <si>
+    <t>11.05.202655</t>
+  </si>
+  <si>
+    <t>11.05.202656</t>
+  </si>
+  <si>
+    <t>11.05.202657</t>
+  </si>
+  <si>
+    <t>11.05.202658</t>
+  </si>
+  <si>
+    <t>11.05.202659</t>
+  </si>
+  <si>
+    <t>11.05.202660</t>
+  </si>
+  <si>
+    <t>11.05.202661</t>
+  </si>
+  <si>
+    <t>11.05.202662</t>
+  </si>
+  <si>
+    <t>11.05.202663</t>
+  </si>
+  <si>
+    <t>11.05.202664</t>
+  </si>
+  <si>
+    <t>11.05.202665</t>
+  </si>
+  <si>
+    <t>11.05.202666</t>
+  </si>
+  <si>
+    <t>11.05.202667</t>
+  </si>
+  <si>
+    <t>11.05.202668</t>
+  </si>
+  <si>
+    <t>11.05.202669</t>
+  </si>
+  <si>
+    <t>11.05.202670</t>
+  </si>
+  <si>
+    <t>11.05.202671</t>
+  </si>
+  <si>
+    <t>11.05.202672</t>
+  </si>
+  <si>
+    <t>11.05.202673</t>
+  </si>
+  <si>
+    <t>11.05.202674</t>
+  </si>
+  <si>
+    <t>11.05.202675</t>
+  </si>
+  <si>
+    <t>11.05.202676</t>
+  </si>
+  <si>
+    <t>11.05.202677</t>
+  </si>
+  <si>
+    <t>11.05.202678</t>
+  </si>
+  <si>
+    <t>11.05.202679</t>
+  </si>
+  <si>
+    <t>11.05.202680</t>
+  </si>
+  <si>
+    <t>11.05.202681</t>
+  </si>
+  <si>
+    <t>11.05.202682</t>
+  </si>
+  <si>
+    <t>11.05.202683</t>
+  </si>
+  <si>
+    <t>11.05.202684</t>
+  </si>
+  <si>
+    <t>11.05.202685</t>
+  </si>
+  <si>
+    <t>11.05.202686</t>
+  </si>
+  <si>
+    <t>11.05.202687</t>
+  </si>
+  <si>
+    <t>11.05.202688</t>
+  </si>
+  <si>
+    <t>11.05.202689</t>
+  </si>
+  <si>
+    <t>11.05.202690</t>
+  </si>
+  <si>
+    <t>11.05.202691</t>
+  </si>
+  <si>
+    <t>11.05.202692</t>
+  </si>
+  <si>
+    <t>11.05.202693</t>
+  </si>
+  <si>
+    <t>12.05.202694</t>
+  </si>
+  <si>
+    <t>12.05.202695</t>
+  </si>
+  <si>
+    <t>12.05.202696</t>
+  </si>
+  <si>
+    <t>12.05.20261</t>
+  </si>
+  <si>
+    <t>12.05.20262</t>
+  </si>
+  <si>
+    <t>12.05.20263</t>
+  </si>
+  <si>
+    <t>12.05.20264</t>
+  </si>
+  <si>
+    <t>12.05.20265</t>
+  </si>
+  <si>
+    <t>12.05.20266</t>
+  </si>
+  <si>
+    <t>12.05.20267</t>
+  </si>
+  <si>
+    <t>12.05.20268</t>
+  </si>
+  <si>
+    <t>12.05.20269</t>
+  </si>
+  <si>
+    <t>12.05.202610</t>
+  </si>
+  <si>
+    <t>12.05.202611</t>
+  </si>
+  <si>
+    <t>12.05.202612</t>
+  </si>
+  <si>
+    <t>12.05.202613</t>
+  </si>
+  <si>
+    <t>12.05.202614</t>
+  </si>
+  <si>
+    <t>12.05.202615</t>
+  </si>
+  <si>
+    <t>12.05.202616</t>
+  </si>
+  <si>
+    <t>12.05.202617</t>
+  </si>
+  <si>
+    <t>12.05.202618</t>
+  </si>
+  <si>
+    <t>12.05.202619</t>
+  </si>
+  <si>
+    <t>12.05.202620</t>
+  </si>
+  <si>
+    <t>12.05.202621</t>
+  </si>
+  <si>
+    <t>12.05.202622</t>
+  </si>
+  <si>
+    <t>12.05.202623</t>
+  </si>
+  <si>
+    <t>12.05.202624</t>
+  </si>
+  <si>
+    <t>12.05.202625</t>
+  </si>
+  <si>
+    <t>12.05.202626</t>
+  </si>
+  <si>
+    <t>12.05.202627</t>
+  </si>
+  <si>
+    <t>12.05.202628</t>
+  </si>
+  <si>
+    <t>12.05.202629</t>
+  </si>
+  <si>
+    <t>12.05.202630</t>
+  </si>
+  <si>
+    <t>12.05.202631</t>
+  </si>
+  <si>
+    <t>12.05.202632</t>
+  </si>
+  <si>
+    <t>12.05.202633</t>
+  </si>
+  <si>
+    <t>12.05.202634</t>
+  </si>
+  <si>
+    <t>12.05.202635</t>
+  </si>
+  <si>
+    <t>12.05.202636</t>
+  </si>
+  <si>
+    <t>12.05.202637</t>
+  </si>
+  <si>
+    <t>12.05.202638</t>
+  </si>
+  <si>
+    <t>12.05.202639</t>
+  </si>
+  <si>
+    <t>12.05.202640</t>
+  </si>
+  <si>
+    <t>12.05.202641</t>
+  </si>
+  <si>
+    <t>12.05.202642</t>
+  </si>
+  <si>
+    <t>12.05.202643</t>
+  </si>
+  <si>
+    <t>12.05.202644</t>
+  </si>
+  <si>
+    <t>12.05.202645</t>
+  </si>
+  <si>
+    <t>12.05.202646</t>
+  </si>
+  <si>
+    <t>12.05.202647</t>
+  </si>
+  <si>
+    <t>12.05.202648</t>
+  </si>
+  <si>
+    <t>12.05.202649</t>
+  </si>
+  <si>
+    <t>12.05.202650</t>
+  </si>
+  <si>
+    <t>12.05.202651</t>
+  </si>
+  <si>
+    <t>12.05.202652</t>
+  </si>
+  <si>
+    <t>12.05.202653</t>
+  </si>
+  <si>
+    <t>12.05.202654</t>
+  </si>
+  <si>
+    <t>12.05.202655</t>
+  </si>
+  <si>
+    <t>12.05.202656</t>
+  </si>
+  <si>
+    <t>12.05.202657</t>
+  </si>
+  <si>
+    <t>12.05.202658</t>
+  </si>
+  <si>
+    <t>12.05.202659</t>
+  </si>
+  <si>
+    <t>12.05.202660</t>
+  </si>
+  <si>
+    <t>12.05.202661</t>
+  </si>
+  <si>
+    <t>12.05.202662</t>
+  </si>
+  <si>
+    <t>12.05.202663</t>
+  </si>
+  <si>
+    <t>12.05.202664</t>
+  </si>
+  <si>
+    <t>12.05.202665</t>
+  </si>
+  <si>
+    <t>12.05.202666</t>
+  </si>
+  <si>
+    <t>12.05.202667</t>
+  </si>
+  <si>
+    <t>12.05.202668</t>
+  </si>
+  <si>
+    <t>12.05.202669</t>
+  </si>
+  <si>
+    <t>12.05.202670</t>
+  </si>
+  <si>
+    <t>12.05.202671</t>
+  </si>
+  <si>
+    <t>12.05.202672</t>
+  </si>
+  <si>
+    <t>12.05.202673</t>
+  </si>
+  <si>
+    <t>12.05.202674</t>
+  </si>
+  <si>
+    <t>12.05.202675</t>
+  </si>
+  <si>
+    <t>12.05.202676</t>
+  </si>
+  <si>
+    <t>12.05.202677</t>
+  </si>
+  <si>
+    <t>12.05.202678</t>
+  </si>
+  <si>
+    <t>12.05.202679</t>
+  </si>
+  <si>
+    <t>12.05.202680</t>
+  </si>
+  <si>
+    <t>12.05.202681</t>
+  </si>
+  <si>
+    <t>12.05.202682</t>
+  </si>
+  <si>
+    <t>12.05.202683</t>
+  </si>
+  <si>
+    <t>12.05.202684</t>
+  </si>
+  <si>
+    <t>12.05.202685</t>
+  </si>
+  <si>
+    <t>12.05.202686</t>
+  </si>
+  <si>
+    <t>12.05.202687</t>
+  </si>
+  <si>
+    <t>12.05.202688</t>
+  </si>
+  <si>
+    <t>12.05.202689</t>
+  </si>
+  <si>
+    <t>12.05.202690</t>
+  </si>
+  <si>
+    <t>12.05.202691</t>
+  </si>
+  <si>
+    <t>12.05.202692</t>
+  </si>
+  <si>
+    <t>12.05.202693</t>
+  </si>
+  <si>
+    <t>13.05.202695</t>
+  </si>
+  <si>
+    <t>13.05.202696</t>
+  </si>
+  <si>
+    <t>13.05.20261</t>
+  </si>
+  <si>
+    <t>13.05.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46149.03611111111</v>
+        <v>46153.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46149.04652777778</v>
+        <v>46153.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46149.05694444444</v>
+        <v>46153.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46149.06736111111</v>
+        <v>46153.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46149.07777777778</v>
+        <v>46153.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46149.08819444444</v>
+        <v>46153.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46149.09861111111</v>
+        <v>46153.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46149.10902777778</v>
+        <v>46153.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46149.11944444444</v>
+        <v>46153.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46149.12986111111</v>
+        <v>46153.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46149.14027777778</v>
+        <v>46153.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46149.15069444444</v>
+        <v>46153.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46149.16111111111</v>
+        <v>46153.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46149.17152777778</v>
+        <v>46153.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46149.18194444444</v>
+        <v>46153.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46149.19236111111</v>
+        <v>46153.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46149.20277777778</v>
+        <v>46153.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46149.21319444444</v>
+        <v>46153.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46149.22361111111</v>
+        <v>46153.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46149.23402777778</v>
+        <v>46153.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46149.24444444444</v>
+        <v>46153.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46149.25486111111</v>
+        <v>46153.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46149.26527777778</v>
+        <v>46153.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46149.27569444444</v>
+        <v>46153.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46149.28611111111</v>
+        <v>46153.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46149.29652777778</v>
+        <v>46153.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46149.30694444444</v>
+        <v>46153.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46149.31736111111</v>
+        <v>46153.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46149.32777777778</v>
+        <v>46153.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46149.33819444444</v>
+        <v>46153.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46149.34861111111</v>
+        <v>46153.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46149.35902777778</v>
+        <v>46153.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46149.36944444444</v>
+        <v>46153.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46149.37986111111</v>
+        <v>46153.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46149.39027777778</v>
+        <v>46153.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46149.40069444444</v>
+        <v>46153.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46149.41111111111</v>
+        <v>46153.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46149.42152777778</v>
+        <v>46153.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46149.43194444444</v>
+        <v>46153.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46149.44236111111</v>
+        <v>46153.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46149.45277777778</v>
+        <v>46153.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46149.46319444444</v>
+        <v>46153.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46149.47361111111</v>
+        <v>46153.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46149.48402777778</v>
+        <v>46153.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46149.49444444444</v>
+        <v>46153.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46149.50486111111</v>
+        <v>46153.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46149.51527777778</v>
+        <v>46153.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46149.52569444444</v>
+        <v>46153.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46149.53611111111</v>
+        <v>46153.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46149.54652777778</v>
+        <v>46153.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46149.55694444444</v>
+        <v>46153.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46149.56736111111</v>
+        <v>46153.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46149.57777777778</v>
+        <v>46153.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46149.58819444444</v>
+        <v>46153.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46149.59861111111</v>
+        <v>46153.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46149.60902777778</v>
+        <v>46153.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46149.61944444444</v>
+        <v>46153.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46149.62986111111</v>
+        <v>46153.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46149.64027777778</v>
+        <v>46153.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46149.65069444444</v>
+        <v>46153.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46149.66111111111</v>
+        <v>46153.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46149.67152777778</v>
+        <v>46153.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46149.68194444444</v>
+        <v>46153.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46149.69236111111</v>
+        <v>46153.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46149.70277777778</v>
+        <v>46153.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46149.71319444444</v>
+        <v>46153.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46149.72361111111</v>
+        <v>46153.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46149.73402777778</v>
+        <v>46153.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46149.74444444444</v>
+        <v>46153.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46149.75486111111</v>
+        <v>46153.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46149.76527777778</v>
+        <v>46153.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46149.77569444444</v>
+        <v>46153.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46149.78611111111</v>
+        <v>46153.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46149.79652777778</v>
+        <v>46153.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46149.80694444444</v>
+        <v>46153.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46149.81736111111</v>
+        <v>46153.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46149.82777777778</v>
+        <v>46153.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46149.83819444444</v>
+        <v>46153.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46149.84861111111</v>
+        <v>46153.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46149.85902777778</v>
+        <v>46153.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46149.86944444444</v>
+        <v>46153.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46149.87986111111</v>
+        <v>46153.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46149.89027777778</v>
+        <v>46153.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46149.90069444444</v>
+        <v>46153.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46149.91111111111</v>
+        <v>46153.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46149.92152777778</v>
+        <v>46153.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46149.93194444444</v>
+        <v>46153.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46149.94236111111</v>
+        <v>46153.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46149.95277777778</v>
+        <v>46153.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46149.96319444444</v>
+        <v>46153.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46149.97361111111</v>
+        <v>46153.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46149.98402777778</v>
+        <v>46153.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46149.99444444444</v>
+        <v>46153.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46150.00486111111</v>
+        <v>46154.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46150.01527777778</v>
+        <v>46154.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46150.02569444444</v>
+        <v>46154.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46150.03611111111</v>
+        <v>46154.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46150.03611111111</v>
+        <v>46154.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46150.04652777778</v>
+        <v>46154.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46150.05694444444</v>
+        <v>46154.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46150.06736111111</v>
+        <v>46154.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46150.07777777778</v>
+        <v>46154.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46150.08819444444</v>
+        <v>46154.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46150.09861111111</v>
+        <v>46154.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46150.10902777778</v>
+        <v>46154.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46150.11944444444</v>
+        <v>46154.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46150.12986111111</v>
+        <v>46154.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46150.14027777778</v>
+        <v>46154.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46150.15069444444</v>
+        <v>46154.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46150.16111111111</v>
+        <v>46154.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46150.17152777778</v>
+        <v>46154.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46150.18194444444</v>
+        <v>46154.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46150.19236111111</v>
+        <v>46154.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46150.20277777778</v>
+        <v>46154.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46150.21319444444</v>
+        <v>46154.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46150.22361111111</v>
+        <v>46154.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46150.23402777778</v>
+        <v>46154.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46150.24444444444</v>
+        <v>46154.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46150.25486111111</v>
+        <v>46154.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46150.26527777778</v>
+        <v>46154.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46150.27569444444</v>
+        <v>46154.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46150.28611111111</v>
+        <v>46154.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46150.29652777778</v>
+        <v>46154.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46150.30694444444</v>
+        <v>46154.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46150.31736111111</v>
+        <v>46154.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46150.32777777778</v>
+        <v>46154.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46150.33819444444</v>
+        <v>46154.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46150.34861111111</v>
+        <v>46154.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46150.35902777778</v>
+        <v>46154.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46150.36944444444</v>
+        <v>46154.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46150.37986111111</v>
+        <v>46154.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46150.39027777778</v>
+        <v>46154.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46150.40069444444</v>
+        <v>46154.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46150.41111111111</v>
+        <v>46154.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46150.42152777778</v>
+        <v>46154.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46150.43194444444</v>
+        <v>46154.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46150.44236111111</v>
+        <v>46154.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46150.45277777778</v>
+        <v>46154.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46150.46319444444</v>
+        <v>46154.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46150.47361111111</v>
+        <v>46154.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46150.48402777778</v>
+        <v>46154.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46150.49444444444</v>
+        <v>46154.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46150.50486111111</v>
+        <v>46154.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46150.51527777778</v>
+        <v>46154.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46150.52569444444</v>
+        <v>46154.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46150.53611111111</v>
+        <v>46154.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46150.54652777778</v>
+        <v>46154.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46150.55694444444</v>
+        <v>46154.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46150.56736111111</v>
+        <v>46154.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46150.57777777778</v>
+        <v>46154.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46150.58819444444</v>
+        <v>46154.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46150.59861111111</v>
+        <v>46154.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46150.60902777778</v>
+        <v>46154.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46150.61944444444</v>
+        <v>46154.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46150.62986111111</v>
+        <v>46154.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46150.64027777778</v>
+        <v>46154.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46150.65069444444</v>
+        <v>46154.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46150.66111111111</v>
+        <v>46154.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46150.67152777778</v>
+        <v>46154.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46150.68194444444</v>
+        <v>46154.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46150.69236111111</v>
+        <v>46154.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46150.70277777778</v>
+        <v>46154.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46150.71319444444</v>
+        <v>46154.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46150.72361111111</v>
+        <v>46154.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46150.73402777778</v>
+        <v>46154.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46150.74444444444</v>
+        <v>46154.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46150.75486111111</v>
+        <v>46154.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46150.76527777778</v>
+        <v>46154.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46150.77569444444</v>
+        <v>46154.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46150.78611111111</v>
+        <v>46154.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46150.79652777778</v>
+        <v>46154.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46150.80694444444</v>
+        <v>46154.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46150.81736111111</v>
+        <v>46154.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46150.82777777778</v>
+        <v>46154.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46150.83819444444</v>
+        <v>46154.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46150.84861111111</v>
+        <v>46154.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46150.85902777778</v>
+        <v>46154.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46150.86944444444</v>
+        <v>46154.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46150.87986111111</v>
+        <v>46154.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46150.89027777778</v>
+        <v>46154.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46150.90069444444</v>
+        <v>46154.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46150.91111111111</v>
+        <v>46154.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46150.92152777778</v>
+        <v>46154.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46150.93194444444</v>
+        <v>46154.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46150.94236111111</v>
+        <v>46154.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46150.95277777778</v>
+        <v>46154.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46150.96319444444</v>
+        <v>46154.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46150.97361111111</v>
+        <v>46154.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46150.98402777778</v>
+        <v>46154.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46150.99444444444</v>
+        <v>46154.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46151.00486111111</v>
+        <v>46155.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46151.01527777778</v>
+        <v>46155.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46151.02569444444</v>
+        <v>46155.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46151.03611111111</v>
+        <v>46155.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,583 +31,583 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.05.20261</t>
-  </si>
-  <si>
-    <t>11.05.20262</t>
-  </si>
-  <si>
-    <t>11.05.20263</t>
-  </si>
-  <si>
-    <t>11.05.20264</t>
-  </si>
-  <si>
-    <t>11.05.20265</t>
-  </si>
-  <si>
-    <t>11.05.20266</t>
-  </si>
-  <si>
-    <t>11.05.20267</t>
-  </si>
-  <si>
-    <t>11.05.20268</t>
-  </si>
-  <si>
-    <t>11.05.20269</t>
-  </si>
-  <si>
-    <t>11.05.202610</t>
-  </si>
-  <si>
-    <t>11.05.202611</t>
-  </si>
-  <si>
-    <t>11.05.202612</t>
-  </si>
-  <si>
-    <t>11.05.202613</t>
-  </si>
-  <si>
-    <t>11.05.202614</t>
-  </si>
-  <si>
-    <t>11.05.202615</t>
-  </si>
-  <si>
-    <t>11.05.202616</t>
-  </si>
-  <si>
-    <t>11.05.202617</t>
-  </si>
-  <si>
-    <t>11.05.202618</t>
-  </si>
-  <si>
-    <t>11.05.202619</t>
-  </si>
-  <si>
-    <t>11.05.202620</t>
-  </si>
-  <si>
-    <t>11.05.202621</t>
-  </si>
-  <si>
-    <t>11.05.202622</t>
-  </si>
-  <si>
-    <t>11.05.202623</t>
-  </si>
-  <si>
-    <t>11.05.202624</t>
-  </si>
-  <si>
-    <t>11.05.202625</t>
-  </si>
-  <si>
-    <t>11.05.202626</t>
-  </si>
-  <si>
-    <t>11.05.202627</t>
-  </si>
-  <si>
-    <t>11.05.202628</t>
-  </si>
-  <si>
-    <t>11.05.202629</t>
-  </si>
-  <si>
-    <t>11.05.202630</t>
-  </si>
-  <si>
-    <t>11.05.202631</t>
-  </si>
-  <si>
-    <t>11.05.202632</t>
-  </si>
-  <si>
-    <t>11.05.202633</t>
-  </si>
-  <si>
-    <t>11.05.202634</t>
-  </si>
-  <si>
-    <t>11.05.202635</t>
-  </si>
-  <si>
-    <t>11.05.202636</t>
-  </si>
-  <si>
-    <t>11.05.202637</t>
-  </si>
-  <si>
-    <t>11.05.202638</t>
-  </si>
-  <si>
-    <t>11.05.202639</t>
-  </si>
-  <si>
-    <t>11.05.202640</t>
-  </si>
-  <si>
-    <t>11.05.202641</t>
-  </si>
-  <si>
-    <t>11.05.202642</t>
-  </si>
-  <si>
-    <t>11.05.202643</t>
-  </si>
-  <si>
-    <t>11.05.202644</t>
-  </si>
-  <si>
-    <t>11.05.202645</t>
-  </si>
-  <si>
-    <t>11.05.202646</t>
-  </si>
-  <si>
-    <t>11.05.202647</t>
-  </si>
-  <si>
-    <t>11.05.202648</t>
-  </si>
-  <si>
-    <t>11.05.202649</t>
-  </si>
-  <si>
-    <t>11.05.202650</t>
-  </si>
-  <si>
-    <t>11.05.202651</t>
-  </si>
-  <si>
-    <t>11.05.202652</t>
-  </si>
-  <si>
-    <t>11.05.202653</t>
-  </si>
-  <si>
-    <t>11.05.202654</t>
-  </si>
-  <si>
-    <t>11.05.202655</t>
-  </si>
-  <si>
-    <t>11.05.202656</t>
-  </si>
-  <si>
-    <t>11.05.202657</t>
-  </si>
-  <si>
-    <t>11.05.202658</t>
-  </si>
-  <si>
-    <t>11.05.202659</t>
-  </si>
-  <si>
-    <t>11.05.202660</t>
-  </si>
-  <si>
-    <t>11.05.202661</t>
-  </si>
-  <si>
-    <t>11.05.202662</t>
-  </si>
-  <si>
-    <t>11.05.202663</t>
-  </si>
-  <si>
-    <t>11.05.202664</t>
-  </si>
-  <si>
-    <t>11.05.202665</t>
-  </si>
-  <si>
-    <t>11.05.202666</t>
-  </si>
-  <si>
-    <t>11.05.202667</t>
-  </si>
-  <si>
-    <t>11.05.202668</t>
-  </si>
-  <si>
-    <t>11.05.202669</t>
-  </si>
-  <si>
-    <t>11.05.202670</t>
-  </si>
-  <si>
-    <t>11.05.202671</t>
-  </si>
-  <si>
-    <t>11.05.202672</t>
-  </si>
-  <si>
-    <t>11.05.202673</t>
-  </si>
-  <si>
-    <t>11.05.202674</t>
-  </si>
-  <si>
-    <t>11.05.202675</t>
-  </si>
-  <si>
-    <t>11.05.202676</t>
-  </si>
-  <si>
-    <t>11.05.202677</t>
-  </si>
-  <si>
-    <t>11.05.202678</t>
-  </si>
-  <si>
-    <t>11.05.202679</t>
-  </si>
-  <si>
-    <t>11.05.202680</t>
-  </si>
-  <si>
-    <t>11.05.202681</t>
-  </si>
-  <si>
-    <t>11.05.202682</t>
-  </si>
-  <si>
-    <t>11.05.202683</t>
-  </si>
-  <si>
-    <t>11.05.202684</t>
-  </si>
-  <si>
-    <t>11.05.202685</t>
-  </si>
-  <si>
-    <t>11.05.202686</t>
-  </si>
-  <si>
-    <t>11.05.202687</t>
-  </si>
-  <si>
-    <t>11.05.202688</t>
-  </si>
-  <si>
-    <t>11.05.202689</t>
-  </si>
-  <si>
-    <t>11.05.202690</t>
-  </si>
-  <si>
-    <t>11.05.202691</t>
-  </si>
-  <si>
-    <t>11.05.202692</t>
-  </si>
-  <si>
-    <t>11.05.202693</t>
-  </si>
-  <si>
-    <t>12.05.202694</t>
-  </si>
-  <si>
-    <t>12.05.202695</t>
-  </si>
-  <si>
-    <t>12.05.202696</t>
-  </si>
-  <si>
-    <t>12.05.20261</t>
-  </si>
-  <si>
-    <t>12.05.20262</t>
-  </si>
-  <si>
-    <t>12.05.20263</t>
-  </si>
-  <si>
-    <t>12.05.20264</t>
-  </si>
-  <si>
-    <t>12.05.20265</t>
-  </si>
-  <si>
-    <t>12.05.20266</t>
-  </si>
-  <si>
-    <t>12.05.20267</t>
-  </si>
-  <si>
-    <t>12.05.20268</t>
-  </si>
-  <si>
-    <t>12.05.20269</t>
-  </si>
-  <si>
-    <t>12.05.202610</t>
-  </si>
-  <si>
-    <t>12.05.202611</t>
-  </si>
-  <si>
-    <t>12.05.202612</t>
-  </si>
-  <si>
-    <t>12.05.202613</t>
-  </si>
-  <si>
-    <t>12.05.202614</t>
-  </si>
-  <si>
-    <t>12.05.202615</t>
-  </si>
-  <si>
-    <t>12.05.202616</t>
-  </si>
-  <si>
-    <t>12.05.202617</t>
-  </si>
-  <si>
-    <t>12.05.202618</t>
-  </si>
-  <si>
-    <t>12.05.202619</t>
-  </si>
-  <si>
-    <t>12.05.202620</t>
-  </si>
-  <si>
-    <t>12.05.202621</t>
-  </si>
-  <si>
-    <t>12.05.202622</t>
-  </si>
-  <si>
-    <t>12.05.202623</t>
-  </si>
-  <si>
-    <t>12.05.202624</t>
-  </si>
-  <si>
-    <t>12.05.202625</t>
-  </si>
-  <si>
-    <t>12.05.202626</t>
-  </si>
-  <si>
-    <t>12.05.202627</t>
-  </si>
-  <si>
-    <t>12.05.202628</t>
-  </si>
-  <si>
-    <t>12.05.202629</t>
-  </si>
-  <si>
-    <t>12.05.202630</t>
-  </si>
-  <si>
-    <t>12.05.202631</t>
-  </si>
-  <si>
-    <t>12.05.202632</t>
-  </si>
-  <si>
-    <t>12.05.202633</t>
-  </si>
-  <si>
-    <t>12.05.202634</t>
-  </si>
-  <si>
-    <t>12.05.202635</t>
-  </si>
-  <si>
-    <t>12.05.202636</t>
-  </si>
-  <si>
-    <t>12.05.202637</t>
-  </si>
-  <si>
-    <t>12.05.202638</t>
-  </si>
-  <si>
-    <t>12.05.202639</t>
-  </si>
-  <si>
-    <t>12.05.202640</t>
-  </si>
-  <si>
-    <t>12.05.202641</t>
-  </si>
-  <si>
-    <t>12.05.202642</t>
-  </si>
-  <si>
-    <t>12.05.202643</t>
-  </si>
-  <si>
-    <t>12.05.202644</t>
-  </si>
-  <si>
-    <t>12.05.202645</t>
-  </si>
-  <si>
-    <t>12.05.202646</t>
-  </si>
-  <si>
-    <t>12.05.202647</t>
-  </si>
-  <si>
-    <t>12.05.202648</t>
-  </si>
-  <si>
-    <t>12.05.202649</t>
-  </si>
-  <si>
-    <t>12.05.202650</t>
-  </si>
-  <si>
-    <t>12.05.202651</t>
-  </si>
-  <si>
-    <t>12.05.202652</t>
-  </si>
-  <si>
-    <t>12.05.202653</t>
-  </si>
-  <si>
-    <t>12.05.202654</t>
-  </si>
-  <si>
-    <t>12.05.202655</t>
-  </si>
-  <si>
-    <t>12.05.202656</t>
-  </si>
-  <si>
-    <t>12.05.202657</t>
-  </si>
-  <si>
-    <t>12.05.202658</t>
-  </si>
-  <si>
-    <t>12.05.202659</t>
-  </si>
-  <si>
-    <t>12.05.202660</t>
-  </si>
-  <si>
-    <t>12.05.202661</t>
-  </si>
-  <si>
-    <t>12.05.202662</t>
-  </si>
-  <si>
-    <t>12.05.202663</t>
-  </si>
-  <si>
-    <t>12.05.202664</t>
-  </si>
-  <si>
-    <t>12.05.202665</t>
-  </si>
-  <si>
-    <t>12.05.202666</t>
-  </si>
-  <si>
-    <t>12.05.202667</t>
-  </si>
-  <si>
-    <t>12.05.202668</t>
-  </si>
-  <si>
-    <t>12.05.202669</t>
-  </si>
-  <si>
-    <t>12.05.202670</t>
-  </si>
-  <si>
-    <t>12.05.202671</t>
-  </si>
-  <si>
-    <t>12.05.202672</t>
-  </si>
-  <si>
-    <t>12.05.202673</t>
-  </si>
-  <si>
-    <t>12.05.202674</t>
-  </si>
-  <si>
-    <t>12.05.202675</t>
-  </si>
-  <si>
-    <t>12.05.202676</t>
-  </si>
-  <si>
-    <t>12.05.202677</t>
-  </si>
-  <si>
-    <t>12.05.202678</t>
-  </si>
-  <si>
-    <t>12.05.202679</t>
-  </si>
-  <si>
-    <t>12.05.202680</t>
-  </si>
-  <si>
-    <t>12.05.202681</t>
-  </si>
-  <si>
-    <t>12.05.202682</t>
-  </si>
-  <si>
-    <t>12.05.202683</t>
-  </si>
-  <si>
-    <t>12.05.202684</t>
-  </si>
-  <si>
-    <t>12.05.202685</t>
-  </si>
-  <si>
-    <t>12.05.202686</t>
-  </si>
-  <si>
-    <t>12.05.202687</t>
-  </si>
-  <si>
-    <t>12.05.202688</t>
-  </si>
-  <si>
-    <t>12.05.202689</t>
-  </si>
-  <si>
-    <t>12.05.202690</t>
-  </si>
-  <si>
-    <t>12.05.202691</t>
-  </si>
-  <si>
-    <t>12.05.202692</t>
-  </si>
-  <si>
-    <t>12.05.202693</t>
-  </si>
-  <si>
-    <t>13.05.202695</t>
-  </si>
-  <si>
-    <t>13.05.202696</t>
-  </si>
-  <si>
     <t>13.05.20261</t>
   </si>
   <si>
     <t>13.05.20262</t>
+  </si>
+  <si>
+    <t>13.05.20263</t>
+  </si>
+  <si>
+    <t>13.05.20264</t>
+  </si>
+  <si>
+    <t>13.05.20265</t>
+  </si>
+  <si>
+    <t>13.05.20266</t>
+  </si>
+  <si>
+    <t>13.05.20267</t>
+  </si>
+  <si>
+    <t>13.05.20268</t>
+  </si>
+  <si>
+    <t>13.05.20269</t>
+  </si>
+  <si>
+    <t>13.05.202610</t>
+  </si>
+  <si>
+    <t>13.05.202611</t>
+  </si>
+  <si>
+    <t>13.05.202612</t>
+  </si>
+  <si>
+    <t>13.05.202613</t>
+  </si>
+  <si>
+    <t>13.05.202614</t>
+  </si>
+  <si>
+    <t>13.05.202615</t>
+  </si>
+  <si>
+    <t>13.05.202616</t>
+  </si>
+  <si>
+    <t>13.05.202617</t>
+  </si>
+  <si>
+    <t>13.05.202618</t>
+  </si>
+  <si>
+    <t>13.05.202619</t>
+  </si>
+  <si>
+    <t>13.05.202620</t>
+  </si>
+  <si>
+    <t>13.05.202621</t>
+  </si>
+  <si>
+    <t>13.05.202622</t>
+  </si>
+  <si>
+    <t>13.05.202623</t>
+  </si>
+  <si>
+    <t>13.05.202624</t>
+  </si>
+  <si>
+    <t>13.05.202625</t>
+  </si>
+  <si>
+    <t>13.05.202626</t>
+  </si>
+  <si>
+    <t>13.05.202627</t>
+  </si>
+  <si>
+    <t>13.05.202628</t>
+  </si>
+  <si>
+    <t>13.05.202629</t>
+  </si>
+  <si>
+    <t>13.05.202630</t>
+  </si>
+  <si>
+    <t>13.05.202631</t>
+  </si>
+  <si>
+    <t>13.05.202632</t>
+  </si>
+  <si>
+    <t>13.05.202633</t>
+  </si>
+  <si>
+    <t>13.05.202634</t>
+  </si>
+  <si>
+    <t>13.05.202635</t>
+  </si>
+  <si>
+    <t>13.05.202636</t>
+  </si>
+  <si>
+    <t>13.05.202637</t>
+  </si>
+  <si>
+    <t>13.05.202638</t>
+  </si>
+  <si>
+    <t>13.05.202639</t>
+  </si>
+  <si>
+    <t>13.05.202640</t>
+  </si>
+  <si>
+    <t>13.05.202641</t>
+  </si>
+  <si>
+    <t>13.05.202642</t>
+  </si>
+  <si>
+    <t>13.05.202643</t>
+  </si>
+  <si>
+    <t>13.05.202644</t>
+  </si>
+  <si>
+    <t>13.05.202645</t>
+  </si>
+  <si>
+    <t>13.05.202646</t>
+  </si>
+  <si>
+    <t>13.05.202647</t>
+  </si>
+  <si>
+    <t>13.05.202648</t>
+  </si>
+  <si>
+    <t>13.05.202649</t>
+  </si>
+  <si>
+    <t>13.05.202650</t>
+  </si>
+  <si>
+    <t>13.05.202651</t>
+  </si>
+  <si>
+    <t>13.05.202652</t>
+  </si>
+  <si>
+    <t>13.05.202653</t>
+  </si>
+  <si>
+    <t>13.05.202654</t>
+  </si>
+  <si>
+    <t>13.05.202655</t>
+  </si>
+  <si>
+    <t>13.05.202656</t>
+  </si>
+  <si>
+    <t>13.05.202657</t>
+  </si>
+  <si>
+    <t>13.05.202658</t>
+  </si>
+  <si>
+    <t>13.05.202659</t>
+  </si>
+  <si>
+    <t>13.05.202660</t>
+  </si>
+  <si>
+    <t>13.05.202661</t>
+  </si>
+  <si>
+    <t>13.05.202662</t>
+  </si>
+  <si>
+    <t>13.05.202663</t>
+  </si>
+  <si>
+    <t>13.05.202664</t>
+  </si>
+  <si>
+    <t>13.05.202665</t>
+  </si>
+  <si>
+    <t>13.05.202666</t>
+  </si>
+  <si>
+    <t>13.05.202667</t>
+  </si>
+  <si>
+    <t>13.05.202668</t>
+  </si>
+  <si>
+    <t>13.05.202669</t>
+  </si>
+  <si>
+    <t>13.05.202670</t>
+  </si>
+  <si>
+    <t>13.05.202671</t>
+  </si>
+  <si>
+    <t>13.05.202672</t>
+  </si>
+  <si>
+    <t>13.05.202673</t>
+  </si>
+  <si>
+    <t>13.05.202674</t>
+  </si>
+  <si>
+    <t>13.05.202675</t>
+  </si>
+  <si>
+    <t>13.05.202676</t>
+  </si>
+  <si>
+    <t>13.05.202677</t>
+  </si>
+  <si>
+    <t>13.05.202678</t>
+  </si>
+  <si>
+    <t>13.05.202679</t>
+  </si>
+  <si>
+    <t>13.05.202680</t>
+  </si>
+  <si>
+    <t>13.05.202681</t>
+  </si>
+  <si>
+    <t>13.05.202682</t>
+  </si>
+  <si>
+    <t>13.05.202683</t>
+  </si>
+  <si>
+    <t>13.05.202684</t>
+  </si>
+  <si>
+    <t>13.05.202685</t>
+  </si>
+  <si>
+    <t>13.05.202686</t>
+  </si>
+  <si>
+    <t>13.05.202687</t>
+  </si>
+  <si>
+    <t>13.05.202688</t>
+  </si>
+  <si>
+    <t>13.05.202689</t>
+  </si>
+  <si>
+    <t>13.05.202690</t>
+  </si>
+  <si>
+    <t>13.05.202691</t>
+  </si>
+  <si>
+    <t>13.05.202692</t>
+  </si>
+  <si>
+    <t>13.05.202693</t>
+  </si>
+  <si>
+    <t>14.05.202694</t>
+  </si>
+  <si>
+    <t>14.05.202695</t>
+  </si>
+  <si>
+    <t>14.05.202696</t>
+  </si>
+  <si>
+    <t>14.05.20261</t>
+  </si>
+  <si>
+    <t>14.05.20262</t>
+  </si>
+  <si>
+    <t>14.05.20263</t>
+  </si>
+  <si>
+    <t>14.05.20264</t>
+  </si>
+  <si>
+    <t>14.05.20265</t>
+  </si>
+  <si>
+    <t>14.05.20266</t>
+  </si>
+  <si>
+    <t>14.05.20267</t>
+  </si>
+  <si>
+    <t>14.05.20268</t>
+  </si>
+  <si>
+    <t>14.05.20269</t>
+  </si>
+  <si>
+    <t>14.05.202610</t>
+  </si>
+  <si>
+    <t>14.05.202611</t>
+  </si>
+  <si>
+    <t>14.05.202612</t>
+  </si>
+  <si>
+    <t>14.05.202613</t>
+  </si>
+  <si>
+    <t>14.05.202614</t>
+  </si>
+  <si>
+    <t>14.05.202615</t>
+  </si>
+  <si>
+    <t>14.05.202616</t>
+  </si>
+  <si>
+    <t>14.05.202617</t>
+  </si>
+  <si>
+    <t>14.05.202618</t>
+  </si>
+  <si>
+    <t>14.05.202619</t>
+  </si>
+  <si>
+    <t>14.05.202620</t>
+  </si>
+  <si>
+    <t>14.05.202621</t>
+  </si>
+  <si>
+    <t>14.05.202622</t>
+  </si>
+  <si>
+    <t>14.05.202623</t>
+  </si>
+  <si>
+    <t>14.05.202624</t>
+  </si>
+  <si>
+    <t>14.05.202625</t>
+  </si>
+  <si>
+    <t>14.05.202626</t>
+  </si>
+  <si>
+    <t>14.05.202627</t>
+  </si>
+  <si>
+    <t>14.05.202628</t>
+  </si>
+  <si>
+    <t>14.05.202629</t>
+  </si>
+  <si>
+    <t>14.05.202630</t>
+  </si>
+  <si>
+    <t>14.05.202631</t>
+  </si>
+  <si>
+    <t>14.05.202632</t>
+  </si>
+  <si>
+    <t>14.05.202633</t>
+  </si>
+  <si>
+    <t>14.05.202634</t>
+  </si>
+  <si>
+    <t>14.05.202635</t>
+  </si>
+  <si>
+    <t>14.05.202636</t>
+  </si>
+  <si>
+    <t>14.05.202637</t>
+  </si>
+  <si>
+    <t>14.05.202638</t>
+  </si>
+  <si>
+    <t>14.05.202639</t>
+  </si>
+  <si>
+    <t>14.05.202640</t>
+  </si>
+  <si>
+    <t>14.05.202641</t>
+  </si>
+  <si>
+    <t>14.05.202642</t>
+  </si>
+  <si>
+    <t>14.05.202643</t>
+  </si>
+  <si>
+    <t>14.05.202644</t>
+  </si>
+  <si>
+    <t>14.05.202645</t>
+  </si>
+  <si>
+    <t>14.05.202646</t>
+  </si>
+  <si>
+    <t>14.05.202647</t>
+  </si>
+  <si>
+    <t>14.05.202648</t>
+  </si>
+  <si>
+    <t>14.05.202649</t>
+  </si>
+  <si>
+    <t>14.05.202650</t>
+  </si>
+  <si>
+    <t>14.05.202651</t>
+  </si>
+  <si>
+    <t>14.05.202652</t>
+  </si>
+  <si>
+    <t>14.05.202653</t>
+  </si>
+  <si>
+    <t>14.05.202654</t>
+  </si>
+  <si>
+    <t>14.05.202655</t>
+  </si>
+  <si>
+    <t>14.05.202656</t>
+  </si>
+  <si>
+    <t>14.05.202657</t>
+  </si>
+  <si>
+    <t>14.05.202658</t>
+  </si>
+  <si>
+    <t>14.05.202659</t>
+  </si>
+  <si>
+    <t>14.05.202660</t>
+  </si>
+  <si>
+    <t>14.05.202661</t>
+  </si>
+  <si>
+    <t>14.05.202662</t>
+  </si>
+  <si>
+    <t>14.05.202663</t>
+  </si>
+  <si>
+    <t>14.05.202664</t>
+  </si>
+  <si>
+    <t>14.05.202665</t>
+  </si>
+  <si>
+    <t>14.05.202666</t>
+  </si>
+  <si>
+    <t>14.05.202667</t>
+  </si>
+  <si>
+    <t>14.05.202668</t>
+  </si>
+  <si>
+    <t>14.05.202669</t>
+  </si>
+  <si>
+    <t>14.05.202670</t>
+  </si>
+  <si>
+    <t>14.05.202671</t>
+  </si>
+  <si>
+    <t>14.05.202672</t>
+  </si>
+  <si>
+    <t>14.05.202673</t>
+  </si>
+  <si>
+    <t>14.05.202674</t>
+  </si>
+  <si>
+    <t>14.05.202675</t>
+  </si>
+  <si>
+    <t>14.05.202676</t>
+  </si>
+  <si>
+    <t>14.05.202677</t>
+  </si>
+  <si>
+    <t>14.05.202678</t>
+  </si>
+  <si>
+    <t>14.05.202679</t>
+  </si>
+  <si>
+    <t>14.05.202680</t>
+  </si>
+  <si>
+    <t>14.05.202681</t>
+  </si>
+  <si>
+    <t>14.05.202682</t>
+  </si>
+  <si>
+    <t>14.05.202683</t>
+  </si>
+  <si>
+    <t>14.05.202684</t>
+  </si>
+  <si>
+    <t>14.05.202685</t>
+  </si>
+  <si>
+    <t>14.05.202686</t>
+  </si>
+  <si>
+    <t>14.05.202687</t>
+  </si>
+  <si>
+    <t>14.05.202688</t>
+  </si>
+  <si>
+    <t>14.05.202689</t>
+  </si>
+  <si>
+    <t>14.05.202690</t>
+  </si>
+  <si>
+    <t>14.05.202691</t>
+  </si>
+  <si>
+    <t>14.05.202692</t>
+  </si>
+  <si>
+    <t>14.05.202693</t>
+  </si>
+  <si>
+    <t>15.05.202695</t>
+  </si>
+  <si>
+    <t>15.05.202696</t>
+  </si>
+  <si>
+    <t>15.05.20261</t>
+  </si>
+  <si>
+    <t>15.05.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46153.03611111111</v>
+        <v>46155.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46153.04652777778</v>
+        <v>46155.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46153.05694444444</v>
+        <v>46155.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46153.06736111111</v>
+        <v>46155.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46153.07777777778</v>
+        <v>46155.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46153.08819444444</v>
+        <v>46155.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46153.09861111111</v>
+        <v>46155.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46153.10902777778</v>
+        <v>46155.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46153.11944444444</v>
+        <v>46155.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46153.12986111111</v>
+        <v>46155.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46153.14027777778</v>
+        <v>46155.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46153.15069444444</v>
+        <v>46155.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46153.16111111111</v>
+        <v>46155.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46153.17152777778</v>
+        <v>46155.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46153.18194444444</v>
+        <v>46155.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46153.19236111111</v>
+        <v>46155.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46153.20277777778</v>
+        <v>46155.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46153.21319444444</v>
+        <v>46155.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46153.22361111111</v>
+        <v>46155.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46153.23402777778</v>
+        <v>46155.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46153.24444444444</v>
+        <v>46155.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46153.25486111111</v>
+        <v>46155.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46153.26527777778</v>
+        <v>46155.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46153.27569444444</v>
+        <v>46155.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46153.28611111111</v>
+        <v>46155.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46153.29652777778</v>
+        <v>46155.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46153.30694444444</v>
+        <v>46155.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46153.31736111111</v>
+        <v>46155.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46153.32777777778</v>
+        <v>46155.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46153.33819444444</v>
+        <v>46155.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46153.34861111111</v>
+        <v>46155.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46153.35902777778</v>
+        <v>46155.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46153.36944444444</v>
+        <v>46155.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46153.37986111111</v>
+        <v>46155.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46153.39027777778</v>
+        <v>46155.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46153.40069444444</v>
+        <v>46155.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46153.41111111111</v>
+        <v>46155.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46153.42152777778</v>
+        <v>46155.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46153.43194444444</v>
+        <v>46155.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46153.44236111111</v>
+        <v>46155.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46153.45277777778</v>
+        <v>46155.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46153.46319444444</v>
+        <v>46155.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46153.47361111111</v>
+        <v>46155.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46153.48402777778</v>
+        <v>46155.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46153.49444444444</v>
+        <v>46155.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46153.50486111111</v>
+        <v>46155.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46153.51527777778</v>
+        <v>46155.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46153.52569444444</v>
+        <v>46155.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46153.53611111111</v>
+        <v>46155.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46153.54652777778</v>
+        <v>46155.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46153.55694444444</v>
+        <v>46155.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46153.56736111111</v>
+        <v>46155.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46153.57777777778</v>
+        <v>46155.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46153.58819444444</v>
+        <v>46155.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46153.59861111111</v>
+        <v>46155.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46153.60902777778</v>
+        <v>46155.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46153.61944444444</v>
+        <v>46155.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46153.62986111111</v>
+        <v>46155.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46153.64027777778</v>
+        <v>46155.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46153.65069444444</v>
+        <v>46155.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46153.66111111111</v>
+        <v>46155.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46153.67152777778</v>
+        <v>46155.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46153.68194444444</v>
+        <v>46155.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46153.69236111111</v>
+        <v>46155.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46153.70277777778</v>
+        <v>46155.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46153.71319444444</v>
+        <v>46155.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46153.72361111111</v>
+        <v>46155.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46153.73402777778</v>
+        <v>46155.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46153.74444444444</v>
+        <v>46155.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46153.75486111111</v>
+        <v>46155.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46153.76527777778</v>
+        <v>46155.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46153.77569444444</v>
+        <v>46155.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46153.78611111111</v>
+        <v>46155.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46153.79652777778</v>
+        <v>46155.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46153.80694444444</v>
+        <v>46155.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46153.81736111111</v>
+        <v>46155.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46153.82777777778</v>
+        <v>46155.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46153.83819444444</v>
+        <v>46155.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46153.84861111111</v>
+        <v>46155.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46153.85902777778</v>
+        <v>46155.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46153.86944444444</v>
+        <v>46155.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46153.87986111111</v>
+        <v>46155.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46153.89027777778</v>
+        <v>46155.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46153.90069444444</v>
+        <v>46155.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46153.91111111111</v>
+        <v>46155.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46153.92152777778</v>
+        <v>46155.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46153.93194444444</v>
+        <v>46155.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46153.94236111111</v>
+        <v>46155.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46153.95277777778</v>
+        <v>46155.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46153.96319444444</v>
+        <v>46155.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46153.97361111111</v>
+        <v>46155.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46153.98402777778</v>
+        <v>46155.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46153.99444444444</v>
+        <v>46155.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46154.00486111111</v>
+        <v>46156.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46154.01527777778</v>
+        <v>46156.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46154.02569444444</v>
+        <v>46156.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46154.03611111111</v>
+        <v>46156.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46154.03611111111</v>
+        <v>46156.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46154.04652777778</v>
+        <v>46156.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46154.05694444444</v>
+        <v>46156.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46154.06736111111</v>
+        <v>46156.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46154.07777777778</v>
+        <v>46156.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46154.08819444444</v>
+        <v>46156.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46154.09861111111</v>
+        <v>46156.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46154.10902777778</v>
+        <v>46156.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46154.11944444444</v>
+        <v>46156.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46154.12986111111</v>
+        <v>46156.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46154.14027777778</v>
+        <v>46156.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46154.15069444444</v>
+        <v>46156.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46154.16111111111</v>
+        <v>46156.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46154.17152777778</v>
+        <v>46156.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46154.18194444444</v>
+        <v>46156.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46154.19236111111</v>
+        <v>46156.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46154.20277777778</v>
+        <v>46156.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46154.21319444444</v>
+        <v>46156.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46154.22361111111</v>
+        <v>46156.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46154.23402777778</v>
+        <v>46156.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46154.24444444444</v>
+        <v>46156.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46154.25486111111</v>
+        <v>46156.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46154.26527777778</v>
+        <v>46156.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46154.27569444444</v>
+        <v>46156.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46154.28611111111</v>
+        <v>46156.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46154.29652777778</v>
+        <v>46156.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46154.30694444444</v>
+        <v>46156.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46154.31736111111</v>
+        <v>46156.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46154.32777777778</v>
+        <v>46156.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46154.33819444444</v>
+        <v>46156.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46154.34861111111</v>
+        <v>46156.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46154.35902777778</v>
+        <v>46156.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46154.36944444444</v>
+        <v>46156.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46154.37986111111</v>
+        <v>46156.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46154.39027777778</v>
+        <v>46156.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46154.40069444444</v>
+        <v>46156.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46154.41111111111</v>
+        <v>46156.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46154.42152777778</v>
+        <v>46156.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46154.43194444444</v>
+        <v>46156.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46154.44236111111</v>
+        <v>46156.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46154.45277777778</v>
+        <v>46156.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46154.46319444444</v>
+        <v>46156.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46154.47361111111</v>
+        <v>46156.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46154.48402777778</v>
+        <v>46156.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46154.49444444444</v>
+        <v>46156.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46154.50486111111</v>
+        <v>46156.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46154.51527777778</v>
+        <v>46156.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46154.52569444444</v>
+        <v>46156.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46154.53611111111</v>
+        <v>46156.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46154.54652777778</v>
+        <v>46156.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46154.55694444444</v>
+        <v>46156.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46154.56736111111</v>
+        <v>46156.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46154.57777777778</v>
+        <v>46156.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46154.58819444444</v>
+        <v>46156.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46154.59861111111</v>
+        <v>46156.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46154.60902777778</v>
+        <v>46156.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46154.61944444444</v>
+        <v>46156.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46154.62986111111</v>
+        <v>46156.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46154.64027777778</v>
+        <v>46156.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46154.65069444444</v>
+        <v>46156.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46154.66111111111</v>
+        <v>46156.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46154.67152777778</v>
+        <v>46156.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46154.68194444444</v>
+        <v>46156.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46154.69236111111</v>
+        <v>46156.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46154.70277777778</v>
+        <v>46156.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46154.71319444444</v>
+        <v>46156.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46154.72361111111</v>
+        <v>46156.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46154.73402777778</v>
+        <v>46156.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46154.74444444444</v>
+        <v>46156.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46154.75486111111</v>
+        <v>46156.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46154.76527777778</v>
+        <v>46156.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46154.77569444444</v>
+        <v>46156.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46154.78611111111</v>
+        <v>46156.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46154.79652777778</v>
+        <v>46156.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46154.80694444444</v>
+        <v>46156.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46154.81736111111</v>
+        <v>46156.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46154.82777777778</v>
+        <v>46156.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46154.83819444444</v>
+        <v>46156.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46154.84861111111</v>
+        <v>46156.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46154.85902777778</v>
+        <v>46156.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46154.86944444444</v>
+        <v>46156.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46154.87986111111</v>
+        <v>46156.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46154.89027777778</v>
+        <v>46156.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46154.90069444444</v>
+        <v>46156.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46154.91111111111</v>
+        <v>46156.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46154.92152777778</v>
+        <v>46156.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46154.93194444444</v>
+        <v>46156.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46154.94236111111</v>
+        <v>46156.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46154.95277777778</v>
+        <v>46156.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46154.96319444444</v>
+        <v>46156.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46154.97361111111</v>
+        <v>46156.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46154.98402777778</v>
+        <v>46156.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46154.99444444444</v>
+        <v>46156.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46155.00486111111</v>
+        <v>46157.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46155.01527777778</v>
+        <v>46157.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46155.02569444444</v>
+        <v>46157.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46155.03611111111</v>
+        <v>46157.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>13.05.20261</t>
-  </si>
-  <si>
-    <t>13.05.20262</t>
-  </si>
-  <si>
-    <t>13.05.20263</t>
-  </si>
-  <si>
-    <t>13.05.20264</t>
-  </si>
-  <si>
-    <t>13.05.20265</t>
-  </si>
-  <si>
-    <t>13.05.20266</t>
-  </si>
-  <si>
-    <t>13.05.20267</t>
-  </si>
-  <si>
-    <t>13.05.20268</t>
-  </si>
-  <si>
-    <t>13.05.20269</t>
-  </si>
-  <si>
-    <t>13.05.202610</t>
-  </si>
-  <si>
-    <t>13.05.202611</t>
-  </si>
-  <si>
-    <t>13.05.202612</t>
-  </si>
-  <si>
-    <t>13.05.202613</t>
-  </si>
-  <si>
-    <t>13.05.202614</t>
-  </si>
-  <si>
-    <t>13.05.202615</t>
-  </si>
-  <si>
-    <t>13.05.202616</t>
-  </si>
-  <si>
-    <t>13.05.202617</t>
-  </si>
-  <si>
-    <t>13.05.202618</t>
-  </si>
-  <si>
-    <t>13.05.202619</t>
-  </si>
-  <si>
-    <t>13.05.202620</t>
-  </si>
-  <si>
-    <t>13.05.202621</t>
-  </si>
-  <si>
-    <t>13.05.202622</t>
-  </si>
-  <si>
-    <t>13.05.202623</t>
-  </si>
-  <si>
-    <t>13.05.202624</t>
-  </si>
-  <si>
-    <t>13.05.202625</t>
-  </si>
-  <si>
-    <t>13.05.202626</t>
-  </si>
-  <si>
-    <t>13.05.202627</t>
-  </si>
-  <si>
-    <t>13.05.202628</t>
-  </si>
-  <si>
-    <t>13.05.202629</t>
-  </si>
-  <si>
-    <t>13.05.202630</t>
-  </si>
-  <si>
-    <t>13.05.202631</t>
-  </si>
-  <si>
-    <t>13.05.202632</t>
-  </si>
-  <si>
-    <t>13.05.202633</t>
-  </si>
-  <si>
-    <t>13.05.202634</t>
-  </si>
-  <si>
-    <t>13.05.202635</t>
-  </si>
-  <si>
-    <t>13.05.202636</t>
-  </si>
-  <si>
-    <t>13.05.202637</t>
-  </si>
-  <si>
-    <t>13.05.202638</t>
-  </si>
-  <si>
-    <t>13.05.202639</t>
-  </si>
-  <si>
-    <t>13.05.202640</t>
-  </si>
-  <si>
-    <t>13.05.202641</t>
-  </si>
-  <si>
-    <t>13.05.202642</t>
-  </si>
-  <si>
-    <t>13.05.202643</t>
-  </si>
-  <si>
-    <t>13.05.202644</t>
-  </si>
-  <si>
-    <t>13.05.202645</t>
-  </si>
-  <si>
-    <t>13.05.202646</t>
-  </si>
-  <si>
-    <t>13.05.202647</t>
-  </si>
-  <si>
-    <t>13.05.202648</t>
-  </si>
-  <si>
-    <t>13.05.202649</t>
-  </si>
-  <si>
-    <t>13.05.202650</t>
-  </si>
-  <si>
-    <t>13.05.202651</t>
-  </si>
-  <si>
-    <t>13.05.202652</t>
-  </si>
-  <si>
-    <t>13.05.202653</t>
-  </si>
-  <si>
-    <t>13.05.202654</t>
-  </si>
-  <si>
-    <t>13.05.202655</t>
-  </si>
-  <si>
-    <t>13.05.202656</t>
-  </si>
-  <si>
-    <t>13.05.202657</t>
-  </si>
-  <si>
-    <t>13.05.202658</t>
-  </si>
-  <si>
-    <t>13.05.202659</t>
-  </si>
-  <si>
-    <t>13.05.202660</t>
-  </si>
-  <si>
-    <t>13.05.202661</t>
-  </si>
-  <si>
-    <t>13.05.202662</t>
-  </si>
-  <si>
-    <t>13.05.202663</t>
-  </si>
-  <si>
-    <t>13.05.202664</t>
-  </si>
-  <si>
-    <t>13.05.202665</t>
-  </si>
-  <si>
-    <t>13.05.202666</t>
-  </si>
-  <si>
-    <t>13.05.202667</t>
-  </si>
-  <si>
-    <t>13.05.202668</t>
-  </si>
-  <si>
-    <t>13.05.202669</t>
-  </si>
-  <si>
-    <t>13.05.202670</t>
-  </si>
-  <si>
-    <t>13.05.202671</t>
-  </si>
-  <si>
-    <t>13.05.202672</t>
-  </si>
-  <si>
-    <t>13.05.202673</t>
-  </si>
-  <si>
-    <t>13.05.202674</t>
-  </si>
-  <si>
-    <t>13.05.202675</t>
-  </si>
-  <si>
-    <t>13.05.202676</t>
-  </si>
-  <si>
-    <t>13.05.202677</t>
-  </si>
-  <si>
-    <t>13.05.202678</t>
-  </si>
-  <si>
-    <t>13.05.202679</t>
-  </si>
-  <si>
-    <t>13.05.202680</t>
-  </si>
-  <si>
-    <t>13.05.202681</t>
-  </si>
-  <si>
-    <t>13.05.202682</t>
-  </si>
-  <si>
-    <t>13.05.202683</t>
-  </si>
-  <si>
-    <t>13.05.202684</t>
-  </si>
-  <si>
-    <t>13.05.202685</t>
-  </si>
-  <si>
-    <t>13.05.202686</t>
-  </si>
-  <si>
-    <t>13.05.202687</t>
-  </si>
-  <si>
-    <t>13.05.202688</t>
-  </si>
-  <si>
-    <t>13.05.202689</t>
-  </si>
-  <si>
-    <t>13.05.202690</t>
-  </si>
-  <si>
-    <t>13.05.202691</t>
-  </si>
-  <si>
-    <t>13.05.202692</t>
-  </si>
-  <si>
-    <t>13.05.202693</t>
-  </si>
-  <si>
-    <t>14.05.202694</t>
-  </si>
-  <si>
-    <t>14.05.202695</t>
-  </si>
-  <si>
-    <t>14.05.202696</t>
-  </si>
-  <si>
     <t>14.05.20261</t>
   </si>
   <si>
@@ -598,6 +310,9 @@
     <t>14.05.202693</t>
   </si>
   <si>
+    <t>15.05.202694</t>
+  </si>
+  <si>
     <t>15.05.202695</t>
   </si>
   <si>
@@ -608,6 +323,291 @@
   </si>
   <si>
     <t>15.05.20262</t>
+  </si>
+  <si>
+    <t>15.05.20263</t>
+  </si>
+  <si>
+    <t>15.05.20264</t>
+  </si>
+  <si>
+    <t>15.05.20265</t>
+  </si>
+  <si>
+    <t>15.05.20266</t>
+  </si>
+  <si>
+    <t>15.05.20267</t>
+  </si>
+  <si>
+    <t>15.05.20268</t>
+  </si>
+  <si>
+    <t>15.05.20269</t>
+  </si>
+  <si>
+    <t>15.05.202610</t>
+  </si>
+  <si>
+    <t>15.05.202611</t>
+  </si>
+  <si>
+    <t>15.05.202612</t>
+  </si>
+  <si>
+    <t>15.05.202613</t>
+  </si>
+  <si>
+    <t>15.05.202614</t>
+  </si>
+  <si>
+    <t>15.05.202615</t>
+  </si>
+  <si>
+    <t>15.05.202616</t>
+  </si>
+  <si>
+    <t>15.05.202617</t>
+  </si>
+  <si>
+    <t>15.05.202618</t>
+  </si>
+  <si>
+    <t>15.05.202619</t>
+  </si>
+  <si>
+    <t>15.05.202620</t>
+  </si>
+  <si>
+    <t>15.05.202621</t>
+  </si>
+  <si>
+    <t>15.05.202622</t>
+  </si>
+  <si>
+    <t>15.05.202623</t>
+  </si>
+  <si>
+    <t>15.05.202624</t>
+  </si>
+  <si>
+    <t>15.05.202625</t>
+  </si>
+  <si>
+    <t>15.05.202626</t>
+  </si>
+  <si>
+    <t>15.05.202627</t>
+  </si>
+  <si>
+    <t>15.05.202628</t>
+  </si>
+  <si>
+    <t>15.05.202629</t>
+  </si>
+  <si>
+    <t>15.05.202630</t>
+  </si>
+  <si>
+    <t>15.05.202631</t>
+  </si>
+  <si>
+    <t>15.05.202632</t>
+  </si>
+  <si>
+    <t>15.05.202633</t>
+  </si>
+  <si>
+    <t>15.05.202634</t>
+  </si>
+  <si>
+    <t>15.05.202635</t>
+  </si>
+  <si>
+    <t>15.05.202636</t>
+  </si>
+  <si>
+    <t>15.05.202637</t>
+  </si>
+  <si>
+    <t>15.05.202638</t>
+  </si>
+  <si>
+    <t>15.05.202639</t>
+  </si>
+  <si>
+    <t>15.05.202640</t>
+  </si>
+  <si>
+    <t>15.05.202641</t>
+  </si>
+  <si>
+    <t>15.05.202642</t>
+  </si>
+  <si>
+    <t>15.05.202643</t>
+  </si>
+  <si>
+    <t>15.05.202644</t>
+  </si>
+  <si>
+    <t>15.05.202645</t>
+  </si>
+  <si>
+    <t>15.05.202646</t>
+  </si>
+  <si>
+    <t>15.05.202647</t>
+  </si>
+  <si>
+    <t>15.05.202648</t>
+  </si>
+  <si>
+    <t>15.05.202649</t>
+  </si>
+  <si>
+    <t>15.05.202650</t>
+  </si>
+  <si>
+    <t>15.05.202651</t>
+  </si>
+  <si>
+    <t>15.05.202652</t>
+  </si>
+  <si>
+    <t>15.05.202653</t>
+  </si>
+  <si>
+    <t>15.05.202654</t>
+  </si>
+  <si>
+    <t>15.05.202655</t>
+  </si>
+  <si>
+    <t>15.05.202656</t>
+  </si>
+  <si>
+    <t>15.05.202657</t>
+  </si>
+  <si>
+    <t>15.05.202658</t>
+  </si>
+  <si>
+    <t>15.05.202659</t>
+  </si>
+  <si>
+    <t>15.05.202660</t>
+  </si>
+  <si>
+    <t>15.05.202661</t>
+  </si>
+  <si>
+    <t>15.05.202662</t>
+  </si>
+  <si>
+    <t>15.05.202663</t>
+  </si>
+  <si>
+    <t>15.05.202664</t>
+  </si>
+  <si>
+    <t>15.05.202665</t>
+  </si>
+  <si>
+    <t>15.05.202666</t>
+  </si>
+  <si>
+    <t>15.05.202667</t>
+  </si>
+  <si>
+    <t>15.05.202668</t>
+  </si>
+  <si>
+    <t>15.05.202669</t>
+  </si>
+  <si>
+    <t>15.05.202670</t>
+  </si>
+  <si>
+    <t>15.05.202671</t>
+  </si>
+  <si>
+    <t>15.05.202672</t>
+  </si>
+  <si>
+    <t>15.05.202673</t>
+  </si>
+  <si>
+    <t>15.05.202674</t>
+  </si>
+  <si>
+    <t>15.05.202675</t>
+  </si>
+  <si>
+    <t>15.05.202676</t>
+  </si>
+  <si>
+    <t>15.05.202677</t>
+  </si>
+  <si>
+    <t>15.05.202678</t>
+  </si>
+  <si>
+    <t>15.05.202679</t>
+  </si>
+  <si>
+    <t>15.05.202680</t>
+  </si>
+  <si>
+    <t>15.05.202681</t>
+  </si>
+  <si>
+    <t>15.05.202682</t>
+  </si>
+  <si>
+    <t>15.05.202683</t>
+  </si>
+  <si>
+    <t>15.05.202684</t>
+  </si>
+  <si>
+    <t>15.05.202685</t>
+  </si>
+  <si>
+    <t>15.05.202686</t>
+  </si>
+  <si>
+    <t>15.05.202687</t>
+  </si>
+  <si>
+    <t>15.05.202688</t>
+  </si>
+  <si>
+    <t>15.05.202689</t>
+  </si>
+  <si>
+    <t>15.05.202690</t>
+  </si>
+  <si>
+    <t>15.05.202691</t>
+  </si>
+  <si>
+    <t>15.05.202692</t>
+  </si>
+  <si>
+    <t>15.05.202693</t>
+  </si>
+  <si>
+    <t>16.05.202695</t>
+  </si>
+  <si>
+    <t>16.05.202696</t>
+  </si>
+  <si>
+    <t>16.05.20261</t>
+  </si>
+  <si>
+    <t>16.05.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46155.03611111111</v>
+        <v>46156.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46155.04652777778</v>
+        <v>46156.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46155.05694444444</v>
+        <v>46156.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46155.06736111111</v>
+        <v>46156.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46155.07777777778</v>
+        <v>46156.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46155.08819444444</v>
+        <v>46156.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46155.09861111111</v>
+        <v>46156.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46155.10902777778</v>
+        <v>46156.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46155.11944444444</v>
+        <v>46156.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46155.12986111111</v>
+        <v>46156.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46155.14027777778</v>
+        <v>46156.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46155.15069444444</v>
+        <v>46156.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46155.16111111111</v>
+        <v>46156.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46155.17152777778</v>
+        <v>46156.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46155.18194444444</v>
+        <v>46156.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46155.19236111111</v>
+        <v>46156.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46155.20277777778</v>
+        <v>46156.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46155.21319444444</v>
+        <v>46156.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46155.22361111111</v>
+        <v>46156.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46155.23402777778</v>
+        <v>46156.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46155.24444444444</v>
+        <v>46156.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46155.25486111111</v>
+        <v>46156.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46155.26527777778</v>
+        <v>46156.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46155.27569444444</v>
+        <v>46156.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46155.28611111111</v>
+        <v>46156.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46155.29652777778</v>
+        <v>46156.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46155.30694444444</v>
+        <v>46156.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46155.31736111111</v>
+        <v>46156.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46155.32777777778</v>
+        <v>46156.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46155.33819444444</v>
+        <v>46156.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46155.34861111111</v>
+        <v>46156.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46155.35902777778</v>
+        <v>46156.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46155.36944444444</v>
+        <v>46156.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46155.37986111111</v>
+        <v>46156.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46155.39027777778</v>
+        <v>46156.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46155.40069444444</v>
+        <v>46156.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46155.41111111111</v>
+        <v>46156.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46155.42152777778</v>
+        <v>46156.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46155.43194444444</v>
+        <v>46156.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46155.44236111111</v>
+        <v>46156.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46155.45277777778</v>
+        <v>46156.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46155.46319444444</v>
+        <v>46156.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46155.47361111111</v>
+        <v>46156.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46155.48402777778</v>
+        <v>46156.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46155.49444444444</v>
+        <v>46156.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46155.50486111111</v>
+        <v>46156.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46155.51527777778</v>
+        <v>46156.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46155.52569444444</v>
+        <v>46156.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46155.53611111111</v>
+        <v>46156.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46155.54652777778</v>
+        <v>46156.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46155.55694444444</v>
+        <v>46156.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46155.56736111111</v>
+        <v>46156.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46155.57777777778</v>
+        <v>46156.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46155.58819444444</v>
+        <v>46156.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46155.59861111111</v>
+        <v>46156.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46155.60902777778</v>
+        <v>46156.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46155.61944444444</v>
+        <v>46156.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46155.62986111111</v>
+        <v>46156.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46155.64027777778</v>
+        <v>46156.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46155.65069444444</v>
+        <v>46156.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46155.66111111111</v>
+        <v>46156.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46155.67152777778</v>
+        <v>46156.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46155.68194444444</v>
+        <v>46156.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46155.69236111111</v>
+        <v>46156.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46155.70277777778</v>
+        <v>46156.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46155.71319444444</v>
+        <v>46156.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46155.72361111111</v>
+        <v>46156.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46155.73402777778</v>
+        <v>46156.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46155.74444444444</v>
+        <v>46156.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46155.75486111111</v>
+        <v>46156.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46155.76527777778</v>
+        <v>46156.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46155.77569444444</v>
+        <v>46156.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46155.78611111111</v>
+        <v>46156.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46155.79652777778</v>
+        <v>46156.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46155.80694444444</v>
+        <v>46156.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46155.81736111111</v>
+        <v>46156.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46155.82777777778</v>
+        <v>46156.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46155.83819444444</v>
+        <v>46156.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46155.84861111111</v>
+        <v>46156.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46155.85902777778</v>
+        <v>46156.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46155.86944444444</v>
+        <v>46156.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46155.87986111111</v>
+        <v>46156.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46155.89027777778</v>
+        <v>46156.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46155.90069444444</v>
+        <v>46156.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46155.91111111111</v>
+        <v>46156.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46155.92152777778</v>
+        <v>46156.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46155.93194444444</v>
+        <v>46156.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46155.94236111111</v>
+        <v>46156.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46155.95277777778</v>
+        <v>46156.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46155.96319444444</v>
+        <v>46156.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46155.97361111111</v>
+        <v>46156.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46155.98402777778</v>
+        <v>46156.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46155.99444444444</v>
+        <v>46156.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46156.00486111111</v>
+        <v>46157.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46156.01527777778</v>
+        <v>46157.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46156.02569444444</v>
+        <v>46157.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46156.03611111111</v>
+        <v>46157.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46156.03611111111</v>
+        <v>46157.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46156.04652777778</v>
+        <v>46157.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46156.05694444444</v>
+        <v>46157.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46156.06736111111</v>
+        <v>46157.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46156.07777777778</v>
+        <v>46157.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46156.08819444444</v>
+        <v>46157.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46156.09861111111</v>
+        <v>46157.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46156.10902777778</v>
+        <v>46157.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46156.11944444444</v>
+        <v>46157.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46156.12986111111</v>
+        <v>46157.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46156.14027777778</v>
+        <v>46157.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46156.15069444444</v>
+        <v>46157.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46156.16111111111</v>
+        <v>46157.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46156.17152777778</v>
+        <v>46157.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46156.18194444444</v>
+        <v>46157.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46156.19236111111</v>
+        <v>46157.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46156.20277777778</v>
+        <v>46157.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46156.21319444444</v>
+        <v>46157.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46156.22361111111</v>
+        <v>46157.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46156.23402777778</v>
+        <v>46157.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46156.24444444444</v>
+        <v>46157.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46156.25486111111</v>
+        <v>46157.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46156.26527777778</v>
+        <v>46157.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46156.27569444444</v>
+        <v>46157.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46156.28611111111</v>
+        <v>46157.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46156.29652777778</v>
+        <v>46157.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46156.30694444444</v>
+        <v>46157.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46156.31736111111</v>
+        <v>46157.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46156.32777777778</v>
+        <v>46157.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46156.33819444444</v>
+        <v>46157.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46156.34861111111</v>
+        <v>46157.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46156.35902777778</v>
+        <v>46157.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46156.36944444444</v>
+        <v>46157.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46156.37986111111</v>
+        <v>46157.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46156.39027777778</v>
+        <v>46157.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46156.40069444444</v>
+        <v>46157.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46156.41111111111</v>
+        <v>46157.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46156.42152777778</v>
+        <v>46157.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46156.43194444444</v>
+        <v>46157.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46156.44236111111</v>
+        <v>46157.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46156.45277777778</v>
+        <v>46157.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46156.46319444444</v>
+        <v>46157.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46156.47361111111</v>
+        <v>46157.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46156.48402777778</v>
+        <v>46157.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46156.49444444444</v>
+        <v>46157.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46156.50486111111</v>
+        <v>46157.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46156.51527777778</v>
+        <v>46157.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46156.52569444444</v>
+        <v>46157.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46156.53611111111</v>
+        <v>46157.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46156.54652777778</v>
+        <v>46157.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46156.55694444444</v>
+        <v>46157.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46156.56736111111</v>
+        <v>46157.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46156.57777777778</v>
+        <v>46157.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46156.58819444444</v>
+        <v>46157.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46156.59861111111</v>
+        <v>46157.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46156.60902777778</v>
+        <v>46157.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46156.61944444444</v>
+        <v>46157.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46156.62986111111</v>
+        <v>46157.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46156.64027777778</v>
+        <v>46157.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46156.65069444444</v>
+        <v>46157.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46156.66111111111</v>
+        <v>46157.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46156.67152777778</v>
+        <v>46157.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46156.68194444444</v>
+        <v>46157.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46156.69236111111</v>
+        <v>46157.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46156.70277777778</v>
+        <v>46157.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46156.71319444444</v>
+        <v>46157.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46156.72361111111</v>
+        <v>46157.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46156.73402777778</v>
+        <v>46157.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46156.74444444444</v>
+        <v>46157.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46156.75486111111</v>
+        <v>46157.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46156.76527777778</v>
+        <v>46157.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46156.77569444444</v>
+        <v>46157.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46156.78611111111</v>
+        <v>46157.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46156.79652777778</v>
+        <v>46157.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46156.80694444444</v>
+        <v>46157.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46156.81736111111</v>
+        <v>46157.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46156.82777777778</v>
+        <v>46157.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46156.83819444444</v>
+        <v>46157.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46156.84861111111</v>
+        <v>46157.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46156.85902777778</v>
+        <v>46157.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46156.86944444444</v>
+        <v>46157.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46156.87986111111</v>
+        <v>46157.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46156.89027777778</v>
+        <v>46157.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46156.90069444444</v>
+        <v>46157.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46156.91111111111</v>
+        <v>46157.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46156.92152777778</v>
+        <v>46157.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46156.93194444444</v>
+        <v>46157.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46156.94236111111</v>
+        <v>46157.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46156.95277777778</v>
+        <v>46157.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46156.96319444444</v>
+        <v>46157.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46156.97361111111</v>
+        <v>46157.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46156.98402777778</v>
+        <v>46157.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46156.99444444444</v>
+        <v>46157.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46157.00486111111</v>
+        <v>46158.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46157.01527777778</v>
+        <v>46158.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46157.02569444444</v>
+        <v>46158.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46157.03611111111</v>
+        <v>46158.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,583 +31,583 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>14.05.20261</t>
-  </si>
-  <si>
-    <t>14.05.20262</t>
-  </si>
-  <si>
-    <t>14.05.20263</t>
-  </si>
-  <si>
-    <t>14.05.20264</t>
-  </si>
-  <si>
-    <t>14.05.20265</t>
-  </si>
-  <si>
-    <t>14.05.20266</t>
-  </si>
-  <si>
-    <t>14.05.20267</t>
-  </si>
-  <si>
-    <t>14.05.20268</t>
-  </si>
-  <si>
-    <t>14.05.20269</t>
-  </si>
-  <si>
-    <t>14.05.202610</t>
-  </si>
-  <si>
-    <t>14.05.202611</t>
-  </si>
-  <si>
-    <t>14.05.202612</t>
-  </si>
-  <si>
-    <t>14.05.202613</t>
-  </si>
-  <si>
-    <t>14.05.202614</t>
-  </si>
-  <si>
-    <t>14.05.202615</t>
-  </si>
-  <si>
-    <t>14.05.202616</t>
-  </si>
-  <si>
-    <t>14.05.202617</t>
-  </si>
-  <si>
-    <t>14.05.202618</t>
-  </si>
-  <si>
-    <t>14.05.202619</t>
-  </si>
-  <si>
-    <t>14.05.202620</t>
-  </si>
-  <si>
-    <t>14.05.202621</t>
-  </si>
-  <si>
-    <t>14.05.202622</t>
-  </si>
-  <si>
-    <t>14.05.202623</t>
-  </si>
-  <si>
-    <t>14.05.202624</t>
-  </si>
-  <si>
-    <t>14.05.202625</t>
-  </si>
-  <si>
-    <t>14.05.202626</t>
-  </si>
-  <si>
-    <t>14.05.202627</t>
-  </si>
-  <si>
-    <t>14.05.202628</t>
-  </si>
-  <si>
-    <t>14.05.202629</t>
-  </si>
-  <si>
-    <t>14.05.202630</t>
-  </si>
-  <si>
-    <t>14.05.202631</t>
-  </si>
-  <si>
-    <t>14.05.202632</t>
-  </si>
-  <si>
-    <t>14.05.202633</t>
-  </si>
-  <si>
-    <t>14.05.202634</t>
-  </si>
-  <si>
-    <t>14.05.202635</t>
-  </si>
-  <si>
-    <t>14.05.202636</t>
-  </si>
-  <si>
-    <t>14.05.202637</t>
-  </si>
-  <si>
-    <t>14.05.202638</t>
-  </si>
-  <si>
-    <t>14.05.202639</t>
-  </si>
-  <si>
-    <t>14.05.202640</t>
-  </si>
-  <si>
-    <t>14.05.202641</t>
-  </si>
-  <si>
-    <t>14.05.202642</t>
-  </si>
-  <si>
-    <t>14.05.202643</t>
-  </si>
-  <si>
-    <t>14.05.202644</t>
-  </si>
-  <si>
-    <t>14.05.202645</t>
-  </si>
-  <si>
-    <t>14.05.202646</t>
-  </si>
-  <si>
-    <t>14.05.202647</t>
-  </si>
-  <si>
-    <t>14.05.202648</t>
-  </si>
-  <si>
-    <t>14.05.202649</t>
-  </si>
-  <si>
-    <t>14.05.202650</t>
-  </si>
-  <si>
-    <t>14.05.202651</t>
-  </si>
-  <si>
-    <t>14.05.202652</t>
-  </si>
-  <si>
-    <t>14.05.202653</t>
-  </si>
-  <si>
-    <t>14.05.202654</t>
-  </si>
-  <si>
-    <t>14.05.202655</t>
-  </si>
-  <si>
-    <t>14.05.202656</t>
-  </si>
-  <si>
-    <t>14.05.202657</t>
-  </si>
-  <si>
-    <t>14.05.202658</t>
-  </si>
-  <si>
-    <t>14.05.202659</t>
-  </si>
-  <si>
-    <t>14.05.202660</t>
-  </si>
-  <si>
-    <t>14.05.202661</t>
-  </si>
-  <si>
-    <t>14.05.202662</t>
-  </si>
-  <si>
-    <t>14.05.202663</t>
-  </si>
-  <si>
-    <t>14.05.202664</t>
-  </si>
-  <si>
-    <t>14.05.202665</t>
-  </si>
-  <si>
-    <t>14.05.202666</t>
-  </si>
-  <si>
-    <t>14.05.202667</t>
-  </si>
-  <si>
-    <t>14.05.202668</t>
-  </si>
-  <si>
-    <t>14.05.202669</t>
-  </si>
-  <si>
-    <t>14.05.202670</t>
-  </si>
-  <si>
-    <t>14.05.202671</t>
-  </si>
-  <si>
-    <t>14.05.202672</t>
-  </si>
-  <si>
-    <t>14.05.202673</t>
-  </si>
-  <si>
-    <t>14.05.202674</t>
-  </si>
-  <si>
-    <t>14.05.202675</t>
-  </si>
-  <si>
-    <t>14.05.202676</t>
-  </si>
-  <si>
-    <t>14.05.202677</t>
-  </si>
-  <si>
-    <t>14.05.202678</t>
-  </si>
-  <si>
-    <t>14.05.202679</t>
-  </si>
-  <si>
-    <t>14.05.202680</t>
-  </si>
-  <si>
-    <t>14.05.202681</t>
-  </si>
-  <si>
-    <t>14.05.202682</t>
-  </si>
-  <si>
-    <t>14.05.202683</t>
-  </si>
-  <si>
-    <t>14.05.202684</t>
-  </si>
-  <si>
-    <t>14.05.202685</t>
-  </si>
-  <si>
-    <t>14.05.202686</t>
-  </si>
-  <si>
-    <t>14.05.202687</t>
-  </si>
-  <si>
-    <t>14.05.202688</t>
-  </si>
-  <si>
-    <t>14.05.202689</t>
-  </si>
-  <si>
-    <t>14.05.202690</t>
-  </si>
-  <si>
-    <t>14.05.202691</t>
-  </si>
-  <si>
-    <t>14.05.202692</t>
-  </si>
-  <si>
-    <t>14.05.202693</t>
-  </si>
-  <si>
-    <t>15.05.202694</t>
-  </si>
-  <si>
-    <t>15.05.202695</t>
-  </si>
-  <si>
-    <t>15.05.202696</t>
-  </si>
-  <si>
-    <t>15.05.20261</t>
-  </si>
-  <si>
-    <t>15.05.20262</t>
-  </si>
-  <si>
-    <t>15.05.20263</t>
-  </si>
-  <si>
-    <t>15.05.20264</t>
-  </si>
-  <si>
-    <t>15.05.20265</t>
-  </si>
-  <si>
-    <t>15.05.20266</t>
-  </si>
-  <si>
-    <t>15.05.20267</t>
-  </si>
-  <si>
-    <t>15.05.20268</t>
-  </si>
-  <si>
-    <t>15.05.20269</t>
-  </si>
-  <si>
-    <t>15.05.202610</t>
-  </si>
-  <si>
-    <t>15.05.202611</t>
-  </si>
-  <si>
-    <t>15.05.202612</t>
-  </si>
-  <si>
-    <t>15.05.202613</t>
-  </si>
-  <si>
-    <t>15.05.202614</t>
-  </si>
-  <si>
-    <t>15.05.202615</t>
-  </si>
-  <si>
-    <t>15.05.202616</t>
-  </si>
-  <si>
-    <t>15.05.202617</t>
-  </si>
-  <si>
-    <t>15.05.202618</t>
-  </si>
-  <si>
-    <t>15.05.202619</t>
-  </si>
-  <si>
-    <t>15.05.202620</t>
-  </si>
-  <si>
-    <t>15.05.202621</t>
-  </si>
-  <si>
-    <t>15.05.202622</t>
-  </si>
-  <si>
-    <t>15.05.202623</t>
-  </si>
-  <si>
-    <t>15.05.202624</t>
-  </si>
-  <si>
-    <t>15.05.202625</t>
-  </si>
-  <si>
-    <t>15.05.202626</t>
-  </si>
-  <si>
-    <t>15.05.202627</t>
-  </si>
-  <si>
-    <t>15.05.202628</t>
-  </si>
-  <si>
-    <t>15.05.202629</t>
-  </si>
-  <si>
-    <t>15.05.202630</t>
-  </si>
-  <si>
-    <t>15.05.202631</t>
-  </si>
-  <si>
-    <t>15.05.202632</t>
-  </si>
-  <si>
-    <t>15.05.202633</t>
-  </si>
-  <si>
-    <t>15.05.202634</t>
-  </si>
-  <si>
-    <t>15.05.202635</t>
-  </si>
-  <si>
-    <t>15.05.202636</t>
-  </si>
-  <si>
-    <t>15.05.202637</t>
-  </si>
-  <si>
-    <t>15.05.202638</t>
-  </si>
-  <si>
-    <t>15.05.202639</t>
-  </si>
-  <si>
-    <t>15.05.202640</t>
-  </si>
-  <si>
-    <t>15.05.202641</t>
-  </si>
-  <si>
-    <t>15.05.202642</t>
-  </si>
-  <si>
-    <t>15.05.202643</t>
-  </si>
-  <si>
-    <t>15.05.202644</t>
-  </si>
-  <si>
-    <t>15.05.202645</t>
-  </si>
-  <si>
-    <t>15.05.202646</t>
-  </si>
-  <si>
-    <t>15.05.202647</t>
-  </si>
-  <si>
-    <t>15.05.202648</t>
-  </si>
-  <si>
-    <t>15.05.202649</t>
-  </si>
-  <si>
-    <t>15.05.202650</t>
-  </si>
-  <si>
-    <t>15.05.202651</t>
-  </si>
-  <si>
-    <t>15.05.202652</t>
-  </si>
-  <si>
-    <t>15.05.202653</t>
-  </si>
-  <si>
-    <t>15.05.202654</t>
-  </si>
-  <si>
-    <t>15.05.202655</t>
-  </si>
-  <si>
-    <t>15.05.202656</t>
-  </si>
-  <si>
-    <t>15.05.202657</t>
-  </si>
-  <si>
-    <t>15.05.202658</t>
-  </si>
-  <si>
-    <t>15.05.202659</t>
-  </si>
-  <si>
-    <t>15.05.202660</t>
-  </si>
-  <si>
-    <t>15.05.202661</t>
-  </si>
-  <si>
-    <t>15.05.202662</t>
-  </si>
-  <si>
-    <t>15.05.202663</t>
-  </si>
-  <si>
-    <t>15.05.202664</t>
-  </si>
-  <si>
-    <t>15.05.202665</t>
-  </si>
-  <si>
-    <t>15.05.202666</t>
-  </si>
-  <si>
-    <t>15.05.202667</t>
-  </si>
-  <si>
-    <t>15.05.202668</t>
-  </si>
-  <si>
-    <t>15.05.202669</t>
-  </si>
-  <si>
-    <t>15.05.202670</t>
-  </si>
-  <si>
-    <t>15.05.202671</t>
-  </si>
-  <si>
-    <t>15.05.202672</t>
-  </si>
-  <si>
-    <t>15.05.202673</t>
-  </si>
-  <si>
-    <t>15.05.202674</t>
-  </si>
-  <si>
-    <t>15.05.202675</t>
-  </si>
-  <si>
-    <t>15.05.202676</t>
-  </si>
-  <si>
-    <t>15.05.202677</t>
-  </si>
-  <si>
-    <t>15.05.202678</t>
-  </si>
-  <si>
-    <t>15.05.202679</t>
-  </si>
-  <si>
-    <t>15.05.202680</t>
-  </si>
-  <si>
-    <t>15.05.202681</t>
-  </si>
-  <si>
-    <t>15.05.202682</t>
-  </si>
-  <si>
-    <t>15.05.202683</t>
-  </si>
-  <si>
-    <t>15.05.202684</t>
-  </si>
-  <si>
-    <t>15.05.202685</t>
-  </si>
-  <si>
-    <t>15.05.202686</t>
-  </si>
-  <si>
-    <t>15.05.202687</t>
-  </si>
-  <si>
-    <t>15.05.202688</t>
-  </si>
-  <si>
-    <t>15.05.202689</t>
-  </si>
-  <si>
-    <t>15.05.202690</t>
-  </si>
-  <si>
-    <t>15.05.202691</t>
-  </si>
-  <si>
-    <t>15.05.202692</t>
-  </si>
-  <si>
-    <t>15.05.202693</t>
-  </si>
-  <si>
-    <t>16.05.202695</t>
-  </si>
-  <si>
-    <t>16.05.202696</t>
-  </si>
-  <si>
-    <t>16.05.20261</t>
-  </si>
-  <si>
-    <t>16.05.20262</t>
+    <t>20.05.20261</t>
+  </si>
+  <si>
+    <t>20.05.20262</t>
+  </si>
+  <si>
+    <t>20.05.20263</t>
+  </si>
+  <si>
+    <t>20.05.20264</t>
+  </si>
+  <si>
+    <t>20.05.20265</t>
+  </si>
+  <si>
+    <t>20.05.20266</t>
+  </si>
+  <si>
+    <t>20.05.20267</t>
+  </si>
+  <si>
+    <t>20.05.20268</t>
+  </si>
+  <si>
+    <t>20.05.20269</t>
+  </si>
+  <si>
+    <t>20.05.202610</t>
+  </si>
+  <si>
+    <t>20.05.202611</t>
+  </si>
+  <si>
+    <t>20.05.202612</t>
+  </si>
+  <si>
+    <t>20.05.202613</t>
+  </si>
+  <si>
+    <t>20.05.202614</t>
+  </si>
+  <si>
+    <t>20.05.202615</t>
+  </si>
+  <si>
+    <t>20.05.202616</t>
+  </si>
+  <si>
+    <t>20.05.202617</t>
+  </si>
+  <si>
+    <t>20.05.202618</t>
+  </si>
+  <si>
+    <t>20.05.202619</t>
+  </si>
+  <si>
+    <t>20.05.202620</t>
+  </si>
+  <si>
+    <t>20.05.202621</t>
+  </si>
+  <si>
+    <t>20.05.202622</t>
+  </si>
+  <si>
+    <t>20.05.202623</t>
+  </si>
+  <si>
+    <t>20.05.202624</t>
+  </si>
+  <si>
+    <t>20.05.202625</t>
+  </si>
+  <si>
+    <t>20.05.202626</t>
+  </si>
+  <si>
+    <t>20.05.202627</t>
+  </si>
+  <si>
+    <t>20.05.202628</t>
+  </si>
+  <si>
+    <t>20.05.202629</t>
+  </si>
+  <si>
+    <t>20.05.202630</t>
+  </si>
+  <si>
+    <t>20.05.202631</t>
+  </si>
+  <si>
+    <t>20.05.202632</t>
+  </si>
+  <si>
+    <t>20.05.202633</t>
+  </si>
+  <si>
+    <t>20.05.202634</t>
+  </si>
+  <si>
+    <t>20.05.202635</t>
+  </si>
+  <si>
+    <t>20.05.202636</t>
+  </si>
+  <si>
+    <t>20.05.202637</t>
+  </si>
+  <si>
+    <t>20.05.202638</t>
+  </si>
+  <si>
+    <t>20.05.202639</t>
+  </si>
+  <si>
+    <t>20.05.202640</t>
+  </si>
+  <si>
+    <t>20.05.202641</t>
+  </si>
+  <si>
+    <t>20.05.202642</t>
+  </si>
+  <si>
+    <t>20.05.202643</t>
+  </si>
+  <si>
+    <t>20.05.202644</t>
+  </si>
+  <si>
+    <t>20.05.202645</t>
+  </si>
+  <si>
+    <t>20.05.202646</t>
+  </si>
+  <si>
+    <t>20.05.202647</t>
+  </si>
+  <si>
+    <t>20.05.202648</t>
+  </si>
+  <si>
+    <t>20.05.202649</t>
+  </si>
+  <si>
+    <t>20.05.202650</t>
+  </si>
+  <si>
+    <t>20.05.202651</t>
+  </si>
+  <si>
+    <t>20.05.202652</t>
+  </si>
+  <si>
+    <t>20.05.202653</t>
+  </si>
+  <si>
+    <t>20.05.202654</t>
+  </si>
+  <si>
+    <t>20.05.202655</t>
+  </si>
+  <si>
+    <t>20.05.202656</t>
+  </si>
+  <si>
+    <t>20.05.202657</t>
+  </si>
+  <si>
+    <t>20.05.202658</t>
+  </si>
+  <si>
+    <t>20.05.202659</t>
+  </si>
+  <si>
+    <t>20.05.202660</t>
+  </si>
+  <si>
+    <t>20.05.202661</t>
+  </si>
+  <si>
+    <t>20.05.202662</t>
+  </si>
+  <si>
+    <t>20.05.202663</t>
+  </si>
+  <si>
+    <t>20.05.202664</t>
+  </si>
+  <si>
+    <t>20.05.202665</t>
+  </si>
+  <si>
+    <t>20.05.202666</t>
+  </si>
+  <si>
+    <t>20.05.202667</t>
+  </si>
+  <si>
+    <t>20.05.202668</t>
+  </si>
+  <si>
+    <t>20.05.202669</t>
+  </si>
+  <si>
+    <t>20.05.202670</t>
+  </si>
+  <si>
+    <t>20.05.202671</t>
+  </si>
+  <si>
+    <t>20.05.202672</t>
+  </si>
+  <si>
+    <t>20.05.202673</t>
+  </si>
+  <si>
+    <t>20.05.202674</t>
+  </si>
+  <si>
+    <t>20.05.202675</t>
+  </si>
+  <si>
+    <t>20.05.202676</t>
+  </si>
+  <si>
+    <t>20.05.202677</t>
+  </si>
+  <si>
+    <t>20.05.202678</t>
+  </si>
+  <si>
+    <t>20.05.202679</t>
+  </si>
+  <si>
+    <t>20.05.202680</t>
+  </si>
+  <si>
+    <t>20.05.202681</t>
+  </si>
+  <si>
+    <t>20.05.202682</t>
+  </si>
+  <si>
+    <t>20.05.202683</t>
+  </si>
+  <si>
+    <t>20.05.202684</t>
+  </si>
+  <si>
+    <t>20.05.202685</t>
+  </si>
+  <si>
+    <t>20.05.202686</t>
+  </si>
+  <si>
+    <t>20.05.202687</t>
+  </si>
+  <si>
+    <t>20.05.202688</t>
+  </si>
+  <si>
+    <t>20.05.202689</t>
+  </si>
+  <si>
+    <t>20.05.202690</t>
+  </si>
+  <si>
+    <t>20.05.202691</t>
+  </si>
+  <si>
+    <t>20.05.202692</t>
+  </si>
+  <si>
+    <t>20.05.202693</t>
+  </si>
+  <si>
+    <t>21.05.202694</t>
+  </si>
+  <si>
+    <t>21.05.202695</t>
+  </si>
+  <si>
+    <t>21.05.202696</t>
+  </si>
+  <si>
+    <t>21.05.20261</t>
+  </si>
+  <si>
+    <t>21.05.20262</t>
+  </si>
+  <si>
+    <t>21.05.20263</t>
+  </si>
+  <si>
+    <t>21.05.20264</t>
+  </si>
+  <si>
+    <t>21.05.20265</t>
+  </si>
+  <si>
+    <t>21.05.20266</t>
+  </si>
+  <si>
+    <t>21.05.20267</t>
+  </si>
+  <si>
+    <t>21.05.20268</t>
+  </si>
+  <si>
+    <t>21.05.20269</t>
+  </si>
+  <si>
+    <t>21.05.202610</t>
+  </si>
+  <si>
+    <t>21.05.202611</t>
+  </si>
+  <si>
+    <t>21.05.202612</t>
+  </si>
+  <si>
+    <t>21.05.202613</t>
+  </si>
+  <si>
+    <t>21.05.202614</t>
+  </si>
+  <si>
+    <t>21.05.202615</t>
+  </si>
+  <si>
+    <t>21.05.202616</t>
+  </si>
+  <si>
+    <t>21.05.202617</t>
+  </si>
+  <si>
+    <t>21.05.202618</t>
+  </si>
+  <si>
+    <t>21.05.202619</t>
+  </si>
+  <si>
+    <t>21.05.202620</t>
+  </si>
+  <si>
+    <t>21.05.202621</t>
+  </si>
+  <si>
+    <t>21.05.202622</t>
+  </si>
+  <si>
+    <t>21.05.202623</t>
+  </si>
+  <si>
+    <t>21.05.202624</t>
+  </si>
+  <si>
+    <t>21.05.202625</t>
+  </si>
+  <si>
+    <t>21.05.202626</t>
+  </si>
+  <si>
+    <t>21.05.202627</t>
+  </si>
+  <si>
+    <t>21.05.202628</t>
+  </si>
+  <si>
+    <t>21.05.202629</t>
+  </si>
+  <si>
+    <t>21.05.202630</t>
+  </si>
+  <si>
+    <t>21.05.202631</t>
+  </si>
+  <si>
+    <t>21.05.202632</t>
+  </si>
+  <si>
+    <t>21.05.202633</t>
+  </si>
+  <si>
+    <t>21.05.202634</t>
+  </si>
+  <si>
+    <t>21.05.202635</t>
+  </si>
+  <si>
+    <t>21.05.202636</t>
+  </si>
+  <si>
+    <t>21.05.202637</t>
+  </si>
+  <si>
+    <t>21.05.202638</t>
+  </si>
+  <si>
+    <t>21.05.202639</t>
+  </si>
+  <si>
+    <t>21.05.202640</t>
+  </si>
+  <si>
+    <t>21.05.202641</t>
+  </si>
+  <si>
+    <t>21.05.202642</t>
+  </si>
+  <si>
+    <t>21.05.202643</t>
+  </si>
+  <si>
+    <t>21.05.202644</t>
+  </si>
+  <si>
+    <t>21.05.202645</t>
+  </si>
+  <si>
+    <t>21.05.202646</t>
+  </si>
+  <si>
+    <t>21.05.202647</t>
+  </si>
+  <si>
+    <t>21.05.202648</t>
+  </si>
+  <si>
+    <t>21.05.202649</t>
+  </si>
+  <si>
+    <t>21.05.202650</t>
+  </si>
+  <si>
+    <t>21.05.202651</t>
+  </si>
+  <si>
+    <t>21.05.202652</t>
+  </si>
+  <si>
+    <t>21.05.202653</t>
+  </si>
+  <si>
+    <t>21.05.202654</t>
+  </si>
+  <si>
+    <t>21.05.202655</t>
+  </si>
+  <si>
+    <t>21.05.202656</t>
+  </si>
+  <si>
+    <t>21.05.202657</t>
+  </si>
+  <si>
+    <t>21.05.202658</t>
+  </si>
+  <si>
+    <t>21.05.202659</t>
+  </si>
+  <si>
+    <t>21.05.202660</t>
+  </si>
+  <si>
+    <t>21.05.202661</t>
+  </si>
+  <si>
+    <t>21.05.202662</t>
+  </si>
+  <si>
+    <t>21.05.202663</t>
+  </si>
+  <si>
+    <t>21.05.202664</t>
+  </si>
+  <si>
+    <t>21.05.202665</t>
+  </si>
+  <si>
+    <t>21.05.202666</t>
+  </si>
+  <si>
+    <t>21.05.202667</t>
+  </si>
+  <si>
+    <t>21.05.202668</t>
+  </si>
+  <si>
+    <t>21.05.202669</t>
+  </si>
+  <si>
+    <t>21.05.202670</t>
+  </si>
+  <si>
+    <t>21.05.202671</t>
+  </si>
+  <si>
+    <t>21.05.202672</t>
+  </si>
+  <si>
+    <t>21.05.202673</t>
+  </si>
+  <si>
+    <t>21.05.202674</t>
+  </si>
+  <si>
+    <t>21.05.202675</t>
+  </si>
+  <si>
+    <t>21.05.202676</t>
+  </si>
+  <si>
+    <t>21.05.202677</t>
+  </si>
+  <si>
+    <t>21.05.202678</t>
+  </si>
+  <si>
+    <t>21.05.202679</t>
+  </si>
+  <si>
+    <t>21.05.202680</t>
+  </si>
+  <si>
+    <t>21.05.202681</t>
+  </si>
+  <si>
+    <t>21.05.202682</t>
+  </si>
+  <si>
+    <t>21.05.202683</t>
+  </si>
+  <si>
+    <t>21.05.202684</t>
+  </si>
+  <si>
+    <t>21.05.202685</t>
+  </si>
+  <si>
+    <t>21.05.202686</t>
+  </si>
+  <si>
+    <t>21.05.202687</t>
+  </si>
+  <si>
+    <t>21.05.202688</t>
+  </si>
+  <si>
+    <t>21.05.202689</t>
+  </si>
+  <si>
+    <t>21.05.202690</t>
+  </si>
+  <si>
+    <t>21.05.202691</t>
+  </si>
+  <si>
+    <t>21.05.202692</t>
+  </si>
+  <si>
+    <t>21.05.202693</t>
+  </si>
+  <si>
+    <t>22.05.202695</t>
+  </si>
+  <si>
+    <t>22.05.202696</t>
+  </si>
+  <si>
+    <t>22.05.20261</t>
+  </si>
+  <si>
+    <t>22.05.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46156.03611111111</v>
+        <v>46162.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46156.04652777778</v>
+        <v>46162.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46156.05694444444</v>
+        <v>46162.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46156.06736111111</v>
+        <v>46162.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46156.07777777778</v>
+        <v>46162.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46156.08819444444</v>
+        <v>46162.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46156.09861111111</v>
+        <v>46162.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46156.10902777778</v>
+        <v>46162.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46156.11944444444</v>
+        <v>46162.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46156.12986111111</v>
+        <v>46162.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46156.14027777778</v>
+        <v>46162.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46156.15069444444</v>
+        <v>46162.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46156.16111111111</v>
+        <v>46162.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46156.17152777778</v>
+        <v>46162.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46156.18194444444</v>
+        <v>46162.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46156.19236111111</v>
+        <v>46162.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46156.20277777778</v>
+        <v>46162.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46156.21319444444</v>
+        <v>46162.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46156.22361111111</v>
+        <v>46162.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46156.23402777778</v>
+        <v>46162.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46156.24444444444</v>
+        <v>46162.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46156.25486111111</v>
+        <v>46162.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46156.26527777778</v>
+        <v>46162.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46156.27569444444</v>
+        <v>46162.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46156.28611111111</v>
+        <v>46162.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46156.29652777778</v>
+        <v>46162.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46156.30694444444</v>
+        <v>46162.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46156.31736111111</v>
+        <v>46162.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46156.32777777778</v>
+        <v>46162.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46156.33819444444</v>
+        <v>46162.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46156.34861111111</v>
+        <v>46162.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46156.35902777778</v>
+        <v>46162.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46156.36944444444</v>
+        <v>46162.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46156.37986111111</v>
+        <v>46162.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46156.39027777778</v>
+        <v>46162.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46156.40069444444</v>
+        <v>46162.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46156.41111111111</v>
+        <v>46162.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46156.42152777778</v>
+        <v>46162.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46156.43194444444</v>
+        <v>46162.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46156.44236111111</v>
+        <v>46162.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46156.45277777778</v>
+        <v>46162.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46156.46319444444</v>
+        <v>46162.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46156.47361111111</v>
+        <v>46162.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46156.48402777778</v>
+        <v>46162.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46156.49444444444</v>
+        <v>46162.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46156.50486111111</v>
+        <v>46162.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46156.51527777778</v>
+        <v>46162.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46156.52569444444</v>
+        <v>46162.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46156.53611111111</v>
+        <v>46162.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46156.54652777778</v>
+        <v>46162.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46156.55694444444</v>
+        <v>46162.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46156.56736111111</v>
+        <v>46162.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46156.57777777778</v>
+        <v>46162.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46156.58819444444</v>
+        <v>46162.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46156.59861111111</v>
+        <v>46162.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46156.60902777778</v>
+        <v>46162.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46156.61944444444</v>
+        <v>46162.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46156.62986111111</v>
+        <v>46162.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46156.64027777778</v>
+        <v>46162.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46156.65069444444</v>
+        <v>46162.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46156.66111111111</v>
+        <v>46162.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46156.67152777778</v>
+        <v>46162.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46156.68194444444</v>
+        <v>46162.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46156.69236111111</v>
+        <v>46162.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46156.70277777778</v>
+        <v>46162.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46156.71319444444</v>
+        <v>46162.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46156.72361111111</v>
+        <v>46162.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46156.73402777778</v>
+        <v>46162.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46156.74444444444</v>
+        <v>46162.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46156.75486111111</v>
+        <v>46162.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46156.76527777778</v>
+        <v>46162.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46156.77569444444</v>
+        <v>46162.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46156.78611111111</v>
+        <v>46162.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46156.79652777778</v>
+        <v>46162.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46156.80694444444</v>
+        <v>46162.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46156.81736111111</v>
+        <v>46162.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46156.82777777778</v>
+        <v>46162.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46156.83819444444</v>
+        <v>46162.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46156.84861111111</v>
+        <v>46162.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46156.85902777778</v>
+        <v>46162.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46156.86944444444</v>
+        <v>46162.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46156.87986111111</v>
+        <v>46162.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46156.89027777778</v>
+        <v>46162.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46156.90069444444</v>
+        <v>46162.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46156.91111111111</v>
+        <v>46162.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46156.92152777778</v>
+        <v>46162.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46156.93194444444</v>
+        <v>46162.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46156.94236111111</v>
+        <v>46162.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46156.95277777778</v>
+        <v>46162.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46156.96319444444</v>
+        <v>46162.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46156.97361111111</v>
+        <v>46162.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46156.98402777778</v>
+        <v>46162.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46156.99444444444</v>
+        <v>46162.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46157.00486111111</v>
+        <v>46163.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46157.01527777778</v>
+        <v>46163.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46157.02569444444</v>
+        <v>46163.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46157.03611111111</v>
+        <v>46163.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46157.03611111111</v>
+        <v>46163.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46157.04652777778</v>
+        <v>46163.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46157.05694444444</v>
+        <v>46163.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46157.06736111111</v>
+        <v>46163.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46157.07777777778</v>
+        <v>46163.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46157.08819444444</v>
+        <v>46163.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46157.09861111111</v>
+        <v>46163.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46157.10902777778</v>
+        <v>46163.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46157.11944444444</v>
+        <v>46163.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46157.12986111111</v>
+        <v>46163.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46157.14027777778</v>
+        <v>46163.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46157.15069444444</v>
+        <v>46163.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46157.16111111111</v>
+        <v>46163.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46157.17152777778</v>
+        <v>46163.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46157.18194444444</v>
+        <v>46163.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46157.19236111111</v>
+        <v>46163.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46157.20277777778</v>
+        <v>46163.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46157.21319444444</v>
+        <v>46163.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46157.22361111111</v>
+        <v>46163.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46157.23402777778</v>
+        <v>46163.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46157.24444444444</v>
+        <v>46163.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46157.25486111111</v>
+        <v>46163.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46157.26527777778</v>
+        <v>46163.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46157.27569444444</v>
+        <v>46163.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46157.28611111111</v>
+        <v>46163.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46157.29652777778</v>
+        <v>46163.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46157.30694444444</v>
+        <v>46163.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46157.31736111111</v>
+        <v>46163.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46157.32777777778</v>
+        <v>46163.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46157.33819444444</v>
+        <v>46163.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46157.34861111111</v>
+        <v>46163.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46157.35902777778</v>
+        <v>46163.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46157.36944444444</v>
+        <v>46163.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46157.37986111111</v>
+        <v>46163.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46157.39027777778</v>
+        <v>46163.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46157.40069444444</v>
+        <v>46163.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46157.41111111111</v>
+        <v>46163.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46157.42152777778</v>
+        <v>46163.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46157.43194444444</v>
+        <v>46163.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46157.44236111111</v>
+        <v>46163.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46157.45277777778</v>
+        <v>46163.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46157.46319444444</v>
+        <v>46163.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46157.47361111111</v>
+        <v>46163.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46157.48402777778</v>
+        <v>46163.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46157.49444444444</v>
+        <v>46163.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46157.50486111111</v>
+        <v>46163.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46157.51527777778</v>
+        <v>46163.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46157.52569444444</v>
+        <v>46163.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46157.53611111111</v>
+        <v>46163.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46157.54652777778</v>
+        <v>46163.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46157.55694444444</v>
+        <v>46163.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46157.56736111111</v>
+        <v>46163.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46157.57777777778</v>
+        <v>46163.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46157.58819444444</v>
+        <v>46163.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46157.59861111111</v>
+        <v>46163.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46157.60902777778</v>
+        <v>46163.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46157.61944444444</v>
+        <v>46163.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46157.62986111111</v>
+        <v>46163.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46157.64027777778</v>
+        <v>46163.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46157.65069444444</v>
+        <v>46163.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46157.66111111111</v>
+        <v>46163.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46157.67152777778</v>
+        <v>46163.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46157.68194444444</v>
+        <v>46163.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46157.69236111111</v>
+        <v>46163.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46157.70277777778</v>
+        <v>46163.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46157.71319444444</v>
+        <v>46163.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46157.72361111111</v>
+        <v>46163.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46157.73402777778</v>
+        <v>46163.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46157.74444444444</v>
+        <v>46163.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46157.75486111111</v>
+        <v>46163.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46157.76527777778</v>
+        <v>46163.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46157.77569444444</v>
+        <v>46163.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46157.78611111111</v>
+        <v>46163.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46157.79652777778</v>
+        <v>46163.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46157.80694444444</v>
+        <v>46163.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46157.81736111111</v>
+        <v>46163.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46157.82777777778</v>
+        <v>46163.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46157.83819444444</v>
+        <v>46163.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46157.84861111111</v>
+        <v>46163.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46157.85902777778</v>
+        <v>46163.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46157.86944444444</v>
+        <v>46163.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46157.87986111111</v>
+        <v>46163.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46157.89027777778</v>
+        <v>46163.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46157.90069444444</v>
+        <v>46163.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46157.91111111111</v>
+        <v>46163.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46157.92152777778</v>
+        <v>46163.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46157.93194444444</v>
+        <v>46163.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46157.94236111111</v>
+        <v>46163.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46157.95277777778</v>
+        <v>46163.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46157.96319444444</v>
+        <v>46163.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46157.97361111111</v>
+        <v>46163.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46157.98402777778</v>
+        <v>46163.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46157.99444444444</v>
+        <v>46163.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46158.00486111111</v>
+        <v>46164.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46158.01527777778</v>
+        <v>46164.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46158.02569444444</v>
+        <v>46164.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46158.03611111111</v>
+        <v>46164.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>20.05.20261</t>
-  </si>
-  <si>
-    <t>20.05.20262</t>
-  </si>
-  <si>
-    <t>20.05.20263</t>
-  </si>
-  <si>
-    <t>20.05.20264</t>
-  </si>
-  <si>
-    <t>20.05.20265</t>
-  </si>
-  <si>
-    <t>20.05.20266</t>
-  </si>
-  <si>
-    <t>20.05.20267</t>
-  </si>
-  <si>
-    <t>20.05.20268</t>
-  </si>
-  <si>
-    <t>20.05.20269</t>
-  </si>
-  <si>
-    <t>20.05.202610</t>
-  </si>
-  <si>
-    <t>20.05.202611</t>
-  </si>
-  <si>
-    <t>20.05.202612</t>
-  </si>
-  <si>
-    <t>20.05.202613</t>
-  </si>
-  <si>
-    <t>20.05.202614</t>
-  </si>
-  <si>
-    <t>20.05.202615</t>
-  </si>
-  <si>
-    <t>20.05.202616</t>
-  </si>
-  <si>
-    <t>20.05.202617</t>
-  </si>
-  <si>
-    <t>20.05.202618</t>
-  </si>
-  <si>
-    <t>20.05.202619</t>
-  </si>
-  <si>
-    <t>20.05.202620</t>
-  </si>
-  <si>
-    <t>20.05.202621</t>
-  </si>
-  <si>
-    <t>20.05.202622</t>
-  </si>
-  <si>
-    <t>20.05.202623</t>
-  </si>
-  <si>
-    <t>20.05.202624</t>
-  </si>
-  <si>
-    <t>20.05.202625</t>
-  </si>
-  <si>
-    <t>20.05.202626</t>
-  </si>
-  <si>
-    <t>20.05.202627</t>
-  </si>
-  <si>
-    <t>20.05.202628</t>
-  </si>
-  <si>
-    <t>20.05.202629</t>
-  </si>
-  <si>
-    <t>20.05.202630</t>
-  </si>
-  <si>
-    <t>20.05.202631</t>
-  </si>
-  <si>
-    <t>20.05.202632</t>
-  </si>
-  <si>
-    <t>20.05.202633</t>
-  </si>
-  <si>
-    <t>20.05.202634</t>
-  </si>
-  <si>
-    <t>20.05.202635</t>
-  </si>
-  <si>
-    <t>20.05.202636</t>
-  </si>
-  <si>
-    <t>20.05.202637</t>
-  </si>
-  <si>
-    <t>20.05.202638</t>
-  </si>
-  <si>
-    <t>20.05.202639</t>
-  </si>
-  <si>
-    <t>20.05.202640</t>
-  </si>
-  <si>
-    <t>20.05.202641</t>
-  </si>
-  <si>
-    <t>20.05.202642</t>
-  </si>
-  <si>
-    <t>20.05.202643</t>
-  </si>
-  <si>
-    <t>20.05.202644</t>
-  </si>
-  <si>
-    <t>20.05.202645</t>
-  </si>
-  <si>
-    <t>20.05.202646</t>
-  </si>
-  <si>
-    <t>20.05.202647</t>
-  </si>
-  <si>
-    <t>20.05.202648</t>
-  </si>
-  <si>
-    <t>20.05.202649</t>
-  </si>
-  <si>
-    <t>20.05.202650</t>
-  </si>
-  <si>
-    <t>20.05.202651</t>
-  </si>
-  <si>
-    <t>20.05.202652</t>
-  </si>
-  <si>
-    <t>20.05.202653</t>
-  </si>
-  <si>
-    <t>20.05.202654</t>
-  </si>
-  <si>
-    <t>20.05.202655</t>
-  </si>
-  <si>
-    <t>20.05.202656</t>
-  </si>
-  <si>
-    <t>20.05.202657</t>
-  </si>
-  <si>
-    <t>20.05.202658</t>
-  </si>
-  <si>
-    <t>20.05.202659</t>
-  </si>
-  <si>
-    <t>20.05.202660</t>
-  </si>
-  <si>
-    <t>20.05.202661</t>
-  </si>
-  <si>
-    <t>20.05.202662</t>
-  </si>
-  <si>
-    <t>20.05.202663</t>
-  </si>
-  <si>
-    <t>20.05.202664</t>
-  </si>
-  <si>
-    <t>20.05.202665</t>
-  </si>
-  <si>
-    <t>20.05.202666</t>
-  </si>
-  <si>
-    <t>20.05.202667</t>
-  </si>
-  <si>
-    <t>20.05.202668</t>
-  </si>
-  <si>
-    <t>20.05.202669</t>
-  </si>
-  <si>
-    <t>20.05.202670</t>
-  </si>
-  <si>
-    <t>20.05.202671</t>
-  </si>
-  <si>
-    <t>20.05.202672</t>
-  </si>
-  <si>
-    <t>20.05.202673</t>
-  </si>
-  <si>
-    <t>20.05.202674</t>
-  </si>
-  <si>
-    <t>20.05.202675</t>
-  </si>
-  <si>
-    <t>20.05.202676</t>
-  </si>
-  <si>
-    <t>20.05.202677</t>
-  </si>
-  <si>
-    <t>20.05.202678</t>
-  </si>
-  <si>
-    <t>20.05.202679</t>
-  </si>
-  <si>
-    <t>20.05.202680</t>
-  </si>
-  <si>
-    <t>20.05.202681</t>
-  </si>
-  <si>
-    <t>20.05.202682</t>
-  </si>
-  <si>
-    <t>20.05.202683</t>
-  </si>
-  <si>
-    <t>20.05.202684</t>
-  </si>
-  <si>
-    <t>20.05.202685</t>
-  </si>
-  <si>
-    <t>20.05.202686</t>
-  </si>
-  <si>
-    <t>20.05.202687</t>
-  </si>
-  <si>
-    <t>20.05.202688</t>
-  </si>
-  <si>
-    <t>20.05.202689</t>
-  </si>
-  <si>
-    <t>20.05.202690</t>
-  </si>
-  <si>
-    <t>20.05.202691</t>
-  </si>
-  <si>
-    <t>20.05.202692</t>
-  </si>
-  <si>
-    <t>20.05.202693</t>
-  </si>
-  <si>
-    <t>21.05.202694</t>
-  </si>
-  <si>
-    <t>21.05.202695</t>
-  </si>
-  <si>
-    <t>21.05.202696</t>
-  </si>
-  <si>
     <t>21.05.20261</t>
   </si>
   <si>
@@ -598,6 +310,9 @@
     <t>21.05.202693</t>
   </si>
   <si>
+    <t>22.05.202694</t>
+  </si>
+  <si>
     <t>22.05.202695</t>
   </si>
   <si>
@@ -608,6 +323,291 @@
   </si>
   <si>
     <t>22.05.20262</t>
+  </si>
+  <si>
+    <t>22.05.20263</t>
+  </si>
+  <si>
+    <t>22.05.20264</t>
+  </si>
+  <si>
+    <t>22.05.20265</t>
+  </si>
+  <si>
+    <t>22.05.20266</t>
+  </si>
+  <si>
+    <t>22.05.20267</t>
+  </si>
+  <si>
+    <t>22.05.20268</t>
+  </si>
+  <si>
+    <t>22.05.20269</t>
+  </si>
+  <si>
+    <t>22.05.202610</t>
+  </si>
+  <si>
+    <t>22.05.202611</t>
+  </si>
+  <si>
+    <t>22.05.202612</t>
+  </si>
+  <si>
+    <t>22.05.202613</t>
+  </si>
+  <si>
+    <t>22.05.202614</t>
+  </si>
+  <si>
+    <t>22.05.202615</t>
+  </si>
+  <si>
+    <t>22.05.202616</t>
+  </si>
+  <si>
+    <t>22.05.202617</t>
+  </si>
+  <si>
+    <t>22.05.202618</t>
+  </si>
+  <si>
+    <t>22.05.202619</t>
+  </si>
+  <si>
+    <t>22.05.202620</t>
+  </si>
+  <si>
+    <t>22.05.202621</t>
+  </si>
+  <si>
+    <t>22.05.202622</t>
+  </si>
+  <si>
+    <t>22.05.202623</t>
+  </si>
+  <si>
+    <t>22.05.202624</t>
+  </si>
+  <si>
+    <t>22.05.202625</t>
+  </si>
+  <si>
+    <t>22.05.202626</t>
+  </si>
+  <si>
+    <t>22.05.202627</t>
+  </si>
+  <si>
+    <t>22.05.202628</t>
+  </si>
+  <si>
+    <t>22.05.202629</t>
+  </si>
+  <si>
+    <t>22.05.202630</t>
+  </si>
+  <si>
+    <t>22.05.202631</t>
+  </si>
+  <si>
+    <t>22.05.202632</t>
+  </si>
+  <si>
+    <t>22.05.202633</t>
+  </si>
+  <si>
+    <t>22.05.202634</t>
+  </si>
+  <si>
+    <t>22.05.202635</t>
+  </si>
+  <si>
+    <t>22.05.202636</t>
+  </si>
+  <si>
+    <t>22.05.202637</t>
+  </si>
+  <si>
+    <t>22.05.202638</t>
+  </si>
+  <si>
+    <t>22.05.202639</t>
+  </si>
+  <si>
+    <t>22.05.202640</t>
+  </si>
+  <si>
+    <t>22.05.202641</t>
+  </si>
+  <si>
+    <t>22.05.202642</t>
+  </si>
+  <si>
+    <t>22.05.202643</t>
+  </si>
+  <si>
+    <t>22.05.202644</t>
+  </si>
+  <si>
+    <t>22.05.202645</t>
+  </si>
+  <si>
+    <t>22.05.202646</t>
+  </si>
+  <si>
+    <t>22.05.202647</t>
+  </si>
+  <si>
+    <t>22.05.202648</t>
+  </si>
+  <si>
+    <t>22.05.202649</t>
+  </si>
+  <si>
+    <t>22.05.202650</t>
+  </si>
+  <si>
+    <t>22.05.202651</t>
+  </si>
+  <si>
+    <t>22.05.202652</t>
+  </si>
+  <si>
+    <t>22.05.202653</t>
+  </si>
+  <si>
+    <t>22.05.202654</t>
+  </si>
+  <si>
+    <t>22.05.202655</t>
+  </si>
+  <si>
+    <t>22.05.202656</t>
+  </si>
+  <si>
+    <t>22.05.202657</t>
+  </si>
+  <si>
+    <t>22.05.202658</t>
+  </si>
+  <si>
+    <t>22.05.202659</t>
+  </si>
+  <si>
+    <t>22.05.202660</t>
+  </si>
+  <si>
+    <t>22.05.202661</t>
+  </si>
+  <si>
+    <t>22.05.202662</t>
+  </si>
+  <si>
+    <t>22.05.202663</t>
+  </si>
+  <si>
+    <t>22.05.202664</t>
+  </si>
+  <si>
+    <t>22.05.202665</t>
+  </si>
+  <si>
+    <t>22.05.202666</t>
+  </si>
+  <si>
+    <t>22.05.202667</t>
+  </si>
+  <si>
+    <t>22.05.202668</t>
+  </si>
+  <si>
+    <t>22.05.202669</t>
+  </si>
+  <si>
+    <t>22.05.202670</t>
+  </si>
+  <si>
+    <t>22.05.202671</t>
+  </si>
+  <si>
+    <t>22.05.202672</t>
+  </si>
+  <si>
+    <t>22.05.202673</t>
+  </si>
+  <si>
+    <t>22.05.202674</t>
+  </si>
+  <si>
+    <t>22.05.202675</t>
+  </si>
+  <si>
+    <t>22.05.202676</t>
+  </si>
+  <si>
+    <t>22.05.202677</t>
+  </si>
+  <si>
+    <t>22.05.202678</t>
+  </si>
+  <si>
+    <t>22.05.202679</t>
+  </si>
+  <si>
+    <t>22.05.202680</t>
+  </si>
+  <si>
+    <t>22.05.202681</t>
+  </si>
+  <si>
+    <t>22.05.202682</t>
+  </si>
+  <si>
+    <t>22.05.202683</t>
+  </si>
+  <si>
+    <t>22.05.202684</t>
+  </si>
+  <si>
+    <t>22.05.202685</t>
+  </si>
+  <si>
+    <t>22.05.202686</t>
+  </si>
+  <si>
+    <t>22.05.202687</t>
+  </si>
+  <si>
+    <t>22.05.202688</t>
+  </si>
+  <si>
+    <t>22.05.202689</t>
+  </si>
+  <si>
+    <t>22.05.202690</t>
+  </si>
+  <si>
+    <t>22.05.202691</t>
+  </si>
+  <si>
+    <t>22.05.202692</t>
+  </si>
+  <si>
+    <t>22.05.202693</t>
+  </si>
+  <si>
+    <t>23.05.202695</t>
+  </si>
+  <si>
+    <t>23.05.202696</t>
+  </si>
+  <si>
+    <t>23.05.20261</t>
+  </si>
+  <si>
+    <t>23.05.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46162.03611111111</v>
+        <v>46163.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46162.04652777778</v>
+        <v>46163.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46162.05694444444</v>
+        <v>46163.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46162.06736111111</v>
+        <v>46163.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46162.07777777778</v>
+        <v>46163.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46162.08819444444</v>
+        <v>46163.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46162.09861111111</v>
+        <v>46163.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46162.10902777778</v>
+        <v>46163.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46162.11944444444</v>
+        <v>46163.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46162.12986111111</v>
+        <v>46163.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46162.14027777778</v>
+        <v>46163.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46162.15069444444</v>
+        <v>46163.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46162.16111111111</v>
+        <v>46163.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46162.17152777778</v>
+        <v>46163.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46162.18194444444</v>
+        <v>46163.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46162.19236111111</v>
+        <v>46163.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46162.20277777778</v>
+        <v>46163.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46162.21319444444</v>
+        <v>46163.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46162.22361111111</v>
+        <v>46163.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46162.23402777778</v>
+        <v>46163.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46162.24444444444</v>
+        <v>46163.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46162.25486111111</v>
+        <v>46163.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46162.26527777778</v>
+        <v>46163.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46162.27569444444</v>
+        <v>46163.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46162.28611111111</v>
+        <v>46163.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46162.29652777778</v>
+        <v>46163.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46162.30694444444</v>
+        <v>46163.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46162.31736111111</v>
+        <v>46163.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46162.32777777778</v>
+        <v>46163.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46162.33819444444</v>
+        <v>46163.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46162.34861111111</v>
+        <v>46163.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46162.35902777778</v>
+        <v>46163.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46162.36944444444</v>
+        <v>46163.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46162.37986111111</v>
+        <v>46163.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46162.39027777778</v>
+        <v>46163.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46162.40069444444</v>
+        <v>46163.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46162.41111111111</v>
+        <v>46163.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46162.42152777778</v>
+        <v>46163.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46162.43194444444</v>
+        <v>46163.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46162.44236111111</v>
+        <v>46163.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46162.45277777778</v>
+        <v>46163.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46162.46319444444</v>
+        <v>46163.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46162.47361111111</v>
+        <v>46163.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46162.48402777778</v>
+        <v>46163.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46162.49444444444</v>
+        <v>46163.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46162.50486111111</v>
+        <v>46163.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46162.51527777778</v>
+        <v>46163.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46162.52569444444</v>
+        <v>46163.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46162.53611111111</v>
+        <v>46163.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46162.54652777778</v>
+        <v>46163.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46162.55694444444</v>
+        <v>46163.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46162.56736111111</v>
+        <v>46163.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46162.57777777778</v>
+        <v>46163.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46162.58819444444</v>
+        <v>46163.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46162.59861111111</v>
+        <v>46163.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46162.60902777778</v>
+        <v>46163.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46162.61944444444</v>
+        <v>46163.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46162.62986111111</v>
+        <v>46163.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46162.64027777778</v>
+        <v>46163.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46162.65069444444</v>
+        <v>46163.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46162.66111111111</v>
+        <v>46163.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46162.67152777778</v>
+        <v>46163.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46162.68194444444</v>
+        <v>46163.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46162.69236111111</v>
+        <v>46163.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46162.70277777778</v>
+        <v>46163.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46162.71319444444</v>
+        <v>46163.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46162.72361111111</v>
+        <v>46163.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46162.73402777778</v>
+        <v>46163.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46162.74444444444</v>
+        <v>46163.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46162.75486111111</v>
+        <v>46163.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46162.76527777778</v>
+        <v>46163.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46162.77569444444</v>
+        <v>46163.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46162.78611111111</v>
+        <v>46163.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46162.79652777778</v>
+        <v>46163.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46162.80694444444</v>
+        <v>46163.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46162.81736111111</v>
+        <v>46163.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46162.82777777778</v>
+        <v>46163.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46162.83819444444</v>
+        <v>46163.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46162.84861111111</v>
+        <v>46163.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46162.85902777778</v>
+        <v>46163.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46162.86944444444</v>
+        <v>46163.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46162.87986111111</v>
+        <v>46163.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46162.89027777778</v>
+        <v>46163.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46162.90069444444</v>
+        <v>46163.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46162.91111111111</v>
+        <v>46163.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46162.92152777778</v>
+        <v>46163.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46162.93194444444</v>
+        <v>46163.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46162.94236111111</v>
+        <v>46163.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46162.95277777778</v>
+        <v>46163.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46162.96319444444</v>
+        <v>46163.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46162.97361111111</v>
+        <v>46163.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46162.98402777778</v>
+        <v>46163.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46162.99444444444</v>
+        <v>46163.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46163.00486111111</v>
+        <v>46164.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46163.01527777778</v>
+        <v>46164.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46163.02569444444</v>
+        <v>46164.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46163.03611111111</v>
+        <v>46164.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46163.03611111111</v>
+        <v>46164.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46163.04652777778</v>
+        <v>46164.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46163.05694444444</v>
+        <v>46164.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46163.06736111111</v>
+        <v>46164.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46163.07777777778</v>
+        <v>46164.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46163.08819444444</v>
+        <v>46164.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46163.09861111111</v>
+        <v>46164.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46163.10902777778</v>
+        <v>46164.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46163.11944444444</v>
+        <v>46164.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46163.12986111111</v>
+        <v>46164.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46163.14027777778</v>
+        <v>46164.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46163.15069444444</v>
+        <v>46164.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46163.16111111111</v>
+        <v>46164.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46163.17152777778</v>
+        <v>46164.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46163.18194444444</v>
+        <v>46164.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46163.19236111111</v>
+        <v>46164.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46163.20277777778</v>
+        <v>46164.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46163.21319444444</v>
+        <v>46164.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46163.22361111111</v>
+        <v>46164.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46163.23402777778</v>
+        <v>46164.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46163.24444444444</v>
+        <v>46164.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46163.25486111111</v>
+        <v>46164.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46163.26527777778</v>
+        <v>46164.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46163.27569444444</v>
+        <v>46164.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46163.28611111111</v>
+        <v>46164.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46163.29652777778</v>
+        <v>46164.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46163.30694444444</v>
+        <v>46164.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46163.31736111111</v>
+        <v>46164.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46163.32777777778</v>
+        <v>46164.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46163.33819444444</v>
+        <v>46164.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46163.34861111111</v>
+        <v>46164.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46163.35902777778</v>
+        <v>46164.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46163.36944444444</v>
+        <v>46164.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46163.37986111111</v>
+        <v>46164.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46163.39027777778</v>
+        <v>46164.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46163.40069444444</v>
+        <v>46164.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46163.41111111111</v>
+        <v>46164.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46163.42152777778</v>
+        <v>46164.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46163.43194444444</v>
+        <v>46164.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46163.44236111111</v>
+        <v>46164.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46163.45277777778</v>
+        <v>46164.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46163.46319444444</v>
+        <v>46164.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46163.47361111111</v>
+        <v>46164.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46163.48402777778</v>
+        <v>46164.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46163.49444444444</v>
+        <v>46164.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46163.50486111111</v>
+        <v>46164.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46163.51527777778</v>
+        <v>46164.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46163.52569444444</v>
+        <v>46164.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46163.53611111111</v>
+        <v>46164.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46163.54652777778</v>
+        <v>46164.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46163.55694444444</v>
+        <v>46164.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46163.56736111111</v>
+        <v>46164.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46163.57777777778</v>
+        <v>46164.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46163.58819444444</v>
+        <v>46164.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46163.59861111111</v>
+        <v>46164.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46163.60902777778</v>
+        <v>46164.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46163.61944444444</v>
+        <v>46164.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46163.62986111111</v>
+        <v>46164.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46163.64027777778</v>
+        <v>46164.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46163.65069444444</v>
+        <v>46164.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46163.66111111111</v>
+        <v>46164.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46163.67152777778</v>
+        <v>46164.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46163.68194444444</v>
+        <v>46164.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46163.69236111111</v>
+        <v>46164.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46163.70277777778</v>
+        <v>46164.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46163.71319444444</v>
+        <v>46164.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46163.72361111111</v>
+        <v>46164.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46163.73402777778</v>
+        <v>46164.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46163.74444444444</v>
+        <v>46164.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46163.75486111111</v>
+        <v>46164.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46163.76527777778</v>
+        <v>46164.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46163.77569444444</v>
+        <v>46164.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46163.78611111111</v>
+        <v>46164.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46163.79652777778</v>
+        <v>46164.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46163.80694444444</v>
+        <v>46164.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46163.81736111111</v>
+        <v>46164.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46163.82777777778</v>
+        <v>46164.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46163.83819444444</v>
+        <v>46164.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46163.84861111111</v>
+        <v>46164.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46163.85902777778</v>
+        <v>46164.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46163.86944444444</v>
+        <v>46164.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46163.87986111111</v>
+        <v>46164.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46163.89027777778</v>
+        <v>46164.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46163.90069444444</v>
+        <v>46164.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46163.91111111111</v>
+        <v>46164.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46163.92152777778</v>
+        <v>46164.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46163.93194444444</v>
+        <v>46164.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46163.94236111111</v>
+        <v>46164.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46163.95277777778</v>
+        <v>46164.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46163.96319444444</v>
+        <v>46164.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46163.97361111111</v>
+        <v>46164.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46163.98402777778</v>
+        <v>46164.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46163.99444444444</v>
+        <v>46164.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46164.00486111111</v>
+        <v>46165.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46164.01527777778</v>
+        <v>46165.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46164.02569444444</v>
+        <v>46165.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46164.03611111111</v>
+        <v>46165.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="390">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>21.05.20261</t>
-  </si>
-  <si>
-    <t>21.05.20262</t>
-  </si>
-  <si>
-    <t>21.05.20263</t>
-  </si>
-  <si>
-    <t>21.05.20264</t>
-  </si>
-  <si>
-    <t>21.05.20265</t>
-  </si>
-  <si>
-    <t>21.05.20266</t>
-  </si>
-  <si>
-    <t>21.05.20267</t>
-  </si>
-  <si>
-    <t>21.05.20268</t>
-  </si>
-  <si>
-    <t>21.05.20269</t>
-  </si>
-  <si>
-    <t>21.05.202610</t>
-  </si>
-  <si>
-    <t>21.05.202611</t>
-  </si>
-  <si>
-    <t>21.05.202612</t>
-  </si>
-  <si>
-    <t>21.05.202613</t>
-  </si>
-  <si>
-    <t>21.05.202614</t>
-  </si>
-  <si>
-    <t>21.05.202615</t>
-  </si>
-  <si>
-    <t>21.05.202616</t>
-  </si>
-  <si>
-    <t>21.05.202617</t>
-  </si>
-  <si>
-    <t>21.05.202618</t>
-  </si>
-  <si>
-    <t>21.05.202619</t>
-  </si>
-  <si>
-    <t>21.05.202620</t>
-  </si>
-  <si>
-    <t>21.05.202621</t>
-  </si>
-  <si>
-    <t>21.05.202622</t>
-  </si>
-  <si>
-    <t>21.05.202623</t>
-  </si>
-  <si>
-    <t>21.05.202624</t>
-  </si>
-  <si>
-    <t>21.05.202625</t>
-  </si>
-  <si>
-    <t>21.05.202626</t>
-  </si>
-  <si>
-    <t>21.05.202627</t>
-  </si>
-  <si>
-    <t>21.05.202628</t>
-  </si>
-  <si>
-    <t>21.05.202629</t>
-  </si>
-  <si>
-    <t>21.05.202630</t>
-  </si>
-  <si>
-    <t>21.05.202631</t>
-  </si>
-  <si>
-    <t>21.05.202632</t>
-  </si>
-  <si>
-    <t>21.05.202633</t>
-  </si>
-  <si>
-    <t>21.05.202634</t>
-  </si>
-  <si>
-    <t>21.05.202635</t>
-  </si>
-  <si>
-    <t>21.05.202636</t>
-  </si>
-  <si>
-    <t>21.05.202637</t>
-  </si>
-  <si>
-    <t>21.05.202638</t>
-  </si>
-  <si>
-    <t>21.05.202639</t>
-  </si>
-  <si>
-    <t>21.05.202640</t>
-  </si>
-  <si>
-    <t>21.05.202641</t>
-  </si>
-  <si>
-    <t>21.05.202642</t>
-  </si>
-  <si>
-    <t>21.05.202643</t>
-  </si>
-  <si>
-    <t>21.05.202644</t>
-  </si>
-  <si>
-    <t>21.05.202645</t>
-  </si>
-  <si>
-    <t>21.05.202646</t>
-  </si>
-  <si>
-    <t>21.05.202647</t>
-  </si>
-  <si>
-    <t>21.05.202648</t>
-  </si>
-  <si>
-    <t>21.05.202649</t>
-  </si>
-  <si>
-    <t>21.05.202650</t>
-  </si>
-  <si>
-    <t>21.05.202651</t>
-  </si>
-  <si>
-    <t>21.05.202652</t>
-  </si>
-  <si>
-    <t>21.05.202653</t>
-  </si>
-  <si>
-    <t>21.05.202654</t>
-  </si>
-  <si>
-    <t>21.05.202655</t>
-  </si>
-  <si>
-    <t>21.05.202656</t>
-  </si>
-  <si>
-    <t>21.05.202657</t>
-  </si>
-  <si>
-    <t>21.05.202658</t>
-  </si>
-  <si>
-    <t>21.05.202659</t>
-  </si>
-  <si>
-    <t>21.05.202660</t>
-  </si>
-  <si>
-    <t>21.05.202661</t>
-  </si>
-  <si>
-    <t>21.05.202662</t>
-  </si>
-  <si>
-    <t>21.05.202663</t>
-  </si>
-  <si>
-    <t>21.05.202664</t>
-  </si>
-  <si>
-    <t>21.05.202665</t>
-  </si>
-  <si>
-    <t>21.05.202666</t>
-  </si>
-  <si>
-    <t>21.05.202667</t>
-  </si>
-  <si>
-    <t>21.05.202668</t>
-  </si>
-  <si>
-    <t>21.05.202669</t>
-  </si>
-  <si>
-    <t>21.05.202670</t>
-  </si>
-  <si>
-    <t>21.05.202671</t>
-  </si>
-  <si>
-    <t>21.05.202672</t>
-  </si>
-  <si>
-    <t>21.05.202673</t>
-  </si>
-  <si>
-    <t>21.05.202674</t>
-  </si>
-  <si>
-    <t>21.05.202675</t>
-  </si>
-  <si>
-    <t>21.05.202676</t>
-  </si>
-  <si>
-    <t>21.05.202677</t>
-  </si>
-  <si>
-    <t>21.05.202678</t>
-  </si>
-  <si>
-    <t>21.05.202679</t>
-  </si>
-  <si>
-    <t>21.05.202680</t>
-  </si>
-  <si>
-    <t>21.05.202681</t>
-  </si>
-  <si>
-    <t>21.05.202682</t>
-  </si>
-  <si>
-    <t>21.05.202683</t>
-  </si>
-  <si>
-    <t>21.05.202684</t>
-  </si>
-  <si>
-    <t>21.05.202685</t>
-  </si>
-  <si>
-    <t>21.05.202686</t>
-  </si>
-  <si>
-    <t>21.05.202687</t>
-  </si>
-  <si>
-    <t>21.05.202688</t>
-  </si>
-  <si>
-    <t>21.05.202689</t>
-  </si>
-  <si>
-    <t>21.05.202690</t>
-  </si>
-  <si>
-    <t>21.05.202691</t>
-  </si>
-  <si>
-    <t>21.05.202692</t>
-  </si>
-  <si>
-    <t>21.05.202693</t>
-  </si>
-  <si>
-    <t>22.05.202694</t>
-  </si>
-  <si>
-    <t>22.05.202695</t>
-  </si>
-  <si>
-    <t>22.05.202696</t>
-  </si>
-  <si>
     <t>22.05.20261</t>
   </si>
   <si>
@@ -598,6 +310,9 @@
     <t>22.05.202693</t>
   </si>
   <si>
+    <t>23.05.202694</t>
+  </si>
+  <si>
     <t>23.05.202695</t>
   </si>
   <si>
@@ -608,6 +323,867 @@
   </si>
   <si>
     <t>23.05.20262</t>
+  </si>
+  <si>
+    <t>23.05.20263</t>
+  </si>
+  <si>
+    <t>23.05.20264</t>
+  </si>
+  <si>
+    <t>23.05.20265</t>
+  </si>
+  <si>
+    <t>23.05.20266</t>
+  </si>
+  <si>
+    <t>23.05.20267</t>
+  </si>
+  <si>
+    <t>23.05.20268</t>
+  </si>
+  <si>
+    <t>23.05.20269</t>
+  </si>
+  <si>
+    <t>23.05.202610</t>
+  </si>
+  <si>
+    <t>23.05.202611</t>
+  </si>
+  <si>
+    <t>23.05.202612</t>
+  </si>
+  <si>
+    <t>23.05.202613</t>
+  </si>
+  <si>
+    <t>23.05.202614</t>
+  </si>
+  <si>
+    <t>23.05.202615</t>
+  </si>
+  <si>
+    <t>23.05.202616</t>
+  </si>
+  <si>
+    <t>23.05.202617</t>
+  </si>
+  <si>
+    <t>23.05.202618</t>
+  </si>
+  <si>
+    <t>23.05.202619</t>
+  </si>
+  <si>
+    <t>23.05.202620</t>
+  </si>
+  <si>
+    <t>23.05.202621</t>
+  </si>
+  <si>
+    <t>23.05.202622</t>
+  </si>
+  <si>
+    <t>23.05.202623</t>
+  </si>
+  <si>
+    <t>23.05.202624</t>
+  </si>
+  <si>
+    <t>23.05.202625</t>
+  </si>
+  <si>
+    <t>23.05.202626</t>
+  </si>
+  <si>
+    <t>23.05.202627</t>
+  </si>
+  <si>
+    <t>23.05.202628</t>
+  </si>
+  <si>
+    <t>23.05.202629</t>
+  </si>
+  <si>
+    <t>23.05.202630</t>
+  </si>
+  <si>
+    <t>23.05.202631</t>
+  </si>
+  <si>
+    <t>23.05.202632</t>
+  </si>
+  <si>
+    <t>23.05.202633</t>
+  </si>
+  <si>
+    <t>23.05.202634</t>
+  </si>
+  <si>
+    <t>23.05.202635</t>
+  </si>
+  <si>
+    <t>23.05.202636</t>
+  </si>
+  <si>
+    <t>23.05.202637</t>
+  </si>
+  <si>
+    <t>23.05.202638</t>
+  </si>
+  <si>
+    <t>23.05.202639</t>
+  </si>
+  <si>
+    <t>23.05.202640</t>
+  </si>
+  <si>
+    <t>23.05.202641</t>
+  </si>
+  <si>
+    <t>23.05.202642</t>
+  </si>
+  <si>
+    <t>23.05.202643</t>
+  </si>
+  <si>
+    <t>23.05.202644</t>
+  </si>
+  <si>
+    <t>23.05.202645</t>
+  </si>
+  <si>
+    <t>23.05.202646</t>
+  </si>
+  <si>
+    <t>23.05.202647</t>
+  </si>
+  <si>
+    <t>23.05.202648</t>
+  </si>
+  <si>
+    <t>23.05.202649</t>
+  </si>
+  <si>
+    <t>23.05.202650</t>
+  </si>
+  <si>
+    <t>23.05.202651</t>
+  </si>
+  <si>
+    <t>23.05.202652</t>
+  </si>
+  <si>
+    <t>23.05.202653</t>
+  </si>
+  <si>
+    <t>23.05.202654</t>
+  </si>
+  <si>
+    <t>23.05.202655</t>
+  </si>
+  <si>
+    <t>23.05.202656</t>
+  </si>
+  <si>
+    <t>23.05.202657</t>
+  </si>
+  <si>
+    <t>23.05.202658</t>
+  </si>
+  <si>
+    <t>23.05.202659</t>
+  </si>
+  <si>
+    <t>23.05.202660</t>
+  </si>
+  <si>
+    <t>23.05.202661</t>
+  </si>
+  <si>
+    <t>23.05.202662</t>
+  </si>
+  <si>
+    <t>23.05.202663</t>
+  </si>
+  <si>
+    <t>23.05.202664</t>
+  </si>
+  <si>
+    <t>23.05.202665</t>
+  </si>
+  <si>
+    <t>23.05.202666</t>
+  </si>
+  <si>
+    <t>23.05.202667</t>
+  </si>
+  <si>
+    <t>23.05.202668</t>
+  </si>
+  <si>
+    <t>23.05.202669</t>
+  </si>
+  <si>
+    <t>23.05.202670</t>
+  </si>
+  <si>
+    <t>23.05.202671</t>
+  </si>
+  <si>
+    <t>23.05.202672</t>
+  </si>
+  <si>
+    <t>23.05.202673</t>
+  </si>
+  <si>
+    <t>23.05.202674</t>
+  </si>
+  <si>
+    <t>23.05.202675</t>
+  </si>
+  <si>
+    <t>23.05.202676</t>
+  </si>
+  <si>
+    <t>23.05.202677</t>
+  </si>
+  <si>
+    <t>23.05.202678</t>
+  </si>
+  <si>
+    <t>23.05.202679</t>
+  </si>
+  <si>
+    <t>23.05.202680</t>
+  </si>
+  <si>
+    <t>23.05.202681</t>
+  </si>
+  <si>
+    <t>23.05.202682</t>
+  </si>
+  <si>
+    <t>23.05.202683</t>
+  </si>
+  <si>
+    <t>23.05.202684</t>
+  </si>
+  <si>
+    <t>23.05.202685</t>
+  </si>
+  <si>
+    <t>23.05.202686</t>
+  </si>
+  <si>
+    <t>23.05.202687</t>
+  </si>
+  <si>
+    <t>23.05.202688</t>
+  </si>
+  <si>
+    <t>23.05.202689</t>
+  </si>
+  <si>
+    <t>23.05.202690</t>
+  </si>
+  <si>
+    <t>23.05.202691</t>
+  </si>
+  <si>
+    <t>23.05.202692</t>
+  </si>
+  <si>
+    <t>23.05.202693</t>
+  </si>
+  <si>
+    <t>24.05.202695</t>
+  </si>
+  <si>
+    <t>24.05.202696</t>
+  </si>
+  <si>
+    <t>24.05.20261</t>
+  </si>
+  <si>
+    <t>24.05.20262</t>
+  </si>
+  <si>
+    <t>24.05.20263</t>
+  </si>
+  <si>
+    <t>24.05.20264</t>
+  </si>
+  <si>
+    <t>24.05.20265</t>
+  </si>
+  <si>
+    <t>24.05.20266</t>
+  </si>
+  <si>
+    <t>24.05.20267</t>
+  </si>
+  <si>
+    <t>24.05.20268</t>
+  </si>
+  <si>
+    <t>24.05.20269</t>
+  </si>
+  <si>
+    <t>24.05.202610</t>
+  </si>
+  <si>
+    <t>24.05.202611</t>
+  </si>
+  <si>
+    <t>24.05.202612</t>
+  </si>
+  <si>
+    <t>24.05.202613</t>
+  </si>
+  <si>
+    <t>24.05.202614</t>
+  </si>
+  <si>
+    <t>24.05.202615</t>
+  </si>
+  <si>
+    <t>24.05.202616</t>
+  </si>
+  <si>
+    <t>24.05.202617</t>
+  </si>
+  <si>
+    <t>24.05.202618</t>
+  </si>
+  <si>
+    <t>24.05.202619</t>
+  </si>
+  <si>
+    <t>24.05.202620</t>
+  </si>
+  <si>
+    <t>24.05.202621</t>
+  </si>
+  <si>
+    <t>24.05.202622</t>
+  </si>
+  <si>
+    <t>24.05.202623</t>
+  </si>
+  <si>
+    <t>24.05.202624</t>
+  </si>
+  <si>
+    <t>24.05.202625</t>
+  </si>
+  <si>
+    <t>24.05.202626</t>
+  </si>
+  <si>
+    <t>24.05.202627</t>
+  </si>
+  <si>
+    <t>24.05.202628</t>
+  </si>
+  <si>
+    <t>24.05.202629</t>
+  </si>
+  <si>
+    <t>24.05.202630</t>
+  </si>
+  <si>
+    <t>24.05.202631</t>
+  </si>
+  <si>
+    <t>24.05.202632</t>
+  </si>
+  <si>
+    <t>24.05.202633</t>
+  </si>
+  <si>
+    <t>24.05.202634</t>
+  </si>
+  <si>
+    <t>24.05.202635</t>
+  </si>
+  <si>
+    <t>24.05.202636</t>
+  </si>
+  <si>
+    <t>24.05.202637</t>
+  </si>
+  <si>
+    <t>24.05.202638</t>
+  </si>
+  <si>
+    <t>24.05.202639</t>
+  </si>
+  <si>
+    <t>24.05.202640</t>
+  </si>
+  <si>
+    <t>24.05.202641</t>
+  </si>
+  <si>
+    <t>24.05.202642</t>
+  </si>
+  <si>
+    <t>24.05.202643</t>
+  </si>
+  <si>
+    <t>24.05.202644</t>
+  </si>
+  <si>
+    <t>24.05.202645</t>
+  </si>
+  <si>
+    <t>24.05.202646</t>
+  </si>
+  <si>
+    <t>24.05.202647</t>
+  </si>
+  <si>
+    <t>24.05.202648</t>
+  </si>
+  <si>
+    <t>24.05.202649</t>
+  </si>
+  <si>
+    <t>24.05.202650</t>
+  </si>
+  <si>
+    <t>24.05.202651</t>
+  </si>
+  <si>
+    <t>24.05.202652</t>
+  </si>
+  <si>
+    <t>24.05.202653</t>
+  </si>
+  <si>
+    <t>24.05.202654</t>
+  </si>
+  <si>
+    <t>24.05.202655</t>
+  </si>
+  <si>
+    <t>24.05.202656</t>
+  </si>
+  <si>
+    <t>24.05.202657</t>
+  </si>
+  <si>
+    <t>24.05.202658</t>
+  </si>
+  <si>
+    <t>24.05.202659</t>
+  </si>
+  <si>
+    <t>24.05.202660</t>
+  </si>
+  <si>
+    <t>24.05.202661</t>
+  </si>
+  <si>
+    <t>24.05.202662</t>
+  </si>
+  <si>
+    <t>24.05.202663</t>
+  </si>
+  <si>
+    <t>24.05.202664</t>
+  </si>
+  <si>
+    <t>24.05.202665</t>
+  </si>
+  <si>
+    <t>24.05.202666</t>
+  </si>
+  <si>
+    <t>24.05.202667</t>
+  </si>
+  <si>
+    <t>24.05.202668</t>
+  </si>
+  <si>
+    <t>24.05.202669</t>
+  </si>
+  <si>
+    <t>24.05.202670</t>
+  </si>
+  <si>
+    <t>24.05.202671</t>
+  </si>
+  <si>
+    <t>24.05.202672</t>
+  </si>
+  <si>
+    <t>24.05.202673</t>
+  </si>
+  <si>
+    <t>24.05.202674</t>
+  </si>
+  <si>
+    <t>24.05.202675</t>
+  </si>
+  <si>
+    <t>24.05.202676</t>
+  </si>
+  <si>
+    <t>24.05.202677</t>
+  </si>
+  <si>
+    <t>24.05.202678</t>
+  </si>
+  <si>
+    <t>24.05.202679</t>
+  </si>
+  <si>
+    <t>24.05.202680</t>
+  </si>
+  <si>
+    <t>24.05.202681</t>
+  </si>
+  <si>
+    <t>24.05.202682</t>
+  </si>
+  <si>
+    <t>24.05.202683</t>
+  </si>
+  <si>
+    <t>24.05.202684</t>
+  </si>
+  <si>
+    <t>24.05.202685</t>
+  </si>
+  <si>
+    <t>24.05.202686</t>
+  </si>
+  <si>
+    <t>24.05.202687</t>
+  </si>
+  <si>
+    <t>24.05.202688</t>
+  </si>
+  <si>
+    <t>24.05.202689</t>
+  </si>
+  <si>
+    <t>24.05.202690</t>
+  </si>
+  <si>
+    <t>24.05.202691</t>
+  </si>
+  <si>
+    <t>24.05.202692</t>
+  </si>
+  <si>
+    <t>24.05.202693</t>
+  </si>
+  <si>
+    <t>24.05.202694</t>
+  </si>
+  <si>
+    <t>25.05.202696</t>
+  </si>
+  <si>
+    <t>25.05.20261</t>
+  </si>
+  <si>
+    <t>25.05.20262</t>
+  </si>
+  <si>
+    <t>25.05.20263</t>
+  </si>
+  <si>
+    <t>25.05.20264</t>
+  </si>
+  <si>
+    <t>25.05.20265</t>
+  </si>
+  <si>
+    <t>25.05.20266</t>
+  </si>
+  <si>
+    <t>25.05.20267</t>
+  </si>
+  <si>
+    <t>25.05.20268</t>
+  </si>
+  <si>
+    <t>25.05.20269</t>
+  </si>
+  <si>
+    <t>25.05.202610</t>
+  </si>
+  <si>
+    <t>25.05.202611</t>
+  </si>
+  <si>
+    <t>25.05.202612</t>
+  </si>
+  <si>
+    <t>25.05.202613</t>
+  </si>
+  <si>
+    <t>25.05.202614</t>
+  </si>
+  <si>
+    <t>25.05.202615</t>
+  </si>
+  <si>
+    <t>25.05.202616</t>
+  </si>
+  <si>
+    <t>25.05.202617</t>
+  </si>
+  <si>
+    <t>25.05.202618</t>
+  </si>
+  <si>
+    <t>25.05.202619</t>
+  </si>
+  <si>
+    <t>25.05.202620</t>
+  </si>
+  <si>
+    <t>25.05.202621</t>
+  </si>
+  <si>
+    <t>25.05.202622</t>
+  </si>
+  <si>
+    <t>25.05.202623</t>
+  </si>
+  <si>
+    <t>25.05.202624</t>
+  </si>
+  <si>
+    <t>25.05.202625</t>
+  </si>
+  <si>
+    <t>25.05.202626</t>
+  </si>
+  <si>
+    <t>25.05.202627</t>
+  </si>
+  <si>
+    <t>25.05.202628</t>
+  </si>
+  <si>
+    <t>25.05.202629</t>
+  </si>
+  <si>
+    <t>25.05.202630</t>
+  </si>
+  <si>
+    <t>25.05.202631</t>
+  </si>
+  <si>
+    <t>25.05.202632</t>
+  </si>
+  <si>
+    <t>25.05.202633</t>
+  </si>
+  <si>
+    <t>25.05.202634</t>
+  </si>
+  <si>
+    <t>25.05.202635</t>
+  </si>
+  <si>
+    <t>25.05.202636</t>
+  </si>
+  <si>
+    <t>25.05.202637</t>
+  </si>
+  <si>
+    <t>25.05.202638</t>
+  </si>
+  <si>
+    <t>25.05.202639</t>
+  </si>
+  <si>
+    <t>25.05.202640</t>
+  </si>
+  <si>
+    <t>25.05.202641</t>
+  </si>
+  <si>
+    <t>25.05.202642</t>
+  </si>
+  <si>
+    <t>25.05.202643</t>
+  </si>
+  <si>
+    <t>25.05.202644</t>
+  </si>
+  <si>
+    <t>25.05.202645</t>
+  </si>
+  <si>
+    <t>25.05.202646</t>
+  </si>
+  <si>
+    <t>25.05.202647</t>
+  </si>
+  <si>
+    <t>25.05.202648</t>
+  </si>
+  <si>
+    <t>25.05.202649</t>
+  </si>
+  <si>
+    <t>25.05.202650</t>
+  </si>
+  <si>
+    <t>25.05.202651</t>
+  </si>
+  <si>
+    <t>25.05.202652</t>
+  </si>
+  <si>
+    <t>25.05.202653</t>
+  </si>
+  <si>
+    <t>25.05.202654</t>
+  </si>
+  <si>
+    <t>25.05.202655</t>
+  </si>
+  <si>
+    <t>25.05.202656</t>
+  </si>
+  <si>
+    <t>25.05.202657</t>
+  </si>
+  <si>
+    <t>25.05.202658</t>
+  </si>
+  <si>
+    <t>25.05.202659</t>
+  </si>
+  <si>
+    <t>25.05.202660</t>
+  </si>
+  <si>
+    <t>25.05.202661</t>
+  </si>
+  <si>
+    <t>25.05.202662</t>
+  </si>
+  <si>
+    <t>25.05.202663</t>
+  </si>
+  <si>
+    <t>25.05.202664</t>
+  </si>
+  <si>
+    <t>25.05.202665</t>
+  </si>
+  <si>
+    <t>25.05.202666</t>
+  </si>
+  <si>
+    <t>25.05.202667</t>
+  </si>
+  <si>
+    <t>25.05.202668</t>
+  </si>
+  <si>
+    <t>25.05.202669</t>
+  </si>
+  <si>
+    <t>25.05.202670</t>
+  </si>
+  <si>
+    <t>25.05.202671</t>
+  </si>
+  <si>
+    <t>25.05.202672</t>
+  </si>
+  <si>
+    <t>25.05.202673</t>
+  </si>
+  <si>
+    <t>25.05.202674</t>
+  </si>
+  <si>
+    <t>25.05.202675</t>
+  </si>
+  <si>
+    <t>25.05.202676</t>
+  </si>
+  <si>
+    <t>25.05.202677</t>
+  </si>
+  <si>
+    <t>25.05.202678</t>
+  </si>
+  <si>
+    <t>25.05.202679</t>
+  </si>
+  <si>
+    <t>25.05.202680</t>
+  </si>
+  <si>
+    <t>25.05.202681</t>
+  </si>
+  <si>
+    <t>25.05.202682</t>
+  </si>
+  <si>
+    <t>25.05.202683</t>
+  </si>
+  <si>
+    <t>25.05.202684</t>
+  </si>
+  <si>
+    <t>25.05.202685</t>
+  </si>
+  <si>
+    <t>25.05.202686</t>
+  </si>
+  <si>
+    <t>25.05.202687</t>
+  </si>
+  <si>
+    <t>25.05.202688</t>
+  </si>
+  <si>
+    <t>25.05.202689</t>
+  </si>
+  <si>
+    <t>25.05.202690</t>
+  </si>
+  <si>
+    <t>25.05.202691</t>
+  </si>
+  <si>
+    <t>25.05.202692</t>
+  </si>
+  <si>
+    <t>25.05.202693</t>
+  </si>
+  <si>
+    <t>25.05.202694</t>
+  </si>
+  <si>
+    <t>25.05.202695</t>
+  </si>
+  <si>
+    <t>26.05.20261</t>
+  </si>
+  <si>
+    <t>26.05.20262</t>
+  </si>
+  <si>
+    <t>26.05.20263</t>
+  </si>
+  <si>
+    <t>26.05.20264</t>
   </si>
 </sst>
 </file>
@@ -969,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E389"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -991,7 +1567,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46163.03611111111</v>
+        <v>46164.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1584,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46163.04652777778</v>
+        <v>46164.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1601,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46163.05694444444</v>
+        <v>46164.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1618,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46163.06736111111</v>
+        <v>46164.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1635,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46163.07777777778</v>
+        <v>46164.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1652,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46163.08819444444</v>
+        <v>46164.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1669,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46163.09861111111</v>
+        <v>46164.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1686,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46163.10902777778</v>
+        <v>46164.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1703,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46163.11944444444</v>
+        <v>46164.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1720,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46163.12986111111</v>
+        <v>46164.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1737,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46163.14027777778</v>
+        <v>46164.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1754,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46163.15069444444</v>
+        <v>46164.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1771,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46163.16111111111</v>
+        <v>46164.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1788,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46163.17152777778</v>
+        <v>46164.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1805,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46163.18194444444</v>
+        <v>46164.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1822,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46163.19236111111</v>
+        <v>46164.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1839,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46163.20277777778</v>
+        <v>46164.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1856,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46163.21319444444</v>
+        <v>46164.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1873,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46163.22361111111</v>
+        <v>46164.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1890,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46163.23402777778</v>
+        <v>46164.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1907,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46163.24444444444</v>
+        <v>46164.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1924,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46163.25486111111</v>
+        <v>46164.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1941,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46163.26527777778</v>
+        <v>46164.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1958,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46163.27569444444</v>
+        <v>46164.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1975,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46163.28611111111</v>
+        <v>46164.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1992,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46163.29652777778</v>
+        <v>46164.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +2009,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46163.30694444444</v>
+        <v>46164.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +2026,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46163.31736111111</v>
+        <v>46164.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +2043,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46163.32777777778</v>
+        <v>46164.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +2060,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46163.33819444444</v>
+        <v>46164.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +2077,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46163.34861111111</v>
+        <v>46164.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +2094,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46163.35902777778</v>
+        <v>46164.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +2111,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46163.36944444444</v>
+        <v>46164.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +2128,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46163.37986111111</v>
+        <v>46164.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +2145,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46163.39027777778</v>
+        <v>46164.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +2162,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46163.40069444444</v>
+        <v>46164.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +2179,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46163.41111111111</v>
+        <v>46164.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +2196,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46163.42152777778</v>
+        <v>46164.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +2213,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46163.43194444444</v>
+        <v>46164.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +2230,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46163.44236111111</v>
+        <v>46164.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +2247,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46163.45277777778</v>
+        <v>46164.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +2264,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46163.46319444444</v>
+        <v>46164.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +2281,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46163.47361111111</v>
+        <v>46164.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +2298,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46163.48402777778</v>
+        <v>46164.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +2315,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46163.49444444444</v>
+        <v>46164.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +2332,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46163.50486111111</v>
+        <v>46164.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +2349,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46163.51527777778</v>
+        <v>46164.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +2366,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46163.52569444444</v>
+        <v>46164.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +2383,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46163.53611111111</v>
+        <v>46164.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +2400,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46163.54652777778</v>
+        <v>46164.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +2417,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46163.55694444444</v>
+        <v>46164.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +2434,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46163.56736111111</v>
+        <v>46164.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +2451,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46163.57777777778</v>
+        <v>46164.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +2468,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46163.58819444444</v>
+        <v>46164.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +2485,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46163.59861111111</v>
+        <v>46164.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +2502,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46163.60902777778</v>
+        <v>46164.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +2519,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46163.61944444444</v>
+        <v>46164.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +2536,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46163.62986111111</v>
+        <v>46164.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +2553,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46163.64027777778</v>
+        <v>46164.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +2570,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46163.65069444444</v>
+        <v>46164.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2587,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46163.66111111111</v>
+        <v>46164.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2604,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46163.67152777778</v>
+        <v>46164.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2621,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46163.68194444444</v>
+        <v>46164.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2638,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46163.69236111111</v>
+        <v>46164.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2655,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46163.70277777778</v>
+        <v>46164.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2672,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46163.71319444444</v>
+        <v>46164.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2689,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46163.72361111111</v>
+        <v>46164.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2706,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46163.73402777778</v>
+        <v>46164.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2723,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46163.74444444444</v>
+        <v>46164.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2740,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46163.75486111111</v>
+        <v>46164.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2757,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46163.76527777778</v>
+        <v>46164.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2774,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46163.77569444444</v>
+        <v>46164.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2791,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46163.78611111111</v>
+        <v>46164.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2808,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46163.79652777778</v>
+        <v>46164.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2825,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46163.80694444444</v>
+        <v>46164.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2842,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46163.81736111111</v>
+        <v>46164.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2859,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46163.82777777778</v>
+        <v>46164.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2876,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46163.83819444444</v>
+        <v>46164.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2893,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46163.84861111111</v>
+        <v>46164.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2910,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46163.85902777778</v>
+        <v>46164.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2927,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46163.86944444444</v>
+        <v>46164.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2944,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46163.87986111111</v>
+        <v>46164.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2961,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46163.89027777778</v>
+        <v>46164.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2978,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46163.90069444444</v>
+        <v>46164.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2995,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46163.91111111111</v>
+        <v>46164.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +3012,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46163.92152777778</v>
+        <v>46164.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +3029,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46163.93194444444</v>
+        <v>46164.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +3046,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46163.94236111111</v>
+        <v>46164.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +3063,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46163.95277777778</v>
+        <v>46164.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +3080,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46163.96319444444</v>
+        <v>46164.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +3097,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46163.97361111111</v>
+        <v>46164.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +3114,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46163.98402777778</v>
+        <v>46164.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +3131,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46163.99444444444</v>
+        <v>46164.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +3148,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46164.00486111111</v>
+        <v>46165.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +3165,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46164.01527777778</v>
+        <v>46165.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +3182,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46164.02569444444</v>
+        <v>46165.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +3199,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46164.03611111111</v>
+        <v>46165.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +3216,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46164.03611111111</v>
+        <v>46165.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +3233,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46164.04652777778</v>
+        <v>46165.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +3250,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46164.05694444444</v>
+        <v>46165.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +3267,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46164.06736111111</v>
+        <v>46165.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +3284,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46164.07777777778</v>
+        <v>46165.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +3301,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46164.08819444444</v>
+        <v>46165.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +3318,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46164.09861111111</v>
+        <v>46165.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +3335,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46164.10902777778</v>
+        <v>46165.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +3352,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46164.11944444444</v>
+        <v>46165.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +3369,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46164.12986111111</v>
+        <v>46165.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +3386,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46164.14027777778</v>
+        <v>46165.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +3403,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46164.15069444444</v>
+        <v>46165.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +3420,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46164.16111111111</v>
+        <v>46165.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +3437,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46164.17152777778</v>
+        <v>46165.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +3454,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46164.18194444444</v>
+        <v>46165.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +3471,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46164.19236111111</v>
+        <v>46165.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +3488,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46164.20277777778</v>
+        <v>46165.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +3505,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46164.21319444444</v>
+        <v>46165.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +3522,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46164.22361111111</v>
+        <v>46165.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +3539,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46164.23402777778</v>
+        <v>46165.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +3556,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46164.24444444444</v>
+        <v>46165.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +3573,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46164.25486111111</v>
+        <v>46165.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3590,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46164.26527777778</v>
+        <v>46165.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3607,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46164.27569444444</v>
+        <v>46165.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3624,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46164.28611111111</v>
+        <v>46165.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3641,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46164.29652777778</v>
+        <v>46165.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3658,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46164.30694444444</v>
+        <v>46165.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3675,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46164.31736111111</v>
+        <v>46165.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3692,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46164.32777777778</v>
+        <v>46165.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3709,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46164.33819444444</v>
+        <v>46165.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3726,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46164.34861111111</v>
+        <v>46165.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3743,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46164.35902777778</v>
+        <v>46165.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3760,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46164.36944444444</v>
+        <v>46165.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3777,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46164.37986111111</v>
+        <v>46165.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3794,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46164.39027777778</v>
+        <v>46165.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3811,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46164.40069444444</v>
+        <v>46165.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3828,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46164.41111111111</v>
+        <v>46165.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3845,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46164.42152777778</v>
+        <v>46165.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3862,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46164.43194444444</v>
+        <v>46165.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3879,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46164.44236111111</v>
+        <v>46165.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3896,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46164.45277777778</v>
+        <v>46165.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3913,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46164.46319444444</v>
+        <v>46165.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3930,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46164.47361111111</v>
+        <v>46165.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3947,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46164.48402777778</v>
+        <v>46165.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3964,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46164.49444444444</v>
+        <v>46165.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3981,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46164.50486111111</v>
+        <v>46165.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3998,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46164.51527777778</v>
+        <v>46165.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +4015,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46164.52569444444</v>
+        <v>46165.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +4032,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46164.53611111111</v>
+        <v>46165.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +4049,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46164.54652777778</v>
+        <v>46165.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +4066,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46164.55694444444</v>
+        <v>46165.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +4083,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46164.56736111111</v>
+        <v>46165.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +4100,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46164.57777777778</v>
+        <v>46165.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +4117,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46164.58819444444</v>
+        <v>46165.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +4134,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46164.59861111111</v>
+        <v>46165.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +4151,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46164.60902777778</v>
+        <v>46165.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +4168,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46164.61944444444</v>
+        <v>46165.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +4185,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46164.62986111111</v>
+        <v>46165.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +4202,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46164.64027777778</v>
+        <v>46165.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +4219,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46164.65069444444</v>
+        <v>46165.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +4236,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46164.66111111111</v>
+        <v>46165.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +4253,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46164.67152777778</v>
+        <v>46165.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +4270,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46164.68194444444</v>
+        <v>46165.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +4287,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46164.69236111111</v>
+        <v>46165.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +4304,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46164.70277777778</v>
+        <v>46165.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +4321,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46164.71319444444</v>
+        <v>46165.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +4338,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46164.72361111111</v>
+        <v>46165.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +4355,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46164.73402777778</v>
+        <v>46165.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +4372,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46164.74444444444</v>
+        <v>46165.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +4389,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46164.75486111111</v>
+        <v>46165.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +4406,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46164.76527777778</v>
+        <v>46165.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +4423,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46164.77569444444</v>
+        <v>46165.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +4440,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46164.78611111111</v>
+        <v>46165.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +4457,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46164.79652777778</v>
+        <v>46165.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +4474,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46164.80694444444</v>
+        <v>46165.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +4491,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46164.81736111111</v>
+        <v>46165.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +4508,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46164.82777777778</v>
+        <v>46165.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +4525,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46164.83819444444</v>
+        <v>46165.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +4542,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46164.84861111111</v>
+        <v>46165.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +4559,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46164.85902777778</v>
+        <v>46165.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4576,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46164.86944444444</v>
+        <v>46165.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4593,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46164.87986111111</v>
+        <v>46165.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4610,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46164.89027777778</v>
+        <v>46165.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4627,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46164.90069444444</v>
+        <v>46165.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4644,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46164.91111111111</v>
+        <v>46165.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4661,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46164.92152777778</v>
+        <v>46165.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4678,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46164.93194444444</v>
+        <v>46165.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4695,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46164.94236111111</v>
+        <v>46165.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4712,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46164.95277777778</v>
+        <v>46165.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4729,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46164.96319444444</v>
+        <v>46165.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4746,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46164.97361111111</v>
+        <v>46165.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4763,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46164.98402777778</v>
+        <v>46165.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4780,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46164.99444444444</v>
+        <v>46165.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4797,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46165.00486111111</v>
+        <v>46166.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4814,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46165.01527777778</v>
+        <v>46166.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4831,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46165.02569444444</v>
+        <v>46166.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4848,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46165.03611111111</v>
+        <v>46166.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>
@@ -4285,6 +4861,3304 @@
       </c>
       <c r="E195" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46166.03611111111</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46166.04652777778</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46166.05694444444</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46166.06736111111</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46166.07777777778</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46166.08819444444</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46166.09861111111</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46166.10902777778</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46166.11944444444</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46166.12986111111</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46166.14027777778</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46166.15069444444</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46166.16111111111</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46166.17152777778</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46166.18194444444</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46166.19236111111</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46166.20277777778</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46166.21319444444</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46166.22361111111</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46166.23402777778</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46166.24444444444</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46166.25486111111</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46166.26527777778</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46166.27569444444</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46166.28611111111</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46166.29652777778</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46166.30694444444</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46166.31736111111</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46166.32777777778</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46166.33819444444</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46166.34861111111</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46166.35902777778</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46166.36944444444</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46166.37986111111</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46166.39027777778</v>
+      </c>
+      <c r="B230">
+        <v>0</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46166.40069444444</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46166.41111111111</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46166.42152777778</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46166.43194444444</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46166.44236111111</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46166.45277777778</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46166.46319444444</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46166.47361111111</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46166.48402777778</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46166.49444444444</v>
+      </c>
+      <c r="B240">
+        <v>0</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46166.50486111111</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46166.51527777778</v>
+      </c>
+      <c r="B242">
+        <v>0</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46166.52569444444</v>
+      </c>
+      <c r="B243">
+        <v>0</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46166.53611111111</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46166.54652777778</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46166.55694444444</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46166.56736111111</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46166.57777777778</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46166.58819444444</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46166.59861111111</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46166.60902777778</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46166.61944444444</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46166.62986111111</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46166.64027777778</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46166.65069444444</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46166.66111111111</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46166.67152777778</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46166.68194444444</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46166.69236111111</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46166.70277777778</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46166.71319444444</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46166.72361111111</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46166.73402777778</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46166.74444444444</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46166.75486111111</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46166.76527777778</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46166.77569444444</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46166.78611111111</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46166.79652777778</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46166.80694444444</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46166.81736111111</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46166.82777777778</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46166.83819444444</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46166.84861111111</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46166.85902777778</v>
+      </c>
+      <c r="B275">
+        <v>0</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46166.86944444444</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46166.87986111111</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46166.89027777778</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46166.90069444444</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46166.91111111111</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46166.92152777778</v>
+      </c>
+      <c r="B281">
+        <v>0</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46166.93194444444</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46166.94236111111</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46166.95277777778</v>
+      </c>
+      <c r="B284">
+        <v>0</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46166.96319444444</v>
+      </c>
+      <c r="B285">
+        <v>0</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46166.97361111111</v>
+      </c>
+      <c r="B286">
+        <v>0</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46166.98402777778</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46166.99444444444</v>
+      </c>
+      <c r="B288">
+        <v>0</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46167.00486111111</v>
+      </c>
+      <c r="B289">
+        <v>0</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46167.01527777778</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46167.02569444444</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46167.03611111111</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46167.03611111111</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46167.04652777778</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46167.05694444444</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46167.06736111111</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46167.07777777778</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46167.08819444444</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46167.09861111111</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46167.10902777778</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46167.11944444444</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46167.12986111111</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46167.14027777778</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46167.15069444444</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46167.16111111111</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46167.17152777778</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46167.18194444444</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46167.19236111111</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46167.20277777778</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46167.21319444444</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46167.22361111111</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46167.23402777778</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46167.24444444444</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46167.25486111111</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46167.26527777778</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46167.27569444444</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46167.28611111111</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46167.29652777778</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46167.30694444444</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46167.31736111111</v>
+      </c>
+      <c r="B320">
+        <v>0</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46167.32777777778</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46167.33819444444</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46167.34861111111</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46167.35902777778</v>
+      </c>
+      <c r="B324">
+        <v>0</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46167.36944444444</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46167.37986111111</v>
+      </c>
+      <c r="B326">
+        <v>0</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46167.39027777778</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46167.40069444444</v>
+      </c>
+      <c r="B328">
+        <v>0</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46167.41111111111</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46167.42152777778</v>
+      </c>
+      <c r="B330">
+        <v>0</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46167.43194444444</v>
+      </c>
+      <c r="B331">
+        <v>0</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46167.44236111111</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46167.45277777778</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46167.46319444444</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46167.47361111111</v>
+      </c>
+      <c r="B335">
+        <v>0</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46167.48402777778</v>
+      </c>
+      <c r="B336">
+        <v>0</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46167.49444444444</v>
+      </c>
+      <c r="B337">
+        <v>0</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46167.50486111111</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46167.51527777778</v>
+      </c>
+      <c r="B339">
+        <v>0</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46167.52569444444</v>
+      </c>
+      <c r="B340">
+        <v>0</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46167.53611111111</v>
+      </c>
+      <c r="B341">
+        <v>0</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5">
+      <c r="A342" s="2">
+        <v>46167.54652777778</v>
+      </c>
+      <c r="B342">
+        <v>0</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>53</v>
+      </c>
+      <c r="E342" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
+      <c r="A343" s="2">
+        <v>46167.55694444444</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>54</v>
+      </c>
+      <c r="E343" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5">
+      <c r="A344" s="2">
+        <v>46167.56736111111</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>55</v>
+      </c>
+      <c r="E344" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5">
+      <c r="A345" s="2">
+        <v>46167.57777777778</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>56</v>
+      </c>
+      <c r="E345" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5">
+      <c r="A346" s="2">
+        <v>46167.58819444444</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>57</v>
+      </c>
+      <c r="E346" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
+      <c r="A347" s="2">
+        <v>46167.59861111111</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>58</v>
+      </c>
+      <c r="E347" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5">
+      <c r="A348" s="2">
+        <v>46167.60902777778</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>59</v>
+      </c>
+      <c r="E348" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5">
+      <c r="A349" s="2">
+        <v>46167.61944444444</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>60</v>
+      </c>
+      <c r="E349" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5">
+      <c r="A350" s="2">
+        <v>46167.62986111111</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>61</v>
+      </c>
+      <c r="E350" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5">
+      <c r="A351" s="2">
+        <v>46167.64027777778</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>62</v>
+      </c>
+      <c r="E351" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5">
+      <c r="A352" s="2">
+        <v>46167.65069444444</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>63</v>
+      </c>
+      <c r="E352" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5">
+      <c r="A353" s="2">
+        <v>46167.66111111111</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>64</v>
+      </c>
+      <c r="E353" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
+      <c r="A354" s="2">
+        <v>46167.67152777778</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>65</v>
+      </c>
+      <c r="E354" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5">
+      <c r="A355" s="2">
+        <v>46167.68194444444</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>66</v>
+      </c>
+      <c r="E355" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
+      <c r="A356" s="2">
+        <v>46167.69236111111</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>67</v>
+      </c>
+      <c r="E356" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5">
+      <c r="A357" s="2">
+        <v>46167.70277777778</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>68</v>
+      </c>
+      <c r="E357" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5">
+      <c r="A358" s="2">
+        <v>46167.71319444444</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>69</v>
+      </c>
+      <c r="E358" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5">
+      <c r="A359" s="2">
+        <v>46167.72361111111</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>70</v>
+      </c>
+      <c r="E359" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5">
+      <c r="A360" s="2">
+        <v>46167.73402777778</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>71</v>
+      </c>
+      <c r="E360" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5">
+      <c r="A361" s="2">
+        <v>46167.74444444444</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>72</v>
+      </c>
+      <c r="E361" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5">
+      <c r="A362" s="2">
+        <v>46167.75486111111</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>73</v>
+      </c>
+      <c r="E362" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5">
+      <c r="A363" s="2">
+        <v>46167.76527777778</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>74</v>
+      </c>
+      <c r="E363" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5">
+      <c r="A364" s="2">
+        <v>46167.77569444444</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>75</v>
+      </c>
+      <c r="E364" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5">
+      <c r="A365" s="2">
+        <v>46167.78611111111</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>76</v>
+      </c>
+      <c r="E365" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5">
+      <c r="A366" s="2">
+        <v>46167.79652777778</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>77</v>
+      </c>
+      <c r="E366" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5">
+      <c r="A367" s="2">
+        <v>46167.80694444444</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>78</v>
+      </c>
+      <c r="E367" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5">
+      <c r="A368" s="2">
+        <v>46167.81736111111</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>79</v>
+      </c>
+      <c r="E368" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5">
+      <c r="A369" s="2">
+        <v>46167.82777777778</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>80</v>
+      </c>
+      <c r="E369" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5">
+      <c r="A370" s="2">
+        <v>46167.83819444444</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>81</v>
+      </c>
+      <c r="E370" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5">
+      <c r="A371" s="2">
+        <v>46167.84861111111</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>82</v>
+      </c>
+      <c r="E371" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5">
+      <c r="A372" s="2">
+        <v>46167.85902777778</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>83</v>
+      </c>
+      <c r="E372" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5">
+      <c r="A373" s="2">
+        <v>46167.86944444444</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>84</v>
+      </c>
+      <c r="E373" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5">
+      <c r="A374" s="2">
+        <v>46167.87986111111</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>85</v>
+      </c>
+      <c r="E374" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5">
+      <c r="A375" s="2">
+        <v>46167.89027777778</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>86</v>
+      </c>
+      <c r="E375" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5">
+      <c r="A376" s="2">
+        <v>46167.90069444444</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>87</v>
+      </c>
+      <c r="E376" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5">
+      <c r="A377" s="2">
+        <v>46167.91111111111</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>88</v>
+      </c>
+      <c r="E377" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5">
+      <c r="A378" s="2">
+        <v>46167.92152777778</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>89</v>
+      </c>
+      <c r="E378" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5">
+      <c r="A379" s="2">
+        <v>46167.93194444444</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>90</v>
+      </c>
+      <c r="E379" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5">
+      <c r="A380" s="2">
+        <v>46167.94236111111</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>91</v>
+      </c>
+      <c r="E380" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5">
+      <c r="A381" s="2">
+        <v>46167.95277777778</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>92</v>
+      </c>
+      <c r="E381" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5">
+      <c r="A382" s="2">
+        <v>46167.96319444444</v>
+      </c>
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>93</v>
+      </c>
+      <c r="E382" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5">
+      <c r="A383" s="2">
+        <v>46167.97361111111</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>94</v>
+      </c>
+      <c r="E383" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5">
+      <c r="A384" s="2">
+        <v>46167.98402777778</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>95</v>
+      </c>
+      <c r="E384" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5">
+      <c r="A385" s="2">
+        <v>46167.99444444444</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5">
+      <c r="A386" s="2">
+        <v>46168.00486111111</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
+      <c r="A387" s="2">
+        <v>46168.01527777778</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>2</v>
+      </c>
+      <c r="E387" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5">
+      <c r="A388" s="2">
+        <v>46168.02569444444</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>3</v>
+      </c>
+      <c r="E388" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5">
+      <c r="A389" s="2">
+        <v>46168.03611111111</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>4</v>
+      </c>
+      <c r="E389" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>25.05.20261</t>
-  </si>
-  <si>
-    <t>25.05.20262</t>
-  </si>
-  <si>
-    <t>25.05.20263</t>
-  </si>
-  <si>
-    <t>25.05.20264</t>
-  </si>
-  <si>
-    <t>25.05.20265</t>
-  </si>
-  <si>
-    <t>25.05.20266</t>
-  </si>
-  <si>
-    <t>25.05.20267</t>
-  </si>
-  <si>
-    <t>25.05.20268</t>
-  </si>
-  <si>
-    <t>25.05.20269</t>
-  </si>
-  <si>
-    <t>25.05.202610</t>
-  </si>
-  <si>
-    <t>25.05.202611</t>
-  </si>
-  <si>
-    <t>25.05.202612</t>
-  </si>
-  <si>
-    <t>25.05.202613</t>
-  </si>
-  <si>
-    <t>25.05.202614</t>
-  </si>
-  <si>
-    <t>25.05.202615</t>
-  </si>
-  <si>
-    <t>25.05.202616</t>
-  </si>
-  <si>
-    <t>25.05.202617</t>
-  </si>
-  <si>
-    <t>25.05.202618</t>
-  </si>
-  <si>
-    <t>25.05.202619</t>
-  </si>
-  <si>
-    <t>25.05.202620</t>
-  </si>
-  <si>
-    <t>25.05.202621</t>
-  </si>
-  <si>
-    <t>25.05.202622</t>
-  </si>
-  <si>
-    <t>25.05.202623</t>
-  </si>
-  <si>
-    <t>25.05.202624</t>
-  </si>
-  <si>
-    <t>25.05.202625</t>
-  </si>
-  <si>
-    <t>25.05.202626</t>
-  </si>
-  <si>
-    <t>25.05.202627</t>
-  </si>
-  <si>
-    <t>25.05.202628</t>
-  </si>
-  <si>
-    <t>25.05.202629</t>
-  </si>
-  <si>
-    <t>25.05.202630</t>
-  </si>
-  <si>
-    <t>25.05.202631</t>
-  </si>
-  <si>
-    <t>25.05.202632</t>
-  </si>
-  <si>
-    <t>25.05.202633</t>
-  </si>
-  <si>
-    <t>25.05.202634</t>
-  </si>
-  <si>
-    <t>25.05.202635</t>
-  </si>
-  <si>
-    <t>25.05.202636</t>
-  </si>
-  <si>
-    <t>25.05.202637</t>
-  </si>
-  <si>
-    <t>25.05.202638</t>
-  </si>
-  <si>
-    <t>25.05.202639</t>
-  </si>
-  <si>
-    <t>25.05.202640</t>
-  </si>
-  <si>
-    <t>25.05.202641</t>
-  </si>
-  <si>
-    <t>25.05.202642</t>
-  </si>
-  <si>
-    <t>25.05.202643</t>
-  </si>
-  <si>
-    <t>25.05.202644</t>
-  </si>
-  <si>
-    <t>25.05.202645</t>
-  </si>
-  <si>
-    <t>25.05.202646</t>
-  </si>
-  <si>
-    <t>25.05.202647</t>
-  </si>
-  <si>
-    <t>25.05.202648</t>
-  </si>
-  <si>
-    <t>25.05.202649</t>
-  </si>
-  <si>
-    <t>25.05.202650</t>
-  </si>
-  <si>
-    <t>25.05.202651</t>
-  </si>
-  <si>
-    <t>25.05.202652</t>
-  </si>
-  <si>
-    <t>25.05.202653</t>
-  </si>
-  <si>
-    <t>25.05.202654</t>
-  </si>
-  <si>
-    <t>25.05.202655</t>
-  </si>
-  <si>
-    <t>25.05.202656</t>
-  </si>
-  <si>
-    <t>25.05.202657</t>
-  </si>
-  <si>
-    <t>25.05.202658</t>
-  </si>
-  <si>
-    <t>25.05.202659</t>
-  </si>
-  <si>
-    <t>25.05.202660</t>
-  </si>
-  <si>
-    <t>25.05.202661</t>
-  </si>
-  <si>
-    <t>25.05.202662</t>
-  </si>
-  <si>
-    <t>25.05.202663</t>
-  </si>
-  <si>
-    <t>25.05.202664</t>
-  </si>
-  <si>
-    <t>25.05.202665</t>
-  </si>
-  <si>
-    <t>25.05.202666</t>
-  </si>
-  <si>
-    <t>25.05.202667</t>
-  </si>
-  <si>
-    <t>25.05.202668</t>
-  </si>
-  <si>
-    <t>25.05.202669</t>
-  </si>
-  <si>
-    <t>25.05.202670</t>
-  </si>
-  <si>
-    <t>25.05.202671</t>
-  </si>
-  <si>
-    <t>25.05.202672</t>
-  </si>
-  <si>
-    <t>25.05.202673</t>
-  </si>
-  <si>
-    <t>25.05.202674</t>
-  </si>
-  <si>
-    <t>25.05.202675</t>
-  </si>
-  <si>
-    <t>25.05.202676</t>
-  </si>
-  <si>
-    <t>25.05.202677</t>
-  </si>
-  <si>
-    <t>25.05.202678</t>
-  </si>
-  <si>
-    <t>25.05.202679</t>
-  </si>
-  <si>
-    <t>25.05.202680</t>
-  </si>
-  <si>
-    <t>25.05.202681</t>
-  </si>
-  <si>
-    <t>25.05.202682</t>
-  </si>
-  <si>
-    <t>25.05.202683</t>
-  </si>
-  <si>
-    <t>25.05.202684</t>
-  </si>
-  <si>
-    <t>25.05.202685</t>
-  </si>
-  <si>
-    <t>25.05.202686</t>
-  </si>
-  <si>
-    <t>25.05.202687</t>
-  </si>
-  <si>
-    <t>25.05.202688</t>
-  </si>
-  <si>
-    <t>25.05.202689</t>
-  </si>
-  <si>
-    <t>25.05.202690</t>
-  </si>
-  <si>
-    <t>25.05.202691</t>
-  </si>
-  <si>
-    <t>25.05.202692</t>
-  </si>
-  <si>
-    <t>25.05.202693</t>
-  </si>
-  <si>
-    <t>26.05.202694</t>
-  </si>
-  <si>
-    <t>26.05.202695</t>
-  </si>
-  <si>
-    <t>26.05.202696</t>
-  </si>
-  <si>
     <t>26.05.20261</t>
   </si>
   <si>
@@ -598,6 +310,9 @@
     <t>26.05.202693</t>
   </si>
   <si>
+    <t>27.05.202694</t>
+  </si>
+  <si>
     <t>27.05.202695</t>
   </si>
   <si>
@@ -608,6 +323,291 @@
   </si>
   <si>
     <t>27.05.20262</t>
+  </si>
+  <si>
+    <t>27.05.20263</t>
+  </si>
+  <si>
+    <t>27.05.20264</t>
+  </si>
+  <si>
+    <t>27.05.20265</t>
+  </si>
+  <si>
+    <t>27.05.20266</t>
+  </si>
+  <si>
+    <t>27.05.20267</t>
+  </si>
+  <si>
+    <t>27.05.20268</t>
+  </si>
+  <si>
+    <t>27.05.20269</t>
+  </si>
+  <si>
+    <t>27.05.202610</t>
+  </si>
+  <si>
+    <t>27.05.202611</t>
+  </si>
+  <si>
+    <t>27.05.202612</t>
+  </si>
+  <si>
+    <t>27.05.202613</t>
+  </si>
+  <si>
+    <t>27.05.202614</t>
+  </si>
+  <si>
+    <t>27.05.202615</t>
+  </si>
+  <si>
+    <t>27.05.202616</t>
+  </si>
+  <si>
+    <t>27.05.202617</t>
+  </si>
+  <si>
+    <t>27.05.202618</t>
+  </si>
+  <si>
+    <t>27.05.202619</t>
+  </si>
+  <si>
+    <t>27.05.202620</t>
+  </si>
+  <si>
+    <t>27.05.202621</t>
+  </si>
+  <si>
+    <t>27.05.202622</t>
+  </si>
+  <si>
+    <t>27.05.202623</t>
+  </si>
+  <si>
+    <t>27.05.202624</t>
+  </si>
+  <si>
+    <t>27.05.202625</t>
+  </si>
+  <si>
+    <t>27.05.202626</t>
+  </si>
+  <si>
+    <t>27.05.202627</t>
+  </si>
+  <si>
+    <t>27.05.202628</t>
+  </si>
+  <si>
+    <t>27.05.202629</t>
+  </si>
+  <si>
+    <t>27.05.202630</t>
+  </si>
+  <si>
+    <t>27.05.202631</t>
+  </si>
+  <si>
+    <t>27.05.202632</t>
+  </si>
+  <si>
+    <t>27.05.202633</t>
+  </si>
+  <si>
+    <t>27.05.202634</t>
+  </si>
+  <si>
+    <t>27.05.202635</t>
+  </si>
+  <si>
+    <t>27.05.202636</t>
+  </si>
+  <si>
+    <t>27.05.202637</t>
+  </si>
+  <si>
+    <t>27.05.202638</t>
+  </si>
+  <si>
+    <t>27.05.202639</t>
+  </si>
+  <si>
+    <t>27.05.202640</t>
+  </si>
+  <si>
+    <t>27.05.202641</t>
+  </si>
+  <si>
+    <t>27.05.202642</t>
+  </si>
+  <si>
+    <t>27.05.202643</t>
+  </si>
+  <si>
+    <t>27.05.202644</t>
+  </si>
+  <si>
+    <t>27.05.202645</t>
+  </si>
+  <si>
+    <t>27.05.202646</t>
+  </si>
+  <si>
+    <t>27.05.202647</t>
+  </si>
+  <si>
+    <t>27.05.202648</t>
+  </si>
+  <si>
+    <t>27.05.202649</t>
+  </si>
+  <si>
+    <t>27.05.202650</t>
+  </si>
+  <si>
+    <t>27.05.202651</t>
+  </si>
+  <si>
+    <t>27.05.202652</t>
+  </si>
+  <si>
+    <t>27.05.202653</t>
+  </si>
+  <si>
+    <t>27.05.202654</t>
+  </si>
+  <si>
+    <t>27.05.202655</t>
+  </si>
+  <si>
+    <t>27.05.202656</t>
+  </si>
+  <si>
+    <t>27.05.202657</t>
+  </si>
+  <si>
+    <t>27.05.202658</t>
+  </si>
+  <si>
+    <t>27.05.202659</t>
+  </si>
+  <si>
+    <t>27.05.202660</t>
+  </si>
+  <si>
+    <t>27.05.202661</t>
+  </si>
+  <si>
+    <t>27.05.202662</t>
+  </si>
+  <si>
+    <t>27.05.202663</t>
+  </si>
+  <si>
+    <t>27.05.202664</t>
+  </si>
+  <si>
+    <t>27.05.202665</t>
+  </si>
+  <si>
+    <t>27.05.202666</t>
+  </si>
+  <si>
+    <t>27.05.202667</t>
+  </si>
+  <si>
+    <t>27.05.202668</t>
+  </si>
+  <si>
+    <t>27.05.202669</t>
+  </si>
+  <si>
+    <t>27.05.202670</t>
+  </si>
+  <si>
+    <t>27.05.202671</t>
+  </si>
+  <si>
+    <t>27.05.202672</t>
+  </si>
+  <si>
+    <t>27.05.202673</t>
+  </si>
+  <si>
+    <t>27.05.202674</t>
+  </si>
+  <si>
+    <t>27.05.202675</t>
+  </si>
+  <si>
+    <t>27.05.202676</t>
+  </si>
+  <si>
+    <t>27.05.202677</t>
+  </si>
+  <si>
+    <t>27.05.202678</t>
+  </si>
+  <si>
+    <t>27.05.202679</t>
+  </si>
+  <si>
+    <t>27.05.202680</t>
+  </si>
+  <si>
+    <t>27.05.202681</t>
+  </si>
+  <si>
+    <t>27.05.202682</t>
+  </si>
+  <si>
+    <t>27.05.202683</t>
+  </si>
+  <si>
+    <t>27.05.202684</t>
+  </si>
+  <si>
+    <t>27.05.202685</t>
+  </si>
+  <si>
+    <t>27.05.202686</t>
+  </si>
+  <si>
+    <t>27.05.202687</t>
+  </si>
+  <si>
+    <t>27.05.202688</t>
+  </si>
+  <si>
+    <t>27.05.202689</t>
+  </si>
+  <si>
+    <t>27.05.202690</t>
+  </si>
+  <si>
+    <t>27.05.202691</t>
+  </si>
+  <si>
+    <t>27.05.202692</t>
+  </si>
+  <si>
+    <t>27.05.202693</t>
+  </si>
+  <si>
+    <t>28.05.202695</t>
+  </si>
+  <si>
+    <t>28.05.202696</t>
+  </si>
+  <si>
+    <t>28.05.20261</t>
+  </si>
+  <si>
+    <t>28.05.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46167.03611111111</v>
+        <v>46168.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46167.04652777778</v>
+        <v>46168.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46167.05694444444</v>
+        <v>46168.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46167.06736111111</v>
+        <v>46168.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46167.07777777778</v>
+        <v>46168.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46167.08819444444</v>
+        <v>46168.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46167.09861111111</v>
+        <v>46168.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46167.10902777778</v>
+        <v>46168.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46167.11944444444</v>
+        <v>46168.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46167.12986111111</v>
+        <v>46168.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46167.14027777778</v>
+        <v>46168.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46167.15069444444</v>
+        <v>46168.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46167.16111111111</v>
+        <v>46168.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46167.17152777778</v>
+        <v>46168.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46167.18194444444</v>
+        <v>46168.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46167.19236111111</v>
+        <v>46168.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46167.20277777778</v>
+        <v>46168.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46167.21319444444</v>
+        <v>46168.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46167.22361111111</v>
+        <v>46168.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46167.23402777778</v>
+        <v>46168.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46167.24444444444</v>
+        <v>46168.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46167.25486111111</v>
+        <v>46168.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46167.26527777778</v>
+        <v>46168.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46167.27569444444</v>
+        <v>46168.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46167.28611111111</v>
+        <v>46168.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46167.29652777778</v>
+        <v>46168.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46167.30694444444</v>
+        <v>46168.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46167.31736111111</v>
+        <v>46168.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46167.32777777778</v>
+        <v>46168.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46167.33819444444</v>
+        <v>46168.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46167.34861111111</v>
+        <v>46168.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46167.35902777778</v>
+        <v>46168.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46167.36944444444</v>
+        <v>46168.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46167.37986111111</v>
+        <v>46168.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46167.39027777778</v>
+        <v>46168.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46167.40069444444</v>
+        <v>46168.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46167.41111111111</v>
+        <v>46168.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46167.42152777778</v>
+        <v>46168.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46167.43194444444</v>
+        <v>46168.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46167.44236111111</v>
+        <v>46168.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46167.45277777778</v>
+        <v>46168.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46167.46319444444</v>
+        <v>46168.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46167.47361111111</v>
+        <v>46168.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46167.48402777778</v>
+        <v>46168.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46167.49444444444</v>
+        <v>46168.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46167.50486111111</v>
+        <v>46168.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46167.51527777778</v>
+        <v>46168.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46167.52569444444</v>
+        <v>46168.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46167.53611111111</v>
+        <v>46168.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46167.54652777778</v>
+        <v>46168.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46167.55694444444</v>
+        <v>46168.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46167.56736111111</v>
+        <v>46168.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46167.57777777778</v>
+        <v>46168.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46167.58819444444</v>
+        <v>46168.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46167.59861111111</v>
+        <v>46168.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46167.60902777778</v>
+        <v>46168.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46167.61944444444</v>
+        <v>46168.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46167.62986111111</v>
+        <v>46168.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46167.64027777778</v>
+        <v>46168.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46167.65069444444</v>
+        <v>46168.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46167.66111111111</v>
+        <v>46168.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46167.67152777778</v>
+        <v>46168.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46167.68194444444</v>
+        <v>46168.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46167.69236111111</v>
+        <v>46168.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46167.70277777778</v>
+        <v>46168.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46167.71319444444</v>
+        <v>46168.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46167.72361111111</v>
+        <v>46168.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46167.73402777778</v>
+        <v>46168.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46167.74444444444</v>
+        <v>46168.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46167.75486111111</v>
+        <v>46168.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46167.76527777778</v>
+        <v>46168.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46167.77569444444</v>
+        <v>46168.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46167.78611111111</v>
+        <v>46168.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46167.79652777778</v>
+        <v>46168.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46167.80694444444</v>
+        <v>46168.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46167.81736111111</v>
+        <v>46168.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46167.82777777778</v>
+        <v>46168.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46167.83819444444</v>
+        <v>46168.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46167.84861111111</v>
+        <v>46168.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46167.85902777778</v>
+        <v>46168.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46167.86944444444</v>
+        <v>46168.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46167.87986111111</v>
+        <v>46168.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46167.89027777778</v>
+        <v>46168.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46167.90069444444</v>
+        <v>46168.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46167.91111111111</v>
+        <v>46168.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46167.92152777778</v>
+        <v>46168.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46167.93194444444</v>
+        <v>46168.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46167.94236111111</v>
+        <v>46168.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46167.95277777778</v>
+        <v>46168.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46167.96319444444</v>
+        <v>46168.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46167.97361111111</v>
+        <v>46168.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46167.98402777778</v>
+        <v>46168.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46167.99444444444</v>
+        <v>46168.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46168.00486111111</v>
+        <v>46169.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46168.01527777778</v>
+        <v>46169.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46168.02569444444</v>
+        <v>46169.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46168.03611111111</v>
+        <v>46169.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46168.03611111111</v>
+        <v>46169.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46168.04652777778</v>
+        <v>46169.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46168.05694444444</v>
+        <v>46169.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46168.06736111111</v>
+        <v>46169.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46168.07777777778</v>
+        <v>46169.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46168.08819444444</v>
+        <v>46169.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46168.09861111111</v>
+        <v>46169.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46168.10902777778</v>
+        <v>46169.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46168.11944444444</v>
+        <v>46169.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46168.12986111111</v>
+        <v>46169.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46168.14027777778</v>
+        <v>46169.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46168.15069444444</v>
+        <v>46169.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46168.16111111111</v>
+        <v>46169.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46168.17152777778</v>
+        <v>46169.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46168.18194444444</v>
+        <v>46169.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46168.19236111111</v>
+        <v>46169.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46168.20277777778</v>
+        <v>46169.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46168.21319444444</v>
+        <v>46169.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46168.22361111111</v>
+        <v>46169.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46168.23402777778</v>
+        <v>46169.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46168.24444444444</v>
+        <v>46169.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46168.25486111111</v>
+        <v>46169.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46168.26527777778</v>
+        <v>46169.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46168.27569444444</v>
+        <v>46169.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46168.28611111111</v>
+        <v>46169.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46168.29652777778</v>
+        <v>46169.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46168.30694444444</v>
+        <v>46169.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46168.31736111111</v>
+        <v>46169.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46168.32777777778</v>
+        <v>46169.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46168.33819444444</v>
+        <v>46169.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46168.34861111111</v>
+        <v>46169.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46168.35902777778</v>
+        <v>46169.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46168.36944444444</v>
+        <v>46169.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46168.37986111111</v>
+        <v>46169.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46168.39027777778</v>
+        <v>46169.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46168.40069444444</v>
+        <v>46169.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46168.41111111111</v>
+        <v>46169.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46168.42152777778</v>
+        <v>46169.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46168.43194444444</v>
+        <v>46169.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46168.44236111111</v>
+        <v>46169.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46168.45277777778</v>
+        <v>46169.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46168.46319444444</v>
+        <v>46169.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46168.47361111111</v>
+        <v>46169.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46168.48402777778</v>
+        <v>46169.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46168.49444444444</v>
+        <v>46169.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46168.50486111111</v>
+        <v>46169.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46168.51527777778</v>
+        <v>46169.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46168.52569444444</v>
+        <v>46169.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46168.53611111111</v>
+        <v>46169.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46168.54652777778</v>
+        <v>46169.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46168.55694444444</v>
+        <v>46169.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46168.56736111111</v>
+        <v>46169.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46168.57777777778</v>
+        <v>46169.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46168.58819444444</v>
+        <v>46169.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46168.59861111111</v>
+        <v>46169.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46168.60902777778</v>
+        <v>46169.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46168.61944444444</v>
+        <v>46169.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46168.62986111111</v>
+        <v>46169.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46168.64027777778</v>
+        <v>46169.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46168.65069444444</v>
+        <v>46169.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46168.66111111111</v>
+        <v>46169.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46168.67152777778</v>
+        <v>46169.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46168.68194444444</v>
+        <v>46169.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46168.69236111111</v>
+        <v>46169.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46168.70277777778</v>
+        <v>46169.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46168.71319444444</v>
+        <v>46169.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46168.72361111111</v>
+        <v>46169.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46168.73402777778</v>
+        <v>46169.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46168.74444444444</v>
+        <v>46169.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46168.75486111111</v>
+        <v>46169.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46168.76527777778</v>
+        <v>46169.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46168.77569444444</v>
+        <v>46169.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46168.78611111111</v>
+        <v>46169.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46168.79652777778</v>
+        <v>46169.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46168.80694444444</v>
+        <v>46169.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46168.81736111111</v>
+        <v>46169.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46168.82777777778</v>
+        <v>46169.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46168.83819444444</v>
+        <v>46169.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46168.84861111111</v>
+        <v>46169.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46168.85902777778</v>
+        <v>46169.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46168.86944444444</v>
+        <v>46169.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46168.87986111111</v>
+        <v>46169.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46168.89027777778</v>
+        <v>46169.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46168.90069444444</v>
+        <v>46169.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46168.91111111111</v>
+        <v>46169.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46168.92152777778</v>
+        <v>46169.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46168.93194444444</v>
+        <v>46169.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46168.94236111111</v>
+        <v>46169.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46168.95277777778</v>
+        <v>46169.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46168.96319444444</v>
+        <v>46169.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46168.97361111111</v>
+        <v>46169.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46168.98402777778</v>
+        <v>46169.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46168.99444444444</v>
+        <v>46169.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46169.00486111111</v>
+        <v>46170.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46169.01527777778</v>
+        <v>46170.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46169.02569444444</v>
+        <v>46170.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46169.03611111111</v>
+        <v>46170.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>26.05.20261</t>
-  </si>
-  <si>
-    <t>26.05.20262</t>
-  </si>
-  <si>
-    <t>26.05.20263</t>
-  </si>
-  <si>
-    <t>26.05.20264</t>
-  </si>
-  <si>
-    <t>26.05.20265</t>
-  </si>
-  <si>
-    <t>26.05.20266</t>
-  </si>
-  <si>
-    <t>26.05.20267</t>
-  </si>
-  <si>
-    <t>26.05.20268</t>
-  </si>
-  <si>
-    <t>26.05.20269</t>
-  </si>
-  <si>
-    <t>26.05.202610</t>
-  </si>
-  <si>
-    <t>26.05.202611</t>
-  </si>
-  <si>
-    <t>26.05.202612</t>
-  </si>
-  <si>
-    <t>26.05.202613</t>
-  </si>
-  <si>
-    <t>26.05.202614</t>
-  </si>
-  <si>
-    <t>26.05.202615</t>
-  </si>
-  <si>
-    <t>26.05.202616</t>
-  </si>
-  <si>
-    <t>26.05.202617</t>
-  </si>
-  <si>
-    <t>26.05.202618</t>
-  </si>
-  <si>
-    <t>26.05.202619</t>
-  </si>
-  <si>
-    <t>26.05.202620</t>
-  </si>
-  <si>
-    <t>26.05.202621</t>
-  </si>
-  <si>
-    <t>26.05.202622</t>
-  </si>
-  <si>
-    <t>26.05.202623</t>
-  </si>
-  <si>
-    <t>26.05.202624</t>
-  </si>
-  <si>
-    <t>26.05.202625</t>
-  </si>
-  <si>
-    <t>26.05.202626</t>
-  </si>
-  <si>
-    <t>26.05.202627</t>
-  </si>
-  <si>
-    <t>26.05.202628</t>
-  </si>
-  <si>
-    <t>26.05.202629</t>
-  </si>
-  <si>
-    <t>26.05.202630</t>
-  </si>
-  <si>
-    <t>26.05.202631</t>
-  </si>
-  <si>
-    <t>26.05.202632</t>
-  </si>
-  <si>
-    <t>26.05.202633</t>
-  </si>
-  <si>
-    <t>26.05.202634</t>
-  </si>
-  <si>
-    <t>26.05.202635</t>
-  </si>
-  <si>
-    <t>26.05.202636</t>
-  </si>
-  <si>
-    <t>26.05.202637</t>
-  </si>
-  <si>
-    <t>26.05.202638</t>
-  </si>
-  <si>
-    <t>26.05.202639</t>
-  </si>
-  <si>
-    <t>26.05.202640</t>
-  </si>
-  <si>
-    <t>26.05.202641</t>
-  </si>
-  <si>
-    <t>26.05.202642</t>
-  </si>
-  <si>
-    <t>26.05.202643</t>
-  </si>
-  <si>
-    <t>26.05.202644</t>
-  </si>
-  <si>
-    <t>26.05.202645</t>
-  </si>
-  <si>
-    <t>26.05.202646</t>
-  </si>
-  <si>
-    <t>26.05.202647</t>
-  </si>
-  <si>
-    <t>26.05.202648</t>
-  </si>
-  <si>
-    <t>26.05.202649</t>
-  </si>
-  <si>
-    <t>26.05.202650</t>
-  </si>
-  <si>
-    <t>26.05.202651</t>
-  </si>
-  <si>
-    <t>26.05.202652</t>
-  </si>
-  <si>
-    <t>26.05.202653</t>
-  </si>
-  <si>
-    <t>26.05.202654</t>
-  </si>
-  <si>
-    <t>26.05.202655</t>
-  </si>
-  <si>
-    <t>26.05.202656</t>
-  </si>
-  <si>
-    <t>26.05.202657</t>
-  </si>
-  <si>
-    <t>26.05.202658</t>
-  </si>
-  <si>
-    <t>26.05.202659</t>
-  </si>
-  <si>
-    <t>26.05.202660</t>
-  </si>
-  <si>
-    <t>26.05.202661</t>
-  </si>
-  <si>
-    <t>26.05.202662</t>
-  </si>
-  <si>
-    <t>26.05.202663</t>
-  </si>
-  <si>
-    <t>26.05.202664</t>
-  </si>
-  <si>
-    <t>26.05.202665</t>
-  </si>
-  <si>
-    <t>26.05.202666</t>
-  </si>
-  <si>
-    <t>26.05.202667</t>
-  </si>
-  <si>
-    <t>26.05.202668</t>
-  </si>
-  <si>
-    <t>26.05.202669</t>
-  </si>
-  <si>
-    <t>26.05.202670</t>
-  </si>
-  <si>
-    <t>26.05.202671</t>
-  </si>
-  <si>
-    <t>26.05.202672</t>
-  </si>
-  <si>
-    <t>26.05.202673</t>
-  </si>
-  <si>
-    <t>26.05.202674</t>
-  </si>
-  <si>
-    <t>26.05.202675</t>
-  </si>
-  <si>
-    <t>26.05.202676</t>
-  </si>
-  <si>
-    <t>26.05.202677</t>
-  </si>
-  <si>
-    <t>26.05.202678</t>
-  </si>
-  <si>
-    <t>26.05.202679</t>
-  </si>
-  <si>
-    <t>26.05.202680</t>
-  </si>
-  <si>
-    <t>26.05.202681</t>
-  </si>
-  <si>
-    <t>26.05.202682</t>
-  </si>
-  <si>
-    <t>26.05.202683</t>
-  </si>
-  <si>
-    <t>26.05.202684</t>
-  </si>
-  <si>
-    <t>26.05.202685</t>
-  </si>
-  <si>
-    <t>26.05.202686</t>
-  </si>
-  <si>
-    <t>26.05.202687</t>
-  </si>
-  <si>
-    <t>26.05.202688</t>
-  </si>
-  <si>
-    <t>26.05.202689</t>
-  </si>
-  <si>
-    <t>26.05.202690</t>
-  </si>
-  <si>
-    <t>26.05.202691</t>
-  </si>
-  <si>
-    <t>26.05.202692</t>
-  </si>
-  <si>
-    <t>26.05.202693</t>
-  </si>
-  <si>
-    <t>27.05.202694</t>
-  </si>
-  <si>
-    <t>27.05.202695</t>
-  </si>
-  <si>
-    <t>27.05.202696</t>
-  </si>
-  <si>
     <t>27.05.20261</t>
   </si>
   <si>
@@ -598,6 +310,9 @@
     <t>27.05.202693</t>
   </si>
   <si>
+    <t>28.05.202694</t>
+  </si>
+  <si>
     <t>28.05.202695</t>
   </si>
   <si>
@@ -608,6 +323,291 @@
   </si>
   <si>
     <t>28.05.20262</t>
+  </si>
+  <si>
+    <t>28.05.20263</t>
+  </si>
+  <si>
+    <t>28.05.20264</t>
+  </si>
+  <si>
+    <t>28.05.20265</t>
+  </si>
+  <si>
+    <t>28.05.20266</t>
+  </si>
+  <si>
+    <t>28.05.20267</t>
+  </si>
+  <si>
+    <t>28.05.20268</t>
+  </si>
+  <si>
+    <t>28.05.20269</t>
+  </si>
+  <si>
+    <t>28.05.202610</t>
+  </si>
+  <si>
+    <t>28.05.202611</t>
+  </si>
+  <si>
+    <t>28.05.202612</t>
+  </si>
+  <si>
+    <t>28.05.202613</t>
+  </si>
+  <si>
+    <t>28.05.202614</t>
+  </si>
+  <si>
+    <t>28.05.202615</t>
+  </si>
+  <si>
+    <t>28.05.202616</t>
+  </si>
+  <si>
+    <t>28.05.202617</t>
+  </si>
+  <si>
+    <t>28.05.202618</t>
+  </si>
+  <si>
+    <t>28.05.202619</t>
+  </si>
+  <si>
+    <t>28.05.202620</t>
+  </si>
+  <si>
+    <t>28.05.202621</t>
+  </si>
+  <si>
+    <t>28.05.202622</t>
+  </si>
+  <si>
+    <t>28.05.202623</t>
+  </si>
+  <si>
+    <t>28.05.202624</t>
+  </si>
+  <si>
+    <t>28.05.202625</t>
+  </si>
+  <si>
+    <t>28.05.202626</t>
+  </si>
+  <si>
+    <t>28.05.202627</t>
+  </si>
+  <si>
+    <t>28.05.202628</t>
+  </si>
+  <si>
+    <t>28.05.202629</t>
+  </si>
+  <si>
+    <t>28.05.202630</t>
+  </si>
+  <si>
+    <t>28.05.202631</t>
+  </si>
+  <si>
+    <t>28.05.202632</t>
+  </si>
+  <si>
+    <t>28.05.202633</t>
+  </si>
+  <si>
+    <t>28.05.202634</t>
+  </si>
+  <si>
+    <t>28.05.202635</t>
+  </si>
+  <si>
+    <t>28.05.202636</t>
+  </si>
+  <si>
+    <t>28.05.202637</t>
+  </si>
+  <si>
+    <t>28.05.202638</t>
+  </si>
+  <si>
+    <t>28.05.202639</t>
+  </si>
+  <si>
+    <t>28.05.202640</t>
+  </si>
+  <si>
+    <t>28.05.202641</t>
+  </si>
+  <si>
+    <t>28.05.202642</t>
+  </si>
+  <si>
+    <t>28.05.202643</t>
+  </si>
+  <si>
+    <t>28.05.202644</t>
+  </si>
+  <si>
+    <t>28.05.202645</t>
+  </si>
+  <si>
+    <t>28.05.202646</t>
+  </si>
+  <si>
+    <t>28.05.202647</t>
+  </si>
+  <si>
+    <t>28.05.202648</t>
+  </si>
+  <si>
+    <t>28.05.202649</t>
+  </si>
+  <si>
+    <t>28.05.202650</t>
+  </si>
+  <si>
+    <t>28.05.202651</t>
+  </si>
+  <si>
+    <t>28.05.202652</t>
+  </si>
+  <si>
+    <t>28.05.202653</t>
+  </si>
+  <si>
+    <t>28.05.202654</t>
+  </si>
+  <si>
+    <t>28.05.202655</t>
+  </si>
+  <si>
+    <t>28.05.202656</t>
+  </si>
+  <si>
+    <t>28.05.202657</t>
+  </si>
+  <si>
+    <t>28.05.202658</t>
+  </si>
+  <si>
+    <t>28.05.202659</t>
+  </si>
+  <si>
+    <t>28.05.202660</t>
+  </si>
+  <si>
+    <t>28.05.202661</t>
+  </si>
+  <si>
+    <t>28.05.202662</t>
+  </si>
+  <si>
+    <t>28.05.202663</t>
+  </si>
+  <si>
+    <t>28.05.202664</t>
+  </si>
+  <si>
+    <t>28.05.202665</t>
+  </si>
+  <si>
+    <t>28.05.202666</t>
+  </si>
+  <si>
+    <t>28.05.202667</t>
+  </si>
+  <si>
+    <t>28.05.202668</t>
+  </si>
+  <si>
+    <t>28.05.202669</t>
+  </si>
+  <si>
+    <t>28.05.202670</t>
+  </si>
+  <si>
+    <t>28.05.202671</t>
+  </si>
+  <si>
+    <t>28.05.202672</t>
+  </si>
+  <si>
+    <t>28.05.202673</t>
+  </si>
+  <si>
+    <t>28.05.202674</t>
+  </si>
+  <si>
+    <t>28.05.202675</t>
+  </si>
+  <si>
+    <t>28.05.202676</t>
+  </si>
+  <si>
+    <t>28.05.202677</t>
+  </si>
+  <si>
+    <t>28.05.202678</t>
+  </si>
+  <si>
+    <t>28.05.202679</t>
+  </si>
+  <si>
+    <t>28.05.202680</t>
+  </si>
+  <si>
+    <t>28.05.202681</t>
+  </si>
+  <si>
+    <t>28.05.202682</t>
+  </si>
+  <si>
+    <t>28.05.202683</t>
+  </si>
+  <si>
+    <t>28.05.202684</t>
+  </si>
+  <si>
+    <t>28.05.202685</t>
+  </si>
+  <si>
+    <t>28.05.202686</t>
+  </si>
+  <si>
+    <t>28.05.202687</t>
+  </si>
+  <si>
+    <t>28.05.202688</t>
+  </si>
+  <si>
+    <t>28.05.202689</t>
+  </si>
+  <si>
+    <t>28.05.202690</t>
+  </si>
+  <si>
+    <t>28.05.202691</t>
+  </si>
+  <si>
+    <t>28.05.202692</t>
+  </si>
+  <si>
+    <t>28.05.202693</t>
+  </si>
+  <si>
+    <t>29.05.202695</t>
+  </si>
+  <si>
+    <t>29.05.202696</t>
+  </si>
+  <si>
+    <t>29.05.20261</t>
+  </si>
+  <si>
+    <t>29.05.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46168.03611111111</v>
+        <v>46169.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46168.04652777778</v>
+        <v>46169.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46168.05694444444</v>
+        <v>46169.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46168.06736111111</v>
+        <v>46169.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46168.07777777778</v>
+        <v>46169.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46168.08819444444</v>
+        <v>46169.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46168.09861111111</v>
+        <v>46169.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46168.10902777778</v>
+        <v>46169.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46168.11944444444</v>
+        <v>46169.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46168.12986111111</v>
+        <v>46169.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46168.14027777778</v>
+        <v>46169.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46168.15069444444</v>
+        <v>46169.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46168.16111111111</v>
+        <v>46169.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46168.17152777778</v>
+        <v>46169.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46168.18194444444</v>
+        <v>46169.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46168.19236111111</v>
+        <v>46169.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46168.20277777778</v>
+        <v>46169.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46168.21319444444</v>
+        <v>46169.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46168.22361111111</v>
+        <v>46169.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46168.23402777778</v>
+        <v>46169.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46168.24444444444</v>
+        <v>46169.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46168.25486111111</v>
+        <v>46169.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46168.26527777778</v>
+        <v>46169.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46168.27569444444</v>
+        <v>46169.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46168.28611111111</v>
+        <v>46169.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46168.29652777778</v>
+        <v>46169.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46168.30694444444</v>
+        <v>46169.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46168.31736111111</v>
+        <v>46169.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46168.32777777778</v>
+        <v>46169.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46168.33819444444</v>
+        <v>46169.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46168.34861111111</v>
+        <v>46169.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46168.35902777778</v>
+        <v>46169.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46168.36944444444</v>
+        <v>46169.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46168.37986111111</v>
+        <v>46169.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46168.39027777778</v>
+        <v>46169.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46168.40069444444</v>
+        <v>46169.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46168.41111111111</v>
+        <v>46169.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46168.42152777778</v>
+        <v>46169.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46168.43194444444</v>
+        <v>46169.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46168.44236111111</v>
+        <v>46169.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46168.45277777778</v>
+        <v>46169.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46168.46319444444</v>
+        <v>46169.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46168.47361111111</v>
+        <v>46169.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46168.48402777778</v>
+        <v>46169.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46168.49444444444</v>
+        <v>46169.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46168.50486111111</v>
+        <v>46169.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46168.51527777778</v>
+        <v>46169.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46168.52569444444</v>
+        <v>46169.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46168.53611111111</v>
+        <v>46169.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46168.54652777778</v>
+        <v>46169.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46168.55694444444</v>
+        <v>46169.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46168.56736111111</v>
+        <v>46169.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46168.57777777778</v>
+        <v>46169.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46168.58819444444</v>
+        <v>46169.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46168.59861111111</v>
+        <v>46169.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46168.60902777778</v>
+        <v>46169.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46168.61944444444</v>
+        <v>46169.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46168.62986111111</v>
+        <v>46169.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46168.64027777778</v>
+        <v>46169.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46168.65069444444</v>
+        <v>46169.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46168.66111111111</v>
+        <v>46169.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46168.67152777778</v>
+        <v>46169.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46168.68194444444</v>
+        <v>46169.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46168.69236111111</v>
+        <v>46169.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46168.70277777778</v>
+        <v>46169.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46168.71319444444</v>
+        <v>46169.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46168.72361111111</v>
+        <v>46169.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46168.73402777778</v>
+        <v>46169.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46168.74444444444</v>
+        <v>46169.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46168.75486111111</v>
+        <v>46169.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46168.76527777778</v>
+        <v>46169.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46168.77569444444</v>
+        <v>46169.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46168.78611111111</v>
+        <v>46169.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46168.79652777778</v>
+        <v>46169.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46168.80694444444</v>
+        <v>46169.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46168.81736111111</v>
+        <v>46169.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46168.82777777778</v>
+        <v>46169.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46168.83819444444</v>
+        <v>46169.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46168.84861111111</v>
+        <v>46169.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46168.85902777778</v>
+        <v>46169.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46168.86944444444</v>
+        <v>46169.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46168.87986111111</v>
+        <v>46169.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46168.89027777778</v>
+        <v>46169.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46168.90069444444</v>
+        <v>46169.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46168.91111111111</v>
+        <v>46169.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46168.92152777778</v>
+        <v>46169.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46168.93194444444</v>
+        <v>46169.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46168.94236111111</v>
+        <v>46169.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46168.95277777778</v>
+        <v>46169.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46168.96319444444</v>
+        <v>46169.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46168.97361111111</v>
+        <v>46169.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46168.98402777778</v>
+        <v>46169.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46168.99444444444</v>
+        <v>46169.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46169.00486111111</v>
+        <v>46170.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46169.01527777778</v>
+        <v>46170.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46169.02569444444</v>
+        <v>46170.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46169.03611111111</v>
+        <v>46170.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46169.03611111111</v>
+        <v>46170.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46169.04652777778</v>
+        <v>46170.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46169.05694444444</v>
+        <v>46170.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46169.06736111111</v>
+        <v>46170.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46169.07777777778</v>
+        <v>46170.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46169.08819444444</v>
+        <v>46170.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46169.09861111111</v>
+        <v>46170.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46169.10902777778</v>
+        <v>46170.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46169.11944444444</v>
+        <v>46170.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46169.12986111111</v>
+        <v>46170.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46169.14027777778</v>
+        <v>46170.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46169.15069444444</v>
+        <v>46170.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46169.16111111111</v>
+        <v>46170.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46169.17152777778</v>
+        <v>46170.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46169.18194444444</v>
+        <v>46170.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46169.19236111111</v>
+        <v>46170.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46169.20277777778</v>
+        <v>46170.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46169.21319444444</v>
+        <v>46170.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46169.22361111111</v>
+        <v>46170.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46169.23402777778</v>
+        <v>46170.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46169.24444444444</v>
+        <v>46170.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46169.25486111111</v>
+        <v>46170.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46169.26527777778</v>
+        <v>46170.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46169.27569444444</v>
+        <v>46170.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46169.28611111111</v>
+        <v>46170.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46169.29652777778</v>
+        <v>46170.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46169.30694444444</v>
+        <v>46170.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46169.31736111111</v>
+        <v>46170.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46169.32777777778</v>
+        <v>46170.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46169.33819444444</v>
+        <v>46170.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46169.34861111111</v>
+        <v>46170.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46169.35902777778</v>
+        <v>46170.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46169.36944444444</v>
+        <v>46170.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46169.37986111111</v>
+        <v>46170.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46169.39027777778</v>
+        <v>46170.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46169.40069444444</v>
+        <v>46170.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46169.41111111111</v>
+        <v>46170.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46169.42152777778</v>
+        <v>46170.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46169.43194444444</v>
+        <v>46170.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46169.44236111111</v>
+        <v>46170.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46169.45277777778</v>
+        <v>46170.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46169.46319444444</v>
+        <v>46170.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46169.47361111111</v>
+        <v>46170.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46169.48402777778</v>
+        <v>46170.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46169.49444444444</v>
+        <v>46170.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46169.50486111111</v>
+        <v>46170.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46169.51527777778</v>
+        <v>46170.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46169.52569444444</v>
+        <v>46170.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46169.53611111111</v>
+        <v>46170.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46169.54652777778</v>
+        <v>46170.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46169.55694444444</v>
+        <v>46170.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46169.56736111111</v>
+        <v>46170.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46169.57777777778</v>
+        <v>46170.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46169.58819444444</v>
+        <v>46170.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46169.59861111111</v>
+        <v>46170.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46169.60902777778</v>
+        <v>46170.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46169.61944444444</v>
+        <v>46170.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46169.62986111111</v>
+        <v>46170.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46169.64027777778</v>
+        <v>46170.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46169.65069444444</v>
+        <v>46170.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46169.66111111111</v>
+        <v>46170.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46169.67152777778</v>
+        <v>46170.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46169.68194444444</v>
+        <v>46170.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46169.69236111111</v>
+        <v>46170.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46169.70277777778</v>
+        <v>46170.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46169.71319444444</v>
+        <v>46170.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46169.72361111111</v>
+        <v>46170.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46169.73402777778</v>
+        <v>46170.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46169.74444444444</v>
+        <v>46170.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46169.75486111111</v>
+        <v>46170.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46169.76527777778</v>
+        <v>46170.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46169.77569444444</v>
+        <v>46170.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46169.78611111111</v>
+        <v>46170.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46169.79652777778</v>
+        <v>46170.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46169.80694444444</v>
+        <v>46170.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46169.81736111111</v>
+        <v>46170.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46169.82777777778</v>
+        <v>46170.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46169.83819444444</v>
+        <v>46170.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46169.84861111111</v>
+        <v>46170.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46169.85902777778</v>
+        <v>46170.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46169.86944444444</v>
+        <v>46170.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46169.87986111111</v>
+        <v>46170.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46169.89027777778</v>
+        <v>46170.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46169.90069444444</v>
+        <v>46170.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46169.91111111111</v>
+        <v>46170.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46169.92152777778</v>
+        <v>46170.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46169.93194444444</v>
+        <v>46170.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46169.94236111111</v>
+        <v>46170.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46169.95277777778</v>
+        <v>46170.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46169.96319444444</v>
+        <v>46170.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46169.97361111111</v>
+        <v>46170.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46169.98402777778</v>
+        <v>46170.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46169.99444444444</v>
+        <v>46170.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46170.00486111111</v>
+        <v>46171.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46170.01527777778</v>
+        <v>46171.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46170.02569444444</v>
+        <v>46171.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46170.03611111111</v>
+        <v>46171.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>27.05.20261</t>
-  </si>
-  <si>
-    <t>27.05.20262</t>
-  </si>
-  <si>
-    <t>27.05.20263</t>
-  </si>
-  <si>
-    <t>27.05.20264</t>
-  </si>
-  <si>
-    <t>27.05.20265</t>
-  </si>
-  <si>
-    <t>27.05.20266</t>
-  </si>
-  <si>
-    <t>27.05.20267</t>
-  </si>
-  <si>
-    <t>27.05.20268</t>
-  </si>
-  <si>
-    <t>27.05.20269</t>
-  </si>
-  <si>
-    <t>27.05.202610</t>
-  </si>
-  <si>
-    <t>27.05.202611</t>
-  </si>
-  <si>
-    <t>27.05.202612</t>
-  </si>
-  <si>
-    <t>27.05.202613</t>
-  </si>
-  <si>
-    <t>27.05.202614</t>
-  </si>
-  <si>
-    <t>27.05.202615</t>
-  </si>
-  <si>
-    <t>27.05.202616</t>
-  </si>
-  <si>
-    <t>27.05.202617</t>
-  </si>
-  <si>
-    <t>27.05.202618</t>
-  </si>
-  <si>
-    <t>27.05.202619</t>
-  </si>
-  <si>
-    <t>27.05.202620</t>
-  </si>
-  <si>
-    <t>27.05.202621</t>
-  </si>
-  <si>
-    <t>27.05.202622</t>
-  </si>
-  <si>
-    <t>27.05.202623</t>
-  </si>
-  <si>
-    <t>27.05.202624</t>
-  </si>
-  <si>
-    <t>27.05.202625</t>
-  </si>
-  <si>
-    <t>27.05.202626</t>
-  </si>
-  <si>
-    <t>27.05.202627</t>
-  </si>
-  <si>
-    <t>27.05.202628</t>
-  </si>
-  <si>
-    <t>27.05.202629</t>
-  </si>
-  <si>
-    <t>27.05.202630</t>
-  </si>
-  <si>
-    <t>27.05.202631</t>
-  </si>
-  <si>
-    <t>27.05.202632</t>
-  </si>
-  <si>
-    <t>27.05.202633</t>
-  </si>
-  <si>
-    <t>27.05.202634</t>
-  </si>
-  <si>
-    <t>27.05.202635</t>
-  </si>
-  <si>
-    <t>27.05.202636</t>
-  </si>
-  <si>
-    <t>27.05.202637</t>
-  </si>
-  <si>
-    <t>27.05.202638</t>
-  </si>
-  <si>
-    <t>27.05.202639</t>
-  </si>
-  <si>
-    <t>27.05.202640</t>
-  </si>
-  <si>
-    <t>27.05.202641</t>
-  </si>
-  <si>
-    <t>27.05.202642</t>
-  </si>
-  <si>
-    <t>27.05.202643</t>
-  </si>
-  <si>
-    <t>27.05.202644</t>
-  </si>
-  <si>
-    <t>27.05.202645</t>
-  </si>
-  <si>
-    <t>27.05.202646</t>
-  </si>
-  <si>
-    <t>27.05.202647</t>
-  </si>
-  <si>
-    <t>27.05.202648</t>
-  </si>
-  <si>
-    <t>27.05.202649</t>
-  </si>
-  <si>
-    <t>27.05.202650</t>
-  </si>
-  <si>
-    <t>27.05.202651</t>
-  </si>
-  <si>
-    <t>27.05.202652</t>
-  </si>
-  <si>
-    <t>27.05.202653</t>
-  </si>
-  <si>
-    <t>27.05.202654</t>
-  </si>
-  <si>
-    <t>27.05.202655</t>
-  </si>
-  <si>
-    <t>27.05.202656</t>
-  </si>
-  <si>
-    <t>27.05.202657</t>
-  </si>
-  <si>
-    <t>27.05.202658</t>
-  </si>
-  <si>
-    <t>27.05.202659</t>
-  </si>
-  <si>
-    <t>27.05.202660</t>
-  </si>
-  <si>
-    <t>27.05.202661</t>
-  </si>
-  <si>
-    <t>27.05.202662</t>
-  </si>
-  <si>
-    <t>27.05.202663</t>
-  </si>
-  <si>
-    <t>27.05.202664</t>
-  </si>
-  <si>
-    <t>27.05.202665</t>
-  </si>
-  <si>
-    <t>27.05.202666</t>
-  </si>
-  <si>
-    <t>27.05.202667</t>
-  </si>
-  <si>
-    <t>27.05.202668</t>
-  </si>
-  <si>
-    <t>27.05.202669</t>
-  </si>
-  <si>
-    <t>27.05.202670</t>
-  </si>
-  <si>
-    <t>27.05.202671</t>
-  </si>
-  <si>
-    <t>27.05.202672</t>
-  </si>
-  <si>
-    <t>27.05.202673</t>
-  </si>
-  <si>
-    <t>27.05.202674</t>
-  </si>
-  <si>
-    <t>27.05.202675</t>
-  </si>
-  <si>
-    <t>27.05.202676</t>
-  </si>
-  <si>
-    <t>27.05.202677</t>
-  </si>
-  <si>
-    <t>27.05.202678</t>
-  </si>
-  <si>
-    <t>27.05.202679</t>
-  </si>
-  <si>
-    <t>27.05.202680</t>
-  </si>
-  <si>
-    <t>27.05.202681</t>
-  </si>
-  <si>
-    <t>27.05.202682</t>
-  </si>
-  <si>
-    <t>27.05.202683</t>
-  </si>
-  <si>
-    <t>27.05.202684</t>
-  </si>
-  <si>
-    <t>27.05.202685</t>
-  </si>
-  <si>
-    <t>27.05.202686</t>
-  </si>
-  <si>
-    <t>27.05.202687</t>
-  </si>
-  <si>
-    <t>27.05.202688</t>
-  </si>
-  <si>
-    <t>27.05.202689</t>
-  </si>
-  <si>
-    <t>27.05.202690</t>
-  </si>
-  <si>
-    <t>27.05.202691</t>
-  </si>
-  <si>
-    <t>27.05.202692</t>
-  </si>
-  <si>
-    <t>27.05.202693</t>
-  </si>
-  <si>
-    <t>28.05.202694</t>
-  </si>
-  <si>
-    <t>28.05.202695</t>
-  </si>
-  <si>
-    <t>28.05.202696</t>
-  </si>
-  <si>
     <t>28.05.20261</t>
   </si>
   <si>
@@ -598,6 +310,9 @@
     <t>28.05.202693</t>
   </si>
   <si>
+    <t>29.05.202694</t>
+  </si>
+  <si>
     <t>29.05.202695</t>
   </si>
   <si>
@@ -608,6 +323,291 @@
   </si>
   <si>
     <t>29.05.20262</t>
+  </si>
+  <si>
+    <t>29.05.20263</t>
+  </si>
+  <si>
+    <t>29.05.20264</t>
+  </si>
+  <si>
+    <t>29.05.20265</t>
+  </si>
+  <si>
+    <t>29.05.20266</t>
+  </si>
+  <si>
+    <t>29.05.20267</t>
+  </si>
+  <si>
+    <t>29.05.20268</t>
+  </si>
+  <si>
+    <t>29.05.20269</t>
+  </si>
+  <si>
+    <t>29.05.202610</t>
+  </si>
+  <si>
+    <t>29.05.202611</t>
+  </si>
+  <si>
+    <t>29.05.202612</t>
+  </si>
+  <si>
+    <t>29.05.202613</t>
+  </si>
+  <si>
+    <t>29.05.202614</t>
+  </si>
+  <si>
+    <t>29.05.202615</t>
+  </si>
+  <si>
+    <t>29.05.202616</t>
+  </si>
+  <si>
+    <t>29.05.202617</t>
+  </si>
+  <si>
+    <t>29.05.202618</t>
+  </si>
+  <si>
+    <t>29.05.202619</t>
+  </si>
+  <si>
+    <t>29.05.202620</t>
+  </si>
+  <si>
+    <t>29.05.202621</t>
+  </si>
+  <si>
+    <t>29.05.202622</t>
+  </si>
+  <si>
+    <t>29.05.202623</t>
+  </si>
+  <si>
+    <t>29.05.202624</t>
+  </si>
+  <si>
+    <t>29.05.202625</t>
+  </si>
+  <si>
+    <t>29.05.202626</t>
+  </si>
+  <si>
+    <t>29.05.202627</t>
+  </si>
+  <si>
+    <t>29.05.202628</t>
+  </si>
+  <si>
+    <t>29.05.202629</t>
+  </si>
+  <si>
+    <t>29.05.202630</t>
+  </si>
+  <si>
+    <t>29.05.202631</t>
+  </si>
+  <si>
+    <t>29.05.202632</t>
+  </si>
+  <si>
+    <t>29.05.202633</t>
+  </si>
+  <si>
+    <t>29.05.202634</t>
+  </si>
+  <si>
+    <t>29.05.202635</t>
+  </si>
+  <si>
+    <t>29.05.202636</t>
+  </si>
+  <si>
+    <t>29.05.202637</t>
+  </si>
+  <si>
+    <t>29.05.202638</t>
+  </si>
+  <si>
+    <t>29.05.202639</t>
+  </si>
+  <si>
+    <t>29.05.202640</t>
+  </si>
+  <si>
+    <t>29.05.202641</t>
+  </si>
+  <si>
+    <t>29.05.202642</t>
+  </si>
+  <si>
+    <t>29.05.202643</t>
+  </si>
+  <si>
+    <t>29.05.202644</t>
+  </si>
+  <si>
+    <t>29.05.202645</t>
+  </si>
+  <si>
+    <t>29.05.202646</t>
+  </si>
+  <si>
+    <t>29.05.202647</t>
+  </si>
+  <si>
+    <t>29.05.202648</t>
+  </si>
+  <si>
+    <t>29.05.202649</t>
+  </si>
+  <si>
+    <t>29.05.202650</t>
+  </si>
+  <si>
+    <t>29.05.202651</t>
+  </si>
+  <si>
+    <t>29.05.202652</t>
+  </si>
+  <si>
+    <t>29.05.202653</t>
+  </si>
+  <si>
+    <t>29.05.202654</t>
+  </si>
+  <si>
+    <t>29.05.202655</t>
+  </si>
+  <si>
+    <t>29.05.202656</t>
+  </si>
+  <si>
+    <t>29.05.202657</t>
+  </si>
+  <si>
+    <t>29.05.202658</t>
+  </si>
+  <si>
+    <t>29.05.202659</t>
+  </si>
+  <si>
+    <t>29.05.202660</t>
+  </si>
+  <si>
+    <t>29.05.202661</t>
+  </si>
+  <si>
+    <t>29.05.202662</t>
+  </si>
+  <si>
+    <t>29.05.202663</t>
+  </si>
+  <si>
+    <t>29.05.202664</t>
+  </si>
+  <si>
+    <t>29.05.202665</t>
+  </si>
+  <si>
+    <t>29.05.202666</t>
+  </si>
+  <si>
+    <t>29.05.202667</t>
+  </si>
+  <si>
+    <t>29.05.202668</t>
+  </si>
+  <si>
+    <t>29.05.202669</t>
+  </si>
+  <si>
+    <t>29.05.202670</t>
+  </si>
+  <si>
+    <t>29.05.202671</t>
+  </si>
+  <si>
+    <t>29.05.202672</t>
+  </si>
+  <si>
+    <t>29.05.202673</t>
+  </si>
+  <si>
+    <t>29.05.202674</t>
+  </si>
+  <si>
+    <t>29.05.202675</t>
+  </si>
+  <si>
+    <t>29.05.202676</t>
+  </si>
+  <si>
+    <t>29.05.202677</t>
+  </si>
+  <si>
+    <t>29.05.202678</t>
+  </si>
+  <si>
+    <t>29.05.202679</t>
+  </si>
+  <si>
+    <t>29.05.202680</t>
+  </si>
+  <si>
+    <t>29.05.202681</t>
+  </si>
+  <si>
+    <t>29.05.202682</t>
+  </si>
+  <si>
+    <t>29.05.202683</t>
+  </si>
+  <si>
+    <t>29.05.202684</t>
+  </si>
+  <si>
+    <t>29.05.202685</t>
+  </si>
+  <si>
+    <t>29.05.202686</t>
+  </si>
+  <si>
+    <t>29.05.202687</t>
+  </si>
+  <si>
+    <t>29.05.202688</t>
+  </si>
+  <si>
+    <t>29.05.202689</t>
+  </si>
+  <si>
+    <t>29.05.202690</t>
+  </si>
+  <si>
+    <t>29.05.202691</t>
+  </si>
+  <si>
+    <t>29.05.202692</t>
+  </si>
+  <si>
+    <t>29.05.202693</t>
+  </si>
+  <si>
+    <t>30.05.202695</t>
+  </si>
+  <si>
+    <t>30.05.202696</t>
+  </si>
+  <si>
+    <t>30.05.20261</t>
+  </si>
+  <si>
+    <t>30.05.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46169.03611111111</v>
+        <v>46170.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46169.04652777778</v>
+        <v>46170.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46169.05694444444</v>
+        <v>46170.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46169.06736111111</v>
+        <v>46170.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46169.07777777778</v>
+        <v>46170.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46169.08819444444</v>
+        <v>46170.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46169.09861111111</v>
+        <v>46170.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46169.10902777778</v>
+        <v>46170.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46169.11944444444</v>
+        <v>46170.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46169.12986111111</v>
+        <v>46170.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46169.14027777778</v>
+        <v>46170.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46169.15069444444</v>
+        <v>46170.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46169.16111111111</v>
+        <v>46170.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46169.17152777778</v>
+        <v>46170.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46169.18194444444</v>
+        <v>46170.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46169.19236111111</v>
+        <v>46170.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46169.20277777778</v>
+        <v>46170.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46169.21319444444</v>
+        <v>46170.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46169.22361111111</v>
+        <v>46170.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46169.23402777778</v>
+        <v>46170.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46169.24444444444</v>
+        <v>46170.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46169.25486111111</v>
+        <v>46170.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46169.26527777778</v>
+        <v>46170.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46169.27569444444</v>
+        <v>46170.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46169.28611111111</v>
+        <v>46170.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46169.29652777778</v>
+        <v>46170.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46169.30694444444</v>
+        <v>46170.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46169.31736111111</v>
+        <v>46170.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46169.32777777778</v>
+        <v>46170.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46169.33819444444</v>
+        <v>46170.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46169.34861111111</v>
+        <v>46170.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46169.35902777778</v>
+        <v>46170.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46169.36944444444</v>
+        <v>46170.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46169.37986111111</v>
+        <v>46170.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46169.39027777778</v>
+        <v>46170.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46169.40069444444</v>
+        <v>46170.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46169.41111111111</v>
+        <v>46170.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46169.42152777778</v>
+        <v>46170.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46169.43194444444</v>
+        <v>46170.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46169.44236111111</v>
+        <v>46170.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46169.45277777778</v>
+        <v>46170.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46169.46319444444</v>
+        <v>46170.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46169.47361111111</v>
+        <v>46170.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46169.48402777778</v>
+        <v>46170.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46169.49444444444</v>
+        <v>46170.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46169.50486111111</v>
+        <v>46170.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46169.51527777778</v>
+        <v>46170.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46169.52569444444</v>
+        <v>46170.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46169.53611111111</v>
+        <v>46170.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46169.54652777778</v>
+        <v>46170.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46169.55694444444</v>
+        <v>46170.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46169.56736111111</v>
+        <v>46170.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46169.57777777778</v>
+        <v>46170.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46169.58819444444</v>
+        <v>46170.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46169.59861111111</v>
+        <v>46170.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46169.60902777778</v>
+        <v>46170.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46169.61944444444</v>
+        <v>46170.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46169.62986111111</v>
+        <v>46170.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46169.64027777778</v>
+        <v>46170.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46169.65069444444</v>
+        <v>46170.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46169.66111111111</v>
+        <v>46170.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46169.67152777778</v>
+        <v>46170.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46169.68194444444</v>
+        <v>46170.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46169.69236111111</v>
+        <v>46170.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46169.70277777778</v>
+        <v>46170.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46169.71319444444</v>
+        <v>46170.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46169.72361111111</v>
+        <v>46170.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46169.73402777778</v>
+        <v>46170.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46169.74444444444</v>
+        <v>46170.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46169.75486111111</v>
+        <v>46170.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46169.76527777778</v>
+        <v>46170.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46169.77569444444</v>
+        <v>46170.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46169.78611111111</v>
+        <v>46170.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46169.79652777778</v>
+        <v>46170.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46169.80694444444</v>
+        <v>46170.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46169.81736111111</v>
+        <v>46170.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46169.82777777778</v>
+        <v>46170.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46169.83819444444</v>
+        <v>46170.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46169.84861111111</v>
+        <v>46170.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46169.85902777778</v>
+        <v>46170.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46169.86944444444</v>
+        <v>46170.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46169.87986111111</v>
+        <v>46170.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46169.89027777778</v>
+        <v>46170.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46169.90069444444</v>
+        <v>46170.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46169.91111111111</v>
+        <v>46170.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46169.92152777778</v>
+        <v>46170.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46169.93194444444</v>
+        <v>46170.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46169.94236111111</v>
+        <v>46170.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46169.95277777778</v>
+        <v>46170.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46169.96319444444</v>
+        <v>46170.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46169.97361111111</v>
+        <v>46170.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46169.98402777778</v>
+        <v>46170.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46169.99444444444</v>
+        <v>46170.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46170.00486111111</v>
+        <v>46171.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46170.01527777778</v>
+        <v>46171.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46170.02569444444</v>
+        <v>46171.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46170.03611111111</v>
+        <v>46171.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46170.03611111111</v>
+        <v>46171.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46170.04652777778</v>
+        <v>46171.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46170.05694444444</v>
+        <v>46171.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46170.06736111111</v>
+        <v>46171.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46170.07777777778</v>
+        <v>46171.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46170.08819444444</v>
+        <v>46171.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46170.09861111111</v>
+        <v>46171.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46170.10902777778</v>
+        <v>46171.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46170.11944444444</v>
+        <v>46171.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46170.12986111111</v>
+        <v>46171.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46170.14027777778</v>
+        <v>46171.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46170.15069444444</v>
+        <v>46171.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46170.16111111111</v>
+        <v>46171.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46170.17152777778</v>
+        <v>46171.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46170.18194444444</v>
+        <v>46171.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46170.19236111111</v>
+        <v>46171.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46170.20277777778</v>
+        <v>46171.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46170.21319444444</v>
+        <v>46171.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46170.22361111111</v>
+        <v>46171.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46170.23402777778</v>
+        <v>46171.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46170.24444444444</v>
+        <v>46171.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46170.25486111111</v>
+        <v>46171.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46170.26527777778</v>
+        <v>46171.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46170.27569444444</v>
+        <v>46171.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46170.28611111111</v>
+        <v>46171.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46170.29652777778</v>
+        <v>46171.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46170.30694444444</v>
+        <v>46171.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46170.31736111111</v>
+        <v>46171.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46170.32777777778</v>
+        <v>46171.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46170.33819444444</v>
+        <v>46171.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46170.34861111111</v>
+        <v>46171.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46170.35902777778</v>
+        <v>46171.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46170.36944444444</v>
+        <v>46171.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46170.37986111111</v>
+        <v>46171.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46170.39027777778</v>
+        <v>46171.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46170.40069444444</v>
+        <v>46171.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46170.41111111111</v>
+        <v>46171.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46170.42152777778</v>
+        <v>46171.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46170.43194444444</v>
+        <v>46171.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46170.44236111111</v>
+        <v>46171.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46170.45277777778</v>
+        <v>46171.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46170.46319444444</v>
+        <v>46171.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46170.47361111111</v>
+        <v>46171.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46170.48402777778</v>
+        <v>46171.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46170.49444444444</v>
+        <v>46171.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46170.50486111111</v>
+        <v>46171.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46170.51527777778</v>
+        <v>46171.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46170.52569444444</v>
+        <v>46171.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46170.53611111111</v>
+        <v>46171.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46170.54652777778</v>
+        <v>46171.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46170.55694444444</v>
+        <v>46171.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46170.56736111111</v>
+        <v>46171.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46170.57777777778</v>
+        <v>46171.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46170.58819444444</v>
+        <v>46171.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46170.59861111111</v>
+        <v>46171.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46170.60902777778</v>
+        <v>46171.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46170.61944444444</v>
+        <v>46171.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46170.62986111111</v>
+        <v>46171.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46170.64027777778</v>
+        <v>46171.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46170.65069444444</v>
+        <v>46171.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46170.66111111111</v>
+        <v>46171.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46170.67152777778</v>
+        <v>46171.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46170.68194444444</v>
+        <v>46171.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46170.69236111111</v>
+        <v>46171.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46170.70277777778</v>
+        <v>46171.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46170.71319444444</v>
+        <v>46171.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46170.72361111111</v>
+        <v>46171.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46170.73402777778</v>
+        <v>46171.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46170.74444444444</v>
+        <v>46171.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46170.75486111111</v>
+        <v>46171.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46170.76527777778</v>
+        <v>46171.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46170.77569444444</v>
+        <v>46171.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46170.78611111111</v>
+        <v>46171.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46170.79652777778</v>
+        <v>46171.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46170.80694444444</v>
+        <v>46171.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46170.81736111111</v>
+        <v>46171.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46170.82777777778</v>
+        <v>46171.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46170.83819444444</v>
+        <v>46171.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46170.84861111111</v>
+        <v>46171.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46170.85902777778</v>
+        <v>46171.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46170.86944444444</v>
+        <v>46171.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46170.87986111111</v>
+        <v>46171.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46170.89027777778</v>
+        <v>46171.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46170.90069444444</v>
+        <v>46171.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46170.91111111111</v>
+        <v>46171.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46170.92152777778</v>
+        <v>46171.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46170.93194444444</v>
+        <v>46171.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46170.94236111111</v>
+        <v>46171.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46170.95277777778</v>
+        <v>46171.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46170.96319444444</v>
+        <v>46171.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46170.97361111111</v>
+        <v>46171.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46170.98402777778</v>
+        <v>46171.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46170.99444444444</v>
+        <v>46171.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46171.00486111111</v>
+        <v>46172.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46171.01527777778</v>
+        <v>46172.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46171.02569444444</v>
+        <v>46172.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46171.03611111111</v>
+        <v>46172.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,583 +31,583 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>03.06.20261</t>
-  </si>
-  <si>
-    <t>03.06.20262</t>
-  </si>
-  <si>
-    <t>03.06.20263</t>
-  </si>
-  <si>
-    <t>03.06.20264</t>
-  </si>
-  <si>
-    <t>03.06.20265</t>
-  </si>
-  <si>
-    <t>03.06.20266</t>
-  </si>
-  <si>
-    <t>03.06.20267</t>
-  </si>
-  <si>
-    <t>03.06.20268</t>
-  </si>
-  <si>
-    <t>03.06.20269</t>
-  </si>
-  <si>
-    <t>03.06.202610</t>
-  </si>
-  <si>
-    <t>03.06.202611</t>
-  </si>
-  <si>
-    <t>03.06.202612</t>
-  </si>
-  <si>
-    <t>03.06.202613</t>
-  </si>
-  <si>
-    <t>03.06.202614</t>
-  </si>
-  <si>
-    <t>03.06.202615</t>
-  </si>
-  <si>
-    <t>03.06.202616</t>
-  </si>
-  <si>
-    <t>03.06.202617</t>
-  </si>
-  <si>
-    <t>03.06.202618</t>
-  </si>
-  <si>
-    <t>03.06.202619</t>
-  </si>
-  <si>
-    <t>03.06.202620</t>
-  </si>
-  <si>
-    <t>03.06.202621</t>
-  </si>
-  <si>
-    <t>03.06.202622</t>
-  </si>
-  <si>
-    <t>03.06.202623</t>
-  </si>
-  <si>
-    <t>03.06.202624</t>
-  </si>
-  <si>
-    <t>03.06.202625</t>
-  </si>
-  <si>
-    <t>03.06.202626</t>
-  </si>
-  <si>
-    <t>03.06.202627</t>
-  </si>
-  <si>
-    <t>03.06.202628</t>
-  </si>
-  <si>
-    <t>03.06.202629</t>
-  </si>
-  <si>
-    <t>03.06.202630</t>
-  </si>
-  <si>
-    <t>03.06.202631</t>
-  </si>
-  <si>
-    <t>03.06.202632</t>
-  </si>
-  <si>
-    <t>03.06.202633</t>
-  </si>
-  <si>
-    <t>03.06.202634</t>
-  </si>
-  <si>
-    <t>03.06.202635</t>
-  </si>
-  <si>
-    <t>03.06.202636</t>
-  </si>
-  <si>
-    <t>03.06.202637</t>
-  </si>
-  <si>
-    <t>03.06.202638</t>
-  </si>
-  <si>
-    <t>03.06.202639</t>
-  </si>
-  <si>
-    <t>03.06.202640</t>
-  </si>
-  <si>
-    <t>03.06.202641</t>
-  </si>
-  <si>
-    <t>03.06.202642</t>
-  </si>
-  <si>
-    <t>03.06.202643</t>
-  </si>
-  <si>
-    <t>03.06.202644</t>
-  </si>
-  <si>
-    <t>03.06.202645</t>
-  </si>
-  <si>
-    <t>03.06.202646</t>
-  </si>
-  <si>
-    <t>03.06.202647</t>
-  </si>
-  <si>
-    <t>03.06.202648</t>
-  </si>
-  <si>
-    <t>03.06.202649</t>
-  </si>
-  <si>
-    <t>03.06.202650</t>
-  </si>
-  <si>
-    <t>03.06.202651</t>
-  </si>
-  <si>
-    <t>03.06.202652</t>
-  </si>
-  <si>
-    <t>03.06.202653</t>
-  </si>
-  <si>
-    <t>03.06.202654</t>
-  </si>
-  <si>
-    <t>03.06.202655</t>
-  </si>
-  <si>
-    <t>03.06.202656</t>
-  </si>
-  <si>
-    <t>03.06.202657</t>
-  </si>
-  <si>
-    <t>03.06.202658</t>
-  </si>
-  <si>
-    <t>03.06.202659</t>
-  </si>
-  <si>
-    <t>03.06.202660</t>
-  </si>
-  <si>
-    <t>03.06.202661</t>
-  </si>
-  <si>
-    <t>03.06.202662</t>
-  </si>
-  <si>
-    <t>03.06.202663</t>
-  </si>
-  <si>
-    <t>03.06.202664</t>
-  </si>
-  <si>
-    <t>03.06.202665</t>
-  </si>
-  <si>
-    <t>03.06.202666</t>
-  </si>
-  <si>
-    <t>03.06.202667</t>
-  </si>
-  <si>
-    <t>03.06.202668</t>
-  </si>
-  <si>
-    <t>03.06.202669</t>
-  </si>
-  <si>
-    <t>03.06.202670</t>
-  </si>
-  <si>
-    <t>03.06.202671</t>
-  </si>
-  <si>
-    <t>03.06.202672</t>
-  </si>
-  <si>
-    <t>03.06.202673</t>
-  </si>
-  <si>
-    <t>03.06.202674</t>
-  </si>
-  <si>
-    <t>03.06.202675</t>
-  </si>
-  <si>
-    <t>03.06.202676</t>
-  </si>
-  <si>
-    <t>03.06.202677</t>
-  </si>
-  <si>
-    <t>03.06.202678</t>
-  </si>
-  <si>
-    <t>03.06.202679</t>
-  </si>
-  <si>
-    <t>03.06.202680</t>
-  </si>
-  <si>
-    <t>03.06.202681</t>
-  </si>
-  <si>
-    <t>03.06.202682</t>
-  </si>
-  <si>
-    <t>03.06.202683</t>
-  </si>
-  <si>
-    <t>03.06.202684</t>
-  </si>
-  <si>
-    <t>03.06.202685</t>
-  </si>
-  <si>
-    <t>03.06.202686</t>
-  </si>
-  <si>
-    <t>03.06.202687</t>
-  </si>
-  <si>
-    <t>03.06.202688</t>
-  </si>
-  <si>
-    <t>03.06.202689</t>
-  </si>
-  <si>
-    <t>03.06.202690</t>
-  </si>
-  <si>
-    <t>03.06.202691</t>
-  </si>
-  <si>
-    <t>03.06.202692</t>
-  </si>
-  <si>
-    <t>03.06.202693</t>
-  </si>
-  <si>
-    <t>04.06.202694</t>
-  </si>
-  <si>
-    <t>04.06.202695</t>
-  </si>
-  <si>
-    <t>04.06.202696</t>
-  </si>
-  <si>
-    <t>04.06.20261</t>
-  </si>
-  <si>
-    <t>04.06.20262</t>
-  </si>
-  <si>
-    <t>04.06.20263</t>
-  </si>
-  <si>
-    <t>04.06.20264</t>
-  </si>
-  <si>
-    <t>04.06.20265</t>
-  </si>
-  <si>
-    <t>04.06.20266</t>
-  </si>
-  <si>
-    <t>04.06.20267</t>
-  </si>
-  <si>
-    <t>04.06.20268</t>
-  </si>
-  <si>
-    <t>04.06.20269</t>
-  </si>
-  <si>
-    <t>04.06.202610</t>
-  </si>
-  <si>
-    <t>04.06.202611</t>
-  </si>
-  <si>
-    <t>04.06.202612</t>
-  </si>
-  <si>
-    <t>04.06.202613</t>
-  </si>
-  <si>
-    <t>04.06.202614</t>
-  </si>
-  <si>
-    <t>04.06.202615</t>
-  </si>
-  <si>
-    <t>04.06.202616</t>
-  </si>
-  <si>
-    <t>04.06.202617</t>
-  </si>
-  <si>
-    <t>04.06.202618</t>
-  </si>
-  <si>
-    <t>04.06.202619</t>
-  </si>
-  <si>
-    <t>04.06.202620</t>
-  </si>
-  <si>
-    <t>04.06.202621</t>
-  </si>
-  <si>
-    <t>04.06.202622</t>
-  </si>
-  <si>
-    <t>04.06.202623</t>
-  </si>
-  <si>
-    <t>04.06.202624</t>
-  </si>
-  <si>
-    <t>04.06.202625</t>
-  </si>
-  <si>
-    <t>04.06.202626</t>
-  </si>
-  <si>
-    <t>04.06.202627</t>
-  </si>
-  <si>
-    <t>04.06.202628</t>
-  </si>
-  <si>
-    <t>04.06.202629</t>
-  </si>
-  <si>
-    <t>04.06.202630</t>
-  </si>
-  <si>
-    <t>04.06.202631</t>
-  </si>
-  <si>
-    <t>04.06.202632</t>
-  </si>
-  <si>
-    <t>04.06.202633</t>
-  </si>
-  <si>
-    <t>04.06.202634</t>
-  </si>
-  <si>
-    <t>04.06.202635</t>
-  </si>
-  <si>
-    <t>04.06.202636</t>
-  </si>
-  <si>
-    <t>04.06.202637</t>
-  </si>
-  <si>
-    <t>04.06.202638</t>
-  </si>
-  <si>
-    <t>04.06.202639</t>
-  </si>
-  <si>
-    <t>04.06.202640</t>
-  </si>
-  <si>
-    <t>04.06.202641</t>
-  </si>
-  <si>
-    <t>04.06.202642</t>
-  </si>
-  <si>
-    <t>04.06.202643</t>
-  </si>
-  <si>
-    <t>04.06.202644</t>
-  </si>
-  <si>
-    <t>04.06.202645</t>
-  </si>
-  <si>
-    <t>04.06.202646</t>
-  </si>
-  <si>
-    <t>04.06.202647</t>
-  </si>
-  <si>
-    <t>04.06.202648</t>
-  </si>
-  <si>
-    <t>04.06.202649</t>
-  </si>
-  <si>
-    <t>04.06.202650</t>
-  </si>
-  <si>
-    <t>04.06.202651</t>
-  </si>
-  <si>
-    <t>04.06.202652</t>
-  </si>
-  <si>
-    <t>04.06.202653</t>
-  </si>
-  <si>
-    <t>04.06.202654</t>
-  </si>
-  <si>
-    <t>04.06.202655</t>
-  </si>
-  <si>
-    <t>04.06.202656</t>
-  </si>
-  <si>
-    <t>04.06.202657</t>
-  </si>
-  <si>
-    <t>04.06.202658</t>
-  </si>
-  <si>
-    <t>04.06.202659</t>
-  </si>
-  <si>
-    <t>04.06.202660</t>
-  </si>
-  <si>
-    <t>04.06.202661</t>
-  </si>
-  <si>
-    <t>04.06.202662</t>
-  </si>
-  <si>
-    <t>04.06.202663</t>
-  </si>
-  <si>
-    <t>04.06.202664</t>
-  </si>
-  <si>
-    <t>04.06.202665</t>
-  </si>
-  <si>
-    <t>04.06.202666</t>
-  </si>
-  <si>
-    <t>04.06.202667</t>
-  </si>
-  <si>
-    <t>04.06.202668</t>
-  </si>
-  <si>
-    <t>04.06.202669</t>
-  </si>
-  <si>
-    <t>04.06.202670</t>
-  </si>
-  <si>
-    <t>04.06.202671</t>
-  </si>
-  <si>
-    <t>04.06.202672</t>
-  </si>
-  <si>
-    <t>04.06.202673</t>
-  </si>
-  <si>
-    <t>04.06.202674</t>
-  </si>
-  <si>
-    <t>04.06.202675</t>
-  </si>
-  <si>
-    <t>04.06.202676</t>
-  </si>
-  <si>
-    <t>04.06.202677</t>
-  </si>
-  <si>
-    <t>04.06.202678</t>
-  </si>
-  <si>
-    <t>04.06.202679</t>
-  </si>
-  <si>
-    <t>04.06.202680</t>
-  </si>
-  <si>
-    <t>04.06.202681</t>
-  </si>
-  <si>
-    <t>04.06.202682</t>
-  </si>
-  <si>
-    <t>04.06.202683</t>
-  </si>
-  <si>
-    <t>04.06.202684</t>
-  </si>
-  <si>
-    <t>04.06.202685</t>
-  </si>
-  <si>
-    <t>04.06.202686</t>
-  </si>
-  <si>
-    <t>04.06.202687</t>
-  </si>
-  <si>
-    <t>04.06.202688</t>
-  </si>
-  <si>
-    <t>04.06.202689</t>
-  </si>
-  <si>
-    <t>04.06.202690</t>
-  </si>
-  <si>
-    <t>04.06.202691</t>
-  </si>
-  <si>
-    <t>04.06.202692</t>
-  </si>
-  <si>
-    <t>04.06.202693</t>
-  </si>
-  <si>
-    <t>05.06.202695</t>
-  </si>
-  <si>
-    <t>05.06.202696</t>
-  </si>
-  <si>
-    <t>05.06.20261</t>
-  </si>
-  <si>
-    <t>05.06.20262</t>
+    <t>11.06.20261</t>
+  </si>
+  <si>
+    <t>11.06.20262</t>
+  </si>
+  <si>
+    <t>11.06.20263</t>
+  </si>
+  <si>
+    <t>11.06.20264</t>
+  </si>
+  <si>
+    <t>11.06.20265</t>
+  </si>
+  <si>
+    <t>11.06.20266</t>
+  </si>
+  <si>
+    <t>11.06.20267</t>
+  </si>
+  <si>
+    <t>11.06.20268</t>
+  </si>
+  <si>
+    <t>11.06.20269</t>
+  </si>
+  <si>
+    <t>11.06.202610</t>
+  </si>
+  <si>
+    <t>11.06.202611</t>
+  </si>
+  <si>
+    <t>11.06.202612</t>
+  </si>
+  <si>
+    <t>11.06.202613</t>
+  </si>
+  <si>
+    <t>11.06.202614</t>
+  </si>
+  <si>
+    <t>11.06.202615</t>
+  </si>
+  <si>
+    <t>11.06.202616</t>
+  </si>
+  <si>
+    <t>11.06.202617</t>
+  </si>
+  <si>
+    <t>11.06.202618</t>
+  </si>
+  <si>
+    <t>11.06.202619</t>
+  </si>
+  <si>
+    <t>11.06.202620</t>
+  </si>
+  <si>
+    <t>11.06.202621</t>
+  </si>
+  <si>
+    <t>11.06.202622</t>
+  </si>
+  <si>
+    <t>11.06.202623</t>
+  </si>
+  <si>
+    <t>11.06.202624</t>
+  </si>
+  <si>
+    <t>11.06.202625</t>
+  </si>
+  <si>
+    <t>11.06.202626</t>
+  </si>
+  <si>
+    <t>11.06.202627</t>
+  </si>
+  <si>
+    <t>11.06.202628</t>
+  </si>
+  <si>
+    <t>11.06.202629</t>
+  </si>
+  <si>
+    <t>11.06.202630</t>
+  </si>
+  <si>
+    <t>11.06.202631</t>
+  </si>
+  <si>
+    <t>11.06.202632</t>
+  </si>
+  <si>
+    <t>11.06.202633</t>
+  </si>
+  <si>
+    <t>11.06.202634</t>
+  </si>
+  <si>
+    <t>11.06.202635</t>
+  </si>
+  <si>
+    <t>11.06.202636</t>
+  </si>
+  <si>
+    <t>11.06.202637</t>
+  </si>
+  <si>
+    <t>11.06.202638</t>
+  </si>
+  <si>
+    <t>11.06.202639</t>
+  </si>
+  <si>
+    <t>11.06.202640</t>
+  </si>
+  <si>
+    <t>11.06.202641</t>
+  </si>
+  <si>
+    <t>11.06.202642</t>
+  </si>
+  <si>
+    <t>11.06.202643</t>
+  </si>
+  <si>
+    <t>11.06.202644</t>
+  </si>
+  <si>
+    <t>11.06.202645</t>
+  </si>
+  <si>
+    <t>11.06.202646</t>
+  </si>
+  <si>
+    <t>11.06.202647</t>
+  </si>
+  <si>
+    <t>11.06.202648</t>
+  </si>
+  <si>
+    <t>11.06.202649</t>
+  </si>
+  <si>
+    <t>11.06.202650</t>
+  </si>
+  <si>
+    <t>11.06.202651</t>
+  </si>
+  <si>
+    <t>11.06.202652</t>
+  </si>
+  <si>
+    <t>11.06.202653</t>
+  </si>
+  <si>
+    <t>11.06.202654</t>
+  </si>
+  <si>
+    <t>11.06.202655</t>
+  </si>
+  <si>
+    <t>11.06.202656</t>
+  </si>
+  <si>
+    <t>11.06.202657</t>
+  </si>
+  <si>
+    <t>11.06.202658</t>
+  </si>
+  <si>
+    <t>11.06.202659</t>
+  </si>
+  <si>
+    <t>11.06.202660</t>
+  </si>
+  <si>
+    <t>11.06.202661</t>
+  </si>
+  <si>
+    <t>11.06.202662</t>
+  </si>
+  <si>
+    <t>11.06.202663</t>
+  </si>
+  <si>
+    <t>11.06.202664</t>
+  </si>
+  <si>
+    <t>11.06.202665</t>
+  </si>
+  <si>
+    <t>11.06.202666</t>
+  </si>
+  <si>
+    <t>11.06.202667</t>
+  </si>
+  <si>
+    <t>11.06.202668</t>
+  </si>
+  <si>
+    <t>11.06.202669</t>
+  </si>
+  <si>
+    <t>11.06.202670</t>
+  </si>
+  <si>
+    <t>11.06.202671</t>
+  </si>
+  <si>
+    <t>11.06.202672</t>
+  </si>
+  <si>
+    <t>11.06.202673</t>
+  </si>
+  <si>
+    <t>11.06.202674</t>
+  </si>
+  <si>
+    <t>11.06.202675</t>
+  </si>
+  <si>
+    <t>11.06.202676</t>
+  </si>
+  <si>
+    <t>11.06.202677</t>
+  </si>
+  <si>
+    <t>11.06.202678</t>
+  </si>
+  <si>
+    <t>11.06.202679</t>
+  </si>
+  <si>
+    <t>11.06.202680</t>
+  </si>
+  <si>
+    <t>11.06.202681</t>
+  </si>
+  <si>
+    <t>11.06.202682</t>
+  </si>
+  <si>
+    <t>11.06.202683</t>
+  </si>
+  <si>
+    <t>11.06.202684</t>
+  </si>
+  <si>
+    <t>11.06.202685</t>
+  </si>
+  <si>
+    <t>11.06.202686</t>
+  </si>
+  <si>
+    <t>11.06.202687</t>
+  </si>
+  <si>
+    <t>11.06.202688</t>
+  </si>
+  <si>
+    <t>11.06.202689</t>
+  </si>
+  <si>
+    <t>11.06.202690</t>
+  </si>
+  <si>
+    <t>11.06.202691</t>
+  </si>
+  <si>
+    <t>11.06.202692</t>
+  </si>
+  <si>
+    <t>11.06.202693</t>
+  </si>
+  <si>
+    <t>12.06.202694</t>
+  </si>
+  <si>
+    <t>12.06.202695</t>
+  </si>
+  <si>
+    <t>12.06.202696</t>
+  </si>
+  <si>
+    <t>12.06.20261</t>
+  </si>
+  <si>
+    <t>12.06.20262</t>
+  </si>
+  <si>
+    <t>12.06.20263</t>
+  </si>
+  <si>
+    <t>12.06.20264</t>
+  </si>
+  <si>
+    <t>12.06.20265</t>
+  </si>
+  <si>
+    <t>12.06.20266</t>
+  </si>
+  <si>
+    <t>12.06.20267</t>
+  </si>
+  <si>
+    <t>12.06.20268</t>
+  </si>
+  <si>
+    <t>12.06.20269</t>
+  </si>
+  <si>
+    <t>12.06.202610</t>
+  </si>
+  <si>
+    <t>12.06.202611</t>
+  </si>
+  <si>
+    <t>12.06.202612</t>
+  </si>
+  <si>
+    <t>12.06.202613</t>
+  </si>
+  <si>
+    <t>12.06.202614</t>
+  </si>
+  <si>
+    <t>12.06.202615</t>
+  </si>
+  <si>
+    <t>12.06.202616</t>
+  </si>
+  <si>
+    <t>12.06.202617</t>
+  </si>
+  <si>
+    <t>12.06.202618</t>
+  </si>
+  <si>
+    <t>12.06.202619</t>
+  </si>
+  <si>
+    <t>12.06.202620</t>
+  </si>
+  <si>
+    <t>12.06.202621</t>
+  </si>
+  <si>
+    <t>12.06.202622</t>
+  </si>
+  <si>
+    <t>12.06.202623</t>
+  </si>
+  <si>
+    <t>12.06.202624</t>
+  </si>
+  <si>
+    <t>12.06.202625</t>
+  </si>
+  <si>
+    <t>12.06.202626</t>
+  </si>
+  <si>
+    <t>12.06.202627</t>
+  </si>
+  <si>
+    <t>12.06.202628</t>
+  </si>
+  <si>
+    <t>12.06.202629</t>
+  </si>
+  <si>
+    <t>12.06.202630</t>
+  </si>
+  <si>
+    <t>12.06.202631</t>
+  </si>
+  <si>
+    <t>12.06.202632</t>
+  </si>
+  <si>
+    <t>12.06.202633</t>
+  </si>
+  <si>
+    <t>12.06.202634</t>
+  </si>
+  <si>
+    <t>12.06.202635</t>
+  </si>
+  <si>
+    <t>12.06.202636</t>
+  </si>
+  <si>
+    <t>12.06.202637</t>
+  </si>
+  <si>
+    <t>12.06.202638</t>
+  </si>
+  <si>
+    <t>12.06.202639</t>
+  </si>
+  <si>
+    <t>12.06.202640</t>
+  </si>
+  <si>
+    <t>12.06.202641</t>
+  </si>
+  <si>
+    <t>12.06.202642</t>
+  </si>
+  <si>
+    <t>12.06.202643</t>
+  </si>
+  <si>
+    <t>12.06.202644</t>
+  </si>
+  <si>
+    <t>12.06.202645</t>
+  </si>
+  <si>
+    <t>12.06.202646</t>
+  </si>
+  <si>
+    <t>12.06.202647</t>
+  </si>
+  <si>
+    <t>12.06.202648</t>
+  </si>
+  <si>
+    <t>12.06.202649</t>
+  </si>
+  <si>
+    <t>12.06.202650</t>
+  </si>
+  <si>
+    <t>12.06.202651</t>
+  </si>
+  <si>
+    <t>12.06.202652</t>
+  </si>
+  <si>
+    <t>12.06.202653</t>
+  </si>
+  <si>
+    <t>12.06.202654</t>
+  </si>
+  <si>
+    <t>12.06.202655</t>
+  </si>
+  <si>
+    <t>12.06.202656</t>
+  </si>
+  <si>
+    <t>12.06.202657</t>
+  </si>
+  <si>
+    <t>12.06.202658</t>
+  </si>
+  <si>
+    <t>12.06.202659</t>
+  </si>
+  <si>
+    <t>12.06.202660</t>
+  </si>
+  <si>
+    <t>12.06.202661</t>
+  </si>
+  <si>
+    <t>12.06.202662</t>
+  </si>
+  <si>
+    <t>12.06.202663</t>
+  </si>
+  <si>
+    <t>12.06.202664</t>
+  </si>
+  <si>
+    <t>12.06.202665</t>
+  </si>
+  <si>
+    <t>12.06.202666</t>
+  </si>
+  <si>
+    <t>12.06.202667</t>
+  </si>
+  <si>
+    <t>12.06.202668</t>
+  </si>
+  <si>
+    <t>12.06.202669</t>
+  </si>
+  <si>
+    <t>12.06.202670</t>
+  </si>
+  <si>
+    <t>12.06.202671</t>
+  </si>
+  <si>
+    <t>12.06.202672</t>
+  </si>
+  <si>
+    <t>12.06.202673</t>
+  </si>
+  <si>
+    <t>12.06.202674</t>
+  </si>
+  <si>
+    <t>12.06.202675</t>
+  </si>
+  <si>
+    <t>12.06.202676</t>
+  </si>
+  <si>
+    <t>12.06.202677</t>
+  </si>
+  <si>
+    <t>12.06.202678</t>
+  </si>
+  <si>
+    <t>12.06.202679</t>
+  </si>
+  <si>
+    <t>12.06.202680</t>
+  </si>
+  <si>
+    <t>12.06.202681</t>
+  </si>
+  <si>
+    <t>12.06.202682</t>
+  </si>
+  <si>
+    <t>12.06.202683</t>
+  </si>
+  <si>
+    <t>12.06.202684</t>
+  </si>
+  <si>
+    <t>12.06.202685</t>
+  </si>
+  <si>
+    <t>12.06.202686</t>
+  </si>
+  <si>
+    <t>12.06.202687</t>
+  </si>
+  <si>
+    <t>12.06.202688</t>
+  </si>
+  <si>
+    <t>12.06.202689</t>
+  </si>
+  <si>
+    <t>12.06.202690</t>
+  </si>
+  <si>
+    <t>12.06.202691</t>
+  </si>
+  <si>
+    <t>12.06.202692</t>
+  </si>
+  <si>
+    <t>12.06.202693</t>
+  </si>
+  <si>
+    <t>13.06.202695</t>
+  </si>
+  <si>
+    <t>13.06.202696</t>
+  </si>
+  <si>
+    <t>13.06.20261</t>
+  </si>
+  <si>
+    <t>13.06.20262</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46176.03611111111</v>
+        <v>46184.03611111111</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46176.04652777778</v>
+        <v>46184.04652777778</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46176.05694444444</v>
+        <v>46184.05694444444</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46176.06736111111</v>
+        <v>46184.06736111111</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46176.07777777778</v>
+        <v>46184.07777777778</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46176.08819444444</v>
+        <v>46184.08819444444</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46176.09861111111</v>
+        <v>46184.09861111111</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46176.10902777778</v>
+        <v>46184.10902777778</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46176.11944444444</v>
+        <v>46184.11944444444</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46176.12986111111</v>
+        <v>46184.12986111111</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46176.14027777778</v>
+        <v>46184.14027777778</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46176.15069444444</v>
+        <v>46184.15069444444</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46176.16111111111</v>
+        <v>46184.16111111111</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46176.17152777778</v>
+        <v>46184.17152777778</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46176.18194444444</v>
+        <v>46184.18194444444</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1246,7 +1246,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46176.19236111111</v>
+        <v>46184.19236111111</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46176.20277777778</v>
+        <v>46184.20277777778</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46176.21319444444</v>
+        <v>46184.21319444444</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46176.22361111111</v>
+        <v>46184.22361111111</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46176.23402777778</v>
+        <v>46184.23402777778</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1331,7 +1331,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46176.24444444444</v>
+        <v>46184.24444444444</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46176.25486111111</v>
+        <v>46184.25486111111</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46176.26527777778</v>
+        <v>46184.26527777778</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46176.27569444444</v>
+        <v>46184.27569444444</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46176.28611111111</v>
+        <v>46184.28611111111</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46176.29652777778</v>
+        <v>46184.29652777778</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46176.30694444444</v>
+        <v>46184.30694444444</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46176.31736111111</v>
+        <v>46184.31736111111</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46176.32777777778</v>
+        <v>46184.32777777778</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46176.33819444444</v>
+        <v>46184.33819444444</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -1501,7 +1501,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46176.34861111111</v>
+        <v>46184.34861111111</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46176.35902777778</v>
+        <v>46184.35902777778</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46176.36944444444</v>
+        <v>46184.36944444444</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46176.37986111111</v>
+        <v>46184.37986111111</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46176.39027777778</v>
+        <v>46184.39027777778</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46176.40069444444</v>
+        <v>46184.40069444444</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46176.41111111111</v>
+        <v>46184.41111111111</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46176.42152777778</v>
+        <v>46184.42152777778</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46176.43194444444</v>
+        <v>46184.43194444444</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46176.44236111111</v>
+        <v>46184.44236111111</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46176.45277777778</v>
+        <v>46184.45277777778</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46176.46319444444</v>
+        <v>46184.46319444444</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1705,7 +1705,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46176.47361111111</v>
+        <v>46184.47361111111</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46176.48402777778</v>
+        <v>46184.48402777778</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46176.49444444444</v>
+        <v>46184.49444444444</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46176.50486111111</v>
+        <v>46184.50486111111</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46176.51527777778</v>
+        <v>46184.51527777778</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46176.52569444444</v>
+        <v>46184.52569444444</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46176.53611111111</v>
+        <v>46184.53611111111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1824,7 +1824,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46176.54652777778</v>
+        <v>46184.54652777778</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1841,7 +1841,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46176.55694444444</v>
+        <v>46184.55694444444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46176.56736111111</v>
+        <v>46184.56736111111</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46176.57777777778</v>
+        <v>46184.57777777778</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46176.58819444444</v>
+        <v>46184.58819444444</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46176.59861111111</v>
+        <v>46184.59861111111</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46176.60902777778</v>
+        <v>46184.60902777778</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46176.61944444444</v>
+        <v>46184.61944444444</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1960,7 +1960,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46176.62986111111</v>
+        <v>46184.62986111111</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46176.64027777778</v>
+        <v>46184.64027777778</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46176.65069444444</v>
+        <v>46184.65069444444</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46176.66111111111</v>
+        <v>46184.66111111111</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46176.67152777778</v>
+        <v>46184.67152777778</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46176.68194444444</v>
+        <v>46184.68194444444</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46176.69236111111</v>
+        <v>46184.69236111111</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -2079,7 +2079,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46176.70277777778</v>
+        <v>46184.70277777778</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46176.71319444444</v>
+        <v>46184.71319444444</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46176.72361111111</v>
+        <v>46184.72361111111</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46176.73402777778</v>
+        <v>46184.73402777778</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46176.74444444444</v>
+        <v>46184.74444444444</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46176.75486111111</v>
+        <v>46184.75486111111</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46176.76527777778</v>
+        <v>46184.76527777778</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46176.77569444444</v>
+        <v>46184.77569444444</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46176.78611111111</v>
+        <v>46184.78611111111</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46176.79652777778</v>
+        <v>46184.79652777778</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46176.80694444444</v>
+        <v>46184.80694444444</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2266,7 +2266,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46176.81736111111</v>
+        <v>46184.81736111111</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46176.82777777778</v>
+        <v>46184.82777777778</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46176.83819444444</v>
+        <v>46184.83819444444</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46176.84861111111</v>
+        <v>46184.84861111111</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46176.85902777778</v>
+        <v>46184.85902777778</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46176.86944444444</v>
+        <v>46184.86944444444</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46176.87986111111</v>
+        <v>46184.87986111111</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2385,7 +2385,7 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46176.89027777778</v>
+        <v>46184.89027777778</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46176.90069444444</v>
+        <v>46184.90069444444</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46176.91111111111</v>
+        <v>46184.91111111111</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46176.92152777778</v>
+        <v>46184.92152777778</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46176.93194444444</v>
+        <v>46184.93194444444</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46176.94236111111</v>
+        <v>46184.94236111111</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46176.95277777778</v>
+        <v>46184.95277777778</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46176.96319444444</v>
+        <v>46184.96319444444</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46176.97361111111</v>
+        <v>46184.97361111111</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46176.98402777778</v>
+        <v>46184.98402777778</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46176.99444444444</v>
+        <v>46184.99444444444</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46177.00486111111</v>
+        <v>46185.00486111111</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46177.01527777778</v>
+        <v>46185.01527777778</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46177.02569444444</v>
+        <v>46185.02569444444</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46177.03611111111</v>
+        <v>46185.03611111111</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2640,7 +2640,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46177.03611111111</v>
+        <v>46185.03611111111</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46177.04652777778</v>
+        <v>46185.04652777778</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46177.05694444444</v>
+        <v>46185.05694444444</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46177.06736111111</v>
+        <v>46185.06736111111</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46177.07777777778</v>
+        <v>46185.07777777778</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46177.08819444444</v>
+        <v>46185.08819444444</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46177.09861111111</v>
+        <v>46185.09861111111</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46177.10902777778</v>
+        <v>46185.10902777778</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46177.11944444444</v>
+        <v>46185.11944444444</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46177.12986111111</v>
+        <v>46185.12986111111</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46177.14027777778</v>
+        <v>46185.14027777778</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46177.15069444444</v>
+        <v>46185.15069444444</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46177.16111111111</v>
+        <v>46185.16111111111</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46177.17152777778</v>
+        <v>46185.17152777778</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46177.18194444444</v>
+        <v>46185.18194444444</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2895,7 +2895,7 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46177.19236111111</v>
+        <v>46185.19236111111</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46177.20277777778</v>
+        <v>46185.20277777778</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46177.21319444444</v>
+        <v>46185.21319444444</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46177.22361111111</v>
+        <v>46185.22361111111</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46177.23402777778</v>
+        <v>46185.23402777778</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46177.24444444444</v>
+        <v>46185.24444444444</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46177.25486111111</v>
+        <v>46185.25486111111</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46177.26527777778</v>
+        <v>46185.26527777778</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46177.27569444444</v>
+        <v>46185.27569444444</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46177.28611111111</v>
+        <v>46185.28611111111</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46177.29652777778</v>
+        <v>46185.29652777778</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46177.30694444444</v>
+        <v>46185.30694444444</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46177.31736111111</v>
+        <v>46185.31736111111</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46177.32777777778</v>
+        <v>46185.32777777778</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46177.33819444444</v>
+        <v>46185.33819444444</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46177.34861111111</v>
+        <v>46185.34861111111</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46177.35902777778</v>
+        <v>46185.35902777778</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46177.36944444444</v>
+        <v>46185.36944444444</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -3201,7 +3201,7 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46177.37986111111</v>
+        <v>46185.37986111111</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46177.39027777778</v>
+        <v>46185.39027777778</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -3235,7 +3235,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46177.40069444444</v>
+        <v>46185.40069444444</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46177.41111111111</v>
+        <v>46185.41111111111</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46177.42152777778</v>
+        <v>46185.42152777778</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46177.43194444444</v>
+        <v>46185.43194444444</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46177.44236111111</v>
+        <v>46185.44236111111</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -3320,7 +3320,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46177.45277777778</v>
+        <v>46185.45277777778</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46177.46319444444</v>
+        <v>46185.46319444444</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46177.47361111111</v>
+        <v>46185.47361111111</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3371,7 +3371,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="2">
-        <v>46177.48402777778</v>
+        <v>46185.48402777778</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="2">
-        <v>46177.49444444444</v>
+        <v>46185.49444444444</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="2">
-        <v>46177.50486111111</v>
+        <v>46185.50486111111</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="2">
-        <v>46177.51527777778</v>
+        <v>46185.51527777778</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="2">
-        <v>46177.52569444444</v>
+        <v>46185.52569444444</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="2">
-        <v>46177.53611111111</v>
+        <v>46185.53611111111</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="2">
-        <v>46177.54652777778</v>
+        <v>46185.54652777778</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="2">
-        <v>46177.55694444444</v>
+        <v>46185.55694444444</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="2">
-        <v>46177.56736111111</v>
+        <v>46185.56736111111</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="2">
-        <v>46177.57777777778</v>
+        <v>46185.57777777778</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="2">
-        <v>46177.58819444444</v>
+        <v>46185.58819444444</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="2">
-        <v>46177.59861111111</v>
+        <v>46185.59861111111</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="2">
-        <v>46177.60902777778</v>
+        <v>46185.60902777778</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="2">
-        <v>46177.61944444444</v>
+        <v>46185.61944444444</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="2">
-        <v>46177.62986111111</v>
+        <v>46185.62986111111</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="2">
-        <v>46177.64027777778</v>
+        <v>46185.64027777778</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="2">
-        <v>46177.65069444444</v>
+        <v>46185.65069444444</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -3660,7 +3660,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="2">
-        <v>46177.66111111111</v>
+        <v>46185.66111111111</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="2">
-        <v>46177.67152777778</v>
+        <v>46185.67152777778</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="2">
-        <v>46177.68194444444</v>
+        <v>46185.68194444444</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="2">
-        <v>46177.69236111111</v>
+        <v>46185.69236111111</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="2">
-        <v>46177.70277777778</v>
+        <v>46185.70277777778</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="2">
-        <v>46177.71319444444</v>
+        <v>46185.71319444444</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="2">
-        <v>46177.72361111111</v>
+        <v>46185.72361111111</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="2">
-        <v>46177.73402777778</v>
+        <v>46185.73402777778</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="2">
-        <v>46177.74444444444</v>
+        <v>46185.74444444444</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="2">
-        <v>46177.75486111111</v>
+        <v>46185.75486111111</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="2">
-        <v>46177.76527777778</v>
+        <v>46185.76527777778</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="2">
-        <v>46177.77569444444</v>
+        <v>46185.77569444444</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="2">
-        <v>46177.78611111111</v>
+        <v>46185.78611111111</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="2">
-        <v>46177.79652777778</v>
+        <v>46185.79652777778</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="2">
-        <v>46177.80694444444</v>
+        <v>46185.80694444444</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="2">
-        <v>46177.81736111111</v>
+        <v>46185.81736111111</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -3932,7 +3932,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="2">
-        <v>46177.82777777778</v>
+        <v>46185.82777777778</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="2">
-        <v>46177.83819444444</v>
+        <v>46185.83819444444</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="2">
-        <v>46177.84861111111</v>
+        <v>46185.84861111111</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="2">
-        <v>46177.85902777778</v>
+        <v>46185.85902777778</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="2">
-        <v>46177.86944444444</v>
+        <v>46185.86944444444</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="2">
-        <v>46177.87986111111</v>
+        <v>46185.87986111111</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="2">
-        <v>46177.89027777778</v>
+        <v>46185.89027777778</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="2">
-        <v>46177.90069444444</v>
+        <v>46185.90069444444</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="2">
-        <v>46177.91111111111</v>
+        <v>46185.91111111111</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="2">
-        <v>46177.92152777778</v>
+        <v>46185.92152777778</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2">
-        <v>46177.93194444444</v>
+        <v>46185.93194444444</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2">
-        <v>46177.94236111111</v>
+        <v>46185.94236111111</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2">
-        <v>46177.95277777778</v>
+        <v>46185.95277777778</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2">
-        <v>46177.96319444444</v>
+        <v>46185.96319444444</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2">
-        <v>46177.97361111111</v>
+        <v>46185.97361111111</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2">
-        <v>46177.98402777778</v>
+        <v>46185.98402777778</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2">
-        <v>46177.99444444444</v>
+        <v>46185.99444444444</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2">
-        <v>46178.00486111111</v>
+        <v>46186.00486111111</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2">
-        <v>46178.01527777778</v>
+        <v>46186.01527777778</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2">
-        <v>46178.02569444444</v>
+        <v>46186.02569444444</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2">
-        <v>46178.03611111111</v>
+        <v>46186.03611111111</v>
       </c>
       <c r="B195">
         <v>0</v>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,583 +31,424 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>11.06.20261</t>
-  </si>
-  <si>
-    <t>11.06.20262</t>
-  </si>
-  <si>
-    <t>11.06.20263</t>
-  </si>
-  <si>
-    <t>11.06.20264</t>
-  </si>
-  <si>
-    <t>11.06.20265</t>
-  </si>
-  <si>
-    <t>11.06.20266</t>
-  </si>
-  <si>
-    <t>11.06.20267</t>
-  </si>
-  <si>
-    <t>11.06.20268</t>
-  </si>
-  <si>
-    <t>11.06.20269</t>
-  </si>
-  <si>
-    <t>11.06.202610</t>
-  </si>
-  <si>
-    <t>11.06.202611</t>
-  </si>
-  <si>
-    <t>11.06.202612</t>
-  </si>
-  <si>
-    <t>11.06.202613</t>
-  </si>
-  <si>
-    <t>11.06.202614</t>
-  </si>
-  <si>
-    <t>11.06.202615</t>
-  </si>
-  <si>
-    <t>11.06.202616</t>
-  </si>
-  <si>
-    <t>11.06.202617</t>
-  </si>
-  <si>
-    <t>11.06.202618</t>
-  </si>
-  <si>
-    <t>11.06.202619</t>
-  </si>
-  <si>
-    <t>11.06.202620</t>
-  </si>
-  <si>
-    <t>11.06.202621</t>
-  </si>
-  <si>
-    <t>11.06.202622</t>
-  </si>
-  <si>
-    <t>11.06.202623</t>
-  </si>
-  <si>
-    <t>11.06.202624</t>
-  </si>
-  <si>
-    <t>11.06.202625</t>
-  </si>
-  <si>
-    <t>11.06.202626</t>
-  </si>
-  <si>
-    <t>11.06.202627</t>
-  </si>
-  <si>
-    <t>11.06.202628</t>
-  </si>
-  <si>
-    <t>11.06.202629</t>
-  </si>
-  <si>
-    <t>11.06.202630</t>
-  </si>
-  <si>
-    <t>11.06.202631</t>
-  </si>
-  <si>
-    <t>11.06.202632</t>
-  </si>
-  <si>
-    <t>11.06.202633</t>
-  </si>
-  <si>
-    <t>11.06.202634</t>
-  </si>
-  <si>
-    <t>11.06.202635</t>
-  </si>
-  <si>
-    <t>11.06.202636</t>
-  </si>
-  <si>
-    <t>11.06.202637</t>
-  </si>
-  <si>
-    <t>11.06.202638</t>
-  </si>
-  <si>
-    <t>11.06.202639</t>
-  </si>
-  <si>
-    <t>11.06.202640</t>
-  </si>
-  <si>
-    <t>11.06.202641</t>
-  </si>
-  <si>
-    <t>11.06.202642</t>
-  </si>
-  <si>
-    <t>11.06.202643</t>
-  </si>
-  <si>
-    <t>11.06.202644</t>
-  </si>
-  <si>
-    <t>11.06.202645</t>
-  </si>
-  <si>
-    <t>11.06.202646</t>
-  </si>
-  <si>
-    <t>11.06.202647</t>
-  </si>
-  <si>
-    <t>11.06.202648</t>
-  </si>
-  <si>
-    <t>11.06.202649</t>
-  </si>
-  <si>
-    <t>11.06.202650</t>
-  </si>
-  <si>
-    <t>11.06.202651</t>
-  </si>
-  <si>
-    <t>11.06.202652</t>
-  </si>
-  <si>
-    <t>11.06.202653</t>
-  </si>
-  <si>
-    <t>11.06.202654</t>
-  </si>
-  <si>
-    <t>11.06.202655</t>
-  </si>
-  <si>
-    <t>11.06.202656</t>
-  </si>
-  <si>
-    <t>11.06.202657</t>
-  </si>
-  <si>
-    <t>11.06.202658</t>
-  </si>
-  <si>
-    <t>11.06.202659</t>
-  </si>
-  <si>
-    <t>11.06.202660</t>
-  </si>
-  <si>
-    <t>11.06.202661</t>
-  </si>
-  <si>
-    <t>11.06.202662</t>
-  </si>
-  <si>
-    <t>11.06.202663</t>
-  </si>
-  <si>
-    <t>11.06.202664</t>
-  </si>
-  <si>
-    <t>11.06.202665</t>
-  </si>
-  <si>
-    <t>11.06.202666</t>
-  </si>
-  <si>
-    <t>11.06.202667</t>
-  </si>
-  <si>
-    <t>11.06.202668</t>
-  </si>
-  <si>
-    <t>11.06.202669</t>
-  </si>
-  <si>
-    <t>11.06.202670</t>
-  </si>
-  <si>
-    <t>11.06.202671</t>
-  </si>
-  <si>
-    <t>11.06.202672</t>
-  </si>
-  <si>
-    <t>11.06.202673</t>
-  </si>
-  <si>
-    <t>11.06.202674</t>
-  </si>
-  <si>
-    <t>11.06.202675</t>
-  </si>
-  <si>
-    <t>11.06.202676</t>
-  </si>
-  <si>
-    <t>11.06.202677</t>
-  </si>
-  <si>
-    <t>11.06.202678</t>
-  </si>
-  <si>
-    <t>11.06.202679</t>
-  </si>
-  <si>
-    <t>11.06.202680</t>
-  </si>
-  <si>
-    <t>11.06.202681</t>
-  </si>
-  <si>
-    <t>11.06.202682</t>
-  </si>
-  <si>
-    <t>11.06.202683</t>
-  </si>
-  <si>
-    <t>11.06.202684</t>
-  </si>
-  <si>
-    <t>11.06.202685</t>
-  </si>
-  <si>
-    <t>11.06.202686</t>
-  </si>
-  <si>
-    <t>11.06.202687</t>
-  </si>
-  <si>
-    <t>11.06.202688</t>
-  </si>
-  <si>
-    <t>11.06.202689</t>
-  </si>
-  <si>
-    <t>11.06.202690</t>
-  </si>
-  <si>
-    <t>11.06.202691</t>
-  </si>
-  <si>
-    <t>11.06.202692</t>
-  </si>
-  <si>
-    <t>11.06.202693</t>
-  </si>
-  <si>
-    <t>12.06.202694</t>
-  </si>
-  <si>
-    <t>12.06.202695</t>
-  </si>
-  <si>
-    <t>12.06.202696</t>
-  </si>
-  <si>
-    <t>12.06.20261</t>
-  </si>
-  <si>
-    <t>12.06.20262</t>
-  </si>
-  <si>
-    <t>12.06.20263</t>
-  </si>
-  <si>
-    <t>12.06.20264</t>
-  </si>
-  <si>
-    <t>12.06.20265</t>
-  </si>
-  <si>
-    <t>12.06.20266</t>
-  </si>
-  <si>
-    <t>12.06.20267</t>
-  </si>
-  <si>
-    <t>12.06.20268</t>
-  </si>
-  <si>
-    <t>12.06.20269</t>
-  </si>
-  <si>
-    <t>12.06.202610</t>
-  </si>
-  <si>
-    <t>12.06.202611</t>
-  </si>
-  <si>
-    <t>12.06.202612</t>
-  </si>
-  <si>
-    <t>12.06.202613</t>
-  </si>
-  <si>
-    <t>12.06.202614</t>
-  </si>
-  <si>
-    <t>12.06.202615</t>
-  </si>
-  <si>
-    <t>12.06.202616</t>
-  </si>
-  <si>
-    <t>12.06.202617</t>
-  </si>
-  <si>
-    <t>12.06.202618</t>
-  </si>
-  <si>
-    <t>12.06.202619</t>
-  </si>
-  <si>
-    <t>12.06.202620</t>
-  </si>
-  <si>
-    <t>12.06.202621</t>
-  </si>
-  <si>
-    <t>12.06.202622</t>
-  </si>
-  <si>
-    <t>12.06.202623</t>
-  </si>
-  <si>
-    <t>12.06.202624</t>
-  </si>
-  <si>
-    <t>12.06.202625</t>
-  </si>
-  <si>
-    <t>12.06.202626</t>
-  </si>
-  <si>
-    <t>12.06.202627</t>
-  </si>
-  <si>
-    <t>12.06.202628</t>
-  </si>
-  <si>
-    <t>12.06.202629</t>
-  </si>
-  <si>
-    <t>12.06.202630</t>
-  </si>
-  <si>
-    <t>12.06.202631</t>
-  </si>
-  <si>
-    <t>12.06.202632</t>
-  </si>
-  <si>
-    <t>12.06.202633</t>
-  </si>
-  <si>
-    <t>12.06.202634</t>
-  </si>
-  <si>
-    <t>12.06.202635</t>
-  </si>
-  <si>
-    <t>12.06.202636</t>
-  </si>
-  <si>
-    <t>12.06.202637</t>
-  </si>
-  <si>
-    <t>12.06.202638</t>
-  </si>
-  <si>
-    <t>12.06.202639</t>
-  </si>
-  <si>
-    <t>12.06.202640</t>
-  </si>
-  <si>
-    <t>12.06.202641</t>
-  </si>
-  <si>
-    <t>12.06.202642</t>
-  </si>
-  <si>
-    <t>12.06.202643</t>
-  </si>
-  <si>
-    <t>12.06.202644</t>
-  </si>
-  <si>
-    <t>12.06.202645</t>
-  </si>
-  <si>
-    <t>12.06.202646</t>
-  </si>
-  <si>
-    <t>12.06.202647</t>
-  </si>
-  <si>
-    <t>12.06.202648</t>
-  </si>
-  <si>
-    <t>12.06.202649</t>
-  </si>
-  <si>
-    <t>12.06.202650</t>
-  </si>
-  <si>
-    <t>12.06.202651</t>
-  </si>
-  <si>
-    <t>12.06.202652</t>
-  </si>
-  <si>
-    <t>12.06.202653</t>
-  </si>
-  <si>
-    <t>12.06.202654</t>
-  </si>
-  <si>
-    <t>12.06.202655</t>
-  </si>
-  <si>
-    <t>12.06.202656</t>
-  </si>
-  <si>
-    <t>12.06.202657</t>
-  </si>
-  <si>
-    <t>12.06.202658</t>
-  </si>
-  <si>
-    <t>12.06.202659</t>
-  </si>
-  <si>
-    <t>12.06.202660</t>
-  </si>
-  <si>
-    <t>12.06.202661</t>
-  </si>
-  <si>
-    <t>12.06.202662</t>
-  </si>
-  <si>
-    <t>12.06.202663</t>
-  </si>
-  <si>
-    <t>12.06.202664</t>
-  </si>
-  <si>
-    <t>12.06.202665</t>
-  </si>
-  <si>
-    <t>12.06.202666</t>
-  </si>
-  <si>
-    <t>12.06.202667</t>
-  </si>
-  <si>
-    <t>12.06.202668</t>
-  </si>
-  <si>
-    <t>12.06.202669</t>
-  </si>
-  <si>
-    <t>12.06.202670</t>
-  </si>
-  <si>
-    <t>12.06.202671</t>
-  </si>
-  <si>
-    <t>12.06.202672</t>
-  </si>
-  <si>
-    <t>12.06.202673</t>
-  </si>
-  <si>
-    <t>12.06.202674</t>
-  </si>
-  <si>
-    <t>12.06.202675</t>
-  </si>
-  <si>
-    <t>12.06.202676</t>
-  </si>
-  <si>
-    <t>12.06.202677</t>
-  </si>
-  <si>
-    <t>12.06.202678</t>
-  </si>
-  <si>
-    <t>12.06.202679</t>
-  </si>
-  <si>
-    <t>12.06.202680</t>
-  </si>
-  <si>
-    <t>12.06.202681</t>
-  </si>
-  <si>
-    <t>12.06.202682</t>
-  </si>
-  <si>
-    <t>12.06.202683</t>
-  </si>
-  <si>
-    <t>12.06.202684</t>
-  </si>
-  <si>
-    <t>12.06.202685</t>
-  </si>
-  <si>
-    <t>12.06.202686</t>
-  </si>
-  <si>
-    <t>12.06.202687</t>
-  </si>
-  <si>
-    <t>12.06.202688</t>
-  </si>
-  <si>
-    <t>12.06.202689</t>
-  </si>
-  <si>
-    <t>12.06.202690</t>
-  </si>
-  <si>
-    <t>12.06.202691</t>
-  </si>
-  <si>
-    <t>12.06.202692</t>
-  </si>
-  <si>
-    <t>12.06.202693</t>
-  </si>
-  <si>
-    <t>13.06.202695</t>
-  </si>
-  <si>
-    <t>13.06.202696</t>
-  </si>
-  <si>
-    <t>13.06.20261</t>
-  </si>
-  <si>
-    <t>13.06.20262</t>
+    <t>09.07.20261</t>
+  </si>
+  <si>
+    <t>09.07.20262</t>
+  </si>
+  <si>
+    <t>09.07.20263</t>
+  </si>
+  <si>
+    <t>09.07.20264</t>
+  </si>
+  <si>
+    <t>09.07.20265</t>
+  </si>
+  <si>
+    <t>09.07.20266</t>
+  </si>
+  <si>
+    <t>09.07.20267</t>
+  </si>
+  <si>
+    <t>09.07.20268</t>
+  </si>
+  <si>
+    <t>09.07.20269</t>
+  </si>
+  <si>
+    <t>09.07.202610</t>
+  </si>
+  <si>
+    <t>09.07.202611</t>
+  </si>
+  <si>
+    <t>09.07.202612</t>
+  </si>
+  <si>
+    <t>09.07.202613</t>
+  </si>
+  <si>
+    <t>09.07.202614</t>
+  </si>
+  <si>
+    <t>09.07.202615</t>
+  </si>
+  <si>
+    <t>09.07.202616</t>
+  </si>
+  <si>
+    <t>09.07.202617</t>
+  </si>
+  <si>
+    <t>09.07.202618</t>
+  </si>
+  <si>
+    <t>09.07.202619</t>
+  </si>
+  <si>
+    <t>09.07.202620</t>
+  </si>
+  <si>
+    <t>09.07.202621</t>
+  </si>
+  <si>
+    <t>09.07.202622</t>
+  </si>
+  <si>
+    <t>09.07.202623</t>
+  </si>
+  <si>
+    <t>09.07.202624</t>
+  </si>
+  <si>
+    <t>09.07.202625</t>
+  </si>
+  <si>
+    <t>09.07.202626</t>
+  </si>
+  <si>
+    <t>09.07.202627</t>
+  </si>
+  <si>
+    <t>09.07.202628</t>
+  </si>
+  <si>
+    <t>09.07.202629</t>
+  </si>
+  <si>
+    <t>09.07.202630</t>
+  </si>
+  <si>
+    <t>09.07.202631</t>
+  </si>
+  <si>
+    <t>09.07.202632</t>
+  </si>
+  <si>
+    <t>09.07.202633</t>
+  </si>
+  <si>
+    <t>09.07.202634</t>
+  </si>
+  <si>
+    <t>09.07.202635</t>
+  </si>
+  <si>
+    <t>09.07.202636</t>
+  </si>
+  <si>
+    <t>09.07.202637</t>
+  </si>
+  <si>
+    <t>09.07.202638</t>
+  </si>
+  <si>
+    <t>09.07.202639</t>
+  </si>
+  <si>
+    <t>09.07.202640</t>
+  </si>
+  <si>
+    <t>09.07.202641</t>
+  </si>
+  <si>
+    <t>09.07.202642</t>
+  </si>
+  <si>
+    <t>09.07.202643</t>
+  </si>
+  <si>
+    <t>09.07.202644</t>
+  </si>
+  <si>
+    <t>09.07.202645</t>
+  </si>
+  <si>
+    <t>09.07.202646</t>
+  </si>
+  <si>
+    <t>09.07.202647</t>
+  </si>
+  <si>
+    <t>09.07.202648</t>
+  </si>
+  <si>
+    <t>09.07.202649</t>
+  </si>
+  <si>
+    <t>09.07.202650</t>
+  </si>
+  <si>
+    <t>09.07.202651</t>
+  </si>
+  <si>
+    <t>09.07.202652</t>
+  </si>
+  <si>
+    <t>09.07.202653</t>
+  </si>
+  <si>
+    <t>09.07.202654</t>
+  </si>
+  <si>
+    <t>09.07.202655</t>
+  </si>
+  <si>
+    <t>09.07.202656</t>
+  </si>
+  <si>
+    <t>09.07.202657</t>
+  </si>
+  <si>
+    <t>09.07.202658</t>
+  </si>
+  <si>
+    <t>09.07.202659</t>
+  </si>
+  <si>
+    <t>09.07.202660</t>
+  </si>
+  <si>
+    <t>09.07.202661</t>
+  </si>
+  <si>
+    <t>09.07.202662</t>
+  </si>
+  <si>
+    <t>09.07.202663</t>
+  </si>
+  <si>
+    <t>09.07.202664</t>
+  </si>
+  <si>
+    <t>09.07.202665</t>
+  </si>
+  <si>
+    <t>09.07.202666</t>
+  </si>
+  <si>
+    <t>09.07.202667</t>
+  </si>
+  <si>
+    <t>09.07.202668</t>
+  </si>
+  <si>
+    <t>09.07.202669</t>
+  </si>
+  <si>
+    <t>09.07.202670</t>
+  </si>
+  <si>
+    <t>09.07.202671</t>
+  </si>
+  <si>
+    <t>09.07.202672</t>
+  </si>
+  <si>
+    <t>09.07.202673</t>
+  </si>
+  <si>
+    <t>09.07.202674</t>
+  </si>
+  <si>
+    <t>09.07.202675</t>
+  </si>
+  <si>
+    <t>09.07.202676</t>
+  </si>
+  <si>
+    <t>09.07.202677</t>
+  </si>
+  <si>
+    <t>09.07.202678</t>
+  </si>
+  <si>
+    <t>09.07.202679</t>
+  </si>
+  <si>
+    <t>09.07.202680</t>
+  </si>
+  <si>
+    <t>09.07.202681</t>
+  </si>
+  <si>
+    <t>09.07.202682</t>
+  </si>
+  <si>
+    <t>09.07.202683</t>
+  </si>
+  <si>
+    <t>09.07.202684</t>
+  </si>
+  <si>
+    <t>09.07.202685</t>
+  </si>
+  <si>
+    <t>09.07.202686</t>
+  </si>
+  <si>
+    <t>09.07.202687</t>
+  </si>
+  <si>
+    <t>09.07.202688</t>
+  </si>
+  <si>
+    <t>09.07.202689</t>
+  </si>
+  <si>
+    <t>09.07.202690</t>
+  </si>
+  <si>
+    <t>09.07.202691</t>
+  </si>
+  <si>
+    <t>09.07.202692</t>
+  </si>
+  <si>
+    <t>09.07.202693</t>
+  </si>
+  <si>
+    <t>09.07.202694</t>
+  </si>
+  <si>
+    <t>09.07.202695</t>
+  </si>
+  <si>
+    <t>09.07.202696</t>
+  </si>
+  <si>
+    <t>10.07.20261</t>
+  </si>
+  <si>
+    <t>10.07.20262</t>
+  </si>
+  <si>
+    <t>10.07.20263</t>
+  </si>
+  <si>
+    <t>10.07.20264</t>
+  </si>
+  <si>
+    <t>10.07.20265</t>
+  </si>
+  <si>
+    <t>10.07.20266</t>
+  </si>
+  <si>
+    <t>10.07.20267</t>
+  </si>
+  <si>
+    <t>10.07.20268</t>
+  </si>
+  <si>
+    <t>10.07.20269</t>
+  </si>
+  <si>
+    <t>10.07.202610</t>
+  </si>
+  <si>
+    <t>10.07.202611</t>
+  </si>
+  <si>
+    <t>10.07.202612</t>
+  </si>
+  <si>
+    <t>10.07.202613</t>
+  </si>
+  <si>
+    <t>10.07.202614</t>
+  </si>
+  <si>
+    <t>10.07.202615</t>
+  </si>
+  <si>
+    <t>10.07.202616</t>
+  </si>
+  <si>
+    <t>10.07.202617</t>
+  </si>
+  <si>
+    <t>10.07.202618</t>
+  </si>
+  <si>
+    <t>10.07.202619</t>
+  </si>
+  <si>
+    <t>10.07.202620</t>
+  </si>
+  <si>
+    <t>10.07.202621</t>
+  </si>
+  <si>
+    <t>10.07.202622</t>
+  </si>
+  <si>
+    <t>10.07.202623</t>
+  </si>
+  <si>
+    <t>10.07.202624</t>
+  </si>
+  <si>
+    <t>10.07.202625</t>
+  </si>
+  <si>
+    <t>10.07.202626</t>
+  </si>
+  <si>
+    <t>10.07.202627</t>
+  </si>
+  <si>
+    <t>10.07.202628</t>
+  </si>
+  <si>
+    <t>10.07.202629</t>
+  </si>
+  <si>
+    <t>10.07.202630</t>
+  </si>
+  <si>
+    <t>10.07.202631</t>
+  </si>
+  <si>
+    <t>10.07.202632</t>
+  </si>
+  <si>
+    <t>10.07.202633</t>
+  </si>
+  <si>
+    <t>10.07.202634</t>
+  </si>
+  <si>
+    <t>10.07.202635</t>
+  </si>
+  <si>
+    <t>10.07.202636</t>
+  </si>
+  <si>
+    <t>10.07.202637</t>
+  </si>
+  <si>
+    <t>10.07.202638</t>
+  </si>
+  <si>
+    <t>10.07.202639</t>
+  </si>
+  <si>
+    <t>10.07.202640</t>
+  </si>
+  <si>
+    <t>10.07.202641</t>
+  </si>
+  <si>
+    <t>10.07.202642</t>
+  </si>
+  <si>
+    <t>10.07.202643</t>
+  </si>
+  <si>
+    <t>10.07.202644</t>
   </si>
 </sst>
 </file>
@@ -969,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -991,13 +832,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46184.03611111111</v>
+        <v>46212</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3.444</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1008,10 +849,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46184.04652777778</v>
+        <v>46212.01041666666</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1.381</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1025,13 +866,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46184.05694444444</v>
+        <v>46212.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1042,13 +883,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46184.06736111111</v>
+        <v>46212.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1.251</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1059,13 +900,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46184.07777777778</v>
+        <v>46212.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>17.605</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1076,13 +917,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46184.08819444444</v>
+        <v>46212.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>14.393</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1093,10 +934,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46184.09861111111</v>
+        <v>46212.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2.682</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1110,13 +951,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46184.10902777778</v>
+        <v>46212.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1127,13 +968,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46184.11944444444</v>
+        <v>46212.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>11.467</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -1144,13 +985,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46184.12986111111</v>
+        <v>46212.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>20.204</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1161,13 +1002,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46184.14027777778</v>
+        <v>46212.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>22.167</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1178,13 +1019,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46184.15069444444</v>
+        <v>46212.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>7.316</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1195,13 +1036,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46184.16111111111</v>
+        <v>46212.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>5.243</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1212,13 +1053,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46184.17152777778</v>
+        <v>46212.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>13.168</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1229,13 +1070,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46184.18194444444</v>
+        <v>46212.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1.269</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1246,10 +1087,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46184.19236111111</v>
+        <v>46212.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>1.395</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1263,13 +1104,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46184.20277777778</v>
+        <v>46212.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>21.022</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1280,13 +1121,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46184.21319444444</v>
+        <v>46212.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>26.191</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1297,13 +1138,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46184.22361111111</v>
+        <v>46212.1875</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>3.085</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1314,10 +1155,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46184.23402777778</v>
+        <v>46212.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>9.928000000000001</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1331,13 +1172,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46184.24444444444</v>
+        <v>46212.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>6.673</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1348,10 +1189,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46184.25486111111</v>
+        <v>46212.21875</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>9.56</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1365,10 +1206,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46184.26527777778</v>
+        <v>46212.22916666666</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1382,13 +1223,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46184.27569444444</v>
+        <v>46212.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>7.971</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1399,10 +1240,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46184.28611111111</v>
+        <v>46212.25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1416,13 +1257,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46184.29652777778</v>
+        <v>46212.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>3.046</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1433,13 +1274,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46184.30694444444</v>
+        <v>46212.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>2.665</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1450,13 +1291,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46184.31736111111</v>
+        <v>46212.28125</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>7.649</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1467,13 +1308,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46184.32777777778</v>
+        <v>46212.29166666666</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>6.497</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1484,13 +1325,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46184.33819444444</v>
+        <v>46212.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>8.257</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1501,10 +1342,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46184.34861111111</v>
+        <v>46212.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1.095</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -1518,10 +1359,10 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46184.35902777778</v>
+        <v>46212.32291666666</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>5.204</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -1535,13 +1376,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46184.36944444444</v>
+        <v>46212.33333333334</v>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>17.396</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1552,13 +1393,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46184.37986111111</v>
+        <v>46212.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>17.587</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1569,13 +1410,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46184.39027777778</v>
+        <v>46212.35416666666</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>27.124</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1586,13 +1427,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46184.40069444444</v>
+        <v>46212.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>30.921</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1603,13 +1444,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46184.41111111111</v>
+        <v>46212.375</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>18.284</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1620,13 +1461,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46184.42152777778</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>31.589</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1637,13 +1478,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46184.43194444444</v>
+        <v>46212.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>27.937</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1654,13 +1495,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46184.44236111111</v>
+        <v>46212.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>30.73</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1671,10 +1512,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46184.45277777778</v>
+        <v>46212.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>23.059</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1688,10 +1529,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46184.46319444444</v>
+        <v>46212.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>19.147</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1705,10 +1546,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46184.47361111111</v>
+        <v>46212.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>12.465</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1722,10 +1563,10 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46184.48402777778</v>
+        <v>46212.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>12.806</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -1739,13 +1580,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46184.49444444444</v>
+        <v>46212.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>0.901</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1756,10 +1597,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46184.50486111111</v>
+        <v>46212.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>3.064</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -1773,10 +1614,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46184.51527777778</v>
+        <v>46212.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>19.249</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -1790,10 +1631,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46184.52569444444</v>
+        <v>46212.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>29.126</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1807,10 +1648,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46184.53611111111</v>
+        <v>46212.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>30.644</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -1824,10 +1665,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46184.54652777778</v>
+        <v>46212.51041666666</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>43.974</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1841,10 +1682,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46184.55694444444</v>
+        <v>46212.52083333334</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>71.923</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -1858,10 +1699,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46184.56736111111</v>
+        <v>46212.53125</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>25.491</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1875,13 +1716,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46184.57777777778</v>
+        <v>46212.54166666666</v>
       </c>
       <c r="B54">
         <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>16.029</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1892,13 +1733,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46184.58819444444</v>
+        <v>46212.55208333334</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>23.519</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1909,10 +1750,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46184.59861111111</v>
+        <v>46212.5625</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>4.474</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1926,10 +1767,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46184.60902777778</v>
+        <v>46212.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>27.742</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -1943,10 +1784,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46184.61944444444</v>
+        <v>46212.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>2.636</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -1960,10 +1801,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46184.62986111111</v>
+        <v>46212.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>26.397</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -1977,10 +1818,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46184.64027777778</v>
+        <v>46212.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>9.551</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -1994,10 +1835,10 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46184.65069444444</v>
+        <v>46212.61458333334</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>2.572</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2011,10 +1852,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46184.66111111111</v>
+        <v>46212.625</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>8.109</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2028,13 +1869,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46184.67152777778</v>
+        <v>46212.63541666666</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>8.271000000000001</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -2045,13 +1886,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46184.68194444444</v>
+        <v>46212.64583333334</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>6.028</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -2062,10 +1903,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46184.69236111111</v>
+        <v>46212.65625</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>13.503</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2079,13 +1920,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46184.70277777778</v>
+        <v>46212.66666666666</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>0.835</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -2096,13 +1937,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46184.71319444444</v>
+        <v>46212.67708333334</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>13.566</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -2113,13 +1954,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46184.72361111111</v>
+        <v>46212.6875</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -2130,13 +1971,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46184.73402777778</v>
+        <v>46212.69791666666</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>23.775</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -2147,13 +1988,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46184.74444444444</v>
+        <v>46212.70833333334</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>29.209</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2164,13 +2005,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46184.75486111111</v>
+        <v>46212.71875</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>13.39</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2181,13 +2022,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46184.76527777778</v>
+        <v>46212.72916666666</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>23.18</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2198,13 +2039,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46184.77569444444</v>
+        <v>46212.73958333334</v>
       </c>
       <c r="B73">
         <v>0</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>0.555</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2215,13 +2056,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46184.78611111111</v>
+        <v>46212.75</v>
       </c>
       <c r="B74">
         <v>0</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>35.193</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2232,13 +2073,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46184.79652777778</v>
+        <v>46212.76041666666</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>20.956</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2249,13 +2090,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46184.80694444444</v>
+        <v>46212.77083333334</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>3.221</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2266,13 +2107,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46184.81736111111</v>
+        <v>46212.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>6.543</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2283,10 +2124,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46184.82777777778</v>
+        <v>46212.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>4.043</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2300,10 +2141,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46184.83819444444</v>
+        <v>46212.80208333334</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>8.217000000000001</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2317,10 +2158,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46184.84861111111</v>
+        <v>46212.8125</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>12.385</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2334,13 +2175,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46184.85902777778</v>
+        <v>46212.82291666666</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>6.428</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2351,13 +2192,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46184.86944444444</v>
+        <v>46212.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2368,13 +2209,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46184.87986111111</v>
+        <v>46212.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>8.657999999999999</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2385,13 +2226,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46184.89027777778</v>
+        <v>46212.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>17.133</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2402,13 +2243,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46184.90069444444</v>
+        <v>46212.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>55.247</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2419,13 +2260,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46184.91111111111</v>
+        <v>46212.875</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>40.036</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2436,13 +2277,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46184.92152777778</v>
+        <v>46212.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>8.561999999999999</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2453,10 +2294,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46184.93194444444</v>
+        <v>46212.89583333334</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>2.958</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2470,13 +2311,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46184.94236111111</v>
+        <v>46212.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>6.763</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2487,10 +2328,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46184.95277777778</v>
+        <v>46212.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>24.488</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2504,10 +2345,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46184.96319444444</v>
+        <v>46212.92708333334</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>46.889</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2521,10 +2362,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46184.97361111111</v>
+        <v>46212.9375</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>34.139</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2538,10 +2379,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46184.98402777778</v>
+        <v>46212.94791666666</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>26.132</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2555,10 +2396,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46184.99444444444</v>
+        <v>46212.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>20.609</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2572,10 +2413,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46185.00486111111</v>
+        <v>46212.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>20.119</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2589,10 +2430,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46185.01527777778</v>
+        <v>46212.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>29.395</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2606,10 +2447,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46185.02569444444</v>
+        <v>46212.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>42.703</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2623,10 +2464,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46185.03611111111</v>
+        <v>46213</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>8.412000000000001</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2640,13 +2481,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46185.03611111111</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>3.206</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2657,13 +2498,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46185.04652777778</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>2.876</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2674,13 +2515,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46185.05694444444</v>
+        <v>46213.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>22.423</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2691,13 +2532,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46185.06736111111</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>31.319</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2708,13 +2549,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46185.07777777778</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>9.878</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2725,13 +2566,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46185.08819444444</v>
+        <v>46213.0625</v>
       </c>
       <c r="B104">
         <v>0</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>5.821</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2742,13 +2583,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46185.09861111111</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2759,13 +2600,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46185.10902777778</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>10.496</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2776,13 +2617,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46185.11944444444</v>
+        <v>46213.09375</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>4.144</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2793,13 +2634,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46185.12986111111</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>25.946</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2810,13 +2651,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46185.14027777778</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>21.014</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2827,13 +2668,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46185.15069444444</v>
+        <v>46213.125</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>3.613</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2844,13 +2685,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46185.16111111111</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>10.443</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2861,13 +2702,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46185.17152777778</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2878,13 +2719,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46185.18194444444</v>
+        <v>46213.15625</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>13.642</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2895,13 +2736,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46185.19236111111</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B114">
         <v>0</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>2.753</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2912,10 +2753,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46185.20277777778</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>10.926</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2929,10 +2770,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46185.21319444444</v>
+        <v>46213.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>12.94</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2946,10 +2787,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46185.22361111111</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>23.476</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2963,10 +2804,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46185.23402777778</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>17.724</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2980,10 +2821,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46185.24444444444</v>
+        <v>46213.21875</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>12.589</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2997,13 +2838,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46185.25486111111</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>11.99</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -3014,13 +2855,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46185.26527777778</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>4.409</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -3031,13 +2872,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46185.27569444444</v>
+        <v>46213.25</v>
       </c>
       <c r="B122">
         <v>0</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>3.863</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -3048,13 +2889,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46185.28611111111</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>14.781</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -3065,13 +2906,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46185.29652777778</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>23.911</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -3082,13 +2923,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46185.30694444444</v>
+        <v>46213.28125</v>
       </c>
       <c r="B125">
         <v>0</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>20.543</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -3099,13 +2940,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46185.31736111111</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B126">
         <v>0</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>5.537</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -3116,13 +2957,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46185.32777777778</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>9.722</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -3133,13 +2974,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46185.33819444444</v>
+        <v>46213.3125</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>28.735</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -3150,13 +2991,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46185.34861111111</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>15.568</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3167,10 +3008,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46185.35902777778</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B130">
-        <v>0</v>
+        <v>1.317</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3184,10 +3025,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46185.36944444444</v>
+        <v>46213.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3201,10 +3042,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46185.37986111111</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B132">
-        <v>0</v>
+        <v>17.977</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3218,13 +3059,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46185.39027777778</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>2.732</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3235,10 +3076,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46185.40069444444</v>
+        <v>46213.375</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>16.927</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3252,13 +3093,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46185.41111111111</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>32.053</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3269,13 +3110,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46185.42152777778</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>4.695</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3286,13 +3127,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46185.43194444444</v>
+        <v>46213.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>10.008</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3303,10 +3144,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46185.44236111111</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>0.926</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3320,10 +3161,10 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46185.45277777778</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>5.194</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -3337,13 +3178,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46185.46319444444</v>
+        <v>46213.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>3.221</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3354,937 +3195,19 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46185.47361111111</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>8.423999999999999</v>
       </c>
       <c r="D141">
         <v>44</v>
       </c>
       <c r="E141" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" s="2">
-        <v>46185.48402777778</v>
-      </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-      <c r="C142">
-        <v>0</v>
-      </c>
-      <c r="D142">
-        <v>45</v>
-      </c>
-      <c r="E142" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" s="2">
-        <v>46185.49444444444</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-      <c r="C143">
-        <v>0</v>
-      </c>
-      <c r="D143">
-        <v>46</v>
-      </c>
-      <c r="E143" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
-      <c r="A144" s="2">
-        <v>46185.50486111111</v>
-      </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-      <c r="C144">
-        <v>0</v>
-      </c>
-      <c r="D144">
-        <v>47</v>
-      </c>
-      <c r="E144" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
-      <c r="A145" s="2">
-        <v>46185.51527777778</v>
-      </c>
-      <c r="B145">
-        <v>0</v>
-      </c>
-      <c r="C145">
-        <v>0</v>
-      </c>
-      <c r="D145">
-        <v>48</v>
-      </c>
-      <c r="E145" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
-      <c r="A146" s="2">
-        <v>46185.52569444444</v>
-      </c>
-      <c r="B146">
-        <v>0</v>
-      </c>
-      <c r="C146">
-        <v>0</v>
-      </c>
-      <c r="D146">
-        <v>49</v>
-      </c>
-      <c r="E146" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
-      <c r="A147" s="2">
-        <v>46185.53611111111</v>
-      </c>
-      <c r="B147">
-        <v>0</v>
-      </c>
-      <c r="C147">
-        <v>0</v>
-      </c>
-      <c r="D147">
-        <v>50</v>
-      </c>
-      <c r="E147" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="A148" s="2">
-        <v>46185.54652777778</v>
-      </c>
-      <c r="B148">
-        <v>0</v>
-      </c>
-      <c r="C148">
-        <v>0</v>
-      </c>
-      <c r="D148">
-        <v>51</v>
-      </c>
-      <c r="E148" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="A149" s="2">
-        <v>46185.55694444444</v>
-      </c>
-      <c r="B149">
-        <v>0</v>
-      </c>
-      <c r="C149">
-        <v>0</v>
-      </c>
-      <c r="D149">
-        <v>52</v>
-      </c>
-      <c r="E149" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" s="2">
-        <v>46185.56736111111</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-      <c r="C150">
-        <v>0</v>
-      </c>
-      <c r="D150">
-        <v>53</v>
-      </c>
-      <c r="E150" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
-      <c r="A151" s="2">
-        <v>46185.57777777778</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-      <c r="C151">
-        <v>0</v>
-      </c>
-      <c r="D151">
-        <v>54</v>
-      </c>
-      <c r="E151" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" s="2">
-        <v>46185.58819444444</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-      <c r="C152">
-        <v>0</v>
-      </c>
-      <c r="D152">
-        <v>55</v>
-      </c>
-      <c r="E152" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" s="2">
-        <v>46185.59861111111</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
-      </c>
-      <c r="D153">
-        <v>56</v>
-      </c>
-      <c r="E153" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
-      <c r="A154" s="2">
-        <v>46185.60902777778</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-      <c r="C154">
-        <v>0</v>
-      </c>
-      <c r="D154">
-        <v>57</v>
-      </c>
-      <c r="E154" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
-      <c r="A155" s="2">
-        <v>46185.61944444444</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-      <c r="C155">
-        <v>0</v>
-      </c>
-      <c r="D155">
-        <v>58</v>
-      </c>
-      <c r="E155" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
-      <c r="A156" s="2">
-        <v>46185.62986111111</v>
-      </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-      <c r="C156">
-        <v>0</v>
-      </c>
-      <c r="D156">
-        <v>59</v>
-      </c>
-      <c r="E156" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
-      <c r="A157" s="2">
-        <v>46185.64027777778</v>
-      </c>
-      <c r="B157">
-        <v>0</v>
-      </c>
-      <c r="C157">
-        <v>0</v>
-      </c>
-      <c r="D157">
-        <v>60</v>
-      </c>
-      <c r="E157" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
-      <c r="A158" s="2">
-        <v>46185.65069444444</v>
-      </c>
-      <c r="B158">
-        <v>0</v>
-      </c>
-      <c r="C158">
-        <v>0</v>
-      </c>
-      <c r="D158">
-        <v>61</v>
-      </c>
-      <c r="E158" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
-      <c r="A159" s="2">
-        <v>46185.66111111111</v>
-      </c>
-      <c r="B159">
-        <v>0</v>
-      </c>
-      <c r="C159">
-        <v>0</v>
-      </c>
-      <c r="D159">
-        <v>62</v>
-      </c>
-      <c r="E159" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
-      <c r="A160" s="2">
-        <v>46185.67152777778</v>
-      </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-      <c r="C160">
-        <v>0</v>
-      </c>
-      <c r="D160">
-        <v>63</v>
-      </c>
-      <c r="E160" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
-      <c r="A161" s="2">
-        <v>46185.68194444444</v>
-      </c>
-      <c r="B161">
-        <v>0</v>
-      </c>
-      <c r="C161">
-        <v>0</v>
-      </c>
-      <c r="D161">
-        <v>64</v>
-      </c>
-      <c r="E161" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
-      <c r="A162" s="2">
-        <v>46185.69236111111</v>
-      </c>
-      <c r="B162">
-        <v>0</v>
-      </c>
-      <c r="C162">
-        <v>0</v>
-      </c>
-      <c r="D162">
-        <v>65</v>
-      </c>
-      <c r="E162" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
-      <c r="A163" s="2">
-        <v>46185.70277777778</v>
-      </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-      <c r="C163">
-        <v>0</v>
-      </c>
-      <c r="D163">
-        <v>66</v>
-      </c>
-      <c r="E163" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
-      <c r="A164" s="2">
-        <v>46185.71319444444</v>
-      </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-      <c r="C164">
-        <v>0</v>
-      </c>
-      <c r="D164">
-        <v>67</v>
-      </c>
-      <c r="E164" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
-      <c r="A165" s="2">
-        <v>46185.72361111111</v>
-      </c>
-      <c r="B165">
-        <v>0</v>
-      </c>
-      <c r="C165">
-        <v>0</v>
-      </c>
-      <c r="D165">
-        <v>68</v>
-      </c>
-      <c r="E165" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
-      <c r="A166" s="2">
-        <v>46185.73402777778</v>
-      </c>
-      <c r="B166">
-        <v>0</v>
-      </c>
-      <c r="C166">
-        <v>0</v>
-      </c>
-      <c r="D166">
-        <v>69</v>
-      </c>
-      <c r="E166" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
-      <c r="A167" s="2">
-        <v>46185.74444444444</v>
-      </c>
-      <c r="B167">
-        <v>0</v>
-      </c>
-      <c r="C167">
-        <v>0</v>
-      </c>
-      <c r="D167">
-        <v>70</v>
-      </c>
-      <c r="E167" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
-      <c r="A168" s="2">
-        <v>46185.75486111111</v>
-      </c>
-      <c r="B168">
-        <v>0</v>
-      </c>
-      <c r="C168">
-        <v>0</v>
-      </c>
-      <c r="D168">
-        <v>71</v>
-      </c>
-      <c r="E168" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5">
-      <c r="A169" s="2">
-        <v>46185.76527777778</v>
-      </c>
-      <c r="B169">
-        <v>0</v>
-      </c>
-      <c r="C169">
-        <v>0</v>
-      </c>
-      <c r="D169">
-        <v>72</v>
-      </c>
-      <c r="E169" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
-      <c r="A170" s="2">
-        <v>46185.77569444444</v>
-      </c>
-      <c r="B170">
-        <v>0</v>
-      </c>
-      <c r="C170">
-        <v>0</v>
-      </c>
-      <c r="D170">
-        <v>73</v>
-      </c>
-      <c r="E170" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
-      <c r="A171" s="2">
-        <v>46185.78611111111</v>
-      </c>
-      <c r="B171">
-        <v>0</v>
-      </c>
-      <c r="C171">
-        <v>0</v>
-      </c>
-      <c r="D171">
-        <v>74</v>
-      </c>
-      <c r="E171" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5">
-      <c r="A172" s="2">
-        <v>46185.79652777778</v>
-      </c>
-      <c r="B172">
-        <v>0</v>
-      </c>
-      <c r="C172">
-        <v>0</v>
-      </c>
-      <c r="D172">
-        <v>75</v>
-      </c>
-      <c r="E172" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
-      <c r="A173" s="2">
-        <v>46185.80694444444</v>
-      </c>
-      <c r="B173">
-        <v>0</v>
-      </c>
-      <c r="C173">
-        <v>0</v>
-      </c>
-      <c r="D173">
-        <v>76</v>
-      </c>
-      <c r="E173" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5">
-      <c r="A174" s="2">
-        <v>46185.81736111111</v>
-      </c>
-      <c r="B174">
-        <v>0</v>
-      </c>
-      <c r="C174">
-        <v>0</v>
-      </c>
-      <c r="D174">
-        <v>77</v>
-      </c>
-      <c r="E174" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5">
-      <c r="A175" s="2">
-        <v>46185.82777777778</v>
-      </c>
-      <c r="B175">
-        <v>0</v>
-      </c>
-      <c r="C175">
-        <v>0</v>
-      </c>
-      <c r="D175">
-        <v>78</v>
-      </c>
-      <c r="E175" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5">
-      <c r="A176" s="2">
-        <v>46185.83819444444</v>
-      </c>
-      <c r="B176">
-        <v>0</v>
-      </c>
-      <c r="C176">
-        <v>0</v>
-      </c>
-      <c r="D176">
-        <v>79</v>
-      </c>
-      <c r="E176" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
-      <c r="A177" s="2">
-        <v>46185.84861111111</v>
-      </c>
-      <c r="B177">
-        <v>0</v>
-      </c>
-      <c r="C177">
-        <v>0</v>
-      </c>
-      <c r="D177">
-        <v>80</v>
-      </c>
-      <c r="E177" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5">
-      <c r="A178" s="2">
-        <v>46185.85902777778</v>
-      </c>
-      <c r="B178">
-        <v>0</v>
-      </c>
-      <c r="C178">
-        <v>0</v>
-      </c>
-      <c r="D178">
-        <v>81</v>
-      </c>
-      <c r="E178" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5">
-      <c r="A179" s="2">
-        <v>46185.86944444444</v>
-      </c>
-      <c r="B179">
-        <v>0</v>
-      </c>
-      <c r="C179">
-        <v>0</v>
-      </c>
-      <c r="D179">
-        <v>82</v>
-      </c>
-      <c r="E179" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5">
-      <c r="A180" s="2">
-        <v>46185.87986111111</v>
-      </c>
-      <c r="B180">
-        <v>0</v>
-      </c>
-      <c r="C180">
-        <v>0</v>
-      </c>
-      <c r="D180">
-        <v>83</v>
-      </c>
-      <c r="E180" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5">
-      <c r="A181" s="2">
-        <v>46185.89027777778</v>
-      </c>
-      <c r="B181">
-        <v>0</v>
-      </c>
-      <c r="C181">
-        <v>0</v>
-      </c>
-      <c r="D181">
-        <v>84</v>
-      </c>
-      <c r="E181" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5">
-      <c r="A182" s="2">
-        <v>46185.90069444444</v>
-      </c>
-      <c r="B182">
-        <v>0</v>
-      </c>
-      <c r="C182">
-        <v>0</v>
-      </c>
-      <c r="D182">
-        <v>85</v>
-      </c>
-      <c r="E182" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
-      <c r="A183" s="2">
-        <v>46185.91111111111</v>
-      </c>
-      <c r="B183">
-        <v>0</v>
-      </c>
-      <c r="C183">
-        <v>0</v>
-      </c>
-      <c r="D183">
-        <v>86</v>
-      </c>
-      <c r="E183" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5">
-      <c r="A184" s="2">
-        <v>46185.92152777778</v>
-      </c>
-      <c r="B184">
-        <v>0</v>
-      </c>
-      <c r="C184">
-        <v>0</v>
-      </c>
-      <c r="D184">
-        <v>87</v>
-      </c>
-      <c r="E184" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5">
-      <c r="A185" s="2">
-        <v>46185.93194444444</v>
-      </c>
-      <c r="B185">
-        <v>0</v>
-      </c>
-      <c r="C185">
-        <v>0</v>
-      </c>
-      <c r="D185">
-        <v>88</v>
-      </c>
-      <c r="E185" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5">
-      <c r="A186" s="2">
-        <v>46185.94236111111</v>
-      </c>
-      <c r="B186">
-        <v>0</v>
-      </c>
-      <c r="C186">
-        <v>0</v>
-      </c>
-      <c r="D186">
-        <v>89</v>
-      </c>
-      <c r="E186" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5">
-      <c r="A187" s="2">
-        <v>46185.95277777778</v>
-      </c>
-      <c r="B187">
-        <v>0</v>
-      </c>
-      <c r="C187">
-        <v>0</v>
-      </c>
-      <c r="D187">
-        <v>90</v>
-      </c>
-      <c r="E187" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5">
-      <c r="A188" s="2">
-        <v>46185.96319444444</v>
-      </c>
-      <c r="B188">
-        <v>0</v>
-      </c>
-      <c r="C188">
-        <v>0</v>
-      </c>
-      <c r="D188">
-        <v>91</v>
-      </c>
-      <c r="E188" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5">
-      <c r="A189" s="2">
-        <v>46185.97361111111</v>
-      </c>
-      <c r="B189">
-        <v>0</v>
-      </c>
-      <c r="C189">
-        <v>0</v>
-      </c>
-      <c r="D189">
-        <v>92</v>
-      </c>
-      <c r="E189" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5">
-      <c r="A190" s="2">
-        <v>46185.98402777778</v>
-      </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-      <c r="C190">
-        <v>0</v>
-      </c>
-      <c r="D190">
-        <v>93</v>
-      </c>
-      <c r="E190" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5">
-      <c r="A191" s="2">
-        <v>46185.99444444444</v>
-      </c>
-      <c r="B191">
-        <v>0</v>
-      </c>
-      <c r="C191">
-        <v>0</v>
-      </c>
-      <c r="D191">
-        <v>94</v>
-      </c>
-      <c r="E191" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5">
-      <c r="A192" s="2">
-        <v>46186.00486111111</v>
-      </c>
-      <c r="B192">
-        <v>0</v>
-      </c>
-      <c r="C192">
-        <v>0</v>
-      </c>
-      <c r="D192">
-        <v>95</v>
-      </c>
-      <c r="E192" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5">
-      <c r="A193" s="2">
-        <v>46186.01527777778</v>
-      </c>
-      <c r="B193">
-        <v>0</v>
-      </c>
-      <c r="C193">
-        <v>0</v>
-      </c>
-      <c r="D193">
-        <v>96</v>
-      </c>
-      <c r="E193" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5">
-      <c r="A194" s="2">
-        <v>46186.02569444444</v>
-      </c>
-      <c r="B194">
-        <v>0</v>
-      </c>
-      <c r="C194">
-        <v>0</v>
-      </c>
-      <c r="D194">
-        <v>1</v>
-      </c>
-      <c r="E194" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5">
-      <c r="A195" s="2">
-        <v>46186.03611111111</v>
-      </c>
-      <c r="B195">
-        <v>0</v>
-      </c>
-      <c r="C195">
-        <v>0</v>
-      </c>
-      <c r="D195">
-        <v>2</v>
-      </c>
-      <c r="E195" t="s">
-        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="345">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>09.07.20261</t>
-  </si>
-  <si>
-    <t>09.07.20262</t>
-  </si>
-  <si>
-    <t>09.07.20263</t>
-  </si>
-  <si>
-    <t>09.07.20264</t>
-  </si>
-  <si>
-    <t>09.07.20265</t>
-  </si>
-  <si>
-    <t>09.07.20266</t>
-  </si>
-  <si>
-    <t>09.07.20267</t>
-  </si>
-  <si>
-    <t>09.07.20268</t>
-  </si>
-  <si>
-    <t>09.07.20269</t>
-  </si>
-  <si>
-    <t>09.07.202610</t>
-  </si>
-  <si>
-    <t>09.07.202611</t>
-  </si>
-  <si>
-    <t>09.07.202612</t>
-  </si>
-  <si>
-    <t>09.07.202613</t>
-  </si>
-  <si>
-    <t>09.07.202614</t>
-  </si>
-  <si>
-    <t>09.07.202615</t>
-  </si>
-  <si>
-    <t>09.07.202616</t>
-  </si>
-  <si>
-    <t>09.07.202617</t>
-  </si>
-  <si>
-    <t>09.07.202618</t>
-  </si>
-  <si>
-    <t>09.07.202619</t>
-  </si>
-  <si>
-    <t>09.07.202620</t>
-  </si>
-  <si>
-    <t>09.07.202621</t>
-  </si>
-  <si>
-    <t>09.07.202622</t>
-  </si>
-  <si>
-    <t>09.07.202623</t>
-  </si>
-  <si>
-    <t>09.07.202624</t>
-  </si>
-  <si>
-    <t>09.07.202625</t>
-  </si>
-  <si>
-    <t>09.07.202626</t>
-  </si>
-  <si>
-    <t>09.07.202627</t>
-  </si>
-  <si>
-    <t>09.07.202628</t>
-  </si>
-  <si>
-    <t>09.07.202629</t>
-  </si>
-  <si>
-    <t>09.07.202630</t>
-  </si>
-  <si>
-    <t>09.07.202631</t>
-  </si>
-  <si>
-    <t>09.07.202632</t>
-  </si>
-  <si>
-    <t>09.07.202633</t>
-  </si>
-  <si>
-    <t>09.07.202634</t>
-  </si>
-  <si>
-    <t>09.07.202635</t>
-  </si>
-  <si>
-    <t>09.07.202636</t>
-  </si>
-  <si>
-    <t>09.07.202637</t>
-  </si>
-  <si>
-    <t>09.07.202638</t>
-  </si>
-  <si>
-    <t>09.07.202639</t>
-  </si>
-  <si>
-    <t>09.07.202640</t>
-  </si>
-  <si>
-    <t>09.07.202641</t>
-  </si>
-  <si>
-    <t>09.07.202642</t>
-  </si>
-  <si>
-    <t>09.07.202643</t>
-  </si>
-  <si>
-    <t>09.07.202644</t>
-  </si>
-  <si>
-    <t>09.07.202645</t>
-  </si>
-  <si>
-    <t>09.07.202646</t>
-  </si>
-  <si>
-    <t>09.07.202647</t>
-  </si>
-  <si>
-    <t>09.07.202648</t>
-  </si>
-  <si>
-    <t>09.07.202649</t>
-  </si>
-  <si>
-    <t>09.07.202650</t>
-  </si>
-  <si>
-    <t>09.07.202651</t>
-  </si>
-  <si>
-    <t>09.07.202652</t>
-  </si>
-  <si>
-    <t>09.07.202653</t>
-  </si>
-  <si>
-    <t>09.07.202654</t>
-  </si>
-  <si>
-    <t>09.07.202655</t>
-  </si>
-  <si>
-    <t>09.07.202656</t>
-  </si>
-  <si>
-    <t>09.07.202657</t>
-  </si>
-  <si>
-    <t>09.07.202658</t>
-  </si>
-  <si>
-    <t>09.07.202659</t>
-  </si>
-  <si>
-    <t>09.07.202660</t>
-  </si>
-  <si>
-    <t>09.07.202661</t>
-  </si>
-  <si>
-    <t>09.07.202662</t>
-  </si>
-  <si>
-    <t>09.07.202663</t>
-  </si>
-  <si>
-    <t>09.07.202664</t>
-  </si>
-  <si>
-    <t>09.07.202665</t>
-  </si>
-  <si>
-    <t>09.07.202666</t>
-  </si>
-  <si>
-    <t>09.07.202667</t>
-  </si>
-  <si>
-    <t>09.07.202668</t>
-  </si>
-  <si>
-    <t>09.07.202669</t>
-  </si>
-  <si>
-    <t>09.07.202670</t>
-  </si>
-  <si>
-    <t>09.07.202671</t>
-  </si>
-  <si>
-    <t>09.07.202672</t>
-  </si>
-  <si>
-    <t>09.07.202673</t>
-  </si>
-  <si>
-    <t>09.07.202674</t>
-  </si>
-  <si>
-    <t>09.07.202675</t>
-  </si>
-  <si>
-    <t>09.07.202676</t>
-  </si>
-  <si>
-    <t>09.07.202677</t>
-  </si>
-  <si>
-    <t>09.07.202678</t>
-  </si>
-  <si>
-    <t>09.07.202679</t>
-  </si>
-  <si>
-    <t>09.07.202680</t>
-  </si>
-  <si>
-    <t>09.07.202681</t>
-  </si>
-  <si>
-    <t>09.07.202682</t>
-  </si>
-  <si>
-    <t>09.07.202683</t>
-  </si>
-  <si>
-    <t>09.07.202684</t>
-  </si>
-  <si>
-    <t>09.07.202685</t>
-  </si>
-  <si>
-    <t>09.07.202686</t>
-  </si>
-  <si>
-    <t>09.07.202687</t>
-  </si>
-  <si>
-    <t>09.07.202688</t>
-  </si>
-  <si>
-    <t>09.07.202689</t>
-  </si>
-  <si>
-    <t>09.07.202690</t>
-  </si>
-  <si>
-    <t>09.07.202691</t>
-  </si>
-  <si>
-    <t>09.07.202692</t>
-  </si>
-  <si>
-    <t>09.07.202693</t>
-  </si>
-  <si>
-    <t>09.07.202694</t>
-  </si>
-  <si>
-    <t>09.07.202695</t>
-  </si>
-  <si>
-    <t>09.07.202696</t>
-  </si>
-  <si>
     <t>10.07.20261</t>
   </si>
   <si>
@@ -449,6 +161,894 @@
   </si>
   <si>
     <t>10.07.202644</t>
+  </si>
+  <si>
+    <t>10.07.202645</t>
+  </si>
+  <si>
+    <t>10.07.202646</t>
+  </si>
+  <si>
+    <t>10.07.202647</t>
+  </si>
+  <si>
+    <t>10.07.202648</t>
+  </si>
+  <si>
+    <t>10.07.202649</t>
+  </si>
+  <si>
+    <t>10.07.202650</t>
+  </si>
+  <si>
+    <t>10.07.202651</t>
+  </si>
+  <si>
+    <t>10.07.202652</t>
+  </si>
+  <si>
+    <t>10.07.202653</t>
+  </si>
+  <si>
+    <t>10.07.202654</t>
+  </si>
+  <si>
+    <t>10.07.202655</t>
+  </si>
+  <si>
+    <t>10.07.202656</t>
+  </si>
+  <si>
+    <t>10.07.202657</t>
+  </si>
+  <si>
+    <t>10.07.202658</t>
+  </si>
+  <si>
+    <t>10.07.202659</t>
+  </si>
+  <si>
+    <t>10.07.202660</t>
+  </si>
+  <si>
+    <t>10.07.202661</t>
+  </si>
+  <si>
+    <t>10.07.202662</t>
+  </si>
+  <si>
+    <t>10.07.202663</t>
+  </si>
+  <si>
+    <t>10.07.202664</t>
+  </si>
+  <si>
+    <t>10.07.202665</t>
+  </si>
+  <si>
+    <t>10.07.202666</t>
+  </si>
+  <si>
+    <t>10.07.202667</t>
+  </si>
+  <si>
+    <t>10.07.202668</t>
+  </si>
+  <si>
+    <t>10.07.202669</t>
+  </si>
+  <si>
+    <t>10.07.202670</t>
+  </si>
+  <si>
+    <t>10.07.202671</t>
+  </si>
+  <si>
+    <t>10.07.202672</t>
+  </si>
+  <si>
+    <t>10.07.202673</t>
+  </si>
+  <si>
+    <t>10.07.202674</t>
+  </si>
+  <si>
+    <t>10.07.202675</t>
+  </si>
+  <si>
+    <t>10.07.202676</t>
+  </si>
+  <si>
+    <t>10.07.202677</t>
+  </si>
+  <si>
+    <t>10.07.202678</t>
+  </si>
+  <si>
+    <t>10.07.202679</t>
+  </si>
+  <si>
+    <t>10.07.202680</t>
+  </si>
+  <si>
+    <t>10.07.202681</t>
+  </si>
+  <si>
+    <t>10.07.202682</t>
+  </si>
+  <si>
+    <t>10.07.202683</t>
+  </si>
+  <si>
+    <t>10.07.202684</t>
+  </si>
+  <si>
+    <t>10.07.202685</t>
+  </si>
+  <si>
+    <t>10.07.202686</t>
+  </si>
+  <si>
+    <t>10.07.202687</t>
+  </si>
+  <si>
+    <t>10.07.202688</t>
+  </si>
+  <si>
+    <t>10.07.202689</t>
+  </si>
+  <si>
+    <t>10.07.202690</t>
+  </si>
+  <si>
+    <t>10.07.202691</t>
+  </si>
+  <si>
+    <t>10.07.202692</t>
+  </si>
+  <si>
+    <t>10.07.202693</t>
+  </si>
+  <si>
+    <t>10.07.202694</t>
+  </si>
+  <si>
+    <t>10.07.202695</t>
+  </si>
+  <si>
+    <t>10.07.202696</t>
+  </si>
+  <si>
+    <t>11.07.20261</t>
+  </si>
+  <si>
+    <t>11.07.20262</t>
+  </si>
+  <si>
+    <t>11.07.20263</t>
+  </si>
+  <si>
+    <t>11.07.20264</t>
+  </si>
+  <si>
+    <t>11.07.20265</t>
+  </si>
+  <si>
+    <t>11.07.20266</t>
+  </si>
+  <si>
+    <t>11.07.20267</t>
+  </si>
+  <si>
+    <t>11.07.20268</t>
+  </si>
+  <si>
+    <t>11.07.20269</t>
+  </si>
+  <si>
+    <t>11.07.202610</t>
+  </si>
+  <si>
+    <t>11.07.202611</t>
+  </si>
+  <si>
+    <t>11.07.202612</t>
+  </si>
+  <si>
+    <t>11.07.202613</t>
+  </si>
+  <si>
+    <t>11.07.202614</t>
+  </si>
+  <si>
+    <t>11.07.202615</t>
+  </si>
+  <si>
+    <t>11.07.202616</t>
+  </si>
+  <si>
+    <t>11.07.202617</t>
+  </si>
+  <si>
+    <t>11.07.202618</t>
+  </si>
+  <si>
+    <t>11.07.202619</t>
+  </si>
+  <si>
+    <t>11.07.202620</t>
+  </si>
+  <si>
+    <t>11.07.202621</t>
+  </si>
+  <si>
+    <t>11.07.202622</t>
+  </si>
+  <si>
+    <t>11.07.202623</t>
+  </si>
+  <si>
+    <t>11.07.202624</t>
+  </si>
+  <si>
+    <t>11.07.202625</t>
+  </si>
+  <si>
+    <t>11.07.202626</t>
+  </si>
+  <si>
+    <t>11.07.202627</t>
+  </si>
+  <si>
+    <t>11.07.202628</t>
+  </si>
+  <si>
+    <t>11.07.202629</t>
+  </si>
+  <si>
+    <t>11.07.202630</t>
+  </si>
+  <si>
+    <t>11.07.202631</t>
+  </si>
+  <si>
+    <t>11.07.202632</t>
+  </si>
+  <si>
+    <t>11.07.202633</t>
+  </si>
+  <si>
+    <t>11.07.202634</t>
+  </si>
+  <si>
+    <t>11.07.202635</t>
+  </si>
+  <si>
+    <t>11.07.202636</t>
+  </si>
+  <si>
+    <t>11.07.202637</t>
+  </si>
+  <si>
+    <t>11.07.202638</t>
+  </si>
+  <si>
+    <t>11.07.202639</t>
+  </si>
+  <si>
+    <t>11.07.202640</t>
+  </si>
+  <si>
+    <t>11.07.202641</t>
+  </si>
+  <si>
+    <t>11.07.202642</t>
+  </si>
+  <si>
+    <t>11.07.202643</t>
+  </si>
+  <si>
+    <t>11.07.202644</t>
+  </si>
+  <si>
+    <t>11.07.202645</t>
+  </si>
+  <si>
+    <t>11.07.202646</t>
+  </si>
+  <si>
+    <t>11.07.202647</t>
+  </si>
+  <si>
+    <t>11.07.202648</t>
+  </si>
+  <si>
+    <t>11.07.202649</t>
+  </si>
+  <si>
+    <t>11.07.202650</t>
+  </si>
+  <si>
+    <t>11.07.202651</t>
+  </si>
+  <si>
+    <t>11.07.202652</t>
+  </si>
+  <si>
+    <t>11.07.202653</t>
+  </si>
+  <si>
+    <t>11.07.202654</t>
+  </si>
+  <si>
+    <t>11.07.202655</t>
+  </si>
+  <si>
+    <t>11.07.202656</t>
+  </si>
+  <si>
+    <t>11.07.202657</t>
+  </si>
+  <si>
+    <t>11.07.202658</t>
+  </si>
+  <si>
+    <t>11.07.202659</t>
+  </si>
+  <si>
+    <t>11.07.202660</t>
+  </si>
+  <si>
+    <t>11.07.202661</t>
+  </si>
+  <si>
+    <t>11.07.202662</t>
+  </si>
+  <si>
+    <t>11.07.202663</t>
+  </si>
+  <si>
+    <t>11.07.202664</t>
+  </si>
+  <si>
+    <t>11.07.202665</t>
+  </si>
+  <si>
+    <t>11.07.202666</t>
+  </si>
+  <si>
+    <t>11.07.202667</t>
+  </si>
+  <si>
+    <t>11.07.202668</t>
+  </si>
+  <si>
+    <t>11.07.202669</t>
+  </si>
+  <si>
+    <t>11.07.202670</t>
+  </si>
+  <si>
+    <t>11.07.202671</t>
+  </si>
+  <si>
+    <t>11.07.202672</t>
+  </si>
+  <si>
+    <t>11.07.202673</t>
+  </si>
+  <si>
+    <t>11.07.202674</t>
+  </si>
+  <si>
+    <t>11.07.202675</t>
+  </si>
+  <si>
+    <t>11.07.202676</t>
+  </si>
+  <si>
+    <t>11.07.202677</t>
+  </si>
+  <si>
+    <t>11.07.202678</t>
+  </si>
+  <si>
+    <t>11.07.202679</t>
+  </si>
+  <si>
+    <t>11.07.202680</t>
+  </si>
+  <si>
+    <t>11.07.202681</t>
+  </si>
+  <si>
+    <t>11.07.202682</t>
+  </si>
+  <si>
+    <t>11.07.202683</t>
+  </si>
+  <si>
+    <t>11.07.202684</t>
+  </si>
+  <si>
+    <t>11.07.202685</t>
+  </si>
+  <si>
+    <t>11.07.202686</t>
+  </si>
+  <si>
+    <t>11.07.202687</t>
+  </si>
+  <si>
+    <t>11.07.202688</t>
+  </si>
+  <si>
+    <t>11.07.202689</t>
+  </si>
+  <si>
+    <t>11.07.202690</t>
+  </si>
+  <si>
+    <t>11.07.202691</t>
+  </si>
+  <si>
+    <t>11.07.202692</t>
+  </si>
+  <si>
+    <t>11.07.202693</t>
+  </si>
+  <si>
+    <t>11.07.202694</t>
+  </si>
+  <si>
+    <t>11.07.202695</t>
+  </si>
+  <si>
+    <t>11.07.202696</t>
+  </si>
+  <si>
+    <t>12.07.20261</t>
+  </si>
+  <si>
+    <t>12.07.20262</t>
+  </si>
+  <si>
+    <t>12.07.20263</t>
+  </si>
+  <si>
+    <t>12.07.20264</t>
+  </si>
+  <si>
+    <t>12.07.20265</t>
+  </si>
+  <si>
+    <t>12.07.20266</t>
+  </si>
+  <si>
+    <t>12.07.20267</t>
+  </si>
+  <si>
+    <t>12.07.20268</t>
+  </si>
+  <si>
+    <t>12.07.20269</t>
+  </si>
+  <si>
+    <t>12.07.202610</t>
+  </si>
+  <si>
+    <t>12.07.202611</t>
+  </si>
+  <si>
+    <t>12.07.202612</t>
+  </si>
+  <si>
+    <t>12.07.202613</t>
+  </si>
+  <si>
+    <t>12.07.202614</t>
+  </si>
+  <si>
+    <t>12.07.202615</t>
+  </si>
+  <si>
+    <t>12.07.202616</t>
+  </si>
+  <si>
+    <t>12.07.202617</t>
+  </si>
+  <si>
+    <t>12.07.202618</t>
+  </si>
+  <si>
+    <t>12.07.202619</t>
+  </si>
+  <si>
+    <t>12.07.202620</t>
+  </si>
+  <si>
+    <t>12.07.202621</t>
+  </si>
+  <si>
+    <t>12.07.202622</t>
+  </si>
+  <si>
+    <t>12.07.202623</t>
+  </si>
+  <si>
+    <t>12.07.202624</t>
+  </si>
+  <si>
+    <t>12.07.202625</t>
+  </si>
+  <si>
+    <t>12.07.202626</t>
+  </si>
+  <si>
+    <t>12.07.202627</t>
+  </si>
+  <si>
+    <t>12.07.202628</t>
+  </si>
+  <si>
+    <t>12.07.202629</t>
+  </si>
+  <si>
+    <t>12.07.202630</t>
+  </si>
+  <si>
+    <t>12.07.202631</t>
+  </si>
+  <si>
+    <t>12.07.202632</t>
+  </si>
+  <si>
+    <t>12.07.202633</t>
+  </si>
+  <si>
+    <t>12.07.202634</t>
+  </si>
+  <si>
+    <t>12.07.202635</t>
+  </si>
+  <si>
+    <t>12.07.202636</t>
+  </si>
+  <si>
+    <t>12.07.202637</t>
+  </si>
+  <si>
+    <t>12.07.202638</t>
+  </si>
+  <si>
+    <t>12.07.202639</t>
+  </si>
+  <si>
+    <t>12.07.202640</t>
+  </si>
+  <si>
+    <t>12.07.202641</t>
+  </si>
+  <si>
+    <t>12.07.202642</t>
+  </si>
+  <si>
+    <t>12.07.202643</t>
+  </si>
+  <si>
+    <t>12.07.202644</t>
+  </si>
+  <si>
+    <t>12.07.202645</t>
+  </si>
+  <si>
+    <t>12.07.202646</t>
+  </si>
+  <si>
+    <t>12.07.202647</t>
+  </si>
+  <si>
+    <t>12.07.202648</t>
+  </si>
+  <si>
+    <t>12.07.202649</t>
+  </si>
+  <si>
+    <t>12.07.202650</t>
+  </si>
+  <si>
+    <t>12.07.202651</t>
+  </si>
+  <si>
+    <t>12.07.202652</t>
+  </si>
+  <si>
+    <t>12.07.202653</t>
+  </si>
+  <si>
+    <t>12.07.202654</t>
+  </si>
+  <si>
+    <t>12.07.202655</t>
+  </si>
+  <si>
+    <t>12.07.202656</t>
+  </si>
+  <si>
+    <t>12.07.202657</t>
+  </si>
+  <si>
+    <t>12.07.202658</t>
+  </si>
+  <si>
+    <t>12.07.202659</t>
+  </si>
+  <si>
+    <t>12.07.202660</t>
+  </si>
+  <si>
+    <t>12.07.202661</t>
+  </si>
+  <si>
+    <t>12.07.202662</t>
+  </si>
+  <si>
+    <t>12.07.202663</t>
+  </si>
+  <si>
+    <t>12.07.202664</t>
+  </si>
+  <si>
+    <t>12.07.202665</t>
+  </si>
+  <si>
+    <t>12.07.202666</t>
+  </si>
+  <si>
+    <t>12.07.202667</t>
+  </si>
+  <si>
+    <t>12.07.202668</t>
+  </si>
+  <si>
+    <t>12.07.202669</t>
+  </si>
+  <si>
+    <t>12.07.202670</t>
+  </si>
+  <si>
+    <t>12.07.202671</t>
+  </si>
+  <si>
+    <t>12.07.202672</t>
+  </si>
+  <si>
+    <t>12.07.202673</t>
+  </si>
+  <si>
+    <t>12.07.202674</t>
+  </si>
+  <si>
+    <t>12.07.202675</t>
+  </si>
+  <si>
+    <t>12.07.202676</t>
+  </si>
+  <si>
+    <t>12.07.202677</t>
+  </si>
+  <si>
+    <t>12.07.202678</t>
+  </si>
+  <si>
+    <t>12.07.202679</t>
+  </si>
+  <si>
+    <t>12.07.202680</t>
+  </si>
+  <si>
+    <t>12.07.202681</t>
+  </si>
+  <si>
+    <t>12.07.202682</t>
+  </si>
+  <si>
+    <t>12.07.202683</t>
+  </si>
+  <si>
+    <t>12.07.202684</t>
+  </si>
+  <si>
+    <t>12.07.202685</t>
+  </si>
+  <si>
+    <t>12.07.202686</t>
+  </si>
+  <si>
+    <t>12.07.202687</t>
+  </si>
+  <si>
+    <t>12.07.202688</t>
+  </si>
+  <si>
+    <t>12.07.202689</t>
+  </si>
+  <si>
+    <t>12.07.202690</t>
+  </si>
+  <si>
+    <t>12.07.202691</t>
+  </si>
+  <si>
+    <t>12.07.202692</t>
+  </si>
+  <si>
+    <t>12.07.202693</t>
+  </si>
+  <si>
+    <t>12.07.202694</t>
+  </si>
+  <si>
+    <t>12.07.202695</t>
+  </si>
+  <si>
+    <t>12.07.202696</t>
+  </si>
+  <si>
+    <t>13.07.20261</t>
+  </si>
+  <si>
+    <t>13.07.20262</t>
+  </si>
+  <si>
+    <t>13.07.20263</t>
+  </si>
+  <si>
+    <t>13.07.20264</t>
+  </si>
+  <si>
+    <t>13.07.20265</t>
+  </si>
+  <si>
+    <t>13.07.20266</t>
+  </si>
+  <si>
+    <t>13.07.20267</t>
+  </si>
+  <si>
+    <t>13.07.20268</t>
+  </si>
+  <si>
+    <t>13.07.20269</t>
+  </si>
+  <si>
+    <t>13.07.202610</t>
+  </si>
+  <si>
+    <t>13.07.202611</t>
+  </si>
+  <si>
+    <t>13.07.202612</t>
+  </si>
+  <si>
+    <t>13.07.202613</t>
+  </si>
+  <si>
+    <t>13.07.202614</t>
+  </si>
+  <si>
+    <t>13.07.202615</t>
+  </si>
+  <si>
+    <t>13.07.202616</t>
+  </si>
+  <si>
+    <t>13.07.202617</t>
+  </si>
+  <si>
+    <t>13.07.202618</t>
+  </si>
+  <si>
+    <t>13.07.202619</t>
+  </si>
+  <si>
+    <t>13.07.202620</t>
+  </si>
+  <si>
+    <t>13.07.202621</t>
+  </si>
+  <si>
+    <t>13.07.202622</t>
+  </si>
+  <si>
+    <t>13.07.202623</t>
+  </si>
+  <si>
+    <t>13.07.202624</t>
+  </si>
+  <si>
+    <t>13.07.202625</t>
+  </si>
+  <si>
+    <t>13.07.202626</t>
+  </si>
+  <si>
+    <t>13.07.202627</t>
+  </si>
+  <si>
+    <t>13.07.202628</t>
+  </si>
+  <si>
+    <t>13.07.202629</t>
+  </si>
+  <si>
+    <t>13.07.202630</t>
+  </si>
+  <si>
+    <t>13.07.202631</t>
+  </si>
+  <si>
+    <t>13.07.202632</t>
+  </si>
+  <si>
+    <t>13.07.202633</t>
+  </si>
+  <si>
+    <t>13.07.202634</t>
+  </si>
+  <si>
+    <t>13.07.202635</t>
+  </si>
+  <si>
+    <t>13.07.202636</t>
+  </si>
+  <si>
+    <t>13.07.202637</t>
+  </si>
+  <si>
+    <t>13.07.202638</t>
+  </si>
+  <si>
+    <t>13.07.202639</t>
+  </si>
+  <si>
+    <t>13.07.202640</t>
+  </si>
+  <si>
+    <t>13.07.202641</t>
+  </si>
+  <si>
+    <t>13.07.202642</t>
+  </si>
+  <si>
+    <t>13.07.202643</t>
+  </si>
+  <si>
+    <t>13.07.202644</t>
+  </si>
+  <si>
+    <t>13.07.202645</t>
+  </si>
+  <si>
+    <t>13.07.202646</t>
+  </si>
+  <si>
+    <t>13.07.202647</t>
+  </si>
+  <si>
+    <t>13.07.202648</t>
+  </si>
+  <si>
+    <t>13.07.202649</t>
+  </si>
+  <si>
+    <t>13.07.202650</t>
+  </si>
+  <si>
+    <t>13.07.202651</t>
+  </si>
+  <si>
+    <t>13.07.202652</t>
   </si>
 </sst>
 </file>
@@ -810,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -832,13 +1432,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>8.412000000000001</v>
       </c>
       <c r="C2">
-        <v>3.444</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -849,13 +1449,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46212.01041666666</v>
+        <v>46213.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.381</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>3.206</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -866,13 +1466,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46212.02083333334</v>
+        <v>46213.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>6.57</v>
+        <v>2.876</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -883,13 +1483,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46212.03125</v>
+        <v>46213.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>1.251</v>
+        <v>22.423</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -900,13 +1500,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46212.04166666666</v>
+        <v>46213.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>17.605</v>
+        <v>31.319</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -917,13 +1517,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46212.05208333334</v>
+        <v>46213.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>14.393</v>
+        <v>9.878</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -934,13 +1534,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46212.0625</v>
+        <v>46213.0625</v>
       </c>
       <c r="B8">
-        <v>2.682</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>5.821</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -951,13 +1551,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46212.07291666666</v>
+        <v>46213.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>9.449999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -968,13 +1568,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46212.08333333334</v>
+        <v>46213.08333333334</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>11.467</v>
+        <v>10.496</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -985,13 +1585,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46212.09375</v>
+        <v>46213.09375</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11">
-        <v>20.204</v>
+        <v>4.144</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1002,13 +1602,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46212.10416666666</v>
+        <v>46213.10416666666</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12">
-        <v>22.167</v>
+        <v>25.946</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1019,13 +1619,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46212.11458333334</v>
+        <v>46213.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>7.316</v>
+        <v>21.014</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1036,13 +1636,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46212.125</v>
+        <v>46213.125</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14">
-        <v>5.243</v>
+        <v>3.613</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1053,13 +1653,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46212.13541666666</v>
+        <v>46213.13541666666</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>13.168</v>
+        <v>10.443</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1070,13 +1670,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46212.14583333334</v>
+        <v>46213.14583333334</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>1.269</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1087,13 +1687,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46212.15625</v>
+        <v>46213.15625</v>
       </c>
       <c r="B17">
-        <v>1.395</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>13.642</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1104,13 +1704,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46212.16666666666</v>
+        <v>46213.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>21.022</v>
+        <v>2.753</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1121,13 +1721,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46212.17708333334</v>
+        <v>46213.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>10.926</v>
       </c>
       <c r="C19">
-        <v>26.191</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1138,13 +1738,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46212.1875</v>
+        <v>46213.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>12.94</v>
       </c>
       <c r="C20">
-        <v>3.085</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1155,10 +1755,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46212.19791666666</v>
+        <v>46213.19791666666</v>
       </c>
       <c r="B21">
-        <v>9.928000000000001</v>
+        <v>23.476</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1172,13 +1772,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46212.20833333334</v>
+        <v>46213.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>17.724</v>
       </c>
       <c r="C22">
-        <v>6.673</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1189,10 +1789,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46212.21875</v>
+        <v>46213.21875</v>
       </c>
       <c r="B23">
-        <v>9.56</v>
+        <v>12.589</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1206,13 +1806,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46212.22916666666</v>
+        <v>46213.22916666666</v>
       </c>
       <c r="B24">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>11.99</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1223,13 +1823,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46212.23958333334</v>
+        <v>46213.23958333334</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>7.971</v>
+        <v>4.409</v>
       </c>
       <c r="D25">
         <v>24</v>
@@ -1240,13 +1840,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46212.25</v>
+        <v>46213.25</v>
       </c>
       <c r="B26">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>3.863</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1257,13 +1857,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46212.26041666666</v>
+        <v>46213.26041666666</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>3.046</v>
+        <v>14.781</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1274,13 +1874,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46212.27083333334</v>
+        <v>46213.27083333334</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>2.665</v>
+        <v>23.911</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1291,13 +1891,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46212.28125</v>
+        <v>46213.28125</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>7.649</v>
+        <v>20.543</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1308,13 +1908,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46212.29166666666</v>
+        <v>46213.29166666666</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>6.497</v>
+        <v>5.537</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1325,13 +1925,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46212.30208333334</v>
+        <v>46213.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>8.257</v>
+        <v>9.722</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1342,13 +1942,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46212.3125</v>
+        <v>46213.3125</v>
       </c>
       <c r="B32">
-        <v>1.095</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>28.735</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1359,13 +1959,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46212.32291666666</v>
+        <v>46213.32291666666</v>
       </c>
       <c r="B33">
-        <v>5.204</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>15.568</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1376,13 +1976,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46212.33333333334</v>
+        <v>46213.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>1.317</v>
       </c>
       <c r="C34">
-        <v>17.396</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1393,13 +1993,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46212.34375</v>
+        <v>46213.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>0.607</v>
       </c>
       <c r="C35">
-        <v>17.587</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1410,13 +2010,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46212.35416666666</v>
+        <v>46213.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>17.977</v>
       </c>
       <c r="C36">
-        <v>27.124</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1427,13 +2027,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46212.36458333334</v>
+        <v>46213.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>30.921</v>
+        <v>2.732</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1444,13 +2044,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46212.375</v>
+        <v>46213.375</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>16.927</v>
       </c>
       <c r="C38">
-        <v>18.284</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1461,13 +2061,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46212.38541666666</v>
+        <v>46213.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>31.589</v>
+        <v>32.053</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1478,13 +2078,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46212.39583333334</v>
+        <v>46213.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>27.937</v>
+        <v>4.695</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1495,13 +2095,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46212.40625</v>
+        <v>46213.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>30.73</v>
+        <v>10.008</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1512,10 +2112,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46212.41666666666</v>
+        <v>46213.41666666666</v>
       </c>
       <c r="B42">
-        <v>23.059</v>
+        <v>0.926</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1529,10 +2129,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46212.42708333334</v>
+        <v>46213.42708333334</v>
       </c>
       <c r="B43">
-        <v>19.147</v>
+        <v>5.194</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1546,13 +2146,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46212.4375</v>
+        <v>46213.4375</v>
       </c>
       <c r="B44">
-        <v>12.465</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>3.221</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1563,13 +2163,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46212.44791666666</v>
+        <v>46213.44791666666</v>
       </c>
       <c r="B45">
-        <v>12.806</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>8.423999999999999</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1580,13 +2180,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46212.45833333334</v>
+        <v>46213.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>3.818</v>
       </c>
       <c r="C46">
-        <v>0.901</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1597,10 +2197,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46212.46875</v>
+        <v>46213.46875</v>
       </c>
       <c r="B47">
-        <v>3.064</v>
+        <v>2.757</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -1614,10 +2214,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46212.47916666666</v>
+        <v>46213.47916666666</v>
       </c>
       <c r="B48">
-        <v>19.249</v>
+        <v>16.234</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -1631,10 +2231,10 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46212.48958333334</v>
+        <v>46213.48958333334</v>
       </c>
       <c r="B49">
-        <v>29.126</v>
+        <v>47.249</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1648,10 +2248,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46212.5</v>
+        <v>46213.5</v>
       </c>
       <c r="B50">
-        <v>30.644</v>
+        <v>3.015</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -1665,10 +2265,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46212.51041666666</v>
+        <v>46213.51041666666</v>
       </c>
       <c r="B51">
-        <v>43.974</v>
+        <v>30.874</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1682,10 +2282,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46212.52083333334</v>
+        <v>46213.52083333334</v>
       </c>
       <c r="B52">
-        <v>71.923</v>
+        <v>21.977</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -1699,10 +2299,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46212.53125</v>
+        <v>46213.53125</v>
       </c>
       <c r="B53">
-        <v>25.491</v>
+        <v>21.194</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1716,13 +2316,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46212.54166666666</v>
+        <v>46213.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>52.736</v>
       </c>
       <c r="C54">
-        <v>16.029</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1733,13 +2333,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46212.55208333334</v>
+        <v>46213.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>65.279</v>
       </c>
       <c r="C55">
-        <v>23.519</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1750,10 +2350,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46212.5625</v>
+        <v>46213.5625</v>
       </c>
       <c r="B56">
-        <v>4.474</v>
+        <v>46.78</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1767,10 +2367,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46212.57291666666</v>
+        <v>46213.57291666666</v>
       </c>
       <c r="B57">
-        <v>27.742</v>
+        <v>49.093</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -1784,10 +2384,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46212.58333333334</v>
+        <v>46213.58333333334</v>
       </c>
       <c r="B58">
-        <v>2.636</v>
+        <v>79.36</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -1801,10 +2401,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46212.59375</v>
+        <v>46213.59375</v>
       </c>
       <c r="B59">
-        <v>26.397</v>
+        <v>32.641</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -1818,10 +2418,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46212.60416666666</v>
+        <v>46213.60416666666</v>
       </c>
       <c r="B60">
-        <v>9.551</v>
+        <v>45.241</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -1835,10 +2435,10 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46212.61458333334</v>
+        <v>46213.61458333334</v>
       </c>
       <c r="B61">
-        <v>2.572</v>
+        <v>56.052</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -1852,10 +2452,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46212.625</v>
+        <v>46213.625</v>
       </c>
       <c r="B62">
-        <v>8.109</v>
+        <v>29.713</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -1869,13 +2469,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46212.63541666666</v>
+        <v>46213.63541666666</v>
       </c>
       <c r="B63">
         <v>0</v>
       </c>
       <c r="C63">
-        <v>8.271000000000001</v>
+        <v>4.703</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1886,13 +2486,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46212.64583333334</v>
+        <v>46213.64583333334</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>6.028</v>
+        <v>7.178</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -1903,13 +2503,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46212.65625</v>
+        <v>46213.65625</v>
       </c>
       <c r="B65">
-        <v>13.503</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -1920,13 +2520,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46212.66666666666</v>
+        <v>46213.66666666666</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>0.835</v>
+        <v>2.352</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -1937,13 +2537,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46212.67708333334</v>
+        <v>46213.67708333334</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>13.566</v>
+        <v>33.529</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1954,13 +2554,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46212.6875</v>
+        <v>46213.6875</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
       <c r="C68">
-        <v>2.64</v>
+        <v>32.359</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -1971,13 +2571,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46212.69791666666</v>
+        <v>46213.69791666666</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
       <c r="C69">
-        <v>23.775</v>
+        <v>50.811</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -1988,13 +2588,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46212.70833333334</v>
+        <v>46213.70833333334</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>29.209</v>
+        <v>30.381</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2005,13 +2605,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46212.71875</v>
+        <v>46213.71875</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
       <c r="C71">
-        <v>13.39</v>
+        <v>6.692</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2022,13 +2622,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46212.72916666666</v>
+        <v>46213.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>0.452</v>
       </c>
       <c r="C72">
-        <v>23.18</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2039,13 +2639,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46212.73958333334</v>
+        <v>46213.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>15.085</v>
       </c>
       <c r="C73">
-        <v>0.555</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2056,13 +2656,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46212.75</v>
+        <v>46213.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>4.391</v>
       </c>
       <c r="C74">
-        <v>35.193</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2073,13 +2673,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46212.76041666666</v>
+        <v>46213.76041666666</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>20.956</v>
+        <v>0.78</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2090,13 +2690,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46212.77083333334</v>
+        <v>46213.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>4.144</v>
       </c>
       <c r="C76">
-        <v>3.221</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2107,13 +2707,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46212.78125</v>
+        <v>46213.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>6.543</v>
+        <v>6.06</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2124,13 +2724,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46212.79166666666</v>
+        <v>46213.79166666666</v>
       </c>
       <c r="B78">
-        <v>4.043</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2141,10 +2741,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46212.80208333334</v>
+        <v>46213.80208333334</v>
       </c>
       <c r="B79">
-        <v>8.217000000000001</v>
+        <v>5.084</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2158,10 +2758,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46212.8125</v>
+        <v>46213.8125</v>
       </c>
       <c r="B80">
-        <v>12.385</v>
+        <v>10.457</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2175,13 +2775,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46212.82291666666</v>
+        <v>46213.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>18.625</v>
       </c>
       <c r="C81">
-        <v>6.428</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2192,13 +2792,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46212.83333333334</v>
+        <v>46213.83333333334</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>13.387</v>
       </c>
       <c r="C82">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2209,13 +2809,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46212.84375</v>
+        <v>46213.84375</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>2.222</v>
       </c>
       <c r="C83">
-        <v>8.657999999999999</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2226,13 +2826,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46212.85416666666</v>
+        <v>46213.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>17.133</v>
+        <v>1.351</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2243,13 +2843,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46212.86458333334</v>
+        <v>46213.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>55.247</v>
+        <v>4.021</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2260,13 +2860,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46212.875</v>
+        <v>46213.875</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>1.857</v>
       </c>
       <c r="C86">
-        <v>40.036</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2277,13 +2877,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46212.88541666666</v>
+        <v>46213.88541666666</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>1.764</v>
       </c>
       <c r="C87">
-        <v>8.561999999999999</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2294,10 +2894,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46212.89583333334</v>
+        <v>46213.89583333334</v>
       </c>
       <c r="B88">
-        <v>2.958</v>
+        <v>12.662</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -2311,13 +2911,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46212.90625</v>
+        <v>46213.90625</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>5.311</v>
       </c>
       <c r="C89">
-        <v>6.763</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2328,10 +2928,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46212.91666666666</v>
+        <v>46213.91666666666</v>
       </c>
       <c r="B90">
-        <v>24.488</v>
+        <v>9.339</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2345,10 +2945,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46212.92708333334</v>
+        <v>46213.92708333334</v>
       </c>
       <c r="B91">
-        <v>46.889</v>
+        <v>18.998</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2362,10 +2962,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46212.9375</v>
+        <v>46213.9375</v>
       </c>
       <c r="B92">
-        <v>34.139</v>
+        <v>27.217</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2379,10 +2979,10 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46212.94791666666</v>
+        <v>46213.94791666666</v>
       </c>
       <c r="B93">
-        <v>26.132</v>
+        <v>12.98</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2396,10 +2996,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46212.95833333334</v>
+        <v>46213.95833333334</v>
       </c>
       <c r="B94">
-        <v>20.609</v>
+        <v>9.144</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2413,10 +3013,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46212.96875</v>
+        <v>46213.96875</v>
       </c>
       <c r="B95">
-        <v>20.119</v>
+        <v>7.036</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2430,10 +3030,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46212.97916666666</v>
+        <v>46213.97916666666</v>
       </c>
       <c r="B96">
-        <v>29.395</v>
+        <v>10.81</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2447,10 +3047,10 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46212.98958333334</v>
+        <v>46213.98958333334</v>
       </c>
       <c r="B97">
-        <v>42.703</v>
+        <v>11.457</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2464,10 +3064,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B98">
-        <v>8.412000000000001</v>
+        <v>15.514</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2481,13 +3081,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46213.01041666666</v>
+        <v>46214.01041666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>35.391</v>
       </c>
       <c r="C99">
-        <v>3.206</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2498,13 +3098,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46213.02083333334</v>
+        <v>46214.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>18.115</v>
       </c>
       <c r="C100">
-        <v>2.876</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2515,13 +3115,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46213.03125</v>
+        <v>46214.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>12.174</v>
       </c>
       <c r="C101">
-        <v>22.423</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2532,13 +3132,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46213.04166666666</v>
+        <v>46214.04166666666</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>15.554</v>
       </c>
       <c r="C102">
-        <v>31.319</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2549,13 +3149,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46213.05208333334</v>
+        <v>46214.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>31.098</v>
       </c>
       <c r="C103">
-        <v>9.878</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2566,13 +3166,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46213.0625</v>
+        <v>46214.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>35.578</v>
       </c>
       <c r="C104">
-        <v>5.821</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2583,13 +3183,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46213.07291666666</v>
+        <v>46214.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>30.048</v>
       </c>
       <c r="C105">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2600,13 +3200,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46213.08333333334</v>
+        <v>46214.08333333334</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>13.842</v>
       </c>
       <c r="C106">
-        <v>10.496</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2617,13 +3217,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46213.09375</v>
+        <v>46214.09375</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>7.941</v>
       </c>
       <c r="C107">
-        <v>4.144</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2634,13 +3234,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46213.10416666666</v>
+        <v>46214.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>14.419</v>
       </c>
       <c r="C108">
-        <v>25.946</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2651,13 +3251,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46213.11458333334</v>
+        <v>46214.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>6.965</v>
       </c>
       <c r="C109">
-        <v>21.014</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2668,13 +3268,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46213.125</v>
+        <v>46214.125</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>3.613</v>
+        <v>1.787</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2685,13 +3285,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46213.13541666666</v>
+        <v>46214.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>6.444</v>
       </c>
       <c r="C111">
-        <v>10.443</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2702,13 +3302,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46213.14583333334</v>
+        <v>46214.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>5.863</v>
       </c>
       <c r="C112">
-        <v>9.994999999999999</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2719,13 +3319,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46213.15625</v>
+        <v>46214.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>6.741</v>
       </c>
       <c r="C113">
-        <v>13.642</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2736,13 +3336,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46213.16666666666</v>
+        <v>46214.16666666666</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>12.313</v>
       </c>
       <c r="C114">
-        <v>2.753</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2753,13 +3353,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46213.17708333334</v>
+        <v>46214.17708333334</v>
       </c>
       <c r="B115">
-        <v>10.926</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>5.074</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2770,13 +3370,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46213.1875</v>
+        <v>46214.1875</v>
       </c>
       <c r="B116">
-        <v>12.94</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>8.507</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2787,13 +3387,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46213.19791666666</v>
+        <v>46214.19791666666</v>
       </c>
       <c r="B117">
-        <v>23.476</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2804,10 +3404,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46213.20833333334</v>
+        <v>46214.20833333334</v>
       </c>
       <c r="B118">
-        <v>17.724</v>
+        <v>14.279</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2821,10 +3421,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46213.21875</v>
+        <v>46214.21875</v>
       </c>
       <c r="B119">
-        <v>12.589</v>
+        <v>2.779</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2838,13 +3438,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46213.22916666666</v>
+        <v>46214.22916666666</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>13.194</v>
       </c>
       <c r="C120">
-        <v>11.99</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2855,13 +3455,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46213.23958333334</v>
+        <v>46214.23958333334</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121">
-        <v>4.409</v>
+        <v>2.061</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -2872,13 +3472,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46213.25</v>
+        <v>46214.25</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>2.109</v>
       </c>
       <c r="C122">
-        <v>3.863</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -2889,13 +3489,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46213.26041666666</v>
+        <v>46214.26041666666</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>7.674</v>
       </c>
       <c r="C123">
-        <v>14.781</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -2906,13 +3506,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46213.27083333334</v>
+        <v>46214.27083333334</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="C124">
-        <v>23.911</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2923,13 +3523,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46213.28125</v>
+        <v>46214.28125</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>7.008</v>
       </c>
       <c r="C125">
-        <v>20.543</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -2940,13 +3540,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46213.29166666666</v>
+        <v>46214.29166666666</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>12.347</v>
       </c>
       <c r="C126">
-        <v>5.537</v>
+        <v>0</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -2957,13 +3557,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46213.30208333334</v>
+        <v>46214.30208333334</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>22.548</v>
       </c>
       <c r="C127">
-        <v>9.722</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -2974,13 +3574,13 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46213.3125</v>
+        <v>46214.3125</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>24.686</v>
       </c>
       <c r="C128">
-        <v>28.735</v>
+        <v>0</v>
       </c>
       <c r="D128">
         <v>31</v>
@@ -2991,13 +3591,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46213.32291666666</v>
+        <v>46214.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>49.969</v>
       </c>
       <c r="C129">
-        <v>15.568</v>
+        <v>0</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3008,10 +3608,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46213.33333333334</v>
+        <v>46214.33333333334</v>
       </c>
       <c r="B130">
-        <v>1.317</v>
+        <v>22.743</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3025,10 +3625,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46213.34375</v>
+        <v>46214.34375</v>
       </c>
       <c r="B131">
-        <v>0.607</v>
+        <v>0.764</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3042,13 +3642,13 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46213.35416666666</v>
+        <v>46214.35416666666</v>
       </c>
       <c r="B132">
-        <v>17.977</v>
+        <v>0</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>6.254</v>
       </c>
       <c r="D132">
         <v>35</v>
@@ -3059,13 +3659,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46213.36458333334</v>
+        <v>46214.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>2.732</v>
+        <v>5.574</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3076,10 +3676,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46213.375</v>
+        <v>46214.375</v>
       </c>
       <c r="B134">
-        <v>16.927</v>
+        <v>5.843</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3093,13 +3693,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46213.38541666666</v>
+        <v>46214.38541666666</v>
       </c>
       <c r="B135">
         <v>0</v>
       </c>
       <c r="C135">
-        <v>32.053</v>
+        <v>1.935</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3110,13 +3710,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46213.39583333334</v>
+        <v>46214.39583333334</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136">
-        <v>4.695</v>
+        <v>8.394</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3127,13 +3727,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46213.40625</v>
+        <v>46214.40625</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>23.823</v>
       </c>
       <c r="C137">
-        <v>10.008</v>
+        <v>0</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3144,13 +3744,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46213.41666666666</v>
+        <v>46214.41666666666</v>
       </c>
       <c r="B138">
-        <v>0.926</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>5.591</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3161,13 +3761,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46213.42708333334</v>
+        <v>46214.42708333334</v>
       </c>
       <c r="B139">
-        <v>5.194</v>
+        <v>0</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>0.961</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3178,13 +3778,13 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46213.4375</v>
+        <v>46214.4375</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="C140">
-        <v>3.221</v>
+        <v>0</v>
       </c>
       <c r="D140">
         <v>43</v>
@@ -3195,19 +3795,3419 @@
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="2">
-        <v>46213.44791666666</v>
+        <v>46214.44791666666</v>
       </c>
       <c r="B141">
         <v>0</v>
       </c>
       <c r="C141">
-        <v>8.423999999999999</v>
+        <v>14.657</v>
       </c>
       <c r="D141">
         <v>44</v>
       </c>
       <c r="E141" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="2">
+        <v>46214.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>3.536</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>45</v>
+      </c>
+      <c r="E142" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="2">
+        <v>46214.46875</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <v>4.791</v>
+      </c>
+      <c r="D143">
+        <v>46</v>
+      </c>
+      <c r="E143" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="2">
+        <v>46214.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>9.362</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>47</v>
+      </c>
+      <c r="E144" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="2">
+        <v>46214.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>1.97</v>
+      </c>
+      <c r="D145">
+        <v>48</v>
+      </c>
+      <c r="E145" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="2">
+        <v>46214.5</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146">
+        <v>26.53</v>
+      </c>
+      <c r="D146">
+        <v>49</v>
+      </c>
+      <c r="E146" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="2">
+        <v>46214.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147">
+        <v>16.923</v>
+      </c>
+      <c r="D147">
+        <v>50</v>
+      </c>
+      <c r="E147" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="2">
+        <v>46214.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148">
+        <v>0.766</v>
+      </c>
+      <c r="D148">
+        <v>51</v>
+      </c>
+      <c r="E148" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="2">
+        <v>46214.53125</v>
+      </c>
+      <c r="B149">
+        <v>11.424</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+      <c r="D149">
+        <v>52</v>
+      </c>
+      <c r="E149" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="2">
+        <v>46214.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>13.926</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150">
+        <v>53</v>
+      </c>
+      <c r="E150" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="2">
+        <v>46214.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+      <c r="C151">
+        <v>2.898</v>
+      </c>
+      <c r="D151">
+        <v>54</v>
+      </c>
+      <c r="E151" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="2">
+        <v>46214.5625</v>
+      </c>
+      <c r="B152">
+        <v>0.46</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152">
+        <v>55</v>
+      </c>
+      <c r="E152" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="2">
+        <v>46214.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <v>6.458</v>
+      </c>
+      <c r="D153">
+        <v>56</v>
+      </c>
+      <c r="E153" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="2">
+        <v>46214.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+      <c r="C154">
+        <v>0.254</v>
+      </c>
+      <c r="D154">
+        <v>57</v>
+      </c>
+      <c r="E154" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="2">
+        <v>46214.59375</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+      <c r="C155">
+        <v>2.259</v>
+      </c>
+      <c r="D155">
+        <v>58</v>
+      </c>
+      <c r="E155" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="2">
+        <v>46214.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+      <c r="C156">
+        <v>5.998</v>
+      </c>
+      <c r="D156">
+        <v>59</v>
+      </c>
+      <c r="E156" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="2">
+        <v>46214.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>9.34</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157">
+        <v>60</v>
+      </c>
+      <c r="E157" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="2">
+        <v>46214.625</v>
+      </c>
+      <c r="B158">
+        <v>17.07</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158">
+        <v>61</v>
+      </c>
+      <c r="E158" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="2">
+        <v>46214.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>23.228</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+      <c r="D159">
+        <v>62</v>
+      </c>
+      <c r="E159" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="2">
+        <v>46214.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>6.597</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+      <c r="D160">
+        <v>63</v>
+      </c>
+      <c r="E160" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="2">
+        <v>46214.65625</v>
+      </c>
+      <c r="B161">
+        <v>9.863</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161">
+        <v>64</v>
+      </c>
+      <c r="E161" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="2">
+        <v>46214.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>16.748</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+      <c r="D162">
+        <v>65</v>
+      </c>
+      <c r="E162" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="2">
+        <v>46214.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>7.162</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <v>66</v>
+      </c>
+      <c r="E163" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="2">
+        <v>46214.6875</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+      <c r="C164">
+        <v>0.139</v>
+      </c>
+      <c r="D164">
+        <v>67</v>
+      </c>
+      <c r="E164" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="2">
+        <v>46214.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>14.849</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+      <c r="D165">
+        <v>68</v>
+      </c>
+      <c r="E165" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="2">
+        <v>46214.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>5.146</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166">
+        <v>69</v>
+      </c>
+      <c r="E166" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="2">
+        <v>46214.71875</v>
+      </c>
+      <c r="B167">
+        <v>30.433</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+      <c r="D167">
+        <v>70</v>
+      </c>
+      <c r="E167" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="2">
+        <v>46214.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>20.866</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168">
+        <v>71</v>
+      </c>
+      <c r="E168" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="2">
+        <v>46214.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+      <c r="C169">
+        <v>7.597</v>
+      </c>
+      <c r="D169">
+        <v>72</v>
+      </c>
+      <c r="E169" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="2">
+        <v>46214.75</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+      <c r="C170">
+        <v>6.211</v>
+      </c>
+      <c r="D170">
+        <v>73</v>
+      </c>
+      <c r="E170" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="2">
+        <v>46214.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+      <c r="C171">
+        <v>13.712</v>
+      </c>
+      <c r="D171">
+        <v>74</v>
+      </c>
+      <c r="E171" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="2">
+        <v>46214.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>0.626</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
+      <c r="D172">
+        <v>75</v>
+      </c>
+      <c r="E172" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="2">
+        <v>46214.78125</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>14.082</v>
+      </c>
+      <c r="D173">
+        <v>76</v>
+      </c>
+      <c r="E173" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="2">
+        <v>46214.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+      <c r="C174">
+        <v>37.438</v>
+      </c>
+      <c r="D174">
+        <v>77</v>
+      </c>
+      <c r="E174" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="2">
+        <v>46214.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+      <c r="C175">
+        <v>25.509</v>
+      </c>
+      <c r="D175">
+        <v>78</v>
+      </c>
+      <c r="E175" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="2">
+        <v>46214.8125</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+      <c r="C176">
+        <v>16.39</v>
+      </c>
+      <c r="D176">
+        <v>79</v>
+      </c>
+      <c r="E176" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="2">
+        <v>46214.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+      <c r="C177">
+        <v>10.827</v>
+      </c>
+      <c r="D177">
+        <v>80</v>
+      </c>
+      <c r="E177" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="2">
+        <v>46214.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+      <c r="C178">
+        <v>26.349</v>
+      </c>
+      <c r="D178">
+        <v>81</v>
+      </c>
+      <c r="E178" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="2">
+        <v>46214.84375</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+      <c r="C179">
+        <v>22.402</v>
+      </c>
+      <c r="D179">
+        <v>82</v>
+      </c>
+      <c r="E179" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="2">
+        <v>46214.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+      <c r="C180">
+        <v>21.076</v>
+      </c>
+      <c r="D180">
+        <v>83</v>
+      </c>
+      <c r="E180" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="2">
+        <v>46214.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+      <c r="C181">
+        <v>12.656</v>
+      </c>
+      <c r="D181">
+        <v>84</v>
+      </c>
+      <c r="E181" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="2">
+        <v>46214.875</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+      <c r="C182">
+        <v>18.054</v>
+      </c>
+      <c r="D182">
+        <v>85</v>
+      </c>
+      <c r="E182" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="2">
+        <v>46214.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+      <c r="C183">
+        <v>15.341</v>
+      </c>
+      <c r="D183">
+        <v>86</v>
+      </c>
+      <c r="E183" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="2">
+        <v>46214.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+      <c r="C184">
+        <v>27.195</v>
+      </c>
+      <c r="D184">
+        <v>87</v>
+      </c>
+      <c r="E184" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="2">
+        <v>46214.90625</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+      <c r="C185">
+        <v>35.56</v>
+      </c>
+      <c r="D185">
+        <v>88</v>
+      </c>
+      <c r="E185" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="2">
+        <v>46214.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+      <c r="C186">
+        <v>26.99</v>
+      </c>
+      <c r="D186">
+        <v>89</v>
+      </c>
+      <c r="E186" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="2">
+        <v>46214.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+      <c r="C187">
+        <v>4.94</v>
+      </c>
+      <c r="D187">
+        <v>90</v>
+      </c>
+      <c r="E187" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="2">
+        <v>46214.9375</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+      <c r="C188">
+        <v>7.057</v>
+      </c>
+      <c r="D188">
+        <v>91</v>
+      </c>
+      <c r="E188" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="2">
+        <v>46214.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+      <c r="C189">
+        <v>18.273</v>
+      </c>
+      <c r="D189">
+        <v>92</v>
+      </c>
+      <c r="E189" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2">
+        <v>46214.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+      <c r="C190">
+        <v>24.339</v>
+      </c>
+      <c r="D190">
+        <v>93</v>
+      </c>
+      <c r="E190" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2">
+        <v>46214.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+      <c r="C191">
+        <v>19.324</v>
+      </c>
+      <c r="D191">
+        <v>94</v>
+      </c>
+      <c r="E191" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2">
+        <v>46214.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+      <c r="C192">
+        <v>2.98</v>
+      </c>
+      <c r="D192">
+        <v>95</v>
+      </c>
+      <c r="E192" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2">
+        <v>46214.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>0</v>
+      </c>
+      <c r="C193">
+        <v>6.68</v>
+      </c>
+      <c r="D193">
+        <v>96</v>
+      </c>
+      <c r="E193" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46215</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+      <c r="C194">
+        <v>0.122</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46215.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>6.796</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46215.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>26.309</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46215.03125</v>
+      </c>
+      <c r="B197">
+        <v>12.013</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46215.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>17.281</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46215.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>15.625</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46215.0625</v>
+      </c>
+      <c r="B200">
+        <v>8.718</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46215.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>12.723</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46215.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>0.582</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46215.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>1.221</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46215.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>2.979</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46215.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+      <c r="C205">
+        <v>13.751</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46215.125</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206">
+        <v>15.03</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46215.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>30.768</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46215.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+      <c r="C208">
+        <v>17.512</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46215.15625</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+      <c r="C209">
+        <v>21.292</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46215.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+      <c r="C210">
+        <v>18.359</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46215.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>5.911</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46215.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>11.481</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46215.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>1.196</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46215.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>12.953</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46215.21875</v>
+      </c>
+      <c r="B215">
+        <v>19.541</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46215.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+      <c r="C216">
+        <v>4.571</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46215.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217">
+        <v>2.386</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46215.25</v>
+      </c>
+      <c r="B218">
+        <v>12.568</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46215.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>28.108</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46215.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>26.741</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46215.28125</v>
+      </c>
+      <c r="B221">
+        <v>27.702</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46215.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>24.03</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46215.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>23.337</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46215.3125</v>
+      </c>
+      <c r="B224">
+        <v>0.022</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46215.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>5.063</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46215.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+      <c r="C226">
+        <v>4.456</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46215.34375</v>
+      </c>
+      <c r="B227">
+        <v>1.187</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46215.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>5.02</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46215.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>9.589</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46215.375</v>
+      </c>
+      <c r="B230">
+        <v>15.514</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46215.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+      <c r="C231">
+        <v>3.685</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46215.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>11.665</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46215.40625</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>7.832</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46215.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+      <c r="C234">
+        <v>4.086</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46215.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>19.794</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46215.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>6.775</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46215.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>7.432</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46215.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>18.835</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46215.46875</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+      <c r="C239">
+        <v>0.789</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46215.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>3.46</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46215.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>2.613</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46215.5</v>
+      </c>
+      <c r="B242">
+        <v>4.398</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46215.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>14.389</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46215.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>17.224</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46215.53125</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+      <c r="C245">
+        <v>7.281</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46215.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>2.615</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46215.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>2.158</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46215.5625</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+      <c r="C248">
+        <v>1.656</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46215.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>0</v>
+      </c>
+      <c r="C249">
+        <v>3.955</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46215.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>0</v>
+      </c>
+      <c r="C250">
+        <v>2.845</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46215.59375</v>
+      </c>
+      <c r="B251">
+        <v>7.549</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46215.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252">
+        <v>4.006</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46215.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>18.314</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46215.625</v>
+      </c>
+      <c r="B254">
+        <v>27.562</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46215.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>76.86199999999999</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46215.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>90.52</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46215.65625</v>
+      </c>
+      <c r="B257">
+        <v>95.233</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46215.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>119.078</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46215.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>100.312</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46215.6875</v>
+      </c>
+      <c r="B260">
+        <v>86.301</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46215.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>69.78400000000001</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46215.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>23.961</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46215.71875</v>
+      </c>
+      <c r="B263">
+        <v>8.935</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46215.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>20.184</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46215.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>18.405</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46215.75</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>8.621</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46215.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46215.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>4.64</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46215.78125</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>40.482</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46215.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+      <c r="C270">
+        <v>53.011</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46215.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>26.876</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46215.8125</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>24.009</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46215.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>5.257</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46215.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>15.659</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46215.84375</v>
+      </c>
+      <c r="B275">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46215.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>0</v>
+      </c>
+      <c r="C276">
+        <v>6.508</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46215.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>0</v>
+      </c>
+      <c r="C277">
+        <v>18.521</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46215.875</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>13.78</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46215.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>2.877</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46215.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>2.573</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46215.90625</v>
+      </c>
+      <c r="B281">
+        <v>16.96</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46215.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>19.424</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46215.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>12.372</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46215.9375</v>
+      </c>
+      <c r="B284">
+        <v>9.731</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46215.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0.507</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46215.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>3.283</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46215.96875</v>
+      </c>
+      <c r="B287">
+        <v>2.537</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46215.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>12.345</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46215.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>4.525</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>1.417</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46216.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0</v>
+      </c>
+      <c r="C291">
+        <v>7.28</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46216.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0.106</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46216.03125</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>17.988</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46216.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>12.571</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46216.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>0</v>
+      </c>
+      <c r="C295">
+        <v>28.974</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46216.0625</v>
+      </c>
+      <c r="B296">
+        <v>0</v>
+      </c>
+      <c r="C296">
+        <v>45.794</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46216.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+      <c r="C297">
+        <v>17.431</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46216.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>2.519</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46216.09375</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>3.215</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46216.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>8.968</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46216.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>15.441</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46216.125</v>
+      </c>
+      <c r="B302">
+        <v>9.239000000000001</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46216.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>29.79</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46216.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>23.897</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46216.15625</v>
+      </c>
+      <c r="B305">
+        <v>18.221</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46216.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>3.771</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46216.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>14.732</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46216.1875</v>
+      </c>
+      <c r="B308">
+        <v>26.612</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46216.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>8.574</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46216.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>0.185</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46216.21875</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>0.98</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46216.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+      <c r="C312">
+        <v>5.332</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46216.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+      <c r="C313">
+        <v>8.981999999999999</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46216.25</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+      <c r="C314">
+        <v>10.447</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46216.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>6.932</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46216.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>4.571</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46216.28125</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+      <c r="C317">
+        <v>4.349</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46216.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+      <c r="C318">
+        <v>5.614</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46216.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>8.978</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46216.3125</v>
+      </c>
+      <c r="B320">
+        <v>9.273</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" s="2">
+        <v>46216.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+      <c r="C321">
+        <v>11.388</v>
+      </c>
+      <c r="D321">
+        <v>32</v>
+      </c>
+      <c r="E321" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" s="2">
+        <v>46216.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+      <c r="C322">
+        <v>6.412</v>
+      </c>
+      <c r="D322">
+        <v>33</v>
+      </c>
+      <c r="E322" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" s="2">
+        <v>46216.34375</v>
+      </c>
+      <c r="B323">
+        <v>22.232</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>34</v>
+      </c>
+      <c r="E323" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" s="2">
+        <v>46216.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>0.335</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>35</v>
+      </c>
+      <c r="E324" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" s="2">
+        <v>46216.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>0</v>
+      </c>
+      <c r="C325">
+        <v>10.822</v>
+      </c>
+      <c r="D325">
+        <v>36</v>
+      </c>
+      <c r="E325" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" s="2">
+        <v>46216.375</v>
+      </c>
+      <c r="B326">
+        <v>8.417999999999999</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>37</v>
+      </c>
+      <c r="E326" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" s="2">
+        <v>46216.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>0</v>
+      </c>
+      <c r="C327">
+        <v>1.054</v>
+      </c>
+      <c r="D327">
+        <v>38</v>
+      </c>
+      <c r="E327" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" s="2">
+        <v>46216.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>18.956</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>39</v>
+      </c>
+      <c r="E328" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5">
+      <c r="A329" s="2">
+        <v>46216.40625</v>
+      </c>
+      <c r="B329">
+        <v>0</v>
+      </c>
+      <c r="C329">
+        <v>7.655</v>
+      </c>
+      <c r="D329">
+        <v>40</v>
+      </c>
+      <c r="E329" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5">
+      <c r="A330" s="2">
+        <v>46216.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>1.607</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>41</v>
+      </c>
+      <c r="E330" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
+      <c r="A331" s="2">
+        <v>46216.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>8.52</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>42</v>
+      </c>
+      <c r="E331" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5">
+      <c r="A332" s="2">
+        <v>46216.4375</v>
+      </c>
+      <c r="B332">
+        <v>0</v>
+      </c>
+      <c r="C332">
+        <v>10.167</v>
+      </c>
+      <c r="D332">
+        <v>43</v>
+      </c>
+      <c r="E332" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
+      <c r="A333" s="2">
+        <v>46216.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>2.2</v>
+      </c>
+      <c r="D333">
+        <v>44</v>
+      </c>
+      <c r="E333" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5">
+      <c r="A334" s="2">
+        <v>46216.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>0</v>
+      </c>
+      <c r="C334">
+        <v>1.691</v>
+      </c>
+      <c r="D334">
+        <v>45</v>
+      </c>
+      <c r="E334" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5">
+      <c r="A335" s="2">
+        <v>46216.46875</v>
+      </c>
+      <c r="B335">
+        <v>31.567</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>46</v>
+      </c>
+      <c r="E335" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5">
+      <c r="A336" s="2">
+        <v>46216.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>44.941</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>47</v>
+      </c>
+      <c r="E336" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5">
+      <c r="A337" s="2">
+        <v>46216.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>53.44</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>48</v>
+      </c>
+      <c r="E337" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5">
+      <c r="A338" s="2">
+        <v>46216.5</v>
+      </c>
+      <c r="B338">
+        <v>32.957</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>49</v>
+      </c>
+      <c r="E338" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5">
+      <c r="A339" s="2">
+        <v>46216.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>3.955</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>50</v>
+      </c>
+      <c r="E339" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
+      <c r="A340" s="2">
+        <v>46216.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>1.462</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>51</v>
+      </c>
+      <c r="E340" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5">
+      <c r="A341" s="2">
+        <v>46216.53125</v>
+      </c>
+      <c r="B341">
+        <v>8.867000000000001</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>52</v>
+      </c>
+      <c r="E341" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>14.07.20261</t>
-  </si>
-  <si>
-    <t>14.07.20262</t>
-  </si>
-  <si>
-    <t>14.07.20263</t>
-  </si>
-  <si>
-    <t>14.07.20264</t>
-  </si>
-  <si>
-    <t>14.07.20265</t>
-  </si>
-  <si>
-    <t>14.07.20266</t>
-  </si>
-  <si>
-    <t>14.07.20267</t>
-  </si>
-  <si>
-    <t>14.07.20268</t>
-  </si>
-  <si>
-    <t>14.07.20269</t>
-  </si>
-  <si>
-    <t>14.07.202610</t>
-  </si>
-  <si>
-    <t>14.07.202611</t>
-  </si>
-  <si>
-    <t>14.07.202612</t>
-  </si>
-  <si>
-    <t>14.07.202613</t>
-  </si>
-  <si>
-    <t>14.07.202614</t>
-  </si>
-  <si>
-    <t>14.07.202615</t>
-  </si>
-  <si>
-    <t>14.07.202616</t>
-  </si>
-  <si>
-    <t>14.07.202617</t>
-  </si>
-  <si>
-    <t>14.07.202618</t>
-  </si>
-  <si>
-    <t>14.07.202619</t>
-  </si>
-  <si>
-    <t>14.07.202620</t>
-  </si>
-  <si>
-    <t>14.07.202621</t>
-  </si>
-  <si>
-    <t>14.07.202622</t>
-  </si>
-  <si>
-    <t>14.07.202623</t>
-  </si>
-  <si>
-    <t>14.07.202624</t>
-  </si>
-  <si>
-    <t>14.07.202625</t>
-  </si>
-  <si>
-    <t>14.07.202626</t>
-  </si>
-  <si>
-    <t>14.07.202627</t>
-  </si>
-  <si>
-    <t>14.07.202628</t>
-  </si>
-  <si>
-    <t>14.07.202629</t>
-  </si>
-  <si>
-    <t>14.07.202630</t>
-  </si>
-  <si>
-    <t>14.07.202631</t>
-  </si>
-  <si>
-    <t>14.07.202632</t>
-  </si>
-  <si>
-    <t>14.07.202633</t>
-  </si>
-  <si>
-    <t>14.07.202634</t>
-  </si>
-  <si>
-    <t>14.07.202635</t>
-  </si>
-  <si>
-    <t>14.07.202636</t>
-  </si>
-  <si>
-    <t>14.07.202637</t>
-  </si>
-  <si>
-    <t>14.07.202638</t>
-  </si>
-  <si>
-    <t>14.07.202639</t>
-  </si>
-  <si>
-    <t>14.07.202640</t>
-  </si>
-  <si>
-    <t>14.07.202641</t>
-  </si>
-  <si>
-    <t>14.07.202642</t>
-  </si>
-  <si>
-    <t>14.07.202643</t>
-  </si>
-  <si>
-    <t>14.07.202644</t>
-  </si>
-  <si>
-    <t>14.07.202645</t>
-  </si>
-  <si>
-    <t>14.07.202646</t>
-  </si>
-  <si>
-    <t>14.07.202647</t>
-  </si>
-  <si>
-    <t>14.07.202648</t>
-  </si>
-  <si>
-    <t>14.07.202649</t>
-  </si>
-  <si>
-    <t>14.07.202650</t>
-  </si>
-  <si>
-    <t>14.07.202651</t>
-  </si>
-  <si>
-    <t>14.07.202652</t>
-  </si>
-  <si>
-    <t>14.07.202653</t>
-  </si>
-  <si>
-    <t>14.07.202654</t>
-  </si>
-  <si>
-    <t>14.07.202655</t>
-  </si>
-  <si>
-    <t>14.07.202656</t>
-  </si>
-  <si>
-    <t>14.07.202657</t>
-  </si>
-  <si>
-    <t>14.07.202658</t>
-  </si>
-  <si>
-    <t>14.07.202659</t>
-  </si>
-  <si>
-    <t>14.07.202660</t>
-  </si>
-  <si>
-    <t>14.07.202661</t>
-  </si>
-  <si>
-    <t>14.07.202662</t>
-  </si>
-  <si>
-    <t>14.07.202663</t>
-  </si>
-  <si>
-    <t>14.07.202664</t>
-  </si>
-  <si>
-    <t>14.07.202665</t>
-  </si>
-  <si>
-    <t>14.07.202666</t>
-  </si>
-  <si>
-    <t>14.07.202667</t>
-  </si>
-  <si>
-    <t>14.07.202668</t>
-  </si>
-  <si>
-    <t>14.07.202669</t>
-  </si>
-  <si>
-    <t>14.07.202670</t>
-  </si>
-  <si>
-    <t>14.07.202671</t>
-  </si>
-  <si>
-    <t>14.07.202672</t>
-  </si>
-  <si>
-    <t>14.07.202673</t>
-  </si>
-  <si>
-    <t>14.07.202674</t>
-  </si>
-  <si>
-    <t>14.07.202675</t>
-  </si>
-  <si>
-    <t>14.07.202676</t>
-  </si>
-  <si>
-    <t>14.07.202677</t>
-  </si>
-  <si>
-    <t>14.07.202678</t>
-  </si>
-  <si>
-    <t>14.07.202679</t>
-  </si>
-  <si>
-    <t>14.07.202680</t>
-  </si>
-  <si>
-    <t>14.07.202681</t>
-  </si>
-  <si>
-    <t>14.07.202682</t>
-  </si>
-  <si>
-    <t>14.07.202683</t>
-  </si>
-  <si>
-    <t>14.07.202684</t>
-  </si>
-  <si>
-    <t>14.07.202685</t>
-  </si>
-  <si>
-    <t>14.07.202686</t>
-  </si>
-  <si>
-    <t>14.07.202687</t>
-  </si>
-  <si>
-    <t>14.07.202688</t>
-  </si>
-  <si>
-    <t>14.07.202689</t>
-  </si>
-  <si>
-    <t>14.07.202690</t>
-  </si>
-  <si>
-    <t>14.07.202691</t>
-  </si>
-  <si>
-    <t>14.07.202692</t>
-  </si>
-  <si>
-    <t>14.07.202693</t>
-  </si>
-  <si>
-    <t>14.07.202694</t>
-  </si>
-  <si>
-    <t>14.07.202695</t>
-  </si>
-  <si>
-    <t>14.07.202696</t>
-  </si>
-  <si>
     <t>15.07.20261</t>
   </si>
   <si>
@@ -455,6 +167,285 @@
   </si>
   <si>
     <t>15.07.202646</t>
+  </si>
+  <si>
+    <t>15.07.202647</t>
+  </si>
+  <si>
+    <t>15.07.202648</t>
+  </si>
+  <si>
+    <t>15.07.202649</t>
+  </si>
+  <si>
+    <t>15.07.202650</t>
+  </si>
+  <si>
+    <t>15.07.202651</t>
+  </si>
+  <si>
+    <t>15.07.202652</t>
+  </si>
+  <si>
+    <t>15.07.202653</t>
+  </si>
+  <si>
+    <t>15.07.202654</t>
+  </si>
+  <si>
+    <t>15.07.202655</t>
+  </si>
+  <si>
+    <t>15.07.202656</t>
+  </si>
+  <si>
+    <t>15.07.202657</t>
+  </si>
+  <si>
+    <t>15.07.202658</t>
+  </si>
+  <si>
+    <t>15.07.202659</t>
+  </si>
+  <si>
+    <t>15.07.202660</t>
+  </si>
+  <si>
+    <t>15.07.202661</t>
+  </si>
+  <si>
+    <t>15.07.202662</t>
+  </si>
+  <si>
+    <t>15.07.202663</t>
+  </si>
+  <si>
+    <t>15.07.202664</t>
+  </si>
+  <si>
+    <t>15.07.202665</t>
+  </si>
+  <si>
+    <t>15.07.202666</t>
+  </si>
+  <si>
+    <t>15.07.202667</t>
+  </si>
+  <si>
+    <t>15.07.202668</t>
+  </si>
+  <si>
+    <t>15.07.202669</t>
+  </si>
+  <si>
+    <t>15.07.202670</t>
+  </si>
+  <si>
+    <t>15.07.202671</t>
+  </si>
+  <si>
+    <t>15.07.202672</t>
+  </si>
+  <si>
+    <t>15.07.202673</t>
+  </si>
+  <si>
+    <t>15.07.202674</t>
+  </si>
+  <si>
+    <t>15.07.202675</t>
+  </si>
+  <si>
+    <t>15.07.202676</t>
+  </si>
+  <si>
+    <t>15.07.202677</t>
+  </si>
+  <si>
+    <t>15.07.202678</t>
+  </si>
+  <si>
+    <t>15.07.202679</t>
+  </si>
+  <si>
+    <t>15.07.202680</t>
+  </si>
+  <si>
+    <t>15.07.202681</t>
+  </si>
+  <si>
+    <t>15.07.202682</t>
+  </si>
+  <si>
+    <t>15.07.202683</t>
+  </si>
+  <si>
+    <t>15.07.202684</t>
+  </si>
+  <si>
+    <t>15.07.202685</t>
+  </si>
+  <si>
+    <t>15.07.202686</t>
+  </si>
+  <si>
+    <t>15.07.202687</t>
+  </si>
+  <si>
+    <t>15.07.202688</t>
+  </si>
+  <si>
+    <t>15.07.202689</t>
+  </si>
+  <si>
+    <t>15.07.202690</t>
+  </si>
+  <si>
+    <t>15.07.202691</t>
+  </si>
+  <si>
+    <t>15.07.202692</t>
+  </si>
+  <si>
+    <t>15.07.202693</t>
+  </si>
+  <si>
+    <t>15.07.202694</t>
+  </si>
+  <si>
+    <t>15.07.202695</t>
+  </si>
+  <si>
+    <t>15.07.202696</t>
+  </si>
+  <si>
+    <t>16.07.20261</t>
+  </si>
+  <si>
+    <t>16.07.20262</t>
+  </si>
+  <si>
+    <t>16.07.20263</t>
+  </si>
+  <si>
+    <t>16.07.20264</t>
+  </si>
+  <si>
+    <t>16.07.20265</t>
+  </si>
+  <si>
+    <t>16.07.20266</t>
+  </si>
+  <si>
+    <t>16.07.20267</t>
+  </si>
+  <si>
+    <t>16.07.20268</t>
+  </si>
+  <si>
+    <t>16.07.20269</t>
+  </si>
+  <si>
+    <t>16.07.202610</t>
+  </si>
+  <si>
+    <t>16.07.202611</t>
+  </si>
+  <si>
+    <t>16.07.202612</t>
+  </si>
+  <si>
+    <t>16.07.202613</t>
+  </si>
+  <si>
+    <t>16.07.202614</t>
+  </si>
+  <si>
+    <t>16.07.202615</t>
+  </si>
+  <si>
+    <t>16.07.202616</t>
+  </si>
+  <si>
+    <t>16.07.202617</t>
+  </si>
+  <si>
+    <t>16.07.202618</t>
+  </si>
+  <si>
+    <t>16.07.202619</t>
+  </si>
+  <si>
+    <t>16.07.202620</t>
+  </si>
+  <si>
+    <t>16.07.202621</t>
+  </si>
+  <si>
+    <t>16.07.202622</t>
+  </si>
+  <si>
+    <t>16.07.202623</t>
+  </si>
+  <si>
+    <t>16.07.202624</t>
+  </si>
+  <si>
+    <t>16.07.202625</t>
+  </si>
+  <si>
+    <t>16.07.202626</t>
+  </si>
+  <si>
+    <t>16.07.202627</t>
+  </si>
+  <si>
+    <t>16.07.202628</t>
+  </si>
+  <si>
+    <t>16.07.202629</t>
+  </si>
+  <si>
+    <t>16.07.202630</t>
+  </si>
+  <si>
+    <t>16.07.202631</t>
+  </si>
+  <si>
+    <t>16.07.202632</t>
+  </si>
+  <si>
+    <t>16.07.202633</t>
+  </si>
+  <si>
+    <t>16.07.202634</t>
+  </si>
+  <si>
+    <t>16.07.202635</t>
+  </si>
+  <si>
+    <t>16.07.202636</t>
+  </si>
+  <si>
+    <t>16.07.202637</t>
+  </si>
+  <si>
+    <t>16.07.202638</t>
+  </si>
+  <si>
+    <t>16.07.202639</t>
+  </si>
+  <si>
+    <t>16.07.202640</t>
+  </si>
+  <si>
+    <t>16.07.202641</t>
+  </si>
+  <si>
+    <t>16.07.202642</t>
+  </si>
+  <si>
+    <t>16.07.202643</t>
   </si>
 </sst>
 </file>
@@ -816,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -838,13 +829,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>20.296</v>
+        <v>30.782</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -855,13 +846,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46217.01041666666</v>
+        <v>46218.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>31.51</v>
+        <v>25.742</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -872,13 +863,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46217.02083333334</v>
+        <v>46218.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>27.841</v>
+        <v>14.2</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -889,13 +880,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46217.03125</v>
+        <v>46218.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>18.64</v>
+        <v>20.968</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -906,13 +897,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46217.04166666666</v>
+        <v>46218.04166666666</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <v>22.958</v>
+        <v>1.288</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -923,13 +914,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46217.05208333334</v>
+        <v>46218.05208333334</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>29.888</v>
+        <v>6.364</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -940,13 +931,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46217.0625</v>
+        <v>46218.0625</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>26.923</v>
+        <v>1.235</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -957,13 +948,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46217.07291666666</v>
+        <v>46218.07291666666</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.768</v>
+        <v>5.64</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -974,10 +965,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46217.08333333334</v>
+        <v>46218.08333333334</v>
       </c>
       <c r="B10">
-        <v>4.992</v>
+        <v>1.433</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -991,13 +982,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46217.09375</v>
+        <v>46218.09375</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="C11">
-        <v>2.353</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -1008,13 +999,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46217.10416666666</v>
+        <v>46218.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.677</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>3.208</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1025,13 +1016,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46217.11458333334</v>
+        <v>46218.11458333334</v>
       </c>
       <c r="B13">
-        <v>5.191</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2.254</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1042,10 +1033,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46217.125</v>
+        <v>46218.125</v>
       </c>
       <c r="B14">
-        <v>7.344</v>
+        <v>11.106</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1059,13 +1050,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46217.13541666666</v>
+        <v>46218.13541666666</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>16.401</v>
       </c>
       <c r="C15">
-        <v>4.099</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1076,13 +1067,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46217.14583333334</v>
+        <v>46218.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>8.673</v>
       </c>
       <c r="C16">
-        <v>6.944</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1093,13 +1084,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46217.15625</v>
+        <v>46218.15625</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>2.503</v>
       </c>
       <c r="C17">
-        <v>2.975</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1110,13 +1101,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46217.16666666666</v>
+        <v>46218.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>6.794</v>
+        <v>4.218</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1127,13 +1118,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46217.17708333334</v>
+        <v>46218.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>14.636</v>
+        <v>4.316</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1144,13 +1135,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46217.1875</v>
+        <v>46218.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>5.679</v>
       </c>
       <c r="C20">
-        <v>10.643</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1161,13 +1152,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46217.19791666666</v>
+        <v>46218.19791666666</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>4.786</v>
       </c>
       <c r="C21">
-        <v>4.012</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1178,13 +1169,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46217.20833333334</v>
+        <v>46218.20833333334</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="C22">
-        <v>1.296</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1195,10 +1186,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46217.21875</v>
+        <v>46218.21875</v>
       </c>
       <c r="B23">
-        <v>0.931</v>
+        <v>6.049</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1212,10 +1203,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46217.22916666666</v>
+        <v>46218.22916666666</v>
       </c>
       <c r="B24">
-        <v>5.445</v>
+        <v>11.808</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1229,10 +1220,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46217.23958333334</v>
+        <v>46218.23958333334</v>
       </c>
       <c r="B25">
-        <v>18.567</v>
+        <v>26.998</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1246,10 +1237,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46217.25</v>
+        <v>46218.25</v>
       </c>
       <c r="B26">
-        <v>7.885</v>
+        <v>11.056</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1263,10 +1254,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46217.26041666666</v>
+        <v>46218.26041666666</v>
       </c>
       <c r="B27">
-        <v>2.793</v>
+        <v>9.727</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1280,10 +1271,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46217.27083333334</v>
+        <v>46218.27083333334</v>
       </c>
       <c r="B28">
-        <v>22.963</v>
+        <v>26.099</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1297,10 +1288,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46217.28125</v>
+        <v>46218.28125</v>
       </c>
       <c r="B29">
-        <v>20.934</v>
+        <v>23.212</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -1314,10 +1305,10 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46217.29166666666</v>
+        <v>46218.29166666666</v>
       </c>
       <c r="B30">
-        <v>19.132</v>
+        <v>36.776</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1331,13 +1322,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46217.30208333334</v>
+        <v>46218.30208333334</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>22.255</v>
       </c>
       <c r="C31">
-        <v>5.127</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1348,13 +1339,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46217.3125</v>
+        <v>46218.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>7.246</v>
       </c>
       <c r="C32">
-        <v>22.76</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1365,13 +1356,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46217.32291666666</v>
+        <v>46218.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>46.343</v>
+        <v>17.011</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1382,13 +1373,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46217.33333333334</v>
+        <v>46218.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>9.131</v>
       </c>
       <c r="C34">
-        <v>26.768</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1399,13 +1390,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46217.34375</v>
+        <v>46218.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>49.486</v>
+        <v>2.069</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1416,13 +1407,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46217.35416666666</v>
+        <v>46218.35416666666</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>4.778</v>
       </c>
       <c r="C36">
-        <v>0.514</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1433,13 +1424,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46217.36458333334</v>
+        <v>46218.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>8.516</v>
+        <v>4.058</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1450,10 +1441,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46217.375</v>
+        <v>46218.375</v>
       </c>
       <c r="B38">
-        <v>1.62</v>
+        <v>3.478</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -1467,13 +1458,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46217.38541666666</v>
+        <v>46218.38541666666</v>
       </c>
       <c r="B39">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>5.992</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1484,13 +1475,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46217.39583333334</v>
+        <v>46218.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>7.133</v>
+        <v>6.827</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1501,13 +1492,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46217.40625</v>
+        <v>46218.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>6.4</v>
+        <v>0.915</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1518,10 +1509,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46217.41666666666</v>
+        <v>46218.41666666666</v>
       </c>
       <c r="B42">
-        <v>0.045</v>
+        <v>7.633</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1535,13 +1526,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46217.42708333334</v>
+        <v>46218.42708333334</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>10.106</v>
+        <v>1.047</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1552,13 +1543,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46217.4375</v>
+        <v>46218.4375</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>3.545</v>
+        <v>0.054</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1569,13 +1560,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46217.44791666666</v>
+        <v>46218.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>8.84</v>
+        <v>3.38</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1586,13 +1577,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46217.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>9.468999999999999</v>
+        <v>7.757</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1603,13 +1594,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46217.46875</v>
+        <v>46218.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>31.409</v>
+        <v>12.522</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1620,13 +1611,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46217.47916666666</v>
+        <v>46218.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>26.281</v>
+        <v>28.895</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1637,13 +1628,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46217.48958333334</v>
+        <v>46218.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>19.299</v>
+        <v>29.128</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1654,13 +1645,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46217.5</v>
+        <v>46218.5</v>
       </c>
       <c r="B50">
-        <v>21.253</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1671,10 +1662,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46217.51041666666</v>
+        <v>46218.51041666666</v>
       </c>
       <c r="B51">
-        <v>2.054</v>
+        <v>3.333</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1688,10 +1679,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46217.52083333334</v>
+        <v>46218.52083333334</v>
       </c>
       <c r="B52">
-        <v>18.938</v>
+        <v>25.55</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -1705,10 +1696,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46217.53125</v>
+        <v>46218.53125</v>
       </c>
       <c r="B53">
-        <v>28.063</v>
+        <v>23.953</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1722,13 +1713,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46217.54166666666</v>
+        <v>46218.54166666666</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>12.516</v>
       </c>
       <c r="C54">
-        <v>1.735</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1739,13 +1730,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46217.55208333334</v>
+        <v>46218.55208333334</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>40.006</v>
       </c>
       <c r="C55">
-        <v>2.805</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1756,10 +1747,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46217.5625</v>
+        <v>46218.5625</v>
       </c>
       <c r="B56">
-        <v>6.792</v>
+        <v>58.11</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1773,10 +1764,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46217.57291666666</v>
+        <v>46218.57291666666</v>
       </c>
       <c r="B57">
-        <v>13.47</v>
+        <v>94.247</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -1790,10 +1781,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46217.58333333334</v>
+        <v>46218.58333333334</v>
       </c>
       <c r="B58">
-        <v>3.543</v>
+        <v>86.714</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -1807,13 +1798,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46217.59375</v>
+        <v>46218.59375</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>60.502</v>
       </c>
       <c r="C59">
-        <v>7.521</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1824,10 +1815,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46217.60416666666</v>
+        <v>46218.60416666666</v>
       </c>
       <c r="B60">
-        <v>16.142</v>
+        <v>36.123</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -1841,10 +1832,10 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46217.61458333334</v>
+        <v>46218.61458333334</v>
       </c>
       <c r="B61">
-        <v>39.246</v>
+        <v>48.475</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -1858,10 +1849,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46217.625</v>
+        <v>46218.625</v>
       </c>
       <c r="B62">
-        <v>4.963</v>
+        <v>97.893</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -1875,13 +1866,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46217.63541666666</v>
+        <v>46218.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>90.57299999999999</v>
       </c>
       <c r="C63">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1892,10 +1883,10 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46217.64583333334</v>
+        <v>46218.64583333334</v>
       </c>
       <c r="B64">
-        <v>20.943</v>
+        <v>59.375</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -1909,13 +1900,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46217.65625</v>
+        <v>46218.65625</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>41.43</v>
       </c>
       <c r="C65">
-        <v>4.409</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -1926,10 +1917,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46217.66666666666</v>
+        <v>46218.66666666666</v>
       </c>
       <c r="B66">
-        <v>1.412</v>
+        <v>2.54</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -1943,13 +1934,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46217.67708333334</v>
+        <v>46218.67708333334</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>2.435</v>
+        <v>22.613</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1960,13 +1951,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46217.6875</v>
+        <v>46218.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>17.423</v>
       </c>
       <c r="C68">
-        <v>0.367</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -1977,13 +1968,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46217.69791666666</v>
+        <v>46218.69791666666</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>39.054</v>
       </c>
       <c r="C69">
-        <v>0.848</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -1994,13 +1985,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46217.70833333334</v>
+        <v>46218.70833333334</v>
       </c>
       <c r="B70">
-        <v>5.405</v>
+        <v>0</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>29.61</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2011,13 +2002,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46217.71875</v>
+        <v>46218.71875</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
       <c r="C71">
-        <v>0.164</v>
+        <v>4.131</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2028,13 +2019,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46217.72916666666</v>
+        <v>46218.72916666666</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="C72">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2045,10 +2036,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46217.73958333334</v>
+        <v>46218.73958333334</v>
       </c>
       <c r="B73">
-        <v>0.571</v>
+        <v>2.347</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2062,13 +2053,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46217.75</v>
+        <v>46218.75</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>30.877</v>
       </c>
       <c r="C74">
-        <v>15.052</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2079,13 +2070,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46217.76041666666</v>
+        <v>46218.76041666666</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>18.074</v>
       </c>
       <c r="C75">
-        <v>6.359</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2096,13 +2087,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46217.77083333334</v>
+        <v>46218.77083333334</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>3.743</v>
       </c>
       <c r="C76">
-        <v>17.139</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2113,13 +2104,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46217.78125</v>
+        <v>46218.78125</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>0.741</v>
       </c>
       <c r="C77">
-        <v>8.247</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2130,13 +2121,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46217.79166666666</v>
+        <v>46218.79166666666</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>1.588</v>
       </c>
       <c r="C78">
-        <v>47.261</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2147,13 +2138,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46217.80208333334</v>
+        <v>46218.80208333334</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>16.383</v>
       </c>
       <c r="C79">
-        <v>61.063</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2164,13 +2155,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46217.8125</v>
+        <v>46218.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>16.765</v>
+        <v>5.016</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2181,13 +2172,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46217.82291666666</v>
+        <v>46218.82291666666</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="C81">
-        <v>29.225</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2198,13 +2189,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46217.83333333334</v>
+        <v>46218.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>31.73</v>
+        <v>15.1</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2215,13 +2206,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46217.84375</v>
+        <v>46218.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>47.381</v>
+        <v>24.172</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2232,13 +2223,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46217.85416666666</v>
+        <v>46218.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>5.161</v>
+        <v>14.439</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2249,13 +2240,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46217.86458333334</v>
+        <v>46218.86458333334</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>0.122</v>
+        <v>21.278</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2266,13 +2257,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46217.875</v>
+        <v>46218.875</v>
       </c>
       <c r="B86">
-        <v>13.176</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>4.707</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2283,13 +2274,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46217.88541666666</v>
+        <v>46218.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>6.999</v>
+        <v>1.473</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2300,13 +2291,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46217.89583333334</v>
+        <v>46218.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>14.437</v>
+        <v>12.382</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2317,13 +2308,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46217.90625</v>
+        <v>46218.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>4.551</v>
+        <v>35.295</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2334,13 +2325,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46217.91666666666</v>
+        <v>46218.91666666666</v>
       </c>
       <c r="B90">
-        <v>2.443</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>6.288</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2351,13 +2342,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46217.92708333334</v>
+        <v>46218.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>8.781000000000001</v>
+        <v>2.141</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2368,13 +2359,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46217.9375</v>
+        <v>46218.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>1.647</v>
+        <v>1.698</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2385,13 +2376,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46217.94791666666</v>
+        <v>46218.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>5.675</v>
+        <v>12.323</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2402,13 +2393,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46217.95833333334</v>
+        <v>46218.95833333334</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
       <c r="C94">
-        <v>14.743</v>
+        <v>8.805</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2419,13 +2410,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46217.96875</v>
+        <v>46218.96875</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>31.229</v>
+        <v>16.389</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2436,13 +2427,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46217.97916666666</v>
+        <v>46218.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>12.037</v>
+        <v>16.461</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2453,13 +2444,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46217.98958333334</v>
+        <v>46218.98958333334</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>17.411</v>
+        <v>5.379</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2470,13 +2461,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>2.672</v>
       </c>
       <c r="C98">
-        <v>30.782</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2487,13 +2478,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46218.01041666666</v>
+        <v>46219.01041666666</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="C99">
-        <v>25.742</v>
+        <v>6.122</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2504,13 +2495,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46218.02083333334</v>
+        <v>46219.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100">
-        <v>14.2</v>
+        <v>5.665</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2521,13 +2512,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46218.03125</v>
+        <v>46219.03125</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>5.648</v>
       </c>
       <c r="C101">
-        <v>20.968</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2538,13 +2529,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46218.04166666666</v>
+        <v>46219.04166666666</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
       <c r="C102">
-        <v>1.288</v>
+        <v>2.252</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2555,13 +2546,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46218.05208333334</v>
+        <v>46219.05208333334</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="C103">
-        <v>6.364</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2572,13 +2563,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46218.0625</v>
+        <v>46219.0625</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>4.565</v>
       </c>
       <c r="C104">
-        <v>1.235</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2589,13 +2580,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46218.07291666666</v>
+        <v>46219.07291666666</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>2.544</v>
       </c>
       <c r="C105">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2606,10 +2597,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46218.08333333334</v>
+        <v>46219.08333333334</v>
       </c>
       <c r="B106">
-        <v>1.433</v>
+        <v>5.02</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2623,10 +2614,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46218.09375</v>
+        <v>46219.09375</v>
       </c>
       <c r="B107">
-        <v>0.096</v>
+        <v>1.492</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -2640,13 +2631,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46218.10416666666</v>
+        <v>46219.10416666666</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>1.452</v>
       </c>
       <c r="C108">
-        <v>3.208</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2657,13 +2648,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46218.11458333334</v>
+        <v>46219.11458333334</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>2.254</v>
+        <v>8.948</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2674,13 +2665,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46218.125</v>
+        <v>46219.125</v>
       </c>
       <c r="B110">
-        <v>11.106</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>6.162</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2691,13 +2682,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46218.13541666666</v>
+        <v>46219.13541666666</v>
       </c>
       <c r="B111">
-        <v>16.401</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>2.589</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2708,13 +2699,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46218.14583333334</v>
+        <v>46219.14583333334</v>
       </c>
       <c r="B112">
-        <v>8.673</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>3.494</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2725,13 +2716,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46218.15625</v>
+        <v>46219.15625</v>
       </c>
       <c r="B113">
-        <v>2.503</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>3.717</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2742,13 +2733,13 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46218.16666666666</v>
+        <v>46219.16666666666</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>2.398</v>
       </c>
       <c r="C114">
-        <v>4.218</v>
+        <v>0</v>
       </c>
       <c r="D114">
         <v>17</v>
@@ -2759,13 +2750,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46218.17708333334</v>
+        <v>46219.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>9.445</v>
       </c>
       <c r="C115">
-        <v>4.316</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2776,10 +2767,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46218.1875</v>
+        <v>46219.1875</v>
       </c>
       <c r="B116">
-        <v>5.679</v>
+        <v>1.552</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2793,10 +2784,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46218.19791666666</v>
+        <v>46219.19791666666</v>
       </c>
       <c r="B117">
-        <v>4.786</v>
+        <v>9.500999999999999</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2810,10 +2801,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46218.20833333334</v>
+        <v>46219.20833333334</v>
       </c>
       <c r="B118">
-        <v>0.63</v>
+        <v>19.701</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2827,10 +2818,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46218.21875</v>
+        <v>46219.21875</v>
       </c>
       <c r="B119">
-        <v>6.049</v>
+        <v>15.906</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2844,10 +2835,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46218.22916666666</v>
+        <v>46219.22916666666</v>
       </c>
       <c r="B120">
-        <v>11.808</v>
+        <v>24.117</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -2861,10 +2852,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46218.23958333334</v>
+        <v>46219.23958333334</v>
       </c>
       <c r="B121">
-        <v>26.998</v>
+        <v>17.229</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -2878,10 +2869,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46218.25</v>
+        <v>46219.25</v>
       </c>
       <c r="B122">
-        <v>11.056</v>
+        <v>11.659</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -2895,10 +2886,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46218.26041666666</v>
+        <v>46219.26041666666</v>
       </c>
       <c r="B123">
-        <v>9.727</v>
+        <v>10.831</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -2912,13 +2903,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46218.27083333334</v>
+        <v>46219.27083333334</v>
       </c>
       <c r="B124">
-        <v>26.099</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>1.791</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2929,10 +2920,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46218.28125</v>
+        <v>46219.28125</v>
       </c>
       <c r="B125">
-        <v>23.212</v>
+        <v>13.397</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -2946,10 +2937,10 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46218.29166666666</v>
+        <v>46219.29166666666</v>
       </c>
       <c r="B126">
-        <v>36.776</v>
+        <v>7.179</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -2963,13 +2954,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46218.30208333334</v>
+        <v>46219.30208333334</v>
       </c>
       <c r="B127">
-        <v>22.255</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>5.164</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -2980,10 +2971,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46218.3125</v>
+        <v>46219.3125</v>
       </c>
       <c r="B128">
-        <v>7.246</v>
+        <v>5.459</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -2997,13 +2988,13 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46218.32291666666</v>
+        <v>46219.32291666666</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>8.486000000000001</v>
       </c>
       <c r="C129">
-        <v>17.011</v>
+        <v>0</v>
       </c>
       <c r="D129">
         <v>32</v>
@@ -3014,10 +3005,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46218.33333333334</v>
+        <v>46219.33333333334</v>
       </c>
       <c r="B130">
-        <v>9.131</v>
+        <v>7.194</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3031,13 +3022,13 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46218.34375</v>
+        <v>46219.34375</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>7.304</v>
       </c>
       <c r="C131">
-        <v>2.069</v>
+        <v>0</v>
       </c>
       <c r="D131">
         <v>34</v>
@@ -3048,10 +3039,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46218.35416666666</v>
+        <v>46219.35416666666</v>
       </c>
       <c r="B132">
-        <v>4.778</v>
+        <v>2.516</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3065,13 +3056,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46218.36458333334</v>
+        <v>46219.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>4.058</v>
+        <v>1.73</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3082,10 +3073,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46218.375</v>
+        <v>46219.375</v>
       </c>
       <c r="B134">
-        <v>3.478</v>
+        <v>32.139</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3099,13 +3090,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46218.38541666666</v>
+        <v>46219.38541666666</v>
       </c>
       <c r="B135">
-        <v>0</v>
+        <v>17.156</v>
       </c>
       <c r="C135">
-        <v>5.992</v>
+        <v>0</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3116,13 +3107,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46218.39583333334</v>
+        <v>46219.39583333334</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>24.021</v>
       </c>
       <c r="C136">
-        <v>6.827</v>
+        <v>0</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3133,13 +3124,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46218.40625</v>
+        <v>46219.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>0.915</v>
+        <v>7.098</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3150,10 +3141,10 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46218.41666666666</v>
+        <v>46219.41666666666</v>
       </c>
       <c r="B138">
-        <v>7.633</v>
+        <v>1.153</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -3167,13 +3158,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46218.42708333334</v>
+        <v>46219.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
       </c>
       <c r="C139">
-        <v>1.047</v>
+        <v>29.005</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3184,70 +3175,19 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46218.4375</v>
+        <v>46219.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>0.054</v>
+        <v>16.274</v>
       </c>
       <c r="D140">
         <v>43</v>
       </c>
       <c r="E140" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
-      <c r="A141" s="2">
-        <v>46218.44791666666</v>
-      </c>
-      <c r="B141">
-        <v>0</v>
-      </c>
-      <c r="C141">
-        <v>3.38</v>
-      </c>
-      <c r="D141">
-        <v>44</v>
-      </c>
-      <c r="E141" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
-      <c r="A142" s="2">
-        <v>46218.45833333334</v>
-      </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-      <c r="C142">
-        <v>7.757</v>
-      </c>
-      <c r="D142">
-        <v>45</v>
-      </c>
-      <c r="E142" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
-      <c r="A143" s="2">
-        <v>46218.46875</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-      <c r="C143">
-        <v>12.522</v>
-      </c>
-      <c r="D143">
-        <v>46</v>
-      </c>
-      <c r="E143" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="324">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,421 +31,961 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>15.07.20261</t>
-  </si>
-  <si>
-    <t>15.07.20262</t>
-  </si>
-  <si>
-    <t>15.07.20263</t>
-  </si>
-  <si>
-    <t>15.07.20264</t>
-  </si>
-  <si>
-    <t>15.07.20265</t>
-  </si>
-  <si>
-    <t>15.07.20266</t>
-  </si>
-  <si>
-    <t>15.07.20267</t>
-  </si>
-  <si>
-    <t>15.07.20268</t>
-  </si>
-  <si>
-    <t>15.07.20269</t>
-  </si>
-  <si>
-    <t>15.07.202610</t>
-  </si>
-  <si>
-    <t>15.07.202611</t>
-  </si>
-  <si>
-    <t>15.07.202612</t>
-  </si>
-  <si>
-    <t>15.07.202613</t>
-  </si>
-  <si>
-    <t>15.07.202614</t>
-  </si>
-  <si>
-    <t>15.07.202615</t>
-  </si>
-  <si>
-    <t>15.07.202616</t>
-  </si>
-  <si>
-    <t>15.07.202617</t>
-  </si>
-  <si>
-    <t>15.07.202618</t>
-  </si>
-  <si>
-    <t>15.07.202619</t>
-  </si>
-  <si>
-    <t>15.07.202620</t>
-  </si>
-  <si>
-    <t>15.07.202621</t>
-  </si>
-  <si>
-    <t>15.07.202622</t>
-  </si>
-  <si>
-    <t>15.07.202623</t>
-  </si>
-  <si>
-    <t>15.07.202624</t>
-  </si>
-  <si>
-    <t>15.07.202625</t>
-  </si>
-  <si>
-    <t>15.07.202626</t>
-  </si>
-  <si>
-    <t>15.07.202627</t>
-  </si>
-  <si>
-    <t>15.07.202628</t>
-  </si>
-  <si>
-    <t>15.07.202629</t>
-  </si>
-  <si>
-    <t>15.07.202630</t>
-  </si>
-  <si>
-    <t>15.07.202631</t>
-  </si>
-  <si>
-    <t>15.07.202632</t>
-  </si>
-  <si>
-    <t>15.07.202633</t>
-  </si>
-  <si>
-    <t>15.07.202634</t>
-  </si>
-  <si>
-    <t>15.07.202635</t>
-  </si>
-  <si>
-    <t>15.07.202636</t>
-  </si>
-  <si>
-    <t>15.07.202637</t>
-  </si>
-  <si>
-    <t>15.07.202638</t>
-  </si>
-  <si>
-    <t>15.07.202639</t>
-  </si>
-  <si>
-    <t>15.07.202640</t>
-  </si>
-  <si>
-    <t>15.07.202641</t>
-  </si>
-  <si>
-    <t>15.07.202642</t>
-  </si>
-  <si>
-    <t>15.07.202643</t>
-  </si>
-  <si>
-    <t>15.07.202644</t>
-  </si>
-  <si>
-    <t>15.07.202645</t>
-  </si>
-  <si>
-    <t>15.07.202646</t>
-  </si>
-  <si>
-    <t>15.07.202647</t>
-  </si>
-  <si>
-    <t>15.07.202648</t>
-  </si>
-  <si>
-    <t>15.07.202649</t>
-  </si>
-  <si>
-    <t>15.07.202650</t>
-  </si>
-  <si>
-    <t>15.07.202651</t>
-  </si>
-  <si>
-    <t>15.07.202652</t>
-  </si>
-  <si>
-    <t>15.07.202653</t>
-  </si>
-  <si>
-    <t>15.07.202654</t>
-  </si>
-  <si>
-    <t>15.07.202655</t>
-  </si>
-  <si>
-    <t>15.07.202656</t>
-  </si>
-  <si>
-    <t>15.07.202657</t>
-  </si>
-  <si>
-    <t>15.07.202658</t>
-  </si>
-  <si>
-    <t>15.07.202659</t>
-  </si>
-  <si>
-    <t>15.07.202660</t>
-  </si>
-  <si>
-    <t>15.07.202661</t>
-  </si>
-  <si>
-    <t>15.07.202662</t>
-  </si>
-  <si>
-    <t>15.07.202663</t>
-  </si>
-  <si>
-    <t>15.07.202664</t>
-  </si>
-  <si>
-    <t>15.07.202665</t>
-  </si>
-  <si>
-    <t>15.07.202666</t>
-  </si>
-  <si>
-    <t>15.07.202667</t>
-  </si>
-  <si>
-    <t>15.07.202668</t>
-  </si>
-  <si>
-    <t>15.07.202669</t>
-  </si>
-  <si>
-    <t>15.07.202670</t>
-  </si>
-  <si>
-    <t>15.07.202671</t>
-  </si>
-  <si>
-    <t>15.07.202672</t>
-  </si>
-  <si>
-    <t>15.07.202673</t>
-  </si>
-  <si>
-    <t>15.07.202674</t>
-  </si>
-  <si>
-    <t>15.07.202675</t>
-  </si>
-  <si>
-    <t>15.07.202676</t>
-  </si>
-  <si>
-    <t>15.07.202677</t>
-  </si>
-  <si>
-    <t>15.07.202678</t>
-  </si>
-  <si>
-    <t>15.07.202679</t>
-  </si>
-  <si>
-    <t>15.07.202680</t>
-  </si>
-  <si>
-    <t>15.07.202681</t>
-  </si>
-  <si>
-    <t>15.07.202682</t>
-  </si>
-  <si>
-    <t>15.07.202683</t>
-  </si>
-  <si>
-    <t>15.07.202684</t>
-  </si>
-  <si>
-    <t>15.07.202685</t>
-  </si>
-  <si>
-    <t>15.07.202686</t>
-  </si>
-  <si>
-    <t>15.07.202687</t>
-  </si>
-  <si>
-    <t>15.07.202688</t>
-  </si>
-  <si>
-    <t>15.07.202689</t>
-  </si>
-  <si>
-    <t>15.07.202690</t>
-  </si>
-  <si>
-    <t>15.07.202691</t>
-  </si>
-  <si>
-    <t>15.07.202692</t>
-  </si>
-  <si>
-    <t>15.07.202693</t>
-  </si>
-  <si>
-    <t>15.07.202694</t>
-  </si>
-  <si>
-    <t>15.07.202695</t>
-  </si>
-  <si>
-    <t>15.07.202696</t>
-  </si>
-  <si>
-    <t>16.07.20261</t>
-  </si>
-  <si>
-    <t>16.07.20262</t>
-  </si>
-  <si>
-    <t>16.07.20263</t>
-  </si>
-  <si>
-    <t>16.07.20264</t>
-  </si>
-  <si>
-    <t>16.07.20265</t>
-  </si>
-  <si>
-    <t>16.07.20266</t>
-  </si>
-  <si>
-    <t>16.07.20267</t>
-  </si>
-  <si>
-    <t>16.07.20268</t>
-  </si>
-  <si>
-    <t>16.07.20269</t>
-  </si>
-  <si>
-    <t>16.07.202610</t>
-  </si>
-  <si>
-    <t>16.07.202611</t>
-  </si>
-  <si>
-    <t>16.07.202612</t>
-  </si>
-  <si>
-    <t>16.07.202613</t>
-  </si>
-  <si>
-    <t>16.07.202614</t>
-  </si>
-  <si>
-    <t>16.07.202615</t>
-  </si>
-  <si>
-    <t>16.07.202616</t>
-  </si>
-  <si>
-    <t>16.07.202617</t>
-  </si>
-  <si>
-    <t>16.07.202618</t>
-  </si>
-  <si>
-    <t>16.07.202619</t>
-  </si>
-  <si>
-    <t>16.07.202620</t>
-  </si>
-  <si>
-    <t>16.07.202621</t>
-  </si>
-  <si>
-    <t>16.07.202622</t>
-  </si>
-  <si>
-    <t>16.07.202623</t>
-  </si>
-  <si>
-    <t>16.07.202624</t>
-  </si>
-  <si>
-    <t>16.07.202625</t>
-  </si>
-  <si>
-    <t>16.07.202626</t>
-  </si>
-  <si>
-    <t>16.07.202627</t>
-  </si>
-  <si>
-    <t>16.07.202628</t>
-  </si>
-  <si>
-    <t>16.07.202629</t>
-  </si>
-  <si>
-    <t>16.07.202630</t>
-  </si>
-  <si>
-    <t>16.07.202631</t>
-  </si>
-  <si>
-    <t>16.07.202632</t>
-  </si>
-  <si>
-    <t>16.07.202633</t>
-  </si>
-  <si>
-    <t>16.07.202634</t>
-  </si>
-  <si>
-    <t>16.07.202635</t>
-  </si>
-  <si>
-    <t>16.07.202636</t>
-  </si>
-  <si>
-    <t>16.07.202637</t>
-  </si>
-  <si>
-    <t>16.07.202638</t>
-  </si>
-  <si>
-    <t>16.07.202639</t>
-  </si>
-  <si>
-    <t>16.07.202640</t>
-  </si>
-  <si>
-    <t>16.07.202641</t>
-  </si>
-  <si>
-    <t>16.07.202642</t>
-  </si>
-  <si>
-    <t>16.07.202643</t>
+    <t>17.07.20261</t>
+  </si>
+  <si>
+    <t>17.07.20262</t>
+  </si>
+  <si>
+    <t>17.07.20263</t>
+  </si>
+  <si>
+    <t>17.07.20264</t>
+  </si>
+  <si>
+    <t>17.07.20265</t>
+  </si>
+  <si>
+    <t>17.07.20266</t>
+  </si>
+  <si>
+    <t>17.07.20267</t>
+  </si>
+  <si>
+    <t>17.07.20268</t>
+  </si>
+  <si>
+    <t>17.07.20269</t>
+  </si>
+  <si>
+    <t>17.07.202610</t>
+  </si>
+  <si>
+    <t>17.07.202611</t>
+  </si>
+  <si>
+    <t>17.07.202612</t>
+  </si>
+  <si>
+    <t>17.07.202613</t>
+  </si>
+  <si>
+    <t>17.07.202614</t>
+  </si>
+  <si>
+    <t>17.07.202615</t>
+  </si>
+  <si>
+    <t>17.07.202616</t>
+  </si>
+  <si>
+    <t>17.07.202617</t>
+  </si>
+  <si>
+    <t>17.07.202618</t>
+  </si>
+  <si>
+    <t>17.07.202619</t>
+  </si>
+  <si>
+    <t>17.07.202620</t>
+  </si>
+  <si>
+    <t>17.07.202621</t>
+  </si>
+  <si>
+    <t>17.07.202622</t>
+  </si>
+  <si>
+    <t>17.07.202623</t>
+  </si>
+  <si>
+    <t>17.07.202624</t>
+  </si>
+  <si>
+    <t>17.07.202625</t>
+  </si>
+  <si>
+    <t>17.07.202626</t>
+  </si>
+  <si>
+    <t>17.07.202627</t>
+  </si>
+  <si>
+    <t>17.07.202628</t>
+  </si>
+  <si>
+    <t>17.07.202629</t>
+  </si>
+  <si>
+    <t>17.07.202630</t>
+  </si>
+  <si>
+    <t>17.07.202631</t>
+  </si>
+  <si>
+    <t>17.07.202632</t>
+  </si>
+  <si>
+    <t>17.07.202633</t>
+  </si>
+  <si>
+    <t>17.07.202634</t>
+  </si>
+  <si>
+    <t>17.07.202635</t>
+  </si>
+  <si>
+    <t>17.07.202636</t>
+  </si>
+  <si>
+    <t>17.07.202637</t>
+  </si>
+  <si>
+    <t>17.07.202638</t>
+  </si>
+  <si>
+    <t>17.07.202639</t>
+  </si>
+  <si>
+    <t>17.07.202640</t>
+  </si>
+  <si>
+    <t>17.07.202641</t>
+  </si>
+  <si>
+    <t>17.07.202642</t>
+  </si>
+  <si>
+    <t>17.07.202643</t>
+  </si>
+  <si>
+    <t>17.07.202644</t>
+  </si>
+  <si>
+    <t>17.07.202645</t>
+  </si>
+  <si>
+    <t>17.07.202646</t>
+  </si>
+  <si>
+    <t>17.07.202647</t>
+  </si>
+  <si>
+    <t>17.07.202648</t>
+  </si>
+  <si>
+    <t>17.07.202649</t>
+  </si>
+  <si>
+    <t>17.07.202650</t>
+  </si>
+  <si>
+    <t>17.07.202651</t>
+  </si>
+  <si>
+    <t>17.07.202652</t>
+  </si>
+  <si>
+    <t>17.07.202653</t>
+  </si>
+  <si>
+    <t>17.07.202654</t>
+  </si>
+  <si>
+    <t>17.07.202655</t>
+  </si>
+  <si>
+    <t>17.07.202656</t>
+  </si>
+  <si>
+    <t>17.07.202657</t>
+  </si>
+  <si>
+    <t>17.07.202658</t>
+  </si>
+  <si>
+    <t>17.07.202659</t>
+  </si>
+  <si>
+    <t>17.07.202660</t>
+  </si>
+  <si>
+    <t>17.07.202661</t>
+  </si>
+  <si>
+    <t>17.07.202662</t>
+  </si>
+  <si>
+    <t>17.07.202663</t>
+  </si>
+  <si>
+    <t>17.07.202664</t>
+  </si>
+  <si>
+    <t>17.07.202665</t>
+  </si>
+  <si>
+    <t>17.07.202666</t>
+  </si>
+  <si>
+    <t>17.07.202667</t>
+  </si>
+  <si>
+    <t>17.07.202668</t>
+  </si>
+  <si>
+    <t>17.07.202669</t>
+  </si>
+  <si>
+    <t>17.07.202670</t>
+  </si>
+  <si>
+    <t>17.07.202671</t>
+  </si>
+  <si>
+    <t>17.07.202672</t>
+  </si>
+  <si>
+    <t>17.07.202673</t>
+  </si>
+  <si>
+    <t>17.07.202674</t>
+  </si>
+  <si>
+    <t>17.07.202675</t>
+  </si>
+  <si>
+    <t>17.07.202676</t>
+  </si>
+  <si>
+    <t>17.07.202677</t>
+  </si>
+  <si>
+    <t>17.07.202678</t>
+  </si>
+  <si>
+    <t>17.07.202679</t>
+  </si>
+  <si>
+    <t>17.07.202680</t>
+  </si>
+  <si>
+    <t>17.07.202681</t>
+  </si>
+  <si>
+    <t>17.07.202682</t>
+  </si>
+  <si>
+    <t>17.07.202683</t>
+  </si>
+  <si>
+    <t>17.07.202684</t>
+  </si>
+  <si>
+    <t>17.07.202685</t>
+  </si>
+  <si>
+    <t>17.07.202686</t>
+  </si>
+  <si>
+    <t>17.07.202687</t>
+  </si>
+  <si>
+    <t>17.07.202688</t>
+  </si>
+  <si>
+    <t>17.07.202689</t>
+  </si>
+  <si>
+    <t>17.07.202690</t>
+  </si>
+  <si>
+    <t>17.07.202691</t>
+  </si>
+  <si>
+    <t>17.07.202692</t>
+  </si>
+  <si>
+    <t>17.07.202693</t>
+  </si>
+  <si>
+    <t>17.07.202694</t>
+  </si>
+  <si>
+    <t>17.07.202695</t>
+  </si>
+  <si>
+    <t>17.07.202696</t>
+  </si>
+  <si>
+    <t>18.07.20261</t>
+  </si>
+  <si>
+    <t>18.07.20262</t>
+  </si>
+  <si>
+    <t>18.07.20263</t>
+  </si>
+  <si>
+    <t>18.07.20264</t>
+  </si>
+  <si>
+    <t>18.07.20265</t>
+  </si>
+  <si>
+    <t>18.07.20266</t>
+  </si>
+  <si>
+    <t>18.07.20267</t>
+  </si>
+  <si>
+    <t>18.07.20268</t>
+  </si>
+  <si>
+    <t>18.07.20269</t>
+  </si>
+  <si>
+    <t>18.07.202610</t>
+  </si>
+  <si>
+    <t>18.07.202611</t>
+  </si>
+  <si>
+    <t>18.07.202612</t>
+  </si>
+  <si>
+    <t>18.07.202613</t>
+  </si>
+  <si>
+    <t>18.07.202614</t>
+  </si>
+  <si>
+    <t>18.07.202615</t>
+  </si>
+  <si>
+    <t>18.07.202616</t>
+  </si>
+  <si>
+    <t>18.07.202617</t>
+  </si>
+  <si>
+    <t>18.07.202618</t>
+  </si>
+  <si>
+    <t>18.07.202619</t>
+  </si>
+  <si>
+    <t>18.07.202620</t>
+  </si>
+  <si>
+    <t>18.07.202621</t>
+  </si>
+  <si>
+    <t>18.07.202622</t>
+  </si>
+  <si>
+    <t>18.07.202623</t>
+  </si>
+  <si>
+    <t>18.07.202624</t>
+  </si>
+  <si>
+    <t>18.07.202625</t>
+  </si>
+  <si>
+    <t>18.07.202626</t>
+  </si>
+  <si>
+    <t>18.07.202627</t>
+  </si>
+  <si>
+    <t>18.07.202628</t>
+  </si>
+  <si>
+    <t>18.07.202629</t>
+  </si>
+  <si>
+    <t>18.07.202630</t>
+  </si>
+  <si>
+    <t>18.07.202631</t>
+  </si>
+  <si>
+    <t>18.07.202632</t>
+  </si>
+  <si>
+    <t>18.07.202633</t>
+  </si>
+  <si>
+    <t>18.07.202634</t>
+  </si>
+  <si>
+    <t>18.07.202635</t>
+  </si>
+  <si>
+    <t>18.07.202636</t>
+  </si>
+  <si>
+    <t>18.07.202637</t>
+  </si>
+  <si>
+    <t>18.07.202638</t>
+  </si>
+  <si>
+    <t>18.07.202639</t>
+  </si>
+  <si>
+    <t>18.07.202640</t>
+  </si>
+  <si>
+    <t>18.07.202641</t>
+  </si>
+  <si>
+    <t>18.07.202642</t>
+  </si>
+  <si>
+    <t>18.07.202643</t>
+  </si>
+  <si>
+    <t>18.07.202644</t>
+  </si>
+  <si>
+    <t>18.07.202645</t>
+  </si>
+  <si>
+    <t>18.07.202646</t>
+  </si>
+  <si>
+    <t>18.07.202647</t>
+  </si>
+  <si>
+    <t>18.07.202648</t>
+  </si>
+  <si>
+    <t>18.07.202649</t>
+  </si>
+  <si>
+    <t>18.07.202650</t>
+  </si>
+  <si>
+    <t>18.07.202651</t>
+  </si>
+  <si>
+    <t>18.07.202652</t>
+  </si>
+  <si>
+    <t>18.07.202653</t>
+  </si>
+  <si>
+    <t>18.07.202654</t>
+  </si>
+  <si>
+    <t>18.07.202655</t>
+  </si>
+  <si>
+    <t>18.07.202656</t>
+  </si>
+  <si>
+    <t>18.07.202657</t>
+  </si>
+  <si>
+    <t>18.07.202658</t>
+  </si>
+  <si>
+    <t>18.07.202659</t>
+  </si>
+  <si>
+    <t>18.07.202660</t>
+  </si>
+  <si>
+    <t>18.07.202661</t>
+  </si>
+  <si>
+    <t>18.07.202662</t>
+  </si>
+  <si>
+    <t>18.07.202663</t>
+  </si>
+  <si>
+    <t>18.07.202664</t>
+  </si>
+  <si>
+    <t>18.07.202665</t>
+  </si>
+  <si>
+    <t>18.07.202666</t>
+  </si>
+  <si>
+    <t>18.07.202667</t>
+  </si>
+  <si>
+    <t>18.07.202668</t>
+  </si>
+  <si>
+    <t>18.07.202669</t>
+  </si>
+  <si>
+    <t>18.07.202670</t>
+  </si>
+  <si>
+    <t>18.07.202671</t>
+  </si>
+  <si>
+    <t>18.07.202672</t>
+  </si>
+  <si>
+    <t>18.07.202673</t>
+  </si>
+  <si>
+    <t>18.07.202674</t>
+  </si>
+  <si>
+    <t>18.07.202675</t>
+  </si>
+  <si>
+    <t>18.07.202676</t>
+  </si>
+  <si>
+    <t>18.07.202677</t>
+  </si>
+  <si>
+    <t>18.07.202678</t>
+  </si>
+  <si>
+    <t>18.07.202679</t>
+  </si>
+  <si>
+    <t>18.07.202680</t>
+  </si>
+  <si>
+    <t>18.07.202681</t>
+  </si>
+  <si>
+    <t>18.07.202682</t>
+  </si>
+  <si>
+    <t>18.07.202683</t>
+  </si>
+  <si>
+    <t>18.07.202684</t>
+  </si>
+  <si>
+    <t>18.07.202685</t>
+  </si>
+  <si>
+    <t>18.07.202686</t>
+  </si>
+  <si>
+    <t>18.07.202687</t>
+  </si>
+  <si>
+    <t>18.07.202688</t>
+  </si>
+  <si>
+    <t>18.07.202689</t>
+  </si>
+  <si>
+    <t>18.07.202690</t>
+  </si>
+  <si>
+    <t>18.07.202691</t>
+  </si>
+  <si>
+    <t>18.07.202692</t>
+  </si>
+  <si>
+    <t>18.07.202693</t>
+  </si>
+  <si>
+    <t>18.07.202694</t>
+  </si>
+  <si>
+    <t>18.07.202695</t>
+  </si>
+  <si>
+    <t>18.07.202696</t>
+  </si>
+  <si>
+    <t>19.07.20261</t>
+  </si>
+  <si>
+    <t>19.07.20262</t>
+  </si>
+  <si>
+    <t>19.07.20263</t>
+  </si>
+  <si>
+    <t>19.07.20264</t>
+  </si>
+  <si>
+    <t>19.07.20265</t>
+  </si>
+  <si>
+    <t>19.07.20266</t>
+  </si>
+  <si>
+    <t>19.07.20267</t>
+  </si>
+  <si>
+    <t>19.07.20268</t>
+  </si>
+  <si>
+    <t>19.07.20269</t>
+  </si>
+  <si>
+    <t>19.07.202610</t>
+  </si>
+  <si>
+    <t>19.07.202611</t>
+  </si>
+  <si>
+    <t>19.07.202612</t>
+  </si>
+  <si>
+    <t>19.07.202613</t>
+  </si>
+  <si>
+    <t>19.07.202614</t>
+  </si>
+  <si>
+    <t>19.07.202615</t>
+  </si>
+  <si>
+    <t>19.07.202616</t>
+  </si>
+  <si>
+    <t>19.07.202617</t>
+  </si>
+  <si>
+    <t>19.07.202618</t>
+  </si>
+  <si>
+    <t>19.07.202619</t>
+  </si>
+  <si>
+    <t>19.07.202620</t>
+  </si>
+  <si>
+    <t>19.07.202621</t>
+  </si>
+  <si>
+    <t>19.07.202622</t>
+  </si>
+  <si>
+    <t>19.07.202623</t>
+  </si>
+  <si>
+    <t>19.07.202624</t>
+  </si>
+  <si>
+    <t>19.07.202625</t>
+  </si>
+  <si>
+    <t>19.07.202626</t>
+  </si>
+  <si>
+    <t>19.07.202627</t>
+  </si>
+  <si>
+    <t>19.07.202628</t>
+  </si>
+  <si>
+    <t>19.07.202629</t>
+  </si>
+  <si>
+    <t>19.07.202630</t>
+  </si>
+  <si>
+    <t>19.07.202631</t>
+  </si>
+  <si>
+    <t>19.07.202632</t>
+  </si>
+  <si>
+    <t>19.07.202633</t>
+  </si>
+  <si>
+    <t>19.07.202634</t>
+  </si>
+  <si>
+    <t>19.07.202635</t>
+  </si>
+  <si>
+    <t>19.07.202636</t>
+  </si>
+  <si>
+    <t>19.07.202637</t>
+  </si>
+  <si>
+    <t>19.07.202638</t>
+  </si>
+  <si>
+    <t>19.07.202639</t>
+  </si>
+  <si>
+    <t>19.07.202640</t>
+  </si>
+  <si>
+    <t>19.07.202641</t>
+  </si>
+  <si>
+    <t>19.07.202642</t>
+  </si>
+  <si>
+    <t>19.07.202643</t>
+  </si>
+  <si>
+    <t>19.07.202644</t>
+  </si>
+  <si>
+    <t>19.07.202645</t>
+  </si>
+  <si>
+    <t>19.07.202646</t>
+  </si>
+  <si>
+    <t>19.07.202647</t>
+  </si>
+  <si>
+    <t>19.07.202648</t>
+  </si>
+  <si>
+    <t>19.07.202649</t>
+  </si>
+  <si>
+    <t>19.07.202650</t>
+  </si>
+  <si>
+    <t>19.07.202651</t>
+  </si>
+  <si>
+    <t>19.07.202652</t>
+  </si>
+  <si>
+    <t>19.07.202653</t>
+  </si>
+  <si>
+    <t>19.07.202654</t>
+  </si>
+  <si>
+    <t>19.07.202655</t>
+  </si>
+  <si>
+    <t>19.07.202656</t>
+  </si>
+  <si>
+    <t>19.07.202657</t>
+  </si>
+  <si>
+    <t>19.07.202658</t>
+  </si>
+  <si>
+    <t>19.07.202659</t>
+  </si>
+  <si>
+    <t>19.07.202660</t>
+  </si>
+  <si>
+    <t>19.07.202661</t>
+  </si>
+  <si>
+    <t>19.07.202662</t>
+  </si>
+  <si>
+    <t>19.07.202663</t>
+  </si>
+  <si>
+    <t>19.07.202664</t>
+  </si>
+  <si>
+    <t>19.07.202665</t>
+  </si>
+  <si>
+    <t>19.07.202666</t>
+  </si>
+  <si>
+    <t>19.07.202667</t>
+  </si>
+  <si>
+    <t>19.07.202668</t>
+  </si>
+  <si>
+    <t>19.07.202669</t>
+  </si>
+  <si>
+    <t>19.07.202670</t>
+  </si>
+  <si>
+    <t>19.07.202671</t>
+  </si>
+  <si>
+    <t>19.07.202672</t>
+  </si>
+  <si>
+    <t>19.07.202673</t>
+  </si>
+  <si>
+    <t>19.07.202674</t>
+  </si>
+  <si>
+    <t>19.07.202675</t>
+  </si>
+  <si>
+    <t>19.07.202676</t>
+  </si>
+  <si>
+    <t>19.07.202677</t>
+  </si>
+  <si>
+    <t>19.07.202678</t>
+  </si>
+  <si>
+    <t>19.07.202679</t>
+  </si>
+  <si>
+    <t>19.07.202680</t>
+  </si>
+  <si>
+    <t>19.07.202681</t>
+  </si>
+  <si>
+    <t>19.07.202682</t>
+  </si>
+  <si>
+    <t>19.07.202683</t>
+  </si>
+  <si>
+    <t>19.07.202684</t>
+  </si>
+  <si>
+    <t>19.07.202685</t>
+  </si>
+  <si>
+    <t>19.07.202686</t>
+  </si>
+  <si>
+    <t>19.07.202687</t>
+  </si>
+  <si>
+    <t>19.07.202688</t>
+  </si>
+  <si>
+    <t>19.07.202689</t>
+  </si>
+  <si>
+    <t>19.07.202690</t>
+  </si>
+  <si>
+    <t>19.07.202691</t>
+  </si>
+  <si>
+    <t>19.07.202692</t>
+  </si>
+  <si>
+    <t>19.07.202693</t>
+  </si>
+  <si>
+    <t>19.07.202694</t>
+  </si>
+  <si>
+    <t>19.07.202695</t>
+  </si>
+  <si>
+    <t>19.07.202696</t>
+  </si>
+  <si>
+    <t>20.07.20261</t>
+  </si>
+  <si>
+    <t>20.07.20262</t>
+  </si>
+  <si>
+    <t>20.07.20263</t>
+  </si>
+  <si>
+    <t>20.07.20264</t>
+  </si>
+  <si>
+    <t>20.07.20265</t>
+  </si>
+  <si>
+    <t>20.07.20266</t>
+  </si>
+  <si>
+    <t>20.07.20267</t>
+  </si>
+  <si>
+    <t>20.07.20268</t>
+  </si>
+  <si>
+    <t>20.07.20269</t>
+  </si>
+  <si>
+    <t>20.07.202610</t>
+  </si>
+  <si>
+    <t>20.07.202611</t>
+  </si>
+  <si>
+    <t>20.07.202612</t>
+  </si>
+  <si>
+    <t>20.07.202613</t>
+  </si>
+  <si>
+    <t>20.07.202614</t>
+  </si>
+  <si>
+    <t>20.07.202615</t>
+  </si>
+  <si>
+    <t>20.07.202616</t>
+  </si>
+  <si>
+    <t>20.07.202617</t>
+  </si>
+  <si>
+    <t>20.07.202618</t>
+  </si>
+  <si>
+    <t>20.07.202619</t>
+  </si>
+  <si>
+    <t>20.07.202620</t>
+  </si>
+  <si>
+    <t>20.07.202621</t>
+  </si>
+  <si>
+    <t>20.07.202622</t>
+  </si>
+  <si>
+    <t>20.07.202623</t>
+  </si>
+  <si>
+    <t>20.07.202624</t>
+  </si>
+  <si>
+    <t>20.07.202625</t>
+  </si>
+  <si>
+    <t>20.07.202626</t>
+  </si>
+  <si>
+    <t>20.07.202627</t>
+  </si>
+  <si>
+    <t>20.07.202628</t>
+  </si>
+  <si>
+    <t>20.07.202629</t>
+  </si>
+  <si>
+    <t>20.07.202630</t>
+  </si>
+  <si>
+    <t>20.07.202631</t>
   </si>
 </sst>
 </file>
@@ -807,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E320"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -829,13 +1369,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>30.782</v>
+        <v>0.48</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -846,13 +1386,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46218.01041666666</v>
+        <v>46220.01041666666</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>25.742</v>
+        <v>6.055</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -863,13 +1403,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46218.02083333334</v>
+        <v>46220.02083333334</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="C4">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -880,13 +1420,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46218.03125</v>
+        <v>46220.03125</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>4.767</v>
       </c>
       <c r="C5">
-        <v>20.968</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -897,13 +1437,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46218.04166666666</v>
+        <v>46220.04166666666</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>14.801</v>
       </c>
       <c r="C6">
-        <v>1.288</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -914,13 +1454,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46218.05208333334</v>
+        <v>46220.05208333334</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>24.342</v>
       </c>
       <c r="C7">
-        <v>6.364</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -931,13 +1471,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46218.0625</v>
+        <v>46220.0625</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>9.113</v>
       </c>
       <c r="C8">
-        <v>1.235</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -948,13 +1488,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46218.07291666666</v>
+        <v>46220.07291666666</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>15.325</v>
       </c>
       <c r="C9">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -965,10 +1505,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46218.08333333334</v>
+        <v>46220.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.433</v>
+        <v>10.725</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -982,10 +1522,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46218.09375</v>
+        <v>46220.09375</v>
       </c>
       <c r="B11">
-        <v>0.096</v>
+        <v>11.308</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -999,13 +1539,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46218.10416666666</v>
+        <v>46220.10416666666</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>3.522</v>
       </c>
       <c r="C12">
-        <v>3.208</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -1016,13 +1556,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46218.11458333334</v>
+        <v>46220.11458333334</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13">
-        <v>2.254</v>
+        <v>5.502</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1033,13 +1573,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46218.125</v>
+        <v>46220.125</v>
       </c>
       <c r="B14">
-        <v>11.106</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>8.561</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1050,10 +1590,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46218.13541666666</v>
+        <v>46220.13541666666</v>
       </c>
       <c r="B15">
-        <v>16.401</v>
+        <v>0.398</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1067,13 +1607,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46218.14583333334</v>
+        <v>46220.14583333334</v>
       </c>
       <c r="B16">
-        <v>8.673</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>12.401</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1084,13 +1624,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46218.15625</v>
+        <v>46220.15625</v>
       </c>
       <c r="B17">
-        <v>2.503</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1.847</v>
       </c>
       <c r="D17">
         <v>16</v>
@@ -1101,13 +1641,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46218.16666666666</v>
+        <v>46220.16666666666</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18">
-        <v>4.218</v>
+        <v>6.877</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1118,13 +1658,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46218.17708333334</v>
+        <v>46220.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>0.736</v>
       </c>
       <c r="C19">
-        <v>4.316</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1135,10 +1675,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46218.1875</v>
+        <v>46220.1875</v>
       </c>
       <c r="B20">
-        <v>5.679</v>
+        <v>3.861</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1152,13 +1692,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46218.19791666666</v>
+        <v>46220.19791666666</v>
       </c>
       <c r="B21">
-        <v>4.786</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.895</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1169,10 +1709,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46218.20833333334</v>
+        <v>46220.20833333334</v>
       </c>
       <c r="B22">
-        <v>0.63</v>
+        <v>12.798</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1186,10 +1726,10 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46218.21875</v>
+        <v>46220.21875</v>
       </c>
       <c r="B23">
-        <v>6.049</v>
+        <v>12.799</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1203,13 +1743,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46218.22916666666</v>
+        <v>46220.22916666666</v>
       </c>
       <c r="B24">
-        <v>11.808</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1.219</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1220,10 +1760,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46218.23958333334</v>
+        <v>46220.23958333334</v>
       </c>
       <c r="B25">
-        <v>26.998</v>
+        <v>1.655</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1237,13 +1777,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46218.25</v>
+        <v>46220.25</v>
       </c>
       <c r="B26">
-        <v>11.056</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>3.256</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1254,13 +1794,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46218.26041666666</v>
+        <v>46220.26041666666</v>
       </c>
       <c r="B27">
-        <v>9.727</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>4.499</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1271,13 +1811,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46218.27083333334</v>
+        <v>46220.27083333334</v>
       </c>
       <c r="B28">
-        <v>26.099</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1.836</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1288,13 +1828,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46218.28125</v>
+        <v>46220.28125</v>
       </c>
       <c r="B29">
-        <v>23.212</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>51.897</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1305,13 +1845,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46218.29166666666</v>
+        <v>46220.29166666666</v>
       </c>
       <c r="B30">
-        <v>36.776</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>16.555</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1322,13 +1862,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46218.30208333334</v>
+        <v>46220.30208333334</v>
       </c>
       <c r="B31">
-        <v>22.255</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>14.036</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1339,13 +1879,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46218.3125</v>
+        <v>46220.3125</v>
       </c>
       <c r="B32">
-        <v>7.246</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>28.169</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1356,13 +1896,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46218.32291666666</v>
+        <v>46220.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>17.011</v>
+        <v>36.444</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1373,13 +1913,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46218.33333333334</v>
+        <v>46220.33333333334</v>
       </c>
       <c r="B34">
-        <v>9.131</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>24.235</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1390,13 +1930,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46218.34375</v>
+        <v>46220.34375</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>2.069</v>
+        <v>37.395</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1407,13 +1947,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46218.35416666666</v>
+        <v>46220.35416666666</v>
       </c>
       <c r="B36">
-        <v>4.778</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>28.072</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1424,13 +1964,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46218.36458333334</v>
+        <v>46220.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>4.058</v>
+        <v>17.978</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1441,13 +1981,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46218.375</v>
+        <v>46220.375</v>
       </c>
       <c r="B38">
-        <v>3.478</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>12.545</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1458,13 +1998,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46218.38541666666</v>
+        <v>46220.38541666666</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>5.992</v>
+        <v>9.143000000000001</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1475,13 +2015,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46218.39583333334</v>
+        <v>46220.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>6.827</v>
+        <v>13.009</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1492,13 +2032,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46218.40625</v>
+        <v>46220.40625</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0.915</v>
+        <v>23.624</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1509,13 +2049,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46218.41666666666</v>
+        <v>46220.41666666666</v>
       </c>
       <c r="B42">
-        <v>7.633</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>2.791</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1526,13 +2066,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46218.42708333334</v>
+        <v>46220.42708333334</v>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>1.047</v>
+        <v>3.534</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1543,13 +2083,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46218.4375</v>
+        <v>46220.4375</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>0.054</v>
+        <v>28.954</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1560,13 +2100,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46218.44791666666</v>
+        <v>46220.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>3.38</v>
+        <v>44.85</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1577,13 +2117,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46218.45833333334</v>
+        <v>46220.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>7.757</v>
+        <v>31.04</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1594,13 +2134,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46218.46875</v>
+        <v>46220.46875</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>12.522</v>
+        <v>12.208</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1611,13 +2151,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46218.47916666666</v>
+        <v>46220.47916666666</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>28.895</v>
+        <v>23.661</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1628,13 +2168,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46218.48958333334</v>
+        <v>46220.48958333334</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>6.419</v>
       </c>
       <c r="C49">
-        <v>29.128</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1645,13 +2185,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46218.5</v>
+        <v>46220.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>9.364000000000001</v>
       </c>
       <c r="C50">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1662,10 +2202,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46218.51041666666</v>
+        <v>46220.51041666666</v>
       </c>
       <c r="B51">
-        <v>3.333</v>
+        <v>6.447</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1679,10 +2219,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46218.52083333334</v>
+        <v>46220.52083333334</v>
       </c>
       <c r="B52">
-        <v>25.55</v>
+        <v>2.348</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -1696,10 +2236,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46218.53125</v>
+        <v>46220.53125</v>
       </c>
       <c r="B53">
-        <v>23.953</v>
+        <v>2.576</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1713,13 +2253,13 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46218.54166666666</v>
+        <v>46220.54166666666</v>
       </c>
       <c r="B54">
-        <v>12.516</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>37.302</v>
       </c>
       <c r="D54">
         <v>53</v>
@@ -1730,13 +2270,13 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46218.55208333334</v>
+        <v>46220.55208333334</v>
       </c>
       <c r="B55">
-        <v>40.006</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>59.697</v>
       </c>
       <c r="D55">
         <v>54</v>
@@ -1747,13 +2287,13 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46218.5625</v>
+        <v>46220.5625</v>
       </c>
       <c r="B56">
-        <v>58.11</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>19.82</v>
       </c>
       <c r="D56">
         <v>55</v>
@@ -1764,13 +2304,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46218.57291666666</v>
+        <v>46220.57291666666</v>
       </c>
       <c r="B57">
-        <v>94.247</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>6.796</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1781,13 +2321,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46218.58333333334</v>
+        <v>46220.58333333334</v>
       </c>
       <c r="B58">
-        <v>86.714</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>26.032</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1798,13 +2338,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46218.59375</v>
+        <v>46220.59375</v>
       </c>
       <c r="B59">
-        <v>60.502</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>57.971</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1815,13 +2355,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46218.60416666666</v>
+        <v>46220.60416666666</v>
       </c>
       <c r="B60">
-        <v>36.123</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>22.681</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1832,13 +2372,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46218.61458333334</v>
+        <v>46220.61458333334</v>
       </c>
       <c r="B61">
-        <v>48.475</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>22.316</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1849,13 +2389,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46218.625</v>
+        <v>46220.625</v>
       </c>
       <c r="B62">
-        <v>97.893</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>53.059</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -1866,13 +2406,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46218.63541666666</v>
+        <v>46220.63541666666</v>
       </c>
       <c r="B63">
-        <v>90.57299999999999</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>27.111</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1883,13 +2423,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46218.64583333334</v>
+        <v>46220.64583333334</v>
       </c>
       <c r="B64">
-        <v>59.375</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>6.607</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -1900,13 +2440,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46218.65625</v>
+        <v>46220.65625</v>
       </c>
       <c r="B65">
-        <v>41.43</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>15.932</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -1917,13 +2457,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46218.66666666666</v>
+        <v>46220.66666666666</v>
       </c>
       <c r="B66">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>25.179</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -1934,13 +2474,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46218.67708333334</v>
+        <v>46220.67708333334</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>22.613</v>
+        <v>22.987</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1951,13 +2491,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46218.6875</v>
+        <v>46220.6875</v>
       </c>
       <c r="B68">
-        <v>17.423</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>0.536</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -1968,10 +2508,10 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46218.69791666666</v>
+        <v>46220.69791666666</v>
       </c>
       <c r="B69">
-        <v>39.054</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -1985,13 +2525,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46218.70833333334</v>
+        <v>46220.70833333334</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>29.61</v>
+        <v>1.794</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -2002,13 +2542,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46218.71875</v>
+        <v>46220.71875</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>15.82</v>
       </c>
       <c r="C71">
-        <v>4.131</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -2019,10 +2559,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46218.72916666666</v>
+        <v>46220.72916666666</v>
       </c>
       <c r="B72">
-        <v>0.5679999999999999</v>
+        <v>11.03</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2036,10 +2576,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46218.73958333334</v>
+        <v>46220.73958333334</v>
       </c>
       <c r="B73">
-        <v>2.347</v>
+        <v>3.025</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2053,10 +2593,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46218.75</v>
+        <v>46220.75</v>
       </c>
       <c r="B74">
-        <v>30.877</v>
+        <v>4.699</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2070,10 +2610,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46218.76041666666</v>
+        <v>46220.76041666666</v>
       </c>
       <c r="B75">
-        <v>18.074</v>
+        <v>5.65</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2087,10 +2627,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46218.77083333334</v>
+        <v>46220.77083333334</v>
       </c>
       <c r="B76">
-        <v>3.743</v>
+        <v>2.951</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2104,10 +2644,10 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46218.78125</v>
+        <v>46220.78125</v>
       </c>
       <c r="B77">
-        <v>0.741</v>
+        <v>1.823</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2121,13 +2661,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46218.79166666666</v>
+        <v>46220.79166666666</v>
       </c>
       <c r="B78">
-        <v>1.588</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>28.748</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2138,13 +2678,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46218.80208333334</v>
+        <v>46220.80208333334</v>
       </c>
       <c r="B79">
-        <v>16.383</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>61.64</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2155,13 +2695,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46218.8125</v>
+        <v>46220.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>5.016</v>
+        <v>21.882</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2172,13 +2712,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46218.82291666666</v>
+        <v>46220.82291666666</v>
       </c>
       <c r="B81">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>6.149</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2189,13 +2729,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46218.83333333334</v>
+        <v>46220.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>15.1</v>
+        <v>1.962</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2206,13 +2746,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46218.84375</v>
+        <v>46220.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>24.172</v>
+        <v>1.26</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2223,13 +2763,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46218.85416666666</v>
+        <v>46220.85416666666</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>9.786</v>
       </c>
       <c r="C84">
-        <v>14.439</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2240,13 +2780,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46218.86458333334</v>
+        <v>46220.86458333334</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="C85">
-        <v>21.278</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2257,13 +2797,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46218.875</v>
+        <v>46220.875</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
       <c r="C86">
-        <v>4.707</v>
+        <v>44.022</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2274,13 +2814,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46218.88541666666</v>
+        <v>46220.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>1.473</v>
+        <v>40.288</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2291,13 +2831,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46218.89583333334</v>
+        <v>46220.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>12.382</v>
+        <v>65.17400000000001</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2308,13 +2848,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46218.90625</v>
+        <v>46220.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>35.295</v>
+        <v>59.182</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2325,13 +2865,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46218.91666666666</v>
+        <v>46220.91666666666</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>6.288</v>
+        <v>9.747999999999999</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2342,13 +2882,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46218.92708333334</v>
+        <v>46220.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>2.141</v>
+        <v>6.375</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2359,13 +2899,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46218.9375</v>
+        <v>46220.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>1.698</v>
+        <v>1.018</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2376,13 +2916,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46218.94791666666</v>
+        <v>46220.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>12.323</v>
+        <v>17.702</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2393,13 +2933,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46218.95833333334</v>
+        <v>46220.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>3.471</v>
       </c>
       <c r="C94">
-        <v>8.805</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2410,13 +2950,13 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46218.96875</v>
+        <v>46220.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>4.898</v>
       </c>
       <c r="C95">
-        <v>16.389</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>94</v>
@@ -2427,13 +2967,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46218.97916666666</v>
+        <v>46220.97916666666</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>16.461</v>
+        <v>3.95</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2444,13 +2984,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46218.98958333334</v>
+        <v>46220.98958333334</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>7.629</v>
       </c>
       <c r="C97">
-        <v>5.379</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2461,10 +3001,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="B98">
-        <v>2.672</v>
+        <v>1.822</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2478,13 +3018,13 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46219.01041666666</v>
+        <v>46221.01041666666</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>6.232</v>
       </c>
       <c r="C99">
-        <v>6.122</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -2495,13 +3035,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46219.02083333334</v>
+        <v>46221.02083333334</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100">
-        <v>5.665</v>
+        <v>8.721</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2512,13 +3052,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46219.03125</v>
+        <v>46221.03125</v>
       </c>
       <c r="B101">
-        <v>5.648</v>
+        <v>0</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>7.745</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2529,13 +3069,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46219.04166666666</v>
+        <v>46221.04166666666</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>10.592</v>
       </c>
       <c r="C102">
-        <v>2.252</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2546,10 +3086,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46219.05208333334</v>
+        <v>46221.05208333334</v>
       </c>
       <c r="B103">
-        <v>0.6929999999999999</v>
+        <v>16.903</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2563,13 +3103,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46219.0625</v>
+        <v>46221.0625</v>
       </c>
       <c r="B104">
-        <v>4.565</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>0.888</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2580,13 +3120,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46219.07291666666</v>
+        <v>46221.07291666666</v>
       </c>
       <c r="B105">
-        <v>2.544</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>0.908</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2597,10 +3137,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46219.08333333334</v>
+        <v>46221.08333333334</v>
       </c>
       <c r="B106">
-        <v>5.02</v>
+        <v>20.611</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2614,10 +3154,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46219.09375</v>
+        <v>46221.09375</v>
       </c>
       <c r="B107">
-        <v>1.492</v>
+        <v>22.533</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -2631,10 +3171,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46219.10416666666</v>
+        <v>46221.10416666666</v>
       </c>
       <c r="B108">
-        <v>1.452</v>
+        <v>25.963</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -2648,13 +3188,13 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46219.11458333334</v>
+        <v>46221.11458333334</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>15.558</v>
       </c>
       <c r="C109">
-        <v>8.948</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -2665,13 +3205,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46219.125</v>
+        <v>46221.125</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>4.759</v>
       </c>
       <c r="C110">
-        <v>6.162</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2682,13 +3222,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46219.13541666666</v>
+        <v>46221.13541666666</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>9.651999999999999</v>
       </c>
       <c r="C111">
-        <v>2.589</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2699,13 +3239,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46219.14583333334</v>
+        <v>46221.14583333334</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>16.706</v>
       </c>
       <c r="C112">
-        <v>3.494</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2716,13 +3256,13 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46219.15625</v>
+        <v>46221.15625</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>26.612</v>
       </c>
       <c r="C113">
-        <v>3.717</v>
+        <v>0</v>
       </c>
       <c r="D113">
         <v>16</v>
@@ -2733,10 +3273,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46219.16666666666</v>
+        <v>46221.16666666666</v>
       </c>
       <c r="B114">
-        <v>2.398</v>
+        <v>2.36</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2750,10 +3290,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46219.17708333334</v>
+        <v>46221.17708333334</v>
       </c>
       <c r="B115">
-        <v>9.445</v>
+        <v>1.691</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2767,10 +3307,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46219.1875</v>
+        <v>46221.1875</v>
       </c>
       <c r="B116">
-        <v>1.552</v>
+        <v>1.668</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -2784,13 +3324,13 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46219.19791666666</v>
+        <v>46221.19791666666</v>
       </c>
       <c r="B117">
-        <v>9.500999999999999</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>2.279</v>
       </c>
       <c r="D117">
         <v>20</v>
@@ -2801,10 +3341,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46219.20833333334</v>
+        <v>46221.20833333334</v>
       </c>
       <c r="B118">
-        <v>19.701</v>
+        <v>8.558999999999999</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -2818,10 +3358,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46219.21875</v>
+        <v>46221.21875</v>
       </c>
       <c r="B119">
-        <v>15.906</v>
+        <v>1.707</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -2835,10 +3375,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46219.22916666666</v>
+        <v>46221.22916666666</v>
       </c>
       <c r="B120">
-        <v>24.117</v>
+        <v>9.121</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -2852,10 +3392,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46219.23958333334</v>
+        <v>46221.23958333334</v>
       </c>
       <c r="B121">
-        <v>17.229</v>
+        <v>12.516</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -2869,10 +3409,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46219.25</v>
+        <v>46221.25</v>
       </c>
       <c r="B122">
-        <v>11.659</v>
+        <v>11.431</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -2886,10 +3426,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46219.26041666666</v>
+        <v>46221.26041666666</v>
       </c>
       <c r="B123">
-        <v>10.831</v>
+        <v>13.831</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -2903,13 +3443,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46219.27083333334</v>
+        <v>46221.27083333334</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="C124">
-        <v>1.791</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2920,10 +3460,10 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46219.28125</v>
+        <v>46221.28125</v>
       </c>
       <c r="B125">
-        <v>13.397</v>
+        <v>2.524</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -2937,10 +3477,10 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46219.29166666666</v>
+        <v>46221.29166666666</v>
       </c>
       <c r="B126">
-        <v>7.179</v>
+        <v>3.714</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -2954,13 +3494,13 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46219.30208333334</v>
+        <v>46221.30208333334</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>8.074</v>
       </c>
       <c r="C127">
-        <v>5.164</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>30</v>
@@ -2971,10 +3511,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="2">
-        <v>46219.3125</v>
+        <v>46221.3125</v>
       </c>
       <c r="B128">
-        <v>5.459</v>
+        <v>9.076000000000001</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -2988,10 +3528,10 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="2">
-        <v>46219.32291666666</v>
+        <v>46221.32291666666</v>
       </c>
       <c r="B129">
-        <v>8.486000000000001</v>
+        <v>6.077</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -3005,10 +3545,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="2">
-        <v>46219.33333333334</v>
+        <v>46221.33333333334</v>
       </c>
       <c r="B130">
-        <v>7.194</v>
+        <v>16.003</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -3022,10 +3562,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="2">
-        <v>46219.34375</v>
+        <v>46221.34375</v>
       </c>
       <c r="B131">
-        <v>7.304</v>
+        <v>5.305</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -3039,10 +3579,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="2">
-        <v>46219.35416666666</v>
+        <v>46221.35416666666</v>
       </c>
       <c r="B132">
-        <v>2.516</v>
+        <v>6.212</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -3056,13 +3596,13 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="2">
-        <v>46219.36458333334</v>
+        <v>46221.36458333334</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>1.73</v>
+        <v>7.635</v>
       </c>
       <c r="D133">
         <v>36</v>
@@ -3073,10 +3613,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="2">
-        <v>46219.375</v>
+        <v>46221.375</v>
       </c>
       <c r="B134">
-        <v>32.139</v>
+        <v>8.781000000000001</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -3090,13 +3630,13 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="2">
-        <v>46219.38541666666</v>
+        <v>46221.38541666666</v>
       </c>
       <c r="B135">
-        <v>17.156</v>
+        <v>0</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="D135">
         <v>38</v>
@@ -3107,13 +3647,13 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="2">
-        <v>46219.39583333334</v>
+        <v>46221.39583333334</v>
       </c>
       <c r="B136">
-        <v>24.021</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="D136">
         <v>39</v>
@@ -3124,13 +3664,13 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="2">
-        <v>46219.40625</v>
+        <v>46221.40625</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
       <c r="C137">
-        <v>7.098</v>
+        <v>33.909</v>
       </c>
       <c r="D137">
         <v>40</v>
@@ -3141,13 +3681,13 @@
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="2">
-        <v>46219.41666666666</v>
+        <v>46221.41666666666</v>
       </c>
       <c r="B138">
-        <v>1.153</v>
+        <v>0</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>4.814</v>
       </c>
       <c r="D138">
         <v>41</v>
@@ -3158,13 +3698,13 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="2">
-        <v>46219.42708333334</v>
+        <v>46221.42708333334</v>
       </c>
       <c r="B139">
         <v>0</v>
       </c>
       <c r="C139">
-        <v>29.005</v>
+        <v>1.206</v>
       </c>
       <c r="D139">
         <v>42</v>
@@ -3175,19 +3715,3079 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2">
-        <v>46219.4375</v>
+        <v>46221.4375</v>
       </c>
       <c r="B140">
         <v>0</v>
       </c>
       <c r="C140">
-        <v>16.274</v>
+        <v>8.397</v>
       </c>
       <c r="D140">
         <v>43</v>
       </c>
       <c r="E140" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="2">
+        <v>46221.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>4.242</v>
+      </c>
+      <c r="D141">
+        <v>44</v>
+      </c>
+      <c r="E141" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="2">
+        <v>46221.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142">
+        <v>8.69</v>
+      </c>
+      <c r="D142">
+        <v>45</v>
+      </c>
+      <c r="E142" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="2">
+        <v>46221.46875</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <v>5.441</v>
+      </c>
+      <c r="D143">
+        <v>46</v>
+      </c>
+      <c r="E143" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="2">
+        <v>46221.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>6.69</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>47</v>
+      </c>
+      <c r="E144" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" s="2">
+        <v>46221.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>10.293</v>
+      </c>
+      <c r="D145">
+        <v>48</v>
+      </c>
+      <c r="E145" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" s="2">
+        <v>46221.5</v>
+      </c>
+      <c r="B146">
+        <v>4.879</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>49</v>
+      </c>
+      <c r="E146" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" s="2">
+        <v>46221.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>8.196999999999999</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>50</v>
+      </c>
+      <c r="E147" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="2">
+        <v>46221.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>3.974</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>51</v>
+      </c>
+      <c r="E148" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" s="2">
+        <v>46221.53125</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+      <c r="C149">
+        <v>11.161</v>
+      </c>
+      <c r="D149">
+        <v>52</v>
+      </c>
+      <c r="E149" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="2">
+        <v>46221.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>3.586</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150">
+        <v>53</v>
+      </c>
+      <c r="E150" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="2">
+        <v>46221.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>30.181</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151">
+        <v>54</v>
+      </c>
+      <c r="E151" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="2">
+        <v>46221.5625</v>
+      </c>
+      <c r="B152">
+        <v>39.79</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152">
+        <v>55</v>
+      </c>
+      <c r="E152" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="2">
+        <v>46221.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>38.183</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <v>56</v>
+      </c>
+      <c r="E153" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="2">
+        <v>46221.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>22.328</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154">
+        <v>57</v>
+      </c>
+      <c r="E154" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="2">
+        <v>46221.59375</v>
+      </c>
+      <c r="B155">
+        <v>50.884</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155">
+        <v>58</v>
+      </c>
+      <c r="E155" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="2">
+        <v>46221.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>76.913</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156">
+        <v>59</v>
+      </c>
+      <c r="E156" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="2">
+        <v>46221.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>27.613</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157">
+        <v>60</v>
+      </c>
+      <c r="E157" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="2">
+        <v>46221.625</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+      <c r="C158">
+        <v>11.01</v>
+      </c>
+      <c r="D158">
+        <v>61</v>
+      </c>
+      <c r="E158" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="2">
+        <v>46221.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+      <c r="C159">
+        <v>38.093</v>
+      </c>
+      <c r="D159">
+        <v>62</v>
+      </c>
+      <c r="E159" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" s="2">
+        <v>46221.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+      <c r="C160">
+        <v>26.357</v>
+      </c>
+      <c r="D160">
+        <v>63</v>
+      </c>
+      <c r="E160" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="2">
+        <v>46221.65625</v>
+      </c>
+      <c r="B161">
+        <v>3.248</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161">
+        <v>64</v>
+      </c>
+      <c r="E161" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="2">
+        <v>46221.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>19.074</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+      <c r="D162">
+        <v>65</v>
+      </c>
+      <c r="E162" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="2">
+        <v>46221.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>3.419</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <v>66</v>
+      </c>
+      <c r="E163" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="2">
+        <v>46221.6875</v>
+      </c>
+      <c r="B164">
+        <v>19.226</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+      <c r="D164">
+        <v>67</v>
+      </c>
+      <c r="E164" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="2">
+        <v>46221.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>7.556</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+      <c r="D165">
+        <v>68</v>
+      </c>
+      <c r="E165" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="2">
+        <v>46221.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+      <c r="C166">
+        <v>6.695</v>
+      </c>
+      <c r="D166">
+        <v>69</v>
+      </c>
+      <c r="E166" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="2">
+        <v>46221.71875</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+      <c r="C167">
+        <v>1.043</v>
+      </c>
+      <c r="D167">
+        <v>70</v>
+      </c>
+      <c r="E167" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="2">
+        <v>46221.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>9.345000000000001</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168">
+        <v>71</v>
+      </c>
+      <c r="E168" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="2">
+        <v>46221.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>26.82</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+      <c r="D169">
+        <v>72</v>
+      </c>
+      <c r="E169" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="2">
+        <v>46221.75</v>
+      </c>
+      <c r="B170">
+        <v>10.296</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+      <c r="D170">
+        <v>73</v>
+      </c>
+      <c r="E170" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="2">
+        <v>46221.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>3.493</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171">
+        <v>74</v>
+      </c>
+      <c r="E171" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="2">
+        <v>46221.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>4.969</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
+      <c r="D172">
+        <v>75</v>
+      </c>
+      <c r="E172" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="2">
+        <v>46221.78125</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>0.083</v>
+      </c>
+      <c r="D173">
+        <v>76</v>
+      </c>
+      <c r="E173" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="2">
+        <v>46221.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+      <c r="C174">
+        <v>9.026</v>
+      </c>
+      <c r="D174">
+        <v>77</v>
+      </c>
+      <c r="E174" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="2">
+        <v>46221.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+      <c r="C175">
+        <v>6.07</v>
+      </c>
+      <c r="D175">
+        <v>78</v>
+      </c>
+      <c r="E175" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="2">
+        <v>46221.8125</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+      <c r="C176">
+        <v>10.829</v>
+      </c>
+      <c r="D176">
+        <v>79</v>
+      </c>
+      <c r="E176" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="2">
+        <v>46221.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+      <c r="C177">
+        <v>3.093</v>
+      </c>
+      <c r="D177">
+        <v>80</v>
+      </c>
+      <c r="E177" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="2">
+        <v>46221.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+      <c r="C178">
+        <v>15.38</v>
+      </c>
+      <c r="D178">
+        <v>81</v>
+      </c>
+      <c r="E178" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="2">
+        <v>46221.84375</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+      <c r="C179">
+        <v>29.17</v>
+      </c>
+      <c r="D179">
+        <v>82</v>
+      </c>
+      <c r="E179" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="2">
+        <v>46221.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+      <c r="C180">
+        <v>34.267</v>
+      </c>
+      <c r="D180">
+        <v>83</v>
+      </c>
+      <c r="E180" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="2">
+        <v>46221.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+      <c r="C181">
+        <v>45.994</v>
+      </c>
+      <c r="D181">
+        <v>84</v>
+      </c>
+      <c r="E181" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="2">
+        <v>46221.875</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+      <c r="C182">
+        <v>1.852</v>
+      </c>
+      <c r="D182">
+        <v>85</v>
+      </c>
+      <c r="E182" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="2">
+        <v>46221.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+      <c r="C183">
+        <v>4.851</v>
+      </c>
+      <c r="D183">
+        <v>86</v>
+      </c>
+      <c r="E183" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="2">
+        <v>46221.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+      <c r="C184">
+        <v>11.831</v>
+      </c>
+      <c r="D184">
+        <v>87</v>
+      </c>
+      <c r="E184" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="2">
+        <v>46221.90625</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+      <c r="C185">
+        <v>11.865</v>
+      </c>
+      <c r="D185">
+        <v>88</v>
+      </c>
+      <c r="E185" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="2">
+        <v>46221.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>6.172</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="D186">
+        <v>89</v>
+      </c>
+      <c r="E186" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="2">
+        <v>46221.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>4.331</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+      <c r="D187">
+        <v>90</v>
+      </c>
+      <c r="E187" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="2">
+        <v>46221.9375</v>
+      </c>
+      <c r="B188">
+        <v>8.055</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+      <c r="D188">
+        <v>91</v>
+      </c>
+      <c r="E188" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="2">
+        <v>46221.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>11.946</v>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+      <c r="D189">
+        <v>92</v>
+      </c>
+      <c r="E189" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="2">
+        <v>46221.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>1.512</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190">
+        <v>93</v>
+      </c>
+      <c r="E190" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="2">
+        <v>46221.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+      <c r="C191">
+        <v>3.57</v>
+      </c>
+      <c r="D191">
+        <v>94</v>
+      </c>
+      <c r="E191" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="2">
+        <v>46221.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+      <c r="C192">
+        <v>0.152</v>
+      </c>
+      <c r="D192">
+        <v>95</v>
+      </c>
+      <c r="E192" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="2">
+        <v>46221.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>0</v>
+      </c>
+      <c r="C193">
+        <v>13.563</v>
+      </c>
+      <c r="D193">
+        <v>96</v>
+      </c>
+      <c r="E193" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="2">
+        <v>46222</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+      <c r="C194">
+        <v>12.866</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="2">
+        <v>46222.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+      <c r="C195">
+        <v>6.993</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="2">
+        <v>46222.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>1.564</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>3</v>
+      </c>
+      <c r="E196" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="2">
+        <v>46222.03125</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>3.226</v>
+      </c>
+      <c r="D197">
+        <v>4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="2">
+        <v>46222.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>0.84</v>
+      </c>
+      <c r="D198">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="2">
+        <v>46222.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>3.061</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="2">
+        <v>46222.0625</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+      <c r="C200">
+        <v>5.315</v>
+      </c>
+      <c r="D200">
+        <v>7</v>
+      </c>
+      <c r="E200" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="2">
+        <v>46222.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
+      <c r="C201">
+        <v>2.518</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="2">
+        <v>46222.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+      <c r="C202">
+        <v>4.482</v>
+      </c>
+      <c r="D202">
+        <v>9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="2">
+        <v>46222.09375</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>0.703</v>
+      </c>
+      <c r="D203">
+        <v>10</v>
+      </c>
+      <c r="E203" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="2">
+        <v>46222.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>0</v>
+      </c>
+      <c r="C204">
+        <v>10.494</v>
+      </c>
+      <c r="D204">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="2">
+        <v>46222.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>0.92</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>12</v>
+      </c>
+      <c r="E205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="2">
+        <v>46222.125</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+      <c r="C206">
+        <v>8.791</v>
+      </c>
+      <c r="D206">
+        <v>13</v>
+      </c>
+      <c r="E206" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="2">
+        <v>46222.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>2.852</v>
+      </c>
+      <c r="D207">
+        <v>14</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="2">
+        <v>46222.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>4.908</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>15</v>
+      </c>
+      <c r="E208" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="2">
+        <v>46222.15625</v>
+      </c>
+      <c r="B209">
+        <v>9.180999999999999</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>16</v>
+      </c>
+      <c r="E209" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="2">
+        <v>46222.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+      <c r="C210">
+        <v>9.659000000000001</v>
+      </c>
+      <c r="D210">
+        <v>17</v>
+      </c>
+      <c r="E210" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="2">
+        <v>46222.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>0</v>
+      </c>
+      <c r="C211">
+        <v>9.355</v>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="E211" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="2">
+        <v>46222.1875</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+      <c r="C212">
+        <v>10.447</v>
+      </c>
+      <c r="D212">
+        <v>19</v>
+      </c>
+      <c r="E212" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="2">
+        <v>46222.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+      <c r="C213">
+        <v>25.363</v>
+      </c>
+      <c r="D213">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="2">
+        <v>46222.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+      <c r="C214">
+        <v>23.974</v>
+      </c>
+      <c r="D214">
+        <v>21</v>
+      </c>
+      <c r="E214" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="2">
+        <v>46222.21875</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+      <c r="C215">
+        <v>30.509</v>
+      </c>
+      <c r="D215">
+        <v>22</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="2">
+        <v>46222.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+      <c r="C216">
+        <v>8.32</v>
+      </c>
+      <c r="D216">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="2">
+        <v>46222.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217">
+        <v>12.017</v>
+      </c>
+      <c r="D217">
+        <v>24</v>
+      </c>
+      <c r="E217" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="2">
+        <v>46222.25</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>5.636</v>
+      </c>
+      <c r="D218">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="2">
+        <v>46222.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+      <c r="C219">
+        <v>0.636</v>
+      </c>
+      <c r="D219">
+        <v>26</v>
+      </c>
+      <c r="E219" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="2">
+        <v>46222.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+      <c r="C220">
+        <v>0.241</v>
+      </c>
+      <c r="D220">
+        <v>27</v>
+      </c>
+      <c r="E220" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="2">
+        <v>46222.28125</v>
+      </c>
+      <c r="B221">
+        <v>0</v>
+      </c>
+      <c r="C221">
+        <v>0.891</v>
+      </c>
+      <c r="D221">
+        <v>28</v>
+      </c>
+      <c r="E221" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="2">
+        <v>46222.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>13.701</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="2">
+        <v>46222.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>10.695</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="E223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2">
+        <v>46222.3125</v>
+      </c>
+      <c r="B224">
+        <v>3.665</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>31</v>
+      </c>
+      <c r="E224" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="2">
+        <v>46222.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>32.51</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>32</v>
+      </c>
+      <c r="E225" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="2">
+        <v>46222.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>70.014</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>33</v>
+      </c>
+      <c r="E226" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="2">
+        <v>46222.34375</v>
+      </c>
+      <c r="B227">
+        <v>49.822</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>34</v>
+      </c>
+      <c r="E227" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="2">
+        <v>46222.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>6.938</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>35</v>
+      </c>
+      <c r="E228" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="2">
+        <v>46222.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+      <c r="C229">
+        <v>6.048</v>
+      </c>
+      <c r="D229">
+        <v>36</v>
+      </c>
+      <c r="E229" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="2">
+        <v>46222.375</v>
+      </c>
+      <c r="B230">
+        <v>10.244</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>37</v>
+      </c>
+      <c r="E230" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="2">
+        <v>46222.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>9.285</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>38</v>
+      </c>
+      <c r="E231" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="2">
+        <v>46222.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>0</v>
+      </c>
+      <c r="C232">
+        <v>6.1</v>
+      </c>
+      <c r="D232">
+        <v>39</v>
+      </c>
+      <c r="E232" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="2">
+        <v>46222.40625</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>4.974</v>
+      </c>
+      <c r="D233">
+        <v>40</v>
+      </c>
+      <c r="E233" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="2">
+        <v>46222.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>0.712</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234">
+        <v>41</v>
+      </c>
+      <c r="E234" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="2">
+        <v>46222.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>2.174</v>
+      </c>
+      <c r="D235">
+        <v>42</v>
+      </c>
+      <c r="E235" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="2">
+        <v>46222.4375</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+      <c r="C236">
+        <v>4.482</v>
+      </c>
+      <c r="D236">
+        <v>43</v>
+      </c>
+      <c r="E236" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="2">
+        <v>46222.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>0.944</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>44</v>
+      </c>
+      <c r="E237" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="2">
+        <v>46222.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>13.927</v>
+      </c>
+      <c r="D238">
+        <v>45</v>
+      </c>
+      <c r="E238" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="2">
+        <v>46222.46875</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+      <c r="C239">
+        <v>16.983</v>
+      </c>
+      <c r="D239">
+        <v>46</v>
+      </c>
+      <c r="E239" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="2">
+        <v>46222.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>5.27</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>47</v>
+      </c>
+      <c r="E240" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="2">
+        <v>46222.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>12.952</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>48</v>
+      </c>
+      <c r="E241" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="2">
+        <v>46222.5</v>
+      </c>
+      <c r="B242">
+        <v>6.478</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>49</v>
+      </c>
+      <c r="E242" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="2">
+        <v>46222.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>15.968</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>50</v>
+      </c>
+      <c r="E243" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="2">
+        <v>46222.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>17.216</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>51</v>
+      </c>
+      <c r="E244" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="2">
+        <v>46222.53125</v>
+      </c>
+      <c r="B245">
+        <v>6.411</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>52</v>
+      </c>
+      <c r="E245" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="2">
+        <v>46222.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+      <c r="C246">
+        <v>11.288</v>
+      </c>
+      <c r="D246">
+        <v>53</v>
+      </c>
+      <c r="E246" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="2">
+        <v>46222.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>0</v>
+      </c>
+      <c r="C247">
+        <v>0.167</v>
+      </c>
+      <c r="D247">
+        <v>54</v>
+      </c>
+      <c r="E247" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="2">
+        <v>46222.5625</v>
+      </c>
+      <c r="B248">
+        <v>11.355</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>55</v>
+      </c>
+      <c r="E248" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="2">
+        <v>46222.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>20.032</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>56</v>
+      </c>
+      <c r="E249" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="2">
+        <v>46222.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>33.844</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>57</v>
+      </c>
+      <c r="E250" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="2">
+        <v>46222.59375</v>
+      </c>
+      <c r="B251">
+        <v>75.753</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>58</v>
+      </c>
+      <c r="E251" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="2">
+        <v>46222.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>44.31</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>59</v>
+      </c>
+      <c r="E252" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="2">
+        <v>46222.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>37.183</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>60</v>
+      </c>
+      <c r="E253" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="2">
+        <v>46222.625</v>
+      </c>
+      <c r="B254">
+        <v>0</v>
+      </c>
+      <c r="C254">
+        <v>0.441</v>
+      </c>
+      <c r="D254">
+        <v>61</v>
+      </c>
+      <c r="E254" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="2">
+        <v>46222.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+      <c r="C255">
+        <v>4.549</v>
+      </c>
+      <c r="D255">
+        <v>62</v>
+      </c>
+      <c r="E255" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="2">
+        <v>46222.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+      <c r="C256">
+        <v>0.127</v>
+      </c>
+      <c r="D256">
+        <v>63</v>
+      </c>
+      <c r="E256" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="2">
+        <v>46222.65625</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+      <c r="C257">
+        <v>8.137</v>
+      </c>
+      <c r="D257">
+        <v>64</v>
+      </c>
+      <c r="E257" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="2">
+        <v>46222.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>0</v>
+      </c>
+      <c r="C258">
+        <v>14.091</v>
+      </c>
+      <c r="D258">
+        <v>65</v>
+      </c>
+      <c r="E258" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="2">
+        <v>46222.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>0</v>
+      </c>
+      <c r="C259">
+        <v>84.36499999999999</v>
+      </c>
+      <c r="D259">
+        <v>66</v>
+      </c>
+      <c r="E259" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="2">
+        <v>46222.6875</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+      <c r="C260">
+        <v>31.018</v>
+      </c>
+      <c r="D260">
+        <v>67</v>
+      </c>
+      <c r="E260" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="2">
+        <v>46222.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+      <c r="C261">
+        <v>29.525</v>
+      </c>
+      <c r="D261">
+        <v>68</v>
+      </c>
+      <c r="E261" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="2">
+        <v>46222.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>41.19</v>
+      </c>
+      <c r="D262">
+        <v>69</v>
+      </c>
+      <c r="E262" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="2">
+        <v>46222.71875</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>50.875</v>
+      </c>
+      <c r="D263">
+        <v>70</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="2">
+        <v>46222.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+      <c r="C264">
+        <v>57.496</v>
+      </c>
+      <c r="D264">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="2">
+        <v>46222.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+      <c r="C265">
+        <v>33.718</v>
+      </c>
+      <c r="D265">
+        <v>72</v>
+      </c>
+      <c r="E265" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="2">
+        <v>46222.75</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>30.464</v>
+      </c>
+      <c r="D266">
+        <v>73</v>
+      </c>
+      <c r="E266" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="2">
+        <v>46222.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>0</v>
+      </c>
+      <c r="C267">
+        <v>33.575</v>
+      </c>
+      <c r="D267">
+        <v>74</v>
+      </c>
+      <c r="E267" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="2">
+        <v>46222.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>26.337</v>
+      </c>
+      <c r="D268">
+        <v>75</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="2">
+        <v>46222.78125</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>2.585</v>
+      </c>
+      <c r="D269">
+        <v>76</v>
+      </c>
+      <c r="E269" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="2">
+        <v>46222.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>2.789</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>77</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="2">
+        <v>46222.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>8.353</v>
+      </c>
+      <c r="D271">
+        <v>78</v>
+      </c>
+      <c r="E271" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="2">
+        <v>46222.8125</v>
+      </c>
+      <c r="B272">
+        <v>0.866</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>79</v>
+      </c>
+      <c r="E272" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5">
+      <c r="A273" s="2">
+        <v>46222.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>8.131</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>80</v>
+      </c>
+      <c r="E273" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5">
+      <c r="A274" s="2">
+        <v>46222.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>0.988</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>81</v>
+      </c>
+      <c r="E274" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5">
+      <c r="A275" s="2">
+        <v>46222.84375</v>
+      </c>
+      <c r="B275">
+        <v>2.121</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>82</v>
+      </c>
+      <c r="E275" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5">
+      <c r="A276" s="2">
+        <v>46222.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>2.629</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>83</v>
+      </c>
+      <c r="E276" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5">
+      <c r="A277" s="2">
+        <v>46222.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>12.215</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>84</v>
+      </c>
+      <c r="E277" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5">
+      <c r="A278" s="2">
+        <v>46222.875</v>
+      </c>
+      <c r="B278">
+        <v>16.753</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>85</v>
+      </c>
+      <c r="E278" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5">
+      <c r="A279" s="2">
+        <v>46222.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>2.9</v>
+      </c>
+      <c r="D279">
+        <v>86</v>
+      </c>
+      <c r="E279" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5">
+      <c r="A280" s="2">
+        <v>46222.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>1.45</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>87</v>
+      </c>
+      <c r="E280" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5">
+      <c r="A281" s="2">
+        <v>46222.90625</v>
+      </c>
+      <c r="B281">
+        <v>13.164</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>88</v>
+      </c>
+      <c r="E281" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5">
+      <c r="A282" s="2">
+        <v>46222.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>17.233</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>89</v>
+      </c>
+      <c r="E282" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5">
+      <c r="A283" s="2">
+        <v>46222.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>9.502000000000001</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>90</v>
+      </c>
+      <c r="E283" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5">
+      <c r="A284" s="2">
+        <v>46222.9375</v>
+      </c>
+      <c r="B284">
+        <v>3.506</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>91</v>
+      </c>
+      <c r="E284" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5">
+      <c r="A285" s="2">
+        <v>46222.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>0.972</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>92</v>
+      </c>
+      <c r="E285" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5">
+      <c r="A286" s="2">
+        <v>46222.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>0.435</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>93</v>
+      </c>
+      <c r="E286" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
+      <c r="A287" s="2">
+        <v>46222.96875</v>
+      </c>
+      <c r="B287">
+        <v>0</v>
+      </c>
+      <c r="C287">
+        <v>9.833</v>
+      </c>
+      <c r="D287">
+        <v>94</v>
+      </c>
+      <c r="E287" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5">
+      <c r="A288" s="2">
+        <v>46222.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>4.486</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>95</v>
+      </c>
+      <c r="E288" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5">
+      <c r="A289" s="2">
+        <v>46222.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>2.28</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>96</v>
+      </c>
+      <c r="E289" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5">
+      <c r="A290" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B290">
+        <v>19.513</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
+      </c>
+      <c r="E290" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5">
+      <c r="A291" s="2">
+        <v>46223.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>0.521</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>2</v>
+      </c>
+      <c r="E291" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5">
+      <c r="A292" s="2">
+        <v>46223.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>8.622999999999999</v>
+      </c>
+      <c r="D292">
+        <v>3</v>
+      </c>
+      <c r="E292" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5">
+      <c r="A293" s="2">
+        <v>46223.03125</v>
+      </c>
+      <c r="B293">
+        <v>7.392</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>4</v>
+      </c>
+      <c r="E293" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5">
+      <c r="A294" s="2">
+        <v>46223.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>10.006</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>5</v>
+      </c>
+      <c r="E294" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5">
+      <c r="A295" s="2">
+        <v>46223.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>23.015</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>6</v>
+      </c>
+      <c r="E295" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5">
+      <c r="A296" s="2">
+        <v>46223.0625</v>
+      </c>
+      <c r="B296">
+        <v>11.127</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>7</v>
+      </c>
+      <c r="E296" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
+      <c r="A297" s="2">
+        <v>46223.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>7.813</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>8</v>
+      </c>
+      <c r="E297" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5">
+      <c r="A298" s="2">
+        <v>46223.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>7.684</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>9</v>
+      </c>
+      <c r="E298" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5">
+      <c r="A299" s="2">
+        <v>46223.09375</v>
+      </c>
+      <c r="B299">
+        <v>13.481</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>10</v>
+      </c>
+      <c r="E299" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
+      <c r="A300" s="2">
+        <v>46223.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>7.836</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>11</v>
+      </c>
+      <c r="E300" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5">
+      <c r="A301" s="2">
+        <v>46223.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>2.884</v>
+      </c>
+      <c r="D301">
+        <v>12</v>
+      </c>
+      <c r="E301" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5">
+      <c r="A302" s="2">
+        <v>46223.125</v>
+      </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
+      <c r="C302">
+        <v>1.38</v>
+      </c>
+      <c r="D302">
+        <v>13</v>
+      </c>
+      <c r="E302" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5">
+      <c r="A303" s="2">
+        <v>46223.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
+      <c r="C303">
+        <v>0.151</v>
+      </c>
+      <c r="D303">
+        <v>14</v>
+      </c>
+      <c r="E303" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5">
+      <c r="A304" s="2">
+        <v>46223.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
+      <c r="C304">
+        <v>5.853</v>
+      </c>
+      <c r="D304">
+        <v>15</v>
+      </c>
+      <c r="E304" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="2">
+        <v>46223.15625</v>
+      </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
+      <c r="C305">
+        <v>10.372</v>
+      </c>
+      <c r="D305">
+        <v>16</v>
+      </c>
+      <c r="E305" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="2">
+        <v>46223.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
+      <c r="C306">
+        <v>0.488</v>
+      </c>
+      <c r="D306">
+        <v>17</v>
+      </c>
+      <c r="E306" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="2">
+        <v>46223.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+      <c r="C307">
+        <v>20.351</v>
+      </c>
+      <c r="D307">
+        <v>18</v>
+      </c>
+      <c r="E307" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="2">
+        <v>46223.1875</v>
+      </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
+      <c r="C308">
+        <v>14.992</v>
+      </c>
+      <c r="D308">
+        <v>19</v>
+      </c>
+      <c r="E308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="2">
+        <v>46223.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
+      <c r="C309">
+        <v>7.033</v>
+      </c>
+      <c r="D309">
+        <v>20</v>
+      </c>
+      <c r="E309" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="2">
+        <v>46223.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+      <c r="C310">
+        <v>17.732</v>
+      </c>
+      <c r="D310">
+        <v>21</v>
+      </c>
+      <c r="E310" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="2">
+        <v>46223.21875</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+      <c r="C311">
+        <v>3.416</v>
+      </c>
+      <c r="D311">
+        <v>22</v>
+      </c>
+      <c r="E311" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" s="2">
+        <v>46223.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+      <c r="C312">
+        <v>5.719</v>
+      </c>
+      <c r="D312">
+        <v>23</v>
+      </c>
+      <c r="E312" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" s="2">
+        <v>46223.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
+      <c r="C313">
+        <v>6.413</v>
+      </c>
+      <c r="D313">
+        <v>24</v>
+      </c>
+      <c r="E313" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" s="2">
+        <v>46223.25</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+      <c r="C314">
+        <v>30.159</v>
+      </c>
+      <c r="D314">
+        <v>25</v>
+      </c>
+      <c r="E314" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" s="2">
+        <v>46223.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+      <c r="C315">
+        <v>11.297</v>
+      </c>
+      <c r="D315">
+        <v>26</v>
+      </c>
+      <c r="E315" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" s="2">
+        <v>46223.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>0</v>
+      </c>
+      <c r="C316">
+        <v>2.635</v>
+      </c>
+      <c r="D316">
+        <v>27</v>
+      </c>
+      <c r="E316" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" s="2">
+        <v>46223.28125</v>
+      </c>
+      <c r="B317">
+        <v>18.059</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>28</v>
+      </c>
+      <c r="E317" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" s="2">
+        <v>46223.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>11.979</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>29</v>
+      </c>
+      <c r="E318" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" s="2">
+        <v>46223.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>0</v>
+      </c>
+      <c r="C319">
+        <v>3.616</v>
+      </c>
+      <c r="D319">
+        <v>30</v>
+      </c>
+      <c r="E319" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" s="2">
+        <v>46223.3125</v>
+      </c>
+      <c r="B320">
+        <v>2.746</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>31</v>
+      </c>
+      <c r="E320" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>Timestamp</t>
   </si>
@@ -31,294 +31,6 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>22.07.20261</t>
-  </si>
-  <si>
-    <t>22.07.20262</t>
-  </si>
-  <si>
-    <t>22.07.20263</t>
-  </si>
-  <si>
-    <t>22.07.20264</t>
-  </si>
-  <si>
-    <t>22.07.20265</t>
-  </si>
-  <si>
-    <t>22.07.20266</t>
-  </si>
-  <si>
-    <t>22.07.20267</t>
-  </si>
-  <si>
-    <t>22.07.20268</t>
-  </si>
-  <si>
-    <t>22.07.20269</t>
-  </si>
-  <si>
-    <t>22.07.202610</t>
-  </si>
-  <si>
-    <t>22.07.202611</t>
-  </si>
-  <si>
-    <t>22.07.202612</t>
-  </si>
-  <si>
-    <t>22.07.202613</t>
-  </si>
-  <si>
-    <t>22.07.202614</t>
-  </si>
-  <si>
-    <t>22.07.202615</t>
-  </si>
-  <si>
-    <t>22.07.202616</t>
-  </si>
-  <si>
-    <t>22.07.202617</t>
-  </si>
-  <si>
-    <t>22.07.202618</t>
-  </si>
-  <si>
-    <t>22.07.202619</t>
-  </si>
-  <si>
-    <t>22.07.202620</t>
-  </si>
-  <si>
-    <t>22.07.202621</t>
-  </si>
-  <si>
-    <t>22.07.202622</t>
-  </si>
-  <si>
-    <t>22.07.202623</t>
-  </si>
-  <si>
-    <t>22.07.202624</t>
-  </si>
-  <si>
-    <t>22.07.202625</t>
-  </si>
-  <si>
-    <t>22.07.202626</t>
-  </si>
-  <si>
-    <t>22.07.202627</t>
-  </si>
-  <si>
-    <t>22.07.202628</t>
-  </si>
-  <si>
-    <t>22.07.202629</t>
-  </si>
-  <si>
-    <t>22.07.202630</t>
-  </si>
-  <si>
-    <t>22.07.202631</t>
-  </si>
-  <si>
-    <t>22.07.202632</t>
-  </si>
-  <si>
-    <t>22.07.202633</t>
-  </si>
-  <si>
-    <t>22.07.202634</t>
-  </si>
-  <si>
-    <t>22.07.202635</t>
-  </si>
-  <si>
-    <t>22.07.202636</t>
-  </si>
-  <si>
-    <t>22.07.202637</t>
-  </si>
-  <si>
-    <t>22.07.202638</t>
-  </si>
-  <si>
-    <t>22.07.202639</t>
-  </si>
-  <si>
-    <t>22.07.202640</t>
-  </si>
-  <si>
-    <t>22.07.202641</t>
-  </si>
-  <si>
-    <t>22.07.202642</t>
-  </si>
-  <si>
-    <t>22.07.202643</t>
-  </si>
-  <si>
-    <t>22.07.202644</t>
-  </si>
-  <si>
-    <t>22.07.202645</t>
-  </si>
-  <si>
-    <t>22.07.202646</t>
-  </si>
-  <si>
-    <t>22.07.202647</t>
-  </si>
-  <si>
-    <t>22.07.202648</t>
-  </si>
-  <si>
-    <t>22.07.202649</t>
-  </si>
-  <si>
-    <t>22.07.202650</t>
-  </si>
-  <si>
-    <t>22.07.202651</t>
-  </si>
-  <si>
-    <t>22.07.202652</t>
-  </si>
-  <si>
-    <t>22.07.202653</t>
-  </si>
-  <si>
-    <t>22.07.202654</t>
-  </si>
-  <si>
-    <t>22.07.202655</t>
-  </si>
-  <si>
-    <t>22.07.202656</t>
-  </si>
-  <si>
-    <t>22.07.202657</t>
-  </si>
-  <si>
-    <t>22.07.202658</t>
-  </si>
-  <si>
-    <t>22.07.202659</t>
-  </si>
-  <si>
-    <t>22.07.202660</t>
-  </si>
-  <si>
-    <t>22.07.202661</t>
-  </si>
-  <si>
-    <t>22.07.202662</t>
-  </si>
-  <si>
-    <t>22.07.202663</t>
-  </si>
-  <si>
-    <t>22.07.202664</t>
-  </si>
-  <si>
-    <t>22.07.202665</t>
-  </si>
-  <si>
-    <t>22.07.202666</t>
-  </si>
-  <si>
-    <t>22.07.202667</t>
-  </si>
-  <si>
-    <t>22.07.202668</t>
-  </si>
-  <si>
-    <t>22.07.202669</t>
-  </si>
-  <si>
-    <t>22.07.202670</t>
-  </si>
-  <si>
-    <t>22.07.202671</t>
-  </si>
-  <si>
-    <t>22.07.202672</t>
-  </si>
-  <si>
-    <t>22.07.202673</t>
-  </si>
-  <si>
-    <t>22.07.202674</t>
-  </si>
-  <si>
-    <t>22.07.202675</t>
-  </si>
-  <si>
-    <t>22.07.202676</t>
-  </si>
-  <si>
-    <t>22.07.202677</t>
-  </si>
-  <si>
-    <t>22.07.202678</t>
-  </si>
-  <si>
-    <t>22.07.202679</t>
-  </si>
-  <si>
-    <t>22.07.202680</t>
-  </si>
-  <si>
-    <t>22.07.202681</t>
-  </si>
-  <si>
-    <t>22.07.202682</t>
-  </si>
-  <si>
-    <t>22.07.202683</t>
-  </si>
-  <si>
-    <t>22.07.202684</t>
-  </si>
-  <si>
-    <t>22.07.202685</t>
-  </si>
-  <si>
-    <t>22.07.202686</t>
-  </si>
-  <si>
-    <t>22.07.202687</t>
-  </si>
-  <si>
-    <t>22.07.202688</t>
-  </si>
-  <si>
-    <t>22.07.202689</t>
-  </si>
-  <si>
-    <t>22.07.202690</t>
-  </si>
-  <si>
-    <t>22.07.202691</t>
-  </si>
-  <si>
-    <t>22.07.202692</t>
-  </si>
-  <si>
-    <t>22.07.202693</t>
-  </si>
-  <si>
-    <t>22.07.202694</t>
-  </si>
-  <si>
-    <t>22.07.202695</t>
-  </si>
-  <si>
-    <t>22.07.202696</t>
-  </si>
-  <si>
     <t>23.07.20261</t>
   </si>
   <si>
@@ -407,6 +119,300 @@
   </si>
   <si>
     <t>23.07.202630</t>
+  </si>
+  <si>
+    <t>23.07.202631</t>
+  </si>
+  <si>
+    <t>23.07.202632</t>
+  </si>
+  <si>
+    <t>23.07.202633</t>
+  </si>
+  <si>
+    <t>23.07.202634</t>
+  </si>
+  <si>
+    <t>23.07.202635</t>
+  </si>
+  <si>
+    <t>23.07.202636</t>
+  </si>
+  <si>
+    <t>23.07.202637</t>
+  </si>
+  <si>
+    <t>23.07.202638</t>
+  </si>
+  <si>
+    <t>23.07.202639</t>
+  </si>
+  <si>
+    <t>23.07.202640</t>
+  </si>
+  <si>
+    <t>23.07.202641</t>
+  </si>
+  <si>
+    <t>23.07.202642</t>
+  </si>
+  <si>
+    <t>23.07.202643</t>
+  </si>
+  <si>
+    <t>23.07.202644</t>
+  </si>
+  <si>
+    <t>23.07.202645</t>
+  </si>
+  <si>
+    <t>23.07.202646</t>
+  </si>
+  <si>
+    <t>23.07.202647</t>
+  </si>
+  <si>
+    <t>23.07.202648</t>
+  </si>
+  <si>
+    <t>23.07.202649</t>
+  </si>
+  <si>
+    <t>23.07.202650</t>
+  </si>
+  <si>
+    <t>23.07.202651</t>
+  </si>
+  <si>
+    <t>23.07.202652</t>
+  </si>
+  <si>
+    <t>23.07.202653</t>
+  </si>
+  <si>
+    <t>23.07.202654</t>
+  </si>
+  <si>
+    <t>23.07.202655</t>
+  </si>
+  <si>
+    <t>23.07.202656</t>
+  </si>
+  <si>
+    <t>23.07.202657</t>
+  </si>
+  <si>
+    <t>23.07.202658</t>
+  </si>
+  <si>
+    <t>23.07.202659</t>
+  </si>
+  <si>
+    <t>23.07.202660</t>
+  </si>
+  <si>
+    <t>23.07.202661</t>
+  </si>
+  <si>
+    <t>23.07.202662</t>
+  </si>
+  <si>
+    <t>23.07.202663</t>
+  </si>
+  <si>
+    <t>23.07.202664</t>
+  </si>
+  <si>
+    <t>23.07.202665</t>
+  </si>
+  <si>
+    <t>23.07.202666</t>
+  </si>
+  <si>
+    <t>23.07.202667</t>
+  </si>
+  <si>
+    <t>23.07.202668</t>
+  </si>
+  <si>
+    <t>23.07.202669</t>
+  </si>
+  <si>
+    <t>23.07.202670</t>
+  </si>
+  <si>
+    <t>23.07.202671</t>
+  </si>
+  <si>
+    <t>23.07.202672</t>
+  </si>
+  <si>
+    <t>23.07.202673</t>
+  </si>
+  <si>
+    <t>23.07.202674</t>
+  </si>
+  <si>
+    <t>23.07.202675</t>
+  </si>
+  <si>
+    <t>23.07.202676</t>
+  </si>
+  <si>
+    <t>23.07.202677</t>
+  </si>
+  <si>
+    <t>23.07.202678</t>
+  </si>
+  <si>
+    <t>23.07.202679</t>
+  </si>
+  <si>
+    <t>23.07.202680</t>
+  </si>
+  <si>
+    <t>23.07.202681</t>
+  </si>
+  <si>
+    <t>23.07.202682</t>
+  </si>
+  <si>
+    <t>23.07.202683</t>
+  </si>
+  <si>
+    <t>23.07.202684</t>
+  </si>
+  <si>
+    <t>23.07.202685</t>
+  </si>
+  <si>
+    <t>23.07.202686</t>
+  </si>
+  <si>
+    <t>23.07.202687</t>
+  </si>
+  <si>
+    <t>23.07.202688</t>
+  </si>
+  <si>
+    <t>23.07.202689</t>
+  </si>
+  <si>
+    <t>23.07.202690</t>
+  </si>
+  <si>
+    <t>23.07.202691</t>
+  </si>
+  <si>
+    <t>23.07.202692</t>
+  </si>
+  <si>
+    <t>23.07.202693</t>
+  </si>
+  <si>
+    <t>23.07.202694</t>
+  </si>
+  <si>
+    <t>23.07.202695</t>
+  </si>
+  <si>
+    <t>23.07.202696</t>
+  </si>
+  <si>
+    <t>24.07.20261</t>
+  </si>
+  <si>
+    <t>24.07.20262</t>
+  </si>
+  <si>
+    <t>24.07.20263</t>
+  </si>
+  <si>
+    <t>24.07.20264</t>
+  </si>
+  <si>
+    <t>24.07.20265</t>
+  </si>
+  <si>
+    <t>24.07.20266</t>
+  </si>
+  <si>
+    <t>24.07.20267</t>
+  </si>
+  <si>
+    <t>24.07.20268</t>
+  </si>
+  <si>
+    <t>24.07.20269</t>
+  </si>
+  <si>
+    <t>24.07.202610</t>
+  </si>
+  <si>
+    <t>24.07.202611</t>
+  </si>
+  <si>
+    <t>24.07.202612</t>
+  </si>
+  <si>
+    <t>24.07.202613</t>
+  </si>
+  <si>
+    <t>24.07.202614</t>
+  </si>
+  <si>
+    <t>24.07.202615</t>
+  </si>
+  <si>
+    <t>24.07.202616</t>
+  </si>
+  <si>
+    <t>24.07.202617</t>
+  </si>
+  <si>
+    <t>24.07.202618</t>
+  </si>
+  <si>
+    <t>24.07.202619</t>
+  </si>
+  <si>
+    <t>24.07.202620</t>
+  </si>
+  <si>
+    <t>24.07.202621</t>
+  </si>
+  <si>
+    <t>24.07.202622</t>
+  </si>
+  <si>
+    <t>24.07.202623</t>
+  </si>
+  <si>
+    <t>24.07.202624</t>
+  </si>
+  <si>
+    <t>24.07.202625</t>
+  </si>
+  <si>
+    <t>24.07.202626</t>
+  </si>
+  <si>
+    <t>24.07.202627</t>
+  </si>
+  <si>
+    <t>24.07.202628</t>
+  </si>
+  <si>
+    <t>24.07.202629</t>
+  </si>
+  <si>
+    <t>24.07.202630</t>
+  </si>
+  <si>
+    <t>24.07.202631</t>
+  </si>
+  <si>
+    <t>24.07.202632</t>
   </si>
 </sst>
 </file>
@@ -768,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -790,13 +796,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B2">
-        <v>11.397</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>6.068</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -807,10 +813,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46225.01041666666</v>
+        <v>46226.01041666666</v>
       </c>
       <c r="B3">
-        <v>4.149</v>
+        <v>0.283</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -824,13 +830,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46225.02083333334</v>
+        <v>46226.02083333334</v>
       </c>
       <c r="B4">
-        <v>18.427</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>5.298</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -841,13 +847,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46225.03125</v>
+        <v>46226.03125</v>
       </c>
       <c r="B5">
-        <v>16.955</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -858,10 +864,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46225.04166666666</v>
+        <v>46226.04166666666</v>
       </c>
       <c r="B6">
-        <v>23.866</v>
+        <v>7.019</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -875,10 +881,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46225.05208333334</v>
+        <v>46226.05208333334</v>
       </c>
       <c r="B7">
-        <v>27.417</v>
+        <v>7.417</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -892,10 +898,10 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46225.0625</v>
+        <v>46226.0625</v>
       </c>
       <c r="B8">
-        <v>4.885</v>
+        <v>30.441</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -909,10 +915,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46225.07291666666</v>
+        <v>46226.07291666666</v>
       </c>
       <c r="B9">
-        <v>9.445</v>
+        <v>22.621</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -926,10 +932,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46225.08333333334</v>
+        <v>46226.08333333334</v>
       </c>
       <c r="B10">
-        <v>14.999</v>
+        <v>11.601</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -943,10 +949,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46225.09375</v>
+        <v>46226.09375</v>
       </c>
       <c r="B11">
-        <v>32.228</v>
+        <v>26.659</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -960,10 +966,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46225.10416666666</v>
+        <v>46226.10416666666</v>
       </c>
       <c r="B12">
-        <v>36.746</v>
+        <v>36.27</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -977,10 +983,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46225.11458333334</v>
+        <v>46226.11458333334</v>
       </c>
       <c r="B13">
-        <v>15.509</v>
+        <v>30.689</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -994,10 +1000,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46225.125</v>
+        <v>46226.125</v>
       </c>
       <c r="B14">
-        <v>2.044</v>
+        <v>44.156</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1011,10 +1017,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46225.13541666666</v>
+        <v>46226.13541666666</v>
       </c>
       <c r="B15">
-        <v>2.729</v>
+        <v>22.926</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1028,13 +1034,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46225.14583333334</v>
+        <v>46226.14583333334</v>
       </c>
       <c r="B16">
-        <v>10.176</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2.199</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1045,10 +1051,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46225.15625</v>
+        <v>46226.15625</v>
       </c>
       <c r="B17">
-        <v>6.521</v>
+        <v>9.186</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1062,13 +1068,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46225.16666666666</v>
+        <v>46226.16666666666</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="C18">
-        <v>2.519</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>17</v>
@@ -1079,13 +1085,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46225.17708333334</v>
+        <v>46226.17708333334</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0.331</v>
+        <v>3.757</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1096,13 +1102,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46225.1875</v>
+        <v>46226.1875</v>
       </c>
       <c r="B20">
-        <v>4.591</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1113,10 +1119,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46225.19791666666</v>
+        <v>46226.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.975</v>
+        <v>2.491</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1130,13 +1136,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46225.20833333334</v>
+        <v>46226.20833333334</v>
       </c>
       <c r="B22">
-        <v>4.411</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>3.711</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1147,13 +1153,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46225.21875</v>
+        <v>46226.21875</v>
       </c>
       <c r="B23">
-        <v>7.988</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>10.077</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1164,10 +1170,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46225.22916666666</v>
+        <v>46226.22916666666</v>
       </c>
       <c r="B24">
-        <v>14.756</v>
+        <v>2.932</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1181,10 +1187,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46225.23958333334</v>
+        <v>46226.23958333334</v>
       </c>
       <c r="B25">
-        <v>25.53</v>
+        <v>8.718</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1198,13 +1204,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46225.25</v>
+        <v>46226.25</v>
       </c>
       <c r="B26">
-        <v>11.238</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>2.094</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1215,10 +1221,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46225.26041666666</v>
+        <v>46226.26041666666</v>
       </c>
       <c r="B27">
-        <v>5.12</v>
+        <v>6.624</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1232,10 +1238,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46225.27083333334</v>
+        <v>46226.27083333334</v>
       </c>
       <c r="B28">
-        <v>14.833</v>
+        <v>18.982</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1249,10 +1255,10 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46225.28125</v>
+        <v>46226.28125</v>
       </c>
       <c r="B29">
-        <v>18.665</v>
+        <v>1.808</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -1266,13 +1272,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46225.29166666666</v>
+        <v>46226.29166666666</v>
       </c>
       <c r="B30">
-        <v>10.693</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>6.037</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1283,13 +1289,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46225.30208333334</v>
+        <v>46226.30208333334</v>
       </c>
       <c r="B31">
-        <v>41.369</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>11.799</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1300,13 +1306,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46225.3125</v>
+        <v>46226.3125</v>
       </c>
       <c r="B32">
-        <v>53.72</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1.048</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1317,13 +1323,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46225.32291666666</v>
+        <v>46226.32291666666</v>
       </c>
       <c r="B33">
-        <v>98.453</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>17.528</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1334,13 +1340,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46225.33333333334</v>
+        <v>46226.33333333334</v>
       </c>
       <c r="B34">
-        <v>61.051</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>4.378</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1351,13 +1357,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46225.34375</v>
+        <v>46226.34375</v>
       </c>
       <c r="B35">
-        <v>16.975</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>36.155</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1368,13 +1374,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46225.35416666666</v>
+        <v>46226.35416666666</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0.62</v>
+        <v>28.488</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1385,13 +1391,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46225.36458333334</v>
+        <v>46226.36458333334</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>2.768</v>
+        <v>12.155</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1402,13 +1408,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46225.375</v>
+        <v>46226.375</v>
       </c>
       <c r="B38">
-        <v>16.03</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>2.204</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1419,10 +1425,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46225.38541666666</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="B39">
-        <v>33.263</v>
+        <v>1.148</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1436,13 +1442,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46225.39583333334</v>
+        <v>46226.39583333334</v>
       </c>
       <c r="B40">
-        <v>35.055</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1453,13 +1459,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46225.40625</v>
+        <v>46226.40625</v>
       </c>
       <c r="B41">
-        <v>15.869</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>5.716</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1470,13 +1476,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46225.41666666666</v>
+        <v>46226.41666666666</v>
       </c>
       <c r="B42">
-        <v>1.884</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1.617</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1487,13 +1493,13 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46225.42708333334</v>
+        <v>46226.42708333334</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>3.046</v>
       </c>
       <c r="C43">
-        <v>24.085</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>42</v>
@@ -1504,13 +1510,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46225.4375</v>
+        <v>46226.4375</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>5.42</v>
+        <v>8.27</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1521,13 +1527,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46225.44791666666</v>
+        <v>46226.44791666666</v>
       </c>
       <c r="B45">
         <v>0</v>
       </c>
       <c r="C45">
-        <v>6.023</v>
+        <v>19.398</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1538,13 +1544,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46225.45833333334</v>
+        <v>46226.45833333334</v>
       </c>
       <c r="B46">
         <v>0</v>
       </c>
       <c r="C46">
-        <v>7.456</v>
+        <v>21.862</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1555,13 +1561,13 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46225.46875</v>
+        <v>46226.46875</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>21.309</v>
       </c>
       <c r="C47">
-        <v>31.141</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>46</v>
@@ -1572,13 +1578,13 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46225.47916666666</v>
+        <v>46226.47916666666</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>24.696</v>
       </c>
       <c r="C48">
-        <v>13.88</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -1589,13 +1595,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46225.48958333334</v>
+        <v>46226.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>5.191</v>
+        <v>8.541</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1606,13 +1612,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46225.5</v>
+        <v>46226.5</v>
       </c>
       <c r="B50">
-        <v>6.494</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1623,10 +1629,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46225.51041666666</v>
+        <v>46226.51041666666</v>
       </c>
       <c r="B51">
-        <v>38.931</v>
+        <v>43.295</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1640,10 +1646,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46225.52083333334</v>
+        <v>46226.52083333334</v>
       </c>
       <c r="B52">
-        <v>44.169</v>
+        <v>12.377</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -1657,10 +1663,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46225.53125</v>
+        <v>46226.53125</v>
       </c>
       <c r="B53">
-        <v>64.17400000000001</v>
+        <v>12.406</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1674,10 +1680,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46225.54166666666</v>
+        <v>46226.54166666666</v>
       </c>
       <c r="B54">
-        <v>51.06</v>
+        <v>2.806</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1691,10 +1697,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46225.55208333334</v>
+        <v>46226.55208333334</v>
       </c>
       <c r="B55">
-        <v>48.561</v>
+        <v>0.586</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1708,10 +1714,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46225.5625</v>
+        <v>46226.5625</v>
       </c>
       <c r="B56">
-        <v>33.902</v>
+        <v>6.953</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1725,13 +1731,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46225.57291666666</v>
+        <v>46226.57291666666</v>
       </c>
       <c r="B57">
-        <v>18.576</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>7.431</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1742,13 +1748,13 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46225.58333333334</v>
+        <v>46226.58333333334</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>4.783</v>
       </c>
       <c r="C58">
-        <v>15.446</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>57</v>
@@ -1759,13 +1765,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46225.59375</v>
+        <v>46226.59375</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>77.895</v>
+        <v>3.718</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1776,13 +1782,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46225.60416666666</v>
+        <v>46226.60416666666</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>2.337</v>
       </c>
       <c r="C60">
-        <v>77.065</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1793,13 +1799,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46225.61458333334</v>
+        <v>46226.61458333334</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>15.347</v>
+        <v>2.037</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1810,10 +1816,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46225.625</v>
+        <v>46226.625</v>
       </c>
       <c r="B62">
-        <v>1.92</v>
+        <v>1.952</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -1827,13 +1833,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46225.63541666666</v>
+        <v>46226.63541666666</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>6.297</v>
       </c>
       <c r="C63">
-        <v>0.963</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1844,13 +1850,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46225.64583333334</v>
+        <v>46226.64583333334</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>2.237</v>
       </c>
       <c r="C64">
-        <v>3.659</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -1861,13 +1867,13 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46225.65625</v>
+        <v>46226.65625</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>18.624</v>
       </c>
       <c r="C65">
-        <v>4.681</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>64</v>
@@ -1878,13 +1884,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46225.66666666666</v>
+        <v>46226.66666666666</v>
       </c>
       <c r="B66">
-        <v>2.491</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>2.042</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -1895,13 +1901,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46225.67708333334</v>
+        <v>46226.67708333334</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>14.788</v>
+        <v>0.447</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1912,13 +1918,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46225.6875</v>
+        <v>46226.6875</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>0.806</v>
       </c>
       <c r="C68">
-        <v>13.361</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -1929,13 +1935,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46225.69791666666</v>
+        <v>46226.69791666666</v>
       </c>
       <c r="B69">
-        <v>3.271</v>
+        <v>0</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>2.641</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -1946,13 +1952,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46225.70833333334</v>
+        <v>46226.70833333334</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>10.92</v>
+        <v>0.893</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -1963,13 +1969,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46225.71875</v>
+        <v>46226.71875</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>10.236</v>
       </c>
       <c r="C71">
-        <v>12.962</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -1980,13 +1986,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46225.72916666666</v>
+        <v>46226.72916666666</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72">
-        <v>6.778</v>
+        <v>0.503</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -1997,13 +2003,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46225.73958333334</v>
+        <v>46226.73958333334</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>8.259</v>
       </c>
       <c r="C73">
-        <v>22.349</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2014,13 +2020,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46225.75</v>
+        <v>46226.75</v>
       </c>
       <c r="B74">
         <v>0</v>
       </c>
       <c r="C74">
-        <v>13.175</v>
+        <v>11.024</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2031,13 +2037,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46225.76041666666</v>
+        <v>46226.76041666666</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>14.824</v>
+        <v>17.192</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2048,13 +2054,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46225.77083333334</v>
+        <v>46226.77083333334</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76">
-        <v>11.678</v>
+        <v>22.492</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2065,13 +2071,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46225.78125</v>
+        <v>46226.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>17.783</v>
+        <v>20.623</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2082,13 +2088,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46225.79166666666</v>
+        <v>46226.79166666666</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>24.522</v>
+        <v>38.663</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2099,13 +2105,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46225.80208333334</v>
+        <v>46226.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>32.281</v>
+        <v>20.448</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2116,13 +2122,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46225.8125</v>
+        <v>46226.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>33.871</v>
+        <v>29.019</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2133,13 +2139,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46225.82291666666</v>
+        <v>46226.82291666666</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>15.806</v>
+        <v>14.5</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2150,13 +2156,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46225.83333333334</v>
+        <v>46226.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>12.485</v>
+        <v>14.296</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2167,13 +2173,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46225.84375</v>
+        <v>46226.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>9.784000000000001</v>
+        <v>8.228</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2184,13 +2190,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46225.85416666666</v>
+        <v>46226.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>16.679</v>
+        <v>9.022</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2201,10 +2207,10 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46225.86458333334</v>
+        <v>46226.86458333334</v>
       </c>
       <c r="B85">
-        <v>1.746</v>
+        <v>13.215</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -2218,13 +2224,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46225.875</v>
+        <v>46226.875</v>
       </c>
       <c r="B86">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>4.866</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2235,13 +2241,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46225.88541666666</v>
+        <v>46226.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>6.126</v>
+        <v>8.864000000000001</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2252,13 +2258,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46225.89583333334</v>
+        <v>46226.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>26.176</v>
+        <v>8.727</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2269,13 +2275,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46225.90625</v>
+        <v>46226.90625</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>19.091</v>
+        <v>4.942</v>
       </c>
       <c r="D89">
         <v>88</v>
@@ -2286,13 +2292,13 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="2">
-        <v>46225.91666666666</v>
+        <v>46226.91666666666</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>3.435</v>
       </c>
       <c r="C90">
-        <v>29.361</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>89</v>
@@ -2303,13 +2309,13 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="2">
-        <v>46225.92708333334</v>
+        <v>46226.92708333334</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>6.67</v>
+        <v>7.929</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -2320,13 +2326,13 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="2">
-        <v>46225.9375</v>
+        <v>46226.9375</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>32.573</v>
+        <v>7.121</v>
       </c>
       <c r="D92">
         <v>91</v>
@@ -2337,13 +2343,13 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="2">
-        <v>46225.94791666666</v>
+        <v>46226.94791666666</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>22.941</v>
+        <v>5.552</v>
       </c>
       <c r="D93">
         <v>92</v>
@@ -2354,13 +2360,13 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="2">
-        <v>46225.95833333334</v>
+        <v>46226.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>3.229</v>
       </c>
       <c r="C94">
-        <v>5.754</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>93</v>
@@ -2371,10 +2377,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="2">
-        <v>46225.96875</v>
+        <v>46226.96875</v>
       </c>
       <c r="B95">
-        <v>11.348</v>
+        <v>0.659</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2388,13 +2394,13 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="2">
-        <v>46225.97916666666</v>
+        <v>46226.97916666666</v>
       </c>
       <c r="B96">
-        <v>10.554</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1.568</v>
       </c>
       <c r="D96">
         <v>95</v>
@@ -2405,13 +2411,13 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="2">
-        <v>46225.98958333334</v>
+        <v>46226.98958333334</v>
       </c>
       <c r="B97">
-        <v>14.096</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>2.778</v>
       </c>
       <c r="D97">
         <v>96</v>
@@ -2422,13 +2428,13 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>4.119</v>
       </c>
       <c r="C98">
-        <v>6.068</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -2439,10 +2445,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="2">
-        <v>46226.01041666666</v>
+        <v>46227.01041666666</v>
       </c>
       <c r="B99">
-        <v>0.283</v>
+        <v>8.491</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2456,13 +2462,13 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="2">
-        <v>46226.02083333334</v>
+        <v>46227.02083333334</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="C100">
-        <v>5.298</v>
+        <v>0</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -2473,13 +2479,13 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="2">
-        <v>46226.03125</v>
+        <v>46227.03125</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
       <c r="C101">
-        <v>1.158</v>
+        <v>0.5</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -2490,13 +2496,13 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="2">
-        <v>46226.04166666666</v>
+        <v>46227.04166666666</v>
       </c>
       <c r="B102">
-        <v>7.019</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>3.562</v>
       </c>
       <c r="D102">
         <v>5</v>
@@ -2507,13 +2513,13 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="2">
-        <v>46226.05208333334</v>
+        <v>46227.05208333334</v>
       </c>
       <c r="B103">
-        <v>7.417</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>7.831</v>
       </c>
       <c r="D103">
         <v>6</v>
@@ -2524,13 +2530,13 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="2">
-        <v>46226.0625</v>
+        <v>46227.0625</v>
       </c>
       <c r="B104">
-        <v>30.441</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>10.54</v>
       </c>
       <c r="D104">
         <v>7</v>
@@ -2541,13 +2547,13 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="2">
-        <v>46226.07291666666</v>
+        <v>46227.07291666666</v>
       </c>
       <c r="B105">
-        <v>22.621</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -2558,13 +2564,13 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="2">
-        <v>46226.08333333334</v>
+        <v>46227.08333333334</v>
       </c>
       <c r="B106">
-        <v>11.601</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>10.591</v>
       </c>
       <c r="D106">
         <v>9</v>
@@ -2575,13 +2581,13 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="2">
-        <v>46226.09375</v>
+        <v>46227.09375</v>
       </c>
       <c r="B107">
-        <v>26.659</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>6.178</v>
       </c>
       <c r="D107">
         <v>10</v>
@@ -2592,13 +2598,13 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="2">
-        <v>46226.10416666666</v>
+        <v>46227.10416666666</v>
       </c>
       <c r="B108">
-        <v>36.27</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>5.688</v>
       </c>
       <c r="D108">
         <v>11</v>
@@ -2609,10 +2615,10 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="2">
-        <v>46226.11458333334</v>
+        <v>46227.11458333334</v>
       </c>
       <c r="B109">
-        <v>30.689</v>
+        <v>0.578</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2626,13 +2632,13 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="2">
-        <v>46226.125</v>
+        <v>46227.125</v>
       </c>
       <c r="B110">
-        <v>44.156</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>7.778</v>
       </c>
       <c r="D110">
         <v>13</v>
@@ -2643,13 +2649,13 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="2">
-        <v>46226.13541666666</v>
+        <v>46227.13541666666</v>
       </c>
       <c r="B111">
-        <v>22.926</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>23.331</v>
       </c>
       <c r="D111">
         <v>14</v>
@@ -2660,13 +2666,13 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="2">
-        <v>46226.14583333334</v>
+        <v>46227.14583333334</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
       <c r="C112">
-        <v>2.199</v>
+        <v>2.326</v>
       </c>
       <c r="D112">
         <v>15</v>
@@ -2677,10 +2683,10 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="2">
-        <v>46226.15625</v>
+        <v>46227.15625</v>
       </c>
       <c r="B113">
-        <v>9.186</v>
+        <v>2.196</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -2694,10 +2700,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="2">
-        <v>46226.16666666666</v>
+        <v>46227.16666666666</v>
       </c>
       <c r="B114">
-        <v>2.1</v>
+        <v>5.266</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2711,13 +2717,13 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="2">
-        <v>46226.17708333334</v>
+        <v>46227.17708333334</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="C115">
-        <v>3.757</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>18</v>
@@ -2728,13 +2734,13 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="2">
-        <v>46226.1875</v>
+        <v>46227.1875</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="C116">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>19</v>
@@ -2745,10 +2751,10 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="2">
-        <v>46226.19791666666</v>
+        <v>46227.19791666666</v>
       </c>
       <c r="B117">
-        <v>2.491</v>
+        <v>7.083</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -2762,13 +2768,13 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="2">
-        <v>46226.20833333334</v>
+        <v>46227.20833333334</v>
       </c>
       <c r="B118">
         <v>0</v>
       </c>
       <c r="C118">
-        <v>3.711</v>
+        <v>10.937</v>
       </c>
       <c r="D118">
         <v>21</v>
@@ -2779,13 +2785,13 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="2">
-        <v>46226.21875</v>
+        <v>46227.21875</v>
       </c>
       <c r="B119">
         <v>0</v>
       </c>
       <c r="C119">
-        <v>10.077</v>
+        <v>15.234</v>
       </c>
       <c r="D119">
         <v>22</v>
@@ -2796,13 +2802,13 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="2">
-        <v>46226.22916666666</v>
+        <v>46227.22916666666</v>
       </c>
       <c r="B120">
-        <v>2.932</v>
+        <v>0</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>7.815</v>
       </c>
       <c r="D120">
         <v>23</v>
@@ -2813,13 +2819,13 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="2">
-        <v>46226.23958333334</v>
+        <v>46227.23958333334</v>
       </c>
       <c r="B121">
-        <v>8.718</v>
+        <v>0</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>3.864</v>
       </c>
       <c r="D121">
         <v>24</v>
@@ -2830,13 +2836,13 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="2">
-        <v>46226.25</v>
+        <v>46227.25</v>
       </c>
       <c r="B122">
         <v>0</v>
       </c>
       <c r="C122">
-        <v>2.094</v>
+        <v>15.482</v>
       </c>
       <c r="D122">
         <v>25</v>
@@ -2847,13 +2853,13 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="2">
-        <v>46226.26041666666</v>
+        <v>46227.26041666666</v>
       </c>
       <c r="B123">
-        <v>6.624</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>26.811</v>
       </c>
       <c r="D123">
         <v>26</v>
@@ -2864,13 +2870,13 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="2">
-        <v>46226.27083333334</v>
+        <v>46227.27083333334</v>
       </c>
       <c r="B124">
-        <v>18.982</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>2.211</v>
       </c>
       <c r="D124">
         <v>27</v>
@@ -2881,13 +2887,13 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="2">
-        <v>46226.28125</v>
+        <v>46227.28125</v>
       </c>
       <c r="B125">
-        <v>1.808</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>6.121</v>
       </c>
       <c r="D125">
         <v>28</v>
@@ -2898,13 +2904,13 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="2">
-        <v>46226.29166666666</v>
+        <v>46227.29166666666</v>
       </c>
       <c r="B126">
         <v>0</v>
       </c>
       <c r="C126">
-        <v>6.037</v>
+        <v>5.055</v>
       </c>
       <c r="D126">
         <v>29</v>
@@ -2915,19 +2921,53 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="2">
-        <v>46226.30208333334</v>
+        <v>46227.30208333334</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
       <c r="C127">
-        <v>11.799</v>
+        <v>15.712</v>
       </c>
       <c r="D127">
         <v>30</v>
       </c>
       <c r="E127" t="s">
         <v>130</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="2">
+        <v>46227.3125</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>16.329</v>
+      </c>
+      <c r="D128">
+        <v>31</v>
+      </c>
+      <c r="E128" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="2">
+        <v>46227.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>16.228</v>
+      </c>
+      <c r="D129">
+        <v>32</v>
+      </c>
+      <c r="E129" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Unintended_Deviation.xlsx
+++ b/data_fetching/Entsoe/Unintended_Deviation.xlsx
@@ -31,388 +31,388 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>23.07.20261</t>
-  </si>
-  <si>
-    <t>23.07.20262</t>
-  </si>
-  <si>
-    <t>23.07.20263</t>
-  </si>
-  <si>
-    <t>23.07.20264</t>
-  </si>
-  <si>
-    <t>23.07.20265</t>
-  </si>
-  <si>
-    <t>23.07.20266</t>
-  </si>
-  <si>
-    <t>23.07.20267</t>
-  </si>
-  <si>
-    <t>23.07.20268</t>
-  </si>
-  <si>
-    <t>23.07.20269</t>
-  </si>
-  <si>
-    <t>23.07.202610</t>
-  </si>
-  <si>
-    <t>23.07.202611</t>
-  </si>
-  <si>
-    <t>23.07.202612</t>
-  </si>
-  <si>
-    <t>23.07.202613</t>
-  </si>
-  <si>
-    <t>23.07.202614</t>
-  </si>
-  <si>
-    <t>23.07.202615</t>
-  </si>
-  <si>
-    <t>23.07.202616</t>
-  </si>
-  <si>
-    <t>23.07.202617</t>
-  </si>
-  <si>
-    <t>23.07.202618</t>
-  </si>
-  <si>
-    <t>23.07.202619</t>
-  </si>
-  <si>
-    <t>23.07.202620</t>
-  </si>
-  <si>
-    <t>23.07.202621</t>
-  </si>
-  <si>
-    <t>23.07.202622</t>
-  </si>
-  <si>
-    <t>23.07.202623</t>
-  </si>
-  <si>
-    <t>23.07.202624</t>
-  </si>
-  <si>
-    <t>23.07.202625</t>
-  </si>
-  <si>
-    <t>23.07.202626</t>
-  </si>
-  <si>
-    <t>23.07.202627</t>
-  </si>
-  <si>
-    <t>23.07.202628</t>
-  </si>
-  <si>
-    <t>23.07.202629</t>
-  </si>
-  <si>
-    <t>23.07.202630</t>
-  </si>
-  <si>
-    <t>23.07.202631</t>
-  </si>
-  <si>
-    <t>23.07.202632</t>
-  </si>
-  <si>
-    <t>23.07.202633</t>
-  </si>
-  <si>
-    <t>23.07.202634</t>
-  </si>
-  <si>
-    <t>23.07.202635</t>
-  </si>
-  <si>
-    <t>23.07.202636</t>
-  </si>
-  <si>
-    <t>23.07.202637</t>
-  </si>
-  <si>
-    <t>23.07.202638</t>
-  </si>
-  <si>
-    <t>23.07.202639</t>
-  </si>
-  <si>
-    <t>23.07.202640</t>
-  </si>
-  <si>
-    <t>23.07.202641</t>
-  </si>
-  <si>
-    <t>23.07.202642</t>
-  </si>
-  <si>
-    <t>23.07.202643</t>
-  </si>
-  <si>
-    <t>23.07.202644</t>
-  </si>
-  <si>
-    <t>23.07.202645</t>
-  </si>
-  <si>
-    <t>23.07.202646</t>
-  </si>
-  <si>
-    <t>23.07.202647</t>
-  </si>
-  <si>
-    <t>23.07.202648</t>
-  </si>
-  <si>
-    <t>23.07.202649</t>
-  </si>
-  <si>
-    <t>23.07.202650</t>
-  </si>
-  <si>
-    <t>23.07.202651</t>
-  </si>
-  <si>
-    <t>23.07.202652</t>
-  </si>
-  <si>
-    <t>23.07.202653</t>
-  </si>
-  <si>
-    <t>23.07.202654</t>
-  </si>
-  <si>
-    <t>23.07.202655</t>
-  </si>
-  <si>
-    <t>23.07.202656</t>
-  </si>
-  <si>
-    <t>23.07.202657</t>
-  </si>
-  <si>
-    <t>23.07.202658</t>
-  </si>
-  <si>
-    <t>23.07.202659</t>
-  </si>
-  <si>
-    <t>23.07.202660</t>
-  </si>
-  <si>
-    <t>23.07.202661</t>
-  </si>
-  <si>
-    <t>23.07.202662</t>
-  </si>
-  <si>
-    <t>23.07.202663</t>
-  </si>
-  <si>
-    <t>23.07.202664</t>
-  </si>
-  <si>
-    <t>23.07.202665</t>
-  </si>
-  <si>
-    <t>23.07.202666</t>
-  </si>
-  <si>
-    <t>23.07.202667</t>
-  </si>
-  <si>
-    <t>23.07.202668</t>
-  </si>
-  <si>
-    <t>23.07.202669</t>
-  </si>
-  <si>
-    <t>23.07.202670</t>
-  </si>
-  <si>
-    <t>23.07.202671</t>
-  </si>
-  <si>
-    <t>23.07.202672</t>
-  </si>
-  <si>
-    <t>23.07.202673</t>
-  </si>
-  <si>
-    <t>23.07.202674</t>
-  </si>
-  <si>
-    <t>23.07.202675</t>
-  </si>
-  <si>
-    <t>23.07.202676</t>
-  </si>
-  <si>
-    <t>23.07.202677</t>
-  </si>
-  <si>
-    <t>23.07.202678</t>
-  </si>
-  <si>
-    <t>23.07.202679</t>
-  </si>
-  <si>
-    <t>23.07.202680</t>
-  </si>
-  <si>
-    <t>23.07.202681</t>
-  </si>
-  <si>
-    <t>23.07.202682</t>
-  </si>
-  <si>
-    <t>23.07.202683</t>
-  </si>
-  <si>
-    <t>23.07.202684</t>
-  </si>
-  <si>
-    <t>23.07.202685</t>
-  </si>
-  <si>
-    <t>23.07.202686</t>
-  </si>
-  <si>
-    <t>23.07.202687</t>
-  </si>
-  <si>
-    <t>23.07.202688</t>
-  </si>
-  <si>
-    <t>23.07.202689</t>
-  </si>
-  <si>
-    <t>23.07.202690</t>
-  </si>
-  <si>
-    <t>23.07.202691</t>
-  </si>
-  <si>
-    <t>23.07.202692</t>
-  </si>
-  <si>
-    <t>23.07.202693</t>
-  </si>
-  <si>
-    <t>23.07.202694</t>
-  </si>
-  <si>
-    <t>23.07.202695</t>
-  </si>
-  <si>
-    <t>23.07.202696</t>
-  </si>
-  <si>
-    <t>24.07.20261</t>
-  </si>
-  <si>
-    <t>24.07.20262</t>
-  </si>
-  <si>
-    <t>24.07.20263</t>
-  </si>
-  <si>
-    <t>24.07.20264</t>
-  </si>
-  <si>
-    <t>24.07.20265</t>
-  </si>
-  <si>
-    <t>24.07.20266</t>
-  </si>
-  <si>
-    <t>24.07.20267</t>
-  </si>
-  <si>
-    <t>24.07.20268</t>
-  </si>
-  <si>
-    <t>24.07.20269</t>
-  </si>
-  <si>
-    <t>24.07.202610</t>
-  </si>
-  <si>
-    <t>24.07.202611</t>
-  </si>
-  <si>
-    <t>24.07.202612</t>
-  </si>
-  <si>
-    <t>24.07.202613</t>
-  </si>
-  <si>
-    <t>24.07.202614</t>
-  </si>
-  <si>
-    <t>24.07.202615</t>
-  </si>
-  <si>
-    <t>24.07.202616</t>
-  </si>
-  <si>
-    <t>24.07.202617</t>
-  </si>
-  <si>
-    <t>24.07.202618</t>
-  </si>
-  <si>
-    <t>24.07.202619</t>
-  </si>
-  <si>
-    <t>24.07.202620</t>
-  </si>
-  <si>
-    <t>24.07.202621</t>
-  </si>
-  <si>
-    <t>24.07.202622</t>
-  </si>
-  <si>
-    <t>24.07.202623</t>
-  </si>
-  <si>
-    <t>24.07.202624</t>
-  </si>
-  <si>
-    <t>24.07.202625</t>
-  </si>
-  <si>
-    <t>24.07.202626</t>
-  </si>
-  <si>
-    <t>24.07.202627</t>
-  </si>
-  <si>
-    <t>24.07.202628</t>
-  </si>
-  <si>
-    <t>24.07.202629</t>
-  </si>
-  <si>
-    <t>24.07.202630</t>
-  </si>
-  <si>
-    <t>24.07.202631</t>
-  </si>
-  <si>
-    <t>24.07.202632</t>
+    <t>25.07.20261</t>
+  </si>
+  <si>
+    <t>25.07.20262</t>
+  </si>
+  <si>
+    <t>25.07.20263</t>
+  </si>
+  <si>
+    <t>25.07.20264</t>
+  </si>
+  <si>
+    <t>25.07.20265</t>
+  </si>
+  <si>
+    <t>25.07.20266</t>
+  </si>
+  <si>
+    <t>25.07.20267</t>
+  </si>
+  <si>
+    <t>25.07.20268</t>
+  </si>
+  <si>
+    <t>25.07.20269</t>
+  </si>
+  <si>
+    <t>25.07.202610</t>
+  </si>
+  <si>
+    <t>25.07.202611</t>
+  </si>
+  <si>
+    <t>25.07.202612</t>
+  </si>
+  <si>
+    <t>25.07.202613</t>
+  </si>
+  <si>
+    <t>25.07.202614</t>
+  </si>
+  <si>
+    <t>25.07.202615</t>
+  </si>
+  <si>
+    <t>25.07.202616</t>
+  </si>
+  <si>
+    <t>25.07.202617</t>
+  </si>
+  <si>
+    <t>25.07.202618</t>
+  </si>
+  <si>
+    <t>25.07.202619</t>
+  </si>
+  <si>
+    <t>25.07.202620</t>
+  </si>
+  <si>
+    <t>25.07.202621</t>
+  </si>
+  <si>
+    <t>25.07.202622</t>
+  </si>
+  <si>
+    <t>25.07.202623</t>
+  </si>
+  <si>
+    <t>25.07.202624</t>
+  </si>
+  <si>
+    <t>25.07.202625</t>
+  </si>
+  <si>
+    <t>25.07.202626</t>
+  </si>
+  <si>
+    <t>25.07.202627</t>
+  </si>
+  <si>
+    <t>25.07.202628</t>
+  </si>
+  <si>
+    <t>25.07.202629</t>
+  </si>
+  <si>
+    <t>25.07.202630</t>
+  </si>
+  <si>
+    <t>25.07.202631</t>
+  </si>
+  <si>
+    <t>25.07.202632</t>
+  </si>
+  <si>
+    <t>25.07.202633</t>
+  </si>
+  <si>
+    <t>25.07.202634</t>
+  </si>
+  <si>
+    <t>25.07.202635</t>
+  </si>
+  <si>
+    <t>25.07.202636</t>
+  </si>
+  <si>
+    <t>25.07.202637</t>
+  </si>
+  <si>
+    <t>25.07.202638</t>
+  </si>
+  <si>
+    <t>25.07.202639</t>
+  </si>
+  <si>
+    <t>25.07.202640</t>
+  </si>
+  <si>
+    <t>25.07.202641</t>
+  </si>
+  <si>
+    <t>25.07.202642</t>
+  </si>
+  <si>
+    <t>25.07.202643</t>
+  </si>
+  <si>
+    <t>25.07.202644</t>
+  </si>
+  <si>
+    <t>25.07.202645</t>
+  </si>
+  <si>
+    <t>25.07.202646</t>
+  </si>
+  <si>
+    <t>25.07.202647</t>
+  </si>
+  <si>
+    <t>25.07.202648</t>
+  </si>
+  <si>
+    <t>25.07.202649</t>
+  </si>
+  <si>
+    <t>25.07.202650</t>
+  </si>
+  <si>
+    <t>25.07.202651</t>
+  </si>
+  <si>
+    <t>25.07.202652</t>
+  </si>
+  <si>
+    <t>25.07.202653</t>
+  </si>
+  <si>
+    <t>25.07.202654</t>
+  </si>
+  <si>
+    <t>25.07.202655</t>
+  </si>
+  <si>
+    <t>25.07.202656</t>
+  </si>
+  <si>
+    <t>25.07.202657</t>
+  </si>
+  <si>
+    <t>25.07.202658</t>
+  </si>
+  <si>
+    <t>25.07.202659</t>
+  </si>
+  <si>
+    <t>25.07.202660</t>
+  </si>
+  <si>
+    <t>25.07.202661</t>
+  </si>
+  <si>
+    <t>25.07.202662</t>
+  </si>
+  <si>
+    <t>25.07.202663</t>
+  </si>
+  <si>
+    <t>25.07.202664</t>
+  </si>
+  <si>
+    <t>25.07.202665</t>
+  </si>
+  <si>
+    <t>25.07.202666</t>
+  </si>
+  <si>
+    <t>25.07.202667</t>
+  </si>
+  <si>
+    <t>25.07.202668</t>
+  </si>
+  <si>
+    <t>25.07.202669</t>
+  </si>
+  <si>
+    <t>25.07.202670</t>
+  </si>
+  <si>
+    <t>25.07.202671</t>
+  </si>
+  <si>
+    <t>25.07.202672</t>
+  </si>
+  <si>
+    <t>25.07.202673</t>
+  </si>
+  <si>
+    <t>25.07.202674</t>
+  </si>
+  <si>
+    <t>25.07.202675</t>
+  </si>
+  <si>
+    <t>25.07.202676</t>
+  </si>
+  <si>
+    <t>25.07.202677</t>
+  </si>
+  <si>
+    <t>25.07.202678</t>
+  </si>
+  <si>
+    <t>25.07.202679</t>
+  </si>
+  <si>
+    <t>25.07.202680</t>
+  </si>
+  <si>
+    <t>25.07.202681</t>
+  </si>
+  <si>
+    <t>25.07.202682</t>
+  </si>
+  <si>
+    <t>25.07.202683</t>
+  </si>
+  <si>
+    <t>25.07.202684</t>
+  </si>
+  <si>
+    <t>25.07.202685</t>
+  </si>
+  <si>
+    <t>25.07.202686</t>
+  </si>
+  <si>
+    <t>25.07.202687</t>
+  </si>
+  <si>
+    <t>25.07.202688</t>
+  </si>
+  <si>
+    <t>25.07.202689</t>
+  </si>
+  <si>
+    <t>25.07.202690</t>
+  </si>
+  <si>
+    <t>25.07.202691</t>
+  </si>
+  <si>
+    <t>25.07.202692</t>
+  </si>
+  <si>
+    <t>25.07.202693</t>
+  </si>
+  <si>
+    <t>25.07.202694</t>
+  </si>
+  <si>
+    <t>25.07.202695</t>
+  </si>
+  <si>
+    <t>25.07.202696</t>
+  </si>
+  <si>
+    <t>26.07.20261</t>
+  </si>
+  <si>
+    <t>26.07.20262</t>
+  </si>
+  <si>
+    <t>26.07.20263</t>
+  </si>
+  <si>
+    <t>26.07.20264</t>
+  </si>
+  <si>
+    <t>26.07.20265</t>
+  </si>
+  <si>
+    <t>26.07.20266</t>
+  </si>
+  <si>
+    <t>26.07.20267</t>
+  </si>
+  <si>
+    <t>26.07.20268</t>
+  </si>
+  <si>
+    <t>26.07.20269</t>
+  </si>
+  <si>
+    <t>26.07.202610</t>
+  </si>
+  <si>
+    <t>26.07.202611</t>
+  </si>
+  <si>
+    <t>26.07.202612</t>
+  </si>
+  <si>
+    <t>26.07.202613</t>
+  </si>
+  <si>
+    <t>26.07.202614</t>
+  </si>
+  <si>
+    <t>26.07.202615</t>
+  </si>
+  <si>
+    <t>26.07.202616</t>
+  </si>
+  <si>
+    <t>26.07.202617</t>
+  </si>
+  <si>
+    <t>26.07.202618</t>
+  </si>
+  <si>
+    <t>26.07.202619</t>
+  </si>
+  <si>
+    <t>26.07.202620</t>
+  </si>
+  <si>
+    <t>26.07.202621</t>
+  </si>
+  <si>
+    <t>26.07.202622</t>
+  </si>
+  <si>
+    <t>26.07.202623</t>
+  </si>
+  <si>
+    <t>26.07.202624</t>
+  </si>
+  <si>
+    <t>26.07.202625</t>
+  </si>
+  <si>
+    <t>26.07.202626</t>
+  </si>
+  <si>
+    <t>26.07.202627</t>
+  </si>
+  <si>
+    <t>26.07.202628</t>
+  </si>
+  <si>
+    <t>26.07.202629</t>
+  </si>
+  <si>
+    <t>26.07.202630</t>
+  </si>
+  <si>
+    <t>26.07.202631</t>
+  </si>
+  <si>
+    <t>26.07.202632</t>
   </si>
 </sst>
 </file>
@@ -796,13 +796,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>6.068</v>
+        <v>33.677</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -813,13 +813,13 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>46226.01041666666</v>
+        <v>46228.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.283</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>34.937</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -830,13 +830,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>46226.02083333334</v>
+        <v>46228.02083333334</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>5.298</v>
+        <v>20.989</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -847,13 +847,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>46226.03125</v>
+        <v>46228.03125</v>
       </c>
       <c r="B5">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>1.158</v>
+        <v>31.204</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -864,13 +864,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>46226.04166666666</v>
+        <v>46228.04166666666</v>
       </c>
       <c r="B6">
-        <v>7.019</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>47.962</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -881,13 +881,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>46226.05208333334</v>
+        <v>46228.05208333334</v>
       </c>
       <c r="B7">
-        <v>7.417</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>27.301</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -898,13 +898,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>46226.0625</v>
+        <v>46228.0625</v>
       </c>
       <c r="B8">
-        <v>30.441</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>19.127</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -915,13 +915,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>46226.07291666666</v>
+        <v>46228.07291666666</v>
       </c>
       <c r="B9">
-        <v>22.621</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>28.103</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -932,13 +932,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>46226.08333333334</v>
+        <v>46228.08333333334</v>
       </c>
       <c r="B10">
-        <v>11.601</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>19.879</v>
       </c>
       <c r="D10">
         <v>9</v>
@@ -949,13 +949,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>46226.09375</v>
+        <v>46228.09375</v>
       </c>
       <c r="B11">
-        <v>26.659</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>22.391</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -966,13 +966,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>46226.10416666666</v>
+        <v>46228.10416666666</v>
       </c>
       <c r="B12">
-        <v>36.27</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>39.999</v>
       </c>
       <c r="D12">
         <v>11</v>
@@ -983,13 +983,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>46226.11458333334</v>
+        <v>46228.11458333334</v>
       </c>
       <c r="B13">
-        <v>30.689</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>12.818</v>
       </c>
       <c r="D13">
         <v>12</v>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>46226.125</v>
+        <v>46228.125</v>
       </c>
       <c r="B14">
-        <v>44.156</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>19.012</v>
       </c>
       <c r="D14">
         <v>13</v>
@@ -1017,13 +1017,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>46226.13541666666</v>
+        <v>46228.13541666666</v>
       </c>
       <c r="B15">
-        <v>22.926</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="D15">
         <v>14</v>
@@ -1034,13 +1034,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>46226.14583333334</v>
+        <v>46228.14583333334</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="C16">
-        <v>2.199</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>15</v>
@@ -1051,10 +1051,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>46226.15625</v>
+        <v>46228.15625</v>
       </c>
       <c r="B17">
-        <v>9.186</v>
+        <v>5.876</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>46226.16666666666</v>
+        <v>46228.16666666666</v>
       </c>
       <c r="B18">
-        <v>2.1</v>
+        <v>2.124</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1085,13 +1085,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46226.17708333334</v>
+        <v>46228.17708333334</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>11.16</v>
       </c>
       <c r="C19">
-        <v>3.757</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>18</v>
@@ -1102,13 +1102,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46226.1875</v>
+        <v>46228.1875</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>7.444</v>
       </c>
       <c r="C20">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -1119,13 +1119,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46226.19791666666</v>
+        <v>46228.19791666666</v>
       </c>
       <c r="B21">
-        <v>2.491</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="D21">
         <v>20</v>
@@ -1136,13 +1136,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46226.20833333334</v>
+        <v>46228.20833333334</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22">
-        <v>3.711</v>
+        <v>7.77</v>
       </c>
       <c r="D22">
         <v>21</v>
@@ -1153,13 +1153,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46226.21875</v>
+        <v>46228.21875</v>
       </c>
       <c r="B23">
         <v>0</v>
       </c>
       <c r="C23">
-        <v>10.077</v>
+        <v>6.505</v>
       </c>
       <c r="D23">
         <v>22</v>
@@ -1170,13 +1170,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46226.22916666666</v>
+        <v>46228.22916666666</v>
       </c>
       <c r="B24">
-        <v>2.932</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>7.785</v>
       </c>
       <c r="D24">
         <v>23</v>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46226.23958333334</v>
+        <v>46228.23958333334</v>
       </c>
       <c r="B25">
-        <v>8.718</v>
+        <v>1.109</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1204,13 +1204,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46226.25</v>
+        <v>46228.25</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>2.094</v>
+        <v>9.026</v>
       </c>
       <c r="D26">
         <v>25</v>
@@ -1221,13 +1221,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46226.26041666666</v>
+        <v>46228.26041666666</v>
       </c>
       <c r="B27">
-        <v>6.624</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>13.201</v>
       </c>
       <c r="D27">
         <v>26</v>
@@ -1238,13 +1238,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="2">
-        <v>46226.27083333334</v>
+        <v>46228.27083333334</v>
       </c>
       <c r="B28">
-        <v>18.982</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>4.533</v>
       </c>
       <c r="D28">
         <v>27</v>
@@ -1255,13 +1255,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="2">
-        <v>46226.28125</v>
+        <v>46228.28125</v>
       </c>
       <c r="B29">
-        <v>1.808</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>8.98</v>
       </c>
       <c r="D29">
         <v>28</v>
@@ -1272,13 +1272,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="2">
-        <v>46226.29166666666</v>
+        <v>46228.29166666666</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>6.037</v>
+        <v>1.987</v>
       </c>
       <c r="D30">
         <v>29</v>
@@ -1289,13 +1289,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="2">
-        <v>46226.30208333334</v>
+        <v>46228.30208333334</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>11.799</v>
+        <v>12.223</v>
       </c>
       <c r="D31">
         <v>30</v>
@@ -1306,13 +1306,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="2">
-        <v>46226.3125</v>
+        <v>46228.3125</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>4.995</v>
       </c>
       <c r="C32">
-        <v>1.048</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>31</v>
@@ -1323,13 +1323,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="2">
-        <v>46226.32291666666</v>
+        <v>46228.32291666666</v>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>17.528</v>
+        <v>6.486</v>
       </c>
       <c r="D33">
         <v>32</v>
@@ -1340,13 +1340,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="2">
-        <v>46226.33333333334</v>
+        <v>46228.33333333334</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="C34">
-        <v>4.378</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>33</v>
@@ -1357,13 +1357,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="2">
-        <v>46226.34375</v>
+        <v>46228.34375</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>2.195</v>
       </c>
       <c r="C35">
-        <v>36.155</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>34</v>
@@ -1374,13 +1374,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="2">
-        <v>46226.35416666666</v>
+        <v>46228.35416666666</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>28.488</v>
+        <v>4.255</v>
       </c>
       <c r="D36">
         <v>35</v>
@@ -1391,13 +1391,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="2">
-        <v>46226.36458333334</v>
+        <v>46228.36458333334</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>0.891</v>
       </c>
       <c r="C37">
-        <v>12.155</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>36</v>
@@ -1408,13 +1408,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="2">
-        <v>46226.375</v>
+        <v>46228.375</v>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>2.204</v>
+        <v>1.431</v>
       </c>
       <c r="D38">
         <v>37</v>
@@ -1425,13 +1425,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2">
-        <v>46226.38541666666</v>
+        <v>46228.38541666666</v>
       </c>
       <c r="B39">
-        <v>1.148</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D39">
         <v>38</v>
@@ -1442,13 +1442,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="2">
-        <v>46226.39583333334</v>
+        <v>46228.39583333334</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>9.720000000000001</v>
+        <v>9.552</v>
       </c>
       <c r="D40">
         <v>39</v>
@@ -1459,13 +1459,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="2">
-        <v>46226.40625</v>
+        <v>46228.40625</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>4.354</v>
       </c>
       <c r="C41">
-        <v>5.716</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>40</v>
@@ -1476,13 +1476,13 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="2">
-        <v>46226.41666666666</v>
+        <v>46228.41666666666</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>8.101000000000001</v>
       </c>
       <c r="C42">
-        <v>1.617</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>41</v>
@@ -1493,10 +1493,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="2">
-        <v>46226.42708333334</v>
+        <v>46228.42708333334</v>
       </c>
       <c r="B43">
-        <v>3.046</v>
+        <v>23.813</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1510,13 +1510,13 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="2">
-        <v>46226.4375</v>
+        <v>46228.4375</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>6.706</v>
       </c>
       <c r="C44">
-        <v>8.27</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>43</v>
@@ -1527,13 +1527,13 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="2">
-        <v>46226.44791666666</v>
+        <v>46228.44791666666</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>12.831</v>
       </c>
       <c r="C45">
-        <v>19.398</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>44</v>
@@ -1544,13 +1544,13 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="2">
-        <v>46226.45833333334</v>
+        <v>46228.45833333334</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>44.449</v>
       </c>
       <c r="C46">
-        <v>21.862</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>45</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="2">
-        <v>46226.46875</v>
+        <v>46228.46875</v>
       </c>
       <c r="B47">
-        <v>21.309</v>
+        <v>50.17</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="2">
-        <v>46226.47916666666</v>
+        <v>46228.47916666666</v>
       </c>
       <c r="B48">
-        <v>24.696</v>
+        <v>20.441</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -1595,13 +1595,13 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="2">
-        <v>46226.48958333334</v>
+        <v>46228.48958333334</v>
       </c>
       <c r="B49">
         <v>0</v>
       </c>
       <c r="C49">
-        <v>8.541</v>
+        <v>5.894</v>
       </c>
       <c r="D49">
         <v>48</v>
@@ -1612,13 +1612,13 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="2">
-        <v>46226.5</v>
+        <v>46228.5</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>40.14</v>
       </c>
       <c r="C50">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>49</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="2">
-        <v>46226.51041666666</v>
+        <v>46228.51041666666</v>
       </c>
       <c r="B51">
-        <v>43.295</v>
+        <v>35.07</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="2">
-        <v>46226.52083333334</v>
+        <v>46228.52083333334</v>
       </c>
       <c r="B52">
-        <v>12.377</v>
+        <v>15.537</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="2">
-        <v>46226.53125</v>
+        <v>46228.53125</v>
       </c>
       <c r="B53">
-        <v>12.406</v>
+        <v>5.413</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="2">
-        <v>46226.54166666666</v>
+        <v>46228.54166666666</v>
       </c>
       <c r="B54">
-        <v>2.806</v>
+        <v>0.147</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1697,10 +1697,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="2">
-        <v>46226.55208333334</v>
+        <v>46228.55208333334</v>
       </c>
       <c r="B55">
-        <v>0.586</v>
+        <v>1.185</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="2">
-        <v>46226.5625</v>
+        <v>46228.5625</v>
       </c>
       <c r="B56">
-        <v>6.953</v>
+        <v>1.059</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1731,13 +1731,13 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="2">
-        <v>46226.57291666666</v>
+        <v>46228.57291666666</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>0.963</v>
       </c>
       <c r="C57">
-        <v>7.431</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>56</v>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="2">
-        <v>46226.58333333334</v>
+        <v>46228.58333333334</v>
       </c>
       <c r="B58">
-        <v>4.783</v>
+        <v>0.63</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -1765,13 +1765,13 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="2">
-        <v>46226.59375</v>
+        <v>46228.59375</v>
       </c>
       <c r="B59">
         <v>0</v>
       </c>
       <c r="C59">
-        <v>3.718</v>
+        <v>0.011</v>
       </c>
       <c r="D59">
         <v>58</v>
@@ -1782,13 +1782,13 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="2">
-        <v>46226.60416666666</v>
+        <v>46228.60416666666</v>
       </c>
       <c r="B60">
-        <v>2.337</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>3.407</v>
       </c>
       <c r="D60">
         <v>59</v>
@@ -1799,13 +1799,13 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="2">
-        <v>46226.61458333334</v>
+        <v>46228.61458333334</v>
       </c>
       <c r="B61">
         <v>0</v>
       </c>
       <c r="C61">
-        <v>2.037</v>
+        <v>27.094</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -1816,13 +1816,13 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="2">
-        <v>46226.625</v>
+        <v>46228.625</v>
       </c>
       <c r="B62">
-        <v>1.952</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>6.598</v>
       </c>
       <c r="D62">
         <v>61</v>
@@ -1833,13 +1833,13 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="2">
-        <v>46226.63541666666</v>
+        <v>46228.63541666666</v>
       </c>
       <c r="B63">
-        <v>6.297</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>4.713</v>
       </c>
       <c r="D63">
         <v>62</v>
@@ -1850,13 +1850,13 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="2">
-        <v>46226.64583333334</v>
+        <v>46228.64583333334</v>
       </c>
       <c r="B64">
-        <v>2.237</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>4.148</v>
       </c>
       <c r="D64">
         <v>63</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="2">
-        <v>46226.65625</v>
+        <v>46228.65625</v>
       </c>
       <c r="B65">
-        <v>18.624</v>
+        <v>3.182</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -1884,13 +1884,13 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="2">
-        <v>46226.66666666666</v>
+        <v>46228.66666666666</v>
       </c>
       <c r="B66">
         <v>0</v>
       </c>
       <c r="C66">
-        <v>2.042</v>
+        <v>6.225</v>
       </c>
       <c r="D66">
         <v>65</v>
@@ -1901,13 +1901,13 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="2">
-        <v>46226.67708333334</v>
+        <v>46228.67708333334</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>0.447</v>
+        <v>0.482</v>
       </c>
       <c r="D67">
         <v>66</v>
@@ -1918,13 +1918,13 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="2">
-        <v>46226.6875</v>
+        <v>46228.6875</v>
       </c>
       <c r="B68">
-        <v>0.806</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D68">
         <v>67</v>
@@ -1935,13 +1935,13 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="2">
-        <v>46226.69791666666</v>
+        <v>46228.69791666666</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>18.512</v>
       </c>
       <c r="C69">
-        <v>2.641</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>68</v>
@@ -1952,13 +1952,13 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="2">
-        <v>46226.70833333334</v>
+        <v>46228.70833333334</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>0.893</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D70">
         <v>69</v>
@@ -1969,13 +1969,13 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="2">
-        <v>46226.71875</v>
+        <v>46228.71875</v>
       </c>
       <c r="B71">
-        <v>10.236</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>14.174</v>
       </c>
       <c r="D71">
         <v>70</v>
@@ -1986,13 +1986,13 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="2">
-        <v>46226.72916666666</v>
+        <v>46228.72916666666</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72">
-        <v>0.503</v>
+        <v>10.939</v>
       </c>
       <c r="D72">
         <v>71</v>
@@ -2003,13 +2003,13 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="2">
-        <v>46226.73958333334</v>
+        <v>46228.73958333334</v>
       </c>
       <c r="B73">
-        <v>8.259</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="D73">
         <v>72</v>
@@ -2020,13 +2020,13 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="2">
-        <v>46226.75</v>
+        <v>46228.75</v>
       </c>
       <c r="B74">
         <v>0</v>
       </c>
       <c r="C74">
-        <v>11.024</v>
+        <v>3.048</v>
       </c>
       <c r="D74">
         <v>73</v>
@@ -2037,13 +2037,13 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="2">
-        <v>46226.76041666666</v>
+        <v>46228.76041666666</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>17.192</v>
+        <v>44.762</v>
       </c>
       <c r="D75">
         <v>74</v>
@@ -2054,13 +2054,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="2">
-        <v>46226.77083333334</v>
+        <v>46228.77083333334</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76">
-        <v>22.492</v>
+        <v>40.019</v>
       </c>
       <c r="D76">
         <v>75</v>
@@ -2071,13 +2071,13 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="2">
-        <v>46226.78125</v>
+        <v>46228.78125</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>20.623</v>
+        <v>35.65</v>
       </c>
       <c r="D77">
         <v>76</v>
@@ -2088,13 +2088,13 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="2">
-        <v>46226.79166666666</v>
+        <v>46228.79166666666</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>38.663</v>
+        <v>39.59</v>
       </c>
       <c r="D78">
         <v>77</v>
@@ -2105,13 +2105,13 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="2">
-        <v>46226.80208333334</v>
+        <v>46228.80208333334</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>20.448</v>
+        <v>51.176</v>
       </c>
       <c r="D79">
         <v>78</v>
@@ -2122,13 +2122,13 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="2">
-        <v>46226.8125</v>
+        <v>46228.8125</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>29.019</v>
+        <v>27.78</v>
       </c>
       <c r="D80">
         <v>79</v>
@@ -2139,13 +2139,13 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="2">
-        <v>46226.82291666666</v>
+        <v>46228.82291666666</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>14.5</v>
+        <v>18.184</v>
       </c>
       <c r="D81">
         <v>80</v>
@@ -2156,13 +2156,13 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="2">
-        <v>46226.83333333334</v>
+        <v>46228.83333333334</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>14.296</v>
+        <v>18.513</v>
       </c>
       <c r="D82">
         <v>81</v>
@@ -2173,13 +2173,13 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="2">
-        <v>46226.84375</v>
+        <v>46228.84375</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>8.228</v>
+        <v>17.111</v>
       </c>
       <c r="D83">
         <v>82</v>
@@ -2190,13 +2190,13 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="2">
-        <v>46226.85416666666</v>
+        <v>46228.85416666666</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>9.022</v>
+        <v>58.535</v>
       </c>
       <c r="D84">
         <v>83</v>
@@ -2207,13 +2207,13 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2">
-        <v>46226.86458333334</v>
+        <v>46228.86458333334</v>
       </c>
       <c r="B85">
-        <v>13.215</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>18.05</v>
       </c>
       <c r="D85">
         <v>84</v>
@@ -2224,13 +2224,13 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="2">
-        <v>46226.875</v>
+        <v>46228.875</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
       <c r="C86">
-        <v>4.866</v>
+        <v>14.744</v>
       </c>
       <c r="D86">
         <v>85</v>
@@ -2241,13 +2241,13 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="2">
-        <v>46226.88541666666</v>
+        <v>46228.88541666666</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>8.864000000000001</v>
+        <v>11.746</v>
       </c>
       <c r="D87">
         <v>86</v>
@@ -2258,13 +2258,13 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="2">
-        <v>46226.89583333334</v>
+        <v>46228.89583333334</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>8.727</v>
+        <v>26.313</v>
       </c>
       <c r="D88">
         <v>87</v>
@@ -2275,13 +2275,13 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="2">
-        <v>46226.90